--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2718,7 +2718,7 @@
         <v>WO0000000304977</v>
       </c>
       <c r="B290" s="1" t="d">
-        <v>2026-07-17T08:38:45.000Z</v>
+        <v>2026-07-21T06:23:00.000Z</v>
       </c>
     </row>
     <row r="291">
@@ -2822,7 +2822,7 @@
         <v>WO0000000305880</v>
       </c>
       <c r="B303" s="1" t="d">
-        <v>2026-07-17T14:18:27.000Z</v>
+        <v>2026-07-21T06:23:37.000Z</v>
       </c>
     </row>
     <row r="304">
@@ -3006,7 +3006,7 @@
         <v>WO0000000301822</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2026-07-14T09:17:36.000Z</v>
+        <v>2026-07-20T23:27:55.000Z</v>
       </c>
     </row>
     <row r="327">
@@ -3355,610 +3355,610 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>WO0000000306927</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B370" s="1" t="d">
-        <v>2026-07-17T13:46:00.000Z</v>
+        <v>2026-07-15T11:48:34.000Z</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>WO0000000306988</v>
+        <v>WO0000000307033</v>
       </c>
       <c r="B371" s="1" t="d">
-        <v>2026-07-15T11:48:34.000Z</v>
+        <v>2026-07-17T12:30:37.000Z</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>WO0000000307033</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B372" s="1" t="d">
-        <v>2026-07-17T12:30:37.000Z</v>
+        <v>2026-07-11T15:39:05.000Z</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000307106</v>
       </c>
       <c r="B373" s="1" t="d">
-        <v>2026-07-11T15:39:05.000Z</v>
+        <v>2026-07-11T16:22:34.000Z</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>WO0000000307106</v>
+        <v>WO0000000307233</v>
       </c>
       <c r="B374" s="1" t="d">
-        <v>2026-07-11T16:22:34.000Z</v>
+        <v>2026-07-17T14:47:15.000Z</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>WO0000000307233</v>
+        <v>WO0000000307093</v>
       </c>
       <c r="B375" s="1" t="d">
-        <v>2026-07-17T14:47:15.000Z</v>
+        <v>2026-07-14T07:58:26.000Z</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>WO0000000307093</v>
+        <v>WO0000000307237</v>
       </c>
       <c r="B376" s="1" t="d">
-        <v>2026-07-14T07:58:26.000Z</v>
+        <v>2026-07-14T08:00:43.999Z</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>WO0000000307237</v>
+        <v>INC000000151941</v>
       </c>
       <c r="B377" s="1" t="d">
-        <v>2026-07-14T08:00:43.999Z</v>
+        <v>2026-07-17T13:23:13.999Z</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>INC000000151941</v>
+        <v>WO0000000307368</v>
       </c>
       <c r="B378" s="1" t="d">
-        <v>2026-07-17T13:23:13.999Z</v>
+        <v>2026-07-17T09:56:32.000Z</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>WO0000000307368</v>
+        <v>WO0000000307397</v>
       </c>
       <c r="B379" s="1" t="d">
-        <v>2026-07-17T09:56:32.000Z</v>
+        <v>2026-07-15T09:56:22.000Z</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>WO0000000307397</v>
+        <v>WO0000000307437</v>
       </c>
       <c r="B380" s="1" t="d">
-        <v>2026-07-15T09:56:22.000Z</v>
+        <v>2026-07-16T15:04:48.999Z</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>WO0000000307437</v>
+        <v>WO0000000307471</v>
       </c>
       <c r="B381" s="1" t="d">
-        <v>2026-07-16T15:04:48.999Z</v>
+        <v>2026-07-14T11:13:57.999Z</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>WO0000000307471</v>
+        <v>WO0000000307482</v>
       </c>
       <c r="B382" s="1" t="d">
-        <v>2026-07-14T11:13:57.999Z</v>
+        <v>2026-07-14T13:21:57.000Z</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>WO0000000307482</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B383" s="1" t="d">
-        <v>2026-07-14T13:21:57.000Z</v>
+        <v>2026-07-14T12:23:50.000Z</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>WO0000000307624</v>
+        <v>INC000000152040</v>
       </c>
       <c r="B384" s="1" t="d">
-        <v>2026-07-14T12:23:50.000Z</v>
+        <v>2026-07-14T15:45:22.000Z</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>INC000000152040</v>
+        <v>WO0000000307592</v>
       </c>
       <c r="B385" s="1" t="d">
-        <v>2026-07-14T15:45:22.000Z</v>
+        <v>2026-07-17T13:37:57.000Z</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>WO0000000307592</v>
+        <v>INC000000152117</v>
       </c>
       <c r="B386" s="1" t="d">
-        <v>2026-07-17T13:37:57.000Z</v>
+        <v>2026-07-15T14:11:25.000Z</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>INC000000152117</v>
+        <v>WO0000000307667</v>
       </c>
       <c r="B387" s="1" t="d">
-        <v>2026-07-15T14:11:25.000Z</v>
+        <v>2026-07-17T09:40:12.000Z</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>WO0000000307667</v>
+        <v>WO0000000307671</v>
       </c>
       <c r="B388" s="1" t="d">
-        <v>2026-07-17T09:40:12.000Z</v>
+        <v>2026-07-17T09:44:19.000Z</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>WO0000000307671</v>
+        <v>INC000000152124</v>
       </c>
       <c r="B389" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-15T14:11:57.000Z</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>INC000000152124</v>
+        <v>WO0000000307701</v>
       </c>
       <c r="B390" s="1" t="d">
-        <v>2026-07-15T14:11:57.000Z</v>
+        <v>2026-07-17T09:50:26.000Z</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>WO0000000307701</v>
+        <v>INC000000152132</v>
       </c>
       <c r="B391" s="1" t="d">
-        <v>2026-07-17T09:50:26.000Z</v>
+        <v>2026-07-15T14:13:17.000Z</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>INC000000152132</v>
+        <v>INC000000152134</v>
       </c>
       <c r="B392" s="1" t="d">
-        <v>2026-07-15T14:13:17.000Z</v>
+        <v>2026-07-15T14:13:50.000Z</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>INC000000152134</v>
+        <v>INC000000152138</v>
       </c>
       <c r="B393" s="1" t="d">
-        <v>2026-07-15T14:13:50.000Z</v>
+        <v>2026-07-15T14:16:43.999Z</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>INC000000152138</v>
+        <v>INC000000152139</v>
       </c>
       <c r="B394" s="1" t="d">
-        <v>2026-07-15T14:16:43.999Z</v>
+        <v>2026-07-15T14:17:19.000Z</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>INC000000152139</v>
+        <v>WO0000000307733</v>
       </c>
       <c r="B395" s="1" t="d">
-        <v>2026-07-15T14:17:19.000Z</v>
+        <v>2026-07-17T11:13:13.999Z</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>WO0000000307733</v>
+        <v>WO0000000307735</v>
       </c>
       <c r="B396" s="1" t="d">
-        <v>2026-07-17T11:13:13.999Z</v>
+        <v>2026-07-17T08:55:02.999Z</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>WO0000000307735</v>
+        <v>WO0000000307812</v>
       </c>
       <c r="B397" s="1" t="d">
-        <v>2026-07-17T08:55:02.999Z</v>
+        <v>2026-07-17T09:11:25.000Z</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>WO0000000307812</v>
+        <v>WO0000000307820</v>
       </c>
       <c r="B398" s="1" t="d">
-        <v>2026-07-17T09:11:25.000Z</v>
+        <v>2026-07-17T16:33:17.000Z</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>WO0000000307820</v>
+        <v>INC000000152155</v>
       </c>
       <c r="B399" s="1" t="d">
-        <v>2026-07-17T16:33:17.000Z</v>
+        <v>2026-07-15T16:57:39.000Z</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>INC000000152155</v>
+        <v>INC000000152156</v>
       </c>
       <c r="B400" s="1" t="d">
-        <v>2026-07-15T16:57:39.000Z</v>
+        <v>2026-07-15T14:18:27.000Z</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>INC000000152156</v>
+        <v>INC000000152158</v>
       </c>
       <c r="B401" s="1" t="d">
-        <v>2026-07-15T14:18:27.000Z</v>
+        <v>2026-07-15T14:19:58.000Z</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>INC000000152158</v>
+        <v>WO0000000307834</v>
       </c>
       <c r="B402" s="1" t="d">
-        <v>2026-07-15T14:19:58.000Z</v>
+        <v>2026-07-17T10:16:56.000Z</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>WO0000000307834</v>
+        <v>WO0000000307769</v>
       </c>
       <c r="B403" s="1" t="d">
-        <v>2026-07-17T10:16:56.000Z</v>
+        <v>2026-07-14T17:17:47.000Z</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>WO0000000307769</v>
+        <v>WO0000000307852</v>
       </c>
       <c r="B404" s="1" t="d">
-        <v>2026-07-14T17:17:47.000Z</v>
+        <v>2026-07-17T12:30:37.999Z</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>WO0000000307852</v>
+        <v>WO0000000308004</v>
       </c>
       <c r="B405" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-17T10:04:39.999Z</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>WO0000000308004</v>
+        <v>INC000000152301</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2026-07-17T10:04:39.999Z</v>
+        <v>2026-07-15T14:37:10.000Z</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>INC000000152301</v>
+        <v>WO0000000308028</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2026-07-15T14:37:10.000Z</v>
+        <v>2026-07-17T13:50:01.000Z</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>WO0000000308028</v>
+        <v>INC000000152308</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2026-07-17T13:50:01.000Z</v>
+        <v>2026-07-16T09:37:19.000Z</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>INC000000152308</v>
+        <v>INC000000152320</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2026-07-16T09:37:19.000Z</v>
+        <v>2026-07-15T10:29:52.000Z</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>INC000000152320</v>
+        <v>WO0000000307976</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2026-07-15T10:29:52.000Z</v>
+        <v>2026-07-17T13:56:08.000Z</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>WO0000000307976</v>
+        <v>WO0000000307981</v>
       </c>
       <c r="B411" s="1" t="d">
-        <v>2026-07-17T13:56:08.000Z</v>
+        <v>2026-07-17T11:48:02.000Z</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>WO0000000307981</v>
+        <v>WO0000000307984</v>
       </c>
       <c r="B412" s="1" t="d">
-        <v>2026-07-17T11:48:02.000Z</v>
+        <v>2026-07-17T14:08:18.000Z</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>WO0000000307984</v>
+        <v>INC000000152339</v>
       </c>
       <c r="B413" s="1" t="d">
-        <v>2026-07-17T14:08:18.000Z</v>
+        <v>2026-07-16T08:34:04.000Z</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>INC000000152339</v>
+        <v>WO0000000308206</v>
       </c>
       <c r="B414" s="1" t="d">
-        <v>2026-07-16T08:34:04.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>WO0000000308206</v>
+        <v>WO0000000308218</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308218</v>
+        <v>WO0000000308157</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-17T13:56:08.000Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308157</v>
+        <v>WO0000000308163</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-17T13:56:08.000Z</v>
+        <v>2026-07-16T09:05:24.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>WO0000000308163</v>
+        <v>WO0000000308238</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-16T09:05:24.000Z</v>
+        <v>2026-07-17T14:30:48.000Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>WO0000000308238</v>
+        <v>WO0000000308240</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-17T14:30:48.000Z</v>
+        <v>2026-07-17T14:41:09.000Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308240</v>
+        <v>WO0000000308196</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-17T14:41:09.000Z</v>
+        <v>2026-07-17T14:51:24.000Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308196</v>
+        <v>WO0000000308194</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-17T14:51:24.000Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308194</v>
+        <v>WO0000000308255</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-17T15:17:47.000Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308255</v>
+        <v>WO0000000308260</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-17T15:17:47.000Z</v>
+        <v>2026-07-16T12:44:38.000Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308260</v>
+        <v>WO0000000308269</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-16T12:44:38.000Z</v>
+        <v>2026-07-16T12:15:01.000Z</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>WO0000000308269</v>
+        <v>WO0000000308273</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2026-07-16T12:15:01.000Z</v>
+        <v>2026-07-16T12:17:21.999Z</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>WO0000000308273</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2026-07-16T12:17:21.999Z</v>
+        <v>2026-07-16T23:19:07.000Z</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308331</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2026-07-16T23:19:07.000Z</v>
+        <v>2026-07-17T16:57:45.000Z</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>WO0000000308331</v>
+        <v>WO0000000308416</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2026-07-17T16:57:45.000Z</v>
+        <v>2026-07-16T09:47:42.999Z</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>WO0000000308416</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B429" s="1" t="d">
-        <v>2026-07-16T09:47:42.999Z</v>
+        <v>2026-07-17T10:42:18.999Z</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308432</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2026-07-17T10:42:18.999Z</v>
+        <v>2026-07-17T10:48:35.000Z</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>WO0000000308432</v>
+        <v>WO0000000308350</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-17T10:48:35.000Z</v>
+        <v>2026-07-17T10:54:45.999Z</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>WO0000000308350</v>
+        <v>WO0000000308345</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-17T10:54:45.999Z</v>
+        <v>2026-07-17T10:58:53.999Z</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>WO0000000308345</v>
+        <v>WO0000000308442</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-17T10:58:53.999Z</v>
+        <v>2026-07-17T14:15:20.000Z</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>WO0000000308442</v>
+        <v>WO0000000308360</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-17T14:15:20.000Z</v>
+        <v>2026-07-16T12:54:40.000Z</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>WO0000000308360</v>
+        <v>WO0000000308457</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2026-07-16T12:54:40.000Z</v>
+        <v>2026-07-17T11:44:00.000Z</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>WO0000000308457</v>
+        <v>WO0000000308463</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-17T11:44:00.000Z</v>
+        <v>2026-07-17T11:56:09.000Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>WO0000000308463</v>
+        <v>WO0000000308374</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-17T11:56:09.000Z</v>
+        <v>2026-07-17T12:10:22.000Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>WO0000000308374</v>
+        <v>WO0000000308379</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-17T12:10:22.000Z</v>
+        <v>2026-07-15T17:07:55.000Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>WO0000000308379</v>
+        <v>INC000000152289</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-15T17:07:55.000Z</v>
+        <v>2026-07-17T09:12:44.999Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>INC000000152289</v>
+        <v>WO0000000308383</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-17T09:12:44.999Z</v>
+        <v>2026-07-17T12:30:39.000Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000308383</v>
+        <v>WO0000000308483</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-17T12:30:39.000Z</v>
+        <v>2026-07-17T14:45:22.999Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>WO0000000308483</v>
+        <v>WO0000000308398</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-17T14:45:22.999Z</v>
+        <v>2026-07-16T08:57:27.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000308398</v>
+        <v>WO0000000308399</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-16T08:57:27.000Z</v>
+        <v>2026-07-16T09:52:14.999Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>WO0000000308399</v>
+        <v>WO0000000308487</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-16T09:52:14.999Z</v>
+        <v>2026-07-15T22:21:47.000Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>WO0000000308487</v>
+        <v>WO0000000308493</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-15T22:21:47.000Z</v>
+        <v>2026-07-17T12:30:42.000Z</v>
       </c>
     </row>
     <row r="446">
@@ -4150,7 +4150,7 @@
         <v>WO0000000298838</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-17T14:59:34.000Z</v>
+        <v>2026-07-20T23:28:38.000Z</v>
       </c>
     </row>
     <row r="470">
@@ -4563,679 +4563,679 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-17T17:20:58.999Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>WO0000000306877</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-16T14:55:04.000Z</v>
+        <v>2026-07-17T17:20:58.999Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>WO0000000306890</v>
+        <v>WO0000000306877</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-16T14:55:04.000Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>WO0000000306899</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-17T17:44:23.000Z</v>
+        <v>2026-07-17T14:42:13.999Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000306992</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-16T10:42:09.000Z</v>
+        <v>2026-07-17T17:44:23.000Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000306994</v>
+        <v>WO0000000306992</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-16T15:19:33.999Z</v>
+        <v>2026-07-16T10:42:09.000Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>INC000000151586</v>
+        <v>WO0000000306994</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-19T12:57:49.000Z</v>
+        <v>2026-07-16T15:19:33.999Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>WO0000000307224</v>
+        <v>INC000000151586</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-16T16:04:39.999Z</v>
+        <v>2026-07-19T12:57:49.000Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000307224</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-17T14:49:17.000Z</v>
+        <v>2026-07-16T16:04:39.999Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>INC000000151950</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-16T09:20:32.000Z</v>
+        <v>2026-07-17T14:49:17.000Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>INC000000151764</v>
+        <v>INC000000151950</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-16T10:00:04.000Z</v>
+        <v>2026-07-16T09:20:32.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>WO0000000307337</v>
+        <v>INC000000151764</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-16T12:37:35.999Z</v>
+        <v>2026-07-16T10:00:04.000Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>INC000000151965</v>
+        <v>WO0000000307337</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-17T17:01:15.000Z</v>
+        <v>2026-07-16T12:37:35.999Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>WO0000000307513</v>
+        <v>INC000000151965</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-17T09:03:17.000Z</v>
+        <v>2026-07-17T17:01:15.000Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-17T09:03:17.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>INC000000151987</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-16T11:05:28.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>WO0000000307483</v>
+        <v>INC000000151987</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-17T14:43:30.000Z</v>
+        <v>2026-07-16T11:05:28.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>INC000000151994</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-16T07:51:15.000Z</v>
+        <v>2026-07-17T14:43:30.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>WO0000000307604</v>
+        <v>INC000000151994</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-17T14:02:15.000Z</v>
+        <v>2026-07-16T07:51:15.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-17T16:21:08.000Z</v>
+        <v>2026-07-17T14:02:15.000Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>INC000000152000</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-19T12:58:45.000Z</v>
+        <v>2026-07-17T16:21:08.000Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000152000</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-19T12:58:45.000Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>WO0000000307636</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-17T17:21:42.000Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>INC000000152045</v>
+        <v>WO0000000307636</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-16T10:52:09.000Z</v>
+        <v>2026-07-20T22:08:00.000Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>WO0000000307665</v>
+        <v>INC000000152045</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-16T11:24:53.999Z</v>
+        <v>2026-07-16T10:52:09.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000307669</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-16T11:24:53.999Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000307669</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-17T17:21:00.000Z</v>
+        <v>2026-07-17T09:44:19.000Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>WO0000000307725</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-17T15:11:48.000Z</v>
+        <v>2026-07-17T17:21:00.000Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>WO0000000307729</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-16T12:57:39.999Z</v>
+        <v>2026-07-17T15:11:48.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>INC000000152145</v>
+        <v>WO0000000307729</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-17T19:20:59.000Z</v>
+        <v>2026-07-16T12:57:39.999Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>INC000000152073</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-16T09:23:53.000Z</v>
+        <v>2026-07-17T19:20:59.000Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000307923</v>
+        <v>INC000000152073</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-16T09:23:33.000Z</v>
+        <v>2026-07-16T09:23:53.000Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>WO0000000307940</v>
+        <v>WO0000000307923</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-16T09:23:33.000Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>WO0000000307963</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-17T13:31:54.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308029</v>
+        <v>WO0000000307963</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-17T16:02:10.000Z</v>
+        <v>2026-07-17T13:31:54.000Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>INC000000152212</v>
+        <v>WO0000000308029</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-17T16:02:10.000Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>WO0000000308038</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-17T13:48:01.000Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>WO0000000308040</v>
+        <v>WO0000000308038</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-17T13:48:01.000Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>WO0000000307968</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-16T15:02:29.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000307970</v>
+        <v>WO0000000307968</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-16T16:55:20.000Z</v>
+        <v>2026-07-16T15:02:29.000Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>WO0000000308041</v>
+        <v>WO0000000307970</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-17T09:02:42.000Z</v>
+        <v>2026-07-16T16:55:20.000Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>WO0000000308042</v>
+        <v>WO0000000308041</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-17T15:12:03.000Z</v>
+        <v>2026-07-17T09:02:42.000Z</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-20T23:34:20.999Z</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>WO0000000308052</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-07-17T11:04:48.999Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-17T11:04:48.999Z</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>WO0000000308105</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-07-17T15:12:13.999Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>INC000000152328</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-07-17T21:19:20.000Z</v>
+        <v>2026-07-20T23:29:29.999Z</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>WO0000000308075</v>
+        <v>INC000000152328</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-07-17T12:22:31.000Z</v>
+        <v>2026-07-17T21:19:20.000Z</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>WO0000000308106</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-07-17T15:12:30.000Z</v>
+        <v>2026-07-20T23:26:07.000Z</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>WO0000000308107</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-07-17T12:28:36.999Z</v>
+        <v>2026-07-20T23:30:10.000Z</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000308107</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-07-17T15:13:13.000Z</v>
+        <v>2026-07-20T23:27:09.999Z</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>WO0000000308086</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-07-17T14:44:25.000Z</v>
+        <v>2026-07-20T23:31:09.999Z</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>WO0000000308081</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-07-17T13:13:26.999Z</v>
+        <v>2026-07-17T14:44:25.000Z</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>WO0000000308215</v>
+        <v>WO0000000308081</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-07-17T09:26:37.000Z</v>
+        <v>2026-07-17T13:13:26.999Z</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>WO0000000308216</v>
+        <v>WO0000000308215</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-07-17T13:19:29.000Z</v>
+        <v>2026-07-17T09:26:37.000Z</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000308216</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-17T13:19:29.000Z</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-07-18T12:28:17.000Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>INC000000152358</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-07-16T09:12:05.999Z</v>
+        <v>2026-07-18T12:28:17.000Z</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>WO0000000308169</v>
+        <v>INC000000152358</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-17T14:18:27.000Z</v>
+        <v>2026-07-16T09:12:05.999Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>WO0000000308234</v>
+        <v>WO0000000308169</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-19T12:53:47.000Z</v>
+        <v>2026-07-17T14:18:27.000Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>INC000000152251</v>
+        <v>WO0000000308234</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-17T10:26:36.999Z</v>
+        <v>2026-07-19T12:53:47.000Z</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>INC000000152361</v>
+        <v>INC000000152251</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-07-17T16:39:09.000Z</v>
+        <v>2026-07-17T10:26:36.999Z</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>WO0000000308197</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-17T12:34:20.000Z</v>
+        <v>2026-07-17T16:39:09.000Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>WO0000000308249</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-17T13:34:27.999Z</v>
+        <v>2026-07-17T12:34:20.000Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>WO0000000308199</v>
+        <v>WO0000000308249</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-17T13:37:19.000Z</v>
+        <v>2026-07-17T13:34:27.999Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>INC000000152369</v>
+        <v>WO0000000308199</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-17T10:42:03.000Z</v>
+        <v>2026-07-17T13:37:19.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>WO0000000308306</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-07-18T09:01:38.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-18T12:40:57.999Z</v>
+        <v>2026-07-18T09:01:38.000Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>WO0000000308284</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-16T08:08:24.000Z</v>
+        <v>2026-07-18T12:40:57.999Z</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>INC000000152378</v>
+        <v>WO0000000308284</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-07-17T09:05:30.000Z</v>
+        <v>2026-07-16T08:08:24.000Z</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>INC000000152262</v>
+        <v>INC000000152378</v>
       </c>
       <c r="B592" s="1" t="d">
-        <v>2026-07-19T07:36:53.000Z</v>
+        <v>2026-07-17T09:05:30.000Z</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>WO0000000308340</v>
+        <v>INC000000152262</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-07-16T09:24:24.999Z</v>
+        <v>2026-07-19T07:36:53.000Z</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308340</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-07-18T12:08:23.000Z</v>
+        <v>2026-07-16T09:24:24.999Z</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>WO0000000308422</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B595" s="1" t="d">
-        <v>2026-07-17T14:57:31.000Z</v>
+        <v>2026-07-18T12:08:23.000Z</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>WO0000000308426</v>
+        <v>WO0000000308422</v>
       </c>
       <c r="B596" s="1" t="d">
-        <v>2026-07-17T14:48:38.000Z</v>
+        <v>2026-07-17T14:57:31.000Z</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>WO0000000308357</v>
+        <v>WO0000000308426</v>
       </c>
       <c r="B597" s="1" t="d">
-        <v>2026-07-17T15:33:19.999Z</v>
+        <v>2026-07-17T14:48:38.000Z</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308357</v>
       </c>
       <c r="B598" s="1" t="d">
-        <v>2026-07-16T10:44:20.999Z</v>
+        <v>2026-07-17T15:33:19.999Z</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>INC000000152389</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B599" s="1" t="d">
-        <v>2026-07-17T10:53:19.000Z</v>
+        <v>2026-07-16T10:44:20.999Z</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>WO0000000308366</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-07-16T09:45:50.999Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>WO0000000308461</v>
+        <v>WO0000000308366</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-16T18:43:27.999Z</v>
+        <v>2026-07-16T09:45:50.999Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>WO0000000308475</v>
+        <v>WO0000000308461</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-16T18:43:27.999Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>WO0000000308478</v>
+        <v>WO0000000308475</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-17T12:30:39.000Z</v>
+        <v>2026-07-17T12:30:37.999Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>WO0000000308382</v>
+        <v>WO0000000308478</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-17T12:30:40.000Z</v>
+        <v>2026-07-17T12:30:39.000Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000308380</v>
+        <v>WO0000000308382</v>
       </c>
       <c r="B605" s="1" t="d">
         <v>2026-07-17T12:30:40.000Z</v>
@@ -5243,34 +5243,34 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>WO0000000308396</v>
+        <v>WO0000000308380</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-17T12:30:41.000Z</v>
+        <v>2026-07-17T12:30:40.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>WO0000000308503</v>
+        <v>WO0000000308396</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-16T07:14:29.000Z</v>
+        <v>2026-07-17T12:30:41.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>INC000000152417</v>
+        <v>WO0000000308503</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-17T17:20:56.999Z</v>
+        <v>2026-07-16T07:14:29.000Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>WO0000000308493</v>
+        <v>INC000000152417</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-17T12:30:42.000Z</v>
+        <v>2026-07-17T17:20:56.999Z</v>
       </c>
     </row>
     <row r="610">
@@ -6619,3284 +6619,3420 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>WO0000000309127</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-17T09:53:39.000Z</v>
+        <v>2026-07-17T08:07:23.000Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309131</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-17T08:07:23.000Z</v>
+        <v>2026-07-17T08:12:37.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>WO0000000309131</v>
+        <v>WO0000000309212</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-17T08:12:37.000Z</v>
+        <v>2026-07-17T15:11:51.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000309212</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-17T15:11:51.000Z</v>
+        <v>2026-07-17T08:53:07.999Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309136</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-17T08:53:07.999Z</v>
+        <v>2026-07-17T11:36:59.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-17T11:36:59.000Z</v>
+        <v>2026-07-17T12:44:26.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>INC000000152663</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-17T12:44:26.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>INC000000152664</v>
+        <v>WO0000000309216</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T14:47:41.000Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000309216</v>
+        <v>INC000000152746</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-17T14:47:41.000Z</v>
+        <v>2026-07-17T10:32:57.999Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>INC000000152746</v>
+        <v>WO0000000309153</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-17T10:32:57.999Z</v>
+        <v>2026-07-17T09:57:37.000Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>WO0000000309153</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-17T09:57:37.000Z</v>
+        <v>2026-07-17T08:54:14.000Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-17T08:54:14.000Z</v>
+        <v>2026-07-17T08:54:36.999Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>WO0000000309155</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-17T08:54:36.999Z</v>
+        <v>2026-07-18T12:40:15.000Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>INC000000152668</v>
+        <v>WO0000000309226</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-18T12:40:15.000Z</v>
+        <v>2026-07-17T08:58:32.999Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>WO0000000309226</v>
+        <v>INC000000152671</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-17T08:58:32.999Z</v>
+        <v>2026-07-17T10:24:28.999Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>INC000000152671</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-17T10:24:28.999Z</v>
+        <v>2026-07-17T14:29:04.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>WO0000000309231</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-17T14:29:04.000Z</v>
+        <v>2026-07-17T09:57:18.999Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>WO0000000309232</v>
+        <v>INC000000152673</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-17T09:52:29.000Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>INC000000152673</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-17T09:52:29.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309161</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-17T09:22:10.000Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>WO0000000309161</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-17T09:22:10.000Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000309162</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>INC000000152674</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-17T14:47:59.000Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>WO0000000309164</v>
+        <v>WO0000000309237</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-17T14:47:59.000Z</v>
+        <v>2026-07-17T09:24:26.999Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000309237</v>
+        <v>INC000000152758</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-17T09:24:26.999Z</v>
+        <v>2026-07-17T18:54:02.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>INC000000152758</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-17T18:54:02.000Z</v>
+        <v>2026-07-17T09:26:58.999Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>WO0000000309241</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-17T09:26:58.999Z</v>
+        <v>2026-07-17T12:06:25.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>INC000000152678</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-17T12:06:25.000Z</v>
+        <v>2026-07-17T15:50:55.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>INC000000152679</v>
+        <v>WO0000000309246</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-17T15:50:55.000Z</v>
+        <v>2026-07-17T09:32:32.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>WO0000000309246</v>
+        <v>WO0000000309167</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-17T09:32:32.000Z</v>
+        <v>2026-07-17T14:49:27.000Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>WO0000000309167</v>
+        <v>INC000000152761</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-17T14:49:27.000Z</v>
+        <v>2026-07-17T10:05:32.000Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>INC000000152761</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-17T10:05:32.000Z</v>
+        <v>2026-07-17T09:36:30.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>WO0000000309168</v>
+        <v>INC000000152682</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-17T09:36:30.000Z</v>
+        <v>2026-07-17T15:16:50.000Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>INC000000152682</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-17T15:16:50.000Z</v>
+        <v>2026-07-17T09:37:50.000Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-17T09:37:50.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>WO0000000309172</v>
+        <v>WO0000000309249</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-17T09:38:10.000Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>WO0000000309249</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-17T09:54:11.000Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000309250</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-17T09:54:11.000Z</v>
+        <v>2026-07-17T09:43:19.000Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>INC000000152760</v>
+        <v>WO0000000309251</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-17T09:43:19.000Z</v>
+        <v>2026-07-17T09:40:19.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>WO0000000309251</v>
+        <v>INC000000152763</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-17T09:40:19.000Z</v>
+        <v>2026-07-17T10:09:48.000Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>INC000000152763</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-17T10:09:48.000Z</v>
+        <v>2026-07-17T11:30:54.000Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-17T11:30:54.000Z</v>
+        <v>2026-07-17T09:57:50.000Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-17T09:57:50.000Z</v>
+        <v>2026-07-17T11:14:20.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-17T11:14:20.000Z</v>
+        <v>2026-07-17T14:47:53.999Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000309183</v>
+        <v>INC000000152686</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-17T14:47:53.999Z</v>
+        <v>2026-07-17T15:19:55.000Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>INC000000152686</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-17T15:19:55.000Z</v>
+        <v>2026-07-17T11:11:39.000Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-17T11:11:39.000Z</v>
+        <v>2026-07-17T11:15:36.000Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>WO0000000309189</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-17T11:15:36.000Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>WO0000000309258</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-17T11:13:13.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>WO0000000309259</v>
+        <v>INC000000152688</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-17T11:13:13.000Z</v>
+        <v>2026-07-17T17:24:17.000Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>INC000000152688</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-17T17:24:17.000Z</v>
+        <v>2026-07-17T15:17:55.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>INC000000152768</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-17T15:17:55.000Z</v>
+        <v>2026-07-17T10:18:38.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>WO0000000309262</v>
+        <v>WO0000000309263</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-17T10:18:38.000Z</v>
+        <v>2026-07-17T10:19:46.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>WO0000000309263</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-17T10:19:46.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>INC000000152690</v>
+        <v>INC000000152770</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-17T10:27:03.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>INC000000152770</v>
+        <v>WO0000000305263</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-17T10:27:03.000Z</v>
+        <v>2026-07-17T15:28:33.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000305263</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-17T15:28:33.000Z</v>
+        <v>2026-07-17T11:24:41.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>WO0000000309195</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-17T11:24:41.000Z</v>
+        <v>2026-07-17T10:29:44.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>INC000000152772</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-17T10:29:44.000Z</v>
+        <v>2026-07-17T11:25:20.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152691</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-17T11:25:20.000Z</v>
+        <v>2026-07-17T11:21:16.000Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>INC000000152691</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-17T11:21:16.000Z</v>
+        <v>2026-07-17T12:51:35.000Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000309199</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-17T12:51:35.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000309200</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309269</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-17T11:19:32.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000309269</v>
+        <v>WO0000000309270</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-17T11:19:32.000Z</v>
+        <v>2026-07-17T16:48:27.000Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>WO0000000309270</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-17T16:48:27.000Z</v>
+        <v>2026-07-17T14:48:08.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000309271</v>
+        <v>WO0000000309274</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-17T14:48:08.000Z</v>
+        <v>2026-07-17T10:47:30.000Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000309274</v>
+        <v>INC000000152694</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-17T10:47:30.000Z</v>
+        <v>2026-07-18T13:02:06.999Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>INC000000152694</v>
+        <v>WO0000000309407</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-18T13:02:06.999Z</v>
+        <v>2026-07-17T10:43:38.999Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000309407</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-19T12:51:55.999Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>INC000000152777</v>
+        <v>INC000000152778</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-19T12:51:55.999Z</v>
+        <v>2026-07-17T14:11:44.000Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>INC000000152778</v>
+        <v>WO0000000309409</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-17T14:11:44.000Z</v>
+        <v>2026-07-17T11:23:02.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>WO0000000309409</v>
+        <v>WO0000000309277</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-17T11:23:02.000Z</v>
+        <v>2026-07-17T10:50:48.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000309277</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-17T10:50:48.000Z</v>
+        <v>2026-07-17T13:01:11.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-17T13:01:11.000Z</v>
+        <v>2026-07-17T10:48:35.999Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-17T10:48:35.999Z</v>
+        <v>2026-07-17T10:53:18.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-17T10:53:18.000Z</v>
+        <v>2026-07-17T12:28:53.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-17T12:28:53.000Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>WO0000000309282</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-17T10:58:23.000Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309285</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-17T10:58:23.000Z</v>
+        <v>2026-07-17T10:57:51.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>WO0000000309285</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-17T10:57:51.000Z</v>
+        <v>2026-07-17T11:48:14.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>INC000000152802</v>
+        <v>INC000000152782</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-17T11:48:14.000Z</v>
+        <v>2026-07-17T11:46:20.999Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>INC000000152782</v>
+        <v>WO0000000309417</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-17T11:46:20.999Z</v>
+        <v>2026-07-17T11:02:34.000Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>WO0000000309417</v>
+        <v>INC000000152700</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-17T11:02:34.000Z</v>
+        <v>2026-07-17T18:10:18.000Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>INC000000152700</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-17T18:10:18.000Z</v>
+        <v>2026-07-18T08:52:20.999Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-18T08:52:20.999Z</v>
+        <v>2026-07-17T11:12:43.000Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309291</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-17T11:12:43.000Z</v>
+        <v>2026-07-17T11:55:44.999Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>WO0000000309291</v>
+        <v>INC000000152784</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-17T11:55:44.999Z</v>
+        <v>2026-07-17T11:26:12.000Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>INC000000152784</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-17T11:26:12.000Z</v>
+        <v>2026-07-17T11:15:48.000Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-17T11:15:48.000Z</v>
+        <v>2026-07-17T11:17:12.999Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-17T11:17:12.999Z</v>
+        <v>2026-07-17T14:48:17.000Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309429</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-17T14:48:17.000Z</v>
+        <v>2026-07-17T12:07:50.999Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>WO0000000309429</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-17T12:07:50.999Z</v>
+        <v>2026-07-17T11:21:58.000Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309297</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-17T11:21:58.000Z</v>
+        <v>2026-07-17T11:30:58.000Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000309297</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-17T11:30:58.000Z</v>
+        <v>2026-07-17T11:50:50.000Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309432</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-17T11:50:50.000Z</v>
+        <v>2026-07-17T11:29:50.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>WO0000000309432</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-17T11:29:50.000Z</v>
+        <v>2026-07-17T11:26:05.999Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000309433</v>
+        <v>WO0000000309299</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-17T11:26:05.999Z</v>
+        <v>2026-07-17T11:28:13.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>WO0000000309299</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-17T11:28:13.000Z</v>
+        <v>2026-07-17T11:29:56.000Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-17T11:29:56.000Z</v>
+        <v>2026-07-17T16:49:37.000Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>WO0000000309438</v>
+        <v>WO0000000309439</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-17T16:49:37.000Z</v>
+        <v>2026-07-17T11:59:55.999Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>WO0000000309439</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-17T11:59:55.999Z</v>
+        <v>2026-07-17T15:38:05.000Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>WO0000000309503</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-17T15:38:05.000Z</v>
+        <v>2026-07-17T12:04:35.000Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>INC000000152789</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-17T12:04:35.000Z</v>
+        <v>2026-07-18T12:02:37.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-18T12:02:37.000Z</v>
+        <v>2026-07-17T11:41:41.000Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-17T11:41:41.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309504</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-17T11:39:29.000Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>WO0000000309504</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-17T11:39:29.000Z</v>
+        <v>2026-07-17T15:32:46.000Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000309441</v>
+        <v>WO0000000309444</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-17T15:32:46.000Z</v>
+        <v>2026-07-17T11:41:48.000Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>WO0000000309444</v>
+        <v>WO0000000309445</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-17T11:41:48.000Z</v>
+        <v>2026-07-18T00:08:12.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000309445</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-18T00:08:12.000Z</v>
+        <v>2026-07-17T11:44:22.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>WO0000000309447</v>
+        <v>WO0000000309508</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-17T11:44:22.000Z</v>
+        <v>2026-07-17T12:00:28.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>WO0000000309508</v>
+        <v>INC000000152810</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-17T12:00:28.000Z</v>
+        <v>2026-07-17T11:54:26.000Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>INC000000152810</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-17T11:54:26.000Z</v>
+        <v>2026-07-17T11:53:25.999Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-17T11:53:25.999Z</v>
+        <v>2026-07-17T12:07:06.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309510</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-17T12:07:06.000Z</v>
+        <v>2026-07-17T11:57:19.000Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000309510</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-17T11:57:19.000Z</v>
+        <v>2026-07-17T11:55:31.000Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-17T11:55:31.000Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>WO0000000309513</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T14:48:03.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-17T14:48:03.000Z</v>
+        <v>2026-07-17T15:45:57.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-17T15:45:57.000Z</v>
+        <v>2026-07-17T14:48:13.000Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>WO0000000309457</v>
+        <v>INC000000152797</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-17T14:48:13.000Z</v>
+        <v>2026-07-17T12:08:01.000Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>INC000000152797</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-17T12:08:01.000Z</v>
+        <v>2026-07-18T08:52:31.000Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-18T08:52:31.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>WO0000000309514</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>WO0000000309462</v>
+        <v>INC000000152800</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-21T06:37:05.999Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>INC000000152800</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-17T17:51:22.000Z</v>
+        <v>2026-07-17T12:23:35.999Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>WO0000000309465</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-17T12:23:35.999Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000309520</v>
+        <v>INC000000152901</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-17T12:30:00.000Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>INC000000152901</v>
+        <v>WO0000000309466</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-17T12:30:00.000Z</v>
+        <v>2026-07-17T12:32:56.000Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>WO0000000309466</v>
+        <v>INC000000152813</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-17T12:32:56.000Z</v>
+        <v>2026-07-17T12:36:17.000Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>INC000000152813</v>
+        <v>WO0000000309525</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-17T12:36:17.000Z</v>
+        <v>2026-07-17T16:15:45.000Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>WO0000000309525</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-17T16:15:45.000Z</v>
+        <v>2026-07-17T17:44:41.000Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>INC000000152903</v>
+        <v>WO0000000309526</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-17T17:44:41.000Z</v>
+        <v>2026-07-17T12:32:38.999Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>WO0000000309526</v>
+        <v>WO0000000309527</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-17T12:32:38.999Z</v>
+        <v>2026-07-17T12:41:12.999Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>WO0000000309527</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-17T12:41:12.999Z</v>
+        <v>2026-07-18T06:53:07.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000309470</v>
+        <v>INC000000152814</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-18T06:53:07.000Z</v>
+        <v>2026-07-17T12:49:52.000Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>INC000000152814</v>
+        <v>WO0000000309530</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-17T12:49:52.000Z</v>
+        <v>2026-07-17T12:49:35.999Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>WO0000000309530</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-17T12:49:35.999Z</v>
+        <v>2026-07-20T13:33:22.000Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309478</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-20T13:33:22.000Z</v>
+        <v>2026-07-17T15:55:47.000Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>WO0000000309478</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-17T15:55:47.000Z</v>
+        <v>2026-07-17T12:55:06.999Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309534</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-17T12:55:06.999Z</v>
+        <v>2026-07-17T13:00:45.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>WO0000000309534</v>
+        <v>INC000000152910</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-17T13:00:45.000Z</v>
+        <v>2026-07-17T13:05:26.000Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>INC000000152910</v>
+        <v>INC000000152911</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-17T13:05:26.000Z</v>
+        <v>2026-07-17T15:06:03.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>INC000000152911</v>
+        <v>WO0000000309485</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-17T15:06:03.000Z</v>
+        <v>2026-07-17T14:01:24.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>WO0000000309485</v>
+        <v>INC000000152815</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-17T14:01:24.000Z</v>
+        <v>2026-07-17T21:20:43.999Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>INC000000152815</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-17T21:20:43.999Z</v>
+        <v>2026-07-17T15:49:27.999Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>WO0000000309489</v>
+        <v>WO0000000309488</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-17T15:49:27.999Z</v>
+        <v>2026-07-17T13:20:57.999Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>WO0000000309488</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-17T13:20:57.999Z</v>
+        <v>2026-07-17T16:18:10.000Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>INC000000152914</v>
+        <v>WO0000000309541</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-17T16:18:10.000Z</v>
+        <v>2026-07-17T13:27:09.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>WO0000000309541</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-17T13:27:09.000Z</v>
+        <v>2026-07-18T01:16:50.999Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>INC000000152913</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-18T01:16:50.999Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>WO0000000309487</v>
+        <v>INC000000152817</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-17T14:36:59.999Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>INC000000152817</v>
+        <v>INC000000152915</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-17T14:36:59.999Z</v>
+        <v>2026-07-18T12:02:15.999Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>INC000000152915</v>
+        <v>WO0000000309495</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-18T12:02:15.999Z</v>
+        <v>2026-07-17T14:05:25.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>WO0000000309495</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-17T14:05:25.000Z</v>
+        <v>2026-07-17T14:58:42.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>WO0000000309497</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-17T14:58:42.000Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>WO0000000309499</v>
+        <v>WO0000000309545</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-17T14:10:05.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>WO0000000309545</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-17T14:10:05.000Z</v>
+        <v>2026-07-18T01:16:05.000Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>INC000000152919</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-18T01:16:05.000Z</v>
+        <v>2026-07-17T14:11:39.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>WO0000000309546</v>
+        <v>WO0000000309602</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-17T14:16:24.999Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>WO0000000309602</v>
+        <v>INC000000152823</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-17T14:16:24.999Z</v>
+        <v>2026-07-17T15:08:26.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>INC000000152823</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-17T15:08:26.000Z</v>
+        <v>2026-07-20T13:35:30.999Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>INC000000152824</v>
+        <v>WO0000000309548</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-20T13:35:30.999Z</v>
+        <v>2026-07-17T16:40:14.000Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>WO0000000309548</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-17T16:40:14.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>INC000000152921</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T15:55:02.000Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>WO0000000309603</v>
+        <v>INC000000152923</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-17T15:55:02.000Z</v>
+        <v>2026-07-17T15:07:33.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>INC000000152923</v>
+        <v>INC000000152825</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-17T15:07:33.000Z</v>
+        <v>2026-07-17T15:07:59.000Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>INC000000152825</v>
+        <v>WO0000000309604</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-17T15:07:59.000Z</v>
+        <v>2026-07-17T14:28:20.000Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>WO0000000309604</v>
+        <v>INC000000152922</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-17T14:28:20.000Z</v>
+        <v>2026-07-17T15:59:00.999Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>INC000000152922</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-17T15:59:00.999Z</v>
+        <v>2026-07-17T14:30:26.000Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>WO0000000309549</v>
+        <v>INC000000152827</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-17T14:30:26.000Z</v>
+        <v>2026-07-20T13:32:44.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>INC000000152827</v>
+        <v>INC000000152828</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-20T13:32:44.000Z</v>
+        <v>2026-07-17T14:45:48.000Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>INC000000152828</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-17T14:45:48.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>WO0000000309551</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-19T00:08:20.000Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>WO0000000309609</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-19T00:08:20.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>WO0000000309553</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-17T14:57:05.000Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309611</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-17T14:57:05.000Z</v>
+        <v>2026-07-17T16:36:16.000Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>WO0000000309611</v>
+        <v>INC000000152927</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-17T16:36:16.000Z</v>
+        <v>2026-07-17T15:58:26.000Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>INC000000152927</v>
+        <v>WO0000000309613</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-17T15:58:26.000Z</v>
+        <v>2026-07-17T15:01:59.000Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>WO0000000309613</v>
+        <v>INC000000152928</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-17T15:01:59.000Z</v>
+        <v>2026-07-21T06:26:41.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>INC000000152928</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-17T15:08:09.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309559</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-17T15:56:29.000Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000309559</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-17T15:56:29.000Z</v>
+        <v>2026-07-18T08:45:42.000Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-18T08:45:42.000Z</v>
+        <v>2026-07-17T15:57:48.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>WO0000000309616</v>
+        <v>INC000000152931</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-17T15:57:48.000Z</v>
+        <v>2026-07-17T15:23:52.000Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-17T15:23:52.000Z</v>
+        <v>2026-07-17T15:20:43.999Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309563</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-17T15:24:26.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>WO0000000309563</v>
+        <v>WO0000000309304</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-18T00:01:48.000Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>WO0000000309304</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-18T00:01:48.000Z</v>
+        <v>2026-07-18T11:14:25.000Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>INC000000152933</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-18T11:14:25.000Z</v>
+        <v>2026-07-17T16:04:00.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-17T16:04:00.000Z</v>
+        <v>2026-07-17T15:31:50.999Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309572</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-17T15:33:17.000Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>WO0000000309572</v>
+        <v>INC000000152932</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-17T15:33:17.000Z</v>
+        <v>2026-07-17T15:45:07.999Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>INC000000152932</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-17T15:45:07.999Z</v>
+        <v>2026-07-17T16:09:55.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-17T16:09:55.000Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>WO0000000309574</v>
+        <v>INC000000152934</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-18T06:07:51.999Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>INC000000152934</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-18T06:07:51.999Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-17T16:15:16.000Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-17T16:15:16.000Z</v>
+        <v>2026-07-17T16:20:48.000Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>WO0000000309626</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-17T16:20:48.000Z</v>
+        <v>2026-07-17T16:25:00.000Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>WO0000000309627</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-17T16:25:00.000Z</v>
+        <v>2026-07-18T06:53:20.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>WO0000000309629</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-18T06:53:20.000Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>WO0000000309632</v>
+        <v>WO0000000309635</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-17T17:12:32.000Z</v>
+        <v>2026-07-17T16:06:26.000Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>WO0000000309635</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-17T16:06:26.000Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>WO0000000309633</v>
+        <v>INC000000152938</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-17T16:23:43.000Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>INC000000152938</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-17T16:23:43.000Z</v>
+        <v>2026-07-18T07:13:50.000Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>WO0000000309636</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-18T07:13:50.000Z</v>
+        <v>2026-07-17T16:27:45.000Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>INC000000152838</v>
+        <v>INC000000152940</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-17T16:27:45.000Z</v>
+        <v>2026-07-17T16:32:49.000Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>INC000000152940</v>
+        <v>WO0000000309582</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-17T16:32:49.000Z</v>
+        <v>2026-07-17T17:18:59.000Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>WO0000000309582</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-17T17:18:59.000Z</v>
+        <v>2026-07-17T17:05:49.000Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-17T17:05:49.000Z</v>
+        <v>2026-07-18T06:19:47.000Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309583</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-18T06:19:47.000Z</v>
+        <v>2026-07-17T16:34:20.000Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>WO0000000309583</v>
+        <v>WO0000000309585</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-17T16:34:20.000Z</v>
+        <v>2026-07-17T18:48:55.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>WO0000000309585</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-17T18:48:55.000Z</v>
+        <v>2026-07-17T16:39:05.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>WO0000000309586</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-17T16:39:05.000Z</v>
+        <v>2026-07-18T12:55:19.000Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>INC000000152939</v>
+        <v>WO0000000309587</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-18T12:55:19.000Z</v>
+        <v>2026-07-17T16:39:17.000Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000309587</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-17T16:39:17.000Z</v>
+        <v>2026-07-18T07:38:46.000Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>INC000000152944</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-18T07:38:46.000Z</v>
+        <v>2026-07-18T13:55:17.000Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>WO0000000309589</v>
+        <v>INC000000152945</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-18T13:55:17.000Z</v>
+        <v>2026-07-17T16:53:07.000Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>INC000000152945</v>
+        <v>WO0000000309643</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-17T16:53:07.000Z</v>
+        <v>2026-07-17T16:52:17.999Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>WO0000000309643</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-17T16:52:17.999Z</v>
+        <v>2026-07-17T18:16:22.999Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>WO0000000309592</v>
+        <v>WO0000000309307</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-17T18:16:22.999Z</v>
+        <v>2026-07-18T00:06:54.000Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>WO0000000309307</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-18T00:06:54.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309646</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-17T17:00:35.999Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>WO0000000309646</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-17T17:00:35.999Z</v>
+        <v>2026-07-17T17:00:37.000Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>WO0000000309647</v>
+        <v>INC000000152946</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-17T17:00:37.000Z</v>
+        <v>2026-07-17T17:58:53.999Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>INC000000152946</v>
+        <v>WO0000000309648</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-17T17:58:53.999Z</v>
+        <v>2026-07-17T18:19:50.000Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>WO0000000309648</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-17T18:19:50.000Z</v>
+        <v>2026-07-17T18:20:35.000Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309653</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-17T18:20:35.000Z</v>
+        <v>2026-07-17T17:46:49.000Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>WO0000000309653</v>
+        <v>WO0000000309652</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-17T17:46:49.000Z</v>
+        <v>2026-07-20T22:30:37.000Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>WO0000000309652</v>
+        <v>WO0000000309308</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-17T17:14:44.000Z</v>
+        <v>2026-07-17T17:16:21.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>WO0000000309308</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-17T17:16:21.000Z</v>
+        <v>2026-07-17T17:16:28.000Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>WO0000000309595</v>
+        <v>WO0000000309594</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-17T17:16:28.000Z</v>
+        <v>2026-07-20T22:36:47.999Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000309594</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-17T17:17:41.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>WO0000000309596</v>
+        <v>WO0000000309655</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-17T17:58:30.999Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>WO0000000309655</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-17T17:58:30.999Z</v>
+        <v>2026-07-17T17:19:38.000Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>WO0000000309597</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-17T17:19:38.000Z</v>
+        <v>2026-07-17T17:20:39.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>WO0000000309309</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-17T17:20:39.000Z</v>
+        <v>2026-07-18T07:10:07.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>INC000000152948</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-18T07:10:07.000Z</v>
+        <v>2026-07-17T18:03:03.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>INC000000152845</v>
+        <v>INC000000152846</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-17T18:03:03.000Z</v>
+        <v>2026-07-17T17:43:39.999Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>INC000000152846</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-17T17:43:39.999Z</v>
+        <v>2026-07-17T17:30:03.000Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000309310</v>
+        <v>INC000000152950</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-17T17:30:03.000Z</v>
+        <v>2026-07-17T18:02:01.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>INC000000152950</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-17T18:02:01.000Z</v>
+        <v>2026-07-17T18:11:18.000Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>INC000000152848</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309598</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-17T17:34:00.000Z</v>
+        <v>2026-07-17T17:35:30.999Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>WO0000000309598</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-17T17:35:30.999Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>WO0000000309599</v>
+        <v>WO0000000309600</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-17T17:42:21.000Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>WO0000000309600</v>
+        <v>INC000000152844</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-17T17:42:21.000Z</v>
+        <v>2026-07-17T17:45:02.000Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000152844</v>
+        <v>WO0000000309701</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-17T17:45:02.000Z</v>
+        <v>2026-07-17T18:21:13.999Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>WO0000000309701</v>
+        <v>WO0000000309659</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-17T18:21:13.999Z</v>
+        <v>2026-07-17T17:44:25.999Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>WO0000000309659</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-17T17:44:25.999Z</v>
+        <v>2026-07-17T18:21:50.000Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000309704</v>
+        <v>WO0000000309705</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-17T18:21:50.000Z</v>
+        <v>2026-07-17T18:22:25.999Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>WO0000000309705</v>
+        <v>WO0000000309707</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-17T18:22:25.999Z</v>
+        <v>2026-07-17T17:53:46.000Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>WO0000000309707</v>
+        <v>WO0000000309703</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-17T17:53:46.000Z</v>
+        <v>2026-07-17T18:11:24.000Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>WO0000000309703</v>
+        <v>WO0000000309660</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-17T18:11:24.000Z</v>
+        <v>2026-07-17T18:27:35.999Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>WO0000000309660</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-17T18:27:35.999Z</v>
+        <v>2026-07-18T07:09:16.000Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>INC000000152953</v>
+        <v>WO0000000309661</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-18T07:09:16.000Z</v>
+        <v>2026-07-17T18:09:12.000Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>WO0000000309661</v>
+        <v>INC000000152954</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-17T18:09:12.000Z</v>
+        <v>2026-07-18T10:44:32.000Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>INC000000152954</v>
+        <v>INC000000152851</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-18T10:44:32.000Z</v>
+        <v>2026-07-18T07:10:27.999Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>INC000000152851</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-18T07:10:27.999Z</v>
+        <v>2026-07-18T07:06:21.000Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>INC000000152955</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-18T07:06:21.000Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>WO0000000309664</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-18T09:16:52.000Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>INC000000152956</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-18T09:16:52.000Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>WO0000000309666</v>
+        <v>INC000000152957</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-18T11:15:19.000Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>INC000000152957</v>
+        <v>INC000000152853</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-18T11:15:19.000Z</v>
+        <v>2026-07-20T09:22:52.000Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>INC000000152853</v>
+        <v>WO0000000309711</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-20T09:22:52.000Z</v>
+        <v>2026-07-17T20:28:36.999Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>WO0000000309711</v>
+        <v>INC000000152958</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-17T20:28:36.999Z</v>
+        <v>2026-07-20T09:04:48.999Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>INC000000152958</v>
+        <v>WO0000000309712</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-20T09:04:48.999Z</v>
+        <v>2026-07-17T20:32:00.000Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>WO0000000309712</v>
+        <v>INC000000152854</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-17T20:32:00.000Z</v>
+        <v>2026-07-17T21:32:15.999Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>INC000000152854</v>
+        <v>INC000000152855</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-17T21:32:15.999Z</v>
+        <v>2026-07-17T23:28:51.000Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>INC000000152855</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-17T23:28:51.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>WO0000000309714</v>
+        <v>WO0000000309667</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-17T23:52:41.000Z</v>
+        <v>2026-07-18T07:04:58.999Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>WO0000000309667</v>
+        <v>WO0000000309715</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-18T07:04:58.999Z</v>
+        <v>2026-07-18T02:41:04.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>WO0000000309715</v>
+        <v>WO0000000309668</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-18T02:41:04.000Z</v>
+        <v>2026-07-18T07:03:56.000Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>WO0000000309668</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-18T07:03:56.000Z</v>
+        <v>2026-07-18T05:49:03.000Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>WO0000000309669</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-18T05:49:03.000Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>INC000000152856</v>
+        <v>INC000000152863</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-18T11:32:43.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>INC000000152963</v>
+        <v>INC000000152862</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-18T06:52:52.999Z</v>
+        <v>2026-07-18T06:59:49.000Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>INC000000152863</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-18T11:32:43.000Z</v>
+        <v>2026-07-18T11:57:16.000Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>INC000000152862</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-18T06:59:49.000Z</v>
+        <v>2026-07-18T06:52:20.999Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000152869</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-18T11:57:16.000Z</v>
+        <v>2026-07-18T07:00:34.000Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>WO0000000309671</v>
+        <v>INC000000152965</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-18T06:52:20.999Z</v>
+        <v>2026-07-18T12:00:50.000Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>INC000000152869</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-18T07:00:34.000Z</v>
+        <v>2026-07-18T07:31:33.000Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>INC000000152965</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-18T12:00:50.000Z</v>
+        <v>2026-07-18T08:43:13.999Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>INC000000152873</v>
+        <v>WO0000000309678</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-18T07:31:33.000Z</v>
+        <v>2026-07-18T07:42:09.999Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>INC000000152971</v>
+        <v>INC000000152877</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-18T08:43:13.999Z</v>
+        <v>2026-07-19T11:20:00.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>WO0000000309678</v>
+        <v>INC000000152878</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-18T07:42:09.999Z</v>
+        <v>2026-07-18T08:12:08.000Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>INC000000152877</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-19T11:20:00.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>INC000000152878</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-18T08:12:08.000Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>WO0000000309682</v>
+        <v>INC000000152879</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-18T08:11:58.000Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>WO0000000309686</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>INC000000152879</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-18T12:53:54.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>WO0000000309689</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-18T08:29:42.000Z</v>
+        <v>2026-07-18T08:39:53.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>INC000000152978</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-18T12:53:54.000Z</v>
+        <v>2026-07-18T08:48:11.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>INC000000152883</v>
+        <v>WO0000000309693</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-18T08:39:53.000Z</v>
+        <v>2026-07-18T08:41:38.000Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>WO0000000309692</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-18T08:48:11.000Z</v>
+        <v>2026-07-21T00:11:10.000Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>WO0000000309693</v>
+        <v>INC000000152884</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-18T08:41:38.000Z</v>
+        <v>2026-07-18T09:35:54.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>INC000000152981</v>
+        <v>INC000000152980</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-18T10:06:26.000Z</v>
+        <v>2026-07-18T16:16:48.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>INC000000152884</v>
+        <v>WO0000000309728</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-18T09:35:54.000Z</v>
+        <v>2026-07-20T23:05:18.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>INC000000152980</v>
+        <v>WO0000000309732</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-18T16:16:48.000Z</v>
+        <v>2026-07-18T09:10:30.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>WO0000000309728</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-18T08:54:20.000Z</v>
+        <v>2026-07-18T09:16:51.000Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>WO0000000309732</v>
+        <v>INC000000152888</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-18T09:10:30.000Z</v>
+        <v>2026-07-18T09:48:34.000Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>WO0000000309697</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-18T09:16:51.000Z</v>
+        <v>2026-07-18T09:49:22.999Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>INC000000152888</v>
+        <v>WO0000000309698</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-18T09:48:34.000Z</v>
+        <v>2026-07-18T10:07:47.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>INC000000152985</v>
+        <v>INC000000152986</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-18T09:49:22.999Z</v>
+        <v>2026-07-18T09:32:28.999Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000309698</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-18T10:07:47.000Z</v>
+        <v>2026-07-18T10:49:11.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>INC000000152986</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-18T09:32:28.999Z</v>
+        <v>2026-07-18T09:42:12.000Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000152990</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-18T10:49:11.000Z</v>
+        <v>2026-07-18T11:38:28.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>INC000000152989</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-18T09:42:12.000Z</v>
+        <v>2026-07-18T11:41:27.000Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>INC000000152990</v>
+        <v>WO0000000309802</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-18T11:38:28.000Z</v>
+        <v>2026-07-18T10:09:11.999Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>INC000000152890</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-18T11:41:27.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>WO0000000309802</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-18T10:09:11.999Z</v>
+        <v>2026-07-20T19:05:32.000Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>WO0000000309803</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-20T19:04:33.999Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-20T19:05:32.000Z</v>
+        <v>2026-07-20T19:03:52.000Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-20T19:04:33.999Z</v>
+        <v>2026-07-20T19:04:20.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000152894</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-20T19:03:52.000Z</v>
+        <v>2026-07-18T11:23:37.999Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>INC000000152893</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-20T19:04:20.000Z</v>
+        <v>2026-07-19T01:10:57.000Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>INC000000152894</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-18T11:23:37.999Z</v>
+        <v>2026-07-18T11:44:19.999Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>WO0000000309804</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-19T01:10:57.000Z</v>
+        <v>2026-07-19T01:11:11.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>WO0000000309805</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-18T11:44:19.999Z</v>
+        <v>2026-07-18T11:46:33.000Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>WO0000000309807</v>
+        <v>INC000000153000</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-19T01:11:11.000Z</v>
+        <v>2026-07-18T11:39:44.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-18T11:46:33.000Z</v>
+        <v>2026-07-18T11:48:31.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>INC000000153000</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-18T11:39:44.000Z</v>
+        <v>2026-07-18T11:22:17.000Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>INC000000152897</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-18T11:48:31.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>INC000000152898</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-18T11:22:17.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>WO0000000309810</v>
+        <v>INC000000153003</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-18T12:06:28.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>WO0000000309752</v>
+        <v>INC000000152900</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-18T11:50:14.999Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>INC000000153003</v>
+        <v>WO0000000309815</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-18T12:06:28.000Z</v>
+        <v>2026-07-18T11:50:24.000Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>INC000000152900</v>
+        <v>INC000000153006</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-18T11:50:14.999Z</v>
+        <v>2026-07-18T12:03:20.000Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>WO0000000309815</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-18T11:50:24.000Z</v>
+        <v>2026-07-20T18:59:17.000Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>INC000000153006</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-18T12:03:20.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-20T18:59:17.000Z</v>
+        <v>2026-07-21T06:23:37.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>WO0000000309816</v>
+        <v>INC000000153103</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-18T11:58:56.000Z</v>
+        <v>2026-07-18T12:16:56.000Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153009</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-18T12:10:30.000Z</v>
+        <v>2026-07-18T12:37:40.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>INC000000153103</v>
+        <v>INC000000153011</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-18T12:16:56.000Z</v>
+        <v>2026-07-18T12:32:55.000Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>INC000000153009</v>
+        <v>WO0000000309819</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-18T12:37:40.000Z</v>
+        <v>2026-07-20T23:23:23.000Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>INC000000153011</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-18T12:32:55.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>WO0000000309819</v>
+        <v>INC000000153012</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-18T12:40:45.999Z</v>
+        <v>2026-07-18T12:55:00.000Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>WO0000000309759</v>
+        <v>INC000000153013</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-19T11:20:26.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>INC000000153012</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-18T12:55:00.000Z</v>
+        <v>2026-07-18T13:21:05.000Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>INC000000153013</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-19T11:20:26.000Z</v>
+        <v>2026-07-19T11:20:49.000Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>WO0000000309825</v>
+        <v>INC000000153015</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-18T13:21:05.000Z</v>
+        <v>2026-07-20T15:39:51.999Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>INC000000153105</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-19T11:20:49.000Z</v>
+        <v>2026-07-18T13:48:35.000Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>INC000000153015</v>
+        <v>INC000000153017</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-20T15:39:51.999Z</v>
+        <v>2026-07-18T15:26:50.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>WO0000000309826</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-18T13:48:35.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>INC000000153017</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-18T15:26:50.000Z</v>
+        <v>2026-07-18T17:18:50.999Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>WO0000000309768</v>
+        <v>WO0000000309769</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-18T20:32:49.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>INC000000153107</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-18T17:18:50.999Z</v>
+        <v>2026-07-18T20:22:17.000Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>WO0000000309769</v>
+        <v>WO0000000309830</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-18T20:32:49.000Z</v>
+        <v>2026-07-18T21:51:52.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>WO0000000309829</v>
+        <v>INC000000153108</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-18T20:22:17.000Z</v>
+        <v>2026-07-19T08:42:17.000Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>WO0000000309830</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-18T21:51:52.000Z</v>
+        <v>2026-07-19T08:43:56.000Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>INC000000153108</v>
+        <v>INC000000153020</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-19T08:42:17.000Z</v>
+        <v>2026-07-19T08:44:32.000Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>INC000000153019</v>
+        <v>WO0000000309772</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-19T08:43:56.000Z</v>
+        <v>2026-07-19T07:06:45.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>INC000000153020</v>
+        <v>WO0000000309773</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-19T08:44:32.000Z</v>
+        <v>2026-07-19T07:08:51.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>WO0000000309772</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-19T07:06:45.000Z</v>
+        <v>2026-07-21T06:47:56.000Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>WO0000000309773</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-19T07:08:51.000Z</v>
+        <v>2026-07-19T10:27:01.999Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-20T17:17:44.000Z</v>
+        <v>2026-07-19T13:24:13.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>INC000000153022</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-19T10:27:01.999Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153025</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-19T13:24:13.000Z</v>
+        <v>2026-07-19T13:28:43.999Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>INC000000153111</v>
+        <v>INC000000153024</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-19T13:24:41.999Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>INC000000153025</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-19T13:28:43.999Z</v>
+        <v>2026-07-20T18:58:17.000Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>INC000000153024</v>
+        <v>WO0000000309777</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-19T13:24:41.999Z</v>
+        <v>2026-07-19T12:42:01.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>INC000000153027</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-20T18:58:17.000Z</v>
+        <v>2026-07-19T11:10:56.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>WO0000000309777</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-19T12:42:01.000Z</v>
+        <v>2026-07-19T12:52:16.000Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>WO0000000309834</v>
+        <v>INC000000153028</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-19T11:10:56.000Z</v>
+        <v>2026-07-20T18:58:47.999Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153029</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-19T12:52:16.000Z</v>
+        <v>2026-07-19T13:44:46.000Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>INC000000153028</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-20T18:58:47.999Z</v>
+        <v>2026-07-19T13:15:08.999Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>INC000000153029</v>
+        <v>INC000000153118</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-19T13:44:46.000Z</v>
+        <v>2026-07-19T13:24:11.999Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>WO0000000309779</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-19T13:15:08.999Z</v>
+        <v>2026-07-19T14:37:17.999Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>INC000000153118</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-19T13:24:11.999Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153031</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-19T14:37:17.999Z</v>
+        <v>2026-07-20T07:13:50.000Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>INC000000153121</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-19T20:48:52.999Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>INC000000153031</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-20T07:13:50.000Z</v>
+        <v>2026-07-19T21:35:08.000Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>INC000000153032</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-20T16:15:42.000Z</v>
+        <v>2026-07-19T22:08:28.999Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>WO0000000309780</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-19T20:48:52.999Z</v>
+        <v>2026-07-19T23:43:15.999Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>WO0000000309837</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-19T21:35:08.000Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>WO0000000309781</v>
+        <v>INC000000153033</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-19T22:08:28.999Z</v>
+        <v>2026-07-20T06:29:05.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>WO0000000309783</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-19T23:43:15.999Z</v>
+        <v>2026-07-20T06:54:21.999Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>WO0000000309838</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-20T06:55:50.999Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>INC000000153033</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-20T06:29:05.000Z</v>
+        <v>2026-07-20T07:47:44.000Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>INC000000153034</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-20T06:54:21.999Z</v>
+        <v>2026-07-20T07:57:13.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>INC000000153035</v>
+        <v>INC000000153123</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-20T06:55:50.999Z</v>
+        <v>2026-07-20T07:44:34.000Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>INC000000153036</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-20T07:47:44.000Z</v>
+        <v>2026-07-20T08:42:15.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>INC000000153037</v>
+        <v>INC000000153125</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-20T07:57:13.000Z</v>
+        <v>2026-07-20T09:06:58.000Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>INC000000153123</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-20T07:44:34.000Z</v>
+        <v>2026-07-20T12:50:53.000Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>INC000000153038</v>
+        <v>WO0000000309840</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-20T08:42:15.000Z</v>
+        <v>2026-07-20T11:28:11.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>INC000000153125</v>
+        <v>WO0000000309791</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-20T09:06:58.000Z</v>
+        <v>2026-07-20T12:51:30.000Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>INC000000153039</v>
+        <v>WO0000000309792</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-20T16:17:30.999Z</v>
+        <v>2026-07-20T14:10:35.999Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>INC000000153126</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-20T16:18:55.000Z</v>
+        <v>2026-07-20T14:29:59.999Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>INC000000153040</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-20T16:20:12.000Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>INC000000153041</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-20T16:22:33.000Z</v>
+        <v>2026-07-20T15:53:16.999Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-20T12:50:53.000Z</v>
+        <v>2026-07-20T18:35:59.000Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>WO0000000309840</v>
+        <v>WO0000000309794</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-20T11:28:11.000Z</v>
+        <v>2026-07-20T18:20:05.999Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>INC000000153042</v>
+        <v>WO0000000309843</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-20T11:59:39.000Z</v>
+        <v>2026-07-20T18:23:24.000Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>WO0000000309791</v>
+        <v>WO0000000309795</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-20T12:51:30.000Z</v>
+        <v>2026-07-20T18:30:58.000Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>WO0000000309792</v>
+        <v>WO0000000309796</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-20T14:10:35.999Z</v>
+        <v>2026-07-20T18:41:46.000Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>WO0000000309841</v>
+        <v>WO0000000309845</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-20T14:29:59.999Z</v>
+        <v>2026-07-20T21:48:04.000Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>WO0000000309842</v>
+        <v>WO0000000309846</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-20T18:44:29.999Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>INC000000153128</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-20T15:53:16.999Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>WO0000000309793</v>
+        <v>WO0000000309797</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-20T18:35:59.000Z</v>
+        <v>2026-07-20T19:09:36.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>WO0000000309794</v>
+        <v>WO0000000309850</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-20T18:20:05.999Z</v>
+        <v>2026-07-20T20:24:30.000Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>WO0000000309843</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-20T18:23:24.000Z</v>
+        <v>2026-07-20T20:40:39.000Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>WO0000000309795</v>
+        <v>WO0000000309798</v>
       </c>
       <c r="B1181" s="1" t="d">
-        <v>2026-07-20T18:30:58.000Z</v>
+        <v>2026-07-20T22:11:58.999Z</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>WO0000000309796</v>
+        <v>WO0000000309852</v>
       </c>
       <c r="B1182" s="1" t="d">
-        <v>2026-07-20T18:41:46.000Z</v>
+        <v>2026-07-20T22:58:26.999Z</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>WO0000000309845</v>
+        <v>WO0000000309853</v>
       </c>
       <c r="B1183" s="1" t="d">
-        <v>2026-07-20T18:44:11.000Z</v>
+        <v>2026-07-21T05:54:59.000Z</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>WO0000000309846</v>
+        <v>WO0000000309799</v>
       </c>
       <c r="B1184" s="1" t="d">
-        <v>2026-07-20T18:44:29.999Z</v>
+        <v>2026-07-21T05:59:16.000Z</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>WO0000000309848</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B1185" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T06:29:29.000Z</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>WO0000000309797</v>
+        <v>INC000000153129</v>
       </c>
       <c r="B1186" s="1" t="d">
-        <v>2026-07-20T19:09:36.000Z</v>
+        <v>2026-07-21T06:35:33.000Z</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
+        <v>WO0000000309902</v>
+      </c>
+      <c r="B1187" s="1" t="d">
+        <v>2026-07-21T06:35:34.000Z</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="str">
+        <v>INC000000153130</v>
+      </c>
+      <c r="B1188" s="1" t="d">
+        <v>2026-07-21T06:41:37.999Z</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="str">
+        <v>WO0000000309906</v>
+      </c>
+      <c r="B1189" s="1" t="d">
+        <v>2026-07-21T06:28:19.000Z</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="str">
+        <v>INC000000153131</v>
+      </c>
+      <c r="B1190" s="1" t="d">
+        <v>2026-07-21T06:32:02.000Z</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="str">
+        <v>INC000000153132</v>
+      </c>
+      <c r="B1191" s="1" t="d">
+        <v>2026-07-21T06:45:42.000Z</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="str">
+        <v>INC000000153044</v>
+      </c>
+      <c r="B1192" s="1" t="d">
+        <v>2026-07-21T06:58:00.000Z</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="str">
+        <v>WO0000000309909</v>
+      </c>
+      <c r="B1193" s="1" t="d">
+        <v>2026-07-21T06:34:29.000Z</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="str">
+        <v>INC000000153047</v>
+      </c>
+      <c r="B1194" s="1" t="d">
+        <v>2026-07-21T07:01:27.000Z</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="str">
+        <v>INC000000153046</v>
+      </c>
+      <c r="B1195" s="1" t="d">
+        <v>2026-07-21T06:40:04.000Z</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="str">
+        <v>INC000000153134</v>
+      </c>
+      <c r="B1196" s="1" t="d">
+        <v>2026-07-21T06:55:53.000Z</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="str">
+        <v>INC000000153133</v>
+      </c>
+      <c r="B1197" s="1" t="d">
+        <v>2026-07-21T06:54:40.000Z</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="str">
+        <v>INC000000153049</v>
+      </c>
+      <c r="B1198" s="1" t="d">
+        <v>2026-07-21T06:45:54.999Z</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="str">
+        <v>INC000000153050</v>
+      </c>
+      <c r="B1199" s="1" t="d">
+        <v>2026-07-21T06:47:02.000Z</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="str">
+        <v>INC000000153048</v>
+      </c>
+      <c r="B1200" s="1" t="d">
+        <v>2026-07-21T06:54:50.000Z</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="str">
+        <v>INC000000153137</v>
+      </c>
+      <c r="B1201" s="1" t="d">
+        <v>2026-07-21T06:59:38.000Z</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="str">
+        <v>WO0000000309913</v>
+      </c>
+      <c r="B1202" s="1" t="d">
+        <v>2026-07-21T06:59:27.999Z</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="str">
+        <v>WO0000000309858</v>
+      </c>
+      <c r="B1203" s="1" t="d">
+        <v>2026-07-21T07:01:38.000Z</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1187"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1206"/>
+  <dimension ref="A1:B1211"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2115,546 +2115,546 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>INC000000141766</v>
+        <v>INC000000142106</v>
       </c>
       <c r="B215" s="1" t="d">
-        <v>2026-07-17T17:20:51.000Z</v>
+        <v>2026-06-26T20:27:55.000Z</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>INC000000142106</v>
+        <v>WO0000000287464</v>
       </c>
       <c r="B216" s="1" t="d">
-        <v>2026-06-26T20:27:55.000Z</v>
+        <v>2026-07-08T10:11:20.999Z</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>WO0000000287464</v>
+        <v>INC000000142518</v>
       </c>
       <c r="B217" s="1" t="d">
-        <v>2026-07-08T10:11:20.999Z</v>
+        <v>2026-06-26T20:28:21.000Z</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>INC000000142518</v>
+        <v>WO0000000288840</v>
       </c>
       <c r="B218" s="1" t="d">
-        <v>2026-06-26T20:28:21.000Z</v>
+        <v>2026-07-03T12:08:05.000Z</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>WO0000000288840</v>
+        <v>WO0000000288737</v>
       </c>
       <c r="B219" s="1" t="d">
-        <v>2026-07-03T12:08:05.000Z</v>
+        <v>2026-07-03T11:40:50.999Z</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>WO0000000288737</v>
+        <v>INC000000143439</v>
       </c>
       <c r="B220" s="1" t="d">
-        <v>2026-07-03T11:40:50.999Z</v>
+        <v>2026-06-26T20:28:54.000Z</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>INC000000143439</v>
+        <v>INC000000144822</v>
       </c>
       <c r="B221" s="1" t="d">
-        <v>2026-06-26T20:28:54.000Z</v>
+        <v>2026-07-16T08:31:54.000Z</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>INC000000144822</v>
+        <v>INC000000145025</v>
       </c>
       <c r="B222" s="1" t="d">
-        <v>2026-07-16T08:31:54.000Z</v>
+        <v>2026-07-02T12:27:43.000Z</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>INC000000145025</v>
+        <v>INC000000145194</v>
       </c>
       <c r="B223" s="1" t="d">
-        <v>2026-07-02T12:27:43.000Z</v>
+        <v>2026-07-16T09:36:17.000Z</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>INC000000145194</v>
+        <v>INC000000146528</v>
       </c>
       <c r="B224" s="1" t="d">
-        <v>2026-07-16T09:36:17.000Z</v>
+        <v>2026-07-02T12:27:43.000Z</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>INC000000146528</v>
+        <v>WO0000000295650</v>
       </c>
       <c r="B225" s="1" t="d">
-        <v>2026-07-02T12:27:43.000Z</v>
+        <v>2026-07-07T08:33:04.999Z</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>WO0000000295650</v>
+        <v>WO0000000296601</v>
       </c>
       <c r="B226" s="1" t="d">
-        <v>2026-07-07T08:33:04.999Z</v>
+        <v>2026-06-30T09:52:50.999Z</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>WO0000000296601</v>
+        <v>INC000000147297</v>
       </c>
       <c r="B227" s="1" t="d">
-        <v>2026-06-30T09:52:50.999Z</v>
+        <v>2026-07-08T12:27:13.999Z</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>INC000000147297</v>
+        <v>WO0000000297046</v>
       </c>
       <c r="B228" s="1" t="d">
-        <v>2026-07-08T12:27:13.999Z</v>
+        <v>2026-07-16T15:23:18.000Z</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>WO0000000297046</v>
+        <v>WO0000000291773</v>
       </c>
       <c r="B229" s="1" t="d">
-        <v>2026-07-16T15:23:18.000Z</v>
+        <v>2026-07-06T12:05:36.000Z</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>WO0000000291773</v>
+        <v>INC000000147569</v>
       </c>
       <c r="B230" s="1" t="d">
-        <v>2026-07-06T12:05:36.000Z</v>
+        <v>2026-06-26T20:31:22.000Z</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>INC000000147569</v>
+        <v>WO0000000298353</v>
       </c>
       <c r="B231" s="1" t="d">
-        <v>2026-06-26T20:31:22.000Z</v>
+        <v>2026-07-14T11:48:03.000Z</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>WO0000000298353</v>
+        <v>WO0000000298379</v>
       </c>
       <c r="B232" s="1" t="d">
-        <v>2026-07-14T11:48:03.000Z</v>
+        <v>2026-06-24T13:42:23.000Z</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>WO0000000298379</v>
+        <v>WO0000000299246</v>
       </c>
       <c r="B233" s="1" t="d">
-        <v>2026-06-24T13:42:23.000Z</v>
+        <v>2026-06-25T11:19:04.000Z</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>WO0000000299246</v>
+        <v>WO0000000299346</v>
       </c>
       <c r="B234" s="1" t="d">
-        <v>2026-06-25T11:19:04.000Z</v>
+        <v>2026-07-02T15:43:45.000Z</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>WO0000000299346</v>
+        <v>INC000000148375</v>
       </c>
       <c r="B235" s="1" t="d">
-        <v>2026-07-02T15:43:45.000Z</v>
+        <v>2026-07-06T10:46:28.999Z</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>INC000000148375</v>
+        <v>INC000000148478</v>
       </c>
       <c r="B236" s="1" t="d">
-        <v>2026-07-06T10:46:28.999Z</v>
+        <v>2026-07-06T10:47:50.000Z</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>INC000000148478</v>
+        <v>INC000000148483</v>
       </c>
       <c r="B237" s="1" t="d">
-        <v>2026-07-06T10:47:50.000Z</v>
+        <v>2026-07-06T10:46:26.000Z</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>INC000000148483</v>
+        <v>INC000000148391</v>
       </c>
       <c r="B238" s="1" t="d">
-        <v>2026-07-06T10:46:26.000Z</v>
+        <v>2026-07-06T10:46:33.000Z</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>INC000000148391</v>
+        <v>INC000000148617</v>
       </c>
       <c r="B239" s="1" t="d">
-        <v>2026-07-06T10:46:33.000Z</v>
+        <v>2026-06-23T13:06:23.000Z</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>INC000000148617</v>
+        <v>INC000000148567</v>
       </c>
       <c r="B240" s="1" t="d">
-        <v>2026-06-23T13:06:23.000Z</v>
+        <v>2026-06-23T20:51:36.000Z</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>INC000000148567</v>
+        <v>WO0000000299917</v>
       </c>
       <c r="B241" s="1" t="d">
-        <v>2026-06-23T20:51:36.000Z</v>
+        <v>2026-07-14T12:23:04.000Z</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>WO0000000299917</v>
+        <v>INC000000148835</v>
       </c>
       <c r="B242" s="1" t="d">
-        <v>2026-07-14T12:23:04.000Z</v>
+        <v>2026-07-06T10:46:35.000Z</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>INC000000148835</v>
+        <v>WO0000000300350</v>
       </c>
       <c r="B243" s="1" t="d">
-        <v>2026-07-06T10:46:35.000Z</v>
+        <v>2026-07-15T17:13:32.000Z</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>WO0000000300350</v>
+        <v>WO0000000300621</v>
       </c>
       <c r="B244" s="1" t="d">
-        <v>2026-07-15T17:13:32.000Z</v>
+        <v>2026-07-07T08:00:34.000Z</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>WO0000000300621</v>
+        <v>INC000000148932</v>
       </c>
       <c r="B245" s="1" t="d">
-        <v>2026-07-07T08:00:34.000Z</v>
+        <v>2026-06-26T20:05:39.000Z</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>INC000000148932</v>
+        <v>WO0000000300825</v>
       </c>
       <c r="B246" s="1" t="d">
-        <v>2026-06-26T20:05:39.000Z</v>
+        <v>2026-07-06T16:31:51.000Z</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>WO0000000300825</v>
+        <v>INC000000149054</v>
       </c>
       <c r="B247" s="1" t="d">
-        <v>2026-07-06T16:31:51.000Z</v>
+        <v>2026-06-25T12:46:56.999Z</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>INC000000149054</v>
+        <v>WO0000000301205</v>
       </c>
       <c r="B248" s="1" t="d">
-        <v>2026-06-25T12:46:56.999Z</v>
+        <v>2026-07-21T08:00:58.999Z</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>WO0000000301205</v>
+        <v>WO0000000298649</v>
       </c>
       <c r="B249" s="1" t="d">
-        <v>2026-07-21T08:00:58.999Z</v>
+        <v>2026-07-08T10:16:58.999Z</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>WO0000000298649</v>
+        <v>INC000000149262</v>
       </c>
       <c r="B250" s="1" t="d">
-        <v>2026-07-08T10:16:58.999Z</v>
+        <v>2026-07-06T10:46:38.000Z</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>INC000000149262</v>
+        <v>INC000000149363</v>
       </c>
       <c r="B251" s="1" t="d">
-        <v>2026-07-06T10:46:38.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>INC000000149363</v>
+        <v>INC000000149449</v>
       </c>
       <c r="B252" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-06-30T13:18:04.000Z</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>INC000000149449</v>
+        <v>INC000000149711</v>
       </c>
       <c r="B253" s="1" t="d">
-        <v>2026-06-30T13:18:04.000Z</v>
+        <v>2026-07-02T16:46:09.999Z</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>INC000000149711</v>
+        <v>INC000000149814</v>
       </c>
       <c r="B254" s="1" t="d">
-        <v>2026-07-02T16:46:09.999Z</v>
+        <v>2026-07-01T12:39:49.000Z</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>INC000000149814</v>
+        <v>WO0000000302574</v>
       </c>
       <c r="B255" s="1" t="d">
-        <v>2026-07-01T12:39:49.000Z</v>
+        <v>2026-07-10T13:08:33.999Z</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>WO0000000302574</v>
+        <v>INC000000149891</v>
       </c>
       <c r="B256" s="1" t="d">
-        <v>2026-07-10T13:08:33.999Z</v>
+        <v>2026-07-02T10:27:00.000Z</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>INC000000149891</v>
+        <v>INC000000149936</v>
       </c>
       <c r="B257" s="1" t="d">
-        <v>2026-07-02T10:27:00.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>INC000000149936</v>
+        <v>WO0000000303077</v>
       </c>
       <c r="B258" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-17T13:54:02.000Z</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>WO0000000303077</v>
+        <v>INC000000150054</v>
       </c>
       <c r="B259" s="1" t="d">
-        <v>2026-07-17T13:54:02.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>INC000000150054</v>
+        <v>WO0000000303223</v>
       </c>
       <c r="B260" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-10T09:44:01.000Z</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>WO0000000303223</v>
+        <v>INC000000149979</v>
       </c>
       <c r="B261" s="1" t="d">
-        <v>2026-07-10T09:44:01.000Z</v>
+        <v>2026-07-06T09:02:53.000Z</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>INC000000149979</v>
+        <v>INC000000149982</v>
       </c>
       <c r="B262" s="1" t="d">
-        <v>2026-07-06T09:02:53.000Z</v>
+        <v>2026-07-06T10:46:41.999Z</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>INC000000149982</v>
+        <v>INC000000149983</v>
       </c>
       <c r="B263" s="1" t="d">
-        <v>2026-07-06T10:46:41.999Z</v>
+        <v>2026-07-06T09:06:44.000Z</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>INC000000149983</v>
+        <v>INC000000150063</v>
       </c>
       <c r="B264" s="1" t="d">
-        <v>2026-07-06T09:06:44.000Z</v>
+        <v>2026-07-06T09:10:00.999Z</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>INC000000150063</v>
+        <v>INC000000149989</v>
       </c>
       <c r="B265" s="1" t="d">
-        <v>2026-07-06T09:10:00.999Z</v>
+        <v>2026-07-06T09:10:52.000Z</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>INC000000149989</v>
+        <v>WO0000000303319</v>
       </c>
       <c r="B266" s="1" t="d">
-        <v>2026-07-06T09:10:52.000Z</v>
+        <v>2026-07-07T09:11:18.000Z</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>WO0000000303319</v>
+        <v>INC000000150108</v>
       </c>
       <c r="B267" s="1" t="d">
-        <v>2026-07-07T09:11:18.000Z</v>
+        <v>2026-07-06T10:48:13.000Z</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>INC000000150108</v>
+        <v>INC000000150240</v>
       </c>
       <c r="B268" s="1" t="d">
-        <v>2026-07-06T10:48:13.000Z</v>
+        <v>2026-07-17T17:20:51.999Z</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>INC000000150240</v>
+        <v>INC000000150131</v>
       </c>
       <c r="B269" s="1" t="d">
-        <v>2026-07-17T17:20:51.999Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>INC000000150131</v>
+        <v>WO0000000303640</v>
       </c>
       <c r="B270" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T11:51:27.000Z</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>WO0000000303640</v>
+        <v>WO0000000303579</v>
       </c>
       <c r="B271" s="1" t="d">
-        <v>2026-07-15T11:51:27.000Z</v>
+        <v>2026-07-17T12:57:13.000Z</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>WO0000000303579</v>
+        <v>WO0000000303593</v>
       </c>
       <c r="B272" s="1" t="d">
-        <v>2026-07-17T12:57:13.000Z</v>
+        <v>2026-07-15T13:55:27.999Z</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>WO0000000303593</v>
+        <v>INC000000150158</v>
       </c>
       <c r="B273" s="1" t="d">
-        <v>2026-07-15T13:55:27.999Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>INC000000150158</v>
+        <v>WO0000000303803</v>
       </c>
       <c r="B274" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-17T14:43:11.000Z</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>WO0000000303803</v>
+        <v>WO0000000303738</v>
       </c>
       <c r="B275" s="1" t="d">
-        <v>2026-07-17T14:43:11.000Z</v>
+        <v>2026-07-20T00:01:08.000Z</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>WO0000000303738</v>
+        <v>INC000000150172</v>
       </c>
       <c r="B276" s="1" t="d">
-        <v>2026-07-20T00:01:08.000Z</v>
+        <v>2026-07-06T12:25:58.000Z</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>INC000000150172</v>
+        <v>WO0000000303781</v>
       </c>
       <c r="B277" s="1" t="d">
-        <v>2026-07-06T12:25:58.000Z</v>
+        <v>2026-07-10T09:46:00.000Z</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>WO0000000303781</v>
+        <v>INC000000150407</v>
       </c>
       <c r="B278" s="1" t="d">
-        <v>2026-07-10T09:46:00.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>INC000000150407</v>
+        <v>WO0000000304415</v>
       </c>
       <c r="B279" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T12:14:00.000Z</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>WO0000000304415</v>
+        <v>WO0000000304363</v>
       </c>
       <c r="B280" s="1" t="d">
-        <v>2026-07-15T12:14:00.000Z</v>
+        <v>2026-07-15T13:27:05.000Z</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>WO0000000304363</v>
+        <v>INC000000150521</v>
       </c>
       <c r="B281" s="1" t="d">
-        <v>2026-07-15T13:27:05.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>INC000000150521</v>
+        <v>INC000000150630</v>
       </c>
       <c r="B282" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-10T08:48:46.999Z</v>
       </c>
     </row>
     <row r="283">
@@ -2867,226 +2867,226 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>INC000000135134</v>
+        <v>WO0000000306610</v>
       </c>
       <c r="B309" s="1" t="d">
-        <v>2026-07-14T10:35:47.000Z</v>
+        <v>2026-07-16T09:06:23.000Z</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>INC000000136403</v>
+        <v>INC000000135134</v>
       </c>
       <c r="B310" s="1" t="d">
-        <v>2026-07-14T06:43:05.000Z</v>
+        <v>2026-07-14T10:35:47.000Z</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>INC000000138835</v>
+        <v>INC000000136403</v>
       </c>
       <c r="B311" s="1" t="d">
-        <v>2026-07-14T10:35:56.000Z</v>
+        <v>2026-07-14T06:43:05.000Z</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>INC000000139335</v>
+        <v>INC000000138835</v>
       </c>
       <c r="B312" s="1" t="d">
-        <v>2026-07-14T06:43:37.000Z</v>
+        <v>2026-07-14T10:35:56.000Z</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>WO0000000282199</v>
+        <v>INC000000139335</v>
       </c>
       <c r="B313" s="1" t="d">
-        <v>2026-07-14T15:02:42.000Z</v>
+        <v>2026-07-14T06:43:37.000Z</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>INC000000141515</v>
+        <v>WO0000000282199</v>
       </c>
       <c r="B314" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-14T15:02:42.000Z</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>INC000000142452</v>
+        <v>INC000000141515</v>
       </c>
       <c r="B315" s="1" t="d">
-        <v>2026-07-10T09:46:03.999Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>WO0000000293293</v>
+        <v>INC000000142452</v>
       </c>
       <c r="B316" s="1" t="d">
-        <v>2026-07-15T08:29:08.000Z</v>
+        <v>2026-07-10T09:46:03.999Z</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>INC000000145976</v>
+        <v>WO0000000293293</v>
       </c>
       <c r="B317" s="1" t="d">
-        <v>2026-07-15T11:29:45.000Z</v>
+        <v>2026-07-15T08:29:08.000Z</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>INC000000146720</v>
+        <v>INC000000145976</v>
       </c>
       <c r="B318" s="1" t="d">
-        <v>2026-07-16T08:34:09.000Z</v>
+        <v>2026-07-15T11:29:45.000Z</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>INC000000147260</v>
+        <v>INC000000146720</v>
       </c>
       <c r="B319" s="1" t="d">
-        <v>2026-07-14T08:08:06.000Z</v>
+        <v>2026-07-16T08:34:09.000Z</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>INC000000147613</v>
+        <v>INC000000147260</v>
       </c>
       <c r="B320" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-14T08:08:06.000Z</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>WO0000000297578</v>
+        <v>INC000000147613</v>
       </c>
       <c r="B321" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>INC000000149029</v>
+        <v>WO0000000297578</v>
       </c>
       <c r="B322" s="1" t="d">
-        <v>2026-07-10T14:37:50.000Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>WO0000000301822</v>
+        <v>INC000000149029</v>
       </c>
       <c r="B323" s="1" t="d">
-        <v>2026-07-20T23:27:55.000Z</v>
+        <v>2026-07-10T14:37:50.000Z</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>INC000000149860</v>
+        <v>WO0000000301822</v>
       </c>
       <c r="B324" s="1" t="d">
-        <v>2026-07-16T15:59:24.000Z</v>
+        <v>2026-07-20T23:27:55.000Z</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>INC000000150036</v>
+        <v>INC000000149860</v>
       </c>
       <c r="B325" s="1" t="d">
-        <v>2026-07-16T07:28:43.999Z</v>
+        <v>2026-07-16T15:59:24.000Z</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>WO0000000303117</v>
+        <v>INC000000150036</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2026-07-15T10:17:36.000Z</v>
+        <v>2026-07-16T07:28:43.999Z</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>INC000000149964</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B327" s="1" t="d">
-        <v>2026-07-15T15:21:53.000Z</v>
+        <v>2026-07-15T10:17:36.000Z</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>WO0000000303232</v>
+        <v>INC000000149964</v>
       </c>
       <c r="B328" s="1" t="d">
-        <v>2026-07-17T17:20:56.999Z</v>
+        <v>2026-07-15T15:21:53.000Z</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>INC000000150141</v>
+        <v>WO0000000303232</v>
       </c>
       <c r="B329" s="1" t="d">
-        <v>2026-07-15T16:30:22.000Z</v>
+        <v>2026-07-17T17:20:56.999Z</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>INC000000150288</v>
+        <v>INC000000150141</v>
       </c>
       <c r="B330" s="1" t="d">
-        <v>2026-07-10T12:39:00.000Z</v>
+        <v>2026-07-15T16:30:22.000Z</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>INC000000150197</v>
+        <v>INC000000150288</v>
       </c>
       <c r="B331" s="1" t="d">
-        <v>2026-07-17T11:00:31.000Z</v>
+        <v>2026-07-10T12:39:00.000Z</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>WO0000000303791</v>
+        <v>INC000000150197</v>
       </c>
       <c r="B332" s="1" t="d">
-        <v>2026-07-15T12:32:15.000Z</v>
+        <v>2026-07-17T11:00:31.000Z</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>INC000000150475</v>
+        <v>WO0000000303791</v>
       </c>
       <c r="B333" s="1" t="d">
-        <v>2026-07-16T08:36:47.000Z</v>
+        <v>2026-07-15T12:32:15.000Z</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>WO0000000304256</v>
+        <v>INC000000150475</v>
       </c>
       <c r="B334" s="1" t="d">
-        <v>2026-07-16T12:20:08.000Z</v>
+        <v>2026-07-16T08:36:47.000Z</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>WO0000000304437</v>
+        <v>WO0000000304256</v>
       </c>
       <c r="B335" s="1" t="d">
-        <v>2026-07-16T12:22:04.999Z</v>
+        <v>2026-07-16T12:20:08.000Z</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>INC000000150630</v>
+        <v>WO0000000304437</v>
       </c>
       <c r="B336" s="1" t="d">
-        <v>2026-07-10T08:48:46.999Z</v>
+        <v>2026-07-16T12:22:04.999Z</v>
       </c>
     </row>
     <row r="337">
@@ -3123,154 +3123,154 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>WO0000000305312</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B341" s="1" t="d">
-        <v>2026-07-15T11:26:08.000Z</v>
+        <v>2026-07-16T09:01:40.000Z</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305312</v>
       </c>
       <c r="B342" s="1" t="d">
-        <v>2026-07-15T13:10:05.000Z</v>
+        <v>2026-07-15T11:26:08.000Z</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>INC000000150882</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B343" s="1" t="d">
-        <v>2026-07-15T10:45:04.000Z</v>
+        <v>2026-07-15T13:10:05.000Z</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>WO0000000305349</v>
+        <v>INC000000150882</v>
       </c>
       <c r="B344" s="1" t="d">
-        <v>2026-07-14T12:21:19.000Z</v>
+        <v>2026-07-15T10:45:04.000Z</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>WO0000000305815</v>
+        <v>WO0000000305349</v>
       </c>
       <c r="B345" s="1" t="d">
-        <v>2026-07-16T12:28:46.000Z</v>
+        <v>2026-07-14T12:21:19.000Z</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>WO0000000305843</v>
+        <v>WO0000000305815</v>
       </c>
       <c r="B346" s="1" t="d">
-        <v>2026-07-14T12:37:15.000Z</v>
+        <v>2026-07-16T12:28:46.000Z</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>WO0000000305743</v>
+        <v>WO0000000305843</v>
       </c>
       <c r="B347" s="1" t="d">
-        <v>2026-07-14T14:33:44.000Z</v>
+        <v>2026-07-14T12:37:15.000Z</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>INC000000151204</v>
+        <v>WO0000000305743</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2026-07-14T12:46:36.000Z</v>
+        <v>2026-07-14T14:33:44.000Z</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>WO0000000305944</v>
+        <v>INC000000151204</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2026-07-14T12:04:16.999Z</v>
+        <v>2026-07-14T12:46:36.000Z</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>INC000000151134</v>
+        <v>WO0000000305944</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2026-07-14T10:49:05.000Z</v>
+        <v>2026-07-14T12:04:16.999Z</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>INC000000151151</v>
+        <v>INC000000151134</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2026-07-16T08:22:24.000Z</v>
+        <v>2026-07-14T10:49:05.000Z</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>WO0000000306190</v>
+        <v>INC000000151151</v>
       </c>
       <c r="B352" s="1" t="d">
-        <v>2026-07-14T13:13:31.000Z</v>
+        <v>2026-07-16T08:22:24.000Z</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>WO0000000306290</v>
+        <v>WO0000000306190</v>
       </c>
       <c r="B353" s="1" t="d">
-        <v>2026-07-14T16:17:28.999Z</v>
+        <v>2026-07-14T13:13:31.000Z</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>WO0000000306328</v>
+        <v>WO0000000306290</v>
       </c>
       <c r="B354" s="1" t="d">
-        <v>2026-07-14T16:39:44.000Z</v>
+        <v>2026-07-14T16:17:28.999Z</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>INC000000151200</v>
+        <v>WO0000000306328</v>
       </c>
       <c r="B355" s="1" t="d">
-        <v>2026-07-10T10:51:56.000Z</v>
+        <v>2026-07-14T16:39:44.000Z</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>WO0000000306374</v>
+        <v>INC000000151200</v>
       </c>
       <c r="B356" s="1" t="d">
-        <v>2026-07-10T13:36:36.000Z</v>
+        <v>2026-07-10T10:51:56.000Z</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>WO0000000306439</v>
+        <v>WO0000000306374</v>
       </c>
       <c r="B357" s="1" t="d">
-        <v>2026-07-14T16:14:53.000Z</v>
+        <v>2026-07-10T13:36:36.000Z</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>WO0000000306534</v>
+        <v>WO0000000306439</v>
       </c>
       <c r="B358" s="1" t="d">
-        <v>2026-07-15T16:01:14.000Z</v>
+        <v>2026-07-14T16:14:53.000Z</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>WO0000000306610</v>
+        <v>WO0000000306534</v>
       </c>
       <c r="B359" s="1" t="d">
-        <v>2026-07-16T09:06:23.000Z</v>
+        <v>2026-07-15T16:01:14.000Z</v>
       </c>
     </row>
     <row r="360">
@@ -3715,1423 +3715,1423 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>WO0000000308240</v>
+        <v>WO0000000308194</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2026-07-17T14:41:09.000Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308196</v>
+        <v>WO0000000308255</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-17T14:51:24.000Z</v>
+        <v>2026-07-17T15:17:47.000Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308194</v>
+        <v>WO0000000308260</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-21T08:56:50.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>WO0000000308255</v>
+        <v>WO0000000308269</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-17T15:17:47.000Z</v>
+        <v>2026-07-16T12:15:01.000Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>WO0000000308260</v>
+        <v>WO0000000308273</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-16T12:44:38.000Z</v>
+        <v>2026-07-16T12:17:21.999Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308269</v>
+        <v>WO0000000308284</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-16T12:15:01.000Z</v>
+        <v>2026-07-16T08:08:24.000Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308273</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-16T12:17:21.999Z</v>
+        <v>2026-07-16T23:19:07.000Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308284</v>
+        <v>WO0000000308331</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-16T08:08:24.000Z</v>
+        <v>2026-07-17T16:57:45.000Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308416</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-16T23:19:07.000Z</v>
+        <v>2026-07-16T09:47:42.999Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308331</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-17T16:57:45.000Z</v>
+        <v>2026-07-21T09:00:49.000Z</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>WO0000000308416</v>
+        <v>WO0000000308432</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2026-07-16T09:47:42.999Z</v>
+        <v>2026-07-21T08:34:03.000Z</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308350</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>WO0000000308432</v>
+        <v>WO0000000308345</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2026-07-21T08:34:03.000Z</v>
+        <v>2026-07-21T08:44:29.000Z</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>WO0000000308350</v>
+        <v>WO0000000308442</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T08:56:50.000Z</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>WO0000000308345</v>
+        <v>WO0000000308360</v>
       </c>
       <c r="B429" s="1" t="d">
-        <v>2026-07-21T08:44:29.000Z</v>
+        <v>2026-07-16T12:54:40.000Z</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>WO0000000308442</v>
+        <v>WO0000000308457</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2026-07-17T14:15:20.000Z</v>
+        <v>2026-07-17T11:44:00.000Z</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>WO0000000308360</v>
+        <v>WO0000000308463</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-16T12:54:40.000Z</v>
+        <v>2026-07-17T11:56:09.000Z</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>WO0000000308457</v>
+        <v>WO0000000308374</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-17T11:44:00.000Z</v>
+        <v>2026-07-17T12:10:22.000Z</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>WO0000000308463</v>
+        <v>WO0000000308379</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-17T11:56:09.000Z</v>
+        <v>2026-07-15T17:07:55.000Z</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>WO0000000308374</v>
+        <v>WO0000000308383</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-17T12:10:22.000Z</v>
+        <v>2026-07-17T12:30:39.000Z</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>WO0000000308379</v>
+        <v>WO0000000308398</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2026-07-15T17:07:55.000Z</v>
+        <v>2026-07-16T08:57:27.000Z</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>WO0000000308383</v>
+        <v>WO0000000308399</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-17T12:30:39.000Z</v>
+        <v>2026-07-16T09:52:14.999Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>WO0000000308398</v>
+        <v>WO0000000308487</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-16T08:57:27.000Z</v>
+        <v>2026-07-15T22:21:47.000Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>WO0000000308399</v>
+        <v>WO0000000308503</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-16T09:52:14.999Z</v>
+        <v>2026-07-16T07:14:29.000Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>WO0000000308487</v>
+        <v>WO0000000308493</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-15T22:21:47.000Z</v>
+        <v>2026-07-17T12:30:42.000Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>WO0000000308503</v>
+        <v>INC000000152512</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-16T07:14:29.000Z</v>
+        <v>2026-07-16T08:10:32.999Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000308493</v>
+        <v>WO0000000272008</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-17T12:30:42.000Z</v>
+        <v>2026-07-21T09:04:16.999Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>INC000000152512</v>
+        <v>INC000000139655</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-16T08:10:32.999Z</v>
+        <v>2026-07-17T07:37:37.999Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000272008</v>
+        <v>INC000000139903</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-17T12:22:12.999Z</v>
+        <v>2026-07-17T07:37:04.000Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>INC000000139655</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-17T07:37:37.999Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>INC000000139903</v>
+        <v>INC000000140820</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-17T07:37:04.000Z</v>
+        <v>2026-07-17T07:35:42.000Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>INC000000140158</v>
+        <v>INC000000140821</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-17T07:34:57.000Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>INC000000140820</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-17T07:35:42.000Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>INC000000140821</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2026-07-17T07:34:57.000Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>INC000000140767</v>
+        <v>INC000000142421</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-17T07:33:48.000Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>INC000000142421</v>
+        <v>INC000000142515</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-17T07:33:48.000Z</v>
+        <v>2026-07-17T07:33:05.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>INC000000142515</v>
+        <v>WO0000000288110</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-17T07:33:05.000Z</v>
+        <v>2026-07-17T07:47:10.000Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WO0000000288110</v>
+        <v>INC000000143401</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-17T07:47:10.000Z</v>
+        <v>2026-07-17T07:32:06.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>INC000000143401</v>
+        <v>WO0000000292826</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-17T07:32:06.000Z</v>
+        <v>2026-07-17T07:30:34.000Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>WO0000000292826</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-17T07:30:34.000Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>WO0000000295598</v>
+        <v>WO0000000295688</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-16T09:17:24.999Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>WO0000000295688</v>
+        <v>WO0000000295716</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-16T09:17:24.999Z</v>
+        <v>2026-07-16T11:47:42.999Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>WO0000000295716</v>
+        <v>WO0000000295975</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-16T11:47:42.999Z</v>
+        <v>2026-07-17T07:46:27.000Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>WO0000000295975</v>
+        <v>INC000000146886</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-17T07:46:27.000Z</v>
+        <v>2026-07-16T13:10:02.999Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>INC000000146886</v>
+        <v>WO0000000296722</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-16T13:10:02.999Z</v>
+        <v>2026-07-17T07:44:32.000Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>WO0000000296722</v>
+        <v>WO0000000296723</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-17T07:44:32.000Z</v>
+        <v>2026-07-17T07:43:42.999Z</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>WO0000000296723</v>
+        <v>WO0000000297151</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-17T07:43:42.999Z</v>
+        <v>2026-07-17T07:42:36.000Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>WO0000000297151</v>
+        <v>WO0000000297156</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-17T07:42:36.000Z</v>
+        <v>2026-07-17T07:41:50.000Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>WO0000000297156</v>
+        <v>WO0000000297160</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-17T07:41:50.000Z</v>
+        <v>2026-07-17T07:40:23.999Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>WO0000000297160</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-17T07:40:23.999Z</v>
+        <v>2026-07-20T23:28:38.000Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>WO0000000298838</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-20T23:28:38.000Z</v>
+        <v>2026-07-17T14:59:50.999Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>WO0000000299920</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-17T14:59:50.999Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>WO0000000300081</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>INC000000148888</v>
+        <v>WO0000000300496</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-17T11:43:57.000Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>WO0000000300496</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-17T11:43:57.000Z</v>
+        <v>2026-07-17T12:11:40.000Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>WO0000000302331</v>
+        <v>WO0000000302520</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-17T12:11:40.000Z</v>
+        <v>2026-07-17T15:04:39.000Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>WO0000000302520</v>
+        <v>INC000000149827</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-17T15:04:39.000Z</v>
+        <v>2026-07-17T14:03:04.000Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>INC000000149827</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-17T14:03:04.000Z</v>
+        <v>2026-07-16T16:04:01.999Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>INC000000149757</v>
+        <v>INC000000149760</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-16T16:04:01.999Z</v>
+        <v>2026-07-17T07:52:31.999Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>INC000000149760</v>
+        <v>WO0000000303120</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-17T07:52:31.999Z</v>
+        <v>2026-07-17T07:38:45.000Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>WO0000000303120</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-17T07:38:45.000Z</v>
+        <v>2026-07-17T15:09:03.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-17T15:09:03.000Z</v>
+        <v>2026-07-17T15:04:54.000Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>WO0000000303244</v>
+        <v>WO0000000303459</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-17T15:04:54.000Z</v>
+        <v>2026-07-17T11:09:28.999Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>WO0000000303459</v>
+        <v>WO0000000303471</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-17T11:09:28.999Z</v>
+        <v>2026-07-16T14:24:05.000Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000303471</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-16T14:24:05.000Z</v>
+        <v>2026-07-16T12:40:48.000Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-16T12:40:48.000Z</v>
+        <v>2026-07-17T10:37:05.000Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-17T10:37:05.000Z</v>
+        <v>2026-07-17T10:37:33.000Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-17T10:37:33.000Z</v>
+        <v>2026-07-21T08:46:39.000Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WO0000000305009</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-21T08:46:18.000Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>WO0000000305131</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-21T08:46:39.000Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>WO0000000305138</v>
+        <v>INC000000150916</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-17T13:59:57.999Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>INC000000150748</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-16T09:01:40.000Z</v>
+        <v>2026-07-17T18:15:37.999Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>WO0000000305336</v>
+        <v>INC000000151036</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-16T16:01:20.999Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>INC000000150916</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-17T13:59:57.999Z</v>
+        <v>2026-07-16T10:45:43.999Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000150958</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-17T18:15:37.999Z</v>
+        <v>2026-07-17T07:47:57.999Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>INC000000151036</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-16T16:01:20.999Z</v>
+        <v>2026-07-21T08:44:19.000Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-16T10:45:43.999Z</v>
+        <v>2026-07-16T16:12:20.000Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>INC000000150958</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-17T07:47:57.999Z</v>
+        <v>2026-07-17T10:37:57.000Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>WO0000000305863</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-21T08:44:19.000Z</v>
+        <v>2026-07-17T11:07:27.000Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>WO0000000305877</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-16T16:12:20.000Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>WO0000000305769</v>
+        <v>WO0000000306127</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-17T10:37:57.000Z</v>
+        <v>2026-07-21T07:40:38.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>WO0000000305770</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-17T11:07:27.000Z</v>
+        <v>2026-07-17T19:09:33.000Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>INC000000151203</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-17T07:40:02.000Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>WO0000000306127</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-21T07:40:38.000Z</v>
+        <v>2026-07-17T14:41:03.000Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>INC000000151157</v>
+        <v>INC000000151311</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-17T19:09:33.000Z</v>
+        <v>2026-07-16T09:35:09.000Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>INC000000151271</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-17T07:40:02.000Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>WO0000000306256</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-17T14:41:03.000Z</v>
+        <v>2026-07-17T10:39:36.000Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>INC000000151311</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-16T09:35:09.000Z</v>
+        <v>2026-07-17T15:11:14.000Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>INC000000151313</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-17T10:39:57.000Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>WO0000000306718</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-17T10:39:36.000Z</v>
+        <v>2026-07-17T08:21:12.999Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>WO0000000306721</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-17T15:11:14.000Z</v>
+        <v>2026-07-17T19:07:47.000Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>WO0000000306726</v>
+        <v>INC000000151527</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-17T10:39:57.000Z</v>
+        <v>2026-07-17T16:34:54.000Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>WO0000000306799</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-17T08:21:12.999Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-17T19:07:47.000Z</v>
+        <v>2026-07-17T17:20:58.999Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>INC000000151527</v>
+        <v>WO0000000306877</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-17T16:34:54.000Z</v>
+        <v>2026-07-16T14:55:04.000Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>WO0000000306927</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-17T14:42:13.999Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-17T17:20:58.999Z</v>
+        <v>2026-07-17T17:44:23.000Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>WO0000000306877</v>
+        <v>WO0000000306992</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-16T14:55:04.000Z</v>
+        <v>2026-07-16T10:42:09.000Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>WO0000000306890</v>
+        <v>WO0000000306994</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-16T15:19:33.999Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>WO0000000306899</v>
+        <v>INC000000151586</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-17T17:44:23.000Z</v>
+        <v>2026-07-19T12:57:49.000Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>WO0000000306992</v>
+        <v>WO0000000307224</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-16T10:42:09.000Z</v>
+        <v>2026-07-16T16:04:39.999Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>WO0000000306994</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-16T15:19:33.999Z</v>
+        <v>2026-07-17T14:49:17.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>INC000000151586</v>
+        <v>INC000000151950</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-19T12:57:49.000Z</v>
+        <v>2026-07-16T09:20:32.000Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>WO0000000307224</v>
+        <v>INC000000151764</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-16T16:04:39.999Z</v>
+        <v>2026-07-16T10:00:04.000Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-17T14:49:17.000Z</v>
+        <v>2026-07-17T09:03:17.000Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>INC000000151950</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-16T09:20:32.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>INC000000151764</v>
+        <v>INC000000151987</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-16T10:00:04.000Z</v>
+        <v>2026-07-16T11:05:28.000Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>WO0000000307513</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-17T09:03:17.000Z</v>
+        <v>2026-07-17T14:43:30.000Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-17T14:02:15.000Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>INC000000151987</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-16T11:05:28.000Z</v>
+        <v>2026-07-17T16:21:08.000Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000307483</v>
+        <v>INC000000152000</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-17T14:43:30.000Z</v>
+        <v>2026-07-19T12:58:45.000Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-17T14:02:15.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-17T16:21:08.000Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>INC000000152000</v>
+        <v>WO0000000307636</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-19T12:58:45.000Z</v>
+        <v>2026-07-20T22:08:00.000Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000152045</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-16T10:52:09.000Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-16T11:24:53.999Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>WO0000000307636</v>
+        <v>WO0000000307669</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-20T22:08:00.000Z</v>
+        <v>2026-07-17T09:44:19.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>INC000000152045</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-16T10:52:09.000Z</v>
+        <v>2026-07-17T17:21:00.000Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-16T11:24:53.999Z</v>
+        <v>2026-07-17T15:11:48.000Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>WO0000000307669</v>
+        <v>WO0000000307729</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-16T12:57:39.999Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>WO0000000307703</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-17T17:21:00.000Z</v>
+        <v>2026-07-17T19:20:59.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>WO0000000307725</v>
+        <v>INC000000152073</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-17T15:11:48.000Z</v>
+        <v>2026-07-16T09:23:53.000Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>WO0000000307729</v>
+        <v>WO0000000307923</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-16T12:57:39.999Z</v>
+        <v>2026-07-16T09:23:33.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>INC000000152145</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-17T19:20:59.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>INC000000152073</v>
+        <v>WO0000000307963</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-16T09:23:53.000Z</v>
+        <v>2026-07-17T13:31:54.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000307923</v>
+        <v>WO0000000308029</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-16T09:23:33.000Z</v>
+        <v>2026-07-17T16:02:10.000Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>WO0000000307940</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>WO0000000307963</v>
+        <v>WO0000000308038</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-17T13:31:54.000Z</v>
+        <v>2026-07-17T13:48:01.000Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>WO0000000308029</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-17T16:02:10.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>INC000000152212</v>
+        <v>WO0000000307968</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-16T15:02:29.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>WO0000000308038</v>
+        <v>WO0000000307970</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-17T13:48:01.000Z</v>
+        <v>2026-07-16T16:55:20.000Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>WO0000000308040</v>
+        <v>WO0000000308041</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-17T09:02:42.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000307968</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-16T15:02:29.000Z</v>
+        <v>2026-07-20T23:34:20.999Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>WO0000000307970</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-16T16:55:20.000Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>WO0000000308041</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-17T09:02:42.000Z</v>
+        <v>2026-07-17T11:04:48.999Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>WO0000000308042</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-20T23:34:20.999Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-20T23:29:29.999Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>WO0000000308052</v>
+        <v>INC000000152328</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-17T11:04:48.999Z</v>
+        <v>2026-07-17T21:19:20.000Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-20T23:26:07.000Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>WO0000000308105</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-20T23:29:29.999Z</v>
+        <v>2026-07-20T23:30:10.000Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>INC000000152328</v>
+        <v>WO0000000308107</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-17T21:19:20.000Z</v>
+        <v>2026-07-20T23:27:09.999Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308075</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-20T23:26:07.000Z</v>
+        <v>2026-07-20T23:31:09.999Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>WO0000000308106</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-20T23:30:10.000Z</v>
+        <v>2026-07-17T14:44:25.000Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>WO0000000308107</v>
+        <v>WO0000000308215</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-20T23:27:09.999Z</v>
+        <v>2026-07-17T09:26:37.000Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000308216</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-20T23:31:09.999Z</v>
+        <v>2026-07-17T13:19:29.000Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>WO0000000308086</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-17T14:44:25.000Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000308215</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-17T09:26:37.000Z</v>
+        <v>2026-07-18T12:28:17.000Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>WO0000000308216</v>
+        <v>INC000000152358</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-17T13:19:29.000Z</v>
+        <v>2026-07-16T09:12:05.999Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000308169</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-17T14:18:27.000Z</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000308234</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-07-18T12:28:17.000Z</v>
+        <v>2026-07-19T12:53:47.000Z</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>INC000000152358</v>
+        <v>INC000000152251</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-07-16T09:12:05.999Z</v>
+        <v>2026-07-17T10:26:36.999Z</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>WO0000000308169</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-07-17T14:18:27.000Z</v>
+        <v>2026-07-17T16:39:09.000Z</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>WO0000000308234</v>
+        <v>WO0000000308196</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-07-19T12:53:47.000Z</v>
+        <v>2026-07-21T08:49:13.000Z</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>WO0000000308238</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-07-21T08:46:16.000Z</v>
+        <v>2026-07-17T12:34:20.000Z</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>INC000000152251</v>
+        <v>WO0000000308249</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-07-17T10:26:36.999Z</v>
+        <v>2026-07-17T13:34:27.999Z</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>INC000000152361</v>
+        <v>WO0000000308199</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-07-17T16:39:09.000Z</v>
+        <v>2026-07-17T13:37:19.000Z</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>WO0000000308197</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-07-17T12:34:20.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>WO0000000308249</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-07-17T13:34:27.999Z</v>
+        <v>2026-07-18T09:01:38.000Z</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>WO0000000308199</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-07-17T13:37:19.000Z</v>
+        <v>2026-07-18T12:40:57.999Z</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>INC000000152369</v>
+        <v>INC000000152378</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-07-17T10:42:03.000Z</v>
+        <v>2026-07-17T09:05:30.000Z</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>WO0000000308306</v>
+        <v>INC000000152262</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-07-18T09:01:38.000Z</v>
+        <v>2026-07-19T07:36:53.000Z</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308340</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-07-18T12:40:57.999Z</v>
+        <v>2026-07-16T09:24:24.999Z</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>INC000000152378</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-07-17T09:05:30.000Z</v>
+        <v>2026-07-18T12:08:23.000Z</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>INC000000152262</v>
+        <v>WO0000000308422</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-07-19T07:36:53.000Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>WO0000000308340</v>
+        <v>WO0000000308426</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-07-16T09:24:24.999Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308357</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-18T12:08:23.000Z</v>
+        <v>2026-07-21T08:46:37.999Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>WO0000000308422</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-16T10:44:20.999Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>WO0000000308426</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>WO0000000308357</v>
+        <v>WO0000000308366</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-07-21T08:46:37.999Z</v>
+        <v>2026-07-16T09:45:50.999Z</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308461</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-16T10:44:20.999Z</v>
+        <v>2026-07-16T18:43:27.999Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>INC000000152389</v>
+        <v>WO0000000308475</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-17T10:53:19.000Z</v>
+        <v>2026-07-17T12:30:37.999Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>WO0000000308366</v>
+        <v>WO0000000308478</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-16T09:45:50.999Z</v>
+        <v>2026-07-17T12:30:39.000Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>WO0000000308461</v>
+        <v>WO0000000308382</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-16T18:43:27.999Z</v>
+        <v>2026-07-17T12:30:40.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>WO0000000308475</v>
+        <v>WO0000000308380</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-17T12:30:40.000Z</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>WO0000000308478</v>
+        <v>WO0000000308396</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-17T12:30:39.000Z</v>
+        <v>2026-07-17T12:30:41.000Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>WO0000000308382</v>
+        <v>WO0000000308495</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-17T12:30:40.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>WO0000000308380</v>
+        <v>INC000000152419</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-07-17T12:30:40.000Z</v>
+        <v>2026-07-21T08:54:50.000Z</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>WO0000000308396</v>
+        <v>WO0000000308506</v>
       </c>
       <c r="B592" s="1" t="d">
         <v>2026-07-17T12:30:41.000Z</v>
@@ -5139,4916 +5139,4956 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>WO0000000308495</v>
+        <v>INC000000152439</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-16T13:12:03.000Z</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>INC000000152419</v>
+        <v>INC000000152513</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-07-18T04:58:58.000Z</v>
+        <v>2026-07-16T09:23:02.000Z</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>WO0000000308506</v>
+        <v>WO0000000308624</v>
       </c>
       <c r="B595" s="1" t="d">
-        <v>2026-07-17T12:30:41.000Z</v>
+        <v>2026-07-17T12:45:01.000Z</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>INC000000152439</v>
+        <v>INC000000152517</v>
       </c>
       <c r="B596" s="1" t="d">
-        <v>2026-07-16T13:12:03.000Z</v>
+        <v>2026-07-17T10:21:00.000Z</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>INC000000152513</v>
+        <v>INC000000152450</v>
       </c>
       <c r="B597" s="1" t="d">
-        <v>2026-07-16T09:23:02.000Z</v>
+        <v>2026-07-17T13:17:48.000Z</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>WO0000000308624</v>
+        <v>WO0000000308552</v>
       </c>
       <c r="B598" s="1" t="d">
-        <v>2026-07-17T12:45:01.000Z</v>
+        <v>2026-07-16T09:20:55.000Z</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>INC000000152517</v>
+        <v>INC000000152537</v>
       </c>
       <c r="B599" s="1" t="d">
-        <v>2026-07-17T10:21:00.000Z</v>
+        <v>2026-07-17T10:03:46.000Z</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>INC000000152450</v>
+        <v>WO0000000308647</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-07-17T13:17:48.000Z</v>
+        <v>2026-07-17T13:39:57.999Z</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>WO0000000308552</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-16T09:20:55.000Z</v>
+        <v>2026-07-17T15:09:40.000Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>INC000000152537</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-17T10:03:46.000Z</v>
+        <v>2026-07-16T09:22:57.000Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>WO0000000308647</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-17T13:39:57.999Z</v>
+        <v>2026-07-18T12:29:14.000Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>WO0000000308648</v>
+        <v>INC000000152458</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-17T15:09:40.000Z</v>
+        <v>2026-07-17T14:55:27.000Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-07-16T09:22:57.000Z</v>
+        <v>2026-07-17T14:10:20.000Z</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000308661</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-18T12:29:14.000Z</v>
+        <v>2026-07-17T14:16:26.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>INC000000152458</v>
+        <v>WO0000000308662</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-17T14:55:27.000Z</v>
+        <v>2026-07-16T14:23:41.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000308585</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-17T14:10:20.000Z</v>
+        <v>2026-07-16T14:22:46.000Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>WO0000000308580</v>
+        <v>INC000000152461</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-17T14:14:23.000Z</v>
+        <v>2026-07-20T09:23:43.999Z</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>WO0000000308661</v>
+        <v>WO0000000308673</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-07-17T14:16:26.000Z</v>
+        <v>2026-07-16T10:02:00.999Z</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>WO0000000308662</v>
+        <v>WO0000000308679</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-07-16T14:23:41.000Z</v>
+        <v>2026-07-17T14:36:57.000Z</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>WO0000000308585</v>
+        <v>WO0000000308675</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-07-16T14:22:46.000Z</v>
+        <v>2026-07-17T07:31:47.000Z</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>INC000000152461</v>
+        <v>WO0000000308685</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-07-20T09:23:43.999Z</v>
+        <v>2026-07-16T10:12:45.000Z</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>WO0000000308673</v>
+        <v>WO0000000308596</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-07-16T10:02:00.999Z</v>
+        <v>2026-07-16T10:19:52.000Z</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>WO0000000308679</v>
+        <v>WO0000000308701</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-07-17T14:36:57.000Z</v>
+        <v>2026-07-16T10:22:52.000Z</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>WO0000000308675</v>
+        <v>WO0000000308696</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-07-17T07:31:47.000Z</v>
+        <v>2026-07-17T11:22:11.000Z</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>WO0000000308685</v>
+        <v>WO0000000308698</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-07-16T10:12:45.000Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>WO0000000308596</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-07-16T10:19:52.000Z</v>
+        <v>2026-07-16T10:42:24.000Z</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>INC000000152551</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-07-17T15:41:42.000Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>WO0000000308701</v>
+        <v>WO0000000308712</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-07-16T10:22:52.000Z</v>
+        <v>2026-07-17T09:16:22.999Z</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-07-17T11:22:11.000Z</v>
+        <v>2026-07-16T10:40:08.000Z</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>WO0000000308698</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-07-17T15:31:29.000Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>WO0000000308697</v>
+        <v>INC000000152561</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-07-21T08:23:28.999Z</v>
+        <v>2026-07-17T16:04:19.000Z</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>WO0000000308695</v>
+        <v>WO0000000308717</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-07-16T10:42:24.000Z</v>
+        <v>2026-07-16T12:45:40.000Z</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-16T10:46:41.000Z</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>WO0000000308712</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-07-17T09:16:22.999Z</v>
+        <v>2026-07-20T19:01:19.000Z</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-07-16T10:40:08.000Z</v>
+        <v>2026-07-17T16:49:36.000Z</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>WO0000000308715</v>
+        <v>INC000000152565</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-21T07:47:38.999Z</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>INC000000152561</v>
+        <v>WO0000000308727</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-07-17T16:04:19.000Z</v>
+        <v>2026-07-17T09:34:42.000Z</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-07-16T12:45:40.000Z</v>
+        <v>2026-07-21T08:53:31.000Z</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308808</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-07-16T10:46:41.000Z</v>
+        <v>2026-07-17T16:59:44.999Z</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308809</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-07-20T19:01:19.000Z</v>
+        <v>2026-07-16T11:14:01.000Z</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>WO0000000308723</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-07-17T16:49:36.000Z</v>
+        <v>2026-07-17T15:18:13.000Z</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>INC000000152565</v>
+        <v>WO0000000308814</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-07-21T07:47:38.999Z</v>
+        <v>2026-07-17T15:46:22.000Z</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>WO0000000308727</v>
+        <v>WO0000000308742</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-07-17T09:34:42.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000308816</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-07-18T10:23:16.000Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000308743</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-07-17T16:59:44.999Z</v>
+        <v>2026-07-17T15:54:32.000Z</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>WO0000000308809</v>
+        <v>INC000000152477</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-07-16T11:14:01.000Z</v>
+        <v>2026-07-16T12:12:43.000Z</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>INC000000152566</v>
+        <v>WO0000000308749</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-07-17T15:18:13.000Z</v>
+        <v>2026-07-17T16:02:35.000Z</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>WO0000000308814</v>
+        <v>WO0000000308750</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-07-17T15:46:22.000Z</v>
+        <v>2026-07-17T16:02:36.000Z</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>WO0000000308742</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-17T08:38:07.000Z</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>WO0000000308816</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B642" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-16T14:25:41.000Z</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>WO0000000308743</v>
+        <v>WO0000000308755</v>
       </c>
       <c r="B643" s="1" t="d">
-        <v>2026-07-17T15:54:32.000Z</v>
+        <v>2026-07-16T11:35:09.000Z</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>INC000000152477</v>
+        <v>WO0000000308826</v>
       </c>
       <c r="B644" s="1" t="d">
-        <v>2026-07-16T12:12:43.000Z</v>
+        <v>2026-07-17T16:08:41.000Z</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>WO0000000308749</v>
+        <v>WO0000000308817</v>
       </c>
       <c r="B645" s="1" t="d">
-        <v>2026-07-17T16:02:35.000Z</v>
+        <v>2026-07-17T16:14:46.000Z</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>WO0000000308750</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B646" s="1" t="d">
-        <v>2026-07-17T16:02:36.000Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000308758</v>
       </c>
       <c r="B647" s="1" t="d">
-        <v>2026-07-17T08:38:07.000Z</v>
+        <v>2026-07-17T16:16:51.999Z</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>INC000000152573</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B648" s="1" t="d">
-        <v>2026-07-17T14:55:45.999Z</v>
+        <v>2026-07-17T16:19:03.000Z</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>WO0000000308754</v>
+        <v>WO0000000308851</v>
       </c>
       <c r="B649" s="1" t="d">
-        <v>2026-07-16T14:25:41.000Z</v>
+        <v>2026-07-17T16:37:20.999Z</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>WO0000000308755</v>
+        <v>INC000000152486</v>
       </c>
       <c r="B650" s="1" t="d">
-        <v>2026-07-16T11:35:09.000Z</v>
+        <v>2026-07-21T07:42:45.999Z</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>WO0000000308826</v>
+        <v>WO0000000308860</v>
       </c>
       <c r="B651" s="1" t="d">
-        <v>2026-07-17T16:08:41.000Z</v>
+        <v>2026-07-17T16:51:40.000Z</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>WO0000000308817</v>
+        <v>WO0000000308862</v>
       </c>
       <c r="B652" s="1" t="d">
-        <v>2026-07-17T16:14:46.000Z</v>
+        <v>2026-07-17T17:46:11.000Z</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B653" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-21T08:00:16.000Z</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>WO0000000308758</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B654" s="1" t="d">
-        <v>2026-07-17T16:16:51.999Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>WO0000000308834</v>
+        <v>WO0000000308868</v>
       </c>
       <c r="B655" s="1" t="d">
-        <v>2026-07-17T16:19:03.000Z</v>
+        <v>2026-07-21T08:27:45.999Z</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>WO0000000308851</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B656" s="1" t="d">
-        <v>2026-07-17T16:37:20.999Z</v>
+        <v>2026-07-16T14:39:36.999Z</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>INC000000152486</v>
+        <v>INC000000152496</v>
       </c>
       <c r="B657" s="1" t="d">
-        <v>2026-07-21T07:42:45.999Z</v>
+        <v>2026-07-17T18:33:44.000Z</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>WO0000000308860</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B658" s="1" t="d">
-        <v>2026-07-17T16:51:40.000Z</v>
+        <v>2026-07-17T09:53:56.000Z</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>WO0000000308862</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B659" s="1" t="d">
-        <v>2026-07-17T17:46:11.000Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000152594</v>
       </c>
       <c r="B660" s="1" t="d">
-        <v>2026-07-21T08:00:16.000Z</v>
+        <v>2026-07-20T13:46:11.000Z</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>INC000000152586</v>
+        <v>WO0000000308905</v>
       </c>
       <c r="B661" s="1" t="d">
-        <v>2026-07-17T10:46:28.000Z</v>
+        <v>2026-07-16T14:04:26.000Z</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>WO0000000308868</v>
+        <v>WO0000000308880</v>
       </c>
       <c r="B662" s="1" t="d">
-        <v>2026-07-21T08:27:45.999Z</v>
+        <v>2026-07-17T14:08:19.000Z</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>WO0000000308873</v>
+        <v>WO0000000308912</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-16T14:39:36.999Z</v>
+        <v>2026-07-16T14:18:19.000Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>INC000000152496</v>
+        <v>INC000000152598</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-17T18:33:44.000Z</v>
+        <v>2026-07-17T10:04:25.000Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000308794</v>
+        <v>WO0000000308913</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-17T09:53:56.000Z</v>
+        <v>2026-07-17T08:38:16.000Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>INC000000152591</v>
+        <v>WO0000000308917</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-17T11:00:29.999Z</v>
+        <v>2026-07-17T07:59:19.999Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>INC000000152594</v>
+        <v>WO0000000308918</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-20T13:46:11.000Z</v>
+        <v>2026-07-17T14:34:52.999Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>WO0000000308905</v>
+        <v>WO0000000308919</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-16T14:04:26.000Z</v>
+        <v>2026-07-16T14:36:18.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>WO0000000308880</v>
+        <v>WO0000000308923</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-17T14:08:19.000Z</v>
+        <v>2026-07-16T17:34:43.000Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>WO0000000308912</v>
+        <v>INC000000152608</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-16T14:18:19.000Z</v>
+        <v>2026-07-17T15:48:10.000Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>INC000000152598</v>
+        <v>WO0000000308895</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-17T10:04:25.000Z</v>
+        <v>2026-07-17T10:35:42.000Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000308913</v>
+        <v>WO0000000308896</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-17T08:38:16.000Z</v>
+        <v>2026-07-16T15:16:25.000Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>WO0000000308917</v>
+        <v>WO0000000309001</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-17T07:59:19.999Z</v>
+        <v>2026-07-17T08:09:22.000Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000308918</v>
+        <v>WO0000000309004</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-17T14:34:52.999Z</v>
+        <v>2026-07-16T14:55:40.999Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000308919</v>
+        <v>WO0000000308899</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-16T14:36:18.000Z</v>
+        <v>2026-07-16T15:17:36.000Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>INC000000152604</v>
+        <v>WO0000000308926</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-17T08:49:27.000Z</v>
+        <v>2026-07-17T10:04:52.000Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>WO0000000308923</v>
+        <v>WO0000000309007</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-16T17:34:43.000Z</v>
+        <v>2026-07-16T15:03:12.000Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>INC000000152608</v>
+        <v>WO0000000309009</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-17T15:48:10.000Z</v>
+        <v>2026-07-21T08:15:25.000Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>WO0000000308895</v>
+        <v>WO0000000309002</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-17T10:35:42.000Z</v>
+        <v>2026-07-16T15:07:58.000Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000308896</v>
+        <v>WO0000000309011</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-16T15:16:25.000Z</v>
+        <v>2026-07-17T10:44:02.999Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>WO0000000309001</v>
+        <v>INC000000152616</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-17T08:09:22.000Z</v>
+        <v>2026-07-17T09:51:34.000Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>WO0000000309004</v>
+        <v>WO0000000308938</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-16T14:55:40.999Z</v>
+        <v>2026-07-16T15:31:18.000Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000308899</v>
+        <v>WO0000000309018</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-16T15:17:36.000Z</v>
+        <v>2026-07-16T15:30:08.999Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>WO0000000308926</v>
+        <v>WO0000000309021</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-17T10:04:52.000Z</v>
+        <v>2026-07-17T09:59:10.000Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>WO0000000309007</v>
+        <v>INC000000152711</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-16T15:03:12.000Z</v>
+        <v>2026-07-16T16:04:14.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>WO0000000309009</v>
+        <v>WO0000000309024</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-21T08:15:25.000Z</v>
+        <v>2026-07-16T15:43:10.000Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>WO0000000309002</v>
+        <v>WO0000000308947</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-17T10:21:08.000Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000309011</v>
+        <v>WO0000000309026</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-17T10:44:02.999Z</v>
+        <v>2026-07-16T15:49:08.000Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>INC000000152616</v>
+        <v>WO0000000309025</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-17T09:51:34.000Z</v>
+        <v>2026-07-16T15:47:35.000Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>WO0000000308938</v>
+        <v>WO0000000309028</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-17T15:14:51.999Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>WO0000000309018</v>
+        <v>WO0000000309031</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-16T15:30:08.999Z</v>
+        <v>2026-07-16T15:52:24.000Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000309021</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-17T09:59:10.000Z</v>
+        <v>2026-07-17T16:59:46.000Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>INC000000152711</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-16T16:04:14.000Z</v>
+        <v>2026-07-16T16:05:14.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>WO0000000309024</v>
+        <v>WO0000000309039</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-16T15:43:10.000Z</v>
+        <v>2026-07-17T08:39:45.999Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>WO0000000308947</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-17T10:21:08.000Z</v>
+        <v>2026-07-17T16:15:11.000Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>WO0000000309026</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-16T15:49:08.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000309025</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>WO0000000309028</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-17T15:14:51.999Z</v>
+        <v>2026-07-18T14:29:17.000Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-16T15:52:24.000Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308967</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-17T16:59:46.000Z</v>
+        <v>2026-07-16T17:35:59.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>WO0000000309036</v>
+        <v>INC000000152630</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-21T07:35:42.000Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000309044</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-17T08:39:45.999Z</v>
+        <v>2026-07-16T16:26:35.999Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-17T16:15:11.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>INC000000152628</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-17T10:44:38.000Z</v>
+        <v>2026-07-16T16:32:21.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>WO0000000308964</v>
+        <v>WO0000000309047</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-16T17:25:44.000Z</v>
+        <v>2026-07-16T16:37:18.000Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>WO0000000309041</v>
+        <v>WO0000000308970</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-16T16:38:04.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-18T14:29:17.000Z</v>
+        <v>2026-07-16T16:43:04.000Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>WO0000000308966</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>WO0000000308967</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-16T17:35:59.000Z</v>
+        <v>2026-07-17T07:16:12.000Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>INC000000152630</v>
+        <v>WO0000000309052</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-21T07:35:42.000Z</v>
+        <v>2026-07-17T07:44:17.000Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000308984</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-16T16:26:35.999Z</v>
+        <v>2026-07-16T17:10:27.000Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000309060</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-16T22:04:20.000Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000309062</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-16T16:32:21.000Z</v>
+        <v>2026-07-17T10:25:11.000Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>WO0000000309047</v>
+        <v>WO0000000309063</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-16T16:37:18.000Z</v>
+        <v>2026-07-16T17:31:20.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>WO0000000308970</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-16T16:38:04.000Z</v>
+        <v>2026-07-21T07:53:18.000Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>WO0000000308975</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-16T16:43:04.000Z</v>
+        <v>2026-07-16T19:52:29.999Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>WO0000000309050</v>
+        <v>WO0000000309065</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000305262</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-17T07:16:12.000Z</v>
+        <v>2026-07-17T07:53:28.999Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>WO0000000309052</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-17T07:44:17.000Z</v>
+        <v>2026-07-16T19:32:50.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>WO0000000308984</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-16T17:10:27.000Z</v>
+        <v>2026-07-21T07:53:32.000Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000309060</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B721" s="1" t="d">
-        <v>2026-07-16T22:04:20.000Z</v>
+        <v>2026-07-16T19:42:22.000Z</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>WO0000000309062</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-17T10:25:11.000Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>WO0000000309063</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-16T17:31:20.000Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-21T07:53:18.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000308987</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-16T19:52:29.999Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>WO0000000309065</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-17T10:15:24.000Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>WO0000000305262</v>
+        <v>WO0000000309082</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-17T07:53:28.999Z</v>
+        <v>2026-07-17T09:36:16.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>WO0000000309073</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-16T19:32:50.000Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>INC000000152643</v>
+        <v>WO0000000309084</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-21T07:53:32.000Z</v>
+        <v>2026-07-17T10:26:01.000Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>WO0000000309074</v>
+        <v>INC000000152731</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-16T19:42:22.000Z</v>
+        <v>2026-07-17T10:29:59.000Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>WO0000000309077</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-17T06:53:11.000Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>WO0000000309079</v>
+        <v>INC000000152653</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-18T16:16:07.999Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000309097</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T08:03:06.999Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>WO0000000308997</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-17T08:06:35.000Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>WO0000000308999</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-17T10:15:24.000Z</v>
+        <v>2026-07-17T07:45:37.999Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>WO0000000309082</v>
+        <v>INC000000152739</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-17T09:36:16.000Z</v>
+        <v>2026-07-17T09:20:05.999Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-17T08:07:23.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>WO0000000309084</v>
+        <v>WO0000000309131</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-17T10:26:01.000Z</v>
+        <v>2026-07-17T08:12:37.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>INC000000152731</v>
+        <v>WO0000000309212</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-17T10:29:59.000Z</v>
+        <v>2026-07-17T15:11:51.000Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>INC000000152733</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-21T09:04:31.000Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>INC000000152653</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-18T16:16:07.999Z</v>
+        <v>2026-07-17T11:36:59.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>WO0000000309097</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-17T08:03:06.999Z</v>
+        <v>2026-07-17T12:44:26.000Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>INC000000152737</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-17T08:06:35.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>WO0000000309124</v>
+        <v>INC000000152746</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-17T07:45:37.999Z</v>
+        <v>2026-07-17T10:32:57.999Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>INC000000152739</v>
+        <v>WO0000000309153</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-17T09:20:05.999Z</v>
+        <v>2026-07-21T08:54:48.000Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-17T08:07:23.000Z</v>
+        <v>2026-07-17T08:54:14.000Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>WO0000000309131</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-17T08:12:37.000Z</v>
+        <v>2026-07-17T08:54:36.999Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>WO0000000309212</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-17T15:11:51.000Z</v>
+        <v>2026-07-18T12:40:15.000Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>WO0000000309136</v>
+        <v>WO0000000309226</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-17T08:53:07.999Z</v>
+        <v>2026-07-17T08:58:32.999Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-17T11:36:59.000Z</v>
+        <v>2026-07-17T14:29:04.000Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>INC000000152663</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-17T12:44:26.000Z</v>
+        <v>2026-07-17T09:57:18.999Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>INC000000152664</v>
+        <v>INC000000152673</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-21T08:52:59.000Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>WO0000000309216</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-21T08:30:12.999Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>INC000000152746</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-17T10:32:57.999Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>WO0000000309153</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-17T09:57:37.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-17T08:54:14.000Z</v>
+        <v>2026-07-17T14:47:59.000Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>WO0000000309155</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-17T08:54:36.999Z</v>
+        <v>2026-07-17T09:26:58.999Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-18T12:40:15.000Z</v>
+        <v>2026-07-17T12:06:25.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>WO0000000309226</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-17T08:58:32.999Z</v>
+        <v>2026-07-17T15:50:55.000Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>WO0000000309231</v>
+        <v>WO0000000309246</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-17T14:29:04.000Z</v>
+        <v>2026-07-17T09:32:32.000Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309167</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-21T08:57:56.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>INC000000152673</v>
+        <v>INC000000152761</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-21T08:25:17.000Z</v>
+        <v>2026-07-17T10:05:32.000Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-17T09:36:30.000Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-17T09:37:50.000Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>INC000000152674</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>WO0000000309164</v>
+        <v>WO0000000309249</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-17T14:47:59.000Z</v>
+        <v>2026-07-17T09:38:10.000Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-17T09:26:58.999Z</v>
+        <v>2026-07-17T09:54:11.000Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>INC000000152678</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-17T12:06:25.000Z</v>
+        <v>2026-07-21T08:45:24.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>INC000000152679</v>
+        <v>WO0000000309251</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-17T15:50:55.000Z</v>
+        <v>2026-07-17T09:40:19.000Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>WO0000000309246</v>
+        <v>INC000000152763</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-17T09:32:32.000Z</v>
+        <v>2026-07-17T10:09:48.000Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>WO0000000309167</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-17T14:49:27.000Z</v>
+        <v>2026-07-21T08:17:56.000Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>INC000000152761</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-17T10:05:32.000Z</v>
+        <v>2026-07-17T09:57:50.000Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309168</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-17T09:36:30.000Z</v>
+        <v>2026-07-17T11:14:20.000Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-17T09:37:50.000Z</v>
+        <v>2026-07-17T14:47:53.999Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>WO0000000309172</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-17T11:11:39.000Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>WO0000000309249</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-17T11:15:36.000Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>WO0000000309250</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-17T09:54:11.000Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>INC000000152760</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-21T08:45:24.000Z</v>
+        <v>2026-07-17T11:13:13.000Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>WO0000000309251</v>
+        <v>INC000000152688</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-17T09:40:19.000Z</v>
+        <v>2026-07-21T08:15:27.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>INC000000152763</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-17T10:09:48.000Z</v>
+        <v>2026-07-17T15:17:55.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-21T08:17:56.000Z</v>
+        <v>2026-07-17T10:18:38.000Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309254</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-17T09:57:50.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>WO0000000309187</v>
+        <v>INC000000152770</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-17T11:14:20.000Z</v>
+        <v>2026-07-17T10:27:03.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000305263</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-17T14:47:53.999Z</v>
+        <v>2026-07-17T15:28:33.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-17T11:11:39.000Z</v>
+        <v>2026-07-17T11:24:41.000Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000309189</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-17T11:15:36.000Z</v>
+        <v>2026-07-17T10:29:44.000Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>WO0000000309258</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-17T11:25:20.000Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>WO0000000309259</v>
+        <v>INC000000152691</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-17T11:13:13.000Z</v>
+        <v>2026-07-17T11:21:16.000Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>INC000000152688</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-21T08:15:27.000Z</v>
+        <v>2026-07-17T12:51:35.000Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>INC000000152768</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-17T15:17:55.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>WO0000000309262</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-17T10:18:38.000Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>INC000000152690</v>
+        <v>WO0000000309269</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-17T11:19:32.000Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>INC000000152770</v>
+        <v>WO0000000309270</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-17T10:27:03.000Z</v>
+        <v>2026-07-17T16:48:27.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>WO0000000305263</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-17T15:28:33.000Z</v>
+        <v>2026-07-17T14:48:08.000Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>WO0000000309195</v>
+        <v>INC000000152694</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-17T11:24:41.000Z</v>
+        <v>2026-07-18T13:02:06.999Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>INC000000152772</v>
+        <v>WO0000000309407</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-17T10:29:44.000Z</v>
+        <v>2026-07-17T10:43:38.999Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-17T11:25:20.000Z</v>
+        <v>2026-07-19T12:51:55.999Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>INC000000152691</v>
+        <v>WO0000000309409</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-17T11:21:16.000Z</v>
+        <v>2026-07-17T11:23:02.000Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000309199</v>
+        <v>WO0000000309277</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-17T12:51:35.000Z</v>
+        <v>2026-07-17T10:50:48.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>WO0000000309200</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-21T08:19:28.999Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-17T10:48:35.999Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000309269</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-17T11:19:32.000Z</v>
+        <v>2026-07-17T10:53:18.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000309270</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-17T16:48:27.000Z</v>
+        <v>2026-07-17T12:28:53.000Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>WO0000000309271</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-17T14:48:08.000Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>INC000000152694</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-18T13:02:06.999Z</v>
+        <v>2026-07-17T10:58:23.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309407</v>
+        <v>WO0000000309285</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-17T10:57:51.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>INC000000152777</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-19T12:51:55.999Z</v>
+        <v>2026-07-17T11:48:14.000Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>WO0000000309409</v>
+        <v>INC000000152782</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-17T11:23:02.000Z</v>
+        <v>2026-07-17T11:46:20.999Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>WO0000000309277</v>
+        <v>WO0000000309417</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-17T10:50:48.000Z</v>
+        <v>2026-07-17T11:02:34.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>WO0000000309410</v>
+        <v>INC000000152700</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-21T08:19:28.999Z</v>
+        <v>2026-07-17T18:10:18.000Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-17T10:48:35.999Z</v>
+        <v>2026-07-18T08:52:20.999Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-17T10:53:18.000Z</v>
+        <v>2026-07-17T11:12:43.000Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309291</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-17T12:28:53.000Z</v>
+        <v>2026-07-17T11:55:44.999Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>WO0000000309282</v>
+        <v>INC000000152784</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-17T11:26:12.000Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-17T10:58:23.000Z</v>
+        <v>2026-07-17T11:15:48.000Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>WO0000000309285</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-17T10:57:51.000Z</v>
+        <v>2026-07-17T11:17:12.999Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>INC000000152802</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-17T11:48:14.000Z</v>
+        <v>2026-07-17T14:48:17.000Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>INC000000152782</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-17T11:46:20.999Z</v>
+        <v>2026-07-17T11:21:58.000Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>WO0000000309417</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-17T11:02:34.000Z</v>
+        <v>2026-07-17T11:50:50.000Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>INC000000152700</v>
+        <v>WO0000000309432</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-17T18:10:18.000Z</v>
+        <v>2026-07-17T11:29:50.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-18T08:52:20.999Z</v>
+        <v>2026-07-17T11:26:05.999Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309299</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-17T11:12:43.000Z</v>
+        <v>2026-07-17T11:28:13.000Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>WO0000000309291</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-17T11:55:44.999Z</v>
+        <v>2026-07-17T11:29:56.000Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>INC000000152784</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-17T11:26:12.000Z</v>
+        <v>2026-07-17T16:49:37.000Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309439</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-17T11:15:48.000Z</v>
+        <v>2026-07-17T11:59:55.999Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-17T11:17:12.999Z</v>
+        <v>2026-07-17T15:38:05.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>WO0000000309295</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-17T14:48:17.000Z</v>
+        <v>2026-07-17T12:04:35.000Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>WO0000000309430</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-17T11:21:58.000Z</v>
+        <v>2026-07-18T12:02:37.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-17T11:50:50.000Z</v>
+        <v>2026-07-17T11:41:41.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>WO0000000309432</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-17T11:29:50.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>WO0000000309433</v>
+        <v>WO0000000309504</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-17T11:26:05.999Z</v>
+        <v>2026-07-17T11:39:29.000Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>WO0000000309299</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-17T11:28:13.000Z</v>
+        <v>2026-07-17T15:32:46.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309444</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-17T11:29:56.000Z</v>
+        <v>2026-07-17T11:41:48.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000309438</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-17T16:49:37.000Z</v>
+        <v>2026-07-17T11:44:22.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>WO0000000309439</v>
+        <v>INC000000152810</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-17T11:59:55.999Z</v>
+        <v>2026-07-21T07:51:23.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>WO0000000309503</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-17T15:38:05.000Z</v>
+        <v>2026-07-17T11:53:25.999Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>INC000000152789</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-17T12:04:35.000Z</v>
+        <v>2026-07-21T08:25:47.000Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-18T12:02:37.000Z</v>
+        <v>2026-07-17T11:55:31.000Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-17T11:41:41.000Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-17T14:48:03.000Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000309504</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-17T11:39:29.000Z</v>
+        <v>2026-07-17T15:45:57.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000309441</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-17T15:32:46.000Z</v>
+        <v>2026-07-17T14:48:13.000Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>WO0000000309444</v>
+        <v>INC000000152797</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-17T11:41:48.000Z</v>
+        <v>2026-07-21T08:59:18.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000309445</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-18T00:08:12.000Z</v>
+        <v>2026-07-18T08:52:31.000Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000309447</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-17T11:44:22.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>INC000000152810</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-21T07:51:23.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000309509</v>
+        <v>INC000000152800</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-17T11:53:25.999Z</v>
+        <v>2026-07-21T06:37:05.999Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-21T08:25:47.000Z</v>
+        <v>2026-07-17T12:23:35.999Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-17T11:55:31.000Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>WO0000000309513</v>
+        <v>INC000000152901</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T12:30:00.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309466</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-17T14:48:03.000Z</v>
+        <v>2026-07-17T12:32:56.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>WO0000000309515</v>
+        <v>INC000000152813</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-17T15:45:57.000Z</v>
+        <v>2026-07-17T12:36:17.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000309457</v>
+        <v>WO0000000309525</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-17T14:48:13.000Z</v>
+        <v>2026-07-17T16:15:45.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>INC000000152797</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-17T12:08:01.000Z</v>
+        <v>2026-07-17T17:44:41.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309526</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-18T08:52:31.000Z</v>
+        <v>2026-07-21T08:25:19.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>WO0000000309514</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-21T08:14:01.000Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>WO0000000309462</v>
+        <v>INC000000152814</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-17T12:49:52.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>INC000000152800</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-21T06:37:05.999Z</v>
+        <v>2026-07-20T13:33:22.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>WO0000000309465</v>
+        <v>WO0000000309478</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-17T12:23:35.999Z</v>
+        <v>2026-07-17T15:55:47.000Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>WO0000000309520</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-17T12:55:06.999Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>INC000000152901</v>
+        <v>WO0000000309534</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-17T12:30:00.000Z</v>
+        <v>2026-07-17T13:00:45.000Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>WO0000000309466</v>
+        <v>INC000000152910</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-17T12:32:56.000Z</v>
+        <v>2026-07-21T07:51:47.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>INC000000152813</v>
+        <v>INC000000152815</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-17T12:36:17.000Z</v>
+        <v>2026-07-17T21:20:43.999Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000309525</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-17T16:15:45.000Z</v>
+        <v>2026-07-17T15:49:27.999Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>INC000000152903</v>
+        <v>WO0000000309488</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-17T17:44:41.000Z</v>
+        <v>2026-07-17T13:20:57.999Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>WO0000000309526</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-21T08:25:19.000Z</v>
+        <v>2026-07-21T08:46:11.000Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>WO0000000309527</v>
+        <v>WO0000000309541</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-17T12:41:12.999Z</v>
+        <v>2026-07-17T13:27:09.000Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>WO0000000309470</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-21T08:14:01.000Z</v>
+        <v>2026-07-18T01:16:50.999Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>INC000000152814</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-17T12:49:52.000Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>WO0000000309530</v>
+        <v>INC000000152915</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-17T12:49:35.999Z</v>
+        <v>2026-07-18T12:02:15.999Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-20T13:33:22.000Z</v>
+        <v>2026-07-21T08:45:58.000Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000309478</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-17T15:55:47.000Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309545</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-17T12:55:06.999Z</v>
+        <v>2026-07-21T07:54:44.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>WO0000000309534</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-17T13:00:45.000Z</v>
+        <v>2026-07-18T01:16:05.000Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>INC000000152910</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-21T07:51:47.000Z</v>
+        <v>2026-07-17T14:11:39.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>INC000000152815</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-17T21:20:43.999Z</v>
+        <v>2026-07-20T13:35:30.999Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>WO0000000309489</v>
+        <v>WO0000000309548</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-17T15:49:27.999Z</v>
+        <v>2026-07-21T08:38:16.999Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>WO0000000309488</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-17T13:20:57.999Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>INC000000152914</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-21T08:46:11.000Z</v>
+        <v>2026-07-17T15:55:02.000Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>WO0000000309541</v>
+        <v>WO0000000309604</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-17T13:27:09.000Z</v>
+        <v>2026-07-17T14:28:20.000Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>INC000000152913</v>
+        <v>INC000000152922</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-18T01:16:50.999Z</v>
+        <v>2026-07-21T07:10:12.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>WO0000000309487</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-17T14:30:26.000Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>INC000000152817</v>
+        <v>INC000000152827</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-17T14:36:59.999Z</v>
+        <v>2026-07-20T13:32:44.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>INC000000152915</v>
+        <v>INC000000152828</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-18T12:02:15.999Z</v>
+        <v>2026-07-17T14:45:48.000Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>WO0000000309495</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-17T14:05:25.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000309497</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-21T08:45:58.000Z</v>
+        <v>2026-07-19T00:08:20.000Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>WO0000000309499</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000309545</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-21T07:54:44.000Z</v>
+        <v>2026-07-17T14:57:05.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>INC000000152919</v>
+        <v>WO0000000309611</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-18T01:16:05.000Z</v>
+        <v>2026-07-21T08:49:56.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>WO0000000309546</v>
+        <v>INC000000152927</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-17T15:58:26.000Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>INC000000152824</v>
+        <v>WO0000000309613</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-20T13:35:30.999Z</v>
+        <v>2026-07-17T15:01:59.000Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>WO0000000309548</v>
+        <v>INC000000152928</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-21T08:38:16.999Z</v>
+        <v>2026-07-21T06:26:41.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>INC000000152921</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000309603</v>
+        <v>WO0000000309559</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-17T15:55:02.000Z</v>
+        <v>2026-07-17T15:56:29.000Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>WO0000000309604</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-17T14:28:20.000Z</v>
+        <v>2026-07-18T08:45:42.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>INC000000152922</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-21T07:10:12.000Z</v>
+        <v>2026-07-17T15:57:48.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>WO0000000309549</v>
+        <v>INC000000152931</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-17T14:30:26.000Z</v>
+        <v>2026-07-21T08:13:12.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>INC000000152827</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-20T13:32:44.000Z</v>
+        <v>2026-07-17T15:20:43.999Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>INC000000152828</v>
+        <v>WO0000000309563</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-17T14:45:48.000Z</v>
+        <v>2026-07-17T15:24:26.000Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>WO0000000309551</v>
+        <v>WO0000000309304</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-21T08:52:37.999Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>WO0000000309609</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-19T00:08:20.000Z</v>
+        <v>2026-07-18T11:14:25.000Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>WO0000000309553</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-17T16:04:00.000Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-17T14:57:05.000Z</v>
+        <v>2026-07-17T15:31:50.999Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>WO0000000309611</v>
+        <v>WO0000000309572</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-17T16:36:16.000Z</v>
+        <v>2026-07-21T08:34:49.000Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>INC000000152927</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-17T15:58:26.000Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000309613</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-17T15:01:59.000Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>INC000000152928</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-21T06:26:41.000Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>WO0000000309559</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-17T15:56:29.000Z</v>
+        <v>2026-07-21T08:44:02.000Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-18T08:45:42.000Z</v>
+        <v>2026-07-17T16:25:00.000Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>WO0000000309616</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-17T15:57:48.000Z</v>
+        <v>2026-07-18T06:53:20.000Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-21T08:13:12.000Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309635</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-17T16:06:26.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000309563</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>WO0000000309304</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-18T00:01:48.000Z</v>
+        <v>2026-07-18T07:13:50.000Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>INC000000152933</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-18T11:14:25.000Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>WO0000000309569</v>
+        <v>INC000000152940</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-17T16:04:00.000Z</v>
+        <v>2026-07-21T08:42:40.000Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309582</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-21T07:39:39.000Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>WO0000000309572</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-21T08:34:49.000Z</v>
+        <v>2026-07-17T17:05:49.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-18T06:19:47.000Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>WO0000000309574</v>
+        <v>WO0000000309583</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-17T16:34:20.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309585</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-21T08:37:12.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-17T16:39:05.000Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>WO0000000309626</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-21T08:44:02.000Z</v>
+        <v>2026-07-18T12:55:19.000Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>WO0000000309627</v>
+        <v>WO0000000309587</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-17T16:25:00.000Z</v>
+        <v>2026-07-17T16:39:17.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>WO0000000309629</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-18T06:53:20.000Z</v>
+        <v>2026-07-18T07:38:46.000Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>WO0000000309632</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-18T13:55:17.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>WO0000000309635</v>
+        <v>INC000000152945</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-17T16:06:26.000Z</v>
+        <v>2026-07-17T16:53:07.000Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309643</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-17T16:52:17.999Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>INC000000152938</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-21T08:27:18.000Z</v>
+        <v>2026-07-17T18:16:22.999Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>WO0000000309636</v>
+        <v>WO0000000309307</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-18T07:13:50.000Z</v>
+        <v>2026-07-18T00:06:54.000Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>INC000000152838</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>INC000000152940</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-21T08:42:40.000Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>WO0000000309582</v>
+        <v>INC000000152946</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-21T07:39:39.000Z</v>
+        <v>2026-07-17T17:58:53.999Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309648</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-17T17:05:49.000Z</v>
+        <v>2026-07-17T18:19:50.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-18T06:19:47.000Z</v>
+        <v>2026-07-17T18:20:35.000Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>WO0000000309583</v>
+        <v>WO0000000309652</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-17T16:34:20.000Z</v>
+        <v>2026-07-20T22:30:37.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>WO0000000309585</v>
+        <v>WO0000000309308</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-21T08:37:12.000Z</v>
+        <v>2026-07-21T07:44:56.000Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>WO0000000309586</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-17T16:39:05.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>INC000000152939</v>
+        <v>WO0000000309594</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-18T12:55:19.000Z</v>
+        <v>2026-07-20T22:36:47.999Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>WO0000000309587</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-17T16:39:17.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>INC000000152944</v>
+        <v>WO0000000309655</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-18T07:38:46.000Z</v>
+        <v>2026-07-17T17:58:30.999Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>WO0000000309589</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-18T13:55:17.000Z</v>
+        <v>2026-07-17T17:19:38.000Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>INC000000152945</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-17T16:53:07.000Z</v>
+        <v>2026-07-17T17:20:39.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>WO0000000309643</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-17T16:52:17.999Z</v>
+        <v>2026-07-21T08:44:49.000Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>WO0000000309592</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-17T18:16:22.999Z</v>
+        <v>2026-07-17T18:03:03.000Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>WO0000000309307</v>
+        <v>INC000000152846</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-18T00:06:54.000Z</v>
+        <v>2026-07-17T17:43:39.999Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-17T17:30:03.000Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>WO0000000309647</v>
+        <v>INC000000152950</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-17T17:00:37.000Z</v>
+        <v>2026-07-21T08:03:13.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>INC000000152946</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-17T17:58:53.999Z</v>
+        <v>2026-07-17T18:11:18.000Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>WO0000000309648</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-17T18:19:50.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309598</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-17T18:20:35.000Z</v>
+        <v>2026-07-21T08:16:54.999Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>WO0000000309653</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-17T17:46:49.000Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>WO0000000309652</v>
+        <v>WO0000000309600</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-20T22:30:37.000Z</v>
+        <v>2026-07-21T07:30:44.000Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>WO0000000309308</v>
+        <v>INC000000152844</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-21T07:44:56.000Z</v>
+        <v>2026-07-21T08:57:48.000Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>WO0000000309595</v>
+        <v>WO0000000309701</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-17T18:21:13.999Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>WO0000000309594</v>
+        <v>WO0000000309659</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-20T22:36:47.999Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>WO0000000309596</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-17T18:21:50.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>WO0000000309655</v>
+        <v>WO0000000309705</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-17T17:58:30.999Z</v>
+        <v>2026-07-17T18:22:25.999Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>WO0000000309597</v>
+        <v>WO0000000309707</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-17T17:19:38.000Z</v>
+        <v>2026-07-21T08:26:12.000Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000309309</v>
+        <v>WO0000000309660</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-17T17:20:39.000Z</v>
+        <v>2026-07-17T18:27:35.999Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>INC000000152948</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-21T08:44:49.000Z</v>
+        <v>2026-07-21T08:43:57.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>INC000000152845</v>
+        <v>WO0000000309661</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-17T18:03:03.000Z</v>
+        <v>2026-07-21T09:05:58.999Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>INC000000152846</v>
+        <v>INC000000152954</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-17T17:43:39.999Z</v>
+        <v>2026-07-18T10:44:32.000Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>WO0000000309310</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-17T17:30:03.000Z</v>
+        <v>2026-07-21T08:32:45.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>INC000000152950</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-21T08:03:13.000Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>INC000000152848</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-18T09:16:52.000Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>WO0000000309598</v>
+        <v>INC000000152957</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-21T08:16:54.999Z</v>
+        <v>2026-07-18T11:15:19.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>WO0000000309599</v>
+        <v>INC000000152853</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-20T09:22:52.000Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>WO0000000309600</v>
+        <v>INC000000152958</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-21T07:30:44.000Z</v>
+        <v>2026-07-20T09:04:48.999Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>INC000000152844</v>
+        <v>WO0000000309712</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-17T17:45:02.000Z</v>
+        <v>2026-07-17T20:32:00.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>WO0000000309701</v>
+        <v>INC000000152854</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-17T18:21:13.999Z</v>
+        <v>2026-07-17T21:32:15.999Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>WO0000000309659</v>
+        <v>INC000000152855</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-21T08:15:37.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>WO0000000309704</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-17T18:21:50.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>WO0000000309705</v>
+        <v>WO0000000309667</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-17T18:22:25.999Z</v>
+        <v>2026-07-21T07:08:18.000Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>WO0000000309707</v>
+        <v>WO0000000309715</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-21T08:26:12.000Z</v>
+        <v>2026-07-21T07:55:35.000Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>WO0000000309660</v>
+        <v>WO0000000309668</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-17T18:27:35.999Z</v>
+        <v>2026-07-21T07:28:51.000Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>INC000000152953</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-21T08:43:57.000Z</v>
+        <v>2026-07-21T07:55:12.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>WO0000000309661</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-17T18:09:12.000Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>INC000000152954</v>
+        <v>INC000000152863</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-18T10:44:32.000Z</v>
+        <v>2026-07-18T11:32:43.000Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>INC000000152955</v>
+        <v>INC000000152862</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-21T08:32:45.000Z</v>
+        <v>2026-07-18T06:59:49.000Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>WO0000000309664</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-18T11:57:16.000Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>INC000000152956</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-18T09:16:52.000Z</v>
+        <v>2026-07-18T06:52:20.999Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>WO0000000309666</v>
+        <v>INC000000152869</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-21T07:20:13.000Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>INC000000152957</v>
+        <v>INC000000152965</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-18T11:15:19.000Z</v>
+        <v>2026-07-21T09:00:01.999Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>INC000000152853</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-20T09:22:52.000Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>INC000000152958</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-20T09:04:48.999Z</v>
+        <v>2026-07-18T08:43:13.999Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>WO0000000309712</v>
+        <v>WO0000000309678</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-17T20:32:00.000Z</v>
+        <v>2026-07-18T07:42:09.999Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>INC000000152854</v>
+        <v>INC000000152877</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-17T21:32:15.999Z</v>
+        <v>2026-07-21T07:17:20.000Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>INC000000152855</v>
+        <v>INC000000152878</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-21T08:15:37.000Z</v>
+        <v>2026-07-18T08:12:08.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>WO0000000309714</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>WO0000000309667</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-21T07:08:18.000Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>WO0000000309715</v>
+        <v>INC000000152879</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-21T07:55:35.000Z</v>
+        <v>2026-07-18T08:11:58.000Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000309668</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-21T07:28:51.000Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>WO0000000309669</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-21T07:55:12.000Z</v>
+        <v>2026-07-18T12:53:54.000Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>INC000000152856</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-18T08:39:53.000Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>INC000000152863</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-18T11:32:43.000Z</v>
+        <v>2026-07-18T08:48:11.000Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>INC000000152862</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-18T06:59:49.000Z</v>
+        <v>2026-07-21T00:11:10.000Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000152980</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-18T11:57:16.000Z</v>
+        <v>2026-07-18T16:16:48.000Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>WO0000000309671</v>
+        <v>WO0000000309728</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-18T06:52:20.999Z</v>
+        <v>2026-07-20T23:05:18.000Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>INC000000152869</v>
+        <v>WO0000000309732</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-21T07:20:13.000Z</v>
+        <v>2026-07-18T09:10:30.000Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>INC000000152965</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-18T12:00:50.000Z</v>
+        <v>2026-07-21T07:56:14.999Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>INC000000152873</v>
+        <v>INC000000152888</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-18T09:48:34.000Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>INC000000152971</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-18T08:43:13.999Z</v>
+        <v>2026-07-18T09:49:22.999Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>WO0000000309678</v>
+        <v>WO0000000309698</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-18T07:42:09.999Z</v>
+        <v>2026-07-18T10:07:47.000Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>INC000000152877</v>
+        <v>INC000000152986</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-21T07:17:20.000Z</v>
+        <v>2026-07-21T08:16:08.000Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>INC000000152878</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-18T08:12:08.000Z</v>
+        <v>2026-07-18T10:49:11.000Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>WO0000000309682</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-18T09:42:12.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>WO0000000309686</v>
+        <v>INC000000152990</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-21T09:00:11.000Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>INC000000152879</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-21T07:32:12.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000309689</v>
+        <v>WO0000000309802</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-21T07:12:45.999Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>INC000000152978</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-18T12:53:54.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>INC000000152883</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-18T08:39:53.000Z</v>
+        <v>2026-07-20T19:05:32.000Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>WO0000000309692</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-18T08:48:11.000Z</v>
+        <v>2026-07-20T19:04:33.999Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>INC000000152981</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-21T00:11:10.000Z</v>
+        <v>2026-07-20T19:03:52.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>INC000000152980</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-18T16:16:48.000Z</v>
+        <v>2026-07-20T19:04:20.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>WO0000000309728</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-20T23:05:18.000Z</v>
+        <v>2026-07-19T01:10:57.000Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>WO0000000309732</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-18T09:10:30.000Z</v>
+        <v>2026-07-18T11:44:19.999Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000309697</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-21T07:56:14.999Z</v>
+        <v>2026-07-19T01:11:11.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>INC000000152888</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-18T09:48:34.000Z</v>
+        <v>2026-07-21T07:32:42.999Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>INC000000152985</v>
+        <v>INC000000153000</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-18T09:49:22.999Z</v>
+        <v>2026-07-21T07:31:13.000Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>WO0000000309698</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-18T10:07:47.000Z</v>
+        <v>2026-07-21T07:33:22.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>INC000000152986</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T08:16:08.000Z</v>
+        <v>2026-07-21T08:41:17.000Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>INC000000152987</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-18T10:49:11.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>INC000000152989</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-18T09:42:12.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000152990</v>
+        <v>INC000000153003</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T07:30:40.000Z</v>
+        <v>2026-07-21T09:03:17.000Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>INC000000152890</v>
+        <v>INC000000152900</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-21T07:32:12.000Z</v>
+        <v>2026-07-21T08:04:18.000Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>WO0000000309802</v>
+        <v>WO0000000309815</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-21T07:12:45.999Z</v>
+        <v>2026-07-18T11:50:24.000Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000309803</v>
+        <v>INC000000153006</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-20T19:05:32.000Z</v>
+        <v>2026-07-21T07:19:30.000Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>INC000000152994</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-20T19:04:33.999Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-20T19:03:52.000Z</v>
+        <v>2026-07-21T06:23:37.000Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000153103</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-20T19:04:20.000Z</v>
+        <v>2026-07-21T08:04:41.000Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>WO0000000309804</v>
+        <v>INC000000153009</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-19T01:10:57.000Z</v>
+        <v>2026-07-21T08:17:58.999Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>WO0000000309805</v>
+        <v>INC000000153011</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-18T11:44:19.999Z</v>
+        <v>2026-07-18T12:32:55.000Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>WO0000000309807</v>
+        <v>WO0000000309819</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-19T01:11:11.000Z</v>
+        <v>2026-07-20T23:23:23.000Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>INC000000152896</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-21T07:32:42.999Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>INC000000153000</v>
+        <v>INC000000153012</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-21T07:31:13.000Z</v>
+        <v>2026-07-21T08:03:57.000Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000153013</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-21T07:33:22.000Z</v>
+        <v>2026-07-21T07:19:23.999Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>INC000000152898</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-21T08:41:17.000Z</v>
+        <v>2026-07-21T07:31:56.999Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>WO0000000309810</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-21T07:19:54.000Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>WO0000000309752</v>
+        <v>INC000000153015</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-20T15:39:51.999Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>INC000000153003</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-21T08:39:04.000Z</v>
+        <v>2026-07-21T07:30:09.000Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>INC000000152900</v>
+        <v>INC000000153017</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-21T08:04:18.000Z</v>
+        <v>2026-07-18T15:26:50.000Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>WO0000000309815</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-18T11:50:24.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>INC000000153006</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-18T17:18:50.999Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>INC000000153101</v>
+        <v>WO0000000309769</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-21T07:19:30.000Z</v>
+        <v>2026-07-21T07:30:32.000Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>WO0000000309816</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>INC000000153102</v>
+        <v>WO0000000309830</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-21T06:23:37.000Z</v>
+        <v>2026-07-21T07:38:18.000Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>INC000000153103</v>
+        <v>INC000000153108</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-21T08:04:41.000Z</v>
+        <v>2026-07-21T07:53:45.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>INC000000153009</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-21T08:17:58.999Z</v>
+        <v>2026-07-19T08:43:56.000Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>INC000000153011</v>
+        <v>INC000000153020</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-18T12:32:55.000Z</v>
+        <v>2026-07-21T07:53:07.999Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>WO0000000309819</v>
+        <v>WO0000000309772</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-20T23:23:23.000Z</v>
+        <v>2026-07-21T07:55:55.000Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>WO0000000309759</v>
+        <v>WO0000000309773</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-21T07:56:38.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>INC000000153012</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-21T08:03:57.000Z</v>
+        <v>2026-07-21T07:08:54.000Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>INC000000153013</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-21T07:19:23.999Z</v>
+        <v>2026-07-19T10:27:01.999Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>WO0000000309825</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-21T07:31:56.999Z</v>
+        <v>2026-07-19T13:24:13.000Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>INC000000153105</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-21T07:19:54.000Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>INC000000153015</v>
+        <v>INC000000153025</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-20T15:39:51.999Z</v>
+        <v>2026-07-19T13:28:43.999Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>WO0000000309826</v>
+        <v>INC000000153024</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-21T07:30:09.000Z</v>
+        <v>2026-07-19T13:24:41.999Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>INC000000153017</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-18T15:26:50.000Z</v>
+        <v>2026-07-20T18:58:17.000Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>WO0000000309768</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-21T07:52:42.999Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>INC000000153107</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-18T17:18:50.999Z</v>
+        <v>2026-07-19T12:52:16.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>WO0000000309769</v>
+        <v>INC000000153028</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-21T07:30:32.000Z</v>
+        <v>2026-07-20T18:58:47.999Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>WO0000000309829</v>
+        <v>INC000000153029</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-19T13:44:46.000Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>WO0000000309830</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-21T07:38:18.000Z</v>
+        <v>2026-07-21T07:09:08.000Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>INC000000153108</v>
+        <v>INC000000153118</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-21T07:53:45.000Z</v>
+        <v>2026-07-21T08:32:11.000Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>INC000000153019</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-19T08:43:56.000Z</v>
+        <v>2026-07-19T14:37:17.999Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>INC000000153020</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-21T07:53:07.999Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>WO0000000309772</v>
+        <v>INC000000153031</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-21T07:55:55.000Z</v>
+        <v>2026-07-20T07:13:50.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>WO0000000309773</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-21T07:56:38.000Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>INC000000153021</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-21T07:08:54.000Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>INC000000153022</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-19T10:27:01.999Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>INC000000153110</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-19T13:24:13.000Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>INC000000153111</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>INC000000153025</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-19T13:28:43.999Z</v>
+        <v>2026-07-21T07:41:05.999Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>INC000000153024</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-19T13:24:41.999Z</v>
+        <v>2026-07-21T07:47:06.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-20T18:58:17.000Z</v>
+        <v>2026-07-21T07:58:21.000Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>WO0000000309834</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-21T07:52:42.999Z</v>
+        <v>2026-07-21T08:01:28.000Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153123</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-19T12:52:16.000Z</v>
+        <v>2026-07-21T07:54:40.000Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>INC000000153028</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-20T18:58:47.999Z</v>
+        <v>2026-07-20T08:42:15.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>INC000000153029</v>
+        <v>INC000000153125</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-19T13:44:46.000Z</v>
+        <v>2026-07-21T07:46:07.000Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-21T07:09:08.000Z</v>
+        <v>2026-07-20T12:50:53.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>INC000000153118</v>
+        <v>WO0000000309840</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-21T08:32:11.000Z</v>
+        <v>2026-07-21T08:50:20.000Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>INC000000153120</v>
+        <v>WO0000000309791</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-19T14:37:17.999Z</v>
+        <v>2026-07-20T12:51:30.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>INC000000153121</v>
+        <v>WO0000000309792</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-20T14:10:35.999Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>INC000000153031</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-20T07:13:50.000Z</v>
+        <v>2026-07-20T14:29:59.999Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>WO0000000309780</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>WO0000000309837</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-21T08:43:23.000Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>WO0000000309781</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-21T08:29:40.999Z</v>
+        <v>2026-07-20T18:35:59.000Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>WO0000000309783</v>
+        <v>WO0000000309794</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-20T18:20:05.999Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>WO0000000309838</v>
+        <v>WO0000000309843</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-20T18:23:24.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>INC000000153034</v>
+        <v>WO0000000309795</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-21T07:41:05.999Z</v>
+        <v>2026-07-20T18:30:58.000Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>INC000000153035</v>
+        <v>WO0000000309796</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-21T07:47:06.000Z</v>
+        <v>2026-07-21T08:49:16.000Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>INC000000153036</v>
+        <v>WO0000000309845</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-21T07:58:21.000Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>INC000000153037</v>
+        <v>WO0000000309846</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-21T08:01:28.000Z</v>
+        <v>2026-07-21T08:48:32.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>INC000000153123</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-21T07:54:40.000Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>INC000000153038</v>
+        <v>WO0000000309797</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-20T08:42:15.000Z</v>
+        <v>2026-07-20T19:09:36.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>INC000000153125</v>
+        <v>WO0000000309850</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-21T07:46:07.000Z</v>
+        <v>2026-07-21T08:49:50.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-20T12:50:53.000Z</v>
+        <v>2026-07-21T08:36:19.000Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>WO0000000309840</v>
+        <v>WO0000000309798</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-20T11:28:11.000Z</v>
+        <v>2026-07-21T07:04:25.000Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>WO0000000309791</v>
+        <v>WO0000000309852</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-20T12:51:30.000Z</v>
+        <v>2026-07-20T22:58:26.999Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>WO0000000309792</v>
+        <v>WO0000000309853</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-20T14:10:35.999Z</v>
+        <v>2026-07-21T05:54:59.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>WO0000000309841</v>
+        <v>WO0000000309799</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-20T14:29:59.999Z</v>
+        <v>2026-07-21T05:59:16.000Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>WO0000000309842</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T07:13:01.999Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>INC000000153128</v>
+        <v>INC000000153129</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-21T08:43:23.000Z</v>
+        <v>2026-07-21T07:02:26.000Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>WO0000000309793</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-20T18:35:59.000Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>WO0000000309794</v>
+        <v>WO0000000309906</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-20T18:20:05.999Z</v>
+        <v>2026-07-21T07:44:08.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>WO0000000309843</v>
+        <v>INC000000153131</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-20T18:23:24.000Z</v>
+        <v>2026-07-21T06:32:02.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>WO0000000309795</v>
+        <v>INC000000153132</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-20T18:30:58.000Z</v>
+        <v>2026-07-21T07:09:39.000Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>WO0000000309796</v>
+        <v>INC000000153044</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-20T18:41:46.000Z</v>
+        <v>2026-07-21T08:18:16.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>WO0000000309845</v>
+        <v>WO0000000309909</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T07:43:47.000Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>WO0000000309846</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-20T18:44:29.999Z</v>
+        <v>2026-07-21T08:19:35.999Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>WO0000000309848</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T06:40:04.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>WO0000000309797</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-20T19:09:36.000Z</v>
+        <v>2026-07-21T08:16:43.999Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>WO0000000309850</v>
+        <v>INC000000153049</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-20T20:24:30.000Z</v>
+        <v>2026-07-21T07:06:12.999Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>WO0000000309851</v>
+        <v>INC000000153050</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-21T08:36:19.000Z</v>
+        <v>2026-07-21T07:46:48.000Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>WO0000000309798</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-21T07:04:25.000Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>WO0000000309852</v>
+        <v>INC000000153137</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-20T22:58:26.999Z</v>
+        <v>2026-07-21T07:03:14.999Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>WO0000000309853</v>
+        <v>WO0000000309914</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-21T05:54:59.000Z</v>
+        <v>2026-07-21T07:20:13.999Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>WO0000000309799</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-21T05:59:16.000Z</v>
+        <v>2026-07-21T08:53:33.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>WO0000000309901</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-21T07:13:01.999Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>INC000000153129</v>
+        <v>INC000000153051</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-21T07:02:26.000Z</v>
+        <v>2026-07-21T07:31:21.000Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>WO0000000309902</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>WO0000000309906</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-21T07:44:08.000Z</v>
+        <v>2026-07-21T07:22:58.000Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>INC000000153131</v>
+        <v>WO0000000309920</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-21T06:32:02.000Z</v>
+        <v>2026-07-21T09:00:18.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>INC000000153132</v>
+        <v>INC000000153053</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-21T07:09:39.000Z</v>
+        <v>2026-07-21T08:05:04.000Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>INC000000153044</v>
+        <v>INC000000153055</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-21T08:18:16.000Z</v>
+        <v>2026-07-21T08:14:27.000Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>WO0000000309909</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-21T07:43:47.000Z</v>
+        <v>2026-07-21T08:21:47.999Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>INC000000153047</v>
+        <v>WO0000000309927</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-21T08:19:35.999Z</v>
+        <v>2026-07-21T07:54:45.999Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153057</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-21T06:40:04.000Z</v>
+        <v>2026-07-21T08:19:32.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>INC000000153134</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-21T08:16:43.999Z</v>
+        <v>2026-07-21T08:26:45.000Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>INC000000153049</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-21T07:06:12.999Z</v>
+        <v>2026-07-21T08:34:57.999Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>INC000000153050</v>
+        <v>INC000000153059</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-21T07:46:48.000Z</v>
+        <v>2026-07-21T08:27:55.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>INC000000153048</v>
+        <v>WO0000000309871</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T07:50:00.000Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>INC000000153137</v>
+        <v>WO0000000309867</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-21T07:03:14.999Z</v>
+        <v>2026-07-21T08:13:16.000Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>WO0000000309914</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-21T07:20:13.999Z</v>
+        <v>2026-07-21T07:57:56.999Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>INC000000153138</v>
+        <v>INC000000153060</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-21T08:39:33.000Z</v>
+        <v>2026-07-21T08:01:12.999Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153061</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T08:42:12.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>INC000000153051</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-21T07:31:21.000Z</v>
+        <v>2026-07-21T09:05:35.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>WO0000000309862</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>WO0000000309861</v>
+        <v>INC000000153063</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-21T07:22:58.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>WO0000000309920</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-21T07:26:19.000Z</v>
+        <v>2026-07-21T08:51:54.000Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>INC000000153053</v>
+        <v>WO0000000309876</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-21T08:05:04.000Z</v>
+        <v>2026-07-21T08:19:59.000Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>INC000000153055</v>
+        <v>WO0000000309877</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-21T08:14:27.000Z</v>
+        <v>2026-07-21T08:15:48.000Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>INC000000153140</v>
+        <v>WO0000000309875</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-21T08:21:47.999Z</v>
+        <v>2026-07-21T08:23:40.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>WO0000000309927</v>
+        <v>WO0000000309939</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-21T07:54:45.999Z</v>
+        <v>2026-07-21T08:42:26.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>INC000000153057</v>
+        <v>WO0000000309878</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-21T08:19:32.000Z</v>
+        <v>2026-07-21T08:35:47.000Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>INC000000153056</v>
+        <v>WO0000000309941</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-21T08:26:45.000Z</v>
+        <v>2026-07-21T09:01:43.000Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000309879</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-21T08:34:57.999Z</v>
+        <v>2026-07-21T08:17:04.000Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>INC000000153059</v>
+        <v>INC000000153148</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-21T08:27:55.000Z</v>
+        <v>2026-07-21T08:33:18.000Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>WO0000000309871</v>
+        <v>WO0000000309944</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-21T07:50:00.000Z</v>
+        <v>2026-07-21T08:15:03.000Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>WO0000000309867</v>
+        <v>INC000000153149</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-21T08:13:16.000Z</v>
+        <v>2026-07-21T08:58:21.000Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>INC000000153144</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-21T07:57:56.999Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>INC000000153060</v>
+        <v>INC000000153151</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-21T08:01:12.999Z</v>
+        <v>2026-07-21T09:00:58.000Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>INC000000153061</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-21T08:42:12.000Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>INC000000153062</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-21T08:00:04.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>INC000000153143</v>
+        <v>INC000000153147</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T09:06:12.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>INC000000153063</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T08:41:34.000Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>INC000000153145</v>
+        <v>WO0000000309883</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T08:22:19.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>WO0000000309876</v>
+        <v>INC000000153152</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-21T08:19:59.000Z</v>
+        <v>2026-07-21T08:37:55.999Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>WO0000000309877</v>
+        <v>INC000000153064</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-21T08:15:48.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>WO0000000309875</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-21T08:23:40.000Z</v>
+        <v>2026-07-21T08:42:24.999Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>WO0000000309939</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-21T08:42:26.000Z</v>
+        <v>2026-07-21T08:27:24.000Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>WO0000000309878</v>
+        <v>INC000000153067</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-21T08:35:47.000Z</v>
+        <v>2026-07-21T08:44:28.000Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>WO0000000309941</v>
+        <v>WO0000000309888</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-21T08:13:15.000Z</v>
+        <v>2026-07-21T08:44:29.999Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>WO0000000309879</v>
+        <v>WO0000000309950</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-21T08:17:04.000Z</v>
+        <v>2026-07-21T08:39:49.000Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>INC000000153146</v>
+        <v>WO0000000309951</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-21T08:20:47.000Z</v>
+        <v>2026-07-21T08:48:42.000Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>INC000000153148</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-21T08:33:18.000Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>WO0000000309944</v>
+        <v>WO0000000309952</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-21T08:15:03.000Z</v>
+        <v>2026-07-21T08:33:13.000Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>INC000000153149</v>
+        <v>WO0000000309953</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-21T08:40:35.000Z</v>
+        <v>2026-07-21T08:41:50.000Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>WO0000000309880</v>
+        <v>WO0000000309889</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T08:33:25.000Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>INC000000153151</v>
+        <v>INC000000153070</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-21T08:18:49.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>WO0000000309945</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T08:48:14.999Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>INC000000153150</v>
+        <v>INC000000153156</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-21T08:36:11.000Z</v>
+        <v>2026-07-21T08:39:24.000Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>WO0000000309946</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>INC000000153147</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-21T08:33:55.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>INC000000153065</v>
+        <v>WO0000000309893</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-21T08:41:34.000Z</v>
+        <v>2026-07-21T08:58:55.000Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>WO0000000309883</v>
+        <v>INC000000153071</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-21T08:22:19.000Z</v>
+        <v>2026-07-21T08:50:05.000Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>INC000000153152</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B1181" s="1" t="d">
-        <v>2026-07-21T08:37:55.999Z</v>
+        <v>2026-07-21T08:49:28.000Z</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>WO0000000309938</v>
+        <v>INC000000153157</v>
       </c>
       <c r="B1182" s="1" t="d">
-        <v>2026-07-21T08:26:37.000Z</v>
+        <v>2026-07-21T08:51:40.000Z</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>INC000000153064</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B1183" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T09:05:09.000Z</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>INC000000153153</v>
+        <v>INC000000153073</v>
       </c>
       <c r="B1184" s="1" t="d">
-        <v>2026-07-21T08:42:24.999Z</v>
+        <v>2026-07-21T08:55:34.000Z</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>WO0000000309949</v>
+        <v>INC000000153075</v>
       </c>
       <c r="B1185" s="1" t="d">
-        <v>2026-07-21T08:27:24.000Z</v>
+        <v>2026-07-21T09:00:22.000Z</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>INC000000153067</v>
+        <v>WO0000000309956</v>
       </c>
       <c r="B1186" s="1" t="d">
-        <v>2026-07-21T08:44:28.000Z</v>
+        <v>2026-07-21T08:51:44.999Z</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>WO0000000309888</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B1187" s="1" t="d">
-        <v>2026-07-21T08:44:29.999Z</v>
+        <v>2026-07-21T09:05:11.000Z</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>WO0000000309950</v>
+        <v>INC000000153158</v>
       </c>
       <c r="B1188" s="1" t="d">
-        <v>2026-07-21T08:39:49.000Z</v>
+        <v>2026-07-21T08:59:00.000Z</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>WO0000000309951</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B1189" s="1" t="d">
-        <v>2026-07-21T08:44:32.000Z</v>
+        <v>2026-07-21T08:54:42.999Z</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>INC000000153066</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B1190" s="1" t="d">
-        <v>2026-07-21T08:34:24.000Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>INC000000153068</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B1191" s="1" t="d">
-        <v>2026-07-21T08:39:44.000Z</v>
+        <v>2026-07-21T09:03:08.000Z</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>WO0000000309952</v>
+        <v>WO0000000310005</v>
       </c>
       <c r="B1192" s="1" t="d">
-        <v>2026-07-21T08:33:13.000Z</v>
+        <v>2026-07-21T08:57:51.999Z</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>WO0000000309953</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B1193" s="1" t="d">
-        <v>2026-07-21T08:41:50.000Z</v>
+        <v>2026-07-21T08:56:12.000Z</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>WO0000000309889</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B1194" s="1" t="d">
-        <v>2026-07-21T08:33:25.000Z</v>
+        <v>2026-07-21T09:05:13.000Z</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>INC000000153070</v>
+        <v>INC000000153076</v>
       </c>
       <c r="B1195" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T08:57:01.000Z</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>INC000000153069</v>
+        <v>WO0000000310007</v>
       </c>
       <c r="B1196" s="1" t="d">
-        <v>2026-07-21T08:40:40.999Z</v>
+        <v>2026-07-21T08:57:11.000Z</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>INC000000153156</v>
+        <v>WO0000000310008</v>
       </c>
       <c r="B1197" s="1" t="d">
-        <v>2026-07-21T08:39:24.000Z</v>
+        <v>2026-07-21T08:58:48.000Z</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>WO0000000309892</v>
+        <v>WO0000000309962</v>
       </c>
       <c r="B1198" s="1" t="d">
-        <v>2026-07-21T08:46:39.999Z</v>
+        <v>2026-07-21T09:03:49.999Z</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>WO0000000309954</v>
+        <v>WO0000000310009</v>
       </c>
       <c r="B1199" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:00:52.999Z</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>WO0000000309893</v>
+        <v>WO0000000309963</v>
       </c>
       <c r="B1200" s="1" t="d">
-        <v>2026-07-21T08:43:46.000Z</v>
+        <v>2026-07-21T09:00:20.000Z</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>INC000000153071</v>
+        <v>INC000000153161</v>
       </c>
       <c r="B1201" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-21T09:00:46.000Z</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>INC000000153072</v>
+        <v>WO0000000309960</v>
       </c>
       <c r="B1202" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-21T09:00:48.000Z</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>INC000000153155</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B1203" s="1" t="d">
-        <v>2026-07-21T08:45:35.000Z</v>
+        <v>2026-07-21T09:03:20.999Z</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>INC000000153157</v>
+        <v>WO0000000309966</v>
       </c>
       <c r="B1204" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-21T09:01:56.000Z</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>WO0000000309896</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B1205" s="1" t="d">
-        <v>2026-07-21T08:46:53.000Z</v>
+        <v>2026-07-21T09:05:07.999Z</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
+        <v>WO0000000309967</v>
+      </c>
+      <c r="B1206" s="1" t="d">
+        <v>2026-07-21T09:02:23.000Z</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="str">
+        <v>INC000000153078</v>
+      </c>
+      <c r="B1207" s="1" t="d">
+        <v>2026-07-21T09:02:45.000Z</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="str">
+        <v>INC000000153077</v>
+      </c>
+      <c r="B1208" s="1" t="d">
+        <v>2026-07-21T09:03:20.999Z</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="str">
+        <v>WO0000000310011</v>
+      </c>
+      <c r="B1209" s="1" t="d">
+        <v>2026-07-21T09:05:42.000Z</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="str">
+        <v>WO0000000309970</v>
+      </c>
+      <c r="B1210" s="1" t="d">
+        <v>2026-07-21T09:05:28.000Z</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1211"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -2955,394 +2955,394 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>INC000000147260</v>
+        <v>WO0000000295688</v>
       </c>
       <c r="B320" s="1" t="d">
-        <v>2026-07-14T08:08:06.000Z</v>
+        <v>2026-07-16T09:17:24.999Z</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>INC000000147613</v>
+        <v>INC000000147260</v>
       </c>
       <c r="B321" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-14T08:08:06.000Z</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>WO0000000297578</v>
+        <v>INC000000147613</v>
       </c>
       <c r="B322" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>INC000000149029</v>
+        <v>WO0000000297578</v>
       </c>
       <c r="B323" s="1" t="d">
-        <v>2026-07-10T14:37:50.000Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>WO0000000301822</v>
+        <v>INC000000149029</v>
       </c>
       <c r="B324" s="1" t="d">
-        <v>2026-07-20T23:27:55.000Z</v>
+        <v>2026-07-10T14:37:50.000Z</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>INC000000149860</v>
+        <v>WO0000000301822</v>
       </c>
       <c r="B325" s="1" t="d">
-        <v>2026-07-16T15:59:24.000Z</v>
+        <v>2026-07-20T23:27:55.000Z</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>INC000000150036</v>
+        <v>INC000000149860</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2026-07-16T07:28:43.999Z</v>
+        <v>2026-07-16T15:59:24.000Z</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>WO0000000303117</v>
+        <v>INC000000150036</v>
       </c>
       <c r="B327" s="1" t="d">
-        <v>2026-07-15T10:17:36.000Z</v>
+        <v>2026-07-16T07:28:43.999Z</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>INC000000149964</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B328" s="1" t="d">
-        <v>2026-07-15T15:21:53.000Z</v>
+        <v>2026-07-15T10:17:36.000Z</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>WO0000000303232</v>
+        <v>INC000000149964</v>
       </c>
       <c r="B329" s="1" t="d">
-        <v>2026-07-17T17:20:56.999Z</v>
+        <v>2026-07-15T15:21:53.000Z</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>INC000000150141</v>
+        <v>WO0000000303232</v>
       </c>
       <c r="B330" s="1" t="d">
-        <v>2026-07-15T16:30:22.000Z</v>
+        <v>2026-07-17T17:20:56.999Z</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>INC000000150288</v>
+        <v>INC000000150141</v>
       </c>
       <c r="B331" s="1" t="d">
-        <v>2026-07-10T12:39:00.000Z</v>
+        <v>2026-07-15T16:30:22.000Z</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>INC000000150197</v>
+        <v>INC000000150288</v>
       </c>
       <c r="B332" s="1" t="d">
-        <v>2026-07-17T11:00:31.000Z</v>
+        <v>2026-07-10T12:39:00.000Z</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>WO0000000303791</v>
+        <v>INC000000150197</v>
       </c>
       <c r="B333" s="1" t="d">
-        <v>2026-07-15T12:32:15.000Z</v>
+        <v>2026-07-17T11:00:31.000Z</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>INC000000150475</v>
+        <v>WO0000000303791</v>
       </c>
       <c r="B334" s="1" t="d">
-        <v>2026-07-16T08:36:47.000Z</v>
+        <v>2026-07-15T12:32:15.000Z</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>WO0000000304256</v>
+        <v>INC000000150475</v>
       </c>
       <c r="B335" s="1" t="d">
-        <v>2026-07-16T12:20:08.000Z</v>
+        <v>2026-07-16T08:36:47.000Z</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>WO0000000304437</v>
+        <v>WO0000000304256</v>
       </c>
       <c r="B336" s="1" t="d">
-        <v>2026-07-16T12:22:04.999Z</v>
+        <v>2026-07-16T12:20:08.000Z</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>WO0000000304614</v>
+        <v>WO0000000304437</v>
       </c>
       <c r="B337" s="1" t="d">
-        <v>2026-07-16T12:25:00.000Z</v>
+        <v>2026-07-16T12:22:04.999Z</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>INC000000150547</v>
+        <v>WO0000000304614</v>
       </c>
       <c r="B338" s="1" t="d">
-        <v>2026-07-16T08:37:46.000Z</v>
+        <v>2026-07-16T12:25:00.000Z</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>WO0000000304990</v>
+        <v>INC000000150547</v>
       </c>
       <c r="B339" s="1" t="d">
-        <v>2026-07-15T10:54:42.999Z</v>
+        <v>2026-07-16T08:37:46.000Z</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>INC000000150732</v>
+        <v>WO0000000304990</v>
       </c>
       <c r="B340" s="1" t="d">
-        <v>2026-07-16T08:27:41.000Z</v>
+        <v>2026-07-15T10:54:42.999Z</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>INC000000150748</v>
+        <v>INC000000150732</v>
       </c>
       <c r="B341" s="1" t="d">
-        <v>2026-07-16T09:01:40.000Z</v>
+        <v>2026-07-16T08:27:41.000Z</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>WO0000000305312</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B342" s="1" t="d">
-        <v>2026-07-15T11:26:08.000Z</v>
+        <v>2026-07-16T09:01:40.000Z</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305312</v>
       </c>
       <c r="B343" s="1" t="d">
-        <v>2026-07-15T13:10:05.000Z</v>
+        <v>2026-07-15T11:26:08.000Z</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>INC000000150882</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B344" s="1" t="d">
-        <v>2026-07-15T10:45:04.000Z</v>
+        <v>2026-07-15T13:10:05.000Z</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>WO0000000305349</v>
+        <v>INC000000150882</v>
       </c>
       <c r="B345" s="1" t="d">
-        <v>2026-07-14T12:21:19.000Z</v>
+        <v>2026-07-15T10:45:04.000Z</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>WO0000000305815</v>
+        <v>WO0000000305349</v>
       </c>
       <c r="B346" s="1" t="d">
-        <v>2026-07-16T12:28:46.000Z</v>
+        <v>2026-07-14T12:21:19.000Z</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>WO0000000305843</v>
+        <v>WO0000000305815</v>
       </c>
       <c r="B347" s="1" t="d">
-        <v>2026-07-14T12:37:15.000Z</v>
+        <v>2026-07-16T12:28:46.000Z</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>WO0000000305743</v>
+        <v>WO0000000305843</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2026-07-14T14:33:44.000Z</v>
+        <v>2026-07-14T12:37:15.000Z</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>INC000000151204</v>
+        <v>WO0000000305743</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2026-07-14T12:46:36.000Z</v>
+        <v>2026-07-14T14:33:44.000Z</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>WO0000000305944</v>
+        <v>INC000000151204</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2026-07-14T12:04:16.999Z</v>
+        <v>2026-07-14T12:46:36.000Z</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>INC000000151134</v>
+        <v>WO0000000305944</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2026-07-14T10:49:05.000Z</v>
+        <v>2026-07-14T12:04:16.999Z</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>INC000000151151</v>
+        <v>INC000000151134</v>
       </c>
       <c r="B352" s="1" t="d">
-        <v>2026-07-16T08:22:24.000Z</v>
+        <v>2026-07-14T10:49:05.000Z</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>WO0000000306190</v>
+        <v>INC000000151151</v>
       </c>
       <c r="B353" s="1" t="d">
-        <v>2026-07-14T13:13:31.000Z</v>
+        <v>2026-07-16T08:22:24.000Z</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>WO0000000306290</v>
+        <v>WO0000000306190</v>
       </c>
       <c r="B354" s="1" t="d">
-        <v>2026-07-14T16:17:28.999Z</v>
+        <v>2026-07-14T13:13:31.000Z</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>WO0000000306328</v>
+        <v>WO0000000306290</v>
       </c>
       <c r="B355" s="1" t="d">
-        <v>2026-07-14T16:39:44.000Z</v>
+        <v>2026-07-14T16:17:28.999Z</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>INC000000151200</v>
+        <v>WO0000000306328</v>
       </c>
       <c r="B356" s="1" t="d">
-        <v>2026-07-10T10:51:56.000Z</v>
+        <v>2026-07-14T16:39:44.000Z</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>WO0000000306374</v>
+        <v>INC000000151200</v>
       </c>
       <c r="B357" s="1" t="d">
-        <v>2026-07-10T13:36:36.000Z</v>
+        <v>2026-07-10T10:51:56.000Z</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>WO0000000306439</v>
+        <v>WO0000000306374</v>
       </c>
       <c r="B358" s="1" t="d">
-        <v>2026-07-14T16:14:53.000Z</v>
+        <v>2026-07-10T13:36:36.000Z</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>WO0000000306534</v>
+        <v>WO0000000306439</v>
       </c>
       <c r="B359" s="1" t="d">
-        <v>2026-07-15T16:01:14.000Z</v>
+        <v>2026-07-14T16:14:53.000Z</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>INC000000151466</v>
+        <v>WO0000000306534</v>
       </c>
       <c r="B360" s="1" t="d">
-        <v>2026-07-14T15:33:23.000Z</v>
+        <v>2026-07-15T16:01:14.000Z</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>WO0000000304733</v>
+        <v>INC000000151466</v>
       </c>
       <c r="B361" s="1" t="d">
-        <v>2026-07-15T10:28:05.999Z</v>
+        <v>2026-07-14T15:33:23.000Z</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>WO0000000306574</v>
+        <v>WO0000000304733</v>
       </c>
       <c r="B362" s="1" t="d">
-        <v>2026-07-15T12:39:36.999Z</v>
+        <v>2026-07-15T10:28:05.999Z</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>WO0000000306648</v>
+        <v>WO0000000306574</v>
       </c>
       <c r="B363" s="1" t="d">
-        <v>2026-07-16T11:20:21.000Z</v>
+        <v>2026-07-15T12:39:36.999Z</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>INC000000151499</v>
+        <v>WO0000000306648</v>
       </c>
       <c r="B364" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-16T11:20:21.000Z</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>INC000000151512</v>
+        <v>INC000000151499</v>
       </c>
       <c r="B365" s="1" t="d">
-        <v>2026-07-16T09:37:50.000Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>INC000000151525</v>
+        <v>INC000000151512</v>
       </c>
       <c r="B366" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-16T09:37:50.000Z</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>WO0000000306862</v>
+        <v>INC000000151525</v>
       </c>
       <c r="B367" s="1" t="d">
-        <v>2026-07-21T08:05:05.000Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>WO0000000306988</v>
+        <v>WO0000000306862</v>
       </c>
       <c r="B368" s="1" t="d">
-        <v>2026-07-15T11:48:34.000Z</v>
+        <v>2026-07-21T08:05:05.000Z</v>
       </c>
     </row>
     <row r="369">
@@ -3715,82 +3715,82 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>WO0000000308194</v>
+        <v>INC000000152358</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-16T09:12:05.999Z</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308255</v>
+        <v>WO0000000308194</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-17T15:17:47.000Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308260</v>
+        <v>WO0000000308255</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-21T08:56:50.000Z</v>
+        <v>2026-07-17T15:17:47.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>WO0000000308269</v>
+        <v>WO0000000308260</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-16T12:15:01.000Z</v>
+        <v>2026-07-21T08:56:50.000Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>WO0000000308273</v>
+        <v>WO0000000308269</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-16T12:17:21.999Z</v>
+        <v>2026-07-21T09:19:51.000Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308284</v>
+        <v>WO0000000308273</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-16T08:08:24.000Z</v>
+        <v>2026-07-16T12:17:21.999Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308284</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-16T23:19:07.000Z</v>
+        <v>2026-07-16T08:08:24.000Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308331</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-17T16:57:45.000Z</v>
+        <v>2026-07-16T23:19:07.000Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308416</v>
+        <v>WO0000000308331</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-16T09:47:42.999Z</v>
+        <v>2026-07-21T09:13:19.000Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308416</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-21T09:00:49.000Z</v>
+        <v>2026-07-16T09:47:42.999Z</v>
       </c>
     </row>
     <row r="425">
@@ -3923,986 +3923,986 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000272008</v>
+        <v>INC000000152513</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-21T09:04:16.999Z</v>
+        <v>2026-07-16T09:23:02.000Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>INC000000139655</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-17T07:37:37.999Z</v>
+        <v>2026-07-17T15:09:40.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>INC000000139903</v>
+        <v>WO0000000272008</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-17T07:37:04.000Z</v>
+        <v>2026-07-21T09:04:16.999Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>INC000000140158</v>
+        <v>INC000000139655</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-17T07:37:37.999Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>INC000000140820</v>
+        <v>INC000000139903</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-17T07:35:42.000Z</v>
+        <v>2026-07-17T07:37:04.000Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>INC000000140821</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-17T07:34:57.000Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>INC000000140767</v>
+        <v>INC000000140820</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-17T07:35:42.000Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>INC000000141766</v>
+        <v>INC000000140821</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2026-07-21T08:55:08.000Z</v>
+        <v>2026-07-17T07:34:57.000Z</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>INC000000142421</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-17T07:33:48.000Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>INC000000142515</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-17T07:33:05.000Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>WO0000000288110</v>
+        <v>INC000000142421</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-17T07:47:10.000Z</v>
+        <v>2026-07-17T07:33:48.000Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>INC000000143401</v>
+        <v>INC000000142515</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-17T07:32:06.000Z</v>
+        <v>2026-07-17T07:33:05.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WO0000000292826</v>
+        <v>WO0000000288110</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-17T07:30:34.000Z</v>
+        <v>2026-07-17T07:47:10.000Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>WO0000000295598</v>
+        <v>INC000000143401</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-17T07:32:06.000Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>WO0000000295688</v>
+        <v>WO0000000292826</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-16T09:17:24.999Z</v>
+        <v>2026-07-17T07:30:34.000Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>WO0000000295716</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-16T11:47:42.999Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>WO0000000295975</v>
+        <v>WO0000000295716</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-17T07:46:27.000Z</v>
+        <v>2026-07-16T11:47:42.999Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>INC000000146886</v>
+        <v>WO0000000295975</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-16T13:10:02.999Z</v>
+        <v>2026-07-17T07:46:27.000Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>WO0000000296722</v>
+        <v>INC000000146886</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-17T07:44:32.000Z</v>
+        <v>2026-07-16T13:10:02.999Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>WO0000000296723</v>
+        <v>WO0000000296722</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-17T07:43:42.999Z</v>
+        <v>2026-07-17T07:44:32.000Z</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>WO0000000297151</v>
+        <v>WO0000000296723</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-17T07:42:36.000Z</v>
+        <v>2026-07-17T07:43:42.999Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>WO0000000297156</v>
+        <v>WO0000000297151</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-17T07:41:50.000Z</v>
+        <v>2026-07-17T07:42:36.000Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>WO0000000297160</v>
+        <v>WO0000000297156</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-17T07:40:23.999Z</v>
+        <v>2026-07-17T07:41:50.000Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>WO0000000298838</v>
+        <v>WO0000000297160</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-20T23:28:38.000Z</v>
+        <v>2026-07-17T07:40:23.999Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>WO0000000299920</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-17T14:59:50.999Z</v>
+        <v>2026-07-20T23:28:38.000Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>WO0000000300081</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-17T14:59:50.999Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>INC000000148888</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>WO0000000300496</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-17T11:43:57.000Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>WO0000000302331</v>
+        <v>WO0000000300496</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-17T12:11:40.000Z</v>
+        <v>2026-07-17T11:43:57.000Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>WO0000000302520</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-17T15:04:39.000Z</v>
+        <v>2026-07-17T12:11:40.000Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>INC000000149827</v>
+        <v>WO0000000302520</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-17T14:03:04.000Z</v>
+        <v>2026-07-17T15:04:39.000Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>INC000000149757</v>
+        <v>INC000000149827</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-16T16:04:01.999Z</v>
+        <v>2026-07-17T14:03:04.000Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>INC000000149760</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-17T07:52:31.999Z</v>
+        <v>2026-07-16T16:04:01.999Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>WO0000000303120</v>
+        <v>INC000000149760</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-17T07:38:45.000Z</v>
+        <v>2026-07-17T07:52:31.999Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000303120</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-17T15:09:03.000Z</v>
+        <v>2026-07-17T07:38:45.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000303244</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-17T15:04:54.000Z</v>
+        <v>2026-07-17T15:09:03.000Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>WO0000000303459</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-17T11:09:28.999Z</v>
+        <v>2026-07-17T15:04:54.000Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>WO0000000303471</v>
+        <v>WO0000000303459</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-16T14:24:05.000Z</v>
+        <v>2026-07-17T11:09:28.999Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000303471</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-16T12:40:48.000Z</v>
+        <v>2026-07-16T14:24:05.000Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-17T10:37:05.000Z</v>
+        <v>2026-07-16T12:40:48.000Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-17T10:37:33.000Z</v>
+        <v>2026-07-17T10:37:05.000Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WO0000000305131</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-21T08:46:39.000Z</v>
+        <v>2026-07-17T10:37:33.000Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WO0000000305138</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-21T08:46:39.000Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>WO0000000305336</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>INC000000150916</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-17T13:59:57.999Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000150916</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-17T18:15:37.999Z</v>
+        <v>2026-07-17T13:59:57.999Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>INC000000151036</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-16T16:01:20.999Z</v>
+        <v>2026-07-17T18:15:37.999Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WO0000000305566</v>
+        <v>INC000000151036</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-16T10:45:43.999Z</v>
+        <v>2026-07-16T16:01:20.999Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>INC000000150958</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-17T07:47:57.999Z</v>
+        <v>2026-07-16T10:45:43.999Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>WO0000000305863</v>
+        <v>INC000000150958</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-21T08:44:19.000Z</v>
+        <v>2026-07-17T07:47:57.999Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>WO0000000305877</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-16T16:12:20.000Z</v>
+        <v>2026-07-21T08:44:19.000Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>WO0000000305769</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-17T10:37:57.000Z</v>
+        <v>2026-07-16T16:12:20.000Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>WO0000000305770</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-17T11:07:27.000Z</v>
+        <v>2026-07-17T10:37:57.000Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>INC000000151203</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-17T11:07:27.000Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>WO0000000306127</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-21T07:40:38.000Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>INC000000151157</v>
+        <v>WO0000000306127</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-17T19:09:33.000Z</v>
+        <v>2026-07-21T07:40:38.000Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>INC000000151271</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-17T07:40:02.000Z</v>
+        <v>2026-07-17T19:09:33.000Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>WO0000000306256</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-17T14:41:03.000Z</v>
+        <v>2026-07-17T07:40:02.000Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>INC000000151311</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-16T09:35:09.000Z</v>
+        <v>2026-07-17T14:41:03.000Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>INC000000151313</v>
+        <v>INC000000151311</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-16T09:35:09.000Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>WO0000000306718</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-17T10:39:36.000Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>WO0000000306721</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-17T15:11:14.000Z</v>
+        <v>2026-07-17T10:39:36.000Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>WO0000000306726</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-17T10:39:57.000Z</v>
+        <v>2026-07-17T15:11:14.000Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>WO0000000306799</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-17T08:21:12.999Z</v>
+        <v>2026-07-17T10:39:57.000Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-17T19:07:47.000Z</v>
+        <v>2026-07-17T08:21:12.999Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>INC000000151527</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-17T16:34:54.000Z</v>
+        <v>2026-07-17T19:07:47.000Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>WO0000000306927</v>
+        <v>INC000000151527</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-17T16:34:54.000Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-17T17:20:58.999Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>WO0000000306877</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-16T14:55:04.000Z</v>
+        <v>2026-07-17T17:20:58.999Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>WO0000000306890</v>
+        <v>WO0000000306877</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-16T14:55:04.000Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>WO0000000306899</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-17T17:44:23.000Z</v>
+        <v>2026-07-17T14:42:13.999Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>WO0000000306992</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-16T10:42:09.000Z</v>
+        <v>2026-07-17T17:44:23.000Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>WO0000000306994</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-16T15:19:33.999Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>INC000000151586</v>
+        <v>WO0000000306992</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-19T12:57:49.000Z</v>
+        <v>2026-07-16T10:42:09.000Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>WO0000000307224</v>
+        <v>WO0000000306994</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-16T16:04:39.999Z</v>
+        <v>2026-07-16T15:19:33.999Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>WO0000000307090</v>
+        <v>INC000000151586</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-17T14:49:17.000Z</v>
+        <v>2026-07-19T12:57:49.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>INC000000151950</v>
+        <v>WO0000000307224</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-16T09:20:32.000Z</v>
+        <v>2026-07-16T16:04:39.999Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>INC000000151764</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-16T10:00:04.000Z</v>
+        <v>2026-07-17T14:49:17.000Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>WO0000000307513</v>
+        <v>INC000000151950</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-17T09:03:17.000Z</v>
+        <v>2026-07-16T09:20:32.000Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>INC000000152002</v>
+        <v>INC000000151764</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-16T10:00:04.000Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>INC000000151987</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-16T11:05:28.000Z</v>
+        <v>2026-07-17T09:03:17.000Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>WO0000000307483</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-17T14:43:30.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>WO0000000307604</v>
+        <v>INC000000151987</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-17T14:02:15.000Z</v>
+        <v>2026-07-16T11:05:28.000Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-17T16:21:08.000Z</v>
+        <v>2026-07-21T09:13:03.000Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>INC000000152000</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-19T12:58:45.000Z</v>
+        <v>2026-07-17T14:02:15.000Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-17T16:21:08.000Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>WO0000000307635</v>
+        <v>INC000000152000</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-19T12:58:45.000Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>WO0000000307636</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-20T22:08:00.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>INC000000152045</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-16T10:52:09.000Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307636</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-16T11:24:53.999Z</v>
+        <v>2026-07-20T22:08:00.000Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>WO0000000307669</v>
+        <v>INC000000152045</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-16T10:52:09.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-17T17:21:00.000Z</v>
+        <v>2026-07-16T11:24:53.999Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>WO0000000307725</v>
+        <v>WO0000000307669</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-17T15:11:48.000Z</v>
+        <v>2026-07-17T09:44:19.000Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>WO0000000307729</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-16T12:57:39.999Z</v>
+        <v>2026-07-17T17:21:00.000Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>INC000000152145</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-17T19:20:59.000Z</v>
+        <v>2026-07-17T15:11:48.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>INC000000152073</v>
+        <v>WO0000000307729</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-16T09:23:53.000Z</v>
+        <v>2026-07-16T12:57:39.999Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>WO0000000307923</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-16T09:23:33.000Z</v>
+        <v>2026-07-17T19:20:59.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>WO0000000307940</v>
+        <v>INC000000152073</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-16T09:23:53.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>WO0000000307963</v>
+        <v>WO0000000307923</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-17T13:31:54.000Z</v>
+        <v>2026-07-16T09:23:33.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000308029</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-17T16:02:10.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>INC000000152212</v>
+        <v>WO0000000307963</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-17T13:31:54.000Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>WO0000000308038</v>
+        <v>WO0000000308029</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-17T13:48:01.000Z</v>
+        <v>2026-07-17T16:02:10.000Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>WO0000000308040</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>WO0000000307968</v>
+        <v>WO0000000308038</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-16T15:02:29.000Z</v>
+        <v>2026-07-17T13:48:01.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>WO0000000307970</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-16T16:55:20.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>WO0000000308041</v>
+        <v>WO0000000307968</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-17T09:02:42.000Z</v>
+        <v>2026-07-16T15:02:29.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000308042</v>
+        <v>WO0000000307970</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-20T23:34:20.999Z</v>
+        <v>2026-07-16T16:55:20.000Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000308041</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-17T09:02:42.000Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>WO0000000308052</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-17T11:04:48.999Z</v>
+        <v>2026-07-20T23:34:20.999Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>WO0000000307988</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>WO0000000308105</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-20T23:29:29.999Z</v>
+        <v>2026-07-17T11:04:48.999Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>INC000000152328</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-17T21:19:20.000Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000308075</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-20T23:26:07.000Z</v>
+        <v>2026-07-20T23:29:29.999Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>WO0000000308106</v>
+        <v>INC000000152328</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-20T23:30:10.000Z</v>
+        <v>2026-07-17T21:19:20.000Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>WO0000000308107</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-20T23:27:09.999Z</v>
+        <v>2026-07-20T23:26:07.000Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-20T23:31:09.999Z</v>
+        <v>2026-07-20T23:30:10.000Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>WO0000000308086</v>
+        <v>WO0000000308107</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-17T14:44:25.000Z</v>
+        <v>2026-07-20T23:27:09.999Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>WO0000000308215</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-17T09:26:37.000Z</v>
+        <v>2026-07-20T23:31:09.999Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>WO0000000308216</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-17T13:19:29.000Z</v>
+        <v>2026-07-17T14:44:25.000Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000308215</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-17T09:26:37.000Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000308216</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-18T12:28:17.000Z</v>
+        <v>2026-07-17T13:19:29.000Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>INC000000152358</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-16T09:12:05.999Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>WO0000000308169</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-17T14:18:27.000Z</v>
+        <v>2026-07-18T12:28:17.000Z</v>
       </c>
     </row>
     <row r="564">
@@ -5035,71 +5035,71 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>WO0000000308357</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-21T08:46:37.999Z</v>
+        <v>2026-07-21T09:09:06.999Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308357</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-16T10:44:20.999Z</v>
+        <v>2026-07-21T09:07:14.999Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>INC000000152389</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-17T10:53:19.000Z</v>
+        <v>2026-07-16T10:44:20.999Z</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>WO0000000308366</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-07-16T09:45:50.999Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>WO0000000308461</v>
+        <v>WO0000000308366</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-16T18:43:27.999Z</v>
+        <v>2026-07-16T09:45:50.999Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>WO0000000308475</v>
+        <v>WO0000000308461</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-16T18:43:27.999Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>WO0000000308478</v>
+        <v>WO0000000308475</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-17T12:30:39.000Z</v>
+        <v>2026-07-17T12:30:37.999Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>WO0000000308382</v>
+        <v>WO0000000308478</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-17T12:30:40.000Z</v>
+        <v>2026-07-17T12:30:39.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>WO0000000308380</v>
+        <v>WO0000000308382</v>
       </c>
       <c r="B588" s="1" t="d">
         <v>2026-07-17T12:30:40.000Z</v>
@@ -5107,50 +5107,50 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>WO0000000308396</v>
+        <v>WO0000000308380</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-17T12:30:41.000Z</v>
+        <v>2026-07-17T12:30:40.000Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>WO0000000308495</v>
+        <v>WO0000000308396</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-17T12:30:41.000Z</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>INC000000152419</v>
+        <v>WO0000000308495</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-07-21T08:54:50.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>WO0000000308506</v>
+        <v>INC000000152419</v>
       </c>
       <c r="B592" s="1" t="d">
-        <v>2026-07-17T12:30:41.000Z</v>
+        <v>2026-07-21T08:54:50.000Z</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>INC000000152439</v>
+        <v>WO0000000308506</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-07-16T13:12:03.000Z</v>
+        <v>2026-07-17T12:30:41.000Z</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>INC000000152513</v>
+        <v>INC000000152439</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-07-16T09:23:02.000Z</v>
+        <v>2026-07-16T13:12:03.000Z</v>
       </c>
     </row>
     <row r="595">
@@ -5203,4882 +5203,4882 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>WO0000000308648</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-17T15:09:40.000Z</v>
+        <v>2026-07-16T09:22:57.000Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-16T09:22:57.000Z</v>
+        <v>2026-07-18T12:29:14.000Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000152458</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-18T12:29:14.000Z</v>
+        <v>2026-07-17T14:55:27.000Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>INC000000152458</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-17T14:55:27.000Z</v>
+        <v>2026-07-17T14:10:20.000Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000308661</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-07-17T14:10:20.000Z</v>
+        <v>2026-07-17T14:16:26.000Z</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>WO0000000308661</v>
+        <v>WO0000000308662</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-17T14:16:26.000Z</v>
+        <v>2026-07-16T14:23:41.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>WO0000000308662</v>
+        <v>WO0000000308585</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-16T14:23:41.000Z</v>
+        <v>2026-07-16T14:22:46.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>WO0000000308585</v>
+        <v>INC000000152461</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-16T14:22:46.000Z</v>
+        <v>2026-07-20T09:23:43.999Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>INC000000152461</v>
+        <v>WO0000000308673</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-20T09:23:43.999Z</v>
+        <v>2026-07-16T10:02:00.999Z</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>WO0000000308673</v>
+        <v>WO0000000308679</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-07-16T10:02:00.999Z</v>
+        <v>2026-07-17T14:36:57.000Z</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>WO0000000308679</v>
+        <v>WO0000000308675</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-07-17T14:36:57.000Z</v>
+        <v>2026-07-17T07:31:47.000Z</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>WO0000000308675</v>
+        <v>WO0000000308685</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-07-17T07:31:47.000Z</v>
+        <v>2026-07-16T10:12:45.000Z</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>WO0000000308685</v>
+        <v>WO0000000308596</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-07-16T10:12:45.000Z</v>
+        <v>2026-07-16T10:19:52.000Z</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>WO0000000308596</v>
+        <v>WO0000000308701</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-07-16T10:19:52.000Z</v>
+        <v>2026-07-16T10:22:52.000Z</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>WO0000000308701</v>
+        <v>WO0000000308696</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-07-16T10:22:52.000Z</v>
+        <v>2026-07-17T11:22:11.000Z</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308698</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-07-17T11:22:11.000Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>WO0000000308698</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-16T10:42:24.000Z</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>WO0000000308695</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-07-16T10:42:24.000Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308712</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-17T09:16:22.999Z</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>WO0000000308712</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-07-17T09:16:22.999Z</v>
+        <v>2026-07-16T10:40:08.000Z</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-07-16T10:40:08.000Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>WO0000000308715</v>
+        <v>INC000000152561</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-17T16:04:19.000Z</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>INC000000152561</v>
+        <v>WO0000000308717</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-07-17T16:04:19.000Z</v>
+        <v>2026-07-16T12:45:40.000Z</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-07-16T12:45:40.000Z</v>
+        <v>2026-07-16T10:46:41.000Z</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-07-16T10:46:41.000Z</v>
+        <v>2026-07-20T19:01:19.000Z</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-07-20T19:01:19.000Z</v>
+        <v>2026-07-17T16:49:36.000Z</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>WO0000000308723</v>
+        <v>INC000000152565</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-07-17T16:49:36.000Z</v>
+        <v>2026-07-21T07:47:38.999Z</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>INC000000152565</v>
+        <v>WO0000000308727</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-07-21T07:47:38.999Z</v>
+        <v>2026-07-17T09:34:42.000Z</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>WO0000000308727</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-07-17T09:34:42.000Z</v>
+        <v>2026-07-21T08:53:31.000Z</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000308808</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-07-21T08:53:31.000Z</v>
+        <v>2026-07-17T16:59:44.999Z</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000308809</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-07-17T16:59:44.999Z</v>
+        <v>2026-07-16T11:14:01.000Z</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>WO0000000308809</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-07-16T11:14:01.000Z</v>
+        <v>2026-07-17T15:18:13.000Z</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>INC000000152566</v>
+        <v>WO0000000308814</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-07-17T15:18:13.000Z</v>
+        <v>2026-07-17T15:46:22.000Z</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>WO0000000308814</v>
+        <v>WO0000000308742</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-07-17T15:46:22.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>WO0000000308742</v>
+        <v>WO0000000308816</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>WO0000000308816</v>
+        <v>WO0000000308743</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-17T15:54:32.000Z</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>WO0000000308743</v>
+        <v>INC000000152477</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-07-17T15:54:32.000Z</v>
+        <v>2026-07-16T12:12:43.000Z</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>INC000000152477</v>
+        <v>WO0000000308750</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-07-16T12:12:43.000Z</v>
+        <v>2026-07-17T16:02:36.000Z</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>WO0000000308749</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-07-17T16:02:35.000Z</v>
+        <v>2026-07-17T08:38:07.000Z</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>WO0000000308750</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-07-17T16:02:36.000Z</v>
+        <v>2026-07-16T14:25:41.000Z</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000308755</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-07-17T08:38:07.000Z</v>
+        <v>2026-07-16T11:35:09.000Z</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>WO0000000308754</v>
+        <v>WO0000000308826</v>
       </c>
       <c r="B642" s="1" t="d">
-        <v>2026-07-16T14:25:41.000Z</v>
+        <v>2026-07-17T16:08:41.000Z</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>WO0000000308755</v>
+        <v>WO0000000308817</v>
       </c>
       <c r="B643" s="1" t="d">
-        <v>2026-07-16T11:35:09.000Z</v>
+        <v>2026-07-17T16:14:46.000Z</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>WO0000000308826</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B644" s="1" t="d">
-        <v>2026-07-17T16:08:41.000Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>WO0000000308817</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B645" s="1" t="d">
-        <v>2026-07-17T16:14:46.000Z</v>
+        <v>2026-07-17T16:19:03.000Z</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000308851</v>
       </c>
       <c r="B646" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-17T16:37:20.999Z</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>WO0000000308758</v>
+        <v>INC000000152486</v>
       </c>
       <c r="B647" s="1" t="d">
-        <v>2026-07-17T16:16:51.999Z</v>
+        <v>2026-07-21T07:42:45.999Z</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>WO0000000308834</v>
+        <v>WO0000000308860</v>
       </c>
       <c r="B648" s="1" t="d">
-        <v>2026-07-17T16:19:03.000Z</v>
+        <v>2026-07-17T16:51:40.000Z</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>WO0000000308851</v>
+        <v>WO0000000308862</v>
       </c>
       <c r="B649" s="1" t="d">
-        <v>2026-07-17T16:37:20.999Z</v>
+        <v>2026-07-17T17:46:11.000Z</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>INC000000152486</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B650" s="1" t="d">
-        <v>2026-07-21T07:42:45.999Z</v>
+        <v>2026-07-21T08:00:16.000Z</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>WO0000000308860</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B651" s="1" t="d">
-        <v>2026-07-17T16:51:40.000Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>WO0000000308862</v>
+        <v>WO0000000308868</v>
       </c>
       <c r="B652" s="1" t="d">
-        <v>2026-07-17T17:46:11.000Z</v>
+        <v>2026-07-21T08:27:45.999Z</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B653" s="1" t="d">
-        <v>2026-07-21T08:00:16.000Z</v>
+        <v>2026-07-16T14:39:36.999Z</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>INC000000152586</v>
+        <v>INC000000152496</v>
       </c>
       <c r="B654" s="1" t="d">
-        <v>2026-07-17T10:46:28.000Z</v>
+        <v>2026-07-17T18:33:44.000Z</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>WO0000000308868</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B655" s="1" t="d">
-        <v>2026-07-21T08:27:45.999Z</v>
+        <v>2026-07-17T09:53:56.000Z</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>WO0000000308873</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B656" s="1" t="d">
-        <v>2026-07-16T14:39:36.999Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>INC000000152496</v>
+        <v>INC000000152594</v>
       </c>
       <c r="B657" s="1" t="d">
-        <v>2026-07-17T18:33:44.000Z</v>
+        <v>2026-07-20T13:46:11.000Z</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>WO0000000308794</v>
+        <v>WO0000000308905</v>
       </c>
       <c r="B658" s="1" t="d">
-        <v>2026-07-17T09:53:56.000Z</v>
+        <v>2026-07-16T14:04:26.000Z</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>INC000000152591</v>
+        <v>WO0000000308880</v>
       </c>
       <c r="B659" s="1" t="d">
-        <v>2026-07-17T11:00:29.999Z</v>
+        <v>2026-07-17T14:08:19.000Z</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>INC000000152594</v>
+        <v>WO0000000308912</v>
       </c>
       <c r="B660" s="1" t="d">
-        <v>2026-07-20T13:46:11.000Z</v>
+        <v>2026-07-16T14:18:19.000Z</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>WO0000000308905</v>
+        <v>INC000000152598</v>
       </c>
       <c r="B661" s="1" t="d">
-        <v>2026-07-16T14:04:26.000Z</v>
+        <v>2026-07-17T10:04:25.000Z</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>WO0000000308880</v>
+        <v>WO0000000308913</v>
       </c>
       <c r="B662" s="1" t="d">
-        <v>2026-07-17T14:08:19.000Z</v>
+        <v>2026-07-17T08:38:16.000Z</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>WO0000000308912</v>
+        <v>WO0000000308917</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-16T14:18:19.000Z</v>
+        <v>2026-07-17T07:59:19.999Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>INC000000152598</v>
+        <v>WO0000000308918</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-17T10:04:25.000Z</v>
+        <v>2026-07-17T14:34:52.999Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000308913</v>
+        <v>WO0000000308919</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-17T08:38:16.000Z</v>
+        <v>2026-07-16T14:36:18.000Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>WO0000000308917</v>
+        <v>WO0000000308923</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-17T07:59:19.999Z</v>
+        <v>2026-07-21T09:17:59.000Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>WO0000000308918</v>
+        <v>INC000000152608</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-17T14:34:52.999Z</v>
+        <v>2026-07-17T15:48:10.000Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>WO0000000308919</v>
+        <v>WO0000000308895</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-16T14:36:18.000Z</v>
+        <v>2026-07-17T10:35:42.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>WO0000000308923</v>
+        <v>WO0000000308896</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-16T17:34:43.000Z</v>
+        <v>2026-07-16T15:16:25.000Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>INC000000152608</v>
+        <v>WO0000000309001</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-17T15:48:10.000Z</v>
+        <v>2026-07-17T08:09:22.000Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>WO0000000308895</v>
+        <v>WO0000000309004</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-17T10:35:42.000Z</v>
+        <v>2026-07-16T14:55:40.999Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000308896</v>
+        <v>WO0000000308899</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-16T15:16:25.000Z</v>
+        <v>2026-07-16T15:17:36.000Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>WO0000000309001</v>
+        <v>WO0000000308926</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-17T08:09:22.000Z</v>
+        <v>2026-07-17T10:04:52.000Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000309004</v>
+        <v>WO0000000309007</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-16T14:55:40.999Z</v>
+        <v>2026-07-16T15:03:12.000Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000308899</v>
+        <v>WO0000000309009</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-16T15:17:36.000Z</v>
+        <v>2026-07-21T08:15:25.000Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>WO0000000308926</v>
+        <v>WO0000000309002</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-17T10:04:52.000Z</v>
+        <v>2026-07-16T15:07:58.000Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>WO0000000309007</v>
+        <v>WO0000000309011</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-16T15:03:12.000Z</v>
+        <v>2026-07-17T10:44:02.999Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>WO0000000309009</v>
+        <v>INC000000152616</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-21T08:15:25.000Z</v>
+        <v>2026-07-17T09:51:34.000Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>WO0000000309002</v>
+        <v>WO0000000308938</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-16T15:31:18.000Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000309011</v>
+        <v>WO0000000309018</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-17T10:44:02.999Z</v>
+        <v>2026-07-16T15:30:08.999Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>INC000000152616</v>
+        <v>WO0000000309021</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-17T09:51:34.000Z</v>
+        <v>2026-07-17T09:59:10.000Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>WO0000000308938</v>
+        <v>INC000000152711</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-16T16:04:14.000Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000309018</v>
+        <v>WO0000000309024</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-16T15:30:08.999Z</v>
+        <v>2026-07-16T15:43:10.000Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>WO0000000309021</v>
+        <v>WO0000000308947</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-17T09:59:10.000Z</v>
+        <v>2026-07-17T10:21:08.000Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>INC000000152711</v>
+        <v>WO0000000309026</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-16T16:04:14.000Z</v>
+        <v>2026-07-16T15:49:08.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>WO0000000309024</v>
+        <v>WO0000000309025</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-16T15:43:10.000Z</v>
+        <v>2026-07-16T15:47:35.000Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>WO0000000308947</v>
+        <v>WO0000000309028</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-17T10:21:08.000Z</v>
+        <v>2026-07-17T15:14:51.999Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000309026</v>
+        <v>WO0000000309031</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-16T15:49:08.000Z</v>
+        <v>2026-07-16T15:52:24.000Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>WO0000000309025</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-17T16:59:46.000Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>WO0000000309028</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-17T15:14:51.999Z</v>
+        <v>2026-07-16T16:05:14.000Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000309039</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-16T15:52:24.000Z</v>
+        <v>2026-07-17T08:39:45.999Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-17T16:59:46.000Z</v>
+        <v>2026-07-17T16:15:11.000Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>WO0000000309036</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-17T08:39:45.999Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-17T16:15:11.000Z</v>
+        <v>2026-07-18T14:29:17.000Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>INC000000152628</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-17T10:44:38.000Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000309041</v>
+        <v>WO0000000308967</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-21T09:14:56.000Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>WO0000000308965</v>
+        <v>INC000000152630</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-18T14:29:17.000Z</v>
+        <v>2026-07-21T07:35:42.000Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>WO0000000308966</v>
+        <v>WO0000000309044</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-16T16:26:35.999Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>WO0000000308967</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-16T17:35:59.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>INC000000152630</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-21T07:35:42.000Z</v>
+        <v>2026-07-16T16:32:21.000Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000309047</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-16T16:26:35.999Z</v>
+        <v>2026-07-16T16:37:18.000Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000308970</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-16T16:38:04.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-16T16:32:21.000Z</v>
+        <v>2026-07-16T16:43:04.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>WO0000000309047</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-16T16:37:18.000Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>WO0000000308970</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-16T16:38:04.000Z</v>
+        <v>2026-07-17T07:16:12.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>WO0000000308975</v>
+        <v>WO0000000309052</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-16T16:43:04.000Z</v>
+        <v>2026-07-17T07:44:17.000Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>WO0000000309050</v>
+        <v>WO0000000308984</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-16T17:10:27.000Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000309060</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-17T07:16:12.000Z</v>
+        <v>2026-07-16T22:04:20.000Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>WO0000000309052</v>
+        <v>WO0000000309062</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-17T07:44:17.000Z</v>
+        <v>2026-07-17T10:25:11.000Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>WO0000000308984</v>
+        <v>WO0000000309063</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-16T17:10:27.000Z</v>
+        <v>2026-07-16T17:31:20.000Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000309060</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-16T22:04:20.000Z</v>
+        <v>2026-07-21T07:53:18.000Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>WO0000000309062</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-17T10:25:11.000Z</v>
+        <v>2026-07-16T19:52:29.999Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>WO0000000309063</v>
+        <v>WO0000000309065</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-16T17:31:20.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000305262</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-21T07:53:18.000Z</v>
+        <v>2026-07-17T07:53:28.999Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>WO0000000308987</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-16T19:52:29.999Z</v>
+        <v>2026-07-16T19:32:50.000Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>WO0000000309065</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-21T07:53:32.000Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>WO0000000305262</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-17T07:53:28.999Z</v>
+        <v>2026-07-16T19:42:22.000Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>WO0000000309073</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-16T19:32:50.000Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>INC000000152643</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-21T07:53:32.000Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B721" s="1" t="d">
-        <v>2026-07-16T19:42:22.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>WO0000000309077</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>WO0000000309079</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-17T10:15:24.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000309082</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T09:36:16.000Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000308997</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>WO0000000308999</v>
+        <v>WO0000000309084</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-17T10:15:24.000Z</v>
+        <v>2026-07-17T10:26:01.000Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>WO0000000309082</v>
+        <v>INC000000152731</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-17T09:36:16.000Z</v>
+        <v>2026-07-17T10:29:59.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>WO0000000309101</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-17T06:53:11.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>WO0000000309084</v>
+        <v>INC000000152653</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-17T10:26:01.000Z</v>
+        <v>2026-07-18T16:16:07.999Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>INC000000152731</v>
+        <v>WO0000000309097</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-17T10:29:59.000Z</v>
+        <v>2026-07-17T08:03:06.999Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>INC000000152733</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-17T08:06:35.000Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>INC000000152653</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-18T16:16:07.999Z</v>
+        <v>2026-07-17T07:45:37.999Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>WO0000000309097</v>
+        <v>INC000000152739</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-17T08:03:06.999Z</v>
+        <v>2026-07-17T09:20:05.999Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>INC000000152737</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-17T08:06:35.000Z</v>
+        <v>2026-07-17T08:07:23.000Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>WO0000000309124</v>
+        <v>WO0000000309131</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-17T07:45:37.999Z</v>
+        <v>2026-07-17T08:12:37.000Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>INC000000152739</v>
+        <v>WO0000000309212</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-17T09:20:05.999Z</v>
+        <v>2026-07-17T15:11:51.000Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-17T08:07:23.000Z</v>
+        <v>2026-07-21T09:04:31.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>WO0000000309131</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-17T08:12:37.000Z</v>
+        <v>2026-07-17T11:36:59.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>WO0000000309212</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-17T15:11:51.000Z</v>
+        <v>2026-07-17T12:44:26.000Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>WO0000000309136</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-21T09:04:31.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000152746</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-17T11:36:59.000Z</v>
+        <v>2026-07-21T09:11:42.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>INC000000152663</v>
+        <v>WO0000000309153</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-17T12:44:26.000Z</v>
+        <v>2026-07-21T08:54:48.000Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>INC000000152664</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T08:54:14.000Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>INC000000152746</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-17T10:32:57.999Z</v>
+        <v>2026-07-17T08:54:36.999Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>WO0000000309153</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-21T08:54:48.000Z</v>
+        <v>2026-07-18T12:40:15.000Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309226</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-17T08:54:14.000Z</v>
+        <v>2026-07-17T08:58:32.999Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>WO0000000309155</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-17T08:54:36.999Z</v>
+        <v>2026-07-17T14:29:04.000Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>INC000000152668</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-18T12:40:15.000Z</v>
+        <v>2026-07-17T09:57:18.999Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>WO0000000309226</v>
+        <v>INC000000152673</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-17T08:58:32.999Z</v>
+        <v>2026-07-21T08:52:59.000Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>WO0000000309231</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-17T14:29:04.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>INC000000152673</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-21T08:52:59.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-17T14:47:59.000Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-17T09:26:58.999Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-17T12:06:25.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>WO0000000309164</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-17T14:47:59.000Z</v>
+        <v>2026-07-17T15:50:55.000Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309246</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-17T09:26:58.999Z</v>
+        <v>2026-07-17T09:32:32.000Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>INC000000152678</v>
+        <v>WO0000000309167</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-17T12:06:25.000Z</v>
+        <v>2026-07-21T08:57:56.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>INC000000152679</v>
+        <v>INC000000152761</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-17T15:50:55.000Z</v>
+        <v>2026-07-17T10:05:32.000Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>WO0000000309246</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-17T09:32:32.000Z</v>
+        <v>2026-07-17T09:36:30.000Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>WO0000000309167</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-21T08:57:56.000Z</v>
+        <v>2026-07-17T09:37:50.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>INC000000152761</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-17T10:05:32.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309168</v>
+        <v>WO0000000309249</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-17T09:36:30.000Z</v>
+        <v>2026-07-17T09:38:10.000Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-17T09:37:50.000Z</v>
+        <v>2026-07-21T09:14:42.000Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>WO0000000309172</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-21T08:45:24.000Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>WO0000000309249</v>
+        <v>WO0000000309251</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-17T09:40:19.000Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>WO0000000309250</v>
+        <v>INC000000152763</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-17T09:54:11.000Z</v>
+        <v>2026-07-17T10:09:48.000Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>INC000000152760</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-21T08:45:24.000Z</v>
+        <v>2026-07-21T08:17:56.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>WO0000000309251</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-17T09:40:19.000Z</v>
+        <v>2026-07-17T09:57:50.000Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>INC000000152763</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-17T10:09:48.000Z</v>
+        <v>2026-07-17T11:14:20.000Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-21T08:17:56.000Z</v>
+        <v>2026-07-17T14:47:53.999Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-17T09:57:50.000Z</v>
+        <v>2026-07-17T11:11:39.000Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-17T11:14:20.000Z</v>
+        <v>2026-07-17T11:15:36.000Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-17T14:47:53.999Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-17T11:11:39.000Z</v>
+        <v>2026-07-17T11:13:13.000Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>WO0000000309189</v>
+        <v>INC000000152688</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-17T11:15:36.000Z</v>
+        <v>2026-07-21T08:15:27.000Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>WO0000000309258</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-17T15:17:55.000Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>WO0000000309259</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-17T11:13:13.000Z</v>
+        <v>2026-07-17T10:18:38.000Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>INC000000152688</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-21T08:15:27.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152770</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-17T15:17:55.000Z</v>
+        <v>2026-07-17T10:27:03.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000309262</v>
+        <v>WO0000000305263</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-17T10:18:38.000Z</v>
+        <v>2026-07-17T15:28:33.000Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>INC000000152690</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-17T11:24:41.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>INC000000152770</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-17T10:27:03.000Z</v>
+        <v>2026-07-17T10:29:44.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>WO0000000305263</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-17T15:28:33.000Z</v>
+        <v>2026-07-17T11:25:20.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>WO0000000309195</v>
+        <v>INC000000152691</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-17T11:24:41.000Z</v>
+        <v>2026-07-17T11:21:16.000Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>INC000000152772</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-17T10:29:44.000Z</v>
+        <v>2026-07-17T12:51:35.000Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>INC000000152774</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-17T11:25:20.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>INC000000152691</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-17T11:21:16.000Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>WO0000000309199</v>
+        <v>WO0000000309269</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-17T12:51:35.000Z</v>
+        <v>2026-07-17T11:19:32.000Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>WO0000000309200</v>
+        <v>WO0000000309270</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-17T16:48:27.000Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-17T14:48:08.000Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>WO0000000309269</v>
+        <v>INC000000152694</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-17T11:19:32.000Z</v>
+        <v>2026-07-18T13:02:06.999Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>WO0000000309270</v>
+        <v>WO0000000309407</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-17T16:48:27.000Z</v>
+        <v>2026-07-17T10:43:38.999Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>WO0000000309271</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-17T14:48:08.000Z</v>
+        <v>2026-07-19T12:51:55.999Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>INC000000152694</v>
+        <v>WO0000000309409</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-18T13:02:06.999Z</v>
+        <v>2026-07-17T11:23:02.000Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>WO0000000309407</v>
+        <v>WO0000000309277</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-21T09:19:50.000Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>INC000000152777</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-19T12:51:55.999Z</v>
+        <v>2026-07-21T09:07:41.000Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>WO0000000309409</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-17T11:23:02.000Z</v>
+        <v>2026-07-17T10:48:35.999Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000309277</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-17T10:50:48.000Z</v>
+        <v>2026-07-17T10:53:18.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-21T08:19:28.999Z</v>
+        <v>2026-07-17T12:28:53.000Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-17T10:48:35.999Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-17T10:53:18.000Z</v>
+        <v>2026-07-17T10:58:23.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309285</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-17T12:28:53.000Z</v>
+        <v>2026-07-17T10:57:51.000Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>WO0000000309282</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-17T11:48:14.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>WO0000000309413</v>
+        <v>INC000000152782</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-17T10:58:23.000Z</v>
+        <v>2026-07-17T11:46:20.999Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309285</v>
+        <v>WO0000000309417</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-17T10:57:51.000Z</v>
+        <v>2026-07-17T11:02:34.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>INC000000152802</v>
+        <v>INC000000152700</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-17T11:48:14.000Z</v>
+        <v>2026-07-17T18:10:18.000Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>INC000000152782</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-17T11:46:20.999Z</v>
+        <v>2026-07-18T08:52:20.999Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>WO0000000309417</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-17T11:02:34.000Z</v>
+        <v>2026-07-17T11:12:43.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>INC000000152700</v>
+        <v>WO0000000309291</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-17T18:10:18.000Z</v>
+        <v>2026-07-17T11:55:44.999Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>WO0000000309422</v>
+        <v>INC000000152784</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-18T08:52:20.999Z</v>
+        <v>2026-07-17T11:26:12.000Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-17T11:12:43.000Z</v>
+        <v>2026-07-17T11:15:48.000Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>WO0000000309291</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-17T11:55:44.999Z</v>
+        <v>2026-07-17T11:17:12.999Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>INC000000152784</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-17T11:26:12.000Z</v>
+        <v>2026-07-17T14:48:17.000Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-17T11:15:48.000Z</v>
+        <v>2026-07-17T11:21:58.000Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-17T11:17:12.999Z</v>
+        <v>2026-07-21T09:14:29.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309432</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-17T14:48:17.000Z</v>
+        <v>2026-07-17T11:29:50.000Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-17T11:21:58.000Z</v>
+        <v>2026-07-17T11:26:05.999Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309299</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-17T11:50:50.000Z</v>
+        <v>2026-07-17T11:28:13.000Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000309432</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-17T11:29:50.000Z</v>
+        <v>2026-07-17T11:29:56.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>WO0000000309433</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-17T11:26:05.999Z</v>
+        <v>2026-07-17T16:49:37.000Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000309299</v>
+        <v>WO0000000309439</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-17T11:28:13.000Z</v>
+        <v>2026-07-17T11:59:55.999Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-17T11:29:56.000Z</v>
+        <v>2026-07-17T15:38:05.000Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>WO0000000309438</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-17T16:49:37.000Z</v>
+        <v>2026-07-17T12:04:35.000Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>WO0000000309439</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-17T11:59:55.999Z</v>
+        <v>2026-07-18T12:02:37.000Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>WO0000000309503</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-17T15:38:05.000Z</v>
+        <v>2026-07-17T11:41:41.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>INC000000152789</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-17T12:04:35.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-18T12:02:37.000Z</v>
+        <v>2026-07-17T15:32:46.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309444</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-17T11:41:41.000Z</v>
+        <v>2026-07-17T11:41:48.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-17T11:44:22.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>WO0000000309504</v>
+        <v>INC000000152810</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-17T11:39:29.000Z</v>
+        <v>2026-07-21T07:51:23.000Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>WO0000000309441</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-17T15:32:46.000Z</v>
+        <v>2026-07-17T11:53:25.999Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000309444</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-17T11:41:48.000Z</v>
+        <v>2026-07-21T08:25:47.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000309447</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-17T11:44:22.000Z</v>
+        <v>2026-07-17T11:55:31.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>INC000000152810</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-21T07:51:23.000Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-17T11:53:25.999Z</v>
+        <v>2026-07-17T14:48:03.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-21T08:25:47.000Z</v>
+        <v>2026-07-17T15:45:57.000Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-17T11:55:31.000Z</v>
+        <v>2026-07-17T14:48:13.000Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000309513</v>
+        <v>INC000000152797</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-21T08:59:18.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-17T14:48:03.000Z</v>
+        <v>2026-07-18T08:52:31.000Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-17T15:45:57.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000309457</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-17T14:48:13.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>INC000000152797</v>
+        <v>INC000000152800</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-21T08:59:18.000Z</v>
+        <v>2026-07-21T06:37:05.999Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-18T08:52:31.000Z</v>
+        <v>2026-07-17T12:23:35.999Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000309514</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>WO0000000309462</v>
+        <v>INC000000152901</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-17T12:30:00.000Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>INC000000152800</v>
+        <v>WO0000000309466</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-21T06:37:05.999Z</v>
+        <v>2026-07-17T12:32:56.000Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>WO0000000309465</v>
+        <v>INC000000152813</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-17T12:23:35.999Z</v>
+        <v>2026-07-21T09:11:10.999Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000309520</v>
+        <v>WO0000000309525</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-17T16:15:45.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>INC000000152901</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-17T12:30:00.000Z</v>
+        <v>2026-07-17T17:44:41.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000309466</v>
+        <v>WO0000000309526</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-17T12:32:56.000Z</v>
+        <v>2026-07-21T08:25:19.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>INC000000152813</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-17T12:36:17.000Z</v>
+        <v>2026-07-21T09:11:31.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000309525</v>
+        <v>INC000000152814</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-17T16:15:45.000Z</v>
+        <v>2026-07-17T12:49:52.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>INC000000152903</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-17T17:44:41.000Z</v>
+        <v>2026-07-20T13:33:22.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>WO0000000309526</v>
+        <v>WO0000000309478</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-21T08:25:19.000Z</v>
+        <v>2026-07-17T15:55:47.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>WO0000000309470</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-21T08:14:01.000Z</v>
+        <v>2026-07-17T12:55:06.999Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>INC000000152814</v>
+        <v>WO0000000309534</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-17T12:49:52.000Z</v>
+        <v>2026-07-17T13:00:45.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>INC000000152908</v>
+        <v>INC000000152910</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-20T13:33:22.000Z</v>
+        <v>2026-07-21T07:51:47.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>WO0000000309478</v>
+        <v>INC000000152815</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-17T15:55:47.000Z</v>
+        <v>2026-07-17T21:20:43.999Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-17T12:55:06.999Z</v>
+        <v>2026-07-17T15:49:27.999Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>WO0000000309534</v>
+        <v>WO0000000309488</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-17T13:00:45.000Z</v>
+        <v>2026-07-17T13:20:57.999Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>INC000000152910</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-21T07:51:47.000Z</v>
+        <v>2026-07-21T08:46:11.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>INC000000152815</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-17T21:20:43.999Z</v>
+        <v>2026-07-18T01:16:50.999Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000309489</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-17T15:49:27.999Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>WO0000000309488</v>
+        <v>INC000000152915</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-17T13:20:57.999Z</v>
+        <v>2026-07-18T12:02:15.999Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>INC000000152914</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-21T08:46:11.000Z</v>
+        <v>2026-07-21T08:45:58.000Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>WO0000000309541</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-17T13:27:09.000Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>INC000000152913</v>
+        <v>WO0000000309545</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-18T01:16:50.999Z</v>
+        <v>2026-07-21T07:54:44.000Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>WO0000000309487</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-18T01:16:05.000Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>INC000000152915</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-18T12:02:15.999Z</v>
+        <v>2026-07-17T14:11:39.000Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>WO0000000309497</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-21T08:45:58.000Z</v>
+        <v>2026-07-20T13:35:30.999Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000309499</v>
+        <v>WO0000000309548</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-21T08:38:16.999Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000309545</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-21T07:54:44.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>INC000000152919</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-18T01:16:05.000Z</v>
+        <v>2026-07-17T15:55:02.000Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000309546</v>
+        <v>WO0000000309604</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-17T14:28:20.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>INC000000152824</v>
+        <v>INC000000152922</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-20T13:35:30.999Z</v>
+        <v>2026-07-21T07:10:12.000Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>WO0000000309548</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-21T08:38:16.999Z</v>
+        <v>2026-07-17T14:30:26.000Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>INC000000152921</v>
+        <v>INC000000152827</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-20T13:32:44.000Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>WO0000000309603</v>
+        <v>INC000000152828</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-17T15:55:02.000Z</v>
+        <v>2026-07-17T14:45:48.000Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>WO0000000309604</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-17T14:28:20.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>INC000000152922</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-21T07:10:12.000Z</v>
+        <v>2026-07-19T00:08:20.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>WO0000000309549</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-17T14:30:26.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>INC000000152827</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-20T13:32:44.000Z</v>
+        <v>2026-07-17T14:57:05.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>INC000000152828</v>
+        <v>WO0000000309611</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-17T14:45:48.000Z</v>
+        <v>2026-07-21T08:49:56.000Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>WO0000000309551</v>
+        <v>INC000000152927</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-17T15:58:26.000Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000309609</v>
+        <v>WO0000000309613</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-19T00:08:20.000Z</v>
+        <v>2026-07-17T15:01:59.000Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>WO0000000309553</v>
+        <v>INC000000152928</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-21T06:26:41.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-17T14:57:05.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>WO0000000309611</v>
+        <v>WO0000000309559</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-21T08:49:56.000Z</v>
+        <v>2026-07-17T15:56:29.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>INC000000152927</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-17T15:58:26.000Z</v>
+        <v>2026-07-18T08:45:42.000Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>WO0000000309613</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-17T15:01:59.000Z</v>
+        <v>2026-07-17T15:57:48.000Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>INC000000152928</v>
+        <v>INC000000152931</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-21T06:26:41.000Z</v>
+        <v>2026-07-21T08:13:12.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-17T15:20:43.999Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000309559</v>
+        <v>WO0000000309563</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-17T15:56:29.000Z</v>
+        <v>2026-07-17T15:24:26.000Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>WO0000000309615</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-18T08:45:42.000Z</v>
+        <v>2026-07-18T11:14:25.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>WO0000000309616</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-17T15:57:48.000Z</v>
+        <v>2026-07-17T16:04:00.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-21T08:13:12.000Z</v>
+        <v>2026-07-17T15:31:50.999Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309572</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-21T08:34:49.000Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>WO0000000309563</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>WO0000000309304</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-21T08:52:37.999Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>INC000000152933</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-18T11:14:25.000Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-17T16:04:00.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-21T08:44:02.000Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>WO0000000309572</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-21T08:34:49.000Z</v>
+        <v>2026-07-17T16:25:00.000Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-18T06:53:20.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000309574</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309635</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-17T16:06:26.000Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>WO0000000309626</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-21T08:44:02.000Z</v>
+        <v>2026-07-18T07:13:50.000Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>WO0000000309627</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-17T16:25:00.000Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>WO0000000309629</v>
+        <v>INC000000152940</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-18T06:53:20.000Z</v>
+        <v>2026-07-21T08:42:40.000Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>WO0000000309632</v>
+        <v>WO0000000309582</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-21T09:17:55.000Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>WO0000000309635</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-17T16:06:26.000Z</v>
+        <v>2026-07-17T17:05:49.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-18T06:19:47.000Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>WO0000000309636</v>
+        <v>WO0000000309583</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-18T07:13:50.000Z</v>
+        <v>2026-07-17T16:34:20.000Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>INC000000152838</v>
+        <v>WO0000000309585</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-21T09:19:00.000Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>INC000000152940</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-21T08:42:40.000Z</v>
+        <v>2026-07-17T16:39:05.000Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>WO0000000309582</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-21T07:39:39.000Z</v>
+        <v>2026-07-18T12:55:19.000Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309587</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-17T17:05:49.000Z</v>
+        <v>2026-07-17T16:39:17.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>WO0000000309641</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-18T06:19:47.000Z</v>
+        <v>2026-07-18T07:38:46.000Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>WO0000000309583</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-17T16:34:20.000Z</v>
+        <v>2026-07-18T13:55:17.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>WO0000000309585</v>
+        <v>INC000000152945</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-21T08:37:12.000Z</v>
+        <v>2026-07-17T16:53:07.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>WO0000000309586</v>
+        <v>WO0000000309643</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-17T16:39:05.000Z</v>
+        <v>2026-07-17T16:52:17.999Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>INC000000152939</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-18T12:55:19.000Z</v>
+        <v>2026-07-17T18:16:22.999Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>WO0000000309587</v>
+        <v>WO0000000309307</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-17T16:39:17.000Z</v>
+        <v>2026-07-18T00:06:54.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>INC000000152944</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-18T07:38:46.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>WO0000000309589</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-18T13:55:17.000Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>INC000000152945</v>
+        <v>INC000000152946</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-17T16:53:07.000Z</v>
+        <v>2026-07-17T17:58:53.999Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>WO0000000309643</v>
+        <v>WO0000000309648</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-17T16:52:17.999Z</v>
+        <v>2026-07-17T18:19:50.000Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>WO0000000309592</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-17T18:16:22.999Z</v>
+        <v>2026-07-17T18:20:35.000Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>WO0000000309307</v>
+        <v>WO0000000309652</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-18T00:06:54.000Z</v>
+        <v>2026-07-20T22:30:37.000Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309308</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-21T07:44:56.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>WO0000000309647</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-21T09:05:18.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>INC000000152946</v>
+        <v>WO0000000309594</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-17T17:58:53.999Z</v>
+        <v>2026-07-20T22:36:47.999Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>WO0000000309648</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-17T18:19:50.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309655</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-17T18:20:35.000Z</v>
+        <v>2026-07-21T09:15:18.000Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>WO0000000309652</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-20T22:30:37.000Z</v>
+        <v>2026-07-17T17:19:38.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>WO0000000309308</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-21T07:44:56.000Z</v>
+        <v>2026-07-21T09:07:50.999Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>WO0000000309595</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-21T08:44:49.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>WO0000000309594</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-20T22:36:47.999Z</v>
+        <v>2026-07-17T18:03:03.000Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>WO0000000309596</v>
+        <v>INC000000152846</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-17T17:43:39.999Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>WO0000000309655</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-17T17:58:30.999Z</v>
+        <v>2026-07-21T09:12:25.000Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>WO0000000309597</v>
+        <v>INC000000152950</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-17T17:19:38.000Z</v>
+        <v>2026-07-21T08:03:13.000Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>WO0000000309309</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-17T17:20:39.000Z</v>
+        <v>2026-07-17T18:11:18.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>INC000000152948</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-21T08:44:49.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>INC000000152845</v>
+        <v>WO0000000309598</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-17T18:03:03.000Z</v>
+        <v>2026-07-21T08:16:54.999Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>INC000000152846</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-17T17:43:39.999Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>WO0000000309310</v>
+        <v>WO0000000309600</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-17T17:30:03.000Z</v>
+        <v>2026-07-21T07:30:44.000Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>INC000000152950</v>
+        <v>INC000000152844</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-21T08:03:13.000Z</v>
+        <v>2026-07-21T08:57:48.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>INC000000152848</v>
+        <v>WO0000000309659</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-17T18:21:50.000Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>WO0000000309598</v>
+        <v>WO0000000309705</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-21T08:16:54.999Z</v>
+        <v>2026-07-17T18:22:25.999Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>WO0000000309599</v>
+        <v>WO0000000309707</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-21T08:26:12.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>WO0000000309600</v>
+        <v>WO0000000309660</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-21T07:30:44.000Z</v>
+        <v>2026-07-17T18:27:35.999Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>INC000000152844</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-21T08:57:48.000Z</v>
+        <v>2026-07-21T08:43:57.000Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>WO0000000309701</v>
+        <v>WO0000000309661</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-17T18:21:13.999Z</v>
+        <v>2026-07-21T09:05:58.999Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>WO0000000309659</v>
+        <v>INC000000152954</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-18T10:44:32.000Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>WO0000000309704</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-17T18:21:50.000Z</v>
+        <v>2026-07-21T08:32:45.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>WO0000000309705</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-17T18:22:25.999Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>WO0000000309707</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-21T08:26:12.000Z</v>
+        <v>2026-07-18T09:16:52.000Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000309660</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-17T18:27:35.999Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>INC000000152953</v>
+        <v>INC000000152957</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-21T08:43:57.000Z</v>
+        <v>2026-07-18T11:15:19.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>WO0000000309661</v>
+        <v>INC000000152853</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-21T09:05:58.999Z</v>
+        <v>2026-07-20T09:22:52.000Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>INC000000152954</v>
+        <v>INC000000152958</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-18T10:44:32.000Z</v>
+        <v>2026-07-20T09:04:48.999Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>INC000000152955</v>
+        <v>WO0000000309712</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-21T08:32:45.000Z</v>
+        <v>2026-07-17T20:32:00.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>WO0000000309664</v>
+        <v>INC000000152854</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-17T21:32:15.999Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>INC000000152956</v>
+        <v>INC000000152855</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-18T09:16:52.000Z</v>
+        <v>2026-07-21T08:15:37.000Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>WO0000000309666</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>INC000000152957</v>
+        <v>WO0000000309667</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-18T11:15:19.000Z</v>
+        <v>2026-07-21T07:08:18.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>INC000000152853</v>
+        <v>WO0000000309715</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-20T09:22:52.000Z</v>
+        <v>2026-07-21T07:55:35.000Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>INC000000152958</v>
+        <v>WO0000000309668</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-20T09:04:48.999Z</v>
+        <v>2026-07-21T07:28:51.000Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>WO0000000309712</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-17T20:32:00.000Z</v>
+        <v>2026-07-21T07:55:12.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>INC000000152854</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-17T21:32:15.999Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>INC000000152855</v>
+        <v>INC000000152863</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-21T08:15:37.000Z</v>
+        <v>2026-07-18T11:32:43.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>WO0000000309714</v>
+        <v>INC000000152862</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-21T09:08:10.000Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>WO0000000309667</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-21T07:08:18.000Z</v>
+        <v>2026-07-18T11:57:16.000Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>WO0000000309715</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-21T07:55:35.000Z</v>
+        <v>2026-07-21T09:18:02.999Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>WO0000000309668</v>
+        <v>INC000000152869</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-21T07:28:51.000Z</v>
+        <v>2026-07-21T07:20:13.000Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>WO0000000309669</v>
+        <v>INC000000152965</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-21T07:55:12.000Z</v>
+        <v>2026-07-21T09:00:01.999Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>INC000000152856</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>INC000000152863</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-18T11:32:43.000Z</v>
+        <v>2026-07-18T08:43:13.999Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>INC000000152862</v>
+        <v>WO0000000309678</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-18T06:59:49.000Z</v>
+        <v>2026-07-18T07:42:09.999Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000152877</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-18T11:57:16.000Z</v>
+        <v>2026-07-21T07:17:20.000Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>WO0000000309671</v>
+        <v>INC000000152878</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-18T06:52:20.999Z</v>
+        <v>2026-07-18T08:12:08.000Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>INC000000152869</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-21T07:20:13.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>INC000000152965</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-21T09:00:01.999Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>INC000000152873</v>
+        <v>INC000000152879</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-18T08:11:58.000Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>INC000000152971</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-18T08:43:13.999Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>WO0000000309678</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-18T07:42:09.999Z</v>
+        <v>2026-07-18T12:53:54.000Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>INC000000152877</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-21T07:17:20.000Z</v>
+        <v>2026-07-18T08:39:53.000Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>INC000000152878</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-18T08:12:08.000Z</v>
+        <v>2026-07-18T08:48:11.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>WO0000000309682</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-21T00:11:10.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>WO0000000309686</v>
+        <v>INC000000152980</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-18T16:16:48.000Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>INC000000152879</v>
+        <v>WO0000000309728</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-20T23:05:18.000Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000309689</v>
+        <v>WO0000000309732</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-18T09:10:30.000Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>INC000000152978</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-18T12:53:54.000Z</v>
+        <v>2026-07-21T07:56:14.999Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>INC000000152883</v>
+        <v>INC000000152888</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-18T08:39:53.000Z</v>
+        <v>2026-07-18T09:48:34.000Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>WO0000000309692</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-18T08:48:11.000Z</v>
+        <v>2026-07-18T09:49:22.999Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>INC000000152981</v>
+        <v>WO0000000309698</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-21T00:11:10.000Z</v>
+        <v>2026-07-18T10:07:47.000Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>INC000000152980</v>
+        <v>INC000000152986</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-18T16:16:48.000Z</v>
+        <v>2026-07-21T08:16:08.000Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>WO0000000309728</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-20T23:05:18.000Z</v>
+        <v>2026-07-18T10:49:11.000Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>WO0000000309732</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-18T09:10:30.000Z</v>
+        <v>2026-07-18T09:42:12.000Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>WO0000000309697</v>
+        <v>INC000000152990</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-21T07:56:14.999Z</v>
+        <v>2026-07-21T09:00:11.000Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>INC000000152888</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-18T09:48:34.000Z</v>
+        <v>2026-07-21T07:32:12.000Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>INC000000152985</v>
+        <v>WO0000000309802</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-18T09:49:22.999Z</v>
+        <v>2026-07-21T07:12:45.999Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>WO0000000309698</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-18T10:07:47.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>INC000000152986</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-21T08:16:08.000Z</v>
+        <v>2026-07-20T19:05:32.000Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-18T10:49:11.000Z</v>
+        <v>2026-07-20T19:04:33.999Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>INC000000152989</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-18T09:42:12.000Z</v>
+        <v>2026-07-20T19:03:52.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>INC000000152990</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-21T09:00:11.000Z</v>
+        <v>2026-07-20T19:04:20.000Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>INC000000152890</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-21T07:32:12.000Z</v>
+        <v>2026-07-19T01:10:57.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000309802</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-21T07:12:45.999Z</v>
+        <v>2026-07-18T11:44:19.999Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>WO0000000309803</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-19T01:11:11.000Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-20T19:05:32.000Z</v>
+        <v>2026-07-21T07:32:42.999Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000153000</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-20T19:04:33.999Z</v>
+        <v>2026-07-21T07:31:13.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-20T19:03:52.000Z</v>
+        <v>2026-07-21T07:33:22.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-20T19:04:20.000Z</v>
+        <v>2026-07-21T08:41:17.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>WO0000000309804</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-19T01:10:57.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>WO0000000309805</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-18T11:44:19.999Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000309807</v>
+        <v>INC000000153003</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-19T01:11:11.000Z</v>
+        <v>2026-07-21T09:03:17.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000152900</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-21T07:32:42.999Z</v>
+        <v>2026-07-21T08:04:18.000Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>INC000000153000</v>
+        <v>WO0000000309815</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-21T07:31:13.000Z</v>
+        <v>2026-07-21T09:12:13.999Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000153006</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-21T07:33:22.000Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>INC000000152898</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T08:41:17.000Z</v>
+        <v>2026-07-21T07:19:30.000Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>WO0000000309810</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>WO0000000309752</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-21T06:23:37.000Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000153003</v>
+        <v>INC000000153103</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T09:03:17.000Z</v>
+        <v>2026-07-21T08:04:41.000Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>INC000000152900</v>
+        <v>INC000000153009</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-21T08:04:18.000Z</v>
+        <v>2026-07-21T08:17:58.999Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>WO0000000309815</v>
+        <v>INC000000153011</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-18T11:50:24.000Z</v>
+        <v>2026-07-18T12:32:55.000Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>INC000000153006</v>
+        <v>WO0000000309819</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-20T23:23:23.000Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>INC000000153101</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-21T07:19:30.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>WO0000000309816</v>
+        <v>INC000000153012</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-21T08:03:57.000Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153013</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-21T06:23:37.000Z</v>
+        <v>2026-07-21T07:19:23.999Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>INC000000153103</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-21T08:04:41.000Z</v>
+        <v>2026-07-21T07:31:56.999Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>INC000000153009</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-21T08:17:58.999Z</v>
+        <v>2026-07-21T07:19:54.000Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>INC000000153011</v>
+        <v>INC000000153015</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-18T12:32:55.000Z</v>
+        <v>2026-07-20T15:39:51.999Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>WO0000000309819</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-20T23:23:23.000Z</v>
+        <v>2026-07-21T07:30:09.000Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>WO0000000309759</v>
+        <v>INC000000153017</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-18T15:26:50.000Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>INC000000153012</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-21T08:03:57.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>INC000000153013</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-21T07:19:23.999Z</v>
+        <v>2026-07-18T17:18:50.999Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>WO0000000309825</v>
+        <v>WO0000000309769</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-21T07:31:56.999Z</v>
+        <v>2026-07-21T07:30:32.000Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>INC000000153105</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-21T07:19:54.000Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>INC000000153015</v>
+        <v>WO0000000309830</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-20T15:39:51.999Z</v>
+        <v>2026-07-21T07:38:18.000Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>WO0000000309826</v>
+        <v>INC000000153108</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-21T07:30:09.000Z</v>
+        <v>2026-07-21T07:53:45.000Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>INC000000153017</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-18T15:26:50.000Z</v>
+        <v>2026-07-19T08:43:56.000Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>WO0000000309768</v>
+        <v>INC000000153020</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-21T07:53:07.999Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>INC000000153107</v>
+        <v>WO0000000309772</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-18T17:18:50.999Z</v>
+        <v>2026-07-21T07:55:55.000Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>WO0000000309769</v>
+        <v>WO0000000309773</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-21T07:30:32.000Z</v>
+        <v>2026-07-21T07:56:38.000Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>WO0000000309829</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-21T07:08:54.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>WO0000000309830</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-21T07:38:18.000Z</v>
+        <v>2026-07-19T10:27:01.999Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>INC000000153108</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-21T07:53:45.000Z</v>
+        <v>2026-07-19T13:24:13.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>INC000000153019</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-19T08:43:56.000Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>INC000000153020</v>
+        <v>INC000000153025</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-21T07:53:07.999Z</v>
+        <v>2026-07-19T13:28:43.999Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>WO0000000309772</v>
+        <v>INC000000153024</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-21T07:55:55.000Z</v>
+        <v>2026-07-19T13:24:41.999Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>WO0000000309773</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-21T07:56:38.000Z</v>
+        <v>2026-07-20T18:58:17.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>INC000000153021</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-21T07:08:54.000Z</v>
+        <v>2026-07-21T07:52:42.999Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>INC000000153022</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-19T10:27:01.999Z</v>
+        <v>2026-07-19T12:52:16.000Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153028</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-19T13:24:13.000Z</v>
+        <v>2026-07-20T18:58:47.999Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>INC000000153111</v>
+        <v>INC000000153029</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-19T13:44:46.000Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>INC000000153025</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-19T13:28:43.999Z</v>
+        <v>2026-07-21T07:09:08.000Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>INC000000153024</v>
+        <v>INC000000153118</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-19T13:24:41.999Z</v>
+        <v>2026-07-21T08:32:11.000Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-20T18:58:17.000Z</v>
+        <v>2026-07-19T14:37:17.999Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>WO0000000309834</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-21T07:52:42.999Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153031</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-19T12:52:16.000Z</v>
+        <v>2026-07-20T07:13:50.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>INC000000153028</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-20T18:58:47.999Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>INC000000153029</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-19T13:44:46.000Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-21T07:09:08.000Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>INC000000153118</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-21T08:32:11.000Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>INC000000153120</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-19T14:37:17.999Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>INC000000153121</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-21T07:41:05.999Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>INC000000153031</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-20T07:13:50.000Z</v>
+        <v>2026-07-21T07:47:06.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>WO0000000309780</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-21T07:58:21.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>WO0000000309837</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-21T08:01:28.000Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>WO0000000309781</v>
+        <v>INC000000153123</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-21T08:57:28.999Z</v>
+        <v>2026-07-21T07:54:40.000Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>WO0000000309783</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-20T08:42:15.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>WO0000000309838</v>
+        <v>INC000000153125</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-21T07:46:07.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>INC000000153034</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-21T07:41:05.999Z</v>
+        <v>2026-07-20T12:50:53.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>INC000000153035</v>
+        <v>WO0000000309840</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-21T07:47:06.000Z</v>
+        <v>2026-07-21T08:50:20.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>INC000000153036</v>
+        <v>WO0000000309791</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-21T07:58:21.000Z</v>
+        <v>2026-07-20T12:51:30.000Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>INC000000153037</v>
+        <v>WO0000000309792</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-21T08:01:28.000Z</v>
+        <v>2026-07-20T14:10:35.999Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>INC000000153123</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-21T07:54:40.000Z</v>
+        <v>2026-07-20T14:29:59.999Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>INC000000153038</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-20T08:42:15.000Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>INC000000153125</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-21T07:46:07.000Z</v>
+        <v>2026-07-21T08:43:23.000Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-20T12:50:53.000Z</v>
+        <v>2026-07-20T18:35:59.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>WO0000000309840</v>
+        <v>WO0000000309794</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-21T08:50:20.000Z</v>
+        <v>2026-07-20T18:20:05.999Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>WO0000000309791</v>
+        <v>WO0000000309843</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-20T12:51:30.000Z</v>
+        <v>2026-07-20T18:23:24.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>WO0000000309792</v>
+        <v>WO0000000309796</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-20T14:10:35.999Z</v>
+        <v>2026-07-21T08:49:16.000Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>WO0000000309841</v>
+        <v>WO0000000309845</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-20T14:29:59.999Z</v>
+        <v>2026-07-21T09:16:50.000Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>WO0000000309842</v>
+        <v>WO0000000309846</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T08:48:32.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>INC000000153128</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-21T08:43:23.000Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>WO0000000309793</v>
+        <v>WO0000000309797</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-20T18:35:59.000Z</v>
+        <v>2026-07-20T19:09:36.000Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>WO0000000309794</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-20T18:20:05.999Z</v>
+        <v>2026-07-21T08:36:19.000Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>WO0000000309843</v>
+        <v>WO0000000309798</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-20T18:23:24.000Z</v>
+        <v>2026-07-21T07:04:25.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>WO0000000309795</v>
+        <v>WO0000000309852</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-20T18:30:58.000Z</v>
+        <v>2026-07-20T22:58:26.999Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>WO0000000309796</v>
+        <v>WO0000000309853</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-21T08:49:16.000Z</v>
+        <v>2026-07-21T05:54:59.000Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>WO0000000309845</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T07:13:01.999Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>WO0000000309846</v>
+        <v>INC000000153129</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-21T08:48:32.000Z</v>
+        <v>2026-07-21T07:02:26.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>WO0000000309848</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>WO0000000309797</v>
+        <v>WO0000000309906</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-20T19:09:36.000Z</v>
+        <v>2026-07-21T07:44:08.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>WO0000000309850</v>
+        <v>INC000000153131</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-21T08:49:50.000Z</v>
+        <v>2026-07-21T06:32:02.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>WO0000000309851</v>
+        <v>INC000000153132</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-21T08:36:19.000Z</v>
+        <v>2026-07-21T07:09:39.000Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>WO0000000309798</v>
+        <v>INC000000153044</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-21T07:04:25.000Z</v>
+        <v>2026-07-21T08:18:16.000Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>WO0000000309852</v>
+        <v>WO0000000309909</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-20T22:58:26.999Z</v>
+        <v>2026-07-21T07:43:47.000Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>WO0000000309853</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-21T05:54:59.000Z</v>
+        <v>2026-07-21T08:19:35.999Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>WO0000000309799</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-21T05:59:16.000Z</v>
+        <v>2026-07-21T06:40:04.000Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>WO0000000309901</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-21T07:13:01.999Z</v>
+        <v>2026-07-21T08:16:43.999Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>INC000000153129</v>
+        <v>INC000000153049</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-21T07:02:26.000Z</v>
+        <v>2026-07-21T07:06:12.999Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>WO0000000309902</v>
+        <v>INC000000153050</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T07:46:48.000Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>WO0000000309906</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-21T07:44:08.000Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>INC000000153131</v>
+        <v>INC000000153137</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-21T06:32:02.000Z</v>
+        <v>2026-07-21T07:03:14.999Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>INC000000153132</v>
+        <v>WO0000000309914</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-21T07:09:39.000Z</v>
+        <v>2026-07-21T07:20:13.999Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>INC000000153044</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-21T08:18:16.000Z</v>
+        <v>2026-07-21T08:53:33.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>WO0000000309909</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-21T07:43:47.000Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>INC000000153047</v>
+        <v>INC000000153051</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-21T08:19:35.999Z</v>
+        <v>2026-07-21T07:31:21.000Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>INC000000153046</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-21T06:40:04.000Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>INC000000153134</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-21T08:16:43.999Z</v>
+        <v>2026-07-21T07:22:58.000Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>INC000000153049</v>
+        <v>INC000000153053</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-21T07:06:12.999Z</v>
+        <v>2026-07-21T08:05:04.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>INC000000153050</v>
+        <v>INC000000153055</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-21T07:46:48.000Z</v>
+        <v>2026-07-21T08:14:27.000Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>INC000000153048</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T08:21:47.999Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>INC000000153137</v>
+        <v>WO0000000309927</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-21T07:03:14.999Z</v>
+        <v>2026-07-21T07:54:45.999Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>WO0000000309914</v>
+        <v>INC000000153057</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-21T07:20:13.999Z</v>
+        <v>2026-07-21T08:19:32.000Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>INC000000153138</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-21T08:53:33.000Z</v>
+        <v>2026-07-21T08:26:45.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>INC000000153052</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T08:34:57.999Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>INC000000153051</v>
+        <v>WO0000000309867</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-21T07:31:21.000Z</v>
+        <v>2026-07-21T08:13:16.000Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>WO0000000309862</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T07:57:56.999Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>WO0000000309861</v>
+        <v>INC000000153060</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-21T07:22:58.000Z</v>
+        <v>2026-07-21T08:01:12.999Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>WO0000000309920</v>
+        <v>INC000000153061</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-21T09:00:18.000Z</v>
+        <v>2026-07-21T08:42:12.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>INC000000153053</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-21T08:05:04.000Z</v>
+        <v>2026-07-21T09:09:19.000Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>INC000000153055</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-21T08:14:27.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>INC000000153140</v>
+        <v>INC000000153063</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-21T08:21:47.999Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>WO0000000309927</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-21T07:54:45.999Z</v>
+        <v>2026-07-21T08:51:54.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>INC000000153057</v>
+        <v>WO0000000309876</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-21T08:19:32.000Z</v>
+        <v>2026-07-21T08:19:59.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>INC000000153056</v>
+        <v>WO0000000309877</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-21T08:26:45.000Z</v>
+        <v>2026-07-21T08:15:48.000Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000309875</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-21T08:34:57.999Z</v>
+        <v>2026-07-21T08:23:40.000Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>INC000000153059</v>
+        <v>WO0000000309939</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-21T08:27:55.000Z</v>
+        <v>2026-07-21T08:42:26.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>WO0000000309871</v>
+        <v>WO0000000309878</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-21T07:50:00.000Z</v>
+        <v>2026-07-21T08:35:47.000Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>WO0000000309867</v>
+        <v>WO0000000309941</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-21T08:13:16.000Z</v>
+        <v>2026-07-21T09:14:35.999Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>INC000000153144</v>
+        <v>WO0000000309879</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-21T07:57:56.999Z</v>
+        <v>2026-07-21T08:17:04.000Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>INC000000153060</v>
+        <v>INC000000153148</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-21T08:01:12.999Z</v>
+        <v>2026-07-21T08:33:18.000Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>INC000000153061</v>
+        <v>WO0000000309944</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-21T08:42:12.000Z</v>
+        <v>2026-07-21T08:15:03.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>INC000000153062</v>
+        <v>INC000000153149</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-21T09:05:35.000Z</v>
+        <v>2026-07-21T08:58:21.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>INC000000153143</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>INC000000153063</v>
+        <v>INC000000153151</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:13:22.999Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>INC000000153145</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-21T08:51:54.000Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>WO0000000309876</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-21T08:19:59.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>WO0000000309877</v>
+        <v>INC000000153147</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-21T08:15:48.000Z</v>
+        <v>2026-07-21T09:06:12.000Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>WO0000000309875</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-21T08:23:40.000Z</v>
+        <v>2026-07-21T08:41:34.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>WO0000000309939</v>
+        <v>WO0000000309883</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-21T08:42:26.000Z</v>
+        <v>2026-07-21T08:22:19.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>WO0000000309878</v>
+        <v>INC000000153152</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-21T08:35:47.000Z</v>
+        <v>2026-07-21T08:37:55.999Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>WO0000000309941</v>
+        <v>INC000000153064</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-21T09:01:43.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>WO0000000309879</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-21T08:17:04.000Z</v>
+        <v>2026-07-21T08:42:24.999Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>INC000000153148</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-21T08:33:18.000Z</v>
+        <v>2026-07-21T08:27:24.000Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>WO0000000309944</v>
+        <v>INC000000153067</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-21T08:15:03.000Z</v>
+        <v>2026-07-21T08:44:28.000Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>INC000000153149</v>
+        <v>WO0000000309888</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-21T08:58:21.000Z</v>
+        <v>2026-07-21T08:44:29.999Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>WO0000000309880</v>
+        <v>WO0000000309950</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T08:39:49.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>INC000000153151</v>
+        <v>WO0000000309951</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-21T09:00:58.000Z</v>
+        <v>2026-07-21T08:48:42.000Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>WO0000000309945</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>WO0000000309946</v>
+        <v>WO0000000309952</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T08:33:13.000Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>INC000000153147</v>
+        <v>WO0000000309953</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-21T09:06:12.000Z</v>
+        <v>2026-07-21T08:41:50.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>INC000000153065</v>
+        <v>WO0000000309889</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-21T08:41:34.000Z</v>
+        <v>2026-07-21T08:33:25.000Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>WO0000000309883</v>
+        <v>INC000000153070</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-21T08:22:19.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>INC000000153152</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-21T08:37:55.999Z</v>
+        <v>2026-07-21T08:48:14.999Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>INC000000153064</v>
+        <v>INC000000153156</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T08:39:24.000Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>INC000000153153</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-21T08:42:24.999Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>WO0000000309949</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-21T08:27:24.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>INC000000153067</v>
+        <v>WO0000000309893</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-21T08:44:28.000Z</v>
+        <v>2026-07-21T08:58:55.000Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>WO0000000309888</v>
+        <v>INC000000153071</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-21T08:44:29.999Z</v>
+        <v>2026-07-21T08:50:05.000Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>WO0000000309950</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-21T08:39:49.000Z</v>
+        <v>2026-07-21T08:49:28.000Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>WO0000000309951</v>
+        <v>INC000000153157</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-21T08:48:42.000Z</v>
+        <v>2026-07-21T08:51:40.000Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>INC000000153068</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-21T09:05:09.000Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>WO0000000309952</v>
+        <v>INC000000153073</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-21T08:33:13.000Z</v>
+        <v>2026-07-21T09:07:50.000Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>WO0000000309953</v>
+        <v>INC000000153075</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-21T08:41:50.000Z</v>
+        <v>2026-07-21T09:12:07.000Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>WO0000000309889</v>
+        <v>WO0000000309956</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-21T08:33:25.000Z</v>
+        <v>2026-07-21T08:51:44.999Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>INC000000153070</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:09:20.000Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153158</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-21T08:48:14.999Z</v>
+        <v>2026-07-21T09:19:52.999Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>INC000000153156</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-21T08:39:24.000Z</v>
+        <v>2026-07-21T08:54:42.999Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>WO0000000309892</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-21T09:04:46.000Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>WO0000000309954</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:11:32.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>WO0000000309893</v>
+        <v>WO0000000310005</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-21T08:58:55.000Z</v>
+        <v>2026-07-21T08:57:51.999Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>INC000000153071</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-21T08:50:05.000Z</v>
+        <v>2026-07-21T08:56:12.000Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>INC000000153072</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B1181" s="1" t="d">
-        <v>2026-07-21T08:49:28.000Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>INC000000153157</v>
+        <v>INC000000153076</v>
       </c>
       <c r="B1182" s="1" t="d">
-        <v>2026-07-21T08:51:40.000Z</v>
+        <v>2026-07-21T09:11:32.000Z</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>INC000000153159</v>
+        <v>WO0000000310007</v>
       </c>
       <c r="B1183" s="1" t="d">
-        <v>2026-07-21T09:05:09.000Z</v>
+        <v>2026-07-21T08:57:11.000Z</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>INC000000153073</v>
+        <v>WO0000000310008</v>
       </c>
       <c r="B1184" s="1" t="d">
-        <v>2026-07-21T08:55:34.000Z</v>
+        <v>2026-07-21T08:58:48.000Z</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>INC000000153075</v>
+        <v>WO0000000309962</v>
       </c>
       <c r="B1185" s="1" t="d">
-        <v>2026-07-21T09:00:22.000Z</v>
+        <v>2026-07-21T09:15:42.999Z</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>WO0000000309956</v>
+        <v>WO0000000310009</v>
       </c>
       <c r="B1186" s="1" t="d">
-        <v>2026-07-21T08:51:44.999Z</v>
+        <v>2026-07-21T09:00:52.999Z</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>WO0000000310002</v>
+        <v>WO0000000309963</v>
       </c>
       <c r="B1187" s="1" t="d">
-        <v>2026-07-21T09:05:11.000Z</v>
+        <v>2026-07-21T09:00:20.000Z</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>INC000000153158</v>
+        <v>INC000000153161</v>
       </c>
       <c r="B1188" s="1" t="d">
-        <v>2026-07-21T08:59:00.000Z</v>
+        <v>2026-07-21T09:18:35.000Z</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>WO0000000309957</v>
+        <v>WO0000000309960</v>
       </c>
       <c r="B1189" s="1" t="d">
-        <v>2026-07-21T08:54:42.999Z</v>
+        <v>2026-07-21T09:17:47.000Z</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>WO0000000309958</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B1190" s="1" t="d">
-        <v>2026-07-21T08:54:45.000Z</v>
+        <v>2026-07-21T09:03:20.999Z</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>WO0000000310004</v>
+        <v>WO0000000309966</v>
       </c>
       <c r="B1191" s="1" t="d">
-        <v>2026-07-21T09:03:08.000Z</v>
+        <v>2026-07-21T09:17:50.000Z</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>WO0000000310005</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B1192" s="1" t="d">
-        <v>2026-07-21T08:57:51.999Z</v>
+        <v>2026-07-21T09:05:07.999Z</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>WO0000000309959</v>
+        <v>WO0000000309967</v>
       </c>
       <c r="B1193" s="1" t="d">
-        <v>2026-07-21T08:56:12.000Z</v>
+        <v>2026-07-21T09:02:23.000Z</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>WO0000000310006</v>
+        <v>INC000000153078</v>
       </c>
       <c r="B1194" s="1" t="d">
-        <v>2026-07-21T09:05:13.000Z</v>
+        <v>2026-07-21T09:17:45.000Z</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>INC000000153076</v>
+        <v>WO0000000310012</v>
       </c>
       <c r="B1195" s="1" t="d">
-        <v>2026-07-21T08:57:01.000Z</v>
+        <v>2026-07-21T09:18:52.000Z</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>WO0000000310007</v>
+        <v>WO0000000310013</v>
       </c>
       <c r="B1196" s="1" t="d">
-        <v>2026-07-21T08:57:11.000Z</v>
+        <v>2026-07-21T09:07:07.000Z</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>WO0000000310008</v>
+        <v>WO0000000309973</v>
       </c>
       <c r="B1197" s="1" t="d">
-        <v>2026-07-21T08:58:48.000Z</v>
+        <v>2026-07-21T09:08:48.000Z</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>WO0000000309962</v>
+        <v>WO0000000309969</v>
       </c>
       <c r="B1198" s="1" t="d">
-        <v>2026-07-21T09:03:49.999Z</v>
+        <v>2026-07-21T09:19:52.000Z</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>WO0000000310009</v>
+        <v>WO0000000310015</v>
       </c>
       <c r="B1199" s="1" t="d">
-        <v>2026-07-21T09:00:52.999Z</v>
+        <v>2026-07-21T09:12:18.999Z</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>WO0000000309963</v>
+        <v>INC000000153079</v>
       </c>
       <c r="B1200" s="1" t="d">
-        <v>2026-07-21T09:00:20.000Z</v>
+        <v>2026-07-21T09:12:25.000Z</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>INC000000153161</v>
+        <v>INC000000153164</v>
       </c>
       <c r="B1201" s="1" t="d">
-        <v>2026-07-21T09:00:46.000Z</v>
+        <v>2026-07-21T09:16:22.000Z</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>WO0000000309960</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B1202" s="1" t="d">
-        <v>2026-07-21T09:00:48.000Z</v>
+        <v>2026-07-21T09:17:36.999Z</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>INC000000153074</v>
+        <v>WO0000000310016</v>
       </c>
       <c r="B1203" s="1" t="d">
-        <v>2026-07-21T09:03:20.999Z</v>
+        <v>2026-07-21T09:14:48.000Z</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>WO0000000309966</v>
+        <v>INC000000153168</v>
       </c>
       <c r="B1204" s="1" t="d">
-        <v>2026-07-21T09:01:56.000Z</v>
+        <v>2026-07-21T09:15:14.000Z</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>WO0000000309961</v>
+        <v>WO0000000310017</v>
       </c>
       <c r="B1205" s="1" t="d">
-        <v>2026-07-21T09:05:07.999Z</v>
+        <v>2026-07-21T09:16:13.000Z</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>WO0000000309967</v>
+        <v>WO0000000310018</v>
       </c>
       <c r="B1206" s="1" t="d">
-        <v>2026-07-21T09:02:23.000Z</v>
+        <v>2026-07-21T09:18:47.000Z</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="str">
-        <v>INC000000153078</v>
+        <v>INC000000153170</v>
       </c>
       <c r="B1207" s="1" t="d">
-        <v>2026-07-21T09:02:45.000Z</v>
+        <v>2026-07-21T09:18:59.000Z</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>INC000000153077</v>
+        <v>WO0000000310019</v>
       </c>
       <c r="B1208" s="1" t="d">
-        <v>2026-07-21T09:03:20.999Z</v>
+        <v>2026-07-21T09:19:04.000Z</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>WO0000000310011</v>
+        <v>INC000000153169</v>
       </c>
       <c r="B1209" s="1" t="d">
-        <v>2026-07-21T09:05:42.000Z</v>
+        <v>2026-07-21T09:19:13.000Z</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>WO0000000309970</v>
+        <v>WO0000000309981</v>
       </c>
       <c r="B1210" s="1" t="d">
-        <v>2026-07-21T09:05:28.000Z</v>
+        <v>2026-07-21T09:19:50.000Z</v>
       </c>
     </row>
     <row r="1211">

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1211"/>
+  <dimension ref="A1:B1217"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2123,482 +2123,482 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>WO0000000287464</v>
+        <v>INC000000142452</v>
       </c>
       <c r="B216" s="1" t="d">
-        <v>2026-07-08T10:11:20.999Z</v>
+        <v>2026-07-10T09:46:03.999Z</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>INC000000142518</v>
+        <v>WO0000000287464</v>
       </c>
       <c r="B217" s="1" t="d">
-        <v>2026-06-26T20:28:21.000Z</v>
+        <v>2026-07-08T10:11:20.999Z</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>WO0000000288840</v>
+        <v>INC000000142518</v>
       </c>
       <c r="B218" s="1" t="d">
-        <v>2026-07-03T12:08:05.000Z</v>
+        <v>2026-06-26T20:28:21.000Z</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>WO0000000288737</v>
+        <v>WO0000000288840</v>
       </c>
       <c r="B219" s="1" t="d">
-        <v>2026-07-03T11:40:50.999Z</v>
+        <v>2026-07-03T12:08:05.000Z</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>INC000000143439</v>
+        <v>WO0000000288737</v>
       </c>
       <c r="B220" s="1" t="d">
-        <v>2026-06-26T20:28:54.000Z</v>
+        <v>2026-07-03T11:40:50.999Z</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>INC000000144822</v>
+        <v>INC000000143439</v>
       </c>
       <c r="B221" s="1" t="d">
-        <v>2026-07-16T08:31:54.000Z</v>
+        <v>2026-06-26T20:28:54.000Z</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>INC000000145025</v>
+        <v>INC000000144822</v>
       </c>
       <c r="B222" s="1" t="d">
-        <v>2026-07-02T12:27:43.000Z</v>
+        <v>2026-07-16T08:31:54.000Z</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>INC000000145194</v>
+        <v>INC000000145025</v>
       </c>
       <c r="B223" s="1" t="d">
-        <v>2026-07-16T09:36:17.000Z</v>
+        <v>2026-07-02T12:27:43.000Z</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>INC000000146528</v>
+        <v>INC000000145194</v>
       </c>
       <c r="B224" s="1" t="d">
-        <v>2026-07-02T12:27:43.000Z</v>
+        <v>2026-07-16T09:36:17.000Z</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>WO0000000295650</v>
+        <v>INC000000146528</v>
       </c>
       <c r="B225" s="1" t="d">
-        <v>2026-07-07T08:33:04.999Z</v>
+        <v>2026-07-02T12:27:43.000Z</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>WO0000000296601</v>
+        <v>WO0000000295650</v>
       </c>
       <c r="B226" s="1" t="d">
-        <v>2026-06-30T09:52:50.999Z</v>
+        <v>2026-07-07T08:33:04.999Z</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>INC000000147297</v>
+        <v>WO0000000296601</v>
       </c>
       <c r="B227" s="1" t="d">
-        <v>2026-07-08T12:27:13.999Z</v>
+        <v>2026-06-30T09:52:50.999Z</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>WO0000000297046</v>
+        <v>INC000000147297</v>
       </c>
       <c r="B228" s="1" t="d">
-        <v>2026-07-16T15:23:18.000Z</v>
+        <v>2026-07-08T12:27:13.999Z</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>WO0000000291773</v>
+        <v>WO0000000297046</v>
       </c>
       <c r="B229" s="1" t="d">
-        <v>2026-07-06T12:05:36.000Z</v>
+        <v>2026-07-16T15:23:18.000Z</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>INC000000147569</v>
+        <v>WO0000000291773</v>
       </c>
       <c r="B230" s="1" t="d">
-        <v>2026-06-26T20:31:22.000Z</v>
+        <v>2026-07-06T12:05:36.000Z</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>WO0000000298353</v>
+        <v>INC000000147569</v>
       </c>
       <c r="B231" s="1" t="d">
-        <v>2026-07-14T11:48:03.000Z</v>
+        <v>2026-06-26T20:31:22.000Z</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>WO0000000298379</v>
+        <v>WO0000000298353</v>
       </c>
       <c r="B232" s="1" t="d">
-        <v>2026-06-24T13:42:23.000Z</v>
+        <v>2026-07-14T11:48:03.000Z</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>WO0000000299246</v>
+        <v>WO0000000298379</v>
       </c>
       <c r="B233" s="1" t="d">
-        <v>2026-06-25T11:19:04.000Z</v>
+        <v>2026-06-24T13:42:23.000Z</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>WO0000000299346</v>
+        <v>WO0000000299246</v>
       </c>
       <c r="B234" s="1" t="d">
-        <v>2026-07-02T15:43:45.000Z</v>
+        <v>2026-06-25T11:19:04.000Z</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>INC000000148375</v>
+        <v>WO0000000299346</v>
       </c>
       <c r="B235" s="1" t="d">
-        <v>2026-07-06T10:46:28.999Z</v>
+        <v>2026-07-02T15:43:45.000Z</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>INC000000148478</v>
+        <v>INC000000148375</v>
       </c>
       <c r="B236" s="1" t="d">
-        <v>2026-07-06T10:47:50.000Z</v>
+        <v>2026-07-06T10:46:28.999Z</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>INC000000148483</v>
+        <v>INC000000148478</v>
       </c>
       <c r="B237" s="1" t="d">
-        <v>2026-07-06T10:46:26.000Z</v>
+        <v>2026-07-06T10:47:50.000Z</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>INC000000148391</v>
+        <v>INC000000148483</v>
       </c>
       <c r="B238" s="1" t="d">
-        <v>2026-07-06T10:46:33.000Z</v>
+        <v>2026-07-06T10:46:26.000Z</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>INC000000148617</v>
+        <v>INC000000148391</v>
       </c>
       <c r="B239" s="1" t="d">
-        <v>2026-06-23T13:06:23.000Z</v>
+        <v>2026-07-06T10:46:33.000Z</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>INC000000148567</v>
+        <v>INC000000148617</v>
       </c>
       <c r="B240" s="1" t="d">
-        <v>2026-06-23T20:51:36.000Z</v>
+        <v>2026-06-23T13:06:23.000Z</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>WO0000000299917</v>
+        <v>INC000000148567</v>
       </c>
       <c r="B241" s="1" t="d">
-        <v>2026-07-14T12:23:04.000Z</v>
+        <v>2026-06-23T20:51:36.000Z</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>INC000000148835</v>
+        <v>WO0000000299917</v>
       </c>
       <c r="B242" s="1" t="d">
-        <v>2026-07-06T10:46:35.000Z</v>
+        <v>2026-07-14T12:23:04.000Z</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>WO0000000300350</v>
+        <v>INC000000148835</v>
       </c>
       <c r="B243" s="1" t="d">
-        <v>2026-07-15T17:13:32.000Z</v>
+        <v>2026-07-06T10:46:35.000Z</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>WO0000000300621</v>
+        <v>WO0000000300350</v>
       </c>
       <c r="B244" s="1" t="d">
-        <v>2026-07-07T08:00:34.000Z</v>
+        <v>2026-07-15T17:13:32.000Z</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>INC000000148932</v>
+        <v>WO0000000300621</v>
       </c>
       <c r="B245" s="1" t="d">
-        <v>2026-06-26T20:05:39.000Z</v>
+        <v>2026-07-07T08:00:34.000Z</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>WO0000000300825</v>
+        <v>INC000000148932</v>
       </c>
       <c r="B246" s="1" t="d">
-        <v>2026-07-06T16:31:51.000Z</v>
+        <v>2026-06-26T20:05:39.000Z</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>INC000000149054</v>
+        <v>WO0000000300825</v>
       </c>
       <c r="B247" s="1" t="d">
-        <v>2026-06-25T12:46:56.999Z</v>
+        <v>2026-07-06T16:31:51.000Z</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>WO0000000301205</v>
+        <v>INC000000149054</v>
       </c>
       <c r="B248" s="1" t="d">
-        <v>2026-07-21T08:00:58.999Z</v>
+        <v>2026-06-25T12:46:56.999Z</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>WO0000000298649</v>
+        <v>WO0000000301205</v>
       </c>
       <c r="B249" s="1" t="d">
-        <v>2026-07-08T10:16:58.999Z</v>
+        <v>2026-07-21T08:00:58.999Z</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>INC000000149262</v>
+        <v>WO0000000298649</v>
       </c>
       <c r="B250" s="1" t="d">
-        <v>2026-07-06T10:46:38.000Z</v>
+        <v>2026-07-08T10:16:58.999Z</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>INC000000149363</v>
+        <v>INC000000149262</v>
       </c>
       <c r="B251" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-06T10:46:38.000Z</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>INC000000149449</v>
+        <v>INC000000149363</v>
       </c>
       <c r="B252" s="1" t="d">
-        <v>2026-06-30T13:18:04.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>INC000000149711</v>
+        <v>INC000000149449</v>
       </c>
       <c r="B253" s="1" t="d">
-        <v>2026-07-02T16:46:09.999Z</v>
+        <v>2026-06-30T13:18:04.000Z</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>INC000000149814</v>
+        <v>INC000000149711</v>
       </c>
       <c r="B254" s="1" t="d">
-        <v>2026-07-01T12:39:49.000Z</v>
+        <v>2026-07-02T16:46:09.999Z</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>WO0000000302574</v>
+        <v>INC000000149814</v>
       </c>
       <c r="B255" s="1" t="d">
-        <v>2026-07-10T13:08:33.999Z</v>
+        <v>2026-07-01T12:39:49.000Z</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>INC000000149891</v>
+        <v>WO0000000302574</v>
       </c>
       <c r="B256" s="1" t="d">
-        <v>2026-07-02T10:27:00.000Z</v>
+        <v>2026-07-10T13:08:33.999Z</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>INC000000149936</v>
+        <v>INC000000149891</v>
       </c>
       <c r="B257" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-02T10:27:00.000Z</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>WO0000000303077</v>
+        <v>INC000000149936</v>
       </c>
       <c r="B258" s="1" t="d">
-        <v>2026-07-17T13:54:02.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>INC000000150054</v>
+        <v>WO0000000303077</v>
       </c>
       <c r="B259" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-17T13:54:02.000Z</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>WO0000000303223</v>
+        <v>INC000000150054</v>
       </c>
       <c r="B260" s="1" t="d">
-        <v>2026-07-10T09:44:01.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>INC000000149979</v>
+        <v>WO0000000303223</v>
       </c>
       <c r="B261" s="1" t="d">
-        <v>2026-07-06T09:02:53.000Z</v>
+        <v>2026-07-10T09:44:01.000Z</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>INC000000149982</v>
+        <v>INC000000149979</v>
       </c>
       <c r="B262" s="1" t="d">
-        <v>2026-07-06T10:46:41.999Z</v>
+        <v>2026-07-06T09:02:53.000Z</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>INC000000149983</v>
+        <v>INC000000149982</v>
       </c>
       <c r="B263" s="1" t="d">
-        <v>2026-07-06T09:06:44.000Z</v>
+        <v>2026-07-06T10:46:41.999Z</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>INC000000150063</v>
+        <v>INC000000149983</v>
       </c>
       <c r="B264" s="1" t="d">
-        <v>2026-07-06T09:10:00.999Z</v>
+        <v>2026-07-06T09:06:44.000Z</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>INC000000149989</v>
+        <v>INC000000150063</v>
       </c>
       <c r="B265" s="1" t="d">
-        <v>2026-07-06T09:10:52.000Z</v>
+        <v>2026-07-06T09:10:00.999Z</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>WO0000000303319</v>
+        <v>INC000000149989</v>
       </c>
       <c r="B266" s="1" t="d">
-        <v>2026-07-07T09:11:18.000Z</v>
+        <v>2026-07-06T09:10:52.000Z</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>INC000000150108</v>
+        <v>WO0000000303319</v>
       </c>
       <c r="B267" s="1" t="d">
-        <v>2026-07-06T10:48:13.000Z</v>
+        <v>2026-07-07T09:11:18.000Z</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>INC000000150240</v>
+        <v>INC000000150108</v>
       </c>
       <c r="B268" s="1" t="d">
-        <v>2026-07-17T17:20:51.999Z</v>
+        <v>2026-07-06T10:48:13.000Z</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>INC000000150131</v>
+        <v>INC000000150240</v>
       </c>
       <c r="B269" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-17T17:20:51.999Z</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>WO0000000303640</v>
+        <v>INC000000150131</v>
       </c>
       <c r="B270" s="1" t="d">
-        <v>2026-07-15T11:51:27.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>WO0000000303579</v>
+        <v>WO0000000303640</v>
       </c>
       <c r="B271" s="1" t="d">
-        <v>2026-07-17T12:57:13.000Z</v>
+        <v>2026-07-15T11:51:27.000Z</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>WO0000000303593</v>
+        <v>WO0000000303579</v>
       </c>
       <c r="B272" s="1" t="d">
-        <v>2026-07-15T13:55:27.999Z</v>
+        <v>2026-07-17T12:57:13.000Z</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>INC000000150158</v>
+        <v>WO0000000303593</v>
       </c>
       <c r="B273" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T13:55:27.999Z</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>WO0000000303803</v>
+        <v>INC000000150158</v>
       </c>
       <c r="B274" s="1" t="d">
-        <v>2026-07-17T14:43:11.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>WO0000000303738</v>
+        <v>WO0000000303803</v>
       </c>
       <c r="B275" s="1" t="d">
-        <v>2026-07-20T00:01:08.000Z</v>
+        <v>2026-07-17T14:43:11.000Z</v>
       </c>
     </row>
     <row r="276">
@@ -2619,162 +2619,162 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>INC000000150407</v>
+        <v>WO0000000303791</v>
       </c>
       <c r="B278" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T12:32:15.000Z</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>WO0000000304415</v>
+        <v>INC000000150407</v>
       </c>
       <c r="B279" s="1" t="d">
-        <v>2026-07-15T12:14:00.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>WO0000000304363</v>
+        <v>WO0000000304415</v>
       </c>
       <c r="B280" s="1" t="d">
-        <v>2026-07-15T13:27:05.000Z</v>
+        <v>2026-07-15T12:14:00.000Z</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>INC000000150521</v>
+        <v>WO0000000304363</v>
       </c>
       <c r="B281" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T13:27:05.000Z</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>INC000000150630</v>
+        <v>INC000000150521</v>
       </c>
       <c r="B282" s="1" t="d">
-        <v>2026-07-10T08:48:46.999Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>INC000000150536</v>
+        <v>INC000000150630</v>
       </c>
       <c r="B283" s="1" t="d">
-        <v>2026-07-09T11:26:10.999Z</v>
+        <v>2026-07-10T08:48:46.999Z</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>WO0000000304551</v>
+        <v>INC000000150536</v>
       </c>
       <c r="B284" s="1" t="d">
-        <v>2026-07-15T16:39:18.000Z</v>
+        <v>2026-07-09T11:26:10.999Z</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>WO0000000304865</v>
+        <v>WO0000000304551</v>
       </c>
       <c r="B285" s="1" t="d">
-        <v>2026-07-16T14:19:57.000Z</v>
+        <v>2026-07-15T16:39:18.000Z</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>WO0000000304881</v>
+        <v>WO0000000304865</v>
       </c>
       <c r="B286" s="1" t="d">
-        <v>2026-07-16T14:54:34.000Z</v>
+        <v>2026-07-16T14:19:57.000Z</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>WO0000000304977</v>
+        <v>WO0000000304881</v>
       </c>
       <c r="B287" s="1" t="d">
-        <v>2026-07-21T06:23:00.000Z</v>
+        <v>2026-07-16T14:54:34.000Z</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>INC000000150832</v>
+        <v>WO0000000304977</v>
       </c>
       <c r="B288" s="1" t="d">
-        <v>2026-07-10T09:16:28.000Z</v>
+        <v>2026-07-21T06:23:00.000Z</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>INC000000150838</v>
+        <v>INC000000150832</v>
       </c>
       <c r="B289" s="1" t="d">
-        <v>2026-07-08T08:03:19.000Z</v>
+        <v>2026-07-10T09:16:28.000Z</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>WO0000000305041</v>
+        <v>INC000000150838</v>
       </c>
       <c r="B290" s="1" t="d">
-        <v>2026-07-10T13:12:35.999Z</v>
+        <v>2026-07-08T08:03:19.000Z</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>INC000000150843</v>
+        <v>WO0000000305041</v>
       </c>
       <c r="B291" s="1" t="d">
-        <v>2026-07-07T14:07:42.999Z</v>
+        <v>2026-07-10T13:12:35.999Z</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>INC000000150743</v>
+        <v>INC000000150843</v>
       </c>
       <c r="B292" s="1" t="d">
-        <v>2026-07-08T12:53:21.000Z</v>
+        <v>2026-07-07T14:07:42.999Z</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>INC000000150849</v>
+        <v>INC000000150743</v>
       </c>
       <c r="B293" s="1" t="d">
-        <v>2026-07-07T14:25:27.999Z</v>
+        <v>2026-07-08T12:53:21.000Z</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>INC000000150851</v>
+        <v>INC000000150849</v>
       </c>
       <c r="B294" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-07T14:25:27.999Z</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>WO0000000305154</v>
+        <v>INC000000150851</v>
       </c>
       <c r="B295" s="1" t="d">
-        <v>2026-07-16T14:21:59.999Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>WO0000000305077</v>
+        <v>WO0000000305154</v>
       </c>
       <c r="B296" s="1" t="d">
-        <v>2026-07-16T15:27:35.999Z</v>
+        <v>2026-07-16T14:21:59.999Z</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>INC000000151022</v>
+        <v>WO0000000305077</v>
       </c>
       <c r="B297" s="1" t="d">
-        <v>2026-07-10T08:42:56.999Z</v>
+        <v>2026-07-16T15:27:35.999Z</v>
       </c>
     </row>
     <row r="298">
@@ -2835,2226 +2835,2226 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>WO0000000306204</v>
+        <v>INC000000151304</v>
       </c>
       <c r="B305" s="1" t="d">
-        <v>2026-07-09T15:09:36.000Z</v>
+        <v>2026-07-09T15:23:24.000Z</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>INC000000151304</v>
+        <v>WO0000000306433</v>
       </c>
       <c r="B306" s="1" t="d">
-        <v>2026-07-09T15:23:24.000Z</v>
+        <v>2026-07-16T16:04:33.999Z</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>WO0000000306433</v>
+        <v>WO0000000306373</v>
       </c>
       <c r="B307" s="1" t="d">
-        <v>2026-07-16T16:04:33.999Z</v>
+        <v>2026-07-17T17:02:38.000Z</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>WO0000000306373</v>
+        <v>WO0000000306610</v>
       </c>
       <c r="B308" s="1" t="d">
-        <v>2026-07-17T17:02:38.000Z</v>
+        <v>2026-07-16T09:06:23.000Z</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>WO0000000306610</v>
+        <v>INC000000135134</v>
       </c>
       <c r="B309" s="1" t="d">
-        <v>2026-07-16T09:06:23.000Z</v>
+        <v>2026-07-14T10:35:47.000Z</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>INC000000135134</v>
+        <v>INC000000136403</v>
       </c>
       <c r="B310" s="1" t="d">
-        <v>2026-07-14T10:35:47.000Z</v>
+        <v>2026-07-14T06:43:05.000Z</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>INC000000136403</v>
+        <v>INC000000138835</v>
       </c>
       <c r="B311" s="1" t="d">
-        <v>2026-07-14T06:43:05.000Z</v>
+        <v>2026-07-14T10:35:56.000Z</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>INC000000138835</v>
+        <v>INC000000139335</v>
       </c>
       <c r="B312" s="1" t="d">
-        <v>2026-07-14T10:35:56.000Z</v>
+        <v>2026-07-14T06:43:37.000Z</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>INC000000139335</v>
+        <v>WO0000000282199</v>
       </c>
       <c r="B313" s="1" t="d">
-        <v>2026-07-14T06:43:37.000Z</v>
+        <v>2026-07-14T15:02:42.000Z</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>WO0000000282199</v>
+        <v>INC000000141515</v>
       </c>
       <c r="B314" s="1" t="d">
-        <v>2026-07-14T15:02:42.000Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>INC000000141515</v>
+        <v>WO0000000293293</v>
       </c>
       <c r="B315" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-15T08:29:08.000Z</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>INC000000142452</v>
+        <v>INC000000146720</v>
       </c>
       <c r="B316" s="1" t="d">
-        <v>2026-07-10T09:46:03.999Z</v>
+        <v>2026-07-16T08:34:09.000Z</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>WO0000000293293</v>
+        <v>WO0000000295688</v>
       </c>
       <c r="B317" s="1" t="d">
-        <v>2026-07-15T08:29:08.000Z</v>
+        <v>2026-07-16T09:17:24.999Z</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>INC000000145976</v>
+        <v>INC000000147260</v>
       </c>
       <c r="B318" s="1" t="d">
-        <v>2026-07-15T11:29:45.000Z</v>
+        <v>2026-07-14T08:08:06.000Z</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>INC000000146720</v>
+        <v>INC000000147613</v>
       </c>
       <c r="B319" s="1" t="d">
-        <v>2026-07-16T08:34:09.000Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>WO0000000295688</v>
+        <v>INC000000149029</v>
       </c>
       <c r="B320" s="1" t="d">
-        <v>2026-07-16T09:17:24.999Z</v>
+        <v>2026-07-10T14:37:50.000Z</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>INC000000147260</v>
+        <v>WO0000000301822</v>
       </c>
       <c r="B321" s="1" t="d">
-        <v>2026-07-14T08:08:06.000Z</v>
+        <v>2026-07-21T09:48:14.000Z</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>INC000000147613</v>
+        <v>INC000000149860</v>
       </c>
       <c r="B322" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-16T15:59:24.000Z</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>WO0000000297578</v>
+        <v>INC000000150036</v>
       </c>
       <c r="B323" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-16T07:28:43.999Z</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>INC000000149029</v>
+        <v>INC000000149964</v>
       </c>
       <c r="B324" s="1" t="d">
-        <v>2026-07-10T14:37:50.000Z</v>
+        <v>2026-07-15T15:21:53.000Z</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>WO0000000301822</v>
+        <v>WO0000000303232</v>
       </c>
       <c r="B325" s="1" t="d">
-        <v>2026-07-20T23:27:55.000Z</v>
+        <v>2026-07-17T17:20:56.999Z</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>INC000000149860</v>
+        <v>INC000000150141</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2026-07-16T15:59:24.000Z</v>
+        <v>2026-07-15T16:30:22.000Z</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>INC000000150036</v>
+        <v>INC000000150288</v>
       </c>
       <c r="B327" s="1" t="d">
-        <v>2026-07-16T07:28:43.999Z</v>
+        <v>2026-07-10T12:39:00.000Z</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>WO0000000303117</v>
+        <v>INC000000150197</v>
       </c>
       <c r="B328" s="1" t="d">
-        <v>2026-07-15T10:17:36.000Z</v>
+        <v>2026-07-17T11:00:31.000Z</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>INC000000149964</v>
+        <v>INC000000150475</v>
       </c>
       <c r="B329" s="1" t="d">
-        <v>2026-07-15T15:21:53.000Z</v>
+        <v>2026-07-16T08:36:47.000Z</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>WO0000000303232</v>
+        <v>WO0000000304256</v>
       </c>
       <c r="B330" s="1" t="d">
-        <v>2026-07-17T17:20:56.999Z</v>
+        <v>2026-07-16T12:20:08.000Z</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>INC000000150141</v>
+        <v>WO0000000304437</v>
       </c>
       <c r="B331" s="1" t="d">
-        <v>2026-07-15T16:30:22.000Z</v>
+        <v>2026-07-16T12:22:04.999Z</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>INC000000150288</v>
+        <v>WO0000000304614</v>
       </c>
       <c r="B332" s="1" t="d">
-        <v>2026-07-10T12:39:00.000Z</v>
+        <v>2026-07-16T12:25:00.000Z</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>INC000000150197</v>
+        <v>INC000000150547</v>
       </c>
       <c r="B333" s="1" t="d">
-        <v>2026-07-17T11:00:31.000Z</v>
+        <v>2026-07-16T08:37:46.000Z</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>WO0000000303791</v>
+        <v>WO0000000304990</v>
       </c>
       <c r="B334" s="1" t="d">
-        <v>2026-07-15T12:32:15.000Z</v>
+        <v>2026-07-15T10:54:42.999Z</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>INC000000150475</v>
+        <v>INC000000150732</v>
       </c>
       <c r="B335" s="1" t="d">
-        <v>2026-07-16T08:36:47.000Z</v>
+        <v>2026-07-16T08:27:41.000Z</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>WO0000000304256</v>
+        <v>WO0000000305312</v>
       </c>
       <c r="B336" s="1" t="d">
-        <v>2026-07-16T12:20:08.000Z</v>
+        <v>2026-07-15T11:26:08.000Z</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>WO0000000304437</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B337" s="1" t="d">
-        <v>2026-07-16T12:22:04.999Z</v>
+        <v>2026-07-15T13:10:05.000Z</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>WO0000000304614</v>
+        <v>INC000000150882</v>
       </c>
       <c r="B338" s="1" t="d">
-        <v>2026-07-16T12:25:00.000Z</v>
+        <v>2026-07-15T10:45:04.000Z</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>INC000000150547</v>
+        <v>WO0000000305349</v>
       </c>
       <c r="B339" s="1" t="d">
-        <v>2026-07-16T08:37:46.000Z</v>
+        <v>2026-07-14T12:21:19.000Z</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>WO0000000304990</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B340" s="1" t="d">
-        <v>2026-07-15T10:54:42.999Z</v>
+        <v>2026-07-16T10:45:43.999Z</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>INC000000150732</v>
+        <v>WO0000000305815</v>
       </c>
       <c r="B341" s="1" t="d">
-        <v>2026-07-16T08:27:41.000Z</v>
+        <v>2026-07-16T12:28:46.000Z</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>INC000000150748</v>
+        <v>WO0000000305843</v>
       </c>
       <c r="B342" s="1" t="d">
-        <v>2026-07-16T09:01:40.000Z</v>
+        <v>2026-07-14T12:37:15.000Z</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>WO0000000305312</v>
+        <v>WO0000000305743</v>
       </c>
       <c r="B343" s="1" t="d">
-        <v>2026-07-15T11:26:08.000Z</v>
+        <v>2026-07-14T14:33:44.000Z</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000151204</v>
       </c>
       <c r="B344" s="1" t="d">
-        <v>2026-07-15T13:10:05.000Z</v>
+        <v>2026-07-14T12:46:36.000Z</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>INC000000150882</v>
+        <v>WO0000000305944</v>
       </c>
       <c r="B345" s="1" t="d">
-        <v>2026-07-15T10:45:04.000Z</v>
+        <v>2026-07-14T12:04:16.999Z</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>WO0000000305349</v>
+        <v>INC000000151134</v>
       </c>
       <c r="B346" s="1" t="d">
-        <v>2026-07-14T12:21:19.000Z</v>
+        <v>2026-07-14T10:49:05.000Z</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>WO0000000305815</v>
+        <v>INC000000151151</v>
       </c>
       <c r="B347" s="1" t="d">
-        <v>2026-07-16T12:28:46.000Z</v>
+        <v>2026-07-16T08:22:24.000Z</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>WO0000000305843</v>
+        <v>WO0000000306190</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2026-07-14T12:37:15.000Z</v>
+        <v>2026-07-14T13:13:31.000Z</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>WO0000000305743</v>
+        <v>WO0000000306290</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2026-07-14T14:33:44.000Z</v>
+        <v>2026-07-14T16:17:28.999Z</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>INC000000151204</v>
+        <v>WO0000000306328</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2026-07-14T12:46:36.000Z</v>
+        <v>2026-07-14T16:39:44.000Z</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>WO0000000305944</v>
+        <v>INC000000151200</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2026-07-14T12:04:16.999Z</v>
+        <v>2026-07-10T10:51:56.000Z</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>INC000000151134</v>
+        <v>INC000000151311</v>
       </c>
       <c r="B352" s="1" t="d">
-        <v>2026-07-14T10:49:05.000Z</v>
+        <v>2026-07-16T09:35:09.000Z</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>INC000000151151</v>
+        <v>WO0000000306374</v>
       </c>
       <c r="B353" s="1" t="d">
-        <v>2026-07-16T08:22:24.000Z</v>
+        <v>2026-07-10T13:36:36.000Z</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>WO0000000306190</v>
+        <v>WO0000000306439</v>
       </c>
       <c r="B354" s="1" t="d">
-        <v>2026-07-14T13:13:31.000Z</v>
+        <v>2026-07-14T16:14:53.000Z</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>WO0000000306290</v>
+        <v>WO0000000306534</v>
       </c>
       <c r="B355" s="1" t="d">
-        <v>2026-07-14T16:17:28.999Z</v>
+        <v>2026-07-15T16:01:14.000Z</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>WO0000000306328</v>
+        <v>INC000000151466</v>
       </c>
       <c r="B356" s="1" t="d">
-        <v>2026-07-14T16:39:44.000Z</v>
+        <v>2026-07-14T15:33:23.000Z</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>INC000000151200</v>
+        <v>WO0000000304733</v>
       </c>
       <c r="B357" s="1" t="d">
-        <v>2026-07-10T10:51:56.000Z</v>
+        <v>2026-07-15T10:28:05.999Z</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>WO0000000306374</v>
+        <v>WO0000000306648</v>
       </c>
       <c r="B358" s="1" t="d">
-        <v>2026-07-10T13:36:36.000Z</v>
+        <v>2026-07-16T11:20:21.000Z</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>WO0000000306439</v>
+        <v>INC000000151499</v>
       </c>
       <c r="B359" s="1" t="d">
-        <v>2026-07-14T16:14:53.000Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>WO0000000306534</v>
+        <v>INC000000151525</v>
       </c>
       <c r="B360" s="1" t="d">
-        <v>2026-07-15T16:01:14.000Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>INC000000151466</v>
+        <v>WO0000000306862</v>
       </c>
       <c r="B361" s="1" t="d">
-        <v>2026-07-14T15:33:23.000Z</v>
+        <v>2026-07-21T10:40:52.000Z</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>WO0000000304733</v>
+        <v>WO0000000306992</v>
       </c>
       <c r="B362" s="1" t="d">
-        <v>2026-07-15T10:28:05.999Z</v>
+        <v>2026-07-16T10:42:09.000Z</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>WO0000000306574</v>
+        <v>WO0000000307033</v>
       </c>
       <c r="B363" s="1" t="d">
-        <v>2026-07-15T12:39:36.999Z</v>
+        <v>2026-07-17T12:30:37.000Z</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>WO0000000306648</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B364" s="1" t="d">
-        <v>2026-07-16T11:20:21.000Z</v>
+        <v>2026-07-11T15:39:05.000Z</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>INC000000151499</v>
+        <v>WO0000000307106</v>
       </c>
       <c r="B365" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-11T16:22:34.000Z</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>INC000000151512</v>
+        <v>WO0000000307093</v>
       </c>
       <c r="B366" s="1" t="d">
-        <v>2026-07-16T09:37:50.000Z</v>
+        <v>2026-07-14T07:58:26.000Z</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>INC000000151525</v>
+        <v>WO0000000307237</v>
       </c>
       <c r="B367" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-14T08:00:43.999Z</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>WO0000000306862</v>
+        <v>INC000000151941</v>
       </c>
       <c r="B368" s="1" t="d">
-        <v>2026-07-21T08:05:05.000Z</v>
+        <v>2026-07-17T13:23:13.999Z</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>WO0000000307033</v>
+        <v>INC000000151950</v>
       </c>
       <c r="B369" s="1" t="d">
-        <v>2026-07-17T12:30:37.000Z</v>
+        <v>2026-07-16T09:20:32.000Z</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000307368</v>
       </c>
       <c r="B370" s="1" t="d">
-        <v>2026-07-11T15:39:05.000Z</v>
+        <v>2026-07-21T09:55:05.000Z</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>WO0000000307106</v>
+        <v>WO0000000307397</v>
       </c>
       <c r="B371" s="1" t="d">
-        <v>2026-07-11T16:22:34.000Z</v>
+        <v>2026-07-15T09:56:22.000Z</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>WO0000000307093</v>
+        <v>WO0000000307437</v>
       </c>
       <c r="B372" s="1" t="d">
-        <v>2026-07-14T07:58:26.000Z</v>
+        <v>2026-07-21T08:19:28.999Z</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>WO0000000307237</v>
+        <v>WO0000000307471</v>
       </c>
       <c r="B373" s="1" t="d">
-        <v>2026-07-14T08:00:43.999Z</v>
+        <v>2026-07-14T11:13:57.999Z</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>INC000000151941</v>
+        <v>WO0000000307482</v>
       </c>
       <c r="B374" s="1" t="d">
-        <v>2026-07-17T13:23:13.999Z</v>
+        <v>2026-07-14T13:21:57.000Z</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>WO0000000307368</v>
+        <v>INC000000151994</v>
       </c>
       <c r="B375" s="1" t="d">
-        <v>2026-07-17T09:56:32.000Z</v>
+        <v>2026-07-16T07:51:15.000Z</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>WO0000000307397</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B376" s="1" t="d">
-        <v>2026-07-15T09:56:22.000Z</v>
+        <v>2026-07-14T12:23:50.000Z</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>WO0000000307437</v>
+        <v>INC000000152040</v>
       </c>
       <c r="B377" s="1" t="d">
-        <v>2026-07-21T08:19:28.999Z</v>
+        <v>2026-07-14T15:45:22.000Z</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>WO0000000307471</v>
+        <v>WO0000000307592</v>
       </c>
       <c r="B378" s="1" t="d">
-        <v>2026-07-14T11:13:57.999Z</v>
+        <v>2026-07-17T13:37:57.000Z</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>WO0000000307482</v>
+        <v>INC000000152117</v>
       </c>
       <c r="B379" s="1" t="d">
-        <v>2026-07-14T13:21:57.000Z</v>
+        <v>2026-07-15T14:11:25.000Z</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>INC000000151994</v>
+        <v>WO0000000307667</v>
       </c>
       <c r="B380" s="1" t="d">
-        <v>2026-07-16T07:51:15.000Z</v>
+        <v>2026-07-21T08:39:56.000Z</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000307671</v>
       </c>
       <c r="B381" s="1" t="d">
-        <v>2026-07-14T12:23:50.000Z</v>
+        <v>2026-07-17T09:44:19.000Z</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>INC000000152040</v>
+        <v>INC000000152124</v>
       </c>
       <c r="B382" s="1" t="d">
-        <v>2026-07-14T15:45:22.000Z</v>
+        <v>2026-07-15T14:11:57.000Z</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>WO0000000307592</v>
+        <v>WO0000000307701</v>
       </c>
       <c r="B383" s="1" t="d">
-        <v>2026-07-17T13:37:57.000Z</v>
+        <v>2026-07-17T09:50:26.000Z</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>INC000000152117</v>
+        <v>INC000000152132</v>
       </c>
       <c r="B384" s="1" t="d">
-        <v>2026-07-15T14:11:25.000Z</v>
+        <v>2026-07-15T14:13:17.000Z</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>WO0000000307667</v>
+        <v>INC000000152134</v>
       </c>
       <c r="B385" s="1" t="d">
-        <v>2026-07-21T08:39:56.000Z</v>
+        <v>2026-07-15T14:13:50.000Z</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>WO0000000307671</v>
+        <v>INC000000152138</v>
       </c>
       <c r="B386" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-15T14:16:43.999Z</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>INC000000152124</v>
+        <v>INC000000152139</v>
       </c>
       <c r="B387" s="1" t="d">
-        <v>2026-07-15T14:11:57.000Z</v>
+        <v>2026-07-15T14:17:19.000Z</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>WO0000000307701</v>
+        <v>WO0000000307733</v>
       </c>
       <c r="B388" s="1" t="d">
-        <v>2026-07-17T09:50:26.000Z</v>
+        <v>2026-07-17T11:13:13.999Z</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>INC000000152132</v>
+        <v>WO0000000307735</v>
       </c>
       <c r="B389" s="1" t="d">
-        <v>2026-07-15T14:13:17.000Z</v>
+        <v>2026-07-21T09:55:06.000Z</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>INC000000152134</v>
+        <v>WO0000000307812</v>
       </c>
       <c r="B390" s="1" t="d">
-        <v>2026-07-15T14:13:50.000Z</v>
+        <v>2026-07-21T10:09:34.000Z</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>INC000000152138</v>
+        <v>INC000000152155</v>
       </c>
       <c r="B391" s="1" t="d">
-        <v>2026-07-15T14:16:43.999Z</v>
+        <v>2026-07-15T16:57:39.000Z</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>INC000000152139</v>
+        <v>INC000000152156</v>
       </c>
       <c r="B392" s="1" t="d">
-        <v>2026-07-15T14:17:19.000Z</v>
+        <v>2026-07-15T14:18:27.000Z</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>WO0000000307733</v>
+        <v>INC000000152158</v>
       </c>
       <c r="B393" s="1" t="d">
-        <v>2026-07-17T11:13:13.999Z</v>
+        <v>2026-07-15T14:19:58.000Z</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>WO0000000307735</v>
+        <v>INC000000152073</v>
       </c>
       <c r="B394" s="1" t="d">
-        <v>2026-07-17T08:55:02.999Z</v>
+        <v>2026-07-16T09:23:53.000Z</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>WO0000000307812</v>
+        <v>WO0000000307834</v>
       </c>
       <c r="B395" s="1" t="d">
-        <v>2026-07-17T09:11:25.000Z</v>
+        <v>2026-07-21T08:01:01.000Z</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>WO0000000307820</v>
+        <v>WO0000000307769</v>
       </c>
       <c r="B396" s="1" t="d">
-        <v>2026-07-17T16:33:17.000Z</v>
+        <v>2026-07-14T17:17:47.000Z</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>INC000000152155</v>
+        <v>WO0000000307852</v>
       </c>
       <c r="B397" s="1" t="d">
-        <v>2026-07-15T16:57:39.000Z</v>
+        <v>2026-07-17T12:30:37.999Z</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>INC000000152156</v>
+        <v>WO0000000307923</v>
       </c>
       <c r="B398" s="1" t="d">
-        <v>2026-07-15T14:18:27.000Z</v>
+        <v>2026-07-16T09:23:33.000Z</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>INC000000152158</v>
+        <v>WO0000000308004</v>
       </c>
       <c r="B399" s="1" t="d">
-        <v>2026-07-15T14:19:58.000Z</v>
+        <v>2026-07-17T10:04:39.999Z</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>WO0000000307834</v>
+        <v>INC000000152308</v>
       </c>
       <c r="B400" s="1" t="d">
-        <v>2026-07-21T08:01:01.000Z</v>
+        <v>2026-07-16T09:37:19.000Z</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>WO0000000307769</v>
+        <v>INC000000152320</v>
       </c>
       <c r="B401" s="1" t="d">
-        <v>2026-07-14T17:17:47.000Z</v>
+        <v>2026-07-15T10:29:52.000Z</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>WO0000000307852</v>
+        <v>WO0000000307976</v>
       </c>
       <c r="B402" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-21T10:33:10.999Z</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>WO0000000308004</v>
+        <v>WO0000000307981</v>
       </c>
       <c r="B403" s="1" t="d">
-        <v>2026-07-17T10:04:39.999Z</v>
+        <v>2026-07-21T09:32:12.999Z</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>INC000000152301</v>
+        <v>WO0000000307984</v>
       </c>
       <c r="B404" s="1" t="d">
-        <v>2026-07-15T14:37:10.000Z</v>
+        <v>2026-07-17T14:08:18.000Z</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>INC000000152308</v>
+        <v>INC000000152339</v>
       </c>
       <c r="B405" s="1" t="d">
-        <v>2026-07-16T09:37:19.000Z</v>
+        <v>2026-07-16T08:34:04.000Z</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>INC000000152320</v>
+        <v>WO0000000308206</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2026-07-15T10:29:52.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>WO0000000307976</v>
+        <v>WO0000000308218</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2026-07-17T13:56:08.000Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>WO0000000307981</v>
+        <v>WO0000000308157</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2026-07-17T11:48:02.000Z</v>
+        <v>2026-07-17T13:56:08.000Z</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>WO0000000307984</v>
+        <v>WO0000000308163</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2026-07-17T14:08:18.000Z</v>
+        <v>2026-07-16T09:05:24.000Z</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>INC000000152339</v>
+        <v>INC000000152358</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2026-07-16T08:34:04.000Z</v>
+        <v>2026-07-16T09:12:05.999Z</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>WO0000000308206</v>
+        <v>WO0000000308194</v>
       </c>
       <c r="B411" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>WO0000000308218</v>
+        <v>WO0000000308255</v>
       </c>
       <c r="B412" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-17T15:17:47.000Z</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>WO0000000308157</v>
+        <v>WO0000000308260</v>
       </c>
       <c r="B413" s="1" t="d">
-        <v>2026-07-17T13:56:08.000Z</v>
+        <v>2026-07-21T08:56:50.000Z</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>WO0000000308163</v>
+        <v>WO0000000308269</v>
       </c>
       <c r="B414" s="1" t="d">
-        <v>2026-07-16T09:05:24.000Z</v>
+        <v>2026-07-21T09:19:51.000Z</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>INC000000152358</v>
+        <v>WO0000000308273</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2026-07-16T09:12:05.999Z</v>
+        <v>2026-07-21T09:25:58.000Z</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308194</v>
+        <v>WO0000000308284</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-16T08:08:24.000Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308255</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-17T15:17:47.000Z</v>
+        <v>2026-07-21T10:13:57.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>WO0000000308260</v>
+        <v>WO0000000308340</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-21T08:56:50.000Z</v>
+        <v>2026-07-16T09:24:24.999Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>WO0000000308269</v>
+        <v>WO0000000308416</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-21T09:19:51.000Z</v>
+        <v>2026-07-16T09:47:42.999Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308273</v>
+        <v>WO0000000308432</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-16T12:17:21.999Z</v>
+        <v>2026-07-21T08:34:03.000Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308284</v>
+        <v>WO0000000308350</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-16T08:08:24.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308442</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-16T23:19:07.000Z</v>
+        <v>2026-07-21T08:56:50.000Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308331</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-21T09:13:19.000Z</v>
+        <v>2026-07-16T10:44:20.999Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308416</v>
+        <v>WO0000000308360</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-16T09:47:42.999Z</v>
+        <v>2026-07-16T12:54:40.000Z</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>WO0000000308432</v>
+        <v>WO0000000308457</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2026-07-21T08:34:03.000Z</v>
+        <v>2026-07-21T09:30:10.000Z</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>WO0000000308350</v>
+        <v>WO0000000308366</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-16T09:45:50.999Z</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>WO0000000308345</v>
+        <v>WO0000000308463</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2026-07-21T08:44:29.000Z</v>
+        <v>2026-07-21T09:42:42.000Z</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>WO0000000308442</v>
+        <v>WO0000000308374</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2026-07-21T08:56:50.000Z</v>
+        <v>2026-07-21T09:55:06.000Z</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>WO0000000308360</v>
+        <v>WO0000000308379</v>
       </c>
       <c r="B429" s="1" t="d">
-        <v>2026-07-16T12:54:40.000Z</v>
+        <v>2026-07-15T17:07:55.000Z</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>WO0000000308457</v>
+        <v>WO0000000308383</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2026-07-17T11:44:00.000Z</v>
+        <v>2026-07-21T10:16:02.000Z</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>WO0000000308463</v>
+        <v>WO0000000308398</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-17T11:56:09.000Z</v>
+        <v>2026-07-16T08:57:27.000Z</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>WO0000000308374</v>
+        <v>WO0000000308399</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-17T12:10:22.000Z</v>
+        <v>2026-07-16T09:52:14.999Z</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>WO0000000308379</v>
+        <v>WO0000000308487</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-15T17:07:55.000Z</v>
+        <v>2026-07-15T22:21:47.000Z</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>WO0000000308383</v>
+        <v>WO0000000308503</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-17T12:30:39.000Z</v>
+        <v>2026-07-21T10:01:16.000Z</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>WO0000000308398</v>
+        <v>WO0000000308493</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2026-07-16T08:57:27.000Z</v>
+        <v>2026-07-21T10:16:04.000Z</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>WO0000000308399</v>
+        <v>WO0000000308506</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-16T09:52:14.999Z</v>
+        <v>2026-07-21T10:16:03.000Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>WO0000000308487</v>
+        <v>INC000000152512</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-15T22:21:47.000Z</v>
+        <v>2026-07-16T08:10:32.999Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>WO0000000308503</v>
+        <v>INC000000152513</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-16T07:14:29.000Z</v>
+        <v>2026-07-16T09:23:02.000Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>WO0000000308493</v>
+        <v>WO0000000308552</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-17T12:30:42.000Z</v>
+        <v>2026-07-16T09:20:55.000Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>INC000000152512</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-16T08:10:32.999Z</v>
+        <v>2026-07-17T15:09:40.000Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>INC000000152513</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-16T09:23:02.000Z</v>
+        <v>2026-07-16T09:22:57.000Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>WO0000000308648</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-17T15:09:40.000Z</v>
+        <v>2026-07-17T14:10:20.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000272008</v>
+        <v>WO0000000308661</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-21T09:04:16.999Z</v>
+        <v>2026-07-17T14:16:26.000Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>INC000000139655</v>
+        <v>WO0000000308673</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-17T07:37:37.999Z</v>
+        <v>2026-07-16T10:02:00.999Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>INC000000139903</v>
+        <v>WO0000000308679</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-17T07:37:04.000Z</v>
+        <v>2026-07-17T14:36:57.000Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>INC000000140158</v>
+        <v>WO0000000308675</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-17T07:31:47.000Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>INC000000140820</v>
+        <v>WO0000000308685</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-17T07:35:42.000Z</v>
+        <v>2026-07-16T10:12:45.000Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>INC000000140821</v>
+        <v>WO0000000308596</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2026-07-17T07:34:57.000Z</v>
+        <v>2026-07-16T10:19:52.000Z</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>INC000000140767</v>
+        <v>WO0000000308701</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-16T10:22:52.000Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>INC000000141766</v>
+        <v>WO0000000308696</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-21T08:55:08.000Z</v>
+        <v>2026-07-17T11:22:11.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>INC000000142421</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-17T07:33:48.000Z</v>
+        <v>2026-07-16T10:42:24.000Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>INC000000142515</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-17T07:33:05.000Z</v>
+        <v>2026-07-16T10:40:08.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WO0000000288110</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-17T07:47:10.000Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>INC000000143401</v>
+        <v>WO0000000308717</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-17T07:32:06.000Z</v>
+        <v>2026-07-21T10:45:16.999Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>WO0000000292826</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-17T07:30:34.000Z</v>
+        <v>2026-07-16T10:46:41.000Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>WO0000000295598</v>
+        <v>INC000000139655</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-17T07:37:37.999Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>WO0000000295716</v>
+        <v>INC000000139903</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-16T11:47:42.999Z</v>
+        <v>2026-07-17T07:37:04.000Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>WO0000000295975</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-17T07:46:27.000Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>INC000000146886</v>
+        <v>INC000000140820</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-16T13:10:02.999Z</v>
+        <v>2026-07-17T07:35:42.000Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>WO0000000296722</v>
+        <v>INC000000140821</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-17T07:44:32.000Z</v>
+        <v>2026-07-17T07:34:57.000Z</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>WO0000000296723</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-17T07:43:42.999Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>WO0000000297151</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-17T07:42:36.000Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>WO0000000297156</v>
+        <v>INC000000142421</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-17T07:41:50.000Z</v>
+        <v>2026-07-17T07:33:48.000Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>WO0000000297160</v>
+        <v>INC000000142515</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-17T07:40:23.999Z</v>
+        <v>2026-07-17T07:33:05.000Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>WO0000000298838</v>
+        <v>WO0000000288110</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-20T23:28:38.000Z</v>
+        <v>2026-07-17T07:47:10.000Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>WO0000000299920</v>
+        <v>INC000000143401</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-17T14:59:50.999Z</v>
+        <v>2026-07-17T07:32:06.000Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>WO0000000300081</v>
+        <v>WO0000000292826</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-17T07:30:34.000Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>INC000000148888</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>WO0000000300496</v>
+        <v>WO0000000295716</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-17T11:43:57.000Z</v>
+        <v>2026-07-16T11:47:42.999Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>WO0000000302331</v>
+        <v>WO0000000295975</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-17T12:11:40.000Z</v>
+        <v>2026-07-17T07:46:27.000Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>WO0000000302520</v>
+        <v>INC000000146886</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-17T15:04:39.000Z</v>
+        <v>2026-07-16T13:10:02.999Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>INC000000149827</v>
+        <v>WO0000000296722</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-17T14:03:04.000Z</v>
+        <v>2026-07-17T07:44:32.000Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>INC000000149757</v>
+        <v>WO0000000296723</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-16T16:04:01.999Z</v>
+        <v>2026-07-17T07:43:42.999Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>INC000000149760</v>
+        <v>WO0000000297151</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-17T07:52:31.999Z</v>
+        <v>2026-07-17T07:42:36.000Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>WO0000000303120</v>
+        <v>WO0000000297156</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-17T07:38:45.000Z</v>
+        <v>2026-07-17T07:41:50.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000297160</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-17T15:09:03.000Z</v>
+        <v>2026-07-17T07:40:23.999Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>WO0000000303244</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-17T15:04:54.000Z</v>
+        <v>2026-07-20T23:28:38.000Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>WO0000000303459</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-17T11:09:28.999Z</v>
+        <v>2026-07-17T14:59:50.999Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000303471</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-16T14:24:05.000Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-16T12:40:48.000Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000300496</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-17T10:37:05.000Z</v>
+        <v>2026-07-17T11:43:57.000Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-17T10:37:33.000Z</v>
+        <v>2026-07-17T12:11:40.000Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WO0000000305131</v>
+        <v>WO0000000302520</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-21T08:46:39.000Z</v>
+        <v>2026-07-17T15:04:39.000Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>WO0000000305138</v>
+        <v>INC000000149827</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-17T14:03:04.000Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>WO0000000305336</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-16T16:04:01.999Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>INC000000150916</v>
+        <v>INC000000149760</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-17T13:59:57.999Z</v>
+        <v>2026-07-17T07:52:31.999Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-17T18:15:37.999Z</v>
+        <v>2026-07-21T10:43:30.000Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>INC000000151036</v>
+        <v>WO0000000303120</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-16T16:01:20.999Z</v>
+        <v>2026-07-17T07:38:45.000Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-16T10:45:43.999Z</v>
+        <v>2026-07-17T15:09:03.000Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>INC000000150958</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-17T07:47:57.999Z</v>
+        <v>2026-07-17T15:04:54.000Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>WO0000000305863</v>
+        <v>WO0000000303459</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-21T08:44:19.000Z</v>
+        <v>2026-07-17T11:09:28.999Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>WO0000000305877</v>
+        <v>WO0000000303471</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-16T16:12:20.000Z</v>
+        <v>2026-07-16T14:24:05.000Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>WO0000000305769</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-17T10:37:57.000Z</v>
+        <v>2026-07-16T12:40:48.000Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>WO0000000305770</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-17T11:07:27.000Z</v>
+        <v>2026-07-17T10:37:05.000Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>INC000000151203</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-17T10:37:33.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>WO0000000306127</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-21T07:40:38.000Z</v>
+        <v>2026-07-21T08:46:39.000Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>INC000000151157</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-17T19:09:33.000Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>INC000000151271</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-17T07:40:02.000Z</v>
+        <v>2026-07-21T10:15:45.000Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>WO0000000306256</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-17T14:41:03.000Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>INC000000151311</v>
+        <v>INC000000150916</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-16T09:35:09.000Z</v>
+        <v>2026-07-17T13:59:57.999Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>INC000000151313</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-17T18:15:37.999Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>WO0000000306718</v>
+        <v>INC000000151036</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-17T10:39:36.000Z</v>
+        <v>2026-07-16T16:01:20.999Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>WO0000000306721</v>
+        <v>INC000000150958</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-17T15:11:14.000Z</v>
+        <v>2026-07-17T07:47:57.999Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>WO0000000306726</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-17T10:39:57.000Z</v>
+        <v>2026-07-21T08:44:19.000Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>WO0000000306799</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-17T08:21:12.999Z</v>
+        <v>2026-07-16T16:12:20.000Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-17T19:07:47.000Z</v>
+        <v>2026-07-17T10:37:57.000Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>INC000000151527</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-17T16:34:54.000Z</v>
+        <v>2026-07-17T11:07:27.000Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>WO0000000306927</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306127</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-17T17:20:58.999Z</v>
+        <v>2026-07-21T07:40:38.000Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>WO0000000306877</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-16T14:55:04.000Z</v>
+        <v>2026-07-17T19:09:33.000Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>WO0000000306890</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-17T07:40:02.000Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>WO0000000306899</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-17T17:44:23.000Z</v>
+        <v>2026-07-17T14:41:03.000Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>WO0000000306988</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-21T09:13:38.000Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>WO0000000306992</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-16T10:42:09.000Z</v>
+        <v>2026-07-17T10:39:36.000Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>WO0000000306994</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-16T15:19:33.999Z</v>
+        <v>2026-07-17T15:11:14.000Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>INC000000151586</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-19T12:57:49.000Z</v>
+        <v>2026-07-17T10:39:57.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>WO0000000307224</v>
+        <v>INC000000151512</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-16T16:04:39.999Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-17T14:49:17.000Z</v>
+        <v>2026-07-17T08:21:12.999Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>INC000000151950</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-16T09:20:32.000Z</v>
+        <v>2026-07-17T19:07:47.000Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>INC000000151764</v>
+        <v>INC000000151527</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-16T10:00:04.000Z</v>
+        <v>2026-07-17T16:34:54.000Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>WO0000000307513</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-17T09:03:17.000Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-17T17:20:58.999Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>INC000000151987</v>
+        <v>WO0000000306877</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-16T11:05:28.000Z</v>
+        <v>2026-07-16T14:55:04.000Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>WO0000000307483</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-21T09:13:03.000Z</v>
+        <v>2026-07-17T14:42:13.999Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-17T14:02:15.000Z</v>
+        <v>2026-07-21T10:02:55.000Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-17T16:21:08.000Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>INC000000152000</v>
+        <v>WO0000000306994</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-19T12:58:45.000Z</v>
+        <v>2026-07-16T15:19:33.999Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000151586</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-19T12:57:49.000Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000307224</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-16T16:04:39.999Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>WO0000000307636</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-20T22:08:00.000Z</v>
+        <v>2026-07-17T14:49:17.000Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>INC000000152045</v>
+        <v>INC000000151764</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-16T10:52:09.000Z</v>
+        <v>2026-07-21T09:41:12.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-16T11:24:53.999Z</v>
+        <v>2026-07-21T10:03:23.000Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>WO0000000307669</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>WO0000000307703</v>
+        <v>INC000000151987</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-17T17:21:00.000Z</v>
+        <v>2026-07-16T11:05:28.000Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>WO0000000307725</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-17T15:11:48.000Z</v>
+        <v>2026-07-21T09:13:03.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>WO0000000307729</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-16T12:57:39.999Z</v>
+        <v>2026-07-21T10:01:17.000Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>INC000000152145</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-17T19:20:59.000Z</v>
+        <v>2026-07-17T16:21:08.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>INC000000152073</v>
+        <v>INC000000152000</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-16T09:23:53.000Z</v>
+        <v>2026-07-19T12:58:45.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>WO0000000307923</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-16T09:23:33.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000307940</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>WO0000000307963</v>
+        <v>INC000000152045</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-17T13:31:54.000Z</v>
+        <v>2026-07-16T10:52:09.000Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>WO0000000308029</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-17T16:02:10.000Z</v>
+        <v>2026-07-16T11:24:53.999Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>INC000000152212</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-17T17:21:00.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>WO0000000308038</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-17T13:48:01.000Z</v>
+        <v>2026-07-17T15:11:48.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>WO0000000308040</v>
+        <v>WO0000000307729</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-16T12:57:39.999Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>WO0000000307968</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-16T15:02:29.000Z</v>
+        <v>2026-07-17T19:20:59.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000307970</v>
+        <v>WO0000000307820</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-16T16:55:20.000Z</v>
+        <v>2026-07-21T09:49:48.000Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>WO0000000308041</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-17T09:02:42.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>WO0000000308042</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-20T23:34:20.999Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>WO0000000308052</v>
+        <v>WO0000000307968</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-17T11:04:48.999Z</v>
+        <v>2026-07-16T15:02:29.000Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307970</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-16T16:55:20.000Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000308105</v>
+        <v>WO0000000308041</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-20T23:29:29.999Z</v>
+        <v>2026-07-21T10:24:00.000Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>INC000000152328</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-17T21:19:20.000Z</v>
+        <v>2026-07-20T23:34:20.999Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>WO0000000308075</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-20T23:26:07.000Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308106</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-20T23:30:10.000Z</v>
+        <v>2026-07-17T11:04:48.999Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>WO0000000308107</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-20T23:27:09.999Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-20T23:31:09.999Z</v>
+        <v>2026-07-20T23:29:29.999Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>WO0000000308086</v>
+        <v>INC000000152328</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-17T14:44:25.000Z</v>
+        <v>2026-07-21T10:41:49.000Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>WO0000000308215</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-17T09:26:37.000Z</v>
+        <v>2026-07-20T23:26:07.000Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000308216</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-17T13:19:29.000Z</v>
+        <v>2026-07-20T23:30:10.000Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000308107</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-20T23:27:09.999Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-18T12:28:17.000Z</v>
+        <v>2026-07-20T23:31:09.999Z</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>WO0000000308234</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-07-19T12:53:47.000Z</v>
+        <v>2026-07-21T09:28:00.000Z</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>INC000000152251</v>
+        <v>WO0000000308215</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-07-17T10:26:36.999Z</v>
+        <v>2026-07-17T09:26:37.000Z</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>INC000000152361</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-07-17T16:39:09.000Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>WO0000000308196</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-07-21T08:49:13.000Z</v>
+        <v>2026-07-18T12:28:17.000Z</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000308234</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-07-17T12:34:20.000Z</v>
+        <v>2026-07-19T12:53:47.000Z</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>WO0000000308249</v>
+        <v>INC000000152251</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-07-17T13:34:27.999Z</v>
+        <v>2026-07-17T10:26:36.999Z</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>WO0000000308199</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-07-17T13:37:19.000Z</v>
+        <v>2026-07-17T16:39:09.000Z</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>INC000000152369</v>
+        <v>WO0000000308196</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-07-17T10:42:03.000Z</v>
+        <v>2026-07-21T08:49:13.000Z</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-07-18T09:01:38.000Z</v>
+        <v>2026-07-17T12:34:20.000Z</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308249</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-07-18T12:40:57.999Z</v>
+        <v>2026-07-17T13:34:27.999Z</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>INC000000152378</v>
+        <v>WO0000000308199</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-07-17T09:05:30.000Z</v>
+        <v>2026-07-17T13:37:19.000Z</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>INC000000152262</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-07-19T07:36:53.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>WO0000000308340</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-07-16T09:24:24.999Z</v>
+        <v>2026-07-18T09:01:38.000Z</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-07-18T12:08:23.000Z</v>
+        <v>2026-07-18T12:40:57.999Z</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>WO0000000308422</v>
+        <v>INC000000152378</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-17T09:05:30.000Z</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>WO0000000308426</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-18T12:08:23.000Z</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308426</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-21T09:09:06.999Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>WO0000000308357</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-21T09:07:14.999Z</v>
+        <v>2026-07-21T09:09:06.999Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308357</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-16T10:44:20.999Z</v>
+        <v>2026-07-21T10:35:55.000Z</v>
       </c>
     </row>
     <row r="583">
@@ -5067,5028 +5067,5076 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>WO0000000308366</v>
+        <v>WO0000000308461</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-16T09:45:50.999Z</v>
+        <v>2026-07-21T09:25:59.000Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>WO0000000308461</v>
+        <v>WO0000000308475</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-16T18:43:27.999Z</v>
+        <v>2026-07-21T10:16:01.000Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>WO0000000308475</v>
+        <v>WO0000000308478</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-21T10:16:02.000Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>WO0000000308478</v>
+        <v>WO0000000308495</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-17T12:30:39.000Z</v>
+        <v>2026-07-21T10:02:45.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>WO0000000308382</v>
+        <v>INC000000152419</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-07-17T12:30:40.000Z</v>
+        <v>2026-07-21T08:54:50.000Z</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>WO0000000308380</v>
+        <v>INC000000152439</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-17T12:30:40.000Z</v>
+        <v>2026-07-16T13:12:03.000Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>WO0000000308396</v>
+        <v>INC000000152517</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-17T12:30:41.000Z</v>
+        <v>2026-07-17T10:21:00.000Z</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>WO0000000308495</v>
+        <v>INC000000152450</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-17T13:17:48.000Z</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>INC000000152419</v>
+        <v>INC000000152537</v>
       </c>
       <c r="B592" s="1" t="d">
-        <v>2026-07-21T08:54:50.000Z</v>
+        <v>2026-07-17T10:03:46.000Z</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>WO0000000308506</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-07-17T12:30:41.000Z</v>
+        <v>2026-07-18T12:29:14.000Z</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>INC000000152439</v>
+        <v>INC000000152458</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-07-16T13:12:03.000Z</v>
+        <v>2026-07-21T10:45:45.000Z</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>WO0000000308624</v>
+        <v>WO0000000308662</v>
       </c>
       <c r="B595" s="1" t="d">
-        <v>2026-07-17T12:45:01.000Z</v>
+        <v>2026-07-16T14:23:41.000Z</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>INC000000152517</v>
+        <v>WO0000000308585</v>
       </c>
       <c r="B596" s="1" t="d">
-        <v>2026-07-17T10:21:00.000Z</v>
+        <v>2026-07-16T14:22:46.000Z</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>INC000000152450</v>
+        <v>INC000000152461</v>
       </c>
       <c r="B597" s="1" t="d">
-        <v>2026-07-17T13:17:48.000Z</v>
+        <v>2026-07-20T09:23:43.999Z</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>WO0000000308552</v>
+        <v>WO0000000308698</v>
       </c>
       <c r="B598" s="1" t="d">
-        <v>2026-07-16T09:20:55.000Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>INC000000152537</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B599" s="1" t="d">
-        <v>2026-07-17T10:03:46.000Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>WO0000000308647</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-07-17T13:39:57.999Z</v>
+        <v>2026-07-20T19:01:19.000Z</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-16T09:22:57.000Z</v>
+        <v>2026-07-21T10:18:10.000Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000152565</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-18T12:29:14.000Z</v>
+        <v>2026-07-21T07:47:38.999Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>INC000000152458</v>
+        <v>WO0000000308727</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-17T14:55:27.000Z</v>
+        <v>2026-07-17T09:34:42.000Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-17T14:10:20.000Z</v>
+        <v>2026-07-21T09:27:37.000Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000308661</v>
+        <v>WO0000000308809</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-07-17T14:16:26.000Z</v>
+        <v>2026-07-16T11:14:01.000Z</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>WO0000000308662</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-16T14:23:41.000Z</v>
+        <v>2026-07-17T15:18:13.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>WO0000000308585</v>
+        <v>WO0000000308814</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-16T14:22:46.000Z</v>
+        <v>2026-07-17T15:46:22.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>INC000000152461</v>
+        <v>WO0000000308742</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-20T09:23:43.999Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>WO0000000308673</v>
+        <v>WO0000000308816</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-16T10:02:00.999Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>WO0000000308679</v>
+        <v>WO0000000308743</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-07-17T14:36:57.000Z</v>
+        <v>2026-07-17T15:54:32.000Z</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>WO0000000308675</v>
+        <v>INC000000152477</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-07-17T07:31:47.000Z</v>
+        <v>2026-07-16T12:12:43.000Z</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>WO0000000308685</v>
+        <v>WO0000000308750</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-07-16T10:12:45.000Z</v>
+        <v>2026-07-17T16:02:36.000Z</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>WO0000000308596</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-07-16T10:19:52.000Z</v>
+        <v>2026-07-17T08:38:07.000Z</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>WO0000000308701</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-07-16T10:22:52.000Z</v>
+        <v>2026-07-16T14:25:41.000Z</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308755</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-07-17T11:22:11.000Z</v>
+        <v>2026-07-16T11:35:09.000Z</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>WO0000000308698</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>WO0000000308695</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-07-16T10:42:24.000Z</v>
+        <v>2026-07-21T09:29:46.000Z</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308851</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-17T16:37:20.999Z</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>WO0000000308712</v>
+        <v>INC000000152486</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-07-17T09:16:22.999Z</v>
+        <v>2026-07-21T07:42:45.999Z</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308860</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-07-16T10:40:08.000Z</v>
+        <v>2026-07-17T16:51:40.000Z</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>WO0000000308715</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-21T08:00:16.000Z</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>INC000000152561</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-07-17T16:04:19.000Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000308868</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-07-16T12:45:40.000Z</v>
+        <v>2026-07-21T08:27:45.999Z</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-07-16T10:46:41.000Z</v>
+        <v>2026-07-16T14:39:36.999Z</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>WO0000000308722</v>
+        <v>INC000000152496</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-07-20T19:01:19.000Z</v>
+        <v>2026-07-17T18:33:44.000Z</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-07-17T16:49:36.000Z</v>
+        <v>2026-07-17T09:53:56.000Z</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>INC000000152565</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-07-21T07:47:38.999Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>WO0000000308727</v>
+        <v>INC000000152594</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-07-17T09:34:42.000Z</v>
+        <v>2026-07-20T13:46:11.000Z</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000308905</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-07-21T08:53:31.000Z</v>
+        <v>2026-07-21T09:36:24.000Z</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000308880</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-07-17T16:59:44.999Z</v>
+        <v>2026-07-21T09:38:28.000Z</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>WO0000000308809</v>
+        <v>WO0000000308917</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-07-16T11:14:01.000Z</v>
+        <v>2026-07-17T07:59:19.999Z</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>INC000000152566</v>
+        <v>WO0000000308918</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-07-17T15:18:13.000Z</v>
+        <v>2026-07-21T10:05:26.000Z</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>WO0000000308814</v>
+        <v>WO0000000308919</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-07-17T15:46:22.000Z</v>
+        <v>2026-07-21T10:07:31.000Z</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>WO0000000308742</v>
+        <v>WO0000000308923</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-21T09:17:59.000Z</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>WO0000000308816</v>
+        <v>INC000000152608</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-21T10:28:55.000Z</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>WO0000000308743</v>
+        <v>WO0000000308895</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-07-17T15:54:32.000Z</v>
+        <v>2026-07-17T10:35:42.000Z</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>INC000000152477</v>
+        <v>WO0000000308896</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-07-16T12:12:43.000Z</v>
+        <v>2026-07-21T10:24:24.000Z</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>WO0000000308750</v>
+        <v>WO0000000309001</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-07-17T16:02:36.000Z</v>
+        <v>2026-07-21T10:26:28.000Z</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000309004</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-07-17T08:38:07.000Z</v>
+        <v>2026-07-21T10:26:28.000Z</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>WO0000000308754</v>
+        <v>WO0000000308899</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-07-16T14:25:41.000Z</v>
+        <v>2026-07-16T15:17:36.000Z</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>WO0000000308755</v>
+        <v>WO0000000308926</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-07-16T11:35:09.000Z</v>
+        <v>2026-07-17T10:04:52.000Z</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>WO0000000308826</v>
+        <v>WO0000000309007</v>
       </c>
       <c r="B642" s="1" t="d">
-        <v>2026-07-17T16:08:41.000Z</v>
+        <v>2026-07-21T10:47:08.000Z</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>WO0000000308817</v>
+        <v>WO0000000309009</v>
       </c>
       <c r="B643" s="1" t="d">
-        <v>2026-07-17T16:14:46.000Z</v>
+        <v>2026-07-21T10:34:42.000Z</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000309002</v>
       </c>
       <c r="B644" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-16T15:07:58.000Z</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>WO0000000308834</v>
+        <v>WO0000000309011</v>
       </c>
       <c r="B645" s="1" t="d">
-        <v>2026-07-17T16:19:03.000Z</v>
+        <v>2026-07-17T10:44:02.999Z</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>WO0000000308851</v>
+        <v>INC000000152616</v>
       </c>
       <c r="B646" s="1" t="d">
-        <v>2026-07-17T16:37:20.999Z</v>
+        <v>2026-07-17T09:51:34.000Z</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>INC000000152486</v>
+        <v>WO0000000308938</v>
       </c>
       <c r="B647" s="1" t="d">
-        <v>2026-07-21T07:42:45.999Z</v>
+        <v>2026-07-16T15:31:18.000Z</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>WO0000000308860</v>
+        <v>WO0000000309018</v>
       </c>
       <c r="B648" s="1" t="d">
-        <v>2026-07-17T16:51:40.000Z</v>
+        <v>2026-07-16T15:30:08.999Z</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>WO0000000308862</v>
+        <v>WO0000000309021</v>
       </c>
       <c r="B649" s="1" t="d">
-        <v>2026-07-17T17:46:11.000Z</v>
+        <v>2026-07-17T09:59:10.000Z</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000152711</v>
       </c>
       <c r="B650" s="1" t="d">
-        <v>2026-07-21T08:00:16.000Z</v>
+        <v>2026-07-16T16:04:14.000Z</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>INC000000152586</v>
+        <v>WO0000000309024</v>
       </c>
       <c r="B651" s="1" t="d">
-        <v>2026-07-17T10:46:28.000Z</v>
+        <v>2026-07-16T15:43:10.000Z</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>WO0000000308868</v>
+        <v>WO0000000308947</v>
       </c>
       <c r="B652" s="1" t="d">
-        <v>2026-07-21T08:27:45.999Z</v>
+        <v>2026-07-21T10:45:27.000Z</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>WO0000000308873</v>
+        <v>WO0000000309026</v>
       </c>
       <c r="B653" s="1" t="d">
-        <v>2026-07-16T14:39:36.999Z</v>
+        <v>2026-07-16T15:49:08.000Z</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>INC000000152496</v>
+        <v>WO0000000309025</v>
       </c>
       <c r="B654" s="1" t="d">
-        <v>2026-07-17T18:33:44.000Z</v>
+        <v>2026-07-16T15:47:35.000Z</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>WO0000000308794</v>
+        <v>WO0000000309028</v>
       </c>
       <c r="B655" s="1" t="d">
-        <v>2026-07-17T09:53:56.000Z</v>
+        <v>2026-07-17T15:14:51.999Z</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>INC000000152591</v>
+        <v>WO0000000309031</v>
       </c>
       <c r="B656" s="1" t="d">
-        <v>2026-07-17T11:00:29.999Z</v>
+        <v>2026-07-16T15:52:24.000Z</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>INC000000152594</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B657" s="1" t="d">
-        <v>2026-07-20T13:46:11.000Z</v>
+        <v>2026-07-17T16:59:46.000Z</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>WO0000000308905</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B658" s="1" t="d">
-        <v>2026-07-16T14:04:26.000Z</v>
+        <v>2026-07-16T16:05:14.000Z</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>WO0000000308880</v>
+        <v>WO0000000309039</v>
       </c>
       <c r="B659" s="1" t="d">
-        <v>2026-07-17T14:08:19.000Z</v>
+        <v>2026-07-17T08:39:45.999Z</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>WO0000000308912</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B660" s="1" t="d">
-        <v>2026-07-16T14:18:19.000Z</v>
+        <v>2026-07-17T16:15:11.000Z</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>INC000000152598</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B661" s="1" t="d">
-        <v>2026-07-17T10:04:25.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>WO0000000308913</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B662" s="1" t="d">
-        <v>2026-07-17T08:38:16.000Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>WO0000000308917</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-17T07:59:19.999Z</v>
+        <v>2026-07-18T14:29:17.000Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>WO0000000308918</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-17T14:34:52.999Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000308919</v>
+        <v>WO0000000308967</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-16T14:36:18.000Z</v>
+        <v>2026-07-21T10:04:47.000Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>WO0000000308923</v>
+        <v>INC000000152630</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-21T09:17:59.000Z</v>
+        <v>2026-07-21T07:35:42.000Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>INC000000152608</v>
+        <v>WO0000000309044</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-17T15:48:10.000Z</v>
+        <v>2026-07-16T16:26:35.999Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>WO0000000308895</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-17T10:35:42.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>WO0000000308896</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-16T15:16:25.000Z</v>
+        <v>2026-07-16T16:32:21.000Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>WO0000000309001</v>
+        <v>WO0000000309047</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-17T08:09:22.000Z</v>
+        <v>2026-07-16T16:37:18.000Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>WO0000000309004</v>
+        <v>WO0000000308970</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-16T14:55:40.999Z</v>
+        <v>2026-07-16T16:38:04.000Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000308899</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-16T15:17:36.000Z</v>
+        <v>2026-07-16T16:43:04.000Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>WO0000000308926</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-17T10:04:52.000Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000309007</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-16T15:03:12.000Z</v>
+        <v>2026-07-17T07:16:12.000Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000309009</v>
+        <v>WO0000000309052</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-21T08:15:25.000Z</v>
+        <v>2026-07-21T10:20:14.999Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>WO0000000309002</v>
+        <v>WO0000000308984</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-16T17:10:27.000Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>WO0000000309011</v>
+        <v>WO0000000309060</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-17T10:44:02.999Z</v>
+        <v>2026-07-16T22:04:20.000Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>INC000000152616</v>
+        <v>WO0000000309062</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-17T09:51:34.000Z</v>
+        <v>2026-07-17T10:25:11.000Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>WO0000000308938</v>
+        <v>WO0000000309063</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-16T17:31:20.000Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000309018</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-16T15:30:08.999Z</v>
+        <v>2026-07-21T07:53:18.000Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>WO0000000309021</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-17T09:59:10.000Z</v>
+        <v>2026-07-16T19:52:29.999Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>INC000000152711</v>
+        <v>WO0000000305262</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-16T16:04:14.000Z</v>
+        <v>2026-07-17T07:53:28.999Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000309024</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-16T15:43:10.000Z</v>
+        <v>2026-07-16T19:32:50.000Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>WO0000000308947</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-17T10:21:08.000Z</v>
+        <v>2026-07-21T07:53:32.000Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>WO0000000309026</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-16T15:49:08.000Z</v>
+        <v>2026-07-16T19:42:22.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>WO0000000309025</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>WO0000000309028</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-17T15:14:51.999Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-16T15:52:24.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-17T16:59:46.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>WO0000000309036</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-17T10:15:24.000Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000309082</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-17T08:39:45.999Z</v>
+        <v>2026-07-17T09:36:16.000Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-17T16:15:11.000Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>INC000000152628</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-17T10:44:38.000Z</v>
+        <v>2026-07-17T06:53:11.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>WO0000000309041</v>
+        <v>INC000000152653</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-18T16:16:07.999Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000309097</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-18T14:29:17.000Z</v>
+        <v>2026-07-17T08:03:06.999Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>WO0000000308966</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-17T08:06:35.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000308967</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-21T09:14:56.000Z</v>
+        <v>2026-07-17T07:45:37.999Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>INC000000152630</v>
+        <v>INC000000152739</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-21T07:35:42.000Z</v>
+        <v>2026-07-17T09:20:05.999Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-16T16:26:35.999Z</v>
+        <v>2026-07-17T08:07:23.000Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000309131</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-17T08:12:37.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000309212</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-16T16:32:21.000Z</v>
+        <v>2026-07-17T15:11:51.000Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>WO0000000309047</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-16T16:37:18.000Z</v>
+        <v>2026-07-21T09:04:31.000Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>WO0000000308970</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-16T16:38:04.000Z</v>
+        <v>2026-07-17T11:36:59.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>WO0000000308975</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-16T16:43:04.000Z</v>
+        <v>2026-07-17T12:44:26.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>WO0000000309050</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>WO0000000309051</v>
+        <v>INC000000152746</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-17T07:16:12.000Z</v>
+        <v>2026-07-21T09:47:10.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>WO0000000309052</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-17T07:44:17.000Z</v>
+        <v>2026-07-17T08:54:14.000Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>WO0000000308984</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-16T17:10:27.000Z</v>
+        <v>2026-07-17T08:54:36.999Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>WO0000000309060</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-16T22:04:20.000Z</v>
+        <v>2026-07-18T12:40:15.000Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>WO0000000309062</v>
+        <v>WO0000000309226</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-17T10:25:11.000Z</v>
+        <v>2026-07-17T08:58:32.999Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>WO0000000309063</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-16T17:31:20.000Z</v>
+        <v>2026-07-17T14:29:04.000Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-21T07:53:18.000Z</v>
+        <v>2026-07-17T09:57:18.999Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>WO0000000308987</v>
+        <v>INC000000152673</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-16T19:52:29.999Z</v>
+        <v>2026-07-21T08:52:59.000Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>WO0000000309065</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>WO0000000305262</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-17T07:53:28.999Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>WO0000000309073</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-16T19:32:50.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>INC000000152643</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-21T07:53:32.000Z</v>
+        <v>2026-07-17T14:47:59.000Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-16T19:42:22.000Z</v>
+        <v>2026-07-17T09:26:58.999Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>WO0000000309077</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-21T10:42:34.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>WO0000000309079</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-17T15:50:55.000Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000309246</v>
       </c>
       <c r="B721" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T09:32:32.000Z</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>WO0000000308997</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-17T09:36:30.000Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>WO0000000308999</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-17T10:15:24.000Z</v>
+        <v>2026-07-17T09:37:50.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>WO0000000309082</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-17T09:36:16.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309249</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-17T09:38:10.000Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>WO0000000309084</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-17T10:26:01.000Z</v>
+        <v>2026-07-21T10:04:01.000Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>INC000000152731</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-17T10:29:59.000Z</v>
+        <v>2026-07-21T08:45:24.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>INC000000152733</v>
+        <v>WO0000000309251</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-17T09:40:19.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>INC000000152653</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-18T16:16:07.999Z</v>
+        <v>2026-07-21T08:17:56.000Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>WO0000000309097</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-17T08:03:06.999Z</v>
+        <v>2026-07-17T09:57:50.000Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>INC000000152737</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-17T08:06:35.000Z</v>
+        <v>2026-07-17T11:14:20.000Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>WO0000000309124</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-17T07:45:37.999Z</v>
+        <v>2026-07-17T14:47:53.999Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>INC000000152739</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-17T09:20:05.999Z</v>
+        <v>2026-07-17T11:11:39.000Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-17T08:07:23.000Z</v>
+        <v>2026-07-17T11:15:36.000Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>WO0000000309131</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-17T08:12:37.000Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>WO0000000309212</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-17T15:11:51.000Z</v>
+        <v>2026-07-17T11:13:13.000Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>WO0000000309136</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-21T09:04:31.000Z</v>
+        <v>2026-07-21T09:55:04.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-17T11:36:59.000Z</v>
+        <v>2026-07-17T10:18:38.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>INC000000152663</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-17T12:44:26.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>INC000000152664</v>
+        <v>INC000000152770</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T10:27:03.000Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>INC000000152746</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-21T09:11:42.000Z</v>
+        <v>2026-07-17T11:24:41.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>WO0000000309153</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-21T08:54:48.000Z</v>
+        <v>2026-07-21T10:45:43.999Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>WO0000000309154</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-17T08:54:14.000Z</v>
+        <v>2026-07-21T10:37:55.000Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>WO0000000309155</v>
+        <v>INC000000152691</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-17T08:54:36.999Z</v>
+        <v>2026-07-17T11:21:16.000Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>INC000000152668</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-18T12:40:15.000Z</v>
+        <v>2026-07-17T12:51:35.000Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>WO0000000309226</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-17T08:58:32.999Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>WO0000000309231</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-17T14:29:04.000Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309269</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-21T10:34:42.000Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>INC000000152673</v>
+        <v>WO0000000309270</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-21T08:52:59.000Z</v>
+        <v>2026-07-17T16:48:27.000Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-17T14:48:08.000Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>WO0000000309162</v>
+        <v>INC000000152694</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-18T13:02:06.999Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>INC000000152674</v>
+        <v>WO0000000309407</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-17T10:43:38.999Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>WO0000000309164</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-17T14:47:59.000Z</v>
+        <v>2026-07-19T12:51:55.999Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309409</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-17T09:26:58.999Z</v>
+        <v>2026-07-21T10:47:34.000Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>INC000000152678</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-17T12:06:25.000Z</v>
+        <v>2026-07-21T09:07:41.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>INC000000152679</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-17T15:50:55.000Z</v>
+        <v>2026-07-17T10:48:35.999Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>WO0000000309246</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-17T09:32:32.000Z</v>
+        <v>2026-07-17T10:53:18.000Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>WO0000000309167</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-21T08:57:56.000Z</v>
+        <v>2026-07-17T12:28:53.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>INC000000152761</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-17T10:05:32.000Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>WO0000000309168</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-17T09:36:30.000Z</v>
+        <v>2026-07-17T10:58:23.000Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309285</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-17T09:37:50.000Z</v>
+        <v>2026-07-17T10:57:51.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>WO0000000309172</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-21T10:46:30.999Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309249</v>
+        <v>WO0000000309417</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-17T11:02:34.000Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>WO0000000309250</v>
+        <v>INC000000152700</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-21T09:14:42.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>INC000000152760</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-21T08:45:24.000Z</v>
+        <v>2026-07-18T08:52:20.999Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>WO0000000309251</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-17T09:40:19.000Z</v>
+        <v>2026-07-17T11:12:43.000Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>INC000000152763</v>
+        <v>INC000000152784</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-17T10:09:48.000Z</v>
+        <v>2026-07-17T11:26:12.000Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-21T08:17:56.000Z</v>
+        <v>2026-07-17T11:15:48.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-17T09:57:50.000Z</v>
+        <v>2026-07-17T11:17:12.999Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-17T11:14:20.000Z</v>
+        <v>2026-07-17T14:48:17.000Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-17T14:47:53.999Z</v>
+        <v>2026-07-17T11:21:58.000Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-17T11:11:39.000Z</v>
+        <v>2026-07-21T09:14:29.000Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309189</v>
+        <v>WO0000000309432</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-17T11:15:36.000Z</v>
+        <v>2026-07-17T11:29:50.000Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>WO0000000309258</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-17T11:26:05.999Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>WO0000000309259</v>
+        <v>WO0000000309299</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-17T11:13:13.000Z</v>
+        <v>2026-07-17T11:28:13.000Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>INC000000152688</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-21T08:15:27.000Z</v>
+        <v>2026-07-21T10:21:20.000Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>INC000000152768</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-17T15:17:55.000Z</v>
+        <v>2026-07-21T09:27:50.000Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>WO0000000309262</v>
+        <v>WO0000000309439</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-17T10:18:38.000Z</v>
+        <v>2026-07-17T11:59:55.999Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>INC000000152690</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-17T15:38:05.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>INC000000152770</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-17T10:27:03.000Z</v>
+        <v>2026-07-21T10:37:25.999Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000305263</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-17T15:28:33.000Z</v>
+        <v>2026-07-21T10:43:09.999Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309195</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-17T11:24:41.000Z</v>
+        <v>2026-07-17T11:41:41.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>INC000000152772</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-17T10:29:44.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>INC000000152774</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-17T11:25:20.000Z</v>
+        <v>2026-07-17T15:32:46.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>INC000000152691</v>
+        <v>WO0000000309444</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-17T11:21:16.000Z</v>
+        <v>2026-07-17T11:41:48.000Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000309199</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-17T12:51:35.000Z</v>
+        <v>2026-07-21T10:23:15.000Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>WO0000000309200</v>
+        <v>INC000000152810</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-21T07:51:23.000Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-17T11:53:25.999Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>WO0000000309269</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-17T11:19:32.000Z</v>
+        <v>2026-07-21T08:25:47.000Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>WO0000000309270</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-17T16:48:27.000Z</v>
+        <v>2026-07-21T10:24:15.999Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>WO0000000309271</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-17T14:48:08.000Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>INC000000152694</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-18T13:02:06.999Z</v>
+        <v>2026-07-17T14:48:03.000Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>WO0000000309407</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-17T15:45:57.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>INC000000152777</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-19T12:51:55.999Z</v>
+        <v>2026-07-17T14:48:13.000Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>WO0000000309409</v>
+        <v>INC000000152797</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-17T11:23:02.000Z</v>
+        <v>2026-07-21T08:59:18.000Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>WO0000000309277</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-21T09:19:50.000Z</v>
+        <v>2026-07-18T08:52:31.000Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-21T09:07:41.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-17T10:48:35.999Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-17T10:53:18.000Z</v>
+        <v>2026-07-17T12:23:35.999Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-17T12:28:53.000Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>WO0000000309282</v>
+        <v>INC000000152901</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-21T10:47:15.000Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309466</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-17T10:58:23.000Z</v>
+        <v>2026-07-21T10:22:48.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000309285</v>
+        <v>WO0000000309525</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-17T10:57:51.000Z</v>
+        <v>2026-07-17T16:15:45.000Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>INC000000152802</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-17T11:48:14.000Z</v>
+        <v>2026-07-17T17:44:41.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>INC000000152782</v>
+        <v>WO0000000309526</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-17T11:46:20.999Z</v>
+        <v>2026-07-21T08:25:19.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309417</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-17T11:02:34.000Z</v>
+        <v>2026-07-21T09:11:31.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>INC000000152700</v>
+        <v>INC000000152814</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-17T18:10:18.000Z</v>
+        <v>2026-07-17T12:49:52.000Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>WO0000000309422</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-18T08:52:20.999Z</v>
+        <v>2026-07-20T13:33:22.000Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309478</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-17T11:12:43.000Z</v>
+        <v>2026-07-17T15:55:47.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>WO0000000309291</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-17T11:55:44.999Z</v>
+        <v>2026-07-17T12:55:06.999Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>INC000000152784</v>
+        <v>WO0000000309534</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-17T11:26:12.000Z</v>
+        <v>2026-07-17T13:00:45.000Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000309424</v>
+        <v>INC000000152910</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-17T11:15:48.000Z</v>
+        <v>2026-07-21T07:51:47.000Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>WO0000000309412</v>
+        <v>INC000000152815</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-17T11:17:12.999Z</v>
+        <v>2026-07-17T21:20:43.999Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-17T14:48:17.000Z</v>
+        <v>2026-07-17T15:49:27.999Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309488</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-17T11:21:58.000Z</v>
+        <v>2026-07-17T13:20:57.999Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>WO0000000309431</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-21T09:14:29.000Z</v>
+        <v>2026-07-21T08:46:11.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>WO0000000309432</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-17T11:29:50.000Z</v>
+        <v>2026-07-18T01:16:50.999Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>WO0000000309433</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-17T11:26:05.999Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>WO0000000309299</v>
+        <v>INC000000152915</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-17T11:28:13.000Z</v>
+        <v>2026-07-18T12:02:15.999Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-17T11:29:56.000Z</v>
+        <v>2026-07-21T10:39:57.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>WO0000000309438</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-17T16:49:37.000Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000309439</v>
+        <v>WO0000000309545</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-17T11:59:55.999Z</v>
+        <v>2026-07-21T07:54:44.000Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>WO0000000309503</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-17T15:38:05.000Z</v>
+        <v>2026-07-18T01:16:05.000Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>INC000000152789</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-17T12:04:35.000Z</v>
+        <v>2026-07-17T14:11:39.000Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-18T12:02:37.000Z</v>
+        <v>2026-07-21T10:46:28.000Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>WO0000000309436</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-17T11:41:41.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-17T15:55:02.000Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>WO0000000309441</v>
+        <v>INC000000152922</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-17T15:32:46.000Z</v>
+        <v>2026-07-21T07:10:12.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000309444</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-17T11:41:48.000Z</v>
+        <v>2026-07-17T14:30:26.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>WO0000000309447</v>
+        <v>INC000000152828</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-17T11:44:22.000Z</v>
+        <v>2026-07-17T14:45:48.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>INC000000152810</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-21T07:51:23.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-17T11:53:25.999Z</v>
+        <v>2026-07-19T00:08:20.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-21T08:25:47.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-17T11:55:31.000Z</v>
+        <v>2026-07-17T14:57:05.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>WO0000000309513</v>
+        <v>INC000000152927</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T15:58:26.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309613</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-17T14:48:03.000Z</v>
+        <v>2026-07-17T15:01:59.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-17T15:45:57.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>WO0000000309457</v>
+        <v>WO0000000309559</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-17T14:48:13.000Z</v>
+        <v>2026-07-17T15:56:29.000Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>INC000000152797</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-21T08:59:18.000Z</v>
+        <v>2026-07-18T08:45:42.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-18T08:52:31.000Z</v>
+        <v>2026-07-17T15:57:48.000Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000309514</v>
+        <v>INC000000152931</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-21T08:13:12.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000309462</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-17T15:20:43.999Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>INC000000152800</v>
+        <v>WO0000000309563</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-21T06:37:05.999Z</v>
+        <v>2026-07-17T15:24:26.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000309465</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-17T12:23:35.999Z</v>
+        <v>2026-07-18T11:14:25.000Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000309520</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-17T16:04:00.000Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>INC000000152901</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-17T12:30:00.000Z</v>
+        <v>2026-07-17T15:31:50.999Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000309466</v>
+        <v>WO0000000309572</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-17T12:32:56.000Z</v>
+        <v>2026-07-21T08:34:49.000Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>INC000000152813</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-21T09:11:10.999Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000309525</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-17T16:15:45.000Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>INC000000152903</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-17T17:44:41.000Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000309526</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-21T08:25:19.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>WO0000000309470</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-21T09:11:31.000Z</v>
+        <v>2026-07-21T10:39:19.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>INC000000152814</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-17T12:49:52.000Z</v>
+        <v>2026-07-17T16:25:00.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-20T13:33:22.000Z</v>
+        <v>2026-07-18T06:53:20.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>WO0000000309478</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-17T15:55:47.000Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309635</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-17T12:55:06.999Z</v>
+        <v>2026-07-17T16:06:26.000Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>WO0000000309534</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-17T13:00:45.000Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>INC000000152910</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-21T07:51:47.000Z</v>
+        <v>2026-07-21T10:08:02.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>INC000000152815</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-17T21:20:43.999Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>WO0000000309489</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-17T15:49:27.999Z</v>
+        <v>2026-07-17T17:05:49.000Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>WO0000000309488</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-17T13:20:57.999Z</v>
+        <v>2026-07-18T06:19:47.000Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>INC000000152914</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-21T08:46:11.000Z</v>
+        <v>2026-07-17T16:39:05.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>INC000000152913</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-18T01:16:50.999Z</v>
+        <v>2026-07-18T12:55:19.000Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000309487</v>
+        <v>WO0000000309587</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-17T16:39:17.000Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>INC000000152915</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-18T12:02:15.999Z</v>
+        <v>2026-07-18T07:38:46.000Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>WO0000000309497</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-21T08:45:58.000Z</v>
+        <v>2026-07-18T13:55:17.000Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>WO0000000309499</v>
+        <v>INC000000152945</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-17T16:53:07.000Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>WO0000000309545</v>
+        <v>WO0000000309643</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-21T07:54:44.000Z</v>
+        <v>2026-07-17T16:52:17.999Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>INC000000152919</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-18T01:16:05.000Z</v>
+        <v>2026-07-21T10:09:45.000Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>WO0000000309546</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>INC000000152824</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-20T13:35:30.999Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000309548</v>
+        <v>WO0000000309648</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-21T08:38:16.999Z</v>
+        <v>2026-07-17T18:19:50.000Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>INC000000152921</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-21T09:50:43.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>WO0000000309603</v>
+        <v>WO0000000309308</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-17T15:55:02.000Z</v>
+        <v>2026-07-21T07:44:56.000Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000309604</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-17T14:28:20.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>INC000000152922</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-21T07:10:12.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>WO0000000309549</v>
+        <v>WO0000000309655</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-17T14:30:26.000Z</v>
+        <v>2026-07-21T09:15:18.000Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>INC000000152827</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-20T13:32:44.000Z</v>
+        <v>2026-07-21T10:23:48.000Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>INC000000152828</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-17T14:45:48.000Z</v>
+        <v>2026-07-21T09:07:50.999Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>WO0000000309551</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-21T09:27:02.000Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>WO0000000309609</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-19T00:08:20.000Z</v>
+        <v>2026-07-21T10:28:49.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>WO0000000309553</v>
+        <v>INC000000152846</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-17T17:43:39.999Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-17T14:57:05.000Z</v>
+        <v>2026-07-21T09:12:25.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>WO0000000309611</v>
+        <v>INC000000152950</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-21T08:49:56.000Z</v>
+        <v>2026-07-21T09:49:56.000Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>INC000000152927</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-17T15:58:26.000Z</v>
+        <v>2026-07-17T18:11:18.000Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000309613</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-17T15:01:59.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>INC000000152928</v>
+        <v>WO0000000309598</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-21T06:26:41.000Z</v>
+        <v>2026-07-21T08:16:54.999Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>WO0000000309559</v>
+        <v>WO0000000309600</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-17T15:56:29.000Z</v>
+        <v>2026-07-21T07:30:44.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309659</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-18T08:45:42.000Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>WO0000000309616</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-17T15:57:48.000Z</v>
+        <v>2026-07-21T10:32:14.000Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309705</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-21T08:13:12.000Z</v>
+        <v>2026-07-17T18:22:25.999Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309707</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-21T08:26:12.000Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000309563</v>
+        <v>WO0000000309660</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-17T18:27:35.999Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>INC000000152933</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-18T11:14:25.000Z</v>
+        <v>2026-07-21T09:27:40.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309661</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-17T16:04:00.000Z</v>
+        <v>2026-07-21T09:05:58.999Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>WO0000000309570</v>
+        <v>INC000000152954</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-18T10:44:32.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>WO0000000309572</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-21T08:34:49.000Z</v>
+        <v>2026-07-21T09:28:09.000Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>WO0000000309574</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-18T09:16:52.000Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>WO0000000309625</v>
+        <v>INC000000152957</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-18T11:15:19.000Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>WO0000000309626</v>
+        <v>INC000000152958</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-21T08:44:02.000Z</v>
+        <v>2026-07-21T10:46:25.000Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>WO0000000309627</v>
+        <v>INC000000152854</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-17T16:25:00.000Z</v>
+        <v>2026-07-17T21:32:15.999Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>WO0000000309629</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-18T06:53:20.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000309632</v>
+        <v>WO0000000309667</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-21T07:08:18.000Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>WO0000000309635</v>
+        <v>WO0000000309668</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-17T16:06:26.000Z</v>
+        <v>2026-07-21T09:29:44.000Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-21T07:55:12.000Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>WO0000000309636</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-18T07:13:50.000Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>INC000000152838</v>
+        <v>INC000000152863</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-18T11:32:43.000Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>INC000000152940</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-21T08:42:40.000Z</v>
+        <v>2026-07-18T11:57:16.000Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>WO0000000309582</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-21T09:17:55.000Z</v>
+        <v>2026-07-21T09:18:02.999Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>INC000000152943</v>
+        <v>INC000000152869</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-17T17:05:49.000Z</v>
+        <v>2026-07-21T07:20:13.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000309641</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-18T06:19:47.000Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>WO0000000309583</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-17T16:34:20.000Z</v>
+        <v>2026-07-21T10:45:55.999Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>WO0000000309585</v>
+        <v>WO0000000309678</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-21T09:19:00.000Z</v>
+        <v>2026-07-18T07:42:09.999Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>WO0000000309586</v>
+        <v>INC000000152878</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-17T16:39:05.000Z</v>
+        <v>2026-07-18T08:12:08.000Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>INC000000152939</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-18T12:55:19.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>WO0000000309587</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-17T16:39:17.000Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>INC000000152944</v>
+        <v>INC000000152879</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-18T07:38:46.000Z</v>
+        <v>2026-07-18T08:11:58.000Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>WO0000000309589</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-18T13:55:17.000Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>INC000000152945</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-17T16:53:07.000Z</v>
+        <v>2026-07-18T12:53:54.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>WO0000000309643</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-17T16:52:17.999Z</v>
+        <v>2026-07-18T08:39:53.000Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>WO0000000309592</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-17T18:16:22.999Z</v>
+        <v>2026-07-18T08:48:11.000Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>WO0000000309307</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-18T00:06:54.000Z</v>
+        <v>2026-07-21T10:10:23.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>WO0000000309593</v>
+        <v>INC000000152980</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-18T16:16:48.000Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>WO0000000309647</v>
+        <v>WO0000000309732</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-21T09:05:18.000Z</v>
+        <v>2026-07-18T09:10:30.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>INC000000152946</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-17T17:58:53.999Z</v>
+        <v>2026-07-21T07:56:14.999Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>WO0000000309648</v>
+        <v>INC000000152888</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-17T18:19:50.000Z</v>
+        <v>2026-07-21T10:39:53.000Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>WO0000000309651</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-17T18:20:35.000Z</v>
+        <v>2026-07-21T10:00:54.000Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>WO0000000309652</v>
+        <v>WO0000000309698</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-20T22:30:37.000Z</v>
+        <v>2026-07-18T10:07:47.000Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>WO0000000309308</v>
+        <v>INC000000152986</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-21T07:44:56.000Z</v>
+        <v>2026-07-21T08:16:08.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>WO0000000309595</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-18T10:49:11.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>WO0000000309594</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-20T22:36:47.999Z</v>
+        <v>2026-07-21T10:41:02.000Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>WO0000000309596</v>
+        <v>INC000000152990</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-21T09:00:11.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>WO0000000309655</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-21T09:15:18.000Z</v>
+        <v>2026-07-21T07:32:12.000Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>WO0000000309597</v>
+        <v>WO0000000309802</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-17T17:19:38.000Z</v>
+        <v>2026-07-21T09:30:57.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>WO0000000309309</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-21T09:07:50.999Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>INC000000152948</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-21T08:44:49.000Z</v>
+        <v>2026-07-20T19:05:32.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>INC000000152845</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-17T18:03:03.000Z</v>
+        <v>2026-07-20T19:04:33.999Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>INC000000152846</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-17T17:43:39.999Z</v>
+        <v>2026-07-20T19:03:52.000Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>WO0000000309310</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-21T09:12:25.000Z</v>
+        <v>2026-07-20T19:04:20.000Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>INC000000152950</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-21T08:03:13.000Z</v>
+        <v>2026-07-21T10:20:14.999Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>INC000000152848</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-21T09:26:05.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-21T10:21:19.000Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>WO0000000309598</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-21T08:16:54.999Z</v>
+        <v>2026-07-21T07:32:42.999Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>WO0000000309599</v>
+        <v>INC000000153000</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-21T07:31:13.000Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>WO0000000309600</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-21T07:30:44.000Z</v>
+        <v>2026-07-21T07:33:22.000Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>INC000000152844</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-21T08:57:48.000Z</v>
+        <v>2026-07-21T08:41:17.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>WO0000000309659</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>WO0000000309704</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-17T18:21:50.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>WO0000000309705</v>
+        <v>INC000000153003</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-17T18:22:25.999Z</v>
+        <v>2026-07-21T09:03:17.000Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>WO0000000309707</v>
+        <v>INC000000152900</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-21T08:26:12.000Z</v>
+        <v>2026-07-21T08:04:18.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>WO0000000309660</v>
+        <v>WO0000000309815</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-17T18:27:35.999Z</v>
+        <v>2026-07-21T09:12:13.999Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>INC000000152953</v>
+        <v>INC000000153006</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-21T08:43:57.000Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>WO0000000309661</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-21T09:05:58.999Z</v>
+        <v>2026-07-21T07:19:30.000Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>INC000000152954</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-18T10:44:32.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>INC000000152955</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-21T08:32:45.000Z</v>
+        <v>2026-07-21T10:18:57.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>WO0000000309664</v>
+        <v>INC000000153103</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-21T08:04:41.000Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>INC000000152956</v>
+        <v>INC000000153011</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-18T09:16:52.000Z</v>
+        <v>2026-07-21T10:42:50.000Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000309666</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>INC000000152957</v>
+        <v>INC000000153012</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-18T11:15:19.000Z</v>
+        <v>2026-07-21T08:03:57.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>INC000000152853</v>
+        <v>INC000000153013</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-20T09:22:52.000Z</v>
+        <v>2026-07-21T07:19:23.999Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>INC000000152958</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-20T09:04:48.999Z</v>
+        <v>2026-07-21T07:31:56.999Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>WO0000000309712</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-17T20:32:00.000Z</v>
+        <v>2026-07-21T07:19:54.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>INC000000152854</v>
+        <v>INC000000153015</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-17T21:32:15.999Z</v>
+        <v>2026-07-21T10:29:31.000Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>INC000000152855</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-21T08:15:37.000Z</v>
+        <v>2026-07-21T07:30:09.000Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>WO0000000309714</v>
+        <v>INC000000153017</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-18T15:26:50.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>WO0000000309667</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-21T07:08:18.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>WO0000000309715</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-21T07:55:35.000Z</v>
+        <v>2026-07-21T09:58:01.000Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>WO0000000309668</v>
+        <v>WO0000000309769</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-21T07:28:51.000Z</v>
+        <v>2026-07-21T07:30:32.000Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>WO0000000309669</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-21T07:55:12.000Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>INC000000152856</v>
+        <v>WO0000000309830</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-21T09:26:50.000Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>INC000000152863</v>
+        <v>INC000000153108</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-18T11:32:43.000Z</v>
+        <v>2026-07-21T07:53:45.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>INC000000152862</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-21T09:08:10.000Z</v>
+        <v>2026-07-19T08:43:56.000Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000153020</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-18T11:57:16.000Z</v>
+        <v>2026-07-21T07:53:07.999Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>WO0000000309671</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-21T09:18:02.999Z</v>
+        <v>2026-07-21T07:08:54.000Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>INC000000152869</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-21T07:20:13.000Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>INC000000152965</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-21T09:00:01.999Z</v>
+        <v>2026-07-19T13:24:13.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>INC000000152873</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>INC000000152971</v>
+        <v>INC000000153025</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-18T08:43:13.999Z</v>
+        <v>2026-07-19T13:28:43.999Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>WO0000000309678</v>
+        <v>INC000000153024</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-18T07:42:09.999Z</v>
+        <v>2026-07-19T13:24:41.999Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>INC000000152877</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-21T07:17:20.000Z</v>
+        <v>2026-07-20T18:58:17.000Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>INC000000152878</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-18T08:12:08.000Z</v>
+        <v>2026-07-21T07:52:42.999Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>WO0000000309682</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-19T12:52:16.000Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>WO0000000309686</v>
+        <v>INC000000153028</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-20T18:58:47.999Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>INC000000152879</v>
+        <v>INC000000153029</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-21T10:36:31.000Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>WO0000000309689</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-21T07:09:08.000Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000153118</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-18T12:53:54.000Z</v>
+        <v>2026-07-21T09:37:20.000Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>INC000000152883</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-18T08:39:53.000Z</v>
+        <v>2026-07-21T10:36:26.000Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>WO0000000309692</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-18T08:48:11.000Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>INC000000152981</v>
+        <v>INC000000153031</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-21T00:11:10.000Z</v>
+        <v>2026-07-21T09:40:02.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>INC000000152980</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-18T16:16:48.000Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>WO0000000309728</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-20T23:05:18.000Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000309732</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-18T09:10:30.000Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>WO0000000309697</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-21T07:56:14.999Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>INC000000152888</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-18T09:48:34.000Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>INC000000152985</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-18T09:49:22.999Z</v>
+        <v>2026-07-21T07:41:05.999Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>WO0000000309698</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-18T10:07:47.000Z</v>
+        <v>2026-07-21T07:47:06.000Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>INC000000152986</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-21T08:16:08.000Z</v>
+        <v>2026-07-21T07:58:21.000Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-18T10:49:11.000Z</v>
+        <v>2026-07-21T08:01:28.000Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>INC000000152989</v>
+        <v>INC000000153123</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-18T09:42:12.000Z</v>
+        <v>2026-07-21T07:54:40.000Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>INC000000152990</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-21T09:00:11.000Z</v>
+        <v>2026-07-20T08:42:15.000Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>INC000000152890</v>
+        <v>INC000000153125</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-21T07:32:12.000Z</v>
+        <v>2026-07-21T07:46:07.000Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>WO0000000309802</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-21T07:12:45.999Z</v>
+        <v>2026-07-21T09:45:18.000Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>WO0000000309803</v>
+        <v>WO0000000309791</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-20T12:51:30.000Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>INC000000152891</v>
+        <v>WO0000000309792</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-20T19:05:32.000Z</v>
+        <v>2026-07-20T14:10:35.999Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>INC000000152994</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-20T19:04:33.999Z</v>
+        <v>2026-07-21T09:36:30.999Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>INC000000152892</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-20T19:03:52.000Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-20T19:04:20.000Z</v>
+        <v>2026-07-21T08:43:23.000Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>WO0000000309804</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-19T01:10:57.000Z</v>
+        <v>2026-07-20T18:35:59.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000309805</v>
+        <v>WO0000000309794</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-18T11:44:19.999Z</v>
+        <v>2026-07-20T18:20:05.999Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>WO0000000309807</v>
+        <v>WO0000000309843</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-19T01:11:11.000Z</v>
+        <v>2026-07-20T18:23:24.000Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>INC000000152896</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-21T07:32:42.999Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>INC000000153000</v>
+        <v>WO0000000309797</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-21T07:31:13.000Z</v>
+        <v>2026-07-20T19:09:36.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>INC000000152897</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-21T07:33:22.000Z</v>
+        <v>2026-07-21T08:36:19.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>INC000000152898</v>
+        <v>WO0000000309798</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-21T08:41:17.000Z</v>
+        <v>2026-07-21T07:04:25.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>WO0000000309810</v>
+        <v>WO0000000309852</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-20T22:58:26.999Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>WO0000000309752</v>
+        <v>WO0000000309853</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-21T05:54:59.000Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>INC000000153003</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-21T09:03:17.000Z</v>
+        <v>2026-07-21T09:44:12.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>INC000000152900</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-21T08:04:18.000Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>WO0000000309815</v>
+        <v>WO0000000309906</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-21T09:12:13.999Z</v>
+        <v>2026-07-21T07:44:08.000Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>INC000000153006</v>
+        <v>WO0000000309909</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-21T07:43:47.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T07:19:30.000Z</v>
+        <v>2026-07-21T08:19:35.999Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>WO0000000309816</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-21T06:40:04.000Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-21T06:23:37.000Z</v>
+        <v>2026-07-21T08:16:43.999Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000153103</v>
+        <v>INC000000153050</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T08:04:41.000Z</v>
+        <v>2026-07-21T07:46:48.000Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>INC000000153009</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-21T08:17:58.999Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>INC000000153011</v>
+        <v>INC000000153137</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-18T12:32:55.000Z</v>
+        <v>2026-07-21T07:03:14.999Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000309819</v>
+        <v>WO0000000309914</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-20T23:23:23.000Z</v>
+        <v>2026-07-21T07:20:13.999Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>WO0000000309759</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-21T10:44:20.000Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>INC000000153012</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-21T08:03:57.000Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>INC000000153013</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-21T07:19:23.999Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>WO0000000309825</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-21T07:31:56.999Z</v>
+        <v>2026-07-21T09:37:42.999Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>INC000000153105</v>
+        <v>INC000000153053</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-21T07:19:54.000Z</v>
+        <v>2026-07-21T08:05:04.000Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>INC000000153015</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-20T15:39:51.999Z</v>
+        <v>2026-07-21T09:37:31.000Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>WO0000000309826</v>
+        <v>WO0000000309927</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-21T07:30:09.000Z</v>
+        <v>2026-07-21T07:54:45.999Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>INC000000153017</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-18T15:26:50.000Z</v>
+        <v>2026-07-21T10:11:19.999Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>WO0000000309768</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-21T08:34:57.999Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>INC000000153107</v>
+        <v>WO0000000309867</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-18T17:18:50.999Z</v>
+        <v>2026-07-21T08:13:16.000Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>WO0000000309769</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-21T07:30:32.000Z</v>
+        <v>2026-07-21T07:57:56.999Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>WO0000000309829</v>
+        <v>INC000000153060</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-21T08:01:12.999Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>WO0000000309830</v>
+        <v>INC000000153061</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-21T07:38:18.000Z</v>
+        <v>2026-07-21T10:23:25.999Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>INC000000153108</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-21T07:53:45.000Z</v>
+        <v>2026-07-21T10:38:36.000Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>INC000000153019</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-19T08:43:56.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>INC000000153020</v>
+        <v>INC000000153063</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-21T07:53:07.999Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>WO0000000309772</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-21T07:55:55.000Z</v>
+        <v>2026-07-21T10:15:53.000Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>WO0000000309773</v>
+        <v>WO0000000309876</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-21T07:56:38.000Z</v>
+        <v>2026-07-21T08:19:59.000Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>INC000000153021</v>
+        <v>WO0000000309877</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-21T07:08:54.000Z</v>
+        <v>2026-07-21T08:15:48.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>INC000000153022</v>
+        <v>WO0000000309875</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-19T10:27:01.999Z</v>
+        <v>2026-07-21T10:03:29.999Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>INC000000153110</v>
+        <v>WO0000000309939</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-19T13:24:13.000Z</v>
+        <v>2026-07-21T08:42:26.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>INC000000153111</v>
+        <v>WO0000000309878</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-21T08:35:47.000Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>INC000000153025</v>
+        <v>WO0000000309941</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-19T13:28:43.999Z</v>
+        <v>2026-07-21T09:14:35.999Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>INC000000153024</v>
+        <v>WO0000000309879</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-19T13:24:41.999Z</v>
+        <v>2026-07-21T08:17:04.000Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>INC000000153027</v>
+        <v>WO0000000309944</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-20T18:58:17.000Z</v>
+        <v>2026-07-21T08:15:03.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>WO0000000309834</v>
+        <v>INC000000153149</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-21T07:52:42.999Z</v>
+        <v>2026-07-21T08:58:21.000Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>INC000000153114</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-19T12:52:16.000Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>INC000000153028</v>
+        <v>INC000000153151</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-20T18:58:47.999Z</v>
+        <v>2026-07-21T09:13:22.999Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>INC000000153029</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-19T13:44:46.000Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-21T07:09:08.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>INC000000153118</v>
+        <v>INC000000153147</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-21T08:32:11.000Z</v>
+        <v>2026-07-21T09:06:12.000Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-19T14:37:17.999Z</v>
+        <v>2026-07-21T08:41:34.000Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>INC000000153121</v>
+        <v>INC000000153064</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>INC000000153031</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-20T07:13:50.000Z</v>
+        <v>2026-07-21T09:45:12.999Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>WO0000000309780</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-21T09:47:21.999Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>WO0000000309837</v>
+        <v>WO0000000309888</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-21T08:44:29.999Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>WO0000000309781</v>
+        <v>WO0000000309950</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-21T08:57:28.999Z</v>
+        <v>2026-07-21T08:39:49.000Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>WO0000000309783</v>
+        <v>WO0000000309951</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-21T09:40:47.000Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>WO0000000309838</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>INC000000153034</v>
+        <v>WO0000000309952</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-21T07:41:05.999Z</v>
+        <v>2026-07-21T08:33:13.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>INC000000153035</v>
+        <v>WO0000000309953</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-21T07:47:06.000Z</v>
+        <v>2026-07-21T08:41:50.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>INC000000153036</v>
+        <v>WO0000000309889</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-21T07:58:21.000Z</v>
+        <v>2026-07-21T08:33:25.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>INC000000153037</v>
+        <v>INC000000153070</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-21T08:01:28.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>INC000000153123</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-21T07:54:40.000Z</v>
+        <v>2026-07-21T08:48:14.999Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153156</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-20T08:42:15.000Z</v>
+        <v>2026-07-21T08:39:24.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>INC000000153125</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-21T07:46:07.000Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-20T12:50:53.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>WO0000000309840</v>
+        <v>INC000000153071</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-21T08:50:20.000Z</v>
+        <v>2026-07-21T08:50:05.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>WO0000000309791</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-20T12:51:30.000Z</v>
+        <v>2026-07-21T08:49:28.000Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>WO0000000309792</v>
+        <v>INC000000153157</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-20T14:10:35.999Z</v>
+        <v>2026-07-21T08:51:40.000Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>WO0000000309841</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-20T14:29:59.999Z</v>
+        <v>2026-07-21T10:35:54.000Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>WO0000000309842</v>
+        <v>INC000000153073</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T10:27:24.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>INC000000153128</v>
+        <v>INC000000153075</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-21T08:43:23.000Z</v>
+        <v>2026-07-21T09:12:07.000Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000309793</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-20T18:35:59.000Z</v>
+        <v>2026-07-21T09:22:48.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>WO0000000309794</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-20T18:20:05.999Z</v>
+        <v>2026-07-21T10:28:57.999Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>WO0000000309843</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-20T18:23:24.000Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>WO0000000309796</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-21T08:49:16.000Z</v>
+        <v>2026-07-21T09:21:34.000Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>WO0000000309845</v>
+        <v>WO0000000310005</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-21T09:16:50.000Z</v>
+        <v>2026-07-21T09:32:59.000Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>WO0000000309846</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-21T08:48:32.000Z</v>
+        <v>2026-07-21T08:56:12.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>WO0000000309848</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T09:20:33.000Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>WO0000000309797</v>
+        <v>INC000000153076</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-20T19:09:36.000Z</v>
+        <v>2026-07-21T10:25:21.000Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>WO0000000309851</v>
+        <v>WO0000000310008</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-21T08:36:19.000Z</v>
+        <v>2026-07-21T08:58:48.000Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>WO0000000309798</v>
+        <v>WO0000000309962</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-21T07:04:25.000Z</v>
+        <v>2026-07-21T09:15:42.999Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>WO0000000309852</v>
+        <v>WO0000000310009</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-20T22:58:26.999Z</v>
+        <v>2026-07-21T10:38:41.000Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>WO0000000309853</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-21T05:54:59.000Z</v>
+        <v>2026-07-21T09:03:20.999Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-21T07:13:01.999Z</v>
+        <v>2026-07-21T09:28:19.000Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>INC000000153129</v>
+        <v>WO0000000309967</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-21T07:02:26.000Z</v>
+        <v>2026-07-21T09:02:23.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>WO0000000309902</v>
+        <v>WO0000000310013</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T09:07:07.000Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>WO0000000309906</v>
+        <v>WO0000000309973</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-21T07:44:08.000Z</v>
+        <v>2026-07-21T09:08:48.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>INC000000153131</v>
+        <v>WO0000000310015</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-21T06:32:02.000Z</v>
+        <v>2026-07-21T09:27:41.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>INC000000153132</v>
+        <v>INC000000153079</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-21T07:09:39.000Z</v>
+        <v>2026-07-21T09:12:25.000Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>INC000000153044</v>
+        <v>INC000000153164</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-21T08:18:16.000Z</v>
+        <v>2026-07-21T09:16:22.000Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>WO0000000309909</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-21T07:43:47.000Z</v>
+        <v>2026-07-21T09:29:42.999Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>INC000000153047</v>
+        <v>WO0000000310016</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-21T08:19:35.999Z</v>
+        <v>2026-07-21T09:14:48.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153168</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-21T06:40:04.000Z</v>
+        <v>2026-07-21T09:54:40.000Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>INC000000153134</v>
+        <v>WO0000000310017</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-21T08:16:43.999Z</v>
+        <v>2026-07-21T09:29:50.999Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>INC000000153049</v>
+        <v>WO0000000310018</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-21T07:06:12.999Z</v>
+        <v>2026-07-21T09:18:47.000Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>INC000000153050</v>
+        <v>INC000000153170</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-21T07:46:48.000Z</v>
+        <v>2026-07-21T09:38:39.999Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>INC000000153048</v>
+        <v>WO0000000310019</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T10:19:05.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>INC000000153137</v>
+        <v>INC000000153169</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-21T07:03:14.999Z</v>
+        <v>2026-07-21T10:02:51.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>WO0000000309914</v>
+        <v>WO0000000309981</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-21T07:20:13.999Z</v>
+        <v>2026-07-21T09:19:50.000Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>INC000000153138</v>
+        <v>INC000000153165</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-21T08:53:33.000Z</v>
+        <v>2026-07-21T09:36:23.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>INC000000153052</v>
+        <v>WO0000000310021</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T09:24:02.000Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>INC000000153051</v>
+        <v>INC000000153172</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-21T07:31:21.000Z</v>
+        <v>2026-07-21T09:52:46.999Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>WO0000000309862</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T10:36:09.999Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>WO0000000309861</v>
+        <v>INC000000153174</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-21T07:22:58.000Z</v>
+        <v>2026-07-21T09:57:25.000Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>INC000000153053</v>
+        <v>INC000000153175</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-21T08:05:04.000Z</v>
+        <v>2026-07-21T09:28:26.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>INC000000153055</v>
+        <v>WO0000000309986</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-21T08:14:27.000Z</v>
+        <v>2026-07-21T09:28:28.999Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>INC000000153140</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-21T08:21:47.999Z</v>
+        <v>2026-07-21T09:27:18.999Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>WO0000000309927</v>
+        <v>WO0000000309975</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-21T07:54:45.999Z</v>
+        <v>2026-07-21T09:49:40.999Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>INC000000153057</v>
+        <v>WO0000000309984</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-21T08:19:32.000Z</v>
+        <v>2026-07-21T09:31:44.000Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>INC000000153056</v>
+        <v>WO0000000309987</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-21T08:26:45.000Z</v>
+        <v>2026-07-21T09:30:18.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>WO0000000309931</v>
+        <v>INC000000153177</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-21T08:34:57.999Z</v>
+        <v>2026-07-21T09:31:53.000Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>WO0000000309867</v>
+        <v>WO0000000310022</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-21T08:13:16.000Z</v>
+        <v>2026-07-21T09:30:46.000Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153080</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-21T07:57:56.999Z</v>
+        <v>2026-07-21T10:46:26.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>INC000000153060</v>
+        <v>INC000000153171</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-21T08:01:12.999Z</v>
+        <v>2026-07-21T10:25:59.000Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>INC000000153061</v>
+        <v>INC000000153176</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-21T08:42:12.000Z</v>
+        <v>2026-07-21T09:43:34.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>INC000000153062</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-21T09:09:19.000Z</v>
+        <v>2026-07-21T09:37:20.999Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>INC000000153143</v>
+        <v>WO0000000310025</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T09:36:55.000Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>INC000000153063</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:37:57.000Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>INC000000153145</v>
+        <v>INC000000153180</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-21T08:51:54.000Z</v>
+        <v>2026-07-21T09:57:04.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>WO0000000309876</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-21T08:19:59.000Z</v>
+        <v>2026-07-21T09:40:19.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>WO0000000309877</v>
+        <v>INC000000153181</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-21T08:15:48.000Z</v>
+        <v>2026-07-21T09:48:10.999Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>WO0000000309875</v>
+        <v>WO0000000309993</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-21T08:23:40.000Z</v>
+        <v>2026-07-21T09:41:07.000Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>WO0000000309939</v>
+        <v>INC000000153178</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-21T08:42:26.000Z</v>
+        <v>2026-07-21T10:29:02.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>WO0000000309878</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-21T08:35:47.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>WO0000000309941</v>
+        <v>INC000000153082</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-21T09:14:35.999Z</v>
+        <v>2026-07-21T10:22:17.000Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>WO0000000309879</v>
+        <v>WO0000000309991</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-21T08:17:04.000Z</v>
+        <v>2026-07-21T09:45:25.999Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>INC000000153148</v>
+        <v>INC000000153179</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-21T08:33:18.000Z</v>
+        <v>2026-07-21T09:46:47.000Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>WO0000000309944</v>
+        <v>WO0000000309995</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-21T08:15:03.000Z</v>
+        <v>2026-07-21T10:01:19.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>INC000000153149</v>
+        <v>WO0000000305266</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-21T08:58:21.000Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>WO0000000309880</v>
+        <v>WO0000000309997</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T10:09:06.999Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>INC000000153151</v>
+        <v>WO0000000309998</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-21T09:13:22.999Z</v>
+        <v>2026-07-21T09:47:07.999Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>WO0000000309945</v>
+        <v>WO0000000309996</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T09:49:05.999Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>WO0000000309946</v>
+        <v>INC000000153182</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T10:35:39.000Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>INC000000153147</v>
+        <v>WO0000000310000</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-21T09:06:12.000Z</v>
+        <v>2026-07-21T09:49:32.000Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>INC000000153065</v>
+        <v>WO0000000310024</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-21T08:41:34.000Z</v>
+        <v>2026-07-21T09:50:13.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>WO0000000309883</v>
+        <v>WO0000000309999</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-21T08:22:19.000Z</v>
+        <v>2026-07-21T09:50:29.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>INC000000153152</v>
+        <v>WO0000000310102</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-21T08:37:55.999Z</v>
+        <v>2026-07-21T09:50:55.000Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>INC000000153064</v>
+        <v>WO0000000310033</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T09:51:00.000Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>INC000000153153</v>
+        <v>INC000000153185</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-21T08:42:24.999Z</v>
+        <v>2026-07-21T10:21:27.999Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>WO0000000309949</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-21T08:27:24.000Z</v>
+        <v>2026-07-21T09:55:33.000Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>INC000000153067</v>
+        <v>WO0000000305268</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-21T08:44:28.000Z</v>
+        <v>2026-07-21T09:55:25.000Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>WO0000000309888</v>
+        <v>INC000000153083</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-21T08:44:29.999Z</v>
+        <v>2026-07-21T10:29:05.000Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>WO0000000309950</v>
+        <v>WO0000000310105</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-21T08:39:49.000Z</v>
+        <v>2026-07-21T10:09:51.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>WO0000000309951</v>
+        <v>INC000000153084</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-21T08:48:42.000Z</v>
+        <v>2026-07-21T10:22:19.000Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>INC000000153068</v>
+        <v>WO0000000305269</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-21T09:57:11.000Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>WO0000000309952</v>
+        <v>WO0000000310034</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-21T08:33:13.000Z</v>
+        <v>2026-07-21T10:02:08.000Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>WO0000000309953</v>
+        <v>WO0000000310106</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-21T08:41:50.000Z</v>
+        <v>2026-07-21T10:02:21.999Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>WO0000000309889</v>
+        <v>WO0000000310107</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-21T08:33:25.000Z</v>
+        <v>2026-07-21T10:27:27.999Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>INC000000153070</v>
+        <v>WO0000000310036</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:59:20.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153186</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-21T08:48:14.999Z</v>
+        <v>2026-07-21T10:44:35.999Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>INC000000153156</v>
+        <v>WO0000000310109</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-21T08:39:24.000Z</v>
+        <v>2026-07-21T10:07:20.999Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>WO0000000309892</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-21T09:04:46.000Z</v>
+        <v>2026-07-21T10:05:59.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>WO0000000309954</v>
+        <v>WO0000000310039</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>WO0000000309893</v>
+        <v>INC000000153086</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-21T08:58:55.000Z</v>
+        <v>2026-07-21T10:23:37.999Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>INC000000153071</v>
+        <v>WO0000000310040</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-21T08:50:05.000Z</v>
+        <v>2026-07-21T10:09:05.000Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>INC000000153072</v>
+        <v>WO0000000310041</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-21T08:49:28.000Z</v>
+        <v>2026-07-21T10:03:27.999Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>INC000000153157</v>
+        <v>WO0000000310042</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-21T08:51:40.000Z</v>
+        <v>2026-07-21T10:08:51.000Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>INC000000153159</v>
+        <v>INC000000153187</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-21T09:05:09.000Z</v>
+        <v>2026-07-21T10:25:14.000Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>INC000000153073</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-21T09:07:50.000Z</v>
+        <v>2026-07-21T10:31:45.000Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>INC000000153075</v>
+        <v>INC000000153089</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-21T09:12:07.000Z</v>
+        <v>2026-07-21T10:28:35.000Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>WO0000000309956</v>
+        <v>WO0000000310045</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-21T08:51:44.999Z</v>
+        <v>2026-07-21T10:35:09.000Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>WO0000000310002</v>
+        <v>INC000000153090</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-21T09:09:20.000Z</v>
+        <v>2026-07-21T10:32:06.999Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>INC000000153158</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-21T09:19:52.999Z</v>
+        <v>2026-07-21T10:08:14.000Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>WO0000000309957</v>
+        <v>INC000000153091</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-21T08:54:42.999Z</v>
+        <v>2026-07-21T10:30:46.000Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>WO0000000309958</v>
+        <v>INC000000153094</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-21T08:54:45.000Z</v>
+        <v>2026-07-21T10:34:10.000Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>WO0000000310004</v>
+        <v>WO0000000310114</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-21T09:11:32.000Z</v>
+        <v>2026-07-21T10:12:20.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>WO0000000310005</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-21T08:57:51.999Z</v>
+        <v>2026-07-21T10:13:41.000Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>WO0000000309959</v>
+        <v>WO0000000310113</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-21T08:56:12.000Z</v>
+        <v>2026-07-21T10:32:45.000Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>WO0000000310006</v>
+        <v>WO0000000310046</v>
       </c>
       <c r="B1181" s="1" t="d">
-        <v>2026-07-21T09:13:38.000Z</v>
+        <v>2026-07-21T10:13:36.000Z</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>INC000000153076</v>
+        <v>INC000000153088</v>
       </c>
       <c r="B1182" s="1" t="d">
-        <v>2026-07-21T09:11:32.000Z</v>
+        <v>2026-07-21T10:17:32.000Z</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>WO0000000310007</v>
+        <v>WO0000000310047</v>
       </c>
       <c r="B1183" s="1" t="d">
-        <v>2026-07-21T08:57:11.000Z</v>
+        <v>2026-07-21T10:14:06.000Z</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>WO0000000310008</v>
+        <v>INC000000153188</v>
       </c>
       <c r="B1184" s="1" t="d">
-        <v>2026-07-21T08:58:48.000Z</v>
+        <v>2026-07-21T10:16:45.000Z</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>WO0000000309962</v>
+        <v>WO0000000310118</v>
       </c>
       <c r="B1185" s="1" t="d">
-        <v>2026-07-21T09:15:42.999Z</v>
+        <v>2026-07-21T10:29:50.999Z</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>WO0000000310009</v>
+        <v>INC000000153189</v>
       </c>
       <c r="B1186" s="1" t="d">
-        <v>2026-07-21T09:00:52.999Z</v>
+        <v>2026-07-21T10:18:16.000Z</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>WO0000000309963</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B1187" s="1" t="d">
-        <v>2026-07-21T09:00:20.000Z</v>
+        <v>2026-07-21T10:18:38.000Z</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>INC000000153161</v>
+        <v>WO0000000310049</v>
       </c>
       <c r="B1188" s="1" t="d">
-        <v>2026-07-21T09:18:35.000Z</v>
+        <v>2026-07-21T10:20:08.000Z</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>WO0000000309960</v>
+        <v>INC000000153190</v>
       </c>
       <c r="B1189" s="1" t="d">
-        <v>2026-07-21T09:17:47.000Z</v>
+        <v>2026-07-21T10:38:37.999Z</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>INC000000153074</v>
+        <v>WO0000000310050</v>
       </c>
       <c r="B1190" s="1" t="d">
-        <v>2026-07-21T09:03:20.999Z</v>
+        <v>2026-07-21T10:21:12.000Z</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>WO0000000309966</v>
+        <v>INC000000153191</v>
       </c>
       <c r="B1191" s="1" t="d">
-        <v>2026-07-21T09:17:50.000Z</v>
+        <v>2026-07-21T10:39:39.000Z</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>WO0000000309961</v>
+        <v>INC000000153192</v>
       </c>
       <c r="B1192" s="1" t="d">
-        <v>2026-07-21T09:05:07.999Z</v>
+        <v>2026-07-21T10:26:23.999Z</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>WO0000000309967</v>
+        <v>WO0000000310051</v>
       </c>
       <c r="B1193" s="1" t="d">
-        <v>2026-07-21T09:02:23.000Z</v>
+        <v>2026-07-21T10:23:58.000Z</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>INC000000153078</v>
+        <v>INC000000153193</v>
       </c>
       <c r="B1194" s="1" t="d">
-        <v>2026-07-21T09:17:45.000Z</v>
+        <v>2026-07-21T10:25:57.999Z</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>WO0000000310012</v>
+        <v>WO0000000310120</v>
       </c>
       <c r="B1195" s="1" t="d">
-        <v>2026-07-21T09:18:52.000Z</v>
+        <v>2026-07-21T10:35:25.000Z</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>WO0000000310013</v>
+        <v>WO0000000310053</v>
       </c>
       <c r="B1196" s="1" t="d">
-        <v>2026-07-21T09:07:07.000Z</v>
+        <v>2026-07-21T10:27:39.999Z</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>WO0000000309973</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B1197" s="1" t="d">
-        <v>2026-07-21T09:08:48.000Z</v>
+        <v>2026-07-21T10:45:16.999Z</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>WO0000000309969</v>
+        <v>INC000000153100</v>
       </c>
       <c r="B1198" s="1" t="d">
-        <v>2026-07-21T09:19:52.000Z</v>
+        <v>2026-07-21T10:36:40.000Z</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>WO0000000310015</v>
+        <v>INC000000153194</v>
       </c>
       <c r="B1199" s="1" t="d">
-        <v>2026-07-21T09:12:18.999Z</v>
+        <v>2026-07-21T10:31:29.999Z</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>INC000000153079</v>
+        <v>WO0000000310122</v>
       </c>
       <c r="B1200" s="1" t="d">
-        <v>2026-07-21T09:12:25.000Z</v>
+        <v>2026-07-21T10:28:56.999Z</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>INC000000153164</v>
+        <v>INC000000153099</v>
       </c>
       <c r="B1201" s="1" t="d">
-        <v>2026-07-21T09:16:22.000Z</v>
+        <v>2026-07-21T10:34:51.000Z</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153095</v>
       </c>
       <c r="B1202" s="1" t="d">
-        <v>2026-07-21T09:17:36.999Z</v>
+        <v>2026-07-21T10:34:35.999Z</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>WO0000000310016</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B1203" s="1" t="d">
-        <v>2026-07-21T09:14:48.000Z</v>
+        <v>2026-07-21T10:34:07.000Z</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>INC000000153168</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B1204" s="1" t="d">
-        <v>2026-07-21T09:15:14.000Z</v>
+        <v>2026-07-21T10:34:43.999Z</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>WO0000000310017</v>
+        <v>INC000000153201</v>
       </c>
       <c r="B1205" s="1" t="d">
-        <v>2026-07-21T09:16:13.000Z</v>
+        <v>2026-07-21T10:39:28.000Z</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>WO0000000310018</v>
+        <v>WO0000000310123</v>
       </c>
       <c r="B1206" s="1" t="d">
-        <v>2026-07-21T09:18:47.000Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="str">
-        <v>INC000000153170</v>
+        <v>WO0000000310055</v>
       </c>
       <c r="B1207" s="1" t="d">
-        <v>2026-07-21T09:18:59.000Z</v>
+        <v>2026-07-21T10:43:50.000Z</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>WO0000000310019</v>
+        <v>INC000000153202</v>
       </c>
       <c r="B1208" s="1" t="d">
-        <v>2026-07-21T09:19:04.000Z</v>
+        <v>2026-07-21T10:40:42.000Z</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>INC000000153169</v>
+        <v>INC000000153197</v>
       </c>
       <c r="B1209" s="1" t="d">
-        <v>2026-07-21T09:19:13.000Z</v>
+        <v>2026-07-21T10:44:35.999Z</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>WO0000000309981</v>
+        <v>INC000000153203</v>
       </c>
       <c r="B1210" s="1" t="d">
-        <v>2026-07-21T09:19:50.000Z</v>
+        <v>2026-07-21T10:41:24.000Z</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
+        <v>WO0000000310127</v>
+      </c>
+      <c r="B1211" s="1" t="d">
+        <v>2026-07-21T10:42:01.999Z</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="str">
+        <v>INC000000153204</v>
+      </c>
+      <c r="B1212" s="1" t="d">
+        <v>2026-07-21T10:44:56.000Z</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="str">
+        <v>WO0000000310060</v>
+      </c>
+      <c r="B1213" s="1" t="d">
+        <v>2026-07-21T10:46:52.000Z</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="str">
+        <v>WO0000000310061</v>
+      </c>
+      <c r="B1214" s="1" t="d">
+        <v>2026-07-21T10:47:06.000Z</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="str">
+        <v>INC000000153205</v>
+      </c>
+      <c r="B1215" s="1" t="d">
+        <v>2026-07-21T10:47:20.000Z</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="str">
+        <v>WO0000000310130</v>
+      </c>
+      <c r="B1216" s="1" t="d">
+        <v>2026-07-21T10:47:32.000Z</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1211"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1217"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1217"/>
+  <dimension ref="A1:B1222"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2843,370 +2843,370 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>WO0000000306433</v>
+        <v>INC000000151200</v>
       </c>
       <c r="B306" s="1" t="d">
-        <v>2026-07-16T16:04:33.999Z</v>
+        <v>2026-07-10T10:51:56.000Z</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>WO0000000306373</v>
+        <v>WO0000000306433</v>
       </c>
       <c r="B307" s="1" t="d">
-        <v>2026-07-17T17:02:38.000Z</v>
+        <v>2026-07-16T16:04:33.999Z</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>WO0000000306610</v>
+        <v>WO0000000306373</v>
       </c>
       <c r="B308" s="1" t="d">
-        <v>2026-07-16T09:06:23.000Z</v>
+        <v>2026-07-17T17:02:38.000Z</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>INC000000135134</v>
+        <v>WO0000000306610</v>
       </c>
       <c r="B309" s="1" t="d">
-        <v>2026-07-14T10:35:47.000Z</v>
+        <v>2026-07-16T09:06:23.000Z</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>INC000000136403</v>
+        <v>INC000000135134</v>
       </c>
       <c r="B310" s="1" t="d">
-        <v>2026-07-14T06:43:05.000Z</v>
+        <v>2026-07-14T10:35:47.000Z</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>INC000000138835</v>
+        <v>INC000000136403</v>
       </c>
       <c r="B311" s="1" t="d">
-        <v>2026-07-14T10:35:56.000Z</v>
+        <v>2026-07-14T06:43:05.000Z</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>INC000000139335</v>
+        <v>INC000000138835</v>
       </c>
       <c r="B312" s="1" t="d">
-        <v>2026-07-14T06:43:37.000Z</v>
+        <v>2026-07-14T10:35:56.000Z</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>WO0000000282199</v>
+        <v>INC000000139335</v>
       </c>
       <c r="B313" s="1" t="d">
-        <v>2026-07-14T15:02:42.000Z</v>
+        <v>2026-07-14T06:43:37.000Z</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>INC000000141515</v>
+        <v>WO0000000282199</v>
       </c>
       <c r="B314" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-14T15:02:42.000Z</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>WO0000000293293</v>
+        <v>INC000000141515</v>
       </c>
       <c r="B315" s="1" t="d">
-        <v>2026-07-15T08:29:08.000Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>INC000000146720</v>
+        <v>WO0000000293293</v>
       </c>
       <c r="B316" s="1" t="d">
-        <v>2026-07-16T08:34:09.000Z</v>
+        <v>2026-07-15T08:29:08.000Z</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>WO0000000295688</v>
+        <v>INC000000146720</v>
       </c>
       <c r="B317" s="1" t="d">
-        <v>2026-07-16T09:17:24.999Z</v>
+        <v>2026-07-16T08:34:09.000Z</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>INC000000147260</v>
+        <v>WO0000000295688</v>
       </c>
       <c r="B318" s="1" t="d">
-        <v>2026-07-14T08:08:06.000Z</v>
+        <v>2026-07-16T09:17:24.999Z</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>INC000000147613</v>
+        <v>INC000000147260</v>
       </c>
       <c r="B319" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-14T08:08:06.000Z</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>INC000000149029</v>
+        <v>INC000000147613</v>
       </c>
       <c r="B320" s="1" t="d">
-        <v>2026-07-10T14:37:50.000Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>WO0000000301822</v>
+        <v>INC000000149029</v>
       </c>
       <c r="B321" s="1" t="d">
-        <v>2026-07-21T09:48:14.000Z</v>
+        <v>2026-07-10T14:37:50.000Z</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>INC000000149860</v>
+        <v>WO0000000301822</v>
       </c>
       <c r="B322" s="1" t="d">
-        <v>2026-07-16T15:59:24.000Z</v>
+        <v>2026-07-21T09:48:14.000Z</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>INC000000150036</v>
+        <v>INC000000149860</v>
       </c>
       <c r="B323" s="1" t="d">
-        <v>2026-07-16T07:28:43.999Z</v>
+        <v>2026-07-16T15:59:24.000Z</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>INC000000149964</v>
+        <v>INC000000150036</v>
       </c>
       <c r="B324" s="1" t="d">
-        <v>2026-07-15T15:21:53.000Z</v>
+        <v>2026-07-16T07:28:43.999Z</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>WO0000000303232</v>
+        <v>INC000000149964</v>
       </c>
       <c r="B325" s="1" t="d">
-        <v>2026-07-17T17:20:56.999Z</v>
+        <v>2026-07-15T15:21:53.000Z</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>INC000000150141</v>
+        <v>WO0000000303232</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2026-07-15T16:30:22.000Z</v>
+        <v>2026-07-17T17:20:56.999Z</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>INC000000150288</v>
+        <v>INC000000150141</v>
       </c>
       <c r="B327" s="1" t="d">
-        <v>2026-07-10T12:39:00.000Z</v>
+        <v>2026-07-15T16:30:22.000Z</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>INC000000150197</v>
+        <v>INC000000150288</v>
       </c>
       <c r="B328" s="1" t="d">
-        <v>2026-07-17T11:00:31.000Z</v>
+        <v>2026-07-10T12:39:00.000Z</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>INC000000150475</v>
+        <v>INC000000150197</v>
       </c>
       <c r="B329" s="1" t="d">
-        <v>2026-07-16T08:36:47.000Z</v>
+        <v>2026-07-21T10:51:58.000Z</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>WO0000000304256</v>
+        <v>INC000000150475</v>
       </c>
       <c r="B330" s="1" t="d">
-        <v>2026-07-16T12:20:08.000Z</v>
+        <v>2026-07-16T08:36:47.000Z</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>WO0000000304437</v>
+        <v>WO0000000304256</v>
       </c>
       <c r="B331" s="1" t="d">
-        <v>2026-07-16T12:22:04.999Z</v>
+        <v>2026-07-16T12:20:08.000Z</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>WO0000000304614</v>
+        <v>WO0000000304437</v>
       </c>
       <c r="B332" s="1" t="d">
-        <v>2026-07-16T12:25:00.000Z</v>
+        <v>2026-07-16T12:22:04.999Z</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>INC000000150547</v>
+        <v>WO0000000304614</v>
       </c>
       <c r="B333" s="1" t="d">
-        <v>2026-07-16T08:37:46.000Z</v>
+        <v>2026-07-16T12:25:00.000Z</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>WO0000000304990</v>
+        <v>INC000000150547</v>
       </c>
       <c r="B334" s="1" t="d">
-        <v>2026-07-15T10:54:42.999Z</v>
+        <v>2026-07-16T08:37:46.000Z</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>INC000000150732</v>
+        <v>WO0000000304990</v>
       </c>
       <c r="B335" s="1" t="d">
-        <v>2026-07-16T08:27:41.000Z</v>
+        <v>2026-07-15T10:54:42.999Z</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>WO0000000305312</v>
+        <v>INC000000150732</v>
       </c>
       <c r="B336" s="1" t="d">
-        <v>2026-07-15T11:26:08.000Z</v>
+        <v>2026-07-16T08:27:41.000Z</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305312</v>
       </c>
       <c r="B337" s="1" t="d">
-        <v>2026-07-15T13:10:05.000Z</v>
+        <v>2026-07-15T11:26:08.000Z</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>INC000000150882</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B338" s="1" t="d">
-        <v>2026-07-15T10:45:04.000Z</v>
+        <v>2026-07-15T13:10:05.000Z</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>WO0000000305349</v>
+        <v>INC000000150882</v>
       </c>
       <c r="B339" s="1" t="d">
-        <v>2026-07-14T12:21:19.000Z</v>
+        <v>2026-07-15T10:45:04.000Z</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000305349</v>
       </c>
       <c r="B340" s="1" t="d">
-        <v>2026-07-16T10:45:43.999Z</v>
+        <v>2026-07-14T12:21:19.000Z</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>WO0000000305815</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B341" s="1" t="d">
-        <v>2026-07-16T12:28:46.000Z</v>
+        <v>2026-07-16T10:45:43.999Z</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>WO0000000305843</v>
+        <v>WO0000000305815</v>
       </c>
       <c r="B342" s="1" t="d">
-        <v>2026-07-14T12:37:15.000Z</v>
+        <v>2026-07-16T12:28:46.000Z</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>WO0000000305743</v>
+        <v>WO0000000305843</v>
       </c>
       <c r="B343" s="1" t="d">
-        <v>2026-07-14T14:33:44.000Z</v>
+        <v>2026-07-14T12:37:15.000Z</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>INC000000151204</v>
+        <v>WO0000000305743</v>
       </c>
       <c r="B344" s="1" t="d">
-        <v>2026-07-14T12:46:36.000Z</v>
+        <v>2026-07-14T14:33:44.000Z</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>WO0000000305944</v>
+        <v>INC000000151204</v>
       </c>
       <c r="B345" s="1" t="d">
-        <v>2026-07-14T12:04:16.999Z</v>
+        <v>2026-07-14T12:46:36.000Z</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>INC000000151134</v>
+        <v>WO0000000305944</v>
       </c>
       <c r="B346" s="1" t="d">
-        <v>2026-07-14T10:49:05.000Z</v>
+        <v>2026-07-14T12:04:16.999Z</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>INC000000151151</v>
+        <v>INC000000151134</v>
       </c>
       <c r="B347" s="1" t="d">
-        <v>2026-07-16T08:22:24.000Z</v>
+        <v>2026-07-14T10:49:05.000Z</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>WO0000000306190</v>
+        <v>INC000000151151</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2026-07-14T13:13:31.000Z</v>
+        <v>2026-07-16T08:22:24.000Z</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>WO0000000306290</v>
+        <v>WO0000000306190</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2026-07-14T16:17:28.999Z</v>
+        <v>2026-07-14T13:13:31.000Z</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>WO0000000306328</v>
+        <v>WO0000000306290</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2026-07-14T16:39:44.000Z</v>
+        <v>2026-07-14T16:17:28.999Z</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>INC000000151200</v>
+        <v>WO0000000306328</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2026-07-10T10:51:56.000Z</v>
+        <v>2026-07-14T16:39:44.000Z</v>
       </c>
     </row>
     <row r="352">
@@ -3435,1298 +3435,1298 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>WO0000000307667</v>
+        <v>INC000000152045</v>
       </c>
       <c r="B380" s="1" t="d">
-        <v>2026-07-21T08:39:56.000Z</v>
+        <v>2026-07-16T10:52:09.000Z</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>WO0000000307671</v>
+        <v>WO0000000307667</v>
       </c>
       <c r="B381" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-21T08:39:56.000Z</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>INC000000152124</v>
+        <v>WO0000000307671</v>
       </c>
       <c r="B382" s="1" t="d">
-        <v>2026-07-15T14:11:57.000Z</v>
+        <v>2026-07-17T09:44:19.000Z</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>WO0000000307701</v>
+        <v>INC000000152124</v>
       </c>
       <c r="B383" s="1" t="d">
-        <v>2026-07-17T09:50:26.000Z</v>
+        <v>2026-07-15T14:11:57.000Z</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>INC000000152132</v>
+        <v>WO0000000307701</v>
       </c>
       <c r="B384" s="1" t="d">
-        <v>2026-07-15T14:13:17.000Z</v>
+        <v>2026-07-17T09:50:26.000Z</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>INC000000152134</v>
+        <v>INC000000152132</v>
       </c>
       <c r="B385" s="1" t="d">
-        <v>2026-07-15T14:13:50.000Z</v>
+        <v>2026-07-15T14:13:17.000Z</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>INC000000152138</v>
+        <v>INC000000152134</v>
       </c>
       <c r="B386" s="1" t="d">
-        <v>2026-07-15T14:16:43.999Z</v>
+        <v>2026-07-15T14:13:50.000Z</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>INC000000152139</v>
+        <v>INC000000152138</v>
       </c>
       <c r="B387" s="1" t="d">
-        <v>2026-07-15T14:17:19.000Z</v>
+        <v>2026-07-15T14:16:43.999Z</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>WO0000000307733</v>
+        <v>INC000000152139</v>
       </c>
       <c r="B388" s="1" t="d">
-        <v>2026-07-17T11:13:13.999Z</v>
+        <v>2026-07-15T14:17:19.000Z</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>WO0000000307735</v>
+        <v>WO0000000307733</v>
       </c>
       <c r="B389" s="1" t="d">
-        <v>2026-07-21T09:55:06.000Z</v>
+        <v>2026-07-17T11:13:13.999Z</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>WO0000000307812</v>
+        <v>WO0000000307735</v>
       </c>
       <c r="B390" s="1" t="d">
-        <v>2026-07-21T10:09:34.000Z</v>
+        <v>2026-07-21T09:55:06.000Z</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>INC000000152155</v>
+        <v>WO0000000307812</v>
       </c>
       <c r="B391" s="1" t="d">
-        <v>2026-07-15T16:57:39.000Z</v>
+        <v>2026-07-21T10:09:34.000Z</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>INC000000152156</v>
+        <v>INC000000152155</v>
       </c>
       <c r="B392" s="1" t="d">
-        <v>2026-07-15T14:18:27.000Z</v>
+        <v>2026-07-15T16:57:39.000Z</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>INC000000152158</v>
+        <v>INC000000152156</v>
       </c>
       <c r="B393" s="1" t="d">
-        <v>2026-07-15T14:19:58.000Z</v>
+        <v>2026-07-15T14:18:27.000Z</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>INC000000152073</v>
+        <v>INC000000152158</v>
       </c>
       <c r="B394" s="1" t="d">
-        <v>2026-07-16T09:23:53.000Z</v>
+        <v>2026-07-15T14:19:58.000Z</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>WO0000000307834</v>
+        <v>INC000000152073</v>
       </c>
       <c r="B395" s="1" t="d">
-        <v>2026-07-21T08:01:01.000Z</v>
+        <v>2026-07-16T09:23:53.000Z</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>WO0000000307769</v>
+        <v>WO0000000307834</v>
       </c>
       <c r="B396" s="1" t="d">
-        <v>2026-07-14T17:17:47.000Z</v>
+        <v>2026-07-21T08:01:01.000Z</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>WO0000000307852</v>
+        <v>WO0000000307769</v>
       </c>
       <c r="B397" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-14T17:17:47.000Z</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>WO0000000307923</v>
+        <v>WO0000000307852</v>
       </c>
       <c r="B398" s="1" t="d">
-        <v>2026-07-16T09:23:33.000Z</v>
+        <v>2026-07-17T12:30:37.999Z</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>WO0000000308004</v>
+        <v>WO0000000307923</v>
       </c>
       <c r="B399" s="1" t="d">
-        <v>2026-07-17T10:04:39.999Z</v>
+        <v>2026-07-16T09:23:33.000Z</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>INC000000152308</v>
+        <v>WO0000000308004</v>
       </c>
       <c r="B400" s="1" t="d">
-        <v>2026-07-16T09:37:19.000Z</v>
+        <v>2026-07-17T10:04:39.999Z</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>INC000000152320</v>
+        <v>INC000000152308</v>
       </c>
       <c r="B401" s="1" t="d">
-        <v>2026-07-15T10:29:52.000Z</v>
+        <v>2026-07-16T09:37:19.000Z</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>WO0000000307976</v>
+        <v>INC000000152320</v>
       </c>
       <c r="B402" s="1" t="d">
-        <v>2026-07-21T10:33:10.999Z</v>
+        <v>2026-07-15T10:29:52.000Z</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>WO0000000307981</v>
+        <v>WO0000000307976</v>
       </c>
       <c r="B403" s="1" t="d">
-        <v>2026-07-21T09:32:12.999Z</v>
+        <v>2026-07-21T10:33:10.999Z</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>WO0000000307984</v>
+        <v>WO0000000307981</v>
       </c>
       <c r="B404" s="1" t="d">
-        <v>2026-07-17T14:08:18.000Z</v>
+        <v>2026-07-21T09:32:12.999Z</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>INC000000152339</v>
+        <v>WO0000000307984</v>
       </c>
       <c r="B405" s="1" t="d">
-        <v>2026-07-16T08:34:04.000Z</v>
+        <v>2026-07-17T14:08:18.000Z</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>WO0000000308206</v>
+        <v>INC000000152339</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-16T08:34:04.000Z</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>WO0000000308218</v>
+        <v>WO0000000308206</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>WO0000000308157</v>
+        <v>WO0000000308218</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2026-07-17T13:56:08.000Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>WO0000000308163</v>
+        <v>WO0000000308157</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2026-07-16T09:05:24.000Z</v>
+        <v>2026-07-17T13:56:08.000Z</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>INC000000152358</v>
+        <v>WO0000000308163</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2026-07-16T09:12:05.999Z</v>
+        <v>2026-07-16T09:05:24.000Z</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>WO0000000308194</v>
+        <v>INC000000152358</v>
       </c>
       <c r="B411" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-16T09:12:05.999Z</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>WO0000000308255</v>
+        <v>WO0000000308194</v>
       </c>
       <c r="B412" s="1" t="d">
-        <v>2026-07-17T15:17:47.000Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>WO0000000308260</v>
+        <v>WO0000000308255</v>
       </c>
       <c r="B413" s="1" t="d">
-        <v>2026-07-21T08:56:50.000Z</v>
+        <v>2026-07-17T15:17:47.000Z</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>WO0000000308269</v>
+        <v>WO0000000308260</v>
       </c>
       <c r="B414" s="1" t="d">
-        <v>2026-07-21T09:19:51.000Z</v>
+        <v>2026-07-21T08:56:50.000Z</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>WO0000000308273</v>
+        <v>WO0000000308269</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2026-07-21T09:25:58.000Z</v>
+        <v>2026-07-21T09:19:51.000Z</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308284</v>
+        <v>WO0000000308273</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-16T08:08:24.000Z</v>
+        <v>2026-07-21T09:25:58.000Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308284</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-21T10:13:57.000Z</v>
+        <v>2026-07-16T08:08:24.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>WO0000000308340</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-16T09:24:24.999Z</v>
+        <v>2026-07-21T10:13:57.000Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>WO0000000308416</v>
+        <v>WO0000000308340</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-16T09:47:42.999Z</v>
+        <v>2026-07-16T09:24:24.999Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308432</v>
+        <v>WO0000000308416</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-21T08:34:03.000Z</v>
+        <v>2026-07-16T09:47:42.999Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308350</v>
+        <v>WO0000000308432</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T08:34:03.000Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308442</v>
+        <v>WO0000000308350</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-21T08:56:50.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308442</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-16T10:44:20.999Z</v>
+        <v>2026-07-21T08:56:50.000Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308360</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-16T12:54:40.000Z</v>
+        <v>2026-07-16T10:44:20.999Z</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>WO0000000308457</v>
+        <v>WO0000000308360</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2026-07-21T09:30:10.000Z</v>
+        <v>2026-07-16T12:54:40.000Z</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>WO0000000308366</v>
+        <v>WO0000000308457</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2026-07-16T09:45:50.999Z</v>
+        <v>2026-07-21T09:30:10.000Z</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>WO0000000308463</v>
+        <v>WO0000000308366</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2026-07-21T09:42:42.000Z</v>
+        <v>2026-07-16T09:45:50.999Z</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>WO0000000308374</v>
+        <v>WO0000000308463</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2026-07-21T09:55:06.000Z</v>
+        <v>2026-07-21T09:42:42.000Z</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>WO0000000308379</v>
+        <v>WO0000000308374</v>
       </c>
       <c r="B429" s="1" t="d">
-        <v>2026-07-15T17:07:55.000Z</v>
+        <v>2026-07-21T09:55:06.000Z</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>WO0000000308383</v>
+        <v>WO0000000308379</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2026-07-21T10:16:02.000Z</v>
+        <v>2026-07-15T17:07:55.000Z</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>WO0000000308398</v>
+        <v>WO0000000308383</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-16T08:57:27.000Z</v>
+        <v>2026-07-21T10:16:02.000Z</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>WO0000000308399</v>
+        <v>WO0000000308398</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-16T09:52:14.999Z</v>
+        <v>2026-07-16T08:57:27.000Z</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>WO0000000308487</v>
+        <v>WO0000000308399</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-15T22:21:47.000Z</v>
+        <v>2026-07-16T09:52:14.999Z</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>WO0000000308503</v>
+        <v>WO0000000308487</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-21T10:01:16.000Z</v>
+        <v>2026-07-15T22:21:47.000Z</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>WO0000000308493</v>
+        <v>WO0000000308503</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2026-07-21T10:16:04.000Z</v>
+        <v>2026-07-21T10:01:16.000Z</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>WO0000000308506</v>
+        <v>WO0000000308493</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-21T10:16:03.000Z</v>
+        <v>2026-07-21T10:16:04.000Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>INC000000152512</v>
+        <v>WO0000000308506</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-16T08:10:32.999Z</v>
+        <v>2026-07-21T10:16:03.000Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>INC000000152513</v>
+        <v>INC000000152512</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-16T09:23:02.000Z</v>
+        <v>2026-07-16T08:10:32.999Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>WO0000000308552</v>
+        <v>INC000000152513</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-16T09:20:55.000Z</v>
+        <v>2026-07-16T09:23:02.000Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>WO0000000308648</v>
+        <v>WO0000000308552</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-17T15:09:40.000Z</v>
+        <v>2026-07-16T09:20:55.000Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-16T09:22:57.000Z</v>
+        <v>2026-07-17T15:09:40.000Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-17T14:10:20.000Z</v>
+        <v>2026-07-16T09:22:57.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000308661</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-17T14:16:26.000Z</v>
+        <v>2026-07-17T14:10:20.000Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>WO0000000308673</v>
+        <v>WO0000000308661</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-16T10:02:00.999Z</v>
+        <v>2026-07-17T14:16:26.000Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>WO0000000308679</v>
+        <v>WO0000000308673</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-17T14:36:57.000Z</v>
+        <v>2026-07-16T10:02:00.999Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>WO0000000308675</v>
+        <v>WO0000000308679</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-17T07:31:47.000Z</v>
+        <v>2026-07-17T14:36:57.000Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>WO0000000308685</v>
+        <v>WO0000000308675</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-16T10:12:45.000Z</v>
+        <v>2026-07-17T07:31:47.000Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>WO0000000308596</v>
+        <v>WO0000000308685</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2026-07-16T10:19:52.000Z</v>
+        <v>2026-07-16T10:12:45.000Z</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>WO0000000308701</v>
+        <v>WO0000000308596</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-16T10:22:52.000Z</v>
+        <v>2026-07-16T10:19:52.000Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308701</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-17T11:22:11.000Z</v>
+        <v>2026-07-16T10:22:52.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>WO0000000308695</v>
+        <v>WO0000000308696</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-16T10:42:24.000Z</v>
+        <v>2026-07-17T11:22:11.000Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-16T10:40:08.000Z</v>
+        <v>2026-07-16T10:42:24.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WO0000000308715</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-16T10:40:08.000Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-21T10:45:16.999Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308717</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-16T10:46:41.000Z</v>
+        <v>2026-07-21T10:45:16.999Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>INC000000139655</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-17T07:37:37.999Z</v>
+        <v>2026-07-16T10:46:41.000Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>INC000000139903</v>
+        <v>INC000000139655</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-17T07:37:04.000Z</v>
+        <v>2026-07-17T07:37:37.999Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>INC000000140158</v>
+        <v>INC000000139903</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-17T07:37:04.000Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>INC000000140820</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-17T07:35:42.000Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>INC000000140821</v>
+        <v>INC000000140820</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-17T07:34:57.000Z</v>
+        <v>2026-07-17T07:35:42.000Z</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>INC000000140767</v>
+        <v>INC000000140821</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-17T07:34:57.000Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>INC000000141766</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-21T08:55:08.000Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>INC000000142421</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-17T07:33:48.000Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>INC000000142515</v>
+        <v>INC000000142421</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-17T07:33:05.000Z</v>
+        <v>2026-07-17T07:33:48.000Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>WO0000000288110</v>
+        <v>INC000000142515</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-17T07:47:10.000Z</v>
+        <v>2026-07-17T07:33:05.000Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>INC000000143401</v>
+        <v>WO0000000288110</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-17T07:32:06.000Z</v>
+        <v>2026-07-17T07:47:10.000Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>WO0000000292826</v>
+        <v>INC000000143401</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-17T07:30:34.000Z</v>
+        <v>2026-07-17T07:32:06.000Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>WO0000000295598</v>
+        <v>WO0000000292826</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-17T07:30:34.000Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>WO0000000295716</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-16T11:47:42.999Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>WO0000000295975</v>
+        <v>WO0000000295716</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-17T07:46:27.000Z</v>
+        <v>2026-07-16T11:47:42.999Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>INC000000146886</v>
+        <v>WO0000000295975</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-16T13:10:02.999Z</v>
+        <v>2026-07-17T07:46:27.000Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>WO0000000296722</v>
+        <v>INC000000146886</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-17T07:44:32.000Z</v>
+        <v>2026-07-16T13:10:02.999Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>WO0000000296723</v>
+        <v>WO0000000296722</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-17T07:43:42.999Z</v>
+        <v>2026-07-17T07:44:32.000Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>WO0000000297151</v>
+        <v>WO0000000296723</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-17T07:42:36.000Z</v>
+        <v>2026-07-17T07:43:42.999Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>WO0000000297156</v>
+        <v>WO0000000297151</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-17T07:41:50.000Z</v>
+        <v>2026-07-17T07:42:36.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000297160</v>
+        <v>WO0000000297156</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-17T07:40:23.999Z</v>
+        <v>2026-07-17T07:41:50.000Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>WO0000000298838</v>
+        <v>WO0000000297160</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-20T23:28:38.000Z</v>
+        <v>2026-07-17T07:40:23.999Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>WO0000000299920</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-17T14:59:50.999Z</v>
+        <v>2026-07-20T23:28:38.000Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000300081</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-17T14:59:50.999Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>INC000000148888</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>WO0000000300496</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-17T11:43:57.000Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WO0000000302331</v>
+        <v>WO0000000300496</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-17T12:11:40.000Z</v>
+        <v>2026-07-17T11:43:57.000Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WO0000000302520</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-17T15:04:39.000Z</v>
+        <v>2026-07-17T12:11:40.000Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>INC000000149827</v>
+        <v>WO0000000302520</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-17T14:03:04.000Z</v>
+        <v>2026-07-17T15:04:39.000Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>INC000000149757</v>
+        <v>INC000000149827</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-16T16:04:01.999Z</v>
+        <v>2026-07-17T14:03:04.000Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>INC000000149760</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-17T07:52:31.999Z</v>
+        <v>2026-07-16T16:04:01.999Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>WO0000000303117</v>
+        <v>INC000000149760</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-21T10:43:30.000Z</v>
+        <v>2026-07-17T07:52:31.999Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WO0000000303120</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-17T07:38:45.000Z</v>
+        <v>2026-07-21T10:43:30.000Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000303120</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-17T15:09:03.000Z</v>
+        <v>2026-07-17T07:38:45.000Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>WO0000000303244</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-17T15:04:54.000Z</v>
+        <v>2026-07-17T15:09:03.000Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>WO0000000303459</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-17T11:09:28.999Z</v>
+        <v>2026-07-17T15:04:54.000Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>WO0000000303471</v>
+        <v>WO0000000303459</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-16T14:24:05.000Z</v>
+        <v>2026-07-17T11:09:28.999Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000303471</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-16T12:40:48.000Z</v>
+        <v>2026-07-16T14:24:05.000Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-17T10:37:05.000Z</v>
+        <v>2026-07-16T12:40:48.000Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-17T10:37:33.000Z</v>
+        <v>2026-07-17T10:37:05.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>WO0000000305131</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-21T08:46:39.000Z</v>
+        <v>2026-07-17T10:37:33.000Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>WO0000000305138</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-21T08:46:39.000Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>INC000000150748</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-21T10:15:45.000Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>WO0000000305336</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-21T10:15:45.000Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>INC000000150916</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-17T13:59:57.999Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000150916</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-17T18:15:37.999Z</v>
+        <v>2026-07-17T13:59:57.999Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>INC000000151036</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-16T16:01:20.999Z</v>
+        <v>2026-07-17T18:15:37.999Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>INC000000150958</v>
+        <v>INC000000151036</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-17T07:47:57.999Z</v>
+        <v>2026-07-16T16:01:20.999Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>WO0000000305863</v>
+        <v>INC000000150958</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-21T08:44:19.000Z</v>
+        <v>2026-07-17T07:47:57.999Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>WO0000000305877</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-16T16:12:20.000Z</v>
+        <v>2026-07-21T08:44:19.000Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>WO0000000305769</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-17T10:37:57.000Z</v>
+        <v>2026-07-16T16:12:20.000Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>WO0000000305770</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-17T11:07:27.000Z</v>
+        <v>2026-07-17T10:37:57.000Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>INC000000151203</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-17T11:07:27.000Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>WO0000000306127</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-21T07:40:38.000Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>INC000000151157</v>
+        <v>WO0000000306127</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-17T19:09:33.000Z</v>
+        <v>2026-07-21T07:40:38.000Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>INC000000151271</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-17T07:40:02.000Z</v>
+        <v>2026-07-21T10:59:03.000Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>WO0000000306256</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-17T14:41:03.000Z</v>
+        <v>2026-07-17T07:40:02.000Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>INC000000151313</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-17T14:41:03.000Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>WO0000000306718</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-17T10:39:36.000Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>WO0000000306721</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-17T15:11:14.000Z</v>
+        <v>2026-07-17T10:39:36.000Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>WO0000000306726</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-17T10:39:57.000Z</v>
+        <v>2026-07-17T15:11:14.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>INC000000151512</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-21T09:41:08.000Z</v>
+        <v>2026-07-17T10:39:57.000Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>WO0000000306799</v>
+        <v>INC000000151512</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-17T08:21:12.999Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-17T19:07:47.000Z</v>
+        <v>2026-07-17T08:21:12.999Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>INC000000151527</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-17T16:34:54.000Z</v>
+        <v>2026-07-17T19:07:47.000Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>WO0000000306927</v>
+        <v>INC000000151527</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-17T16:34:54.000Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-17T17:20:58.999Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>WO0000000306877</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-16T14:55:04.000Z</v>
+        <v>2026-07-17T17:20:58.999Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>WO0000000306890</v>
+        <v>WO0000000306877</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-16T14:55:04.000Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000306899</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-21T10:02:55.000Z</v>
+        <v>2026-07-17T14:42:13.999Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000306988</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-21T09:13:38.000Z</v>
+        <v>2026-07-21T10:02:55.000Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>WO0000000306994</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-16T15:19:33.999Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>INC000000151586</v>
+        <v>WO0000000306994</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-19T12:57:49.000Z</v>
+        <v>2026-07-16T15:19:33.999Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>WO0000000307224</v>
+        <v>INC000000151586</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-16T16:04:39.999Z</v>
+        <v>2026-07-19T12:57:49.000Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000307224</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-17T14:49:17.000Z</v>
+        <v>2026-07-16T16:04:39.999Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>INC000000151764</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-21T09:41:12.000Z</v>
+        <v>2026-07-17T14:49:17.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>WO0000000307513</v>
+        <v>INC000000151764</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-21T10:03:23.000Z</v>
+        <v>2026-07-21T09:41:12.000Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-21T10:03:23.000Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>INC000000151987</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-16T11:05:28.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>WO0000000307483</v>
+        <v>INC000000151987</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-21T09:13:03.000Z</v>
+        <v>2026-07-16T11:05:28.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-21T10:01:17.000Z</v>
+        <v>2026-07-21T09:13:03.000Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-17T16:21:08.000Z</v>
+        <v>2026-07-21T10:01:17.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>INC000000152000</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-19T12:58:45.000Z</v>
+        <v>2026-07-17T16:21:08.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000152000</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-19T12:58:45.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>INC000000152045</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-16T10:52:09.000Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="542">
@@ -5222,7 +5222,7 @@
         <v>WO0000000308727</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-17T09:34:42.000Z</v>
+        <v>2026-07-21T10:49:39.999Z</v>
       </c>
     </row>
     <row r="604">
@@ -5251,4892 +5251,4932 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>WO0000000308814</v>
+        <v>WO0000000308816</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-17T15:46:22.000Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>WO0000000308742</v>
+        <v>WO0000000308743</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-17T15:54:32.000Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>WO0000000308816</v>
+        <v>INC000000152477</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-16T12:12:43.000Z</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>WO0000000308743</v>
+        <v>WO0000000308750</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-07-17T15:54:32.000Z</v>
+        <v>2026-07-17T16:02:36.000Z</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>INC000000152477</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-07-16T12:12:43.000Z</v>
+        <v>2026-07-17T08:38:07.000Z</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>WO0000000308750</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-07-17T16:02:36.000Z</v>
+        <v>2026-07-16T14:25:41.000Z</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000308755</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-07-17T08:38:07.000Z</v>
+        <v>2026-07-16T11:35:09.000Z</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>WO0000000308754</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-07-16T14:25:41.000Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>WO0000000308755</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-07-16T11:35:09.000Z</v>
+        <v>2026-07-21T09:29:46.000Z</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000308851</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-17T16:37:20.999Z</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>WO0000000308834</v>
+        <v>INC000000152486</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-07-21T09:29:46.000Z</v>
+        <v>2026-07-21T07:42:45.999Z</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>WO0000000308851</v>
+        <v>WO0000000308860</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-07-17T16:37:20.999Z</v>
+        <v>2026-07-17T16:51:40.000Z</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>INC000000152486</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-07-21T07:42:45.999Z</v>
+        <v>2026-07-21T10:54:29.000Z</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>WO0000000308860</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-07-17T16:51:40.000Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000308868</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-07-21T08:00:16.000Z</v>
+        <v>2026-07-21T08:27:45.999Z</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>INC000000152586</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-07-17T10:46:28.000Z</v>
+        <v>2026-07-16T14:39:36.999Z</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>WO0000000308868</v>
+        <v>INC000000152496</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-07-21T08:27:45.999Z</v>
+        <v>2026-07-17T18:33:44.000Z</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>WO0000000308873</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-07-16T14:39:36.999Z</v>
+        <v>2026-07-21T10:58:56.000Z</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>INC000000152496</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-07-17T18:33:44.000Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>WO0000000308794</v>
+        <v>INC000000152594</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-07-17T09:53:56.000Z</v>
+        <v>2026-07-20T13:46:11.000Z</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>INC000000152591</v>
+        <v>WO0000000308905</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-07-17T11:00:29.999Z</v>
+        <v>2026-07-21T09:36:24.000Z</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>INC000000152594</v>
+        <v>WO0000000308880</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-07-20T13:46:11.000Z</v>
+        <v>2026-07-21T09:38:28.000Z</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>WO0000000308905</v>
+        <v>WO0000000308917</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-07-21T09:36:24.000Z</v>
+        <v>2026-07-17T07:59:19.999Z</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>WO0000000308880</v>
+        <v>WO0000000308918</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-07-21T09:38:28.000Z</v>
+        <v>2026-07-21T10:05:26.000Z</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>WO0000000308917</v>
+        <v>WO0000000308919</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-07-17T07:59:19.999Z</v>
+        <v>2026-07-21T10:07:31.000Z</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>WO0000000308918</v>
+        <v>WO0000000308923</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-07-21T10:05:26.000Z</v>
+        <v>2026-07-21T09:17:59.000Z</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>WO0000000308919</v>
+        <v>INC000000152608</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-07-21T10:07:31.000Z</v>
+        <v>2026-07-21T10:28:55.000Z</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>WO0000000308923</v>
+        <v>WO0000000308895</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-07-21T09:17:59.000Z</v>
+        <v>2026-07-17T10:35:42.000Z</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>INC000000152608</v>
+        <v>WO0000000308896</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-07-21T10:28:55.000Z</v>
+        <v>2026-07-21T10:24:24.000Z</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>WO0000000308895</v>
+        <v>WO0000000309001</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-07-17T10:35:42.000Z</v>
+        <v>2026-07-21T10:26:28.000Z</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>WO0000000308896</v>
+        <v>WO0000000309004</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-07-21T10:24:24.000Z</v>
+        <v>2026-07-21T10:26:28.000Z</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>WO0000000309001</v>
+        <v>WO0000000308899</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-07-21T10:26:28.000Z</v>
+        <v>2026-07-21T10:49:36.000Z</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>WO0000000309004</v>
+        <v>WO0000000308926</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-07-21T10:26:28.000Z</v>
+        <v>2026-07-17T10:04:52.000Z</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>WO0000000308899</v>
+        <v>WO0000000309009</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-07-16T15:17:36.000Z</v>
+        <v>2026-07-21T10:34:42.000Z</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>WO0000000308926</v>
+        <v>WO0000000309002</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-07-17T10:04:52.000Z</v>
+        <v>2026-07-16T15:07:58.000Z</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>WO0000000309007</v>
+        <v>WO0000000309011</v>
       </c>
       <c r="B642" s="1" t="d">
-        <v>2026-07-21T10:47:08.000Z</v>
+        <v>2026-07-17T10:44:02.999Z</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>WO0000000309009</v>
+        <v>INC000000152616</v>
       </c>
       <c r="B643" s="1" t="d">
-        <v>2026-07-21T10:34:42.000Z</v>
+        <v>2026-07-17T09:51:34.000Z</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>WO0000000309002</v>
+        <v>WO0000000308938</v>
       </c>
       <c r="B644" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-16T15:31:18.000Z</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>WO0000000309011</v>
+        <v>WO0000000309018</v>
       </c>
       <c r="B645" s="1" t="d">
-        <v>2026-07-17T10:44:02.999Z</v>
+        <v>2026-07-21T11:01:58.000Z</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>INC000000152616</v>
+        <v>WO0000000309021</v>
       </c>
       <c r="B646" s="1" t="d">
-        <v>2026-07-17T09:51:34.000Z</v>
+        <v>2026-07-17T09:59:10.000Z</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>WO0000000308938</v>
+        <v>INC000000152711</v>
       </c>
       <c r="B647" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-16T16:04:14.000Z</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>WO0000000309018</v>
+        <v>WO0000000309024</v>
       </c>
       <c r="B648" s="1" t="d">
-        <v>2026-07-16T15:30:08.999Z</v>
+        <v>2026-07-16T15:43:10.000Z</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>WO0000000309021</v>
+        <v>WO0000000308947</v>
       </c>
       <c r="B649" s="1" t="d">
-        <v>2026-07-17T09:59:10.000Z</v>
+        <v>2026-07-21T10:45:27.000Z</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>INC000000152711</v>
+        <v>WO0000000309026</v>
       </c>
       <c r="B650" s="1" t="d">
-        <v>2026-07-16T16:04:14.000Z</v>
+        <v>2026-07-16T15:49:08.000Z</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>WO0000000309024</v>
+        <v>WO0000000309025</v>
       </c>
       <c r="B651" s="1" t="d">
-        <v>2026-07-16T15:43:10.000Z</v>
+        <v>2026-07-16T15:47:35.000Z</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>WO0000000308947</v>
+        <v>WO0000000309028</v>
       </c>
       <c r="B652" s="1" t="d">
-        <v>2026-07-21T10:45:27.000Z</v>
+        <v>2026-07-21T10:48:23.000Z</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>WO0000000309026</v>
+        <v>WO0000000309031</v>
       </c>
       <c r="B653" s="1" t="d">
-        <v>2026-07-16T15:49:08.000Z</v>
+        <v>2026-07-16T15:52:24.000Z</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>WO0000000309025</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B654" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-17T16:59:46.000Z</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>WO0000000309028</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B655" s="1" t="d">
-        <v>2026-07-17T15:14:51.999Z</v>
+        <v>2026-07-16T16:05:14.000Z</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000309039</v>
       </c>
       <c r="B656" s="1" t="d">
-        <v>2026-07-16T15:52:24.000Z</v>
+        <v>2026-07-17T08:39:45.999Z</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B657" s="1" t="d">
-        <v>2026-07-17T16:59:46.000Z</v>
+        <v>2026-07-17T16:15:11.000Z</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>WO0000000309036</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B658" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B659" s="1" t="d">
-        <v>2026-07-17T08:39:45.999Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B660" s="1" t="d">
-        <v>2026-07-17T16:15:11.000Z</v>
+        <v>2026-07-18T14:29:17.000Z</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>INC000000152628</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B661" s="1" t="d">
-        <v>2026-07-17T10:44:38.000Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>WO0000000309041</v>
+        <v>WO0000000308967</v>
       </c>
       <c r="B662" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-21T10:04:47.000Z</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>WO0000000308965</v>
+        <v>INC000000152630</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-18T14:29:17.000Z</v>
+        <v>2026-07-21T07:35:42.000Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>WO0000000308966</v>
+        <v>WO0000000309044</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-16T16:26:35.999Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000308967</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-21T10:04:47.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>INC000000152630</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-21T07:35:42.000Z</v>
+        <v>2026-07-16T16:32:21.000Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000309047</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-16T16:26:35.999Z</v>
+        <v>2026-07-16T16:37:18.000Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000308970</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-16T16:38:04.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-16T16:32:21.000Z</v>
+        <v>2026-07-16T16:43:04.000Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>WO0000000309047</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-16T16:37:18.000Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>WO0000000308970</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-16T16:38:04.000Z</v>
+        <v>2026-07-17T07:16:12.000Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000308975</v>
+        <v>WO0000000309052</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-16T16:43:04.000Z</v>
+        <v>2026-07-21T10:20:14.999Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>WO0000000309050</v>
+        <v>WO0000000308984</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-16T17:10:27.000Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000309060</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-17T07:16:12.000Z</v>
+        <v>2026-07-16T22:04:20.000Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000309052</v>
+        <v>WO0000000309062</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-21T10:20:14.999Z</v>
+        <v>2026-07-17T10:25:11.000Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>WO0000000308984</v>
+        <v>WO0000000309063</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-16T17:10:27.000Z</v>
+        <v>2026-07-16T17:31:20.000Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>WO0000000309060</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-16T22:04:20.000Z</v>
+        <v>2026-07-21T07:53:18.000Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>WO0000000309062</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-17T10:25:11.000Z</v>
+        <v>2026-07-16T19:52:29.999Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>WO0000000309063</v>
+        <v>WO0000000305262</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-16T17:31:20.000Z</v>
+        <v>2026-07-17T07:53:28.999Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-21T07:53:18.000Z</v>
+        <v>2026-07-16T19:32:50.000Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>WO0000000308987</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-16T19:52:29.999Z</v>
+        <v>2026-07-21T07:53:32.000Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>WO0000000305262</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-17T07:53:28.999Z</v>
+        <v>2026-07-16T19:42:22.000Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000309073</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-16T19:32:50.000Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>INC000000152643</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-21T07:53:32.000Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-16T19:42:22.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>WO0000000309077</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>WO0000000309079</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-17T10:15:24.000Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000309082</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T09:36:16.000Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>WO0000000308997</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>WO0000000308999</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-17T10:15:24.000Z</v>
+        <v>2026-07-17T06:53:11.000Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>WO0000000309082</v>
+        <v>INC000000152653</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-17T09:36:16.000Z</v>
+        <v>2026-07-18T16:16:07.999Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309097</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-17T08:03:06.999Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>INC000000152733</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-17T08:06:35.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>INC000000152653</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-18T16:16:07.999Z</v>
+        <v>2026-07-17T07:45:37.999Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>WO0000000309097</v>
+        <v>INC000000152739</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-17T08:03:06.999Z</v>
+        <v>2026-07-17T09:20:05.999Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>INC000000152737</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-17T08:06:35.000Z</v>
+        <v>2026-07-17T08:07:23.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000309124</v>
+        <v>WO0000000309131</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-17T07:45:37.999Z</v>
+        <v>2026-07-17T08:12:37.000Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>INC000000152739</v>
+        <v>WO0000000309212</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-17T09:20:05.999Z</v>
+        <v>2026-07-17T15:11:51.000Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-17T08:07:23.000Z</v>
+        <v>2026-07-21T09:04:31.000Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>WO0000000309131</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-17T08:12:37.000Z</v>
+        <v>2026-07-17T11:36:59.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>WO0000000309212</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-17T15:11:51.000Z</v>
+        <v>2026-07-17T12:44:26.000Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>WO0000000309136</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-21T09:04:31.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000152746</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-17T11:36:59.000Z</v>
+        <v>2026-07-21T09:47:10.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>INC000000152663</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-17T12:44:26.000Z</v>
+        <v>2026-07-17T08:54:14.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>INC000000152664</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T08:54:36.999Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>INC000000152746</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-21T09:47:10.000Z</v>
+        <v>2026-07-18T12:40:15.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309226</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-17T08:54:14.000Z</v>
+        <v>2026-07-17T08:58:32.999Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>WO0000000309155</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-17T08:54:36.999Z</v>
+        <v>2026-07-21T10:52:02.000Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>INC000000152668</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-18T12:40:15.000Z</v>
+        <v>2026-07-17T09:57:18.999Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>WO0000000309226</v>
+        <v>INC000000152673</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-17T08:58:32.999Z</v>
+        <v>2026-07-21T08:52:59.000Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>WO0000000309231</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-17T14:29:04.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>INC000000152673</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-21T08:52:59.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-17T14:47:59.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-17T09:26:58.999Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-21T10:42:34.000Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>WO0000000309164</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-17T14:47:59.000Z</v>
+        <v>2026-07-17T15:50:55.000Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309246</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-17T09:26:58.999Z</v>
+        <v>2026-07-17T09:32:32.000Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>INC000000152678</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-21T10:42:34.000Z</v>
+        <v>2026-07-17T09:36:30.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>INC000000152679</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-17T15:50:55.000Z</v>
+        <v>2026-07-17T09:37:50.000Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000309246</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B721" s="1" t="d">
-        <v>2026-07-17T09:32:32.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>WO0000000309168</v>
+        <v>WO0000000309249</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-17T09:36:30.000Z</v>
+        <v>2026-07-17T09:38:10.000Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-17T09:37:50.000Z</v>
+        <v>2026-07-21T10:04:01.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>WO0000000309172</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-21T08:45:24.000Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000309249</v>
+        <v>WO0000000309251</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-17T09:40:19.000Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>WO0000000309250</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-21T10:04:01.000Z</v>
+        <v>2026-07-21T08:17:56.000Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>INC000000152760</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-21T08:45:24.000Z</v>
+        <v>2026-07-17T09:57:50.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>WO0000000309251</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-17T09:40:19.000Z</v>
+        <v>2026-07-17T11:14:20.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-21T08:17:56.000Z</v>
+        <v>2026-07-17T14:47:53.999Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-17T09:57:50.000Z</v>
+        <v>2026-07-17T11:11:39.000Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-17T11:14:20.000Z</v>
+        <v>2026-07-17T11:15:36.000Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-17T14:47:53.999Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-17T11:11:39.000Z</v>
+        <v>2026-07-17T11:13:13.000Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>WO0000000309189</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-17T11:15:36.000Z</v>
+        <v>2026-07-21T09:55:04.000Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>WO0000000309258</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-17T10:18:38.000Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>WO0000000309259</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-17T11:13:13.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152770</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-21T09:55:04.000Z</v>
+        <v>2026-07-17T10:27:03.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>WO0000000309262</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-17T10:18:38.000Z</v>
+        <v>2026-07-17T11:24:41.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>INC000000152690</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-21T10:45:43.999Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>INC000000152770</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-17T10:27:03.000Z</v>
+        <v>2026-07-21T10:37:55.000Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>WO0000000309195</v>
+        <v>INC000000152691</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-17T11:24:41.000Z</v>
+        <v>2026-07-17T11:21:16.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>INC000000152772</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-21T10:45:43.999Z</v>
+        <v>2026-07-17T12:51:35.000Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>INC000000152774</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-21T10:37:55.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>INC000000152691</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-17T11:21:16.000Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>WO0000000309199</v>
+        <v>WO0000000309269</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-17T12:51:35.000Z</v>
+        <v>2026-07-21T10:34:42.000Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>WO0000000309200</v>
+        <v>WO0000000309270</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-17T16:48:27.000Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-17T14:48:08.000Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>WO0000000309269</v>
+        <v>INC000000152694</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-21T10:34:42.000Z</v>
+        <v>2026-07-18T13:02:06.999Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>WO0000000309270</v>
+        <v>WO0000000309407</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-17T16:48:27.000Z</v>
+        <v>2026-07-17T10:43:38.999Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>WO0000000309271</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-17T14:48:08.000Z</v>
+        <v>2026-07-19T12:51:55.999Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>INC000000152694</v>
+        <v>WO0000000309409</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-18T13:02:06.999Z</v>
+        <v>2026-07-21T10:47:34.000Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>WO0000000309407</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-21T09:07:41.000Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>INC000000152777</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-19T12:51:55.999Z</v>
+        <v>2026-07-17T10:48:35.999Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>WO0000000309409</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-21T10:47:34.000Z</v>
+        <v>2026-07-17T10:53:18.000Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-21T09:07:41.000Z</v>
+        <v>2026-07-17T12:28:53.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-17T10:48:35.999Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-17T10:53:18.000Z</v>
+        <v>2026-07-17T10:58:23.000Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309285</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-17T12:28:53.000Z</v>
+        <v>2026-07-17T10:57:51.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>WO0000000309282</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-21T10:46:30.999Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309417</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-17T10:58:23.000Z</v>
+        <v>2026-07-17T11:02:34.000Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>WO0000000309285</v>
+        <v>INC000000152700</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-17T10:57:51.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>INC000000152802</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-21T10:46:30.999Z</v>
+        <v>2026-07-18T08:52:20.999Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309417</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-17T11:02:34.000Z</v>
+        <v>2026-07-17T11:12:43.000Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>INC000000152700</v>
+        <v>INC000000152784</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-17T11:26:12.000Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-18T08:52:20.999Z</v>
+        <v>2026-07-17T11:15:48.000Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-17T11:12:43.000Z</v>
+        <v>2026-07-17T11:17:12.999Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>INC000000152784</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-17T11:26:12.000Z</v>
+        <v>2026-07-17T14:48:17.000Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-17T11:15:48.000Z</v>
+        <v>2026-07-17T11:21:58.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-17T11:17:12.999Z</v>
+        <v>2026-07-21T09:14:29.000Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309432</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-17T14:48:17.000Z</v>
+        <v>2026-07-17T11:29:50.000Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-17T11:21:58.000Z</v>
+        <v>2026-07-17T11:26:05.999Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309299</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-21T09:14:29.000Z</v>
+        <v>2026-07-17T11:28:13.000Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309432</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-17T11:29:50.000Z</v>
+        <v>2026-07-21T10:21:20.000Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>WO0000000309433</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-17T11:26:05.999Z</v>
+        <v>2026-07-21T09:27:50.000Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>WO0000000309299</v>
+        <v>WO0000000309439</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-17T11:28:13.000Z</v>
+        <v>2026-07-17T11:59:55.999Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-21T10:21:20.000Z</v>
+        <v>2026-07-17T15:38:05.000Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>WO0000000309438</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-21T09:27:50.000Z</v>
+        <v>2026-07-21T10:37:25.999Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>WO0000000309439</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-17T11:59:55.999Z</v>
+        <v>2026-07-21T10:55:04.000Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>WO0000000309503</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-17T15:38:05.000Z</v>
+        <v>2026-07-17T11:41:41.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>INC000000152789</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-21T10:37:25.999Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-21T10:43:09.999Z</v>
+        <v>2026-07-17T15:32:46.000Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309444</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-17T11:41:41.000Z</v>
+        <v>2026-07-17T11:41:48.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-21T10:23:15.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>WO0000000309441</v>
+        <v>INC000000152810</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-17T15:32:46.000Z</v>
+        <v>2026-07-21T07:51:23.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>WO0000000309444</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-17T11:41:48.000Z</v>
+        <v>2026-07-17T11:53:25.999Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000309447</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-21T10:23:15.000Z</v>
+        <v>2026-07-21T08:25:47.000Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>INC000000152810</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-21T07:51:23.000Z</v>
+        <v>2026-07-21T10:24:15.999Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-17T11:53:25.999Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-21T08:25:47.000Z</v>
+        <v>2026-07-17T14:48:03.000Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-21T10:24:15.999Z</v>
+        <v>2026-07-17T15:45:57.000Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>WO0000000309513</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T14:48:13.000Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>WO0000000309454</v>
+        <v>INC000000152797</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-17T14:48:03.000Z</v>
+        <v>2026-07-21T08:59:18.000Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-17T15:45:57.000Z</v>
+        <v>2026-07-18T08:52:31.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>WO0000000309457</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-17T14:48:13.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>INC000000152797</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-21T08:59:18.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-18T08:52:31.000Z</v>
+        <v>2026-07-17T12:23:35.999Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>WO0000000309514</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>WO0000000309462</v>
+        <v>INC000000152901</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-21T10:47:15.000Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000309465</v>
+        <v>WO0000000309466</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-17T12:23:35.999Z</v>
+        <v>2026-07-21T10:22:48.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>WO0000000309520</v>
+        <v>WO0000000309525</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-17T16:15:45.000Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>INC000000152901</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-21T10:47:15.000Z</v>
+        <v>2026-07-17T17:44:41.000Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000309466</v>
+        <v>WO0000000309526</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-21T10:22:48.000Z</v>
+        <v>2026-07-21T08:25:19.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000309525</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-17T16:15:45.000Z</v>
+        <v>2026-07-21T09:11:31.000Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>INC000000152903</v>
+        <v>INC000000152814</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-17T17:44:41.000Z</v>
+        <v>2026-07-17T12:49:52.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>WO0000000309526</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-21T08:25:19.000Z</v>
+        <v>2026-07-21T10:47:55.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309470</v>
+        <v>WO0000000309478</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-21T09:11:31.000Z</v>
+        <v>2026-07-17T15:55:47.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>INC000000152814</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-17T12:49:52.000Z</v>
+        <v>2026-07-17T12:55:06.999Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309534</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-20T13:33:22.000Z</v>
+        <v>2026-07-17T13:00:45.000Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>WO0000000309478</v>
+        <v>INC000000152910</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-17T15:55:47.000Z</v>
+        <v>2026-07-21T07:51:47.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>WO0000000309479</v>
+        <v>INC000000152815</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-17T12:55:06.999Z</v>
+        <v>2026-07-17T21:20:43.999Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>WO0000000309534</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-17T13:00:45.000Z</v>
+        <v>2026-07-17T15:49:27.999Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>INC000000152910</v>
+        <v>WO0000000309488</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-21T07:51:47.000Z</v>
+        <v>2026-07-17T13:20:57.999Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>INC000000152815</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-17T21:20:43.999Z</v>
+        <v>2026-07-21T08:46:11.000Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>WO0000000309489</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-17T15:49:27.999Z</v>
+        <v>2026-07-18T01:16:50.999Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000309488</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-17T13:20:57.999Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>INC000000152914</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-21T08:46:11.000Z</v>
+        <v>2026-07-21T10:39:57.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>INC000000152913</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-18T01:16:50.999Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>WO0000000309487</v>
+        <v>WO0000000309545</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-21T07:54:44.000Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>INC000000152915</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-18T12:02:15.999Z</v>
+        <v>2026-07-18T01:16:05.000Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000309497</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-21T10:39:57.000Z</v>
+        <v>2026-07-17T14:11:39.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>WO0000000309499</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-21T10:46:28.000Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000309545</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-21T07:54:44.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>INC000000152919</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-18T01:16:05.000Z</v>
+        <v>2026-07-17T15:55:02.000Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>WO0000000309546</v>
+        <v>INC000000152922</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-21T07:10:12.000Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>INC000000152824</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-21T10:46:28.000Z</v>
+        <v>2026-07-17T14:30:26.000Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>INC000000152921</v>
+        <v>INC000000152828</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T14:45:48.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>WO0000000309603</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-17T15:55:02.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>INC000000152922</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-21T07:10:12.000Z</v>
+        <v>2026-07-21T10:51:05.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000309549</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-17T14:30:26.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>INC000000152828</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-17T14:45:48.000Z</v>
+        <v>2026-07-17T14:57:05.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>WO0000000309551</v>
+        <v>INC000000152927</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-17T15:58:26.000Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>WO0000000309609</v>
+        <v>WO0000000309613</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-19T00:08:20.000Z</v>
+        <v>2026-07-17T15:01:59.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000309553</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309559</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-17T14:57:05.000Z</v>
+        <v>2026-07-17T15:56:29.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>INC000000152927</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-17T15:58:26.000Z</v>
+        <v>2026-07-18T08:45:42.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>WO0000000309613</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-17T15:01:59.000Z</v>
+        <v>2026-07-17T15:57:48.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>WO0000000309558</v>
+        <v>INC000000152931</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-21T08:13:12.000Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>WO0000000309559</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-17T15:56:29.000Z</v>
+        <v>2026-07-17T15:20:43.999Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309563</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-18T08:45:42.000Z</v>
+        <v>2026-07-17T15:24:26.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000309616</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-17T15:57:48.000Z</v>
+        <v>2026-07-18T11:14:25.000Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-21T08:13:12.000Z</v>
+        <v>2026-07-17T16:04:00.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-17T15:31:50.999Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>WO0000000309563</v>
+        <v>WO0000000309572</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-21T08:34:49.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>INC000000152933</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-18T11:14:25.000Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-17T16:04:00.000Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000309572</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-21T08:34:49.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-21T10:39:19.000Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000309574</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-17T16:25:00.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-18T06:53:20.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>WO0000000309626</v>
+        <v>WO0000000309635</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-21T10:39:19.000Z</v>
+        <v>2026-07-17T16:06:26.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000309627</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-17T16:25:00.000Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>WO0000000309629</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-18T06:53:20.000Z</v>
+        <v>2026-07-21T10:08:02.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>WO0000000309632</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>WO0000000309635</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-17T16:06:26.000Z</v>
+        <v>2026-07-17T17:05:49.000Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-18T06:19:47.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>WO0000000309636</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-21T10:08:02.000Z</v>
+        <v>2026-07-17T16:39:05.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>INC000000152838</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-18T12:55:19.000Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309587</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-17T17:05:49.000Z</v>
+        <v>2026-07-17T16:39:17.000Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>WO0000000309641</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-18T06:19:47.000Z</v>
+        <v>2026-07-18T07:38:46.000Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>WO0000000309586</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-17T16:39:05.000Z</v>
+        <v>2026-07-18T13:55:17.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000152945</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-18T12:55:19.000Z</v>
+        <v>2026-07-17T16:53:07.000Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000309587</v>
+        <v>WO0000000309643</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-17T16:39:17.000Z</v>
+        <v>2026-07-17T16:52:17.999Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>INC000000152944</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-18T07:38:46.000Z</v>
+        <v>2026-07-21T10:09:45.000Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>WO0000000309589</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-18T13:55:17.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>INC000000152945</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-17T16:53:07.000Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>WO0000000309643</v>
+        <v>WO0000000309648</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-17T16:52:17.999Z</v>
+        <v>2026-07-17T18:19:50.000Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>WO0000000309592</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-21T10:09:45.000Z</v>
+        <v>2026-07-21T09:50:43.000Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309308</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-21T07:44:56.000Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>WO0000000309647</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-21T09:05:18.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000309648</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-17T18:19:50.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309655</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-21T09:50:43.000Z</v>
+        <v>2026-07-21T09:15:18.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>WO0000000309308</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-21T07:44:56.000Z</v>
+        <v>2026-07-21T10:23:48.000Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000309595</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-21T09:07:50.999Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>WO0000000309596</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-21T09:27:02.000Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>WO0000000309655</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-21T09:15:18.000Z</v>
+        <v>2026-07-21T10:28:49.000Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>WO0000000309597</v>
+        <v>INC000000152846</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-21T10:23:48.000Z</v>
+        <v>2026-07-17T17:43:39.999Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>WO0000000309309</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-21T09:07:50.999Z</v>
+        <v>2026-07-21T09:12:25.000Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>INC000000152948</v>
+        <v>INC000000152950</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-21T09:27:02.000Z</v>
+        <v>2026-07-21T09:49:56.000Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>INC000000152845</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-21T10:28:49.000Z</v>
+        <v>2026-07-17T18:11:18.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>INC000000152846</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-17T17:43:39.999Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>WO0000000309310</v>
+        <v>WO0000000309598</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-21T09:12:25.000Z</v>
+        <v>2026-07-21T08:16:54.999Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>INC000000152950</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-21T09:49:56.000Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>INC000000152848</v>
+        <v>WO0000000309600</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-21T07:30:44.000Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309659</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>WO0000000309598</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-21T08:16:54.999Z</v>
+        <v>2026-07-21T10:32:14.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000309599</v>
+        <v>WO0000000309705</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-17T18:22:25.999Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>WO0000000309600</v>
+        <v>WO0000000309707</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-21T07:30:44.000Z</v>
+        <v>2026-07-21T08:26:12.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>WO0000000309659</v>
+        <v>WO0000000309660</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-17T18:27:35.999Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>WO0000000309704</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-21T10:32:14.000Z</v>
+        <v>2026-07-21T09:27:40.000Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>WO0000000309705</v>
+        <v>INC000000152954</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-17T18:22:25.999Z</v>
+        <v>2026-07-18T10:44:32.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>WO0000000309707</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-21T08:26:12.000Z</v>
+        <v>2026-07-21T09:28:09.000Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000309660</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-17T18:27:35.999Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>INC000000152953</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-21T09:27:40.000Z</v>
+        <v>2026-07-18T09:16:52.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>WO0000000309661</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-21T09:05:58.999Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>INC000000152954</v>
+        <v>INC000000152957</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-18T10:44:32.000Z</v>
+        <v>2026-07-18T11:15:19.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>INC000000152955</v>
+        <v>INC000000152854</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-21T09:28:09.000Z</v>
+        <v>2026-07-17T21:32:15.999Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>WO0000000309664</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>INC000000152956</v>
+        <v>WO0000000309667</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-18T09:16:52.000Z</v>
+        <v>2026-07-21T07:08:18.000Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>WO0000000309666</v>
+        <v>WO0000000309668</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-21T09:29:44.000Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>INC000000152957</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-18T11:15:19.000Z</v>
+        <v>2026-07-21T07:55:12.000Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>INC000000152958</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-21T10:46:25.000Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>INC000000152854</v>
+        <v>INC000000152863</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-17T21:32:15.999Z</v>
+        <v>2026-07-18T11:32:43.000Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>WO0000000309714</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-18T11:57:16.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000309667</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-21T07:08:18.000Z</v>
+        <v>2026-07-21T09:18:02.999Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>WO0000000309668</v>
+        <v>INC000000152869</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-21T09:29:44.000Z</v>
+        <v>2026-07-21T07:20:13.000Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>WO0000000309669</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-21T07:55:12.000Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>INC000000152856</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-21T10:48:40.999Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>INC000000152863</v>
+        <v>INC000000152878</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-18T11:32:43.000Z</v>
+        <v>2026-07-18T08:12:08.000Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>INC000000152866</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-18T11:57:16.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>WO0000000309671</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-21T09:18:02.999Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>INC000000152869</v>
+        <v>INC000000152879</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-21T07:20:13.000Z</v>
+        <v>2026-07-18T08:11:58.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>INC000000152873</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>INC000000152971</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-21T10:45:55.999Z</v>
+        <v>2026-07-18T12:53:54.000Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>WO0000000309678</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-18T07:42:09.999Z</v>
+        <v>2026-07-21T10:48:40.000Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>INC000000152878</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-18T08:12:08.000Z</v>
+        <v>2026-07-18T08:48:11.000Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>WO0000000309682</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-21T10:10:23.000Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>WO0000000309686</v>
+        <v>WO0000000309732</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-18T09:10:30.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>INC000000152879</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-21T07:56:14.999Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>WO0000000309689</v>
+        <v>INC000000152888</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-21T10:50:40.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-18T12:53:54.000Z</v>
+        <v>2026-07-21T10:00:54.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>INC000000152883</v>
+        <v>WO0000000309698</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-18T08:39:53.000Z</v>
+        <v>2026-07-18T10:07:47.000Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>WO0000000309692</v>
+        <v>INC000000152986</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-18T08:48:11.000Z</v>
+        <v>2026-07-21T08:16:08.000Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>INC000000152981</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-21T10:10:23.000Z</v>
+        <v>2026-07-18T10:49:11.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>INC000000152980</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-18T16:16:48.000Z</v>
+        <v>2026-07-21T10:41:02.000Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>WO0000000309732</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-18T09:10:30.000Z</v>
+        <v>2026-07-21T07:32:12.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>WO0000000309697</v>
+        <v>WO0000000309802</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-21T07:56:14.999Z</v>
+        <v>2026-07-21T09:30:57.000Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>INC000000152888</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-21T10:39:53.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>INC000000152985</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-21T10:00:54.000Z</v>
+        <v>2026-07-20T19:05:32.000Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>WO0000000309698</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-18T10:07:47.000Z</v>
+        <v>2026-07-20T19:04:33.999Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>INC000000152986</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-21T08:16:08.000Z</v>
+        <v>2026-07-20T19:03:52.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-18T10:49:11.000Z</v>
+        <v>2026-07-20T19:04:20.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>INC000000152989</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-21T10:41:02.000Z</v>
+        <v>2026-07-21T10:20:14.999Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>INC000000152990</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-21T09:00:11.000Z</v>
+        <v>2026-07-21T10:56:34.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>INC000000152890</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-21T07:32:12.000Z</v>
+        <v>2026-07-21T10:21:19.000Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>WO0000000309802</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-21T09:30:57.000Z</v>
+        <v>2026-07-21T07:32:42.999Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>WO0000000309803</v>
+        <v>INC000000153000</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-21T07:31:13.000Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-20T19:05:32.000Z</v>
+        <v>2026-07-21T07:33:22.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-20T19:04:33.999Z</v>
+        <v>2026-07-21T10:52:04.000Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>INC000000152892</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-20T19:03:52.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>INC000000152893</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-20T19:04:20.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>WO0000000309804</v>
+        <v>INC000000153003</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-21T10:20:14.999Z</v>
+        <v>2026-07-21T10:59:38.999Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>WO0000000309805</v>
+        <v>INC000000152900</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-21T09:26:05.000Z</v>
+        <v>2026-07-21T08:04:18.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>WO0000000309807</v>
+        <v>WO0000000309815</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-21T10:21:19.000Z</v>
+        <v>2026-07-21T09:12:13.999Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153006</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-21T07:32:42.999Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>INC000000153000</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-21T07:31:13.000Z</v>
+        <v>2026-07-21T07:19:30.000Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>INC000000152897</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-21T07:33:22.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>INC000000152898</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-21T08:41:17.000Z</v>
+        <v>2026-07-21T10:18:57.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>WO0000000309810</v>
+        <v>INC000000153103</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-21T08:04:41.000Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>WO0000000309752</v>
+        <v>INC000000153011</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-21T10:52:54.000Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>INC000000153003</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-21T09:03:17.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>INC000000152900</v>
+        <v>INC000000153012</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-21T08:04:18.000Z</v>
+        <v>2026-07-21T08:03:57.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>WO0000000309815</v>
+        <v>INC000000153013</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-21T09:12:13.999Z</v>
+        <v>2026-07-21T07:19:23.999Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>INC000000153006</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-21T07:31:56.999Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-21T07:19:30.000Z</v>
+        <v>2026-07-21T07:19:54.000Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>WO0000000309816</v>
+        <v>INC000000153015</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-21T10:29:31.000Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>INC000000153102</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-21T10:18:57.000Z</v>
+        <v>2026-07-21T07:30:09.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>INC000000153103</v>
+        <v>INC000000153017</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-21T08:04:41.000Z</v>
+        <v>2026-07-18T15:26:50.000Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>INC000000153011</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-21T10:42:50.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000309759</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-21T09:58:01.000Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>INC000000153012</v>
+        <v>WO0000000309769</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-21T08:03:57.000Z</v>
+        <v>2026-07-21T07:30:32.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>INC000000153013</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-21T07:19:23.999Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>WO0000000309825</v>
+        <v>WO0000000309830</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-21T07:31:56.999Z</v>
+        <v>2026-07-21T09:26:50.000Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>INC000000153105</v>
+        <v>INC000000153108</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-21T07:19:54.000Z</v>
+        <v>2026-07-21T07:53:45.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>INC000000153015</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-21T10:29:31.000Z</v>
+        <v>2026-07-19T08:43:56.000Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>WO0000000309826</v>
+        <v>INC000000153020</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-21T07:30:09.000Z</v>
+        <v>2026-07-21T07:53:07.999Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>INC000000153017</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-18T15:26:50.000Z</v>
+        <v>2026-07-21T07:08:54.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>WO0000000309768</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>INC000000153107</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-21T09:58:01.000Z</v>
+        <v>2026-07-19T13:24:13.000Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>WO0000000309769</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-21T07:30:32.000Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>WO0000000309829</v>
+        <v>INC000000153025</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-19T13:28:43.999Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>WO0000000309830</v>
+        <v>INC000000153024</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-21T09:26:50.000Z</v>
+        <v>2026-07-19T13:24:41.999Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>INC000000153108</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-21T07:53:45.000Z</v>
+        <v>2026-07-20T18:58:17.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>INC000000153019</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-19T08:43:56.000Z</v>
+        <v>2026-07-21T07:52:42.999Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>INC000000153020</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-21T07:53:07.999Z</v>
+        <v>2026-07-19T12:52:16.000Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153028</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-21T07:08:54.000Z</v>
+        <v>2026-07-20T18:58:47.999Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>INC000000153022</v>
+        <v>INC000000153029</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-21T09:41:08.000Z</v>
+        <v>2026-07-21T10:36:31.000Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>INC000000153110</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-19T13:24:13.000Z</v>
+        <v>2026-07-21T07:09:08.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>INC000000153111</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-21T10:36:26.000Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>INC000000153025</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-19T13:28:43.999Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>INC000000153024</v>
+        <v>INC000000153031</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-19T13:24:41.999Z</v>
+        <v>2026-07-21T09:40:02.000Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>INC000000153027</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-20T18:58:17.000Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-21T07:52:42.999Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>INC000000153114</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-19T12:52:16.000Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>INC000000153028</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-20T18:58:47.999Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>INC000000153029</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-21T10:36:31.000Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>WO0000000309779</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-21T07:09:08.000Z</v>
+        <v>2026-07-21T07:41:05.999Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>INC000000153118</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-21T09:37:20.000Z</v>
+        <v>2026-07-21T07:47:06.000Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-21T10:36:26.000Z</v>
+        <v>2026-07-21T07:58:21.000Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>INC000000153121</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-21T08:01:28.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>INC000000153031</v>
+        <v>INC000000153123</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-21T09:40:02.000Z</v>
+        <v>2026-07-21T07:54:40.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>WO0000000309780</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-20T08:42:15.000Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>WO0000000309837</v>
+        <v>INC000000153125</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-21T07:46:07.000Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000309781</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-21T08:57:28.999Z</v>
+        <v>2026-07-21T09:45:18.000Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>WO0000000309783</v>
+        <v>WO0000000309791</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-20T12:51:30.000Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>WO0000000309838</v>
+        <v>WO0000000309792</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-20T14:10:35.999Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>INC000000153034</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-21T07:41:05.999Z</v>
+        <v>2026-07-21T09:36:30.999Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>INC000000153035</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-21T07:47:06.000Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>INC000000153036</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-21T07:58:21.000Z</v>
+        <v>2026-07-21T08:43:23.000Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>INC000000153037</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-21T08:01:28.000Z</v>
+        <v>2026-07-20T18:35:59.000Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>INC000000153123</v>
+        <v>WO0000000309794</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-21T07:54:40.000Z</v>
+        <v>2026-07-20T18:20:05.999Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>INC000000153038</v>
+        <v>WO0000000309843</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-20T08:42:15.000Z</v>
+        <v>2026-07-20T18:23:24.000Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>INC000000153125</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-21T07:46:07.000Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309797</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-21T09:45:18.000Z</v>
+        <v>2026-07-20T19:09:36.000Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>WO0000000309791</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-20T12:51:30.000Z</v>
+        <v>2026-07-21T10:57:08.000Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>WO0000000309792</v>
+        <v>WO0000000309798</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-20T14:10:35.999Z</v>
+        <v>2026-07-21T07:04:25.000Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>WO0000000309841</v>
+        <v>WO0000000309852</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-21T09:36:30.999Z</v>
+        <v>2026-07-20T22:58:26.999Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>WO0000000309842</v>
+        <v>WO0000000309853</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T05:54:59.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>INC000000153128</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-21T08:43:23.000Z</v>
+        <v>2026-07-21T09:44:12.000Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>WO0000000309793</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-20T18:35:59.000Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000309794</v>
+        <v>WO0000000309906</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-20T18:20:05.999Z</v>
+        <v>2026-07-21T07:44:08.000Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>WO0000000309843</v>
+        <v>WO0000000309909</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-20T18:23:24.000Z</v>
+        <v>2026-07-21T07:43:47.000Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>WO0000000309848</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T08:19:35.999Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>WO0000000309797</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-20T19:09:36.000Z</v>
+        <v>2026-07-21T06:40:04.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>WO0000000309851</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-21T08:36:19.000Z</v>
+        <v>2026-07-21T08:16:43.999Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>WO0000000309798</v>
+        <v>INC000000153050</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-21T07:04:25.000Z</v>
+        <v>2026-07-21T07:46:48.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>WO0000000309852</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-20T22:58:26.999Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>WO0000000309853</v>
+        <v>INC000000153137</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-21T05:54:59.000Z</v>
+        <v>2026-07-21T07:03:14.999Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309914</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-21T09:44:12.000Z</v>
+        <v>2026-07-21T07:20:13.999Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>WO0000000309902</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T10:44:20.000Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>WO0000000309906</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-21T07:44:08.000Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>WO0000000309909</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-21T07:43:47.000Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>INC000000153047</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T08:19:35.999Z</v>
+        <v>2026-07-21T09:37:42.999Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153053</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-21T06:40:04.000Z</v>
+        <v>2026-07-21T08:05:04.000Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>INC000000153134</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-21T08:16:43.999Z</v>
+        <v>2026-07-21T09:37:31.000Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000153050</v>
+        <v>WO0000000309927</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T07:46:48.000Z</v>
+        <v>2026-07-21T07:54:45.999Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>INC000000153048</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T10:11:19.999Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>INC000000153137</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-21T07:03:14.999Z</v>
+        <v>2026-07-21T08:34:57.999Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000309914</v>
+        <v>WO0000000309867</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-21T07:20:13.999Z</v>
+        <v>2026-07-21T08:13:16.000Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>INC000000153138</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-21T10:44:20.000Z</v>
+        <v>2026-07-21T07:57:56.999Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153060</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T08:01:12.999Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>WO0000000309862</v>
+        <v>INC000000153061</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T10:54:42.999Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>WO0000000309861</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-21T09:37:42.999Z</v>
+        <v>2026-07-21T10:38:36.000Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>INC000000153053</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-21T08:05:04.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>INC000000153140</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-21T09:37:31.000Z</v>
+        <v>2026-07-21T10:15:53.000Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>WO0000000309927</v>
+        <v>WO0000000309876</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-21T07:54:45.999Z</v>
+        <v>2026-07-21T08:19:59.000Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>INC000000153056</v>
+        <v>WO0000000309877</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-21T10:11:19.999Z</v>
+        <v>2026-07-21T08:15:48.000Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000309875</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-21T08:34:57.999Z</v>
+        <v>2026-07-21T10:03:29.999Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>WO0000000309867</v>
+        <v>WO0000000309878</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-21T08:13:16.000Z</v>
+        <v>2026-07-21T08:35:47.000Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>INC000000153144</v>
+        <v>WO0000000309941</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-21T07:57:56.999Z</v>
+        <v>2026-07-21T09:14:35.999Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>INC000000153060</v>
+        <v>WO0000000309879</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-21T08:01:12.999Z</v>
+        <v>2026-07-21T08:17:04.000Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>INC000000153061</v>
+        <v>WO0000000309944</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-21T10:23:25.999Z</v>
+        <v>2026-07-21T08:15:03.000Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>INC000000153062</v>
+        <v>INC000000153149</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-21T10:38:36.000Z</v>
+        <v>2026-07-21T08:58:21.000Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>INC000000153143</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>INC000000153063</v>
+        <v>INC000000153151</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:13:22.999Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>INC000000153145</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-21T10:15:53.000Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>WO0000000309876</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-21T08:19:59.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>WO0000000309877</v>
+        <v>INC000000153147</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-21T08:15:48.000Z</v>
+        <v>2026-07-21T10:54:55.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>WO0000000309875</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-21T10:03:29.999Z</v>
+        <v>2026-07-21T10:58:53.000Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>WO0000000309939</v>
+        <v>INC000000153064</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-21T08:42:26.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>WO0000000309878</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-21T08:35:47.000Z</v>
+        <v>2026-07-21T09:45:12.999Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>WO0000000309941</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-21T09:14:35.999Z</v>
+        <v>2026-07-21T09:47:21.999Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>WO0000000309879</v>
+        <v>WO0000000309888</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-21T08:17:04.000Z</v>
+        <v>2026-07-21T08:44:29.999Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>WO0000000309944</v>
+        <v>WO0000000309950</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-21T08:15:03.000Z</v>
+        <v>2026-07-21T08:39:49.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>INC000000153149</v>
+        <v>WO0000000309951</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-21T08:58:21.000Z</v>
+        <v>2026-07-21T09:40:47.000Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>WO0000000309880</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>INC000000153151</v>
+        <v>WO0000000309952</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-21T09:13:22.999Z</v>
+        <v>2026-07-21T08:33:13.000Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>WO0000000309945</v>
+        <v>WO0000000309953</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T08:41:50.000Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>WO0000000309946</v>
+        <v>WO0000000309889</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T08:33:25.000Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>INC000000153147</v>
+        <v>INC000000153070</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-21T09:06:12.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-21T08:41:34.000Z</v>
+        <v>2026-07-21T08:48:14.999Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>INC000000153064</v>
+        <v>INC000000153156</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T08:39:24.000Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>INC000000153153</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-21T09:45:12.999Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>WO0000000309949</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-21T09:47:21.999Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>WO0000000309888</v>
+        <v>INC000000153071</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-21T08:44:29.999Z</v>
+        <v>2026-07-21T08:50:05.000Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>WO0000000309950</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-21T08:39:49.000Z</v>
+        <v>2026-07-21T08:49:28.000Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>WO0000000309951</v>
+        <v>INC000000153157</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-21T09:40:47.000Z</v>
+        <v>2026-07-21T08:51:40.000Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>INC000000153068</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-21T10:35:54.000Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>WO0000000309952</v>
+        <v>INC000000153073</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-21T08:33:13.000Z</v>
+        <v>2026-07-21T10:27:24.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>WO0000000309953</v>
+        <v>INC000000153075</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-21T08:41:50.000Z</v>
+        <v>2026-07-21T09:12:07.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>WO0000000309889</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-21T08:33:25.000Z</v>
+        <v>2026-07-21T09:22:48.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>INC000000153070</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T10:28:57.999Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>INC000000153069</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-21T08:48:14.999Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>INC000000153156</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-21T08:39:24.000Z</v>
+        <v>2026-07-21T09:21:34.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>WO0000000309892</v>
+        <v>WO0000000310005</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-21T09:04:46.000Z</v>
+        <v>2026-07-21T09:32:59.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>WO0000000309954</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T08:56:12.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>INC000000153071</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-21T08:50:05.000Z</v>
+        <v>2026-07-21T09:20:33.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>INC000000153072</v>
+        <v>INC000000153076</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-21T08:49:28.000Z</v>
+        <v>2026-07-21T10:25:21.000Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>INC000000153157</v>
+        <v>WO0000000310008</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-21T08:51:40.000Z</v>
+        <v>2026-07-21T08:58:48.000Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>INC000000153159</v>
+        <v>WO0000000309962</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-21T10:35:54.000Z</v>
+        <v>2026-07-21T09:15:42.999Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>INC000000153073</v>
+        <v>WO0000000310009</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-21T10:27:24.000Z</v>
+        <v>2026-07-21T10:38:41.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>INC000000153075</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-21T09:12:07.000Z</v>
+        <v>2026-07-21T09:03:20.999Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000310002</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-21T09:22:48.000Z</v>
+        <v>2026-07-21T09:28:19.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>WO0000000309957</v>
+        <v>WO0000000309967</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-21T10:28:57.999Z</v>
+        <v>2026-07-21T09:02:23.000Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>WO0000000309958</v>
+        <v>WO0000000310013</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-21T08:54:45.000Z</v>
+        <v>2026-07-21T09:07:07.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>WO0000000310004</v>
+        <v>WO0000000309973</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-21T09:21:34.000Z</v>
+        <v>2026-07-21T09:08:48.000Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>WO0000000310005</v>
+        <v>WO0000000310015</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-21T09:32:59.000Z</v>
+        <v>2026-07-21T09:27:41.000Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>WO0000000309959</v>
+        <v>INC000000153079</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-21T08:56:12.000Z</v>
+        <v>2026-07-21T09:12:25.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>WO0000000310006</v>
+        <v>INC000000153164</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-21T09:20:33.000Z</v>
+        <v>2026-07-21T09:16:22.000Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>INC000000153076</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-21T10:25:21.000Z</v>
+        <v>2026-07-21T09:29:42.999Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>WO0000000310008</v>
+        <v>WO0000000310016</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-21T08:58:48.000Z</v>
+        <v>2026-07-21T09:14:48.000Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>WO0000000309962</v>
+        <v>INC000000153168</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-21T09:15:42.999Z</v>
+        <v>2026-07-21T09:54:40.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>WO0000000310009</v>
+        <v>WO0000000310017</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-21T10:38:41.000Z</v>
+        <v>2026-07-21T09:29:50.999Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>INC000000153074</v>
+        <v>WO0000000310018</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-21T09:03:20.999Z</v>
+        <v>2026-07-21T09:18:47.000Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>WO0000000309961</v>
+        <v>INC000000153170</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-21T09:28:19.000Z</v>
+        <v>2026-07-21T09:38:39.999Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>WO0000000309967</v>
+        <v>WO0000000310019</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-21T09:02:23.000Z</v>
+        <v>2026-07-21T10:19:05.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>WO0000000310013</v>
+        <v>WO0000000309981</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-21T09:07:07.000Z</v>
+        <v>2026-07-21T09:19:50.000Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>WO0000000309973</v>
+        <v>INC000000153165</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-21T09:08:48.000Z</v>
+        <v>2026-07-21T09:36:23.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>WO0000000310015</v>
+        <v>WO0000000310021</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-21T09:27:41.000Z</v>
+        <v>2026-07-21T09:24:02.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>INC000000153079</v>
+        <v>INC000000153172</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-21T09:12:25.000Z</v>
+        <v>2026-07-21T09:52:46.999Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>INC000000153164</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-21T09:16:22.000Z</v>
+        <v>2026-07-21T10:36:09.999Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153174</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-21T09:29:42.999Z</v>
+        <v>2026-07-21T09:57:25.000Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>WO0000000310016</v>
+        <v>INC000000153175</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-21T09:14:48.000Z</v>
+        <v>2026-07-21T09:28:26.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>INC000000153168</v>
+        <v>WO0000000309986</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-21T09:54:40.000Z</v>
+        <v>2026-07-21T09:28:28.999Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>WO0000000310017</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-21T09:29:50.999Z</v>
+        <v>2026-07-21T09:27:18.999Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>WO0000000310018</v>
+        <v>WO0000000309975</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-21T09:18:47.000Z</v>
+        <v>2026-07-21T09:49:40.999Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>INC000000153170</v>
+        <v>WO0000000309984</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-21T09:38:39.999Z</v>
+        <v>2026-07-21T09:31:44.000Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>WO0000000310019</v>
+        <v>WO0000000309987</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-21T10:19:05.000Z</v>
+        <v>2026-07-21T09:30:18.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>INC000000153169</v>
+        <v>INC000000153177</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-21T10:02:51.000Z</v>
+        <v>2026-07-21T09:31:53.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>WO0000000309981</v>
+        <v>INC000000153080</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-21T09:19:50.000Z</v>
+        <v>2026-07-21T10:53:24.000Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>INC000000153165</v>
+        <v>INC000000153171</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-21T09:36:23.000Z</v>
+        <v>2026-07-21T10:25:59.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>WO0000000310021</v>
+        <v>INC000000153176</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-21T09:24:02.000Z</v>
+        <v>2026-07-21T09:43:34.000Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>INC000000153172</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-21T09:52:46.999Z</v>
+        <v>2026-07-21T09:37:20.999Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>INC000000153167</v>
+        <v>WO0000000310025</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-21T10:36:09.999Z</v>
+        <v>2026-07-21T09:36:55.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>INC000000153174</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-21T09:57:25.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>INC000000153175</v>
+        <v>INC000000153180</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-21T09:28:26.000Z</v>
+        <v>2026-07-21T09:57:04.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>WO0000000309986</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-21T09:28:28.999Z</v>
+        <v>2026-07-21T09:40:19.000Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>WO0000000309985</v>
+        <v>INC000000153181</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-21T09:27:18.999Z</v>
+        <v>2026-07-21T09:48:10.999Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>WO0000000309975</v>
+        <v>WO0000000309993</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-21T09:49:40.999Z</v>
+        <v>2026-07-21T09:41:07.000Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>WO0000000309984</v>
+        <v>INC000000153178</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-21T09:31:44.000Z</v>
+        <v>2026-07-21T10:29:02.000Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>WO0000000309987</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-21T09:30:18.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>INC000000153177</v>
+        <v>INC000000153082</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-21T09:31:53.000Z</v>
+        <v>2026-07-21T10:22:17.000Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>WO0000000310022</v>
+        <v>WO0000000309991</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-21T09:30:46.000Z</v>
+        <v>2026-07-21T09:45:25.999Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>INC000000153080</v>
+        <v>INC000000153179</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-21T10:46:26.000Z</v>
+        <v>2026-07-21T09:46:47.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>INC000000153171</v>
+        <v>WO0000000309995</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-21T10:25:59.000Z</v>
+        <v>2026-07-21T10:01:19.000Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>INC000000153176</v>
+        <v>WO0000000305266</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-21T09:43:34.000Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000309997</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-21T09:37:20.999Z</v>
+        <v>2026-07-21T10:09:06.999Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>WO0000000310025</v>
+        <v>WO0000000309998</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-21T09:36:55.000Z</v>
+        <v>2026-07-21T09:47:07.999Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000309996</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-21T09:37:57.000Z</v>
+        <v>2026-07-21T09:49:05.999Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>INC000000153180</v>
+        <v>INC000000153182</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-21T09:57:04.000Z</v>
+        <v>2026-07-21T10:35:39.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310000</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-21T09:40:19.000Z</v>
+        <v>2026-07-21T09:49:32.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>INC000000153181</v>
+        <v>WO0000000310024</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-21T09:48:10.999Z</v>
+        <v>2026-07-21T09:50:13.000Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>WO0000000309993</v>
+        <v>WO0000000309999</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-21T09:41:07.000Z</v>
+        <v>2026-07-21T09:50:29.000Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>INC000000153178</v>
+        <v>WO0000000310102</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-21T10:29:02.000Z</v>
+        <v>2026-07-21T09:50:55.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310033</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-21T09:51:00.000Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>INC000000153082</v>
+        <v>INC000000153185</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-21T10:22:17.000Z</v>
+        <v>2026-07-21T10:21:27.999Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>WO0000000309991</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-21T09:45:25.999Z</v>
+        <v>2026-07-21T09:55:33.000Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>INC000000153179</v>
+        <v>WO0000000305268</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-21T09:46:47.000Z</v>
+        <v>2026-07-21T09:55:25.000Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>WO0000000309995</v>
+        <v>INC000000153083</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-21T10:01:19.000Z</v>
+        <v>2026-07-21T10:29:05.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>WO0000000305266</v>
+        <v>WO0000000310105</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
+        <v>2026-07-21T10:09:51.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>WO0000000309997</v>
+        <v>INC000000153084</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-21T10:09:06.999Z</v>
+        <v>2026-07-21T10:22:19.000Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>WO0000000309998</v>
+        <v>WO0000000305269</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-21T09:47:07.999Z</v>
+        <v>2026-07-21T09:57:11.000Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>WO0000000309996</v>
+        <v>WO0000000310034</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-21T09:49:05.999Z</v>
+        <v>2026-07-21T10:02:08.000Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>INC000000153182</v>
+        <v>WO0000000310106</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-21T10:35:39.000Z</v>
+        <v>2026-07-21T10:02:21.999Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>WO0000000310000</v>
+        <v>WO0000000310107</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-21T09:49:32.000Z</v>
+        <v>2026-07-21T10:27:27.999Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>WO0000000310024</v>
+        <v>WO0000000310036</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-21T09:50:13.000Z</v>
+        <v>2026-07-21T09:59:20.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>WO0000000309999</v>
+        <v>INC000000153186</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-21T09:50:29.000Z</v>
+        <v>2026-07-21T10:51:47.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>WO0000000310102</v>
+        <v>WO0000000310109</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-21T09:50:55.000Z</v>
+        <v>2026-07-21T10:07:20.999Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>WO0000000310033</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-21T09:51:00.000Z</v>
+        <v>2026-07-21T10:05:59.000Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>INC000000153185</v>
+        <v>WO0000000310039</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-21T10:21:27.999Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>INC000000153183</v>
+        <v>INC000000153086</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-21T09:55:33.000Z</v>
+        <v>2026-07-21T10:23:37.999Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>WO0000000305268</v>
+        <v>WO0000000310040</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-21T09:55:25.000Z</v>
+        <v>2026-07-21T10:09:05.000Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>INC000000153083</v>
+        <v>WO0000000310041</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-21T10:29:05.000Z</v>
+        <v>2026-07-21T10:03:27.999Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>WO0000000310105</v>
+        <v>WO0000000310042</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-21T10:09:51.000Z</v>
+        <v>2026-07-21T10:08:51.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>INC000000153084</v>
+        <v>INC000000153187</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-21T10:22:19.000Z</v>
+        <v>2026-07-21T10:25:14.000Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>WO0000000305269</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-21T09:57:11.000Z</v>
+        <v>2026-07-21T10:31:45.000Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>WO0000000310034</v>
+        <v>INC000000153089</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-21T10:02:08.000Z</v>
+        <v>2026-07-21T10:28:35.000Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>WO0000000310106</v>
+        <v>WO0000000310045</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-21T10:02:21.999Z</v>
+        <v>2026-07-21T10:35:09.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>WO0000000310107</v>
+        <v>INC000000153090</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-21T10:27:27.999Z</v>
+        <v>2026-07-21T10:32:06.999Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>WO0000000310036</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-21T09:59:20.000Z</v>
+        <v>2026-07-21T10:08:14.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>INC000000153186</v>
+        <v>INC000000153091</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-21T10:44:35.999Z</v>
+        <v>2026-07-21T10:30:46.000Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>WO0000000310109</v>
+        <v>INC000000153094</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-21T10:07:20.999Z</v>
+        <v>2026-07-21T10:34:10.000Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>INC000000153184</v>
+        <v>WO0000000310114</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-21T10:05:59.000Z</v>
+        <v>2026-07-21T10:12:20.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>WO0000000310039</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-21T10:36:47.999Z</v>
+        <v>2026-07-21T10:13:41.000Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>INC000000153086</v>
+        <v>WO0000000310113</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-21T10:23:37.999Z</v>
+        <v>2026-07-21T10:32:45.000Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>WO0000000310040</v>
+        <v>WO0000000310046</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-21T10:09:05.000Z</v>
+        <v>2026-07-21T10:13:36.000Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>WO0000000310041</v>
+        <v>INC000000153088</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-21T10:03:27.999Z</v>
+        <v>2026-07-21T10:17:32.000Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>WO0000000310042</v>
+        <v>WO0000000310047</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-21T10:08:51.000Z</v>
+        <v>2026-07-21T10:14:06.000Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>INC000000153187</v>
+        <v>INC000000153188</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-21T10:25:14.000Z</v>
+        <v>2026-07-21T10:16:45.000Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310118</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-21T10:31:45.000Z</v>
+        <v>2026-07-21T10:29:50.999Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>INC000000153089</v>
+        <v>INC000000153189</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-21T10:28:35.000Z</v>
+        <v>2026-07-21T10:59:53.000Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>WO0000000310045</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-21T10:35:09.000Z</v>
+        <v>2026-07-21T10:18:38.000Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>INC000000153090</v>
+        <v>WO0000000310049</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-21T10:32:06.999Z</v>
+        <v>2026-07-21T10:20:08.000Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>WO0000000310112</v>
+        <v>INC000000153190</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-21T10:08:14.000Z</v>
+        <v>2026-07-21T10:38:37.999Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>INC000000153091</v>
+        <v>WO0000000310050</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-21T10:30:46.000Z</v>
+        <v>2026-07-21T10:21:12.000Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>INC000000153094</v>
+        <v>INC000000153191</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-21T10:34:10.000Z</v>
+        <v>2026-07-21T10:54:13.999Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>WO0000000310114</v>
+        <v>INC000000153192</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-21T10:12:20.000Z</v>
+        <v>2026-07-21T10:26:23.999Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>INC000000153093</v>
+        <v>WO0000000310051</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-21T10:13:41.000Z</v>
+        <v>2026-07-21T10:23:58.000Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>WO0000000310113</v>
+        <v>INC000000153193</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-21T10:32:45.000Z</v>
+        <v>2026-07-21T10:25:57.999Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>WO0000000310046</v>
+        <v>WO0000000310120</v>
       </c>
       <c r="B1181" s="1" t="d">
-        <v>2026-07-21T10:13:36.000Z</v>
+        <v>2026-07-21T10:35:25.000Z</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>INC000000153088</v>
+        <v>WO0000000310053</v>
       </c>
       <c r="B1182" s="1" t="d">
-        <v>2026-07-21T10:17:32.000Z</v>
+        <v>2026-07-21T10:27:39.999Z</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>WO0000000310047</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B1183" s="1" t="d">
-        <v>2026-07-21T10:14:06.000Z</v>
+        <v>2026-07-21T10:53:52.000Z</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>INC000000153188</v>
+        <v>INC000000153100</v>
       </c>
       <c r="B1184" s="1" t="d">
-        <v>2026-07-21T10:16:45.000Z</v>
+        <v>2026-07-21T10:36:40.000Z</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>WO0000000310118</v>
+        <v>INC000000153194</v>
       </c>
       <c r="B1185" s="1" t="d">
-        <v>2026-07-21T10:29:50.999Z</v>
+        <v>2026-07-21T10:31:29.999Z</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>INC000000153189</v>
+        <v>WO0000000310122</v>
       </c>
       <c r="B1186" s="1" t="d">
-        <v>2026-07-21T10:18:16.000Z</v>
+        <v>2026-07-21T10:28:56.999Z</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153099</v>
       </c>
       <c r="B1187" s="1" t="d">
-        <v>2026-07-21T10:18:38.000Z</v>
+        <v>2026-07-21T10:34:51.000Z</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>WO0000000310049</v>
+        <v>INC000000153095</v>
       </c>
       <c r="B1188" s="1" t="d">
-        <v>2026-07-21T10:20:08.000Z</v>
+        <v>2026-07-21T10:34:35.999Z</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>INC000000153190</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B1189" s="1" t="d">
-        <v>2026-07-21T10:38:37.999Z</v>
+        <v>2026-07-21T10:52:52.999Z</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>WO0000000310050</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B1190" s="1" t="d">
-        <v>2026-07-21T10:21:12.000Z</v>
+        <v>2026-07-21T10:51:40.000Z</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>INC000000153191</v>
+        <v>INC000000153201</v>
       </c>
       <c r="B1191" s="1" t="d">
-        <v>2026-07-21T10:39:39.000Z</v>
+        <v>2026-07-21T10:39:28.000Z</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>INC000000153192</v>
+        <v>WO0000000310123</v>
       </c>
       <c r="B1192" s="1" t="d">
-        <v>2026-07-21T10:26:23.999Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>WO0000000310051</v>
+        <v>WO0000000310055</v>
       </c>
       <c r="B1193" s="1" t="d">
-        <v>2026-07-21T10:23:58.000Z</v>
+        <v>2026-07-21T10:43:50.000Z</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>INC000000153193</v>
+        <v>INC000000153202</v>
       </c>
       <c r="B1194" s="1" t="d">
-        <v>2026-07-21T10:25:57.999Z</v>
+        <v>2026-07-21T10:40:42.000Z</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>WO0000000310120</v>
+        <v>INC000000153197</v>
       </c>
       <c r="B1195" s="1" t="d">
-        <v>2026-07-21T10:35:25.000Z</v>
+        <v>2026-07-21T10:44:35.999Z</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>WO0000000310053</v>
+        <v>INC000000153203</v>
       </c>
       <c r="B1196" s="1" t="d">
-        <v>2026-07-21T10:27:39.999Z</v>
+        <v>2026-07-21T10:57:50.000Z</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>INC000000153195</v>
+        <v>WO0000000310127</v>
       </c>
       <c r="B1197" s="1" t="d">
-        <v>2026-07-21T10:45:16.999Z</v>
+        <v>2026-07-21T11:02:10.000Z</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>INC000000153100</v>
+        <v>INC000000153204</v>
       </c>
       <c r="B1198" s="1" t="d">
-        <v>2026-07-21T10:36:40.000Z</v>
+        <v>2026-07-21T10:57:50.000Z</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>INC000000153194</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B1199" s="1" t="d">
-        <v>2026-07-21T10:31:29.999Z</v>
+        <v>2026-07-21T10:46:52.000Z</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>WO0000000310122</v>
+        <v>WO0000000310061</v>
       </c>
       <c r="B1200" s="1" t="d">
-        <v>2026-07-21T10:28:56.999Z</v>
+        <v>2026-07-21T10:47:06.000Z</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>INC000000153099</v>
+        <v>INC000000153205</v>
       </c>
       <c r="B1201" s="1" t="d">
-        <v>2026-07-21T10:34:51.000Z</v>
+        <v>2026-07-21T10:54:13.999Z</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>INC000000153095</v>
+        <v>WO0000000310130</v>
       </c>
       <c r="B1202" s="1" t="d">
-        <v>2026-07-21T10:34:35.999Z</v>
+        <v>2026-07-21T10:59:55.000Z</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>WO0000000310124</v>
+        <v>INC000000153210</v>
       </c>
       <c r="B1203" s="1" t="d">
-        <v>2026-07-21T10:34:07.000Z</v>
+        <v>2026-07-21T10:50:21.999Z</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>INC000000153196</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B1204" s="1" t="d">
-        <v>2026-07-21T10:34:43.999Z</v>
+        <v>2026-07-21T10:49:56.000Z</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>INC000000153201</v>
+        <v>WO0000000310131</v>
       </c>
       <c r="B1205" s="1" t="d">
-        <v>2026-07-21T10:39:28.000Z</v>
+        <v>2026-07-21T10:48:22.000Z</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>WO0000000310123</v>
+        <v>INC000000153209</v>
       </c>
       <c r="B1206" s="1" t="d">
-        <v>2026-07-21T10:36:47.999Z</v>
+        <v>2026-07-21T10:49:48.000Z</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="str">
-        <v>WO0000000310055</v>
+        <v>WO0000000310132</v>
       </c>
       <c r="B1207" s="1" t="d">
-        <v>2026-07-21T10:43:50.000Z</v>
+        <v>2026-07-21T10:51:57.000Z</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>INC000000153202</v>
+        <v>INC000000153211</v>
       </c>
       <c r="B1208" s="1" t="d">
-        <v>2026-07-21T10:40:42.000Z</v>
+        <v>2026-07-21T10:52:02.000Z</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>INC000000153197</v>
+        <v>WO0000000310135</v>
       </c>
       <c r="B1209" s="1" t="d">
-        <v>2026-07-21T10:44:35.999Z</v>
+        <v>2026-07-21T10:51:40.000Z</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>INC000000153203</v>
+        <v>INC000000153200</v>
       </c>
       <c r="B1210" s="1" t="d">
-        <v>2026-07-21T10:41:24.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
-        <v>WO0000000310127</v>
+        <v>WO0000000310136</v>
       </c>
       <c r="B1211" s="1" t="d">
-        <v>2026-07-21T10:42:01.999Z</v>
+        <v>2026-07-21T10:53:26.000Z</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="str">
-        <v>INC000000153204</v>
+        <v>WO0000000310064</v>
       </c>
       <c r="B1212" s="1" t="d">
-        <v>2026-07-21T10:44:56.000Z</v>
+        <v>2026-07-21T11:01:58.999Z</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310133</v>
       </c>
       <c r="B1213" s="1" t="d">
-        <v>2026-07-21T10:46:52.000Z</v>
+        <v>2026-07-21T10:56:06.999Z</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="str">
-        <v>WO0000000310061</v>
+        <v>INC000000153301</v>
       </c>
       <c r="B1214" s="1" t="d">
-        <v>2026-07-21T10:47:06.000Z</v>
+        <v>2026-07-21T10:56:25.000Z</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="str">
-        <v>INC000000153205</v>
+        <v>INC000000153214</v>
       </c>
       <c r="B1215" s="1" t="d">
-        <v>2026-07-21T10:47:20.000Z</v>
+        <v>2026-07-21T11:00:05.000Z</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="str">
-        <v>WO0000000310130</v>
+        <v>INC000000153302</v>
       </c>
       <c r="B1216" s="1" t="d">
-        <v>2026-07-21T10:47:32.000Z</v>
+        <v>2026-07-21T11:01:37.999Z</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="str">
+        <v>INC000000153216</v>
+      </c>
+      <c r="B1217" s="1" t="d">
+        <v>2026-07-21T10:58:57.000Z</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="str">
+        <v>WO0000000310065</v>
+      </c>
+      <c r="B1218" s="1" t="d">
+        <v>2026-07-21T10:59:33.000Z</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="str">
+        <v>INC000000153303</v>
+      </c>
+      <c r="B1219" s="1" t="d">
+        <v>2026-07-21T10:59:44.000Z</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="str">
+        <v>INC000000153215</v>
+      </c>
+      <c r="B1220" s="1" t="d">
+        <v>2026-07-21T11:01:34.000Z</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="str">
+        <v>WO0000000310066</v>
+      </c>
+      <c r="B1221" s="1" t="d">
+        <v>2026-07-21T11:02:53.000Z</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1217"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1222"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1222"/>
+  <dimension ref="A1:B1232"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2579,802 +2579,802 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>WO0000000303593</v>
+        <v>INC000000150158</v>
       </c>
       <c r="B273" s="1" t="d">
-        <v>2026-07-15T13:55:27.999Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>INC000000150158</v>
+        <v>WO0000000303803</v>
       </c>
       <c r="B274" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-17T14:43:11.000Z</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>WO0000000303803</v>
+        <v>INC000000150172</v>
       </c>
       <c r="B275" s="1" t="d">
-        <v>2026-07-17T14:43:11.000Z</v>
+        <v>2026-07-06T12:25:58.000Z</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>INC000000150172</v>
+        <v>WO0000000303781</v>
       </c>
       <c r="B276" s="1" t="d">
-        <v>2026-07-06T12:25:58.000Z</v>
+        <v>2026-07-10T09:46:00.000Z</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>WO0000000303781</v>
+        <v>WO0000000303791</v>
       </c>
       <c r="B277" s="1" t="d">
-        <v>2026-07-10T09:46:00.000Z</v>
+        <v>2026-07-15T12:32:15.000Z</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>WO0000000303791</v>
+        <v>INC000000150407</v>
       </c>
       <c r="B278" s="1" t="d">
-        <v>2026-07-15T12:32:15.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>INC000000150407</v>
+        <v>WO0000000304363</v>
       </c>
       <c r="B279" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T13:27:05.000Z</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>WO0000000304415</v>
+        <v>INC000000150521</v>
       </c>
       <c r="B280" s="1" t="d">
-        <v>2026-07-15T12:14:00.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>WO0000000304363</v>
+        <v>INC000000150630</v>
       </c>
       <c r="B281" s="1" t="d">
-        <v>2026-07-15T13:27:05.000Z</v>
+        <v>2026-07-10T08:48:46.999Z</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>INC000000150521</v>
+        <v>INC000000150536</v>
       </c>
       <c r="B282" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-09T11:26:10.999Z</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>INC000000150630</v>
+        <v>WO0000000304551</v>
       </c>
       <c r="B283" s="1" t="d">
-        <v>2026-07-10T08:48:46.999Z</v>
+        <v>2026-07-15T16:39:18.000Z</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>INC000000150536</v>
+        <v>WO0000000304865</v>
       </c>
       <c r="B284" s="1" t="d">
-        <v>2026-07-09T11:26:10.999Z</v>
+        <v>2026-07-16T14:19:57.000Z</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>WO0000000304551</v>
+        <v>WO0000000304881</v>
       </c>
       <c r="B285" s="1" t="d">
-        <v>2026-07-15T16:39:18.000Z</v>
+        <v>2026-07-16T14:54:34.000Z</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>WO0000000304865</v>
+        <v>WO0000000304977</v>
       </c>
       <c r="B286" s="1" t="d">
-        <v>2026-07-16T14:19:57.000Z</v>
+        <v>2026-07-21T06:23:00.000Z</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>WO0000000304881</v>
+        <v>INC000000150832</v>
       </c>
       <c r="B287" s="1" t="d">
-        <v>2026-07-16T14:54:34.000Z</v>
+        <v>2026-07-10T09:16:28.000Z</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>WO0000000304977</v>
+        <v>INC000000150838</v>
       </c>
       <c r="B288" s="1" t="d">
-        <v>2026-07-21T06:23:00.000Z</v>
+        <v>2026-07-08T08:03:19.000Z</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>INC000000150832</v>
+        <v>WO0000000305041</v>
       </c>
       <c r="B289" s="1" t="d">
-        <v>2026-07-10T09:16:28.000Z</v>
+        <v>2026-07-10T13:12:35.999Z</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>INC000000150838</v>
+        <v>INC000000150843</v>
       </c>
       <c r="B290" s="1" t="d">
-        <v>2026-07-08T08:03:19.000Z</v>
+        <v>2026-07-07T14:07:42.999Z</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>WO0000000305041</v>
+        <v>INC000000150743</v>
       </c>
       <c r="B291" s="1" t="d">
-        <v>2026-07-10T13:12:35.999Z</v>
+        <v>2026-07-08T12:53:21.000Z</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>INC000000150843</v>
+        <v>INC000000150849</v>
       </c>
       <c r="B292" s="1" t="d">
-        <v>2026-07-07T14:07:42.999Z</v>
+        <v>2026-07-07T14:25:27.999Z</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>INC000000150743</v>
+        <v>INC000000150851</v>
       </c>
       <c r="B293" s="1" t="d">
-        <v>2026-07-08T12:53:21.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>INC000000150849</v>
+        <v>WO0000000305154</v>
       </c>
       <c r="B294" s="1" t="d">
-        <v>2026-07-07T14:25:27.999Z</v>
+        <v>2026-07-16T14:21:59.999Z</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>INC000000150851</v>
+        <v>WO0000000305077</v>
       </c>
       <c r="B295" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-16T15:27:35.999Z</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>WO0000000305154</v>
+        <v>WO0000000305701</v>
       </c>
       <c r="B296" s="1" t="d">
-        <v>2026-07-16T14:21:59.999Z</v>
+        <v>2026-07-17T12:26:34.000Z</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>WO0000000305077</v>
+        <v>WO0000000305706</v>
       </c>
       <c r="B297" s="1" t="d">
-        <v>2026-07-16T15:27:35.999Z</v>
+        <v>2026-07-17T12:32:44.000Z</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>WO0000000305701</v>
+        <v>WO0000000305880</v>
       </c>
       <c r="B298" s="1" t="d">
-        <v>2026-07-17T12:26:34.000Z</v>
+        <v>2026-07-21T06:23:37.000Z</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>WO0000000305706</v>
+        <v>WO0000000305897</v>
       </c>
       <c r="B299" s="1" t="d">
-        <v>2026-07-17T12:32:44.000Z</v>
+        <v>2026-07-17T16:35:20.000Z</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>WO0000000305880</v>
+        <v>WO0000000306041</v>
       </c>
       <c r="B300" s="1" t="d">
-        <v>2026-07-21T06:23:37.000Z</v>
+        <v>2026-07-15T08:16:13.999Z</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>WO0000000305897</v>
+        <v>INC000000151143</v>
       </c>
       <c r="B301" s="1" t="d">
-        <v>2026-07-17T16:35:20.000Z</v>
+        <v>2026-07-09T12:07:14.999Z</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>WO0000000306041</v>
+        <v>WO0000000305998</v>
       </c>
       <c r="B302" s="1" t="d">
-        <v>2026-07-15T08:16:13.999Z</v>
+        <v>2026-07-10T12:10:19.000Z</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>INC000000151143</v>
+        <v>INC000000151304</v>
       </c>
       <c r="B303" s="1" t="d">
-        <v>2026-07-09T12:07:14.999Z</v>
+        <v>2026-07-09T15:23:24.000Z</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>WO0000000305998</v>
+        <v>INC000000151200</v>
       </c>
       <c r="B304" s="1" t="d">
-        <v>2026-07-10T12:10:19.000Z</v>
+        <v>2026-07-10T10:51:56.000Z</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>INC000000151304</v>
+        <v>WO0000000306433</v>
       </c>
       <c r="B305" s="1" t="d">
-        <v>2026-07-09T15:23:24.000Z</v>
+        <v>2026-07-16T16:04:33.999Z</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>INC000000151200</v>
+        <v>WO0000000306373</v>
       </c>
       <c r="B306" s="1" t="d">
-        <v>2026-07-10T10:51:56.000Z</v>
+        <v>2026-07-17T17:02:38.000Z</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>WO0000000306433</v>
+        <v>WO0000000306610</v>
       </c>
       <c r="B307" s="1" t="d">
-        <v>2026-07-16T16:04:33.999Z</v>
+        <v>2026-07-16T09:06:23.000Z</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>WO0000000306373</v>
+        <v>WO0000000304733</v>
       </c>
       <c r="B308" s="1" t="d">
-        <v>2026-07-17T17:02:38.000Z</v>
+        <v>2026-07-15T10:28:05.999Z</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>WO0000000306610</v>
+        <v>INC000000135134</v>
       </c>
       <c r="B309" s="1" t="d">
-        <v>2026-07-16T09:06:23.000Z</v>
+        <v>2026-07-14T10:35:47.000Z</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>INC000000135134</v>
+        <v>INC000000136403</v>
       </c>
       <c r="B310" s="1" t="d">
-        <v>2026-07-14T10:35:47.000Z</v>
+        <v>2026-07-14T06:43:05.000Z</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>INC000000136403</v>
+        <v>INC000000138835</v>
       </c>
       <c r="B311" s="1" t="d">
-        <v>2026-07-14T06:43:05.000Z</v>
+        <v>2026-07-14T10:35:56.000Z</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>INC000000138835</v>
+        <v>INC000000139335</v>
       </c>
       <c r="B312" s="1" t="d">
-        <v>2026-07-14T10:35:56.000Z</v>
+        <v>2026-07-14T06:43:37.000Z</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>INC000000139335</v>
+        <v>WO0000000282199</v>
       </c>
       <c r="B313" s="1" t="d">
-        <v>2026-07-14T06:43:37.000Z</v>
+        <v>2026-07-14T15:02:42.000Z</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>WO0000000282199</v>
+        <v>INC000000141515</v>
       </c>
       <c r="B314" s="1" t="d">
-        <v>2026-07-14T15:02:42.000Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>INC000000141515</v>
+        <v>WO0000000293293</v>
       </c>
       <c r="B315" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-15T08:29:08.000Z</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>WO0000000293293</v>
+        <v>INC000000146720</v>
       </c>
       <c r="B316" s="1" t="d">
-        <v>2026-07-15T08:29:08.000Z</v>
+        <v>2026-07-16T08:34:09.000Z</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>INC000000146720</v>
+        <v>WO0000000295688</v>
       </c>
       <c r="B317" s="1" t="d">
-        <v>2026-07-16T08:34:09.000Z</v>
+        <v>2026-07-16T09:17:24.999Z</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>WO0000000295688</v>
+        <v>WO0000000295716</v>
       </c>
       <c r="B318" s="1" t="d">
-        <v>2026-07-16T09:17:24.999Z</v>
+        <v>2026-07-16T11:47:42.999Z</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>INC000000147260</v>
+        <v>INC000000146886</v>
       </c>
       <c r="B319" s="1" t="d">
-        <v>2026-07-14T08:08:06.000Z</v>
+        <v>2026-07-16T13:10:02.999Z</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>INC000000147613</v>
+        <v>INC000000147260</v>
       </c>
       <c r="B320" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-14T08:08:06.000Z</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>INC000000149029</v>
+        <v>INC000000147613</v>
       </c>
       <c r="B321" s="1" t="d">
-        <v>2026-07-10T14:37:50.000Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>WO0000000301822</v>
+        <v>INC000000149029</v>
       </c>
       <c r="B322" s="1" t="d">
-        <v>2026-07-21T09:48:14.000Z</v>
+        <v>2026-07-10T14:37:50.000Z</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>INC000000149860</v>
+        <v>WO0000000301822</v>
       </c>
       <c r="B323" s="1" t="d">
-        <v>2026-07-16T15:59:24.000Z</v>
+        <v>2026-07-21T09:48:14.000Z</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>INC000000150036</v>
+        <v>INC000000149860</v>
       </c>
       <c r="B324" s="1" t="d">
-        <v>2026-07-16T07:28:43.999Z</v>
+        <v>2026-07-16T15:59:24.000Z</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>INC000000149964</v>
+        <v>INC000000150036</v>
       </c>
       <c r="B325" s="1" t="d">
-        <v>2026-07-15T15:21:53.000Z</v>
+        <v>2026-07-16T07:28:43.999Z</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>WO0000000303232</v>
+        <v>INC000000149964</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2026-07-17T17:20:56.999Z</v>
+        <v>2026-07-15T15:21:53.000Z</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>INC000000150141</v>
+        <v>WO0000000303232</v>
       </c>
       <c r="B327" s="1" t="d">
-        <v>2026-07-15T16:30:22.000Z</v>
+        <v>2026-07-17T17:20:56.999Z</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>INC000000150288</v>
+        <v>INC000000150141</v>
       </c>
       <c r="B328" s="1" t="d">
-        <v>2026-07-10T12:39:00.000Z</v>
+        <v>2026-07-15T16:30:22.000Z</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>INC000000150197</v>
+        <v>INC000000150288</v>
       </c>
       <c r="B329" s="1" t="d">
-        <v>2026-07-21T10:51:58.000Z</v>
+        <v>2026-07-10T12:39:00.000Z</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>INC000000150475</v>
+        <v>INC000000150197</v>
       </c>
       <c r="B330" s="1" t="d">
-        <v>2026-07-16T08:36:47.000Z</v>
+        <v>2026-07-21T10:51:58.000Z</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>WO0000000304256</v>
+        <v>INC000000150475</v>
       </c>
       <c r="B331" s="1" t="d">
-        <v>2026-07-16T12:20:08.000Z</v>
+        <v>2026-07-16T08:36:47.000Z</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>WO0000000304437</v>
+        <v>WO0000000304256</v>
       </c>
       <c r="B332" s="1" t="d">
-        <v>2026-07-16T12:22:04.999Z</v>
+        <v>2026-07-16T12:20:08.000Z</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>WO0000000304614</v>
+        <v>WO0000000304437</v>
       </c>
       <c r="B333" s="1" t="d">
-        <v>2026-07-16T12:25:00.000Z</v>
+        <v>2026-07-16T12:22:04.999Z</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>INC000000150547</v>
+        <v>WO0000000304614</v>
       </c>
       <c r="B334" s="1" t="d">
-        <v>2026-07-16T08:37:46.000Z</v>
+        <v>2026-07-16T12:25:00.000Z</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>WO0000000304990</v>
+        <v>INC000000150547</v>
       </c>
       <c r="B335" s="1" t="d">
-        <v>2026-07-15T10:54:42.999Z</v>
+        <v>2026-07-16T08:37:46.000Z</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>INC000000150732</v>
+        <v>WO0000000304990</v>
       </c>
       <c r="B336" s="1" t="d">
-        <v>2026-07-16T08:27:41.000Z</v>
+        <v>2026-07-15T10:54:42.999Z</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>WO0000000305312</v>
+        <v>INC000000150732</v>
       </c>
       <c r="B337" s="1" t="d">
-        <v>2026-07-15T11:26:08.000Z</v>
+        <v>2026-07-16T08:27:41.000Z</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305312</v>
       </c>
       <c r="B338" s="1" t="d">
-        <v>2026-07-15T13:10:05.000Z</v>
+        <v>2026-07-15T11:26:08.000Z</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>INC000000150882</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B339" s="1" t="d">
-        <v>2026-07-15T10:45:04.000Z</v>
+        <v>2026-07-15T13:10:05.000Z</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>WO0000000305349</v>
+        <v>INC000000150882</v>
       </c>
       <c r="B340" s="1" t="d">
-        <v>2026-07-14T12:21:19.000Z</v>
+        <v>2026-07-15T10:45:04.000Z</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000305349</v>
       </c>
       <c r="B341" s="1" t="d">
-        <v>2026-07-16T10:45:43.999Z</v>
+        <v>2026-07-14T12:21:19.000Z</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>WO0000000305815</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B342" s="1" t="d">
-        <v>2026-07-16T12:28:46.000Z</v>
+        <v>2026-07-16T10:45:43.999Z</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>WO0000000305843</v>
+        <v>WO0000000305815</v>
       </c>
       <c r="B343" s="1" t="d">
-        <v>2026-07-14T12:37:15.000Z</v>
+        <v>2026-07-16T12:28:46.000Z</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>WO0000000305743</v>
+        <v>WO0000000305843</v>
       </c>
       <c r="B344" s="1" t="d">
-        <v>2026-07-14T14:33:44.000Z</v>
+        <v>2026-07-14T12:37:15.000Z</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>INC000000151204</v>
+        <v>WO0000000305743</v>
       </c>
       <c r="B345" s="1" t="d">
-        <v>2026-07-14T12:46:36.000Z</v>
+        <v>2026-07-14T14:33:44.000Z</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>WO0000000305944</v>
+        <v>INC000000151204</v>
       </c>
       <c r="B346" s="1" t="d">
-        <v>2026-07-14T12:04:16.999Z</v>
+        <v>2026-07-14T12:46:36.000Z</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>INC000000151134</v>
+        <v>WO0000000305944</v>
       </c>
       <c r="B347" s="1" t="d">
-        <v>2026-07-14T10:49:05.000Z</v>
+        <v>2026-07-14T12:04:16.999Z</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>INC000000151151</v>
+        <v>INC000000151134</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2026-07-16T08:22:24.000Z</v>
+        <v>2026-07-14T10:49:05.000Z</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>WO0000000306190</v>
+        <v>INC000000151151</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2026-07-14T13:13:31.000Z</v>
+        <v>2026-07-16T08:22:24.000Z</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>WO0000000306290</v>
+        <v>WO0000000306190</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2026-07-14T16:17:28.999Z</v>
+        <v>2026-07-14T13:13:31.000Z</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>WO0000000306328</v>
+        <v>WO0000000306290</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2026-07-14T16:39:44.000Z</v>
+        <v>2026-07-14T16:17:28.999Z</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>INC000000151311</v>
+        <v>WO0000000306328</v>
       </c>
       <c r="B352" s="1" t="d">
-        <v>2026-07-16T09:35:09.000Z</v>
+        <v>2026-07-14T16:39:44.000Z</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>WO0000000306374</v>
+        <v>INC000000151311</v>
       </c>
       <c r="B353" s="1" t="d">
-        <v>2026-07-10T13:36:36.000Z</v>
+        <v>2026-07-16T09:35:09.000Z</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>WO0000000306439</v>
+        <v>WO0000000306374</v>
       </c>
       <c r="B354" s="1" t="d">
-        <v>2026-07-14T16:14:53.000Z</v>
+        <v>2026-07-10T13:36:36.000Z</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>WO0000000306534</v>
+        <v>WO0000000306439</v>
       </c>
       <c r="B355" s="1" t="d">
-        <v>2026-07-15T16:01:14.000Z</v>
+        <v>2026-07-14T16:14:53.000Z</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>INC000000151466</v>
+        <v>WO0000000306534</v>
       </c>
       <c r="B356" s="1" t="d">
-        <v>2026-07-14T15:33:23.000Z</v>
+        <v>2026-07-15T16:01:14.000Z</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>WO0000000304733</v>
+        <v>INC000000151466</v>
       </c>
       <c r="B357" s="1" t="d">
-        <v>2026-07-15T10:28:05.999Z</v>
+        <v>2026-07-14T15:33:23.000Z</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>WO0000000306648</v>
+        <v>INC000000151499</v>
       </c>
       <c r="B358" s="1" t="d">
-        <v>2026-07-16T11:20:21.000Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>INC000000151499</v>
+        <v>INC000000151525</v>
       </c>
       <c r="B359" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>INC000000151525</v>
+        <v>WO0000000306862</v>
       </c>
       <c r="B360" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-21T10:40:52.000Z</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>WO0000000306862</v>
+        <v>WO0000000306992</v>
       </c>
       <c r="B361" s="1" t="d">
-        <v>2026-07-21T10:40:52.000Z</v>
+        <v>2026-07-16T10:42:09.000Z</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>WO0000000306992</v>
+        <v>WO0000000307033</v>
       </c>
       <c r="B362" s="1" t="d">
-        <v>2026-07-16T10:42:09.000Z</v>
+        <v>2026-07-17T12:30:37.000Z</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>WO0000000307033</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B363" s="1" t="d">
-        <v>2026-07-17T12:30:37.000Z</v>
+        <v>2026-07-11T15:39:05.000Z</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000307106</v>
       </c>
       <c r="B364" s="1" t="d">
-        <v>2026-07-11T15:39:05.000Z</v>
+        <v>2026-07-11T16:22:34.000Z</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>WO0000000307106</v>
+        <v>WO0000000307093</v>
       </c>
       <c r="B365" s="1" t="d">
-        <v>2026-07-11T16:22:34.000Z</v>
+        <v>2026-07-14T07:58:26.000Z</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>WO0000000307093</v>
+        <v>WO0000000307237</v>
       </c>
       <c r="B366" s="1" t="d">
-        <v>2026-07-14T07:58:26.000Z</v>
+        <v>2026-07-14T08:00:43.999Z</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>WO0000000307237</v>
+        <v>INC000000151941</v>
       </c>
       <c r="B367" s="1" t="d">
-        <v>2026-07-14T08:00:43.999Z</v>
+        <v>2026-07-17T13:23:13.999Z</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>INC000000151941</v>
+        <v>INC000000151950</v>
       </c>
       <c r="B368" s="1" t="d">
-        <v>2026-07-17T13:23:13.999Z</v>
+        <v>2026-07-16T09:20:32.000Z</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>INC000000151950</v>
+        <v>WO0000000307368</v>
       </c>
       <c r="B369" s="1" t="d">
-        <v>2026-07-16T09:20:32.000Z</v>
+        <v>2026-07-21T09:55:05.000Z</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>WO0000000307368</v>
+        <v>WO0000000307397</v>
       </c>
       <c r="B370" s="1" t="d">
-        <v>2026-07-21T09:55:05.000Z</v>
+        <v>2026-07-15T09:56:22.000Z</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>WO0000000307397</v>
+        <v>WO0000000307437</v>
       </c>
       <c r="B371" s="1" t="d">
-        <v>2026-07-15T09:56:22.000Z</v>
+        <v>2026-07-21T08:19:28.999Z</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>WO0000000307437</v>
+        <v>INC000000151987</v>
       </c>
       <c r="B372" s="1" t="d">
-        <v>2026-07-21T08:19:28.999Z</v>
+        <v>2026-07-16T11:05:28.000Z</v>
       </c>
     </row>
     <row r="373">
@@ -3443,266 +3443,266 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>WO0000000307667</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B381" s="1" t="d">
-        <v>2026-07-21T08:39:56.000Z</v>
+        <v>2026-07-16T11:24:53.999Z</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>WO0000000307671</v>
+        <v>WO0000000307667</v>
       </c>
       <c r="B382" s="1" t="d">
-        <v>2026-07-17T09:44:19.000Z</v>
+        <v>2026-07-21T11:55:18.000Z</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>INC000000152124</v>
+        <v>WO0000000307671</v>
       </c>
       <c r="B383" s="1" t="d">
-        <v>2026-07-15T14:11:57.000Z</v>
+        <v>2026-07-21T11:59:26.000Z</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>WO0000000307701</v>
+        <v>INC000000152124</v>
       </c>
       <c r="B384" s="1" t="d">
-        <v>2026-07-17T09:50:26.000Z</v>
+        <v>2026-07-15T14:11:57.000Z</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>INC000000152132</v>
+        <v>WO0000000307701</v>
       </c>
       <c r="B385" s="1" t="d">
-        <v>2026-07-15T14:13:17.000Z</v>
+        <v>2026-07-17T09:50:26.000Z</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>INC000000152134</v>
+        <v>INC000000152132</v>
       </c>
       <c r="B386" s="1" t="d">
-        <v>2026-07-15T14:13:50.000Z</v>
+        <v>2026-07-15T14:13:17.000Z</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>INC000000152138</v>
+        <v>INC000000152134</v>
       </c>
       <c r="B387" s="1" t="d">
-        <v>2026-07-15T14:16:43.999Z</v>
+        <v>2026-07-15T14:13:50.000Z</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>INC000000152139</v>
+        <v>INC000000152138</v>
       </c>
       <c r="B388" s="1" t="d">
-        <v>2026-07-15T14:17:19.000Z</v>
+        <v>2026-07-15T14:16:43.999Z</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>WO0000000307733</v>
+        <v>INC000000152139</v>
       </c>
       <c r="B389" s="1" t="d">
-        <v>2026-07-17T11:13:13.999Z</v>
+        <v>2026-07-15T14:17:19.000Z</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>WO0000000307735</v>
+        <v>WO0000000307733</v>
       </c>
       <c r="B390" s="1" t="d">
-        <v>2026-07-21T09:55:06.000Z</v>
+        <v>2026-07-17T11:13:13.999Z</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>WO0000000307812</v>
+        <v>WO0000000307735</v>
       </c>
       <c r="B391" s="1" t="d">
-        <v>2026-07-21T10:09:34.000Z</v>
+        <v>2026-07-21T09:55:06.000Z</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>INC000000152155</v>
+        <v>WO0000000307812</v>
       </c>
       <c r="B392" s="1" t="d">
-        <v>2026-07-15T16:57:39.000Z</v>
+        <v>2026-07-21T10:09:34.000Z</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>INC000000152156</v>
+        <v>INC000000152155</v>
       </c>
       <c r="B393" s="1" t="d">
-        <v>2026-07-15T14:18:27.000Z</v>
+        <v>2026-07-15T16:57:39.000Z</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>INC000000152158</v>
+        <v>INC000000152156</v>
       </c>
       <c r="B394" s="1" t="d">
-        <v>2026-07-15T14:19:58.000Z</v>
+        <v>2026-07-15T14:18:27.000Z</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>INC000000152073</v>
+        <v>INC000000152158</v>
       </c>
       <c r="B395" s="1" t="d">
-        <v>2026-07-16T09:23:53.000Z</v>
+        <v>2026-07-15T14:19:58.000Z</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>WO0000000307834</v>
+        <v>INC000000152073</v>
       </c>
       <c r="B396" s="1" t="d">
-        <v>2026-07-21T08:01:01.000Z</v>
+        <v>2026-07-16T09:23:53.000Z</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>WO0000000307769</v>
+        <v>WO0000000307834</v>
       </c>
       <c r="B397" s="1" t="d">
-        <v>2026-07-14T17:17:47.000Z</v>
+        <v>2026-07-21T08:01:01.000Z</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>WO0000000307852</v>
+        <v>WO0000000307769</v>
       </c>
       <c r="B398" s="1" t="d">
-        <v>2026-07-17T12:30:37.999Z</v>
+        <v>2026-07-14T17:17:47.000Z</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>WO0000000307923</v>
+        <v>WO0000000307852</v>
       </c>
       <c r="B399" s="1" t="d">
-        <v>2026-07-16T09:23:33.000Z</v>
+        <v>2026-07-17T12:30:37.999Z</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>WO0000000308004</v>
+        <v>WO0000000307923</v>
       </c>
       <c r="B400" s="1" t="d">
-        <v>2026-07-17T10:04:39.999Z</v>
+        <v>2026-07-16T09:23:33.000Z</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>INC000000152308</v>
+        <v>WO0000000308004</v>
       </c>
       <c r="B401" s="1" t="d">
-        <v>2026-07-16T09:37:19.000Z</v>
+        <v>2026-07-21T11:04:02.000Z</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>INC000000152320</v>
+        <v>INC000000152308</v>
       </c>
       <c r="B402" s="1" t="d">
-        <v>2026-07-15T10:29:52.000Z</v>
+        <v>2026-07-16T09:37:19.000Z</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>WO0000000307976</v>
+        <v>INC000000152320</v>
       </c>
       <c r="B403" s="1" t="d">
-        <v>2026-07-21T10:33:10.999Z</v>
+        <v>2026-07-15T10:29:52.000Z</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>WO0000000307981</v>
+        <v>WO0000000307976</v>
       </c>
       <c r="B404" s="1" t="d">
-        <v>2026-07-21T09:32:12.999Z</v>
+        <v>2026-07-21T10:33:10.999Z</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>WO0000000307984</v>
+        <v>WO0000000307981</v>
       </c>
       <c r="B405" s="1" t="d">
-        <v>2026-07-17T14:08:18.000Z</v>
+        <v>2026-07-21T09:32:12.999Z</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>INC000000152339</v>
+        <v>WO0000000307984</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2026-07-16T08:34:04.000Z</v>
+        <v>2026-07-17T14:08:18.000Z</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>WO0000000308206</v>
+        <v>INC000000152339</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-16T08:34:04.000Z</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>WO0000000308218</v>
+        <v>WO0000000308206</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-17T15:50:26.999Z</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>WO0000000308157</v>
+        <v>WO0000000308218</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2026-07-17T13:56:08.000Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>WO0000000308163</v>
+        <v>WO0000000308157</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2026-07-16T09:05:24.000Z</v>
+        <v>2026-07-21T11:40:53.000Z</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>INC000000152358</v>
+        <v>WO0000000308163</v>
       </c>
       <c r="B411" s="1" t="d">
-        <v>2026-07-16T09:12:05.999Z</v>
+        <v>2026-07-16T09:05:24.000Z</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>WO0000000308194</v>
+        <v>INC000000152358</v>
       </c>
       <c r="B412" s="1" t="d">
-        <v>2026-07-17T14:53:25.999Z</v>
+        <v>2026-07-16T09:12:05.999Z</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>WO0000000308255</v>
+        <v>WO0000000308194</v>
       </c>
       <c r="B413" s="1" t="d">
-        <v>2026-07-17T15:17:47.000Z</v>
+        <v>2026-07-17T14:53:25.999Z</v>
       </c>
     </row>
     <row r="414">
@@ -3835,6348 +3835,6428 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>WO0000000308379</v>
+        <v>WO0000000308475</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2026-07-15T17:07:55.000Z</v>
+        <v>2026-07-21T10:16:01.000Z</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>WO0000000308383</v>
+        <v>WO0000000308379</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-21T10:16:02.000Z</v>
+        <v>2026-07-15T17:07:55.000Z</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>WO0000000308398</v>
+        <v>WO0000000308478</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-16T08:57:27.000Z</v>
+        <v>2026-07-21T10:16:02.000Z</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>WO0000000308399</v>
+        <v>WO0000000308383</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-16T09:52:14.999Z</v>
+        <v>2026-07-21T10:16:02.000Z</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>WO0000000308487</v>
+        <v>WO0000000308398</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-15T22:21:47.000Z</v>
+        <v>2026-07-16T08:57:27.000Z</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>WO0000000308503</v>
+        <v>WO0000000308399</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2026-07-21T10:01:16.000Z</v>
+        <v>2026-07-16T09:52:14.999Z</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>WO0000000308493</v>
+        <v>WO0000000308487</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-21T10:16:04.000Z</v>
+        <v>2026-07-15T22:21:47.000Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>WO0000000308506</v>
+        <v>WO0000000308503</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-21T10:16:03.000Z</v>
+        <v>2026-07-21T10:01:16.000Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>INC000000152512</v>
+        <v>WO0000000308493</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-16T08:10:32.999Z</v>
+        <v>2026-07-21T10:16:04.000Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>INC000000152513</v>
+        <v>WO0000000308506</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-16T09:23:02.000Z</v>
+        <v>2026-07-21T10:16:03.000Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>WO0000000308552</v>
+        <v>INC000000152512</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-16T09:20:55.000Z</v>
+        <v>2026-07-16T08:10:32.999Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000308648</v>
+        <v>INC000000152513</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-17T15:09:40.000Z</v>
+        <v>2026-07-16T09:23:02.000Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000308552</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-16T09:22:57.000Z</v>
+        <v>2026-07-16T09:20:55.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-17T14:10:20.000Z</v>
+        <v>2026-07-21T11:10:08.000Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>WO0000000308661</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-17T14:16:26.000Z</v>
+        <v>2026-07-21T11:24:28.999Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>WO0000000308673</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-16T10:02:00.999Z</v>
+        <v>2026-07-21T11:55:19.000Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>WO0000000308679</v>
+        <v>WO0000000308661</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-17T14:36:57.000Z</v>
+        <v>2026-07-21T12:01:28.999Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>WO0000000308675</v>
+        <v>WO0000000308673</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-17T07:31:47.000Z</v>
+        <v>2026-07-16T10:02:00.999Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>WO0000000308685</v>
+        <v>WO0000000308679</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2026-07-16T10:12:45.000Z</v>
+        <v>2026-07-17T14:36:57.000Z</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>WO0000000308596</v>
+        <v>WO0000000308675</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-16T10:19:52.000Z</v>
+        <v>2026-07-17T07:31:47.000Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>WO0000000308701</v>
+        <v>WO0000000308685</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-16T10:22:52.000Z</v>
+        <v>2026-07-16T10:12:45.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308596</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-17T11:22:11.000Z</v>
+        <v>2026-07-16T10:19:52.000Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WO0000000308695</v>
+        <v>WO0000000308701</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-16T10:42:24.000Z</v>
+        <v>2026-07-16T10:22:52.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308696</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-16T10:40:08.000Z</v>
+        <v>2026-07-17T11:22:11.000Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>WO0000000308715</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-16T10:42:24.000Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-21T10:45:16.999Z</v>
+        <v>2026-07-16T10:40:08.000Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-16T10:46:41.000Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>INC000000139655</v>
+        <v>WO0000000308717</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-17T07:37:37.999Z</v>
+        <v>2026-07-21T10:45:16.999Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>INC000000139903</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-17T07:37:04.000Z</v>
+        <v>2026-07-16T10:46:41.000Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>INC000000140158</v>
+        <v>WO0000000308809</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-16T11:14:01.000Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>INC000000140820</v>
+        <v>WO0000000308816</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-17T07:35:42.000Z</v>
+        <v>2026-07-17T15:52:30.000Z</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>INC000000140821</v>
+        <v>WO0000000308750</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-17T07:34:57.000Z</v>
+        <v>2026-07-17T16:02:36.000Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>INC000000140767</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-17T08:38:07.000Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>INC000000141766</v>
+        <v>WO0000000308755</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-21T08:55:08.000Z</v>
+        <v>2026-07-16T11:35:09.000Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>INC000000142421</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-17T07:33:48.000Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>INC000000142515</v>
+        <v>INC000000139655</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-17T07:33:05.000Z</v>
+        <v>2026-07-17T07:37:37.999Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>WO0000000288110</v>
+        <v>INC000000139903</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-17T07:47:10.000Z</v>
+        <v>2026-07-17T07:37:04.000Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>INC000000143401</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-17T07:32:06.000Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>WO0000000292826</v>
+        <v>INC000000140820</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-17T07:30:34.000Z</v>
+        <v>2026-07-17T07:35:42.000Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>WO0000000295598</v>
+        <v>INC000000140821</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-17T07:34:57.000Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>WO0000000295716</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-16T11:47:42.999Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>WO0000000295975</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-17T07:46:27.000Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>INC000000146886</v>
+        <v>INC000000142421</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-16T13:10:02.999Z</v>
+        <v>2026-07-17T07:33:48.000Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>WO0000000296722</v>
+        <v>INC000000142515</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-17T07:44:32.000Z</v>
+        <v>2026-07-17T07:33:05.000Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>WO0000000296723</v>
+        <v>WO0000000288110</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-17T07:43:42.999Z</v>
+        <v>2026-07-17T07:47:10.000Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>WO0000000297151</v>
+        <v>INC000000143401</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-17T07:42:36.000Z</v>
+        <v>2026-07-17T07:32:06.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000297156</v>
+        <v>WO0000000292826</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-17T07:41:50.000Z</v>
+        <v>2026-07-17T07:30:34.000Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>WO0000000297160</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-17T07:40:23.999Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>WO0000000298838</v>
+        <v>WO0000000295975</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-20T23:28:38.000Z</v>
+        <v>2026-07-17T07:46:27.000Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000299920</v>
+        <v>WO0000000296722</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-17T14:59:50.999Z</v>
+        <v>2026-07-17T07:44:32.000Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>WO0000000300081</v>
+        <v>WO0000000296723</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-17T07:43:42.999Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>INC000000148888</v>
+        <v>WO0000000297151</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-17T07:42:36.000Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WO0000000300496</v>
+        <v>WO0000000297156</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-17T11:43:57.000Z</v>
+        <v>2026-07-17T07:41:50.000Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WO0000000302331</v>
+        <v>WO0000000297160</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-17T12:11:40.000Z</v>
+        <v>2026-07-17T07:40:23.999Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>WO0000000302520</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-17T15:04:39.000Z</v>
+        <v>2026-07-20T23:28:38.000Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>INC000000149827</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-17T14:03:04.000Z</v>
+        <v>2026-07-17T14:59:50.999Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>INC000000149757</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-16T16:04:01.999Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>INC000000149760</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-17T07:52:31.999Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WO0000000303117</v>
+        <v>WO0000000300496</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-21T10:43:30.000Z</v>
+        <v>2026-07-17T11:43:57.000Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>WO0000000303120</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-17T07:38:45.000Z</v>
+        <v>2026-07-17T12:11:40.000Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000302520</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-17T15:09:03.000Z</v>
+        <v>2026-07-17T15:04:39.000Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>WO0000000303244</v>
+        <v>INC000000149827</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-17T15:04:54.000Z</v>
+        <v>2026-07-17T14:03:04.000Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>WO0000000303459</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-17T11:09:28.999Z</v>
+        <v>2026-07-16T16:04:01.999Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>WO0000000303471</v>
+        <v>INC000000149760</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-16T14:24:05.000Z</v>
+        <v>2026-07-17T07:52:31.999Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-16T12:40:48.000Z</v>
+        <v>2026-07-21T10:43:30.000Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000303120</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-17T10:37:05.000Z</v>
+        <v>2026-07-17T07:38:45.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-17T10:37:33.000Z</v>
+        <v>2026-07-17T15:09:03.000Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>WO0000000305131</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-21T08:46:39.000Z</v>
+        <v>2026-07-17T15:04:54.000Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>WO0000000305138</v>
+        <v>WO0000000303459</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-17T11:09:28.999Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>INC000000150748</v>
+        <v>WO0000000303471</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-21T10:15:45.000Z</v>
+        <v>2026-07-16T14:24:05.000Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>WO0000000305336</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-16T12:40:48.000Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>INC000000150916</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-17T13:59:57.999Z</v>
+        <v>2026-07-17T10:37:05.000Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-17T18:15:37.999Z</v>
+        <v>2026-07-17T10:37:33.000Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>INC000000151036</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-16T16:01:20.999Z</v>
+        <v>2026-07-21T08:46:39.000Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>INC000000150958</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-17T07:47:57.999Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>WO0000000305863</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-21T08:44:19.000Z</v>
+        <v>2026-07-21T10:15:45.000Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>WO0000000305877</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-16T16:12:20.000Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>WO0000000305769</v>
+        <v>INC000000150916</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-17T10:37:57.000Z</v>
+        <v>2026-07-17T13:59:57.999Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>WO0000000305770</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-17T11:07:27.000Z</v>
+        <v>2026-07-17T18:15:37.999Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>INC000000151203</v>
+        <v>INC000000151036</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-16T16:01:20.999Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>WO0000000306127</v>
+        <v>INC000000150958</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-21T07:40:38.000Z</v>
+        <v>2026-07-17T07:47:57.999Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>INC000000151157</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-21T10:59:03.000Z</v>
+        <v>2026-07-21T08:44:19.000Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>INC000000151271</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-17T07:40:02.000Z</v>
+        <v>2026-07-21T11:48:06.999Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>WO0000000306256</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-17T14:41:03.000Z</v>
+        <v>2026-07-17T10:37:57.000Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>INC000000151313</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-17T11:07:27.000Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>WO0000000306718</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-17T10:39:36.000Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>WO0000000306721</v>
+        <v>WO0000000306127</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-17T15:11:14.000Z</v>
+        <v>2026-07-21T07:40:38.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>WO0000000306726</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-17T10:39:57.000Z</v>
+        <v>2026-07-21T10:59:03.000Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>INC000000151512</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-21T09:41:08.000Z</v>
+        <v>2026-07-17T07:40:02.000Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>WO0000000306799</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-17T08:21:12.999Z</v>
+        <v>2026-07-17T14:41:03.000Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>WO0000000306908</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-17T19:07:47.000Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>INC000000151527</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-17T16:34:54.000Z</v>
+        <v>2026-07-17T10:39:36.000Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>WO0000000306927</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-17T15:11:14.000Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-17T17:20:58.999Z</v>
+        <v>2026-07-17T10:39:57.000Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>WO0000000306877</v>
+        <v>INC000000151512</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-16T14:55:04.000Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000306890</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-17T08:21:12.999Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000306899</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-21T10:02:55.000Z</v>
+        <v>2026-07-17T19:07:47.000Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>WO0000000306988</v>
+        <v>INC000000151527</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-21T09:13:38.000Z</v>
+        <v>2026-07-17T16:34:54.000Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>WO0000000306994</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-16T15:19:33.999Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>INC000000151586</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-19T12:57:49.000Z</v>
+        <v>2026-07-17T17:20:58.999Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>WO0000000307224</v>
+        <v>WO0000000306877</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-16T16:04:39.999Z</v>
+        <v>2026-07-16T14:55:04.000Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-17T14:49:17.000Z</v>
+        <v>2026-07-17T14:42:13.999Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>INC000000151764</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-21T09:41:12.000Z</v>
+        <v>2026-07-21T11:53:12.999Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>WO0000000307513</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-21T10:03:23.000Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000306994</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-16T15:19:33.999Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>INC000000151987</v>
+        <v>INC000000151586</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-16T11:05:28.000Z</v>
+        <v>2026-07-19T12:57:49.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>WO0000000307483</v>
+        <v>WO0000000307224</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-21T09:13:03.000Z</v>
+        <v>2026-07-16T16:04:39.999Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-21T10:01:17.000Z</v>
+        <v>2026-07-17T14:49:17.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>WO0000000307613</v>
+        <v>INC000000151764</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-17T16:21:08.000Z</v>
+        <v>2026-07-21T09:41:12.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>INC000000152000</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-19T12:58:45.000Z</v>
+        <v>2026-07-21T10:03:23.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-21T09:13:03.000Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-16T11:24:53.999Z</v>
+        <v>2026-07-17T16:21:08.000Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>WO0000000307703</v>
+        <v>INC000000152000</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-17T17:21:00.000Z</v>
+        <v>2026-07-19T12:58:45.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>WO0000000307725</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-17T15:11:48.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>WO0000000307729</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-16T12:57:39.999Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>INC000000152145</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-17T19:20:59.000Z</v>
+        <v>2026-07-17T17:21:00.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000307820</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-21T09:49:48.000Z</v>
+        <v>2026-07-17T15:11:48.000Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>WO0000000307940</v>
+        <v>WO0000000307729</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-16T12:57:39.999Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>INC000000152212</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-17T19:20:59.000Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>WO0000000308040</v>
+        <v>WO0000000307820</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-21T09:49:48.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>WO0000000307968</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-16T15:02:29.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>WO0000000307970</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-16T16:55:20.000Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000308041</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-21T10:24:00.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>WO0000000308042</v>
+        <v>WO0000000307968</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-20T23:34:20.999Z</v>
+        <v>2026-07-16T15:02:29.000Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000307970</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-16T16:55:20.000Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308052</v>
+        <v>WO0000000308041</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-17T11:04:48.999Z</v>
+        <v>2026-07-21T10:24:00.000Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-20T23:34:20.999Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>WO0000000308105</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-20T23:29:29.999Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>INC000000152328</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-21T10:41:49.000Z</v>
+        <v>2026-07-17T11:04:48.999Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>WO0000000308075</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-20T23:26:07.000Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000308106</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-20T23:30:10.000Z</v>
+        <v>2026-07-20T23:29:29.999Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>WO0000000308107</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-20T23:27:09.999Z</v>
+        <v>2026-07-20T23:26:07.000Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-20T23:31:09.999Z</v>
+        <v>2026-07-21T11:15:57.000Z</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>WO0000000308086</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-07-21T09:28:00.000Z</v>
+        <v>2026-07-20T23:31:09.999Z</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>WO0000000308215</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-07-17T09:26:37.000Z</v>
+        <v>2026-07-21T09:28:00.000Z</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000308215</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-17T09:26:37.000Z</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-07-18T12:28:17.000Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>WO0000000308234</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-07-19T12:53:47.000Z</v>
+        <v>2026-07-18T12:28:17.000Z</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>INC000000152251</v>
+        <v>WO0000000308234</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-07-17T10:26:36.999Z</v>
+        <v>2026-07-19T12:53:47.000Z</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>INC000000152361</v>
+        <v>INC000000152251</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-07-17T16:39:09.000Z</v>
+        <v>2026-07-17T10:26:36.999Z</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>WO0000000308196</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-07-21T08:49:13.000Z</v>
+        <v>2026-07-17T16:39:09.000Z</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000308196</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-07-17T12:34:20.000Z</v>
+        <v>2026-07-21T08:49:13.000Z</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>WO0000000308249</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-07-17T13:34:27.999Z</v>
+        <v>2026-07-17T12:34:20.000Z</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>WO0000000308199</v>
+        <v>WO0000000308249</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-07-17T13:37:19.000Z</v>
+        <v>2026-07-17T13:34:27.999Z</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>INC000000152369</v>
+        <v>WO0000000308199</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-07-17T10:42:03.000Z</v>
+        <v>2026-07-17T13:37:19.000Z</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>WO0000000308306</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-07-18T09:01:38.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-07-18T12:40:57.999Z</v>
+        <v>2026-07-18T09:01:38.000Z</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>INC000000152378</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-07-17T09:05:30.000Z</v>
+        <v>2026-07-18T12:40:57.999Z</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>WO0000000308420</v>
+        <v>INC000000152378</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-07-18T12:08:23.000Z</v>
+        <v>2026-07-17T09:05:30.000Z</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>WO0000000308426</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-18T12:08:23.000Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308426</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-21T09:09:06.999Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>WO0000000308357</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-21T10:35:55.000Z</v>
+        <v>2026-07-21T09:09:06.999Z</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>INC000000152389</v>
+        <v>WO0000000308357</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-07-17T10:53:19.000Z</v>
+        <v>2026-07-21T10:35:55.000Z</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>WO0000000308461</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-21T09:25:59.000Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>WO0000000308475</v>
+        <v>WO0000000308461</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-21T10:16:01.000Z</v>
+        <v>2026-07-21T09:25:59.000Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>WO0000000308478</v>
+        <v>WO0000000308495</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-21T10:16:02.000Z</v>
+        <v>2026-07-21T10:02:45.000Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>WO0000000308495</v>
+        <v>INC000000152419</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-21T10:02:45.000Z</v>
+        <v>2026-07-21T08:54:50.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>INC000000152419</v>
+        <v>INC000000152439</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-07-21T08:54:50.000Z</v>
+        <v>2026-07-16T13:12:03.000Z</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>INC000000152439</v>
+        <v>INC000000152517</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-16T13:12:03.000Z</v>
+        <v>2026-07-17T10:21:00.000Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>INC000000152517</v>
+        <v>INC000000152450</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-17T10:21:00.000Z</v>
+        <v>2026-07-17T13:17:48.000Z</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>INC000000152450</v>
+        <v>INC000000152537</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-07-17T13:17:48.000Z</v>
+        <v>2026-07-17T10:03:46.000Z</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>INC000000152537</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B592" s="1" t="d">
-        <v>2026-07-17T10:03:46.000Z</v>
+        <v>2026-07-21T11:34:44.999Z</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000152458</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-07-18T12:29:14.000Z</v>
+        <v>2026-07-21T10:45:45.000Z</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>INC000000152458</v>
+        <v>WO0000000308662</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-07-21T10:45:45.000Z</v>
+        <v>2026-07-16T14:23:41.000Z</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>WO0000000308662</v>
+        <v>WO0000000308585</v>
       </c>
       <c r="B595" s="1" t="d">
-        <v>2026-07-16T14:23:41.000Z</v>
+        <v>2026-07-16T14:22:46.000Z</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>WO0000000308585</v>
+        <v>INC000000152461</v>
       </c>
       <c r="B596" s="1" t="d">
-        <v>2026-07-16T14:22:46.000Z</v>
+        <v>2026-07-20T09:23:43.999Z</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>INC000000152461</v>
+        <v>WO0000000308698</v>
       </c>
       <c r="B597" s="1" t="d">
-        <v>2026-07-20T09:23:43.999Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>WO0000000308698</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B598" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B599" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-20T19:01:19.000Z</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-07-20T19:01:19.000Z</v>
+        <v>2026-07-21T10:18:10.000Z</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>WO0000000308723</v>
+        <v>INC000000152565</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-21T10:18:10.000Z</v>
+        <v>2026-07-21T07:47:38.999Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>INC000000152565</v>
+        <v>WO0000000308727</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-21T07:47:38.999Z</v>
+        <v>2026-07-21T10:49:39.999Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>WO0000000308727</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-21T10:49:39.999Z</v>
+        <v>2026-07-21T09:27:37.000Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-21T09:27:37.000Z</v>
+        <v>2026-07-17T15:18:13.000Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000308809</v>
+        <v>WO0000000308743</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-07-16T11:14:01.000Z</v>
+        <v>2026-07-17T15:54:32.000Z</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>INC000000152566</v>
+        <v>INC000000152477</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-17T15:18:13.000Z</v>
+        <v>2026-07-16T12:12:43.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>WO0000000308816</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-16T14:25:41.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>WO0000000308743</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-17T15:54:32.000Z</v>
+        <v>2026-07-21T09:29:46.000Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>INC000000152477</v>
+        <v>WO0000000308851</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-16T12:12:43.000Z</v>
+        <v>2026-07-17T16:37:20.999Z</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>WO0000000308750</v>
+        <v>INC000000152486</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-07-17T16:02:36.000Z</v>
+        <v>2026-07-21T07:42:45.999Z</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000308860</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-07-17T08:38:07.000Z</v>
+        <v>2026-07-17T16:51:40.000Z</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>WO0000000308754</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-07-16T14:25:41.000Z</v>
+        <v>2026-07-21T11:46:55.000Z</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>WO0000000308755</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-07-16T11:35:09.000Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000308868</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-21T08:27:45.999Z</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>WO0000000308834</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-07-21T09:29:46.000Z</v>
+        <v>2026-07-16T14:39:36.999Z</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>WO0000000308851</v>
+        <v>INC000000152496</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-07-17T16:37:20.999Z</v>
+        <v>2026-07-17T18:33:44.000Z</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>INC000000152486</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-07-21T07:42:45.999Z</v>
+        <v>2026-07-21T10:58:56.000Z</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>WO0000000308860</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-07-17T16:51:40.000Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000152594</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-07-21T10:54:29.000Z</v>
+        <v>2026-07-20T13:46:11.000Z</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>INC000000152586</v>
+        <v>WO0000000308905</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-07-17T10:46:28.000Z</v>
+        <v>2026-07-21T09:36:24.000Z</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>WO0000000308868</v>
+        <v>WO0000000308880</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-07-21T08:27:45.999Z</v>
+        <v>2026-07-21T09:38:28.000Z</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>WO0000000308873</v>
+        <v>WO0000000308917</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-07-16T14:39:36.999Z</v>
+        <v>2026-07-17T07:59:19.999Z</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>INC000000152496</v>
+        <v>WO0000000308919</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-07-17T18:33:44.000Z</v>
+        <v>2026-07-21T10:07:31.000Z</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>WO0000000308794</v>
+        <v>WO0000000308923</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-07-21T10:58:56.000Z</v>
+        <v>2026-07-21T11:52:59.000Z</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>INC000000152591</v>
+        <v>WO0000000308895</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-07-17T11:00:29.999Z</v>
+        <v>2026-07-21T11:27:56.999Z</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>INC000000152594</v>
+        <v>WO0000000309001</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-07-20T13:46:11.000Z</v>
+        <v>2026-07-21T10:26:28.000Z</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>WO0000000308905</v>
+        <v>WO0000000309004</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-07-21T09:36:24.000Z</v>
+        <v>2026-07-21T10:26:28.000Z</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>WO0000000308880</v>
+        <v>WO0000000308899</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-07-21T09:38:28.000Z</v>
+        <v>2026-07-21T10:49:36.000Z</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>WO0000000308917</v>
+        <v>WO0000000308926</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-07-17T07:59:19.999Z</v>
+        <v>2026-07-21T11:31:06.000Z</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>WO0000000308918</v>
+        <v>WO0000000309009</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-07-21T10:05:26.000Z</v>
+        <v>2026-07-21T10:34:42.000Z</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>WO0000000308919</v>
+        <v>WO0000000309002</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-07-21T10:07:31.000Z</v>
+        <v>2026-07-16T15:07:58.000Z</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>WO0000000308923</v>
+        <v>WO0000000309011</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-07-21T09:17:59.000Z</v>
+        <v>2026-07-21T11:40:57.000Z</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>INC000000152608</v>
+        <v>INC000000152616</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-07-21T10:28:55.000Z</v>
+        <v>2026-07-17T09:51:34.000Z</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>WO0000000308895</v>
+        <v>WO0000000308938</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-07-17T10:35:42.000Z</v>
+        <v>2026-07-16T15:31:18.000Z</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>WO0000000308896</v>
+        <v>WO0000000309018</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-07-21T10:24:24.000Z</v>
+        <v>2026-07-21T11:01:58.000Z</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>WO0000000309001</v>
+        <v>WO0000000309021</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-07-21T10:26:28.000Z</v>
+        <v>2026-07-21T11:44:57.000Z</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>WO0000000309004</v>
+        <v>INC000000152711</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-07-21T10:26:28.000Z</v>
+        <v>2026-07-16T16:04:14.000Z</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>WO0000000308899</v>
+        <v>WO0000000308947</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-07-21T10:49:36.000Z</v>
+        <v>2026-07-21T10:45:27.000Z</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>WO0000000308926</v>
+        <v>WO0000000309025</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-07-17T10:04:52.000Z</v>
+        <v>2026-07-16T15:47:35.000Z</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>WO0000000309009</v>
+        <v>WO0000000309028</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-07-21T10:34:42.000Z</v>
+        <v>2026-07-21T10:48:23.000Z</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>WO0000000309002</v>
+        <v>WO0000000309031</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-21T11:22:24.000Z</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>WO0000000309011</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B642" s="1" t="d">
-        <v>2026-07-17T10:44:02.999Z</v>
+        <v>2026-07-17T16:59:46.000Z</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>INC000000152616</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B643" s="1" t="d">
-        <v>2026-07-17T09:51:34.000Z</v>
+        <v>2026-07-16T16:05:14.000Z</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>WO0000000308938</v>
+        <v>WO0000000309039</v>
       </c>
       <c r="B644" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-21T11:34:46.000Z</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>WO0000000309018</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B645" s="1" t="d">
-        <v>2026-07-21T11:01:58.000Z</v>
+        <v>2026-07-17T16:15:11.000Z</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>WO0000000309021</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B646" s="1" t="d">
-        <v>2026-07-17T09:59:10.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>INC000000152711</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B647" s="1" t="d">
-        <v>2026-07-16T16:04:14.000Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>WO0000000309024</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B648" s="1" t="d">
-        <v>2026-07-16T15:43:10.000Z</v>
+        <v>2026-07-21T11:49:07.000Z</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>WO0000000308947</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B649" s="1" t="d">
-        <v>2026-07-21T10:45:27.000Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>WO0000000309026</v>
+        <v>WO0000000308967</v>
       </c>
       <c r="B650" s="1" t="d">
-        <v>2026-07-16T15:49:08.000Z</v>
+        <v>2026-07-21T10:04:47.000Z</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>WO0000000309025</v>
+        <v>INC000000152630</v>
       </c>
       <c r="B651" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-21T07:35:42.000Z</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>WO0000000309028</v>
+        <v>WO0000000309044</v>
       </c>
       <c r="B652" s="1" t="d">
-        <v>2026-07-21T10:48:23.000Z</v>
+        <v>2026-07-21T11:57:24.000Z</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B653" s="1" t="d">
-        <v>2026-07-16T15:52:24.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B654" s="1" t="d">
-        <v>2026-07-17T16:59:46.000Z</v>
+        <v>2026-07-21T12:03:35.000Z</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>WO0000000309036</v>
+        <v>WO0000000308970</v>
       </c>
       <c r="B655" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-16T16:38:04.000Z</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B656" s="1" t="d">
-        <v>2026-07-17T08:39:45.999Z</v>
+        <v>2026-07-16T16:43:04.000Z</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B657" s="1" t="d">
-        <v>2026-07-17T16:15:11.000Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>INC000000152628</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B658" s="1" t="d">
-        <v>2026-07-17T10:44:38.000Z</v>
+        <v>2026-07-17T07:16:12.000Z</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>WO0000000309041</v>
+        <v>WO0000000309052</v>
       </c>
       <c r="B659" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-21T10:20:14.999Z</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000308984</v>
       </c>
       <c r="B660" s="1" t="d">
-        <v>2026-07-18T14:29:17.000Z</v>
+        <v>2026-07-16T17:10:27.000Z</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>WO0000000308966</v>
+        <v>WO0000000309060</v>
       </c>
       <c r="B661" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-21T11:52:59.000Z</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>WO0000000308967</v>
+        <v>WO0000000309062</v>
       </c>
       <c r="B662" s="1" t="d">
-        <v>2026-07-21T10:04:47.000Z</v>
+        <v>2026-07-17T10:25:11.000Z</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>INC000000152630</v>
+        <v>WO0000000309063</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-21T07:35:42.000Z</v>
+        <v>2026-07-21T12:01:39.000Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-16T16:26:35.999Z</v>
+        <v>2026-07-21T07:53:18.000Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-16T19:52:29.999Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000305262</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-16T16:32:21.000Z</v>
+        <v>2026-07-17T07:53:28.999Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>WO0000000309047</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-16T16:37:18.000Z</v>
+        <v>2026-07-16T19:32:50.000Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>WO0000000308970</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-16T16:38:04.000Z</v>
+        <v>2026-07-21T07:53:32.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>WO0000000308975</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-16T16:43:04.000Z</v>
+        <v>2026-07-16T19:42:22.000Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>WO0000000309050</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-17T07:16:12.000Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000309052</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-21T10:20:14.999Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>WO0000000308984</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-16T17:10:27.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000309060</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-16T22:04:20.000Z</v>
+        <v>2026-07-17T10:15:24.000Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000309062</v>
+        <v>WO0000000309082</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-17T10:25:11.000Z</v>
+        <v>2026-07-17T09:36:16.000Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>WO0000000309063</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-16T17:31:20.000Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>WO0000000308986</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-21T07:53:18.000Z</v>
+        <v>2026-07-17T06:53:11.000Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>WO0000000308987</v>
+        <v>WO0000000309097</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-16T19:52:29.999Z</v>
+        <v>2026-07-17T08:03:06.999Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>WO0000000305262</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-17T07:53:28.999Z</v>
+        <v>2026-07-17T08:06:35.000Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000309073</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-16T19:32:50.000Z</v>
+        <v>2026-07-17T07:45:37.999Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>INC000000152643</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-21T07:53:32.000Z</v>
+        <v>2026-07-17T08:07:23.000Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-16T19:42:22.000Z</v>
+        <v>2026-07-21T09:04:31.000Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000309077</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-17T11:36:59.000Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>WO0000000309079</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-17T12:44:26.000Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>WO0000000308996</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>WO0000000308997</v>
+        <v>INC000000152746</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-21T09:47:10.000Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>WO0000000308999</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-17T10:15:24.000Z</v>
+        <v>2026-07-17T08:54:14.000Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000309082</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-17T09:36:16.000Z</v>
+        <v>2026-07-17T08:54:36.999Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>WO0000000309101</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-18T12:40:15.000Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>INC000000152733</v>
+        <v>WO0000000309226</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-17T08:58:32.999Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>INC000000152653</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-18T16:16:07.999Z</v>
+        <v>2026-07-21T10:52:02.000Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000309097</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-17T08:03:06.999Z</v>
+        <v>2026-07-17T09:57:18.999Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>INC000000152737</v>
+        <v>INC000000152673</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-17T08:06:35.000Z</v>
+        <v>2026-07-21T08:52:59.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>WO0000000309124</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-17T07:45:37.999Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>INC000000152739</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-17T09:20:05.999Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>WO0000000309207</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-17T08:07:23.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000309131</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-17T08:12:37.000Z</v>
+        <v>2026-07-17T14:47:59.000Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>WO0000000309212</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-17T15:11:51.000Z</v>
+        <v>2026-07-17T09:26:58.999Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>WO0000000309136</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-21T09:04:31.000Z</v>
+        <v>2026-07-21T10:42:34.000Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-17T11:36:59.000Z</v>
+        <v>2026-07-17T15:50:55.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>INC000000152663</v>
+        <v>WO0000000309246</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-17T12:44:26.000Z</v>
+        <v>2026-07-17T09:32:32.000Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>INC000000152664</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T09:36:30.000Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>INC000000152746</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-21T09:47:10.000Z</v>
+        <v>2026-07-17T09:37:50.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-17T08:54:14.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>WO0000000309155</v>
+        <v>WO0000000309249</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-17T08:54:36.999Z</v>
+        <v>2026-07-17T09:38:10.000Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>INC000000152668</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-18T12:40:15.000Z</v>
+        <v>2026-07-21T10:04:01.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>WO0000000309226</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-17T08:58:32.999Z</v>
+        <v>2026-07-21T08:45:24.000Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>WO0000000309231</v>
+        <v>WO0000000309251</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-21T10:52:02.000Z</v>
+        <v>2026-07-17T09:40:19.000Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-21T08:17:56.000Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>INC000000152673</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-21T08:52:59.000Z</v>
+        <v>2026-07-17T09:57:50.000Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-21T11:59:19.000Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-17T14:47:53.999Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>INC000000152674</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-21T11:58:05.000Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>WO0000000309164</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-17T14:47:59.000Z</v>
+        <v>2026-07-17T11:15:36.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-17T09:26:58.999Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>INC000000152678</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-21T10:42:34.000Z</v>
+        <v>2026-07-17T11:13:13.000Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>INC000000152679</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-17T15:50:55.000Z</v>
+        <v>2026-07-21T09:55:04.000Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>WO0000000309246</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-17T09:32:32.000Z</v>
+        <v>2026-07-17T10:18:38.000Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>WO0000000309168</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-17T09:36:30.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>WO0000000309170</v>
+        <v>INC000000152770</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-17T09:37:50.000Z</v>
+        <v>2026-07-17T10:27:03.000Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000309172</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B721" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-17T11:24:41.000Z</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>WO0000000309249</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-21T10:45:43.999Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>WO0000000309250</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-21T10:04:01.000Z</v>
+        <v>2026-07-21T10:37:55.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152691</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-21T08:45:24.000Z</v>
+        <v>2026-07-17T11:21:16.000Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000309251</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-17T09:40:19.000Z</v>
+        <v>2026-07-17T12:51:35.000Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-21T08:17:56.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-17T09:57:50.000Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309269</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-17T11:14:20.000Z</v>
+        <v>2026-07-21T10:34:42.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000309270</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-17T14:47:53.999Z</v>
+        <v>2026-07-17T16:48:27.000Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-17T11:11:39.000Z</v>
+        <v>2026-07-17T14:48:08.000Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>WO0000000309189</v>
+        <v>WO0000000309407</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-17T11:15:36.000Z</v>
+        <v>2026-07-17T10:43:38.999Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>WO0000000309258</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-19T12:51:55.999Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>WO0000000309259</v>
+        <v>WO0000000309409</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-17T11:13:13.000Z</v>
+        <v>2026-07-21T10:47:34.000Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>INC000000152768</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-21T09:55:04.000Z</v>
+        <v>2026-07-21T09:07:41.000Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>WO0000000309262</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-17T10:18:38.000Z</v>
+        <v>2026-07-17T10:48:35.999Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>INC000000152690</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-17T10:53:18.000Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>INC000000152770</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-17T10:27:03.000Z</v>
+        <v>2026-07-21T11:55:19.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>WO0000000309195</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-17T11:24:41.000Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>INC000000152772</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-21T10:45:43.999Z</v>
+        <v>2026-07-17T10:58:23.000Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-21T10:37:55.000Z</v>
+        <v>2026-07-21T10:46:30.999Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>INC000000152691</v>
+        <v>WO0000000309417</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-17T11:21:16.000Z</v>
+        <v>2026-07-17T11:02:34.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>WO0000000309199</v>
+        <v>INC000000152700</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-17T12:51:35.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>WO0000000309200</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-18T08:52:20.999Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-17T11:12:43.000Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>WO0000000309269</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-21T10:34:42.000Z</v>
+        <v>2026-07-17T11:15:48.000Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>WO0000000309270</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-17T16:48:27.000Z</v>
+        <v>2026-07-17T11:17:12.999Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>WO0000000309271</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-17T14:48:08.000Z</v>
+        <v>2026-07-17T14:48:17.000Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>INC000000152694</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-18T13:02:06.999Z</v>
+        <v>2026-07-17T11:21:58.000Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>WO0000000309407</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-21T09:14:29.000Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>INC000000152777</v>
+        <v>WO0000000309432</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-19T12:51:55.999Z</v>
+        <v>2026-07-21T11:26:35.000Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>WO0000000309409</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-21T10:47:34.000Z</v>
+        <v>2026-07-17T11:26:05.999Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309299</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-21T09:07:41.000Z</v>
+        <v>2026-07-17T11:28:13.000Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-17T10:48:35.999Z</v>
+        <v>2026-07-21T10:21:20.000Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-17T10:53:18.000Z</v>
+        <v>2026-07-21T09:27:50.000Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309439</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-17T12:28:53.000Z</v>
+        <v>2026-07-21T11:34:46.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>WO0000000309282</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-17T15:38:05.000Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>WO0000000309413</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-17T10:58:23.000Z</v>
+        <v>2026-07-21T10:37:25.999Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>WO0000000309285</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-17T10:57:51.000Z</v>
+        <v>2026-07-21T10:55:04.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>INC000000152802</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-21T10:46:30.999Z</v>
+        <v>2026-07-17T11:41:41.000Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>WO0000000309417</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-17T11:02:34.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>INC000000152700</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-17T15:32:46.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309444</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-18T08:52:20.999Z</v>
+        <v>2026-07-17T11:41:48.000Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-17T11:12:43.000Z</v>
+        <v>2026-07-21T10:23:15.000Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>INC000000152784</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-17T11:26:12.000Z</v>
+        <v>2026-07-17T11:53:25.999Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-17T11:15:48.000Z</v>
+        <v>2026-07-21T08:25:47.000Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-17T11:17:12.999Z</v>
+        <v>2026-07-21T10:24:15.999Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-17T14:48:17.000Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-17T11:21:58.000Z</v>
+        <v>2026-07-17T14:48:03.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-21T09:14:29.000Z</v>
+        <v>2026-07-17T15:45:57.000Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>WO0000000309432</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-17T11:29:50.000Z</v>
+        <v>2026-07-17T14:48:13.000Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>WO0000000309433</v>
+        <v>INC000000152797</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-17T11:26:05.999Z</v>
+        <v>2026-07-21T08:59:18.000Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>WO0000000309299</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-17T11:28:13.000Z</v>
+        <v>2026-07-18T08:52:31.000Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-21T10:21:20.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>WO0000000309438</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-21T09:27:50.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>WO0000000309439</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-17T11:59:55.999Z</v>
+        <v>2026-07-17T12:23:35.999Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>WO0000000309503</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-17T15:38:05.000Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>INC000000152789</v>
+        <v>INC000000152901</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-21T10:37:25.999Z</v>
+        <v>2026-07-21T10:47:15.000Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309466</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-21T10:55:04.000Z</v>
+        <v>2026-07-21T10:22:48.000Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309525</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-17T11:41:41.000Z</v>
+        <v>2026-07-17T16:15:45.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>WO0000000309501</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-17T17:44:41.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000309441</v>
+        <v>WO0000000309526</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-17T15:32:46.000Z</v>
+        <v>2026-07-21T08:25:19.000Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309444</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-17T11:41:48.000Z</v>
+        <v>2026-07-21T09:11:31.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>WO0000000309447</v>
+        <v>INC000000152814</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-21T10:23:15.000Z</v>
+        <v>2026-07-21T11:42:56.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>INC000000152810</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-21T07:51:23.000Z</v>
+        <v>2026-07-21T10:47:55.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309478</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-17T11:53:25.999Z</v>
+        <v>2026-07-17T15:55:47.000Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-21T08:25:47.000Z</v>
+        <v>2026-07-17T12:55:06.999Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309534</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-21T10:24:15.999Z</v>
+        <v>2026-07-17T13:00:45.000Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>WO0000000309513</v>
+        <v>INC000000152815</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T21:20:43.999Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-17T14:48:03.000Z</v>
+        <v>2026-07-21T11:54:16.999Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309488</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-17T15:45:57.000Z</v>
+        <v>2026-07-17T13:20:57.999Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>WO0000000309457</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-17T14:48:13.000Z</v>
+        <v>2026-07-21T08:46:11.000Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>INC000000152797</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-21T08:59:18.000Z</v>
+        <v>2026-07-18T01:16:50.999Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-18T08:52:31.000Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>WO0000000309514</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-21T10:39:57.000Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>WO0000000309462</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>WO0000000309465</v>
+        <v>WO0000000309545</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-17T12:23:35.999Z</v>
+        <v>2026-07-21T07:54:44.000Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>WO0000000309520</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-18T01:16:05.000Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>INC000000152901</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-21T10:47:15.000Z</v>
+        <v>2026-07-17T14:11:39.000Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000309466</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-21T10:22:48.000Z</v>
+        <v>2026-07-21T10:46:28.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>WO0000000309525</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-17T16:15:45.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>INC000000152903</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-17T17:44:41.000Z</v>
+        <v>2026-07-17T15:55:02.000Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000309526</v>
+        <v>INC000000152922</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-21T08:25:19.000Z</v>
+        <v>2026-07-21T07:10:12.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000309470</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-21T09:11:31.000Z</v>
+        <v>2026-07-17T14:30:26.000Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>INC000000152814</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-17T12:49:52.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-21T10:47:55.000Z</v>
+        <v>2026-07-21T10:51:05.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309478</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-17T15:55:47.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-17T12:55:06.999Z</v>
+        <v>2026-07-17T14:57:05.000Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>WO0000000309534</v>
+        <v>WO0000000309613</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-17T13:00:45.000Z</v>
+        <v>2026-07-17T15:01:59.000Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>INC000000152910</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-21T07:51:47.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>INC000000152815</v>
+        <v>WO0000000309559</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-17T21:20:43.999Z</v>
+        <v>2026-07-17T15:56:29.000Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>WO0000000309489</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-17T15:49:27.999Z</v>
+        <v>2026-07-18T08:45:42.000Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000309488</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-17T13:20:57.999Z</v>
+        <v>2026-07-17T15:57:48.000Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>INC000000152914</v>
+        <v>INC000000152931</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-21T08:46:11.000Z</v>
+        <v>2026-07-21T08:13:12.000Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>INC000000152913</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-18T01:16:50.999Z</v>
+        <v>2026-07-17T15:20:43.999Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000309487</v>
+        <v>WO0000000309563</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-17T15:24:26.000Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>WO0000000309497</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-21T10:39:57.000Z</v>
+        <v>2026-07-18T11:14:25.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>WO0000000309499</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-17T16:04:00.000Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>WO0000000309545</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-21T07:54:44.000Z</v>
+        <v>2026-07-17T15:31:50.999Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>INC000000152919</v>
+        <v>WO0000000309572</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-18T01:16:05.000Z</v>
+        <v>2026-07-21T08:34:49.000Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000309546</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>INC000000152824</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-21T10:46:28.000Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>INC000000152921</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>WO0000000309603</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-17T15:55:02.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>INC000000152922</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-21T07:10:12.000Z</v>
+        <v>2026-07-21T10:39:19.000Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>WO0000000309549</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-17T14:30:26.000Z</v>
+        <v>2026-07-17T16:25:00.000Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>INC000000152828</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-17T14:45:48.000Z</v>
+        <v>2026-07-18T06:53:20.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>WO0000000309551</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>WO0000000309609</v>
+        <v>WO0000000309635</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-21T10:51:05.000Z</v>
+        <v>2026-07-17T16:06:26.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000309553</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-17T14:57:05.000Z</v>
+        <v>2026-07-21T11:47:03.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>INC000000152927</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-17T15:58:26.000Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>WO0000000309613</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-17T15:01:59.000Z</v>
+        <v>2026-07-17T17:05:49.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-18T06:19:47.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000309559</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-17T15:56:29.000Z</v>
+        <v>2026-07-17T16:39:05.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>WO0000000309615</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-18T08:45:42.000Z</v>
+        <v>2026-07-18T12:55:19.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>WO0000000309616</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-17T15:57:48.000Z</v>
+        <v>2026-07-18T07:38:46.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-21T08:13:12.000Z</v>
+        <v>2026-07-18T13:55:17.000Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>WO0000000309618</v>
+        <v>INC000000152945</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-21T11:38:08.999Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000309563</v>
+        <v>WO0000000309643</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-21T12:04:37.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>INC000000152933</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-18T11:14:25.000Z</v>
+        <v>2026-07-21T10:09:45.000Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-17T16:04:00.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>WO0000000309572</v>
+        <v>WO0000000309648</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-21T08:34:49.000Z</v>
+        <v>2026-07-17T18:19:50.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-21T09:50:43.000Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000309574</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309655</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-21T09:15:18.000Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>WO0000000309626</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-21T10:39:19.000Z</v>
+        <v>2026-07-21T10:23:48.000Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000309627</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-17T16:25:00.000Z</v>
+        <v>2026-07-21T11:20:55.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>WO0000000309629</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-18T06:53:20.000Z</v>
+        <v>2026-07-21T11:13:56.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000309632</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-21T10:28:49.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>WO0000000309635</v>
+        <v>INC000000152846</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-17T16:06:26.000Z</v>
+        <v>2026-07-21T11:38:41.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-21T11:21:15.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>WO0000000309636</v>
+        <v>INC000000152950</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-21T10:08:02.000Z</v>
+        <v>2026-07-21T09:49:56.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>INC000000152838</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-17T18:11:18.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-17T17:05:49.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309598</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-18T06:19:47.000Z</v>
+        <v>2026-07-21T08:16:54.999Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>WO0000000309586</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-17T16:39:05.000Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>INC000000152939</v>
+        <v>WO0000000309600</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-18T12:55:19.000Z</v>
+        <v>2026-07-21T07:30:44.000Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>WO0000000309587</v>
+        <v>WO0000000309659</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-17T16:39:17.000Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>INC000000152944</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-18T07:38:46.000Z</v>
+        <v>2026-07-21T11:52:20.999Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>WO0000000309589</v>
+        <v>WO0000000309705</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-18T13:55:17.000Z</v>
+        <v>2026-07-21T12:03:05.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>INC000000152945</v>
+        <v>WO0000000309660</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-17T16:53:07.000Z</v>
+        <v>2026-07-21T12:02:41.000Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000309643</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-17T16:52:17.999Z</v>
+        <v>2026-07-21T11:50:05.000Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>WO0000000309592</v>
+        <v>INC000000152954</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-21T10:09:45.000Z</v>
+        <v>2026-07-18T10:44:32.000Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>WO0000000309593</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-21T09:28:09.000Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>WO0000000309647</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-21T09:05:18.000Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>WO0000000309648</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-17T18:19:50.000Z</v>
+        <v>2026-07-18T09:16:52.000Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-21T09:50:43.000Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>WO0000000309308</v>
+        <v>INC000000152957</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-21T07:44:56.000Z</v>
+        <v>2026-07-18T11:15:19.000Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>WO0000000309595</v>
+        <v>INC000000152854</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-17T21:32:15.999Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000309596</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000309655</v>
+        <v>WO0000000309667</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-21T09:15:18.000Z</v>
+        <v>2026-07-21T07:08:18.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>WO0000000309597</v>
+        <v>WO0000000309668</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-21T10:23:48.000Z</v>
+        <v>2026-07-21T09:29:44.000Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000309309</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-21T09:07:50.999Z</v>
+        <v>2026-07-21T07:55:12.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>INC000000152948</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-21T09:27:02.000Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>INC000000152845</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-21T10:28:49.000Z</v>
+        <v>2026-07-18T11:57:16.000Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>INC000000152846</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-17T17:43:39.999Z</v>
+        <v>2026-07-21T09:18:02.999Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>WO0000000309310</v>
+        <v>INC000000152869</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-21T09:12:25.000Z</v>
+        <v>2026-07-21T07:20:13.000Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>INC000000152950</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-21T09:49:56.000Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>INC000000152848</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-21T11:13:10.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>WO0000000309598</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-21T08:16:54.999Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>WO0000000309599</v>
+        <v>INC000000152879</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-18T08:11:58.000Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>WO0000000309600</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-21T07:30:44.000Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000309659</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-18T12:53:54.000Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>WO0000000309704</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-21T10:32:14.000Z</v>
+        <v>2026-07-21T10:48:40.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000309705</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-17T18:22:25.999Z</v>
+        <v>2026-07-18T08:48:11.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>WO0000000309707</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-21T08:26:12.000Z</v>
+        <v>2026-07-21T10:10:23.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>WO0000000309660</v>
+        <v>WO0000000309732</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-17T18:27:35.999Z</v>
+        <v>2026-07-18T09:10:30.000Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>INC000000152953</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-21T09:27:40.000Z</v>
+        <v>2026-07-21T07:56:14.999Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>INC000000152954</v>
+        <v>INC000000152888</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-18T10:44:32.000Z</v>
+        <v>2026-07-21T11:56:31.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>INC000000152955</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-21T09:28:09.000Z</v>
+        <v>2026-07-21T10:00:54.000Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000309664</v>
+        <v>WO0000000309698</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-18T10:07:47.000Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>INC000000152956</v>
+        <v>INC000000152986</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-18T09:16:52.000Z</v>
+        <v>2026-07-21T08:16:08.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>WO0000000309666</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-18T10:49:11.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>INC000000152957</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-18T11:15:19.000Z</v>
+        <v>2026-07-21T10:41:02.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>INC000000152854</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-17T21:32:15.999Z</v>
+        <v>2026-07-21T07:32:12.000Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>WO0000000309714</v>
+        <v>WO0000000309802</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-21T09:30:57.000Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>WO0000000309667</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-21T07:08:18.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>WO0000000309668</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-21T09:29:44.000Z</v>
+        <v>2026-07-20T19:05:32.000Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>WO0000000309669</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-21T07:55:12.000Z</v>
+        <v>2026-07-20T19:04:33.999Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>INC000000152856</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-20T19:03:52.000Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>INC000000152863</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-18T11:32:43.000Z</v>
+        <v>2026-07-20T19:04:20.000Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>INC000000152866</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-18T11:57:16.000Z</v>
+        <v>2026-07-21T11:12:41.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000309671</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-21T09:18:02.999Z</v>
+        <v>2026-07-21T11:34:51.000Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>INC000000152869</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-21T07:20:13.000Z</v>
+        <v>2026-07-21T11:11:58.999Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>INC000000152873</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-21T07:32:42.999Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>INC000000152971</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-21T10:48:40.999Z</v>
+        <v>2026-07-21T07:33:22.000Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>INC000000152878</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-18T08:12:08.000Z</v>
+        <v>2026-07-21T10:52:04.000Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>WO0000000309682</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>WO0000000309686</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>INC000000152879</v>
+        <v>INC000000152900</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-21T08:04:18.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000309689</v>
+        <v>WO0000000309815</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-21T09:12:13.999Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000153006</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-18T12:53:54.000Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>INC000000152883</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-21T10:48:40.000Z</v>
+        <v>2026-07-21T07:19:30.000Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>WO0000000309692</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-18T08:48:11.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>INC000000152981</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-21T10:10:23.000Z</v>
+        <v>2026-07-21T10:18:57.000Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>WO0000000309732</v>
+        <v>INC000000153103</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-18T09:10:30.000Z</v>
+        <v>2026-07-21T08:04:41.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>WO0000000309697</v>
+        <v>INC000000153011</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-21T07:56:14.999Z</v>
+        <v>2026-07-21T10:52:54.000Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>INC000000152888</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-21T10:50:40.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>INC000000152985</v>
+        <v>INC000000153012</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-21T10:00:54.000Z</v>
+        <v>2026-07-21T08:03:57.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>WO0000000309698</v>
+        <v>INC000000153013</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-18T10:07:47.000Z</v>
+        <v>2026-07-21T07:19:23.999Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>INC000000152986</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-21T08:16:08.000Z</v>
+        <v>2026-07-21T07:31:56.999Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-18T10:49:11.000Z</v>
+        <v>2026-07-21T07:19:54.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>INC000000152989</v>
+        <v>INC000000153015</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-21T10:41:02.000Z</v>
+        <v>2026-07-21T10:29:31.000Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>INC000000152890</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-21T07:32:12.000Z</v>
+        <v>2026-07-21T07:30:09.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>WO0000000309802</v>
+        <v>INC000000153017</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-21T09:30:57.000Z</v>
+        <v>2026-07-18T15:26:50.000Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>WO0000000309803</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-20T19:05:32.000Z</v>
+        <v>2026-07-21T09:58:01.000Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>INC000000152994</v>
+        <v>WO0000000309769</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-20T19:04:33.999Z</v>
+        <v>2026-07-21T07:30:32.000Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>INC000000152892</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-20T19:03:52.000Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>INC000000152893</v>
+        <v>WO0000000309830</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-20T19:04:20.000Z</v>
+        <v>2026-07-21T11:24:34.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>WO0000000309804</v>
+        <v>INC000000153108</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-21T10:20:14.999Z</v>
+        <v>2026-07-21T07:53:45.000Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>WO0000000309805</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-21T10:56:34.000Z</v>
+        <v>2026-07-19T08:43:56.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>WO0000000309807</v>
+        <v>INC000000153020</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-21T10:21:19.000Z</v>
+        <v>2026-07-21T07:53:07.999Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-21T07:32:42.999Z</v>
+        <v>2026-07-21T07:08:54.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>INC000000153000</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-21T07:31:13.000Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-21T07:33:22.000Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>INC000000152898</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-21T10:52:04.000Z</v>
+        <v>2026-07-20T18:58:17.000Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>WO0000000309810</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-21T07:52:42.999Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>WO0000000309752</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-21T11:43:36.999Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>INC000000153003</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-21T10:59:38.999Z</v>
+        <v>2026-07-21T10:36:26.000Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>INC000000152900</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-21T08:04:18.000Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>WO0000000309815</v>
+        <v>INC000000153031</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-21T09:12:13.999Z</v>
+        <v>2026-07-21T09:40:02.000Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>INC000000153006</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>INC000000153101</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-21T07:19:30.000Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>WO0000000309816</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>INC000000153102</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-21T10:18:57.000Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>INC000000153103</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-21T08:04:41.000Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>INC000000153011</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-21T10:52:54.000Z</v>
+        <v>2026-07-21T07:41:05.999Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>WO0000000309759</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-21T07:47:06.000Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>INC000000153012</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-21T08:03:57.000Z</v>
+        <v>2026-07-21T07:58:21.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>INC000000153013</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-21T07:19:23.999Z</v>
+        <v>2026-07-21T08:01:28.000Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>WO0000000309825</v>
+        <v>INC000000153123</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-21T07:31:56.999Z</v>
+        <v>2026-07-21T07:54:40.000Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>INC000000153105</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-21T07:19:54.000Z</v>
+        <v>2026-07-20T08:42:15.000Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>INC000000153015</v>
+        <v>INC000000153125</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-21T10:29:31.000Z</v>
+        <v>2026-07-21T07:46:07.000Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>WO0000000309826</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-21T07:30:09.000Z</v>
+        <v>2026-07-21T09:45:18.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>INC000000153017</v>
+        <v>WO0000000309791</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-18T15:26:50.000Z</v>
+        <v>2026-07-21T12:02:04.000Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>WO0000000309768</v>
+        <v>WO0000000309792</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-20T14:10:35.999Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>INC000000153107</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-21T09:58:01.000Z</v>
+        <v>2026-07-21T09:36:30.999Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>WO0000000309769</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-21T07:30:32.000Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>WO0000000309829</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-21T08:43:23.000Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>WO0000000309830</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-21T09:26:50.000Z</v>
+        <v>2026-07-20T18:35:59.000Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>INC000000153108</v>
+        <v>WO0000000309794</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-21T07:53:45.000Z</v>
+        <v>2026-07-20T18:20:05.999Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>INC000000153019</v>
+        <v>WO0000000309843</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-19T08:43:56.000Z</v>
+        <v>2026-07-20T18:23:24.000Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>INC000000153020</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-21T07:53:07.999Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>INC000000153021</v>
+        <v>WO0000000309797</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-21T07:08:54.000Z</v>
+        <v>2026-07-20T19:09:36.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>INC000000153022</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-21T09:41:08.000Z</v>
+        <v>2026-07-21T10:57:08.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>INC000000153110</v>
+        <v>WO0000000309798</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-19T13:24:13.000Z</v>
+        <v>2026-07-21T07:04:25.000Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>INC000000153111</v>
+        <v>WO0000000309852</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-20T22:58:26.999Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>INC000000153025</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-19T13:28:43.999Z</v>
+        <v>2026-07-21T11:38:15.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>INC000000153024</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-19T13:24:41.999Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-20T18:58:17.000Z</v>
+        <v>2026-07-21T06:40:04.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>WO0000000309834</v>
+        <v>INC000000153050</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-21T07:52:42.999Z</v>
+        <v>2026-07-21T07:46:48.000Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-19T12:52:16.000Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>INC000000153028</v>
+        <v>INC000000153137</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-20T18:58:47.999Z</v>
+        <v>2026-07-21T07:03:14.999Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>INC000000153029</v>
+        <v>WO0000000309914</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-21T10:36:31.000Z</v>
+        <v>2026-07-21T07:20:13.999Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>WO0000000309779</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-21T07:09:08.000Z</v>
+        <v>2026-07-21T11:41:14.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-21T10:36:26.000Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>INC000000153121</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>INC000000153031</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-21T09:40:02.000Z</v>
+        <v>2026-07-21T09:37:42.999Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>WO0000000309780</v>
+        <v>INC000000153053</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-21T08:05:04.000Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>WO0000000309837</v>
+        <v>WO0000000309927</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-21T07:54:45.999Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>WO0000000309781</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-21T08:57:28.999Z</v>
+        <v>2026-07-21T12:00:33.000Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>WO0000000309783</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-21T08:34:57.999Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>WO0000000309838</v>
+        <v>WO0000000309867</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-21T08:13:16.000Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>INC000000153034</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-21T07:41:05.999Z</v>
+        <v>2026-07-21T07:57:56.999Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>INC000000153035</v>
+        <v>INC000000153060</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-21T07:47:06.000Z</v>
+        <v>2026-07-21T12:04:42.000Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>INC000000153036</v>
+        <v>INC000000153061</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-21T07:58:21.000Z</v>
+        <v>2026-07-21T10:54:42.999Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>INC000000153037</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-21T08:01:28.000Z</v>
+        <v>2026-07-21T10:38:36.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>INC000000153123</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-21T07:54:40.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-20T08:42:15.000Z</v>
+        <v>2026-07-21T10:15:53.000Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>INC000000153125</v>
+        <v>WO0000000309877</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-21T07:46:07.000Z</v>
+        <v>2026-07-21T08:15:48.000Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309878</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-21T09:45:18.000Z</v>
+        <v>2026-07-21T08:35:47.000Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>WO0000000309791</v>
+        <v>WO0000000309941</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-20T12:51:30.000Z</v>
+        <v>2026-07-21T09:14:35.999Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>WO0000000309792</v>
+        <v>WO0000000309879</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-20T14:10:35.999Z</v>
+        <v>2026-07-21T08:17:04.000Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>WO0000000309841</v>
+        <v>WO0000000309944</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-21T09:36:30.999Z</v>
+        <v>2026-07-21T11:26:10.999Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>WO0000000309842</v>
+        <v>INC000000153149</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T08:58:21.000Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>INC000000153128</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-21T08:43:23.000Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>WO0000000309793</v>
+        <v>INC000000153151</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-20T18:35:59.000Z</v>
+        <v>2026-07-21T09:13:22.999Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>WO0000000309794</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-20T18:20:05.999Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>WO0000000309843</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-20T18:23:24.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>WO0000000309848</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T11:32:54.000Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>WO0000000309797</v>
+        <v>INC000000153064</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-20T19:09:36.000Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>WO0000000309851</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-21T10:57:08.000Z</v>
+        <v>2026-07-21T09:45:12.999Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>WO0000000309798</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-21T07:04:25.000Z</v>
+        <v>2026-07-21T09:47:21.999Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>WO0000000309852</v>
+        <v>WO0000000309888</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-20T22:58:26.999Z</v>
+        <v>2026-07-21T08:44:29.999Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>WO0000000309853</v>
+        <v>WO0000000309950</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-21T05:54:59.000Z</v>
+        <v>2026-07-21T08:39:49.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309952</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-21T09:44:12.000Z</v>
+        <v>2026-07-21T08:33:13.000Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>WO0000000309902</v>
+        <v>WO0000000309953</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T08:41:50.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000309906</v>
+        <v>WO0000000309889</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-21T07:44:08.000Z</v>
+        <v>2026-07-21T08:33:25.000Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>WO0000000309909</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-21T07:43:47.000Z</v>
+        <v>2026-07-21T08:48:14.999Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>INC000000153047</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-21T08:19:35.999Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>INC000000153046</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-21T06:40:04.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>INC000000153134</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-21T08:16:43.999Z</v>
+        <v>2026-07-21T08:49:28.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>INC000000153050</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-21T07:46:48.000Z</v>
+        <v>2026-07-21T10:35:54.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>INC000000153048</v>
+        <v>INC000000153073</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T10:27:24.000Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>INC000000153137</v>
+        <v>INC000000153075</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-21T07:03:14.999Z</v>
+        <v>2026-07-21T09:12:07.000Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000309914</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-21T07:20:13.999Z</v>
+        <v>2026-07-21T09:22:48.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>INC000000153138</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-21T10:44:20.000Z</v>
+        <v>2026-07-21T10:28:57.999Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>INC000000153052</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>WO0000000309862</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T09:21:34.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>WO0000000309861</v>
+        <v>WO0000000310005</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T09:37:42.999Z</v>
+        <v>2026-07-21T09:32:59.000Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>INC000000153053</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-21T08:05:04.000Z</v>
+        <v>2026-07-21T11:27:26.000Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>INC000000153140</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-21T09:37:31.000Z</v>
+        <v>2026-07-21T09:20:33.000Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>WO0000000309927</v>
+        <v>INC000000153076</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T07:54:45.999Z</v>
+        <v>2026-07-21T11:26:27.000Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>INC000000153056</v>
+        <v>WO0000000310008</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-21T10:11:19.999Z</v>
+        <v>2026-07-21T11:05:13.999Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000309962</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-21T08:34:57.999Z</v>
+        <v>2026-07-21T09:15:42.999Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000309867</v>
+        <v>WO0000000310009</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-21T08:13:16.000Z</v>
+        <v>2026-07-21T10:38:41.000Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-21T07:57:56.999Z</v>
+        <v>2026-07-21T09:03:20.999Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>INC000000153060</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-21T08:01:12.999Z</v>
+        <v>2026-07-21T09:28:19.000Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>INC000000153061</v>
+        <v>WO0000000309967</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-21T10:54:42.999Z</v>
+        <v>2026-07-21T09:02:23.000Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>INC000000153062</v>
+        <v>WO0000000310013</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-21T10:38:36.000Z</v>
+        <v>2026-07-21T09:07:07.000Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>INC000000153143</v>
+        <v>WO0000000309973</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T11:05:17.000Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>INC000000153145</v>
+        <v>WO0000000310015</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-21T10:15:53.000Z</v>
+        <v>2026-07-21T09:27:41.000Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>WO0000000309876</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-21T08:19:59.000Z</v>
+        <v>2026-07-21T11:44:25.999Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>WO0000000309877</v>
+        <v>WO0000000310016</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-21T08:15:48.000Z</v>
+        <v>2026-07-21T11:47:23.999Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>WO0000000309875</v>
+        <v>INC000000153168</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-21T10:03:29.999Z</v>
+        <v>2026-07-21T09:54:40.000Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>WO0000000309878</v>
+        <v>WO0000000310017</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-21T08:35:47.000Z</v>
+        <v>2026-07-21T09:29:50.999Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>WO0000000309941</v>
+        <v>WO0000000310018</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-21T09:14:35.999Z</v>
+        <v>2026-07-21T09:18:47.000Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>WO0000000309879</v>
+        <v>WO0000000310019</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-21T08:17:04.000Z</v>
+        <v>2026-07-21T10:19:05.000Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>WO0000000309944</v>
+        <v>WO0000000309981</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-21T08:15:03.000Z</v>
+        <v>2026-07-21T11:22:20.000Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>INC000000153149</v>
+        <v>INC000000153165</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-21T08:58:21.000Z</v>
+        <v>2026-07-21T09:36:23.000Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>WO0000000309880</v>
+        <v>WO0000000310021</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T09:24:02.000Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>INC000000153151</v>
+        <v>INC000000153172</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-21T09:13:22.999Z</v>
+        <v>2026-07-21T09:52:46.999Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>WO0000000309945</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T10:36:09.999Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>WO0000000309946</v>
+        <v>INC000000153174</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T09:57:25.000Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>INC000000153147</v>
+        <v>INC000000153175</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-21T10:54:55.000Z</v>
+        <v>2026-07-21T09:28:26.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>INC000000153065</v>
+        <v>WO0000000309986</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-21T10:58:53.000Z</v>
+        <v>2026-07-21T09:28:28.999Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>INC000000153064</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T09:27:18.999Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>INC000000153153</v>
+        <v>WO0000000309975</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-21T09:45:12.999Z</v>
+        <v>2026-07-21T09:49:40.999Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>WO0000000309949</v>
+        <v>WO0000000309984</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-21T09:47:21.999Z</v>
+        <v>2026-07-21T09:31:44.000Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>WO0000000309888</v>
+        <v>WO0000000309987</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-21T08:44:29.999Z</v>
+        <v>2026-07-21T09:30:18.000Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>WO0000000309950</v>
+        <v>INC000000153177</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-21T08:39:49.000Z</v>
+        <v>2026-07-21T09:31:53.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>WO0000000309951</v>
+        <v>INC000000153080</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-21T09:40:47.000Z</v>
+        <v>2026-07-21T11:54:46.000Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>INC000000153068</v>
+        <v>INC000000153171</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-21T10:25:59.000Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>WO0000000309952</v>
+        <v>INC000000153176</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-21T08:33:13.000Z</v>
+        <v>2026-07-21T09:43:34.000Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>WO0000000309953</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-21T08:41:50.000Z</v>
+        <v>2026-07-21T09:37:20.999Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>WO0000000309889</v>
+        <v>WO0000000310025</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-21T08:33:25.000Z</v>
+        <v>2026-07-21T09:36:55.000Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>INC000000153070</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>INC000000153069</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-21T08:48:14.999Z</v>
+        <v>2026-07-21T09:40:19.000Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>INC000000153156</v>
+        <v>INC000000153181</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-21T08:39:24.000Z</v>
+        <v>2026-07-21T09:48:10.999Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>WO0000000309892</v>
+        <v>WO0000000309993</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-21T09:04:46.000Z</v>
+        <v>2026-07-21T09:41:07.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>WO0000000309954</v>
+        <v>INC000000153178</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T10:29:02.000Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>INC000000153071</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-21T08:50:05.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>INC000000153072</v>
+        <v>INC000000153082</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-21T08:49:28.000Z</v>
+        <v>2026-07-21T10:22:17.000Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>INC000000153157</v>
+        <v>WO0000000309991</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-21T08:51:40.000Z</v>
+        <v>2026-07-21T11:20:05.000Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>INC000000153159</v>
+        <v>INC000000153179</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-21T10:35:54.000Z</v>
+        <v>2026-07-21T09:46:47.000Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>INC000000153073</v>
+        <v>WO0000000309995</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-21T10:27:24.000Z</v>
+        <v>2026-07-21T10:01:19.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>INC000000153075</v>
+        <v>WO0000000305266</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-21T09:12:07.000Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>WO0000000310002</v>
+        <v>WO0000000309997</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-21T09:22:48.000Z</v>
+        <v>2026-07-21T11:45:35.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>WO0000000309957</v>
+        <v>WO0000000309998</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-21T10:28:57.999Z</v>
+        <v>2026-07-21T09:47:07.999Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>WO0000000309958</v>
+        <v>WO0000000309996</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-21T08:54:45.000Z</v>
+        <v>2026-07-21T09:49:05.999Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>WO0000000310004</v>
+        <v>INC000000153182</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-21T09:21:34.000Z</v>
+        <v>2026-07-21T10:35:39.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>WO0000000310005</v>
+        <v>WO0000000310000</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-21T09:32:59.000Z</v>
+        <v>2026-07-21T09:49:32.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>WO0000000309959</v>
+        <v>WO0000000309999</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-21T08:56:12.000Z</v>
+        <v>2026-07-21T09:50:29.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>WO0000000310006</v>
+        <v>WO0000000310102</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-21T09:20:33.000Z</v>
+        <v>2026-07-21T09:50:55.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>INC000000153076</v>
+        <v>WO0000000310033</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-21T10:25:21.000Z</v>
+        <v>2026-07-21T09:51:00.000Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>WO0000000310008</v>
+        <v>INC000000153185</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-21T08:58:48.000Z</v>
+        <v>2026-07-21T10:21:27.999Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>WO0000000309962</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-21T09:15:42.999Z</v>
+        <v>2026-07-21T09:55:33.000Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>WO0000000310009</v>
+        <v>WO0000000305268</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-21T10:38:41.000Z</v>
+        <v>2026-07-21T09:55:25.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>INC000000153074</v>
+        <v>INC000000153083</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-21T09:03:20.999Z</v>
+        <v>2026-07-21T10:29:05.000Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000309961</v>
+        <v>WO0000000310105</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-21T09:28:19.000Z</v>
+        <v>2026-07-21T10:09:51.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>WO0000000309967</v>
+        <v>INC000000153084</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-21T09:02:23.000Z</v>
+        <v>2026-07-21T10:22:19.000Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>WO0000000310013</v>
+        <v>WO0000000305269</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-21T09:07:07.000Z</v>
+        <v>2026-07-21T09:57:11.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>WO0000000309973</v>
+        <v>WO0000000310034</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-21T09:08:48.000Z</v>
+        <v>2026-07-21T10:02:08.000Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>WO0000000310015</v>
+        <v>WO0000000310106</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-21T09:27:41.000Z</v>
+        <v>2026-07-21T10:02:21.999Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>INC000000153079</v>
+        <v>WO0000000310107</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-21T09:12:25.000Z</v>
+        <v>2026-07-21T10:27:27.999Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>INC000000153164</v>
+        <v>WO0000000310036</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-21T09:16:22.000Z</v>
+        <v>2026-07-21T09:59:20.000Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153186</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-21T09:29:42.999Z</v>
+        <v>2026-07-21T11:41:02.000Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>WO0000000310016</v>
+        <v>WO0000000310109</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-21T09:14:48.000Z</v>
+        <v>2026-07-21T10:07:20.999Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>INC000000153168</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-21T09:54:40.000Z</v>
+        <v>2026-07-21T10:05:59.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>WO0000000310017</v>
+        <v>WO0000000310039</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-21T09:29:50.999Z</v>
+        <v>2026-07-21T11:49:30.000Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>WO0000000310018</v>
+        <v>INC000000153086</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-21T09:18:47.000Z</v>
+        <v>2026-07-21T10:23:37.999Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>INC000000153170</v>
+        <v>WO0000000310040</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-21T09:38:39.999Z</v>
+        <v>2026-07-21T10:09:05.000Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>WO0000000310019</v>
+        <v>INC000000153187</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-21T10:19:05.000Z</v>
+        <v>2026-07-21T10:25:14.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>WO0000000309981</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-21T09:19:50.000Z</v>
+        <v>2026-07-21T10:31:45.000Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>INC000000153165</v>
+        <v>INC000000153089</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-21T09:36:23.000Z</v>
+        <v>2026-07-21T10:28:35.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>WO0000000310021</v>
+        <v>WO0000000310045</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-21T09:24:02.000Z</v>
+        <v>2026-07-21T11:47:28.999Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>INC000000153172</v>
+        <v>INC000000153090</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-21T09:52:46.999Z</v>
+        <v>2026-07-21T10:32:06.999Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>INC000000153167</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-21T10:36:09.999Z</v>
+        <v>2026-07-21T11:44:30.999Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>INC000000153174</v>
+        <v>INC000000153091</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-21T09:57:25.000Z</v>
+        <v>2026-07-21T10:30:46.000Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>INC000000153175</v>
+        <v>INC000000153094</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-21T09:28:26.000Z</v>
+        <v>2026-07-21T10:34:10.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>WO0000000309986</v>
+        <v>WO0000000310114</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-21T09:28:28.999Z</v>
+        <v>2026-07-21T10:12:20.000Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>WO0000000309985</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-21T09:27:18.999Z</v>
+        <v>2026-07-21T10:13:41.000Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>WO0000000309975</v>
+        <v>WO0000000310113</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-21T09:49:40.999Z</v>
+        <v>2026-07-21T10:32:45.000Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>WO0000000309984</v>
+        <v>WO0000000310046</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-21T09:31:44.000Z</v>
+        <v>2026-07-21T10:13:36.000Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>WO0000000309987</v>
+        <v>INC000000153088</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-21T09:30:18.000Z</v>
+        <v>2026-07-21T10:17:32.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>INC000000153177</v>
+        <v>WO0000000310047</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-21T09:31:53.000Z</v>
+        <v>2026-07-21T10:14:06.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>INC000000153080</v>
+        <v>INC000000153188</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-21T10:53:24.000Z</v>
+        <v>2026-07-21T10:16:45.000Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>INC000000153171</v>
+        <v>WO0000000310118</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-21T10:25:59.000Z</v>
+        <v>2026-07-21T10:29:50.999Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>INC000000153176</v>
+        <v>INC000000153189</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-21T09:43:34.000Z</v>
+        <v>2026-07-21T11:21:36.999Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>WO0000000309990</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-21T09:37:20.999Z</v>
+        <v>2026-07-21T11:39:39.000Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>WO0000000310025</v>
+        <v>WO0000000310049</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-21T09:36:55.000Z</v>
+        <v>2026-07-21T10:20:08.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>WO0000000310026</v>
+        <v>INC000000153190</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T10:38:37.999Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>INC000000153180</v>
+        <v>WO0000000310050</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-21T09:57:04.000Z</v>
+        <v>2026-07-21T10:21:12.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>WO0000000310028</v>
+        <v>INC000000153191</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-21T09:40:19.000Z</v>
+        <v>2026-07-21T10:54:13.999Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>INC000000153181</v>
+        <v>INC000000153192</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-21T09:48:10.999Z</v>
+        <v>2026-07-21T10:26:23.999Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>WO0000000309993</v>
+        <v>WO0000000310051</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-21T09:41:07.000Z</v>
+        <v>2026-07-21T10:23:58.000Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>INC000000153178</v>
+        <v>INC000000153193</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-21T10:29:02.000Z</v>
+        <v>2026-07-21T10:25:57.999Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310120</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-21T10:35:25.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>INC000000153082</v>
+        <v>WO0000000310053</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-21T10:22:17.000Z</v>
+        <v>2026-07-21T10:27:39.999Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>WO0000000309991</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-21T09:45:25.999Z</v>
+        <v>2026-07-21T10:53:52.000Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>INC000000153179</v>
+        <v>INC000000153100</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-21T09:46:47.000Z</v>
+        <v>2026-07-21T10:36:40.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>WO0000000309995</v>
+        <v>INC000000153194</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-21T10:01:19.000Z</v>
+        <v>2026-07-21T10:31:29.999Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>WO0000000305266</v>
+        <v>INC000000153099</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
+        <v>2026-07-21T10:34:51.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>WO0000000309997</v>
+        <v>INC000000153095</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-21T10:09:06.999Z</v>
+        <v>2026-07-21T10:34:35.999Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>WO0000000309998</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-21T09:47:07.999Z</v>
+        <v>2026-07-21T10:52:52.999Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>WO0000000309996</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-21T09:49:05.999Z</v>
+        <v>2026-07-21T11:15:36.000Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>INC000000153182</v>
+        <v>INC000000153201</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-21T10:35:39.000Z</v>
+        <v>2026-07-21T10:39:28.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>WO0000000310000</v>
+        <v>WO0000000310123</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-21T09:49:32.000Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>WO0000000310024</v>
+        <v>WO0000000310055</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-21T09:50:13.000Z</v>
+        <v>2026-07-21T11:51:43.999Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>WO0000000309999</v>
+        <v>INC000000153202</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-21T09:50:29.000Z</v>
+        <v>2026-07-21T10:40:42.000Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>WO0000000310102</v>
+        <v>INC000000153197</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-21T09:50:55.000Z</v>
+        <v>2026-07-21T10:44:35.999Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>WO0000000310033</v>
+        <v>INC000000153203</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-21T09:51:00.000Z</v>
+        <v>2026-07-21T11:06:42.000Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>INC000000153185</v>
+        <v>WO0000000310127</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-21T10:21:27.999Z</v>
+        <v>2026-07-21T11:02:10.000Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>INC000000153183</v>
+        <v>INC000000153204</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-21T09:55:33.000Z</v>
+        <v>2026-07-21T11:17:56.000Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>WO0000000305268</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-21T09:55:25.000Z</v>
+        <v>2026-07-21T10:46:52.000Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>INC000000153083</v>
+        <v>WO0000000310061</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-21T10:29:05.000Z</v>
+        <v>2026-07-21T10:47:06.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>WO0000000310105</v>
+        <v>INC000000153205</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-21T10:09:51.000Z</v>
+        <v>2026-07-21T10:54:13.999Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>INC000000153084</v>
+        <v>WO0000000310130</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-21T10:22:19.000Z</v>
+        <v>2026-07-21T11:43:10.000Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>WO0000000305269</v>
+        <v>INC000000153210</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-21T09:57:11.000Z</v>
+        <v>2026-07-21T10:50:21.999Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>WO0000000310034</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-21T10:02:08.000Z</v>
+        <v>2026-07-21T11:06:54.000Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>WO0000000310106</v>
+        <v>INC000000153209</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-21T10:02:21.999Z</v>
+        <v>2026-07-21T11:43:04.000Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>WO0000000310107</v>
+        <v>INC000000153211</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-21T10:27:27.999Z</v>
+        <v>2026-07-21T10:52:02.000Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>WO0000000310036</v>
+        <v>WO0000000310135</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-21T09:59:20.000Z</v>
+        <v>2026-07-21T10:51:40.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>INC000000153186</v>
+        <v>INC000000153200</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-21T10:51:47.000Z</v>
+        <v>2026-07-21T11:03:32.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>WO0000000310109</v>
+        <v>WO0000000310136</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-21T10:07:20.999Z</v>
+        <v>2026-07-21T10:53:26.000Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>INC000000153184</v>
+        <v>WO0000000310133</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-21T10:05:59.000Z</v>
+        <v>2026-07-21T10:56:06.999Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>WO0000000310039</v>
+        <v>INC000000153301</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-21T10:36:47.999Z</v>
+        <v>2026-07-21T10:56:25.000Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>INC000000153086</v>
+        <v>INC000000153214</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-21T10:23:37.999Z</v>
+        <v>2026-07-21T11:00:05.000Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>WO0000000310040</v>
+        <v>INC000000153302</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-21T10:09:05.000Z</v>
+        <v>2026-07-21T11:41:02.000Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>WO0000000310041</v>
+        <v>INC000000153216</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-21T10:03:27.999Z</v>
+        <v>2026-07-21T11:56:48.000Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>WO0000000310042</v>
+        <v>WO0000000310065</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-21T10:08:51.000Z</v>
+        <v>2026-07-21T10:59:33.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>INC000000153187</v>
+        <v>INC000000153303</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-21T10:25:14.000Z</v>
+        <v>2026-07-21T11:58:21.000Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>WO0000000310111</v>
+        <v>INC000000153215</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-21T10:31:45.000Z</v>
+        <v>2026-07-21T11:22:23.000Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>INC000000153089</v>
+        <v>WO0000000310066</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-21T10:28:35.000Z</v>
+        <v>2026-07-21T11:39:17.000Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>WO0000000310045</v>
+        <v>WO0000000310069</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-21T10:35:09.000Z</v>
+        <v>2026-07-21T11:40:34.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>INC000000153090</v>
+        <v>WO0000000310144</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-21T10:32:06.999Z</v>
+        <v>2026-07-21T11:06:24.000Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>WO0000000310112</v>
+        <v>INC000000153217</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-21T10:08:14.000Z</v>
+        <v>2026-07-21T11:09:03.999Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>INC000000153091</v>
+        <v>WO0000000310145</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-21T10:30:46.000Z</v>
+        <v>2026-07-21T11:44:29.999Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>INC000000153094</v>
+        <v>INC000000153306</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-21T10:34:10.000Z</v>
+        <v>2026-07-21T12:03:12.000Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>WO0000000310114</v>
+        <v>WO0000000310143</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-21T10:12:20.000Z</v>
+        <v>2026-07-21T11:08:15.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153305</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-21T10:13:41.000Z</v>
+        <v>2026-07-21T11:15:25.999Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>WO0000000310113</v>
+        <v>INC000000153307</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-21T10:32:45.000Z</v>
+        <v>2026-07-21T11:58:18.000Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>WO0000000310046</v>
+        <v>INC000000153308</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-21T10:13:36.000Z</v>
+        <v>2026-07-21T11:12:32.000Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>INC000000153088</v>
+        <v>WO0000000310147</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-21T10:17:32.000Z</v>
+        <v>2026-07-21T11:11:37.999Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>WO0000000310047</v>
+        <v>WO0000000310070</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-21T10:14:06.000Z</v>
+        <v>2026-07-21T11:11:55.000Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>INC000000153188</v>
+        <v>WO0000000310148</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-21T10:16:45.000Z</v>
+        <v>2026-07-21T12:03:39.000Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>WO0000000310118</v>
+        <v>WO0000000310071</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-21T10:29:50.999Z</v>
+        <v>2026-07-21T11:47:34.000Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>INC000000153189</v>
+        <v>WO0000000310150</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-21T10:59:53.000Z</v>
+        <v>2026-07-21T11:39:39.000Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153309</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-21T10:18:38.000Z</v>
+        <v>2026-07-21T11:17:57.999Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>WO0000000310049</v>
+        <v>INC000000153218</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-21T10:20:08.000Z</v>
+        <v>2026-07-21T11:47:28.999Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>INC000000153190</v>
+        <v>INC000000153313</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-21T10:38:37.999Z</v>
+        <v>2026-07-21T11:25:19.000Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>WO0000000310050</v>
+        <v>WO0000000310078</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-21T10:21:12.000Z</v>
+        <v>2026-07-21T11:19:43.999Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>INC000000153191</v>
+        <v>WO0000000310079</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-21T10:54:13.999Z</v>
+        <v>2026-07-21T11:48:08.999Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>INC000000153192</v>
+        <v>WO0000000310080</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-21T10:26:23.999Z</v>
+        <v>2026-07-21T11:20:20.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>WO0000000310051</v>
+        <v>WO0000000310082</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-21T10:23:58.000Z</v>
+        <v>2026-07-21T11:21:29.000Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>INC000000153193</v>
+        <v>WO0000000310157</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-21T10:25:57.999Z</v>
+        <v>2026-07-21T11:45:08.999Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>WO0000000310120</v>
+        <v>WO0000000310083</v>
       </c>
       <c r="B1181" s="1" t="d">
-        <v>2026-07-21T10:35:25.000Z</v>
+        <v>2026-07-21T11:46:24.999Z</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>WO0000000310053</v>
+        <v>INC000000153315</v>
       </c>
       <c r="B1182" s="1" t="d">
-        <v>2026-07-21T10:27:39.999Z</v>
+        <v>2026-07-21T11:38:51.000Z</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>INC000000153195</v>
+        <v>WO0000000310160</v>
       </c>
       <c r="B1183" s="1" t="d">
-        <v>2026-07-21T10:53:52.000Z</v>
+        <v>2026-07-21T11:27:58.000Z</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>INC000000153100</v>
+        <v>WO0000000310161</v>
       </c>
       <c r="B1184" s="1" t="d">
-        <v>2026-07-21T10:36:40.000Z</v>
+        <v>2026-07-21T11:25:35.000Z</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>INC000000153194</v>
+        <v>WO0000000310158</v>
       </c>
       <c r="B1185" s="1" t="d">
-        <v>2026-07-21T10:31:29.999Z</v>
+        <v>2026-07-21T11:26:22.000Z</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>WO0000000310122</v>
+        <v>WO0000000310076</v>
       </c>
       <c r="B1186" s="1" t="d">
-        <v>2026-07-21T10:28:56.999Z</v>
+        <v>2026-07-21T11:39:13.000Z</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>INC000000153099</v>
+        <v>WO0000000310087</v>
       </c>
       <c r="B1187" s="1" t="d">
-        <v>2026-07-21T10:34:51.000Z</v>
+        <v>2026-07-21T11:46:35.000Z</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>INC000000153095</v>
+        <v>INC000000153220</v>
       </c>
       <c r="B1188" s="1" t="d">
-        <v>2026-07-21T10:34:35.999Z</v>
+        <v>2026-07-21T11:47:03.000Z</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>WO0000000310124</v>
+        <v>INC000000153219</v>
       </c>
       <c r="B1189" s="1" t="d">
-        <v>2026-07-21T10:52:52.999Z</v>
+        <v>2026-07-21T11:33:12.000Z</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>INC000000153196</v>
+        <v>INC000000153317</v>
       </c>
       <c r="B1190" s="1" t="d">
-        <v>2026-07-21T10:51:40.000Z</v>
+        <v>2026-07-21T11:51:10.000Z</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>INC000000153201</v>
+        <v>INC000000153222</v>
       </c>
       <c r="B1191" s="1" t="d">
-        <v>2026-07-21T10:39:28.000Z</v>
+        <v>2026-07-21T11:45:37.999Z</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>WO0000000310123</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B1192" s="1" t="d">
-        <v>2026-07-21T10:36:47.999Z</v>
+        <v>2026-07-21T11:44:50.999Z</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>WO0000000310055</v>
+        <v>INC000000153316</v>
       </c>
       <c r="B1193" s="1" t="d">
-        <v>2026-07-21T10:43:50.000Z</v>
+        <v>2026-07-21T11:44:00.000Z</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>INC000000153202</v>
+        <v>INC000000153224</v>
       </c>
       <c r="B1194" s="1" t="d">
-        <v>2026-07-21T10:40:42.000Z</v>
+        <v>2026-07-21T11:38:28.999Z</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>INC000000153197</v>
+        <v>WO0000000310091</v>
       </c>
       <c r="B1195" s="1" t="d">
-        <v>2026-07-21T10:44:35.999Z</v>
+        <v>2026-07-21T11:48:18.000Z</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>INC000000153203</v>
+        <v>WO0000000310092</v>
       </c>
       <c r="B1196" s="1" t="d">
-        <v>2026-07-21T10:57:50.000Z</v>
+        <v>2026-07-21T11:41:17.000Z</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>WO0000000310127</v>
+        <v>WO0000000310168</v>
       </c>
       <c r="B1197" s="1" t="d">
-        <v>2026-07-21T11:02:10.000Z</v>
+        <v>2026-07-21T11:47:52.000Z</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>INC000000153204</v>
+        <v>WO0000000310170</v>
       </c>
       <c r="B1198" s="1" t="d">
-        <v>2026-07-21T10:57:50.000Z</v>
+        <v>2026-07-21T11:40:48.000Z</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>WO0000000310060</v>
+        <v>INC000000153225</v>
       </c>
       <c r="B1199" s="1" t="d">
-        <v>2026-07-21T10:46:52.000Z</v>
+        <v>2026-07-21T11:59:26.000Z</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>WO0000000310061</v>
+        <v>INC000000153221</v>
       </c>
       <c r="B1200" s="1" t="d">
-        <v>2026-07-21T10:47:06.000Z</v>
+        <v>2026-07-21T11:45:32.000Z</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>INC000000153205</v>
+        <v>WO0000000310172</v>
       </c>
       <c r="B1201" s="1" t="d">
-        <v>2026-07-21T10:54:13.999Z</v>
+        <v>2026-07-21T11:41:57.000Z</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>WO0000000310130</v>
+        <v>INC000000153223</v>
       </c>
       <c r="B1202" s="1" t="d">
-        <v>2026-07-21T10:59:55.000Z</v>
+        <v>2026-07-21T11:53:49.000Z</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>INC000000153210</v>
+        <v>INC000000153318</v>
       </c>
       <c r="B1203" s="1" t="d">
-        <v>2026-07-21T10:50:21.999Z</v>
+        <v>2026-07-21T11:50:13.000Z</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>INC000000153206</v>
+        <v>WO0000000310173</v>
       </c>
       <c r="B1204" s="1" t="d">
-        <v>2026-07-21T10:49:56.000Z</v>
+        <v>2026-07-21T11:57:54.999Z</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>WO0000000310131</v>
+        <v>WO0000000310174</v>
       </c>
       <c r="B1205" s="1" t="d">
-        <v>2026-07-21T10:48:22.000Z</v>
+        <v>2026-07-21T11:45:39.000Z</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>INC000000153209</v>
+        <v>WO0000000310175</v>
       </c>
       <c r="B1206" s="1" t="d">
-        <v>2026-07-21T10:49:48.000Z</v>
+        <v>2026-07-21T11:46:24.000Z</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="str">
-        <v>WO0000000310132</v>
+        <v>WO0000000310146</v>
       </c>
       <c r="B1207" s="1" t="d">
-        <v>2026-07-21T10:51:57.000Z</v>
+        <v>2026-07-21T11:50:49.000Z</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>INC000000153211</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B1208" s="1" t="d">
-        <v>2026-07-21T10:52:02.000Z</v>
+        <v>2026-07-21T11:51:10.000Z</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>WO0000000310135</v>
+        <v>WO0000000310095</v>
       </c>
       <c r="B1209" s="1" t="d">
-        <v>2026-07-21T10:51:40.000Z</v>
+        <v>2026-07-21T11:48:59.000Z</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>INC000000153200</v>
+        <v>WO0000000310171</v>
       </c>
       <c r="B1210" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T11:57:09.000Z</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
-        <v>WO0000000310136</v>
+        <v>INC000000153320</v>
       </c>
       <c r="B1211" s="1" t="d">
-        <v>2026-07-21T10:53:26.000Z</v>
+        <v>2026-07-21T11:54:43.999Z</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="str">
-        <v>WO0000000310064</v>
+        <v>WO0000000310096</v>
       </c>
       <c r="B1212" s="1" t="d">
-        <v>2026-07-21T11:01:58.999Z</v>
+        <v>2026-07-21T11:51:08.000Z</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="str">
-        <v>WO0000000310133</v>
+        <v>INC000000153227</v>
       </c>
       <c r="B1213" s="1" t="d">
-        <v>2026-07-21T10:56:06.999Z</v>
+        <v>2026-07-21T11:54:36.000Z</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="str">
-        <v>INC000000153301</v>
+        <v>INC000000153229</v>
       </c>
       <c r="B1214" s="1" t="d">
-        <v>2026-07-21T10:56:25.000Z</v>
+        <v>2026-07-21T11:51:48.000Z</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="str">
-        <v>INC000000153214</v>
+        <v>WO0000000310178</v>
       </c>
       <c r="B1215" s="1" t="d">
-        <v>2026-07-21T11:00:05.000Z</v>
+        <v>2026-07-21T11:52:33.000Z</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="str">
-        <v>INC000000153302</v>
+        <v>INC000000153321</v>
       </c>
       <c r="B1216" s="1" t="d">
-        <v>2026-07-21T11:01:37.999Z</v>
+        <v>2026-07-21T11:55:29.999Z</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="str">
-        <v>INC000000153216</v>
+        <v>WO0000000310098</v>
       </c>
       <c r="B1217" s="1" t="d">
-        <v>2026-07-21T10:58:57.000Z</v>
+        <v>2026-07-21T11:52:54.000Z</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="str">
-        <v>WO0000000310065</v>
+        <v>INC000000153231</v>
       </c>
       <c r="B1218" s="1" t="d">
-        <v>2026-07-21T10:59:33.000Z</v>
+        <v>2026-07-21T11:53:42.000Z</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="str">
-        <v>INC000000153303</v>
+        <v>INC000000153230</v>
       </c>
       <c r="B1219" s="1" t="d">
-        <v>2026-07-21T10:59:44.000Z</v>
+        <v>2026-07-21T11:55:49.000Z</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="str">
-        <v>INC000000153215</v>
+        <v>INC000000153322</v>
       </c>
       <c r="B1220" s="1" t="d">
-        <v>2026-07-21T11:01:34.000Z</v>
+        <v>2026-07-21T11:56:58.999Z</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="str">
-        <v>WO0000000310066</v>
+        <v>INC000000153232</v>
       </c>
       <c r="B1221" s="1" t="d">
-        <v>2026-07-21T11:02:53.000Z</v>
+        <v>2026-07-21T12:02:12.999Z</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="str">
+        <v>INC000000153323</v>
+      </c>
+      <c r="B1222" s="1" t="d">
+        <v>2026-07-21T11:57:35.000Z</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="str">
+        <v>WO0000000310179</v>
+      </c>
+      <c r="B1223" s="1" t="d">
+        <v>2026-07-21T12:04:24.000Z</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="str">
+        <v>INC000000153324</v>
+      </c>
+      <c r="B1224" s="1" t="d">
+        <v>2026-07-21T12:03:28.000Z</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="str">
+        <v>WO0000000310202</v>
+      </c>
+      <c r="B1225" s="1" t="d">
+        <v>2026-07-21T11:59:10.000Z</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="str">
+        <v>WO0000000310201</v>
+      </c>
+      <c r="B1226" s="1" t="d">
+        <v>2026-07-21T12:03:23.000Z</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="str">
+        <v>WO0000000310180</v>
+      </c>
+      <c r="B1227" s="1" t="d">
+        <v>2026-07-21T12:00:37.000Z</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="str">
+        <v>WO0000000310097</v>
+      </c>
+      <c r="B1228" s="1" t="d">
+        <v>2026-07-21T12:04:01.999Z</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="str">
+        <v>INC000000153327</v>
+      </c>
+      <c r="B1229" s="1" t="d">
+        <v>2026-07-21T12:02:55.000Z</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="str">
+        <v>WO0000000310181</v>
+      </c>
+      <c r="B1230" s="1" t="d">
+        <v>2026-07-21T12:03:52.999Z</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="str">
+        <v>INC000000153328</v>
+      </c>
+      <c r="B1231" s="1" t="d">
+        <v>2026-07-21T12:04:09.000Z</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1222"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1232"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1232"/>
+  <dimension ref="A1:B1231"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3478,7 +3478,7 @@
         <v>WO0000000307701</v>
       </c>
       <c r="B385" s="1" t="d">
-        <v>2026-07-17T09:50:26.000Z</v>
+        <v>2026-07-21T12:05:38.000Z</v>
       </c>
     </row>
     <row r="386">
@@ -4115,1162 +4115,1162 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>INC000000139655</v>
+        <v>WO0000000308851</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-17T07:37:37.999Z</v>
+        <v>2026-07-17T16:37:20.999Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>INC000000139903</v>
+        <v>INC000000139655</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-17T07:37:04.000Z</v>
+        <v>2026-07-17T07:37:37.999Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>INC000000140158</v>
+        <v>INC000000139903</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-17T07:37:04.000Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>INC000000140820</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-17T07:35:42.000Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>INC000000140821</v>
+        <v>INC000000140820</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-17T07:34:57.000Z</v>
+        <v>2026-07-17T07:35:42.000Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>INC000000140767</v>
+        <v>INC000000140821</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-17T07:34:57.000Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>INC000000141766</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-21T08:55:08.000Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>INC000000142421</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-17T07:33:48.000Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>INC000000142515</v>
+        <v>INC000000142421</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-17T07:33:05.000Z</v>
+        <v>2026-07-17T07:33:48.000Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>WO0000000288110</v>
+        <v>INC000000142515</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-17T07:47:10.000Z</v>
+        <v>2026-07-17T07:33:05.000Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>INC000000143401</v>
+        <v>WO0000000288110</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-17T07:32:06.000Z</v>
+        <v>2026-07-17T07:47:10.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000292826</v>
+        <v>INC000000143401</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-17T07:30:34.000Z</v>
+        <v>2026-07-17T07:32:06.000Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>WO0000000295598</v>
+        <v>WO0000000292826</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-17T07:30:34.000Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>WO0000000295975</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-17T07:46:27.000Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000296722</v>
+        <v>WO0000000295975</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-17T07:44:32.000Z</v>
+        <v>2026-07-17T07:46:27.000Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>WO0000000296723</v>
+        <v>WO0000000296722</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-17T07:43:42.999Z</v>
+        <v>2026-07-17T07:44:32.000Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>WO0000000297151</v>
+        <v>WO0000000296723</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-17T07:42:36.000Z</v>
+        <v>2026-07-17T07:43:42.999Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WO0000000297156</v>
+        <v>WO0000000297151</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-17T07:41:50.000Z</v>
+        <v>2026-07-17T07:42:36.000Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WO0000000297160</v>
+        <v>WO0000000297156</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-17T07:40:23.999Z</v>
+        <v>2026-07-17T07:41:50.000Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>WO0000000298838</v>
+        <v>WO0000000297160</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-20T23:28:38.000Z</v>
+        <v>2026-07-17T07:40:23.999Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>WO0000000299920</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-17T14:59:50.999Z</v>
+        <v>2026-07-20T23:28:38.000Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>WO0000000300081</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-17T14:59:50.999Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>INC000000148888</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WO0000000300496</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-17T11:43:57.000Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>WO0000000302331</v>
+        <v>WO0000000300496</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-17T12:11:40.000Z</v>
+        <v>2026-07-17T11:43:57.000Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>WO0000000302520</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-17T15:04:39.000Z</v>
+        <v>2026-07-17T12:11:40.000Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>INC000000149827</v>
+        <v>WO0000000302520</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-17T14:03:04.000Z</v>
+        <v>2026-07-17T15:04:39.000Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>INC000000149757</v>
+        <v>INC000000149827</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-16T16:04:01.999Z</v>
+        <v>2026-07-17T14:03:04.000Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>INC000000149760</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-17T07:52:31.999Z</v>
+        <v>2026-07-16T16:04:01.999Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>WO0000000303117</v>
+        <v>INC000000149760</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-21T10:43:30.000Z</v>
+        <v>2026-07-17T07:52:31.999Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>WO0000000303120</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-17T07:38:45.000Z</v>
+        <v>2026-07-21T10:43:30.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000303120</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-17T15:09:03.000Z</v>
+        <v>2026-07-17T07:38:45.000Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>WO0000000303244</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-17T15:04:54.000Z</v>
+        <v>2026-07-17T15:09:03.000Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>WO0000000303459</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-17T11:09:28.999Z</v>
+        <v>2026-07-17T15:04:54.000Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>WO0000000303471</v>
+        <v>WO0000000303459</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-16T14:24:05.000Z</v>
+        <v>2026-07-17T11:09:28.999Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000303471</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-16T12:40:48.000Z</v>
+        <v>2026-07-16T14:24:05.000Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-17T10:37:05.000Z</v>
+        <v>2026-07-16T12:40:48.000Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-17T10:37:33.000Z</v>
+        <v>2026-07-17T10:37:05.000Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>WO0000000305131</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-21T08:46:39.000Z</v>
+        <v>2026-07-17T10:37:33.000Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>WO0000000305138</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-21T08:46:39.000Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>INC000000150748</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-21T10:15:45.000Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>WO0000000305336</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-21T10:15:45.000Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>INC000000150916</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-17T13:59:57.999Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000150916</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-17T18:15:37.999Z</v>
+        <v>2026-07-17T13:59:57.999Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>INC000000151036</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-16T16:01:20.999Z</v>
+        <v>2026-07-17T18:15:37.999Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>INC000000150958</v>
+        <v>INC000000151036</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-17T07:47:57.999Z</v>
+        <v>2026-07-16T16:01:20.999Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>WO0000000305863</v>
+        <v>INC000000150958</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-21T08:44:19.000Z</v>
+        <v>2026-07-17T07:47:57.999Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>WO0000000305877</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-21T11:48:06.999Z</v>
+        <v>2026-07-21T08:44:19.000Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>WO0000000305769</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-17T10:37:57.000Z</v>
+        <v>2026-07-21T11:48:06.999Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>WO0000000305770</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-17T11:07:27.000Z</v>
+        <v>2026-07-17T10:37:57.000Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>INC000000151203</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-17T11:07:27.000Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>WO0000000306127</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-21T07:40:38.000Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>INC000000151157</v>
+        <v>WO0000000306127</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-21T10:59:03.000Z</v>
+        <v>2026-07-21T07:40:38.000Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>INC000000151271</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-17T07:40:02.000Z</v>
+        <v>2026-07-21T10:59:03.000Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>WO0000000306256</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-17T14:41:03.000Z</v>
+        <v>2026-07-17T07:40:02.000Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>INC000000151313</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-17T14:41:03.000Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>WO0000000306718</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-17T10:39:36.000Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>WO0000000306721</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-17T15:11:14.000Z</v>
+        <v>2026-07-17T10:39:36.000Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>WO0000000306726</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-17T10:39:57.000Z</v>
+        <v>2026-07-17T15:11:14.000Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>INC000000151512</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-21T09:41:08.000Z</v>
+        <v>2026-07-17T10:39:57.000Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000306799</v>
+        <v>INC000000151512</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-17T08:21:12.999Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-17T19:07:47.000Z</v>
+        <v>2026-07-17T08:21:12.999Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>INC000000151527</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-17T16:34:54.000Z</v>
+        <v>2026-07-17T19:07:47.000Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>WO0000000306927</v>
+        <v>INC000000151527</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-17T16:34:54.000Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-17T17:20:58.999Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>WO0000000306877</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-16T14:55:04.000Z</v>
+        <v>2026-07-17T17:20:58.999Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>WO0000000306890</v>
+        <v>WO0000000306877</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-16T14:55:04.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>WO0000000306899</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-21T11:53:12.999Z</v>
+        <v>2026-07-17T14:42:13.999Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>WO0000000306988</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-21T09:13:38.000Z</v>
+        <v>2026-07-21T11:53:12.999Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>WO0000000306994</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-16T15:19:33.999Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>INC000000151586</v>
+        <v>WO0000000306994</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-19T12:57:49.000Z</v>
+        <v>2026-07-16T15:19:33.999Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>WO0000000307224</v>
+        <v>INC000000151586</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-16T16:04:39.999Z</v>
+        <v>2026-07-19T12:57:49.000Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000307224</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-17T14:49:17.000Z</v>
+        <v>2026-07-16T16:04:39.999Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>INC000000151764</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-21T09:41:12.000Z</v>
+        <v>2026-07-17T14:49:17.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>WO0000000307513</v>
+        <v>INC000000151764</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-21T10:03:23.000Z</v>
+        <v>2026-07-21T09:41:12.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-21T10:03:23.000Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>WO0000000307483</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-21T09:13:03.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-17T16:21:08.000Z</v>
+        <v>2026-07-21T09:13:03.000Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>INC000000152000</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-19T12:58:45.000Z</v>
+        <v>2026-07-17T16:21:08.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000152000</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-19T12:58:45.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-17T17:21:00.000Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000307725</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-17T15:11:48.000Z</v>
+        <v>2026-07-17T17:21:00.000Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>WO0000000307729</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-16T12:57:39.999Z</v>
+        <v>2026-07-17T15:11:48.000Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>INC000000152145</v>
+        <v>WO0000000307729</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-17T19:20:59.000Z</v>
+        <v>2026-07-16T12:57:39.999Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>WO0000000307820</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-21T09:49:48.000Z</v>
+        <v>2026-07-17T19:20:59.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>WO0000000307940</v>
+        <v>WO0000000307820</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-21T09:49:48.000Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>INC000000152212</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000308040</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>WO0000000307968</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-16T15:02:29.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>WO0000000307970</v>
+        <v>WO0000000307968</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-16T16:55:20.000Z</v>
+        <v>2026-07-16T15:02:29.000Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308041</v>
+        <v>WO0000000307970</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-21T10:24:00.000Z</v>
+        <v>2026-07-16T16:55:20.000Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>WO0000000308042</v>
+        <v>WO0000000308041</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-20T23:34:20.999Z</v>
+        <v>2026-07-21T10:24:00.000Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-20T23:34:20.999Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>WO0000000308052</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-17T11:04:48.999Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-17T11:04:48.999Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000308105</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-20T23:29:29.999Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>WO0000000308075</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-20T23:26:07.000Z</v>
+        <v>2026-07-20T23:29:29.999Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>WO0000000308106</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-21T11:15:57.000Z</v>
+        <v>2026-07-20T23:26:07.000Z</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-07-20T23:31:09.999Z</v>
+        <v>2026-07-21T11:15:57.000Z</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>WO0000000308086</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-07-21T09:28:00.000Z</v>
+        <v>2026-07-20T23:31:09.999Z</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>WO0000000308215</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-07-17T09:26:37.000Z</v>
+        <v>2026-07-21T09:28:00.000Z</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000308215</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-17T09:26:37.000Z</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-07-18T12:28:17.000Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>WO0000000308234</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-07-19T12:53:47.000Z</v>
+        <v>2026-07-18T12:28:17.000Z</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>INC000000152251</v>
+        <v>WO0000000308234</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-07-17T10:26:36.999Z</v>
+        <v>2026-07-19T12:53:47.000Z</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>INC000000152361</v>
+        <v>INC000000152251</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-07-17T16:39:09.000Z</v>
+        <v>2026-07-17T10:26:36.999Z</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>WO0000000308196</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-07-21T08:49:13.000Z</v>
+        <v>2026-07-21T12:08:02.000Z</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000308196</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-07-17T12:34:20.000Z</v>
+        <v>2026-07-21T08:49:13.000Z</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>WO0000000308249</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-07-17T13:34:27.999Z</v>
+        <v>2026-07-17T12:34:20.000Z</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>WO0000000308199</v>
+        <v>WO0000000308249</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-07-17T13:37:19.000Z</v>
+        <v>2026-07-17T13:34:27.999Z</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>INC000000152369</v>
+        <v>WO0000000308199</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-07-17T10:42:03.000Z</v>
+        <v>2026-07-17T13:37:19.000Z</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>WO0000000308306</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-07-18T09:01:38.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-07-18T12:40:57.999Z</v>
+        <v>2026-07-18T09:01:38.000Z</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>INC000000152378</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-07-17T09:05:30.000Z</v>
+        <v>2026-07-18T12:40:57.999Z</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>WO0000000308420</v>
+        <v>INC000000152378</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-18T12:08:23.000Z</v>
+        <v>2026-07-17T09:05:30.000Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>WO0000000308426</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-18T12:08:23.000Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308426</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-21T09:09:06.999Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>WO0000000308357</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-07-21T10:35:55.000Z</v>
+        <v>2026-07-21T09:09:06.999Z</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>INC000000152389</v>
+        <v>WO0000000308357</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-17T10:53:19.000Z</v>
+        <v>2026-07-21T10:35:55.000Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>WO0000000308461</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-21T09:25:59.000Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>WO0000000308495</v>
+        <v>WO0000000308461</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-21T10:02:45.000Z</v>
+        <v>2026-07-21T09:25:59.000Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>INC000000152419</v>
+        <v>WO0000000308495</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-21T08:54:50.000Z</v>
+        <v>2026-07-21T10:02:45.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>INC000000152439</v>
+        <v>INC000000152419</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-07-16T13:12:03.000Z</v>
+        <v>2026-07-21T08:54:50.000Z</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>INC000000152517</v>
+        <v>INC000000152439</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-17T10:21:00.000Z</v>
+        <v>2026-07-16T13:12:03.000Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>INC000000152450</v>
+        <v>INC000000152517</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-17T13:17:48.000Z</v>
+        <v>2026-07-17T10:21:00.000Z</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>INC000000152537</v>
+        <v>INC000000152450</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-07-17T10:03:46.000Z</v>
+        <v>2026-07-17T13:17:48.000Z</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000152537</v>
       </c>
       <c r="B592" s="1" t="d">
-        <v>2026-07-21T11:34:44.999Z</v>
+        <v>2026-07-17T10:03:46.000Z</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>INC000000152458</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-07-21T10:45:45.000Z</v>
+        <v>2026-07-21T11:34:44.999Z</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>WO0000000308662</v>
+        <v>INC000000152458</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-07-16T14:23:41.000Z</v>
+        <v>2026-07-21T10:45:45.000Z</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>WO0000000308585</v>
+        <v>WO0000000308662</v>
       </c>
       <c r="B595" s="1" t="d">
-        <v>2026-07-16T14:22:46.000Z</v>
+        <v>2026-07-16T14:23:41.000Z</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>INC000000152461</v>
+        <v>WO0000000308585</v>
       </c>
       <c r="B596" s="1" t="d">
-        <v>2026-07-20T09:23:43.999Z</v>
+        <v>2026-07-16T14:22:46.000Z</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>WO0000000308698</v>
+        <v>INC000000152461</v>
       </c>
       <c r="B597" s="1" t="d">
-        <v>2026-07-21T08:59:12.999Z</v>
+        <v>2026-07-20T09:23:43.999Z</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308698</v>
       </c>
       <c r="B598" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-21T08:59:12.999Z</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>WO0000000308722</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B599" s="1" t="d">
-        <v>2026-07-20T19:01:19.000Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-07-21T10:18:10.000Z</v>
+        <v>2026-07-20T19:01:19.000Z</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>INC000000152565</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-21T07:47:38.999Z</v>
+        <v>2026-07-21T10:18:10.000Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>WO0000000308727</v>
+        <v>INC000000152565</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-21T10:49:39.999Z</v>
+        <v>2026-07-21T07:47:38.999Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000308727</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-21T09:27:37.000Z</v>
+        <v>2026-07-21T10:49:39.999Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>INC000000152566</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-17T15:18:13.000Z</v>
+        <v>2026-07-21T09:27:37.000Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000308743</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-07-17T15:54:32.000Z</v>
+        <v>2026-07-17T15:18:13.000Z</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>INC000000152477</v>
+        <v>WO0000000308743</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-16T12:12:43.000Z</v>
+        <v>2026-07-17T15:54:32.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>WO0000000308754</v>
+        <v>INC000000152477</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-16T14:25:41.000Z</v>
+        <v>2026-07-16T12:12:43.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>WO0000000308834</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-21T09:29:46.000Z</v>
+        <v>2026-07-16T14:25:41.000Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>WO0000000308851</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-17T16:37:20.999Z</v>
+        <v>2026-07-21T09:29:46.000Z</v>
       </c>
     </row>
     <row r="610">
@@ -5699,4564 +5699,4556 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>WO0000000309063</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-21T12:01:39.000Z</v>
+        <v>2026-07-21T07:53:18.000Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-21T07:53:18.000Z</v>
+        <v>2026-07-16T19:52:29.999Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000308987</v>
+        <v>WO0000000305262</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-16T19:52:29.999Z</v>
+        <v>2026-07-17T07:53:28.999Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>WO0000000305262</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-17T07:53:28.999Z</v>
+        <v>2026-07-16T19:32:50.000Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>WO0000000309073</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-16T19:32:50.000Z</v>
+        <v>2026-07-21T07:53:32.000Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>INC000000152643</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-21T07:53:32.000Z</v>
+        <v>2026-07-16T19:42:22.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-16T19:42:22.000Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>WO0000000309077</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>WO0000000309079</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>WO0000000308997</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-17T10:15:24.000Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000308999</v>
+        <v>WO0000000309082</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-17T10:15:24.000Z</v>
+        <v>2026-07-17T09:36:16.000Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000309082</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-17T09:36:16.000Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>WO0000000309101</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-17T06:53:11.000Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>INC000000152733</v>
+        <v>WO0000000309097</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-17T08:03:06.999Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>WO0000000309097</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-17T08:03:06.999Z</v>
+        <v>2026-07-17T08:06:35.000Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>INC000000152737</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-17T08:06:35.000Z</v>
+        <v>2026-07-17T07:45:37.999Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000309124</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-17T07:45:37.999Z</v>
+        <v>2026-07-17T08:07:23.000Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-17T08:07:23.000Z</v>
+        <v>2026-07-21T09:04:31.000Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>WO0000000309136</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-21T09:04:31.000Z</v>
+        <v>2026-07-17T11:36:59.000Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-17T11:36:59.000Z</v>
+        <v>2026-07-17T12:44:26.000Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>INC000000152663</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-17T12:44:26.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>INC000000152664</v>
+        <v>INC000000152746</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-21T09:47:10.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>INC000000152746</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-21T09:47:10.000Z</v>
+        <v>2026-07-17T08:54:14.000Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-17T08:54:14.000Z</v>
+        <v>2026-07-17T08:54:36.999Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000309155</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-17T08:54:36.999Z</v>
+        <v>2026-07-18T12:40:15.000Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>INC000000152668</v>
+        <v>WO0000000309226</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-18T12:40:15.000Z</v>
+        <v>2026-07-17T08:58:32.999Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>WO0000000309226</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-17T08:58:32.999Z</v>
+        <v>2026-07-21T10:52:02.000Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>WO0000000309231</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-21T10:52:02.000Z</v>
+        <v>2026-07-17T09:57:18.999Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000309232</v>
+        <v>INC000000152673</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-21T08:52:59.000Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>INC000000152673</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-21T08:52:59.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>WO0000000309162</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>INC000000152674</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-17T14:47:59.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000309164</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-17T14:47:59.000Z</v>
+        <v>2026-07-17T09:26:58.999Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>WO0000000309241</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-17T09:26:58.999Z</v>
+        <v>2026-07-21T12:08:28.999Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>INC000000152678</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-21T10:42:34.000Z</v>
+        <v>2026-07-17T15:50:55.000Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>INC000000152679</v>
+        <v>WO0000000309246</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-17T15:50:55.000Z</v>
+        <v>2026-07-17T09:32:32.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>WO0000000309246</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-17T09:32:32.000Z</v>
+        <v>2026-07-17T09:36:30.000Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>WO0000000309168</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-17T09:36:30.000Z</v>
+        <v>2026-07-17T09:37:50.000Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-17T09:37:50.000Z</v>
+        <v>2026-07-17T09:38:11.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>WO0000000309172</v>
+        <v>WO0000000309249</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-17T09:38:11.000Z</v>
+        <v>2026-07-17T09:38:10.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>WO0000000309249</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-21T10:04:01.000Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>WO0000000309250</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-21T10:04:01.000Z</v>
+        <v>2026-07-21T08:45:24.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>INC000000152760</v>
+        <v>WO0000000309251</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-21T08:45:24.000Z</v>
+        <v>2026-07-17T09:40:19.000Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>WO0000000309251</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-17T09:40:19.000Z</v>
+        <v>2026-07-21T08:17:56.000Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-21T08:17:56.000Z</v>
+        <v>2026-07-17T09:57:50.000Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-17T09:57:50.000Z</v>
+        <v>2026-07-21T11:59:19.000Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-21T11:59:19.000Z</v>
+        <v>2026-07-17T14:47:53.999Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-17T14:47:53.999Z</v>
+        <v>2026-07-21T11:58:05.000Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-21T11:58:05.000Z</v>
+        <v>2026-07-17T11:15:36.000Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>WO0000000309189</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-17T11:15:36.000Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>WO0000000309258</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-17T11:13:13.000Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>WO0000000309259</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-17T11:13:13.000Z</v>
+        <v>2026-07-21T09:55:04.000Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>INC000000152768</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-21T09:55:04.000Z</v>
+        <v>2026-07-17T10:18:38.000Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>WO0000000309262</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-17T10:18:38.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>INC000000152690</v>
+        <v>INC000000152770</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-17T10:27:03.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>INC000000152770</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-17T10:27:03.000Z</v>
+        <v>2026-07-17T11:24:41.000Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000309195</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B721" s="1" t="d">
-        <v>2026-07-17T11:24:41.000Z</v>
+        <v>2026-07-21T10:45:43.999Z</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>INC000000152772</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-21T10:45:43.999Z</v>
+        <v>2026-07-21T10:37:55.000Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152691</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-21T10:37:55.000Z</v>
+        <v>2026-07-17T11:21:16.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>INC000000152691</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-17T11:21:16.000Z</v>
+        <v>2026-07-17T12:51:35.000Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000309199</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-17T12:51:35.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>WO0000000309200</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309269</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-21T10:34:42.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>WO0000000309269</v>
+        <v>WO0000000309270</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-21T10:34:42.000Z</v>
+        <v>2026-07-17T16:48:27.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>WO0000000309270</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-17T16:48:27.000Z</v>
+        <v>2026-07-17T14:48:08.000Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>WO0000000309271</v>
+        <v>WO0000000309407</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-17T14:48:08.000Z</v>
+        <v>2026-07-17T10:43:38.999Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>WO0000000309407</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-19T12:51:55.999Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>INC000000152777</v>
+        <v>WO0000000309409</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-19T12:51:55.999Z</v>
+        <v>2026-07-21T10:47:34.000Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>WO0000000309409</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-21T10:47:34.000Z</v>
+        <v>2026-07-21T09:07:41.000Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-21T09:07:41.000Z</v>
+        <v>2026-07-17T10:48:35.999Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-17T10:48:35.999Z</v>
+        <v>2026-07-17T10:53:18.000Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-17T10:53:18.000Z</v>
+        <v>2026-07-21T11:55:19.000Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-21T11:55:19.000Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>WO0000000309282</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-17T10:58:23.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>WO0000000309413</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-17T10:58:23.000Z</v>
+        <v>2026-07-21T10:46:30.999Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>INC000000152802</v>
+        <v>WO0000000309417</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-21T10:46:30.999Z</v>
+        <v>2026-07-17T11:02:34.000Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>WO0000000309417</v>
+        <v>INC000000152700</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-17T11:02:34.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>INC000000152700</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-18T08:52:20.999Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-18T08:52:20.999Z</v>
+        <v>2026-07-17T11:12:43.000Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-17T11:12:43.000Z</v>
+        <v>2026-07-17T11:15:48.000Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-17T11:15:48.000Z</v>
+        <v>2026-07-17T11:17:12.999Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-17T11:17:12.999Z</v>
+        <v>2026-07-17T14:48:17.000Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-17T14:48:17.000Z</v>
+        <v>2026-07-17T11:21:58.000Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-17T11:21:58.000Z</v>
+        <v>2026-07-21T09:14:29.000Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309432</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-21T09:14:29.000Z</v>
+        <v>2026-07-21T11:26:35.000Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>WO0000000309432</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-21T11:26:35.000Z</v>
+        <v>2026-07-17T11:26:05.999Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>WO0000000309433</v>
+        <v>WO0000000309299</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-17T11:26:05.999Z</v>
+        <v>2026-07-17T11:28:13.000Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>WO0000000309299</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-17T11:28:13.000Z</v>
+        <v>2026-07-21T10:21:20.000Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-21T10:21:20.000Z</v>
+        <v>2026-07-21T09:27:50.000Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>WO0000000309438</v>
+        <v>WO0000000309439</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-21T09:27:50.000Z</v>
+        <v>2026-07-21T11:34:46.000Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>WO0000000309439</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-21T11:34:46.000Z</v>
+        <v>2026-07-17T15:38:05.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>WO0000000309503</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-17T15:38:05.000Z</v>
+        <v>2026-07-21T12:08:18.000Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>INC000000152789</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-21T10:37:25.999Z</v>
+        <v>2026-07-21T10:55:04.000Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-21T10:55:04.000Z</v>
+        <v>2026-07-17T11:41:41.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-17T11:41:41.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-17T15:32:46.000Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>WO0000000309441</v>
+        <v>WO0000000309444</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-17T15:32:46.000Z</v>
+        <v>2026-07-17T11:41:48.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>WO0000000309444</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-17T11:41:48.000Z</v>
+        <v>2026-07-21T10:23:15.000Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309447</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-21T10:23:15.000Z</v>
+        <v>2026-07-17T11:53:25.999Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-17T11:53:25.999Z</v>
+        <v>2026-07-21T08:25:47.000Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-21T08:25:47.000Z</v>
+        <v>2026-07-21T10:24:15.999Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-21T10:24:15.999Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>WO0000000309513</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T14:48:03.000Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-17T14:48:03.000Z</v>
+        <v>2026-07-17T15:45:57.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-17T15:45:57.000Z</v>
+        <v>2026-07-17T14:48:13.000Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>WO0000000309457</v>
+        <v>INC000000152797</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-17T14:48:13.000Z</v>
+        <v>2026-07-21T08:59:18.000Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>INC000000152797</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-21T08:59:18.000Z</v>
+        <v>2026-07-18T08:52:31.000Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-18T08:52:31.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309514</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>WO0000000309462</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-17T12:23:35.999Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>WO0000000309465</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-17T12:23:35.999Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>WO0000000309520</v>
+        <v>INC000000152901</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-21T10:47:15.000Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>INC000000152901</v>
+        <v>WO0000000309466</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-21T10:47:15.000Z</v>
+        <v>2026-07-21T10:22:48.000Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>WO0000000309466</v>
+        <v>WO0000000309525</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-21T10:22:48.000Z</v>
+        <v>2026-07-17T16:15:45.000Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>WO0000000309525</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-17T16:15:45.000Z</v>
+        <v>2026-07-17T17:44:41.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>INC000000152903</v>
+        <v>WO0000000309526</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-17T17:44:41.000Z</v>
+        <v>2026-07-21T08:25:19.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000309526</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-21T08:25:19.000Z</v>
+        <v>2026-07-21T09:11:31.000Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309470</v>
+        <v>INC000000152814</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-21T09:11:31.000Z</v>
+        <v>2026-07-21T11:42:56.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>INC000000152814</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-21T11:42:56.000Z</v>
+        <v>2026-07-21T10:47:55.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309478</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-21T10:47:55.000Z</v>
+        <v>2026-07-17T15:55:47.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>WO0000000309478</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-17T15:55:47.000Z</v>
+        <v>2026-07-17T12:55:06.999Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309534</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-17T12:55:06.999Z</v>
+        <v>2026-07-17T13:00:45.000Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>WO0000000309534</v>
+        <v>INC000000152815</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-17T13:00:45.000Z</v>
+        <v>2026-07-17T21:20:43.999Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>INC000000152815</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-17T21:20:43.999Z</v>
+        <v>2026-07-21T11:54:16.999Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>WO0000000309489</v>
+        <v>WO0000000309488</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-21T11:54:16.999Z</v>
+        <v>2026-07-17T13:20:57.999Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>WO0000000309488</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-17T13:20:57.999Z</v>
+        <v>2026-07-21T08:46:11.000Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>INC000000152914</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-21T08:46:11.000Z</v>
+        <v>2026-07-18T01:16:50.999Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>INC000000152913</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-18T01:16:50.999Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>WO0000000309487</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-21T10:39:57.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>WO0000000309497</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-21T10:39:57.000Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>WO0000000309499</v>
+        <v>WO0000000309545</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-21T07:54:44.000Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>WO0000000309545</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-21T07:54:44.000Z</v>
+        <v>2026-07-18T01:16:05.000Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>INC000000152919</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-18T01:16:05.000Z</v>
+        <v>2026-07-17T14:11:39.000Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>WO0000000309546</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-21T10:46:28.000Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>INC000000152824</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-21T10:46:28.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>INC000000152921</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T15:55:02.000Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>WO0000000309603</v>
+        <v>INC000000152922</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-17T15:55:02.000Z</v>
+        <v>2026-07-21T07:10:12.000Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>INC000000152922</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-21T07:10:12.000Z</v>
+        <v>2026-07-17T14:30:26.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000309549</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-17T14:30:26.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>WO0000000309551</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-21T10:51:05.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>WO0000000309609</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-21T10:51:05.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309553</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-17T14:57:05.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309613</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-17T14:57:05.000Z</v>
+        <v>2026-07-17T15:01:59.000Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>WO0000000309613</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-17T15:01:59.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309559</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-17T15:56:29.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>WO0000000309559</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-17T15:56:29.000Z</v>
+        <v>2026-07-18T08:45:42.000Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-18T08:45:42.000Z</v>
+        <v>2026-07-17T15:57:48.000Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000309616</v>
+        <v>INC000000152931</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-17T15:57:48.000Z</v>
+        <v>2026-07-21T08:13:12.000Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-21T08:13:12.000Z</v>
+        <v>2026-07-17T15:20:43.999Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309563</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-17T15:24:26.000Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000309563</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-18T11:14:25.000Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>INC000000152933</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-18T11:14:25.000Z</v>
+        <v>2026-07-17T16:04:00.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-17T16:04:00.000Z</v>
+        <v>2026-07-17T15:31:50.999Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309572</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-21T08:34:49.000Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>WO0000000309572</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-21T08:34:49.000Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>WO0000000309574</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-21T10:39:19.000Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>WO0000000309626</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-21T10:39:19.000Z</v>
+        <v>2026-07-17T16:25:00.000Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>WO0000000309627</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-17T16:25:00.000Z</v>
+        <v>2026-07-18T06:53:20.000Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>WO0000000309629</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-18T06:53:20.000Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>WO0000000309632</v>
+        <v>WO0000000309635</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-17T16:06:26.000Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>WO0000000309635</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-17T16:06:26.000Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-21T11:47:03.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>WO0000000309636</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-21T11:47:03.000Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>INC000000152838</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-17T17:05:49.000Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-17T17:05:49.000Z</v>
+        <v>2026-07-18T06:19:47.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-18T06:19:47.000Z</v>
+        <v>2026-07-17T16:39:05.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000309586</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-17T16:39:05.000Z</v>
+        <v>2026-07-18T12:55:19.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-18T12:55:19.000Z</v>
+        <v>2026-07-18T07:38:46.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>INC000000152944</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-18T07:38:46.000Z</v>
+        <v>2026-07-18T13:55:17.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>WO0000000309589</v>
+        <v>INC000000152945</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-18T13:55:17.000Z</v>
+        <v>2026-07-21T11:38:08.999Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>INC000000152945</v>
+        <v>WO0000000309643</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-21T11:38:08.999Z</v>
+        <v>2026-07-21T12:04:37.000Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000309643</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-21T12:04:37.000Z</v>
+        <v>2026-07-21T10:09:45.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000309592</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-21T10:09:45.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000309647</v>
+        <v>WO0000000309648</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-21T09:05:18.000Z</v>
+        <v>2026-07-17T18:19:50.000Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>WO0000000309648</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-17T18:19:50.000Z</v>
+        <v>2026-07-21T09:50:43.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-21T09:50:43.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000309595</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>WO0000000309596</v>
+        <v>WO0000000309655</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-21T09:15:18.000Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000309655</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-21T09:15:18.000Z</v>
+        <v>2026-07-21T10:23:48.000Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>WO0000000309597</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-21T10:23:48.000Z</v>
+        <v>2026-07-21T11:20:55.000Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000309309</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-21T11:20:55.000Z</v>
+        <v>2026-07-21T11:13:56.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>INC000000152948</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-21T11:13:56.000Z</v>
+        <v>2026-07-21T10:28:49.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>INC000000152845</v>
+        <v>INC000000152846</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-21T10:28:49.000Z</v>
+        <v>2026-07-21T11:38:41.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>INC000000152846</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-21T11:38:41.000Z</v>
+        <v>2026-07-21T11:21:15.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000309310</v>
+        <v>INC000000152950</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-21T11:21:15.000Z</v>
+        <v>2026-07-21T09:49:56.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>INC000000152950</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-21T09:49:56.000Z</v>
+        <v>2026-07-17T18:11:18.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>INC000000152848</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309598</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-21T08:16:54.999Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>WO0000000309598</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-21T08:16:54.999Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>WO0000000309599</v>
+        <v>WO0000000309600</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-21T07:30:44.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>WO0000000309600</v>
+        <v>WO0000000309659</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-21T07:30:44.000Z</v>
+        <v>2026-07-21T08:25:42.000Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>WO0000000309659</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-21T08:25:42.000Z</v>
+        <v>2026-07-21T11:52:20.999Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>WO0000000309704</v>
+        <v>WO0000000309705</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-21T11:52:20.999Z</v>
+        <v>2026-07-21T12:03:05.000Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>WO0000000309705</v>
+        <v>WO0000000309660</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-21T12:03:05.000Z</v>
+        <v>2026-07-21T12:02:41.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>WO0000000309660</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-21T12:02:41.000Z</v>
+        <v>2026-07-21T11:50:05.000Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>INC000000152953</v>
+        <v>INC000000152954</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-21T11:50:05.000Z</v>
+        <v>2026-07-18T10:44:32.000Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>INC000000152954</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-18T10:44:32.000Z</v>
+        <v>2026-07-21T12:06:57.000Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>INC000000152955</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-21T09:28:09.000Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>WO0000000309664</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-18T09:16:52.000Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>INC000000152956</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-18T09:16:52.000Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>WO0000000309666</v>
+        <v>INC000000152957</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-18T11:15:19.000Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>INC000000152957</v>
+        <v>INC000000152854</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-18T11:15:19.000Z</v>
+        <v>2026-07-17T21:32:15.999Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>INC000000152854</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-17T21:32:15.999Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000309714</v>
+        <v>WO0000000309667</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-21T07:08:18.000Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000309667</v>
+        <v>WO0000000309668</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-21T07:08:18.000Z</v>
+        <v>2026-07-21T09:29:44.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>WO0000000309668</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-21T09:29:44.000Z</v>
+        <v>2026-07-21T07:55:12.000Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000309669</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-21T07:55:12.000Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>INC000000152856</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-18T11:57:16.000Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>INC000000152866</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-18T11:57:16.000Z</v>
+        <v>2026-07-21T09:18:02.999Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>WO0000000309671</v>
+        <v>INC000000152869</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-21T09:18:02.999Z</v>
+        <v>2026-07-21T07:20:13.000Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>INC000000152869</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-21T07:20:13.000Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>INC000000152873</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-21T11:13:10.000Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>INC000000152971</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-21T11:13:10.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>WO0000000309682</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>WO0000000309686</v>
+        <v>INC000000152879</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-18T08:11:58.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>INC000000152879</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>WO0000000309689</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-18T12:53:54.000Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-18T12:53:54.000Z</v>
+        <v>2026-07-21T10:48:40.000Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>INC000000152883</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-21T10:48:40.000Z</v>
+        <v>2026-07-18T08:48:11.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000309692</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-18T08:48:11.000Z</v>
+        <v>2026-07-21T10:10:23.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>INC000000152981</v>
+        <v>WO0000000309732</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-21T10:10:23.000Z</v>
+        <v>2026-07-18T09:10:30.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>WO0000000309732</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-18T09:10:30.000Z</v>
+        <v>2026-07-21T07:56:14.999Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>WO0000000309697</v>
+        <v>INC000000152888</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-21T07:56:14.999Z</v>
+        <v>2026-07-21T11:56:31.000Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>INC000000152888</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-21T11:56:31.000Z</v>
+        <v>2026-07-21T10:00:54.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>INC000000152985</v>
+        <v>WO0000000309698</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-21T10:00:54.000Z</v>
+        <v>2026-07-18T10:07:47.000Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000309698</v>
+        <v>INC000000152986</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-18T10:07:47.000Z</v>
+        <v>2026-07-21T08:16:08.000Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>INC000000152986</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-21T08:16:08.000Z</v>
+        <v>2026-07-18T10:49:11.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-18T10:49:11.000Z</v>
+        <v>2026-07-21T10:41:02.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>INC000000152989</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-21T10:41:02.000Z</v>
+        <v>2026-07-21T07:32:12.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>INC000000152890</v>
+        <v>WO0000000309802</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-21T07:32:12.000Z</v>
+        <v>2026-07-21T09:30:57.000Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>WO0000000309802</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-21T09:30:57.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>WO0000000309803</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-20T19:05:32.000Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-20T19:05:32.000Z</v>
+        <v>2026-07-20T19:04:33.999Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-20T19:04:33.999Z</v>
+        <v>2026-07-20T19:03:52.000Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-20T19:03:52.000Z</v>
+        <v>2026-07-20T19:04:20.000Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>INC000000152893</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-20T19:04:20.000Z</v>
+        <v>2026-07-21T11:12:41.000Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>WO0000000309804</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-21T11:12:41.000Z</v>
+        <v>2026-07-21T11:34:51.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000309805</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-21T11:34:51.000Z</v>
+        <v>2026-07-21T11:11:58.999Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>WO0000000309807</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-21T11:11:58.999Z</v>
+        <v>2026-07-21T07:32:42.999Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-21T07:32:42.999Z</v>
+        <v>2026-07-21T07:33:22.000Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-21T07:33:22.000Z</v>
+        <v>2026-07-21T10:52:04.000Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>INC000000152898</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-21T10:52:04.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>WO0000000309810</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>WO0000000309752</v>
+        <v>INC000000152900</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-21T08:04:18.000Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>INC000000152900</v>
+        <v>WO0000000309815</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-21T08:04:18.000Z</v>
+        <v>2026-07-21T09:12:13.999Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000309815</v>
+        <v>INC000000153006</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-21T09:12:13.999Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>INC000000153006</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-21T07:19:30.000Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>INC000000153101</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-21T07:19:30.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>WO0000000309816</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-21T10:18:57.000Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153103</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-21T10:18:57.000Z</v>
+        <v>2026-07-21T08:04:41.000Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>INC000000153103</v>
+        <v>INC000000153011</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-21T08:04:41.000Z</v>
+        <v>2026-07-21T10:52:54.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>INC000000153011</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-21T10:52:54.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>WO0000000309759</v>
+        <v>INC000000153012</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-21T08:03:57.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>INC000000153012</v>
+        <v>INC000000153013</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-21T08:03:57.000Z</v>
+        <v>2026-07-21T07:19:23.999Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>INC000000153013</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-21T07:19:23.999Z</v>
+        <v>2026-07-21T07:31:56.999Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>WO0000000309825</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-21T07:31:56.999Z</v>
+        <v>2026-07-21T07:19:54.000Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>INC000000153105</v>
+        <v>INC000000153015</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-21T07:19:54.000Z</v>
+        <v>2026-07-21T10:29:31.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>INC000000153015</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-21T10:29:31.000Z</v>
+        <v>2026-07-21T07:30:09.000Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>WO0000000309826</v>
+        <v>INC000000153017</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-21T07:30:09.000Z</v>
+        <v>2026-07-18T15:26:50.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>INC000000153017</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-18T15:26:50.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>WO0000000309768</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-21T09:58:01.000Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>INC000000153107</v>
+        <v>WO0000000309769</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-21T09:58:01.000Z</v>
+        <v>2026-07-21T07:30:32.000Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>WO0000000309769</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-21T07:30:32.000Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>WO0000000309829</v>
+        <v>WO0000000309830</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-21T11:24:34.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>WO0000000309830</v>
+        <v>INC000000153108</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-21T11:24:34.000Z</v>
+        <v>2026-07-21T07:53:45.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>INC000000153108</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-21T07:53:45.000Z</v>
+        <v>2026-07-19T08:43:56.000Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>INC000000153019</v>
+        <v>INC000000153020</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-19T08:43:56.000Z</v>
+        <v>2026-07-21T07:53:07.999Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>INC000000153020</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-21T07:53:07.999Z</v>
+        <v>2026-07-21T07:08:54.000Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-21T07:08:54.000Z</v>
+        <v>2026-07-21T09:41:08.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>INC000000153022</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-21T09:41:08.000Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>INC000000153111</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-20T18:58:17.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>INC000000153027</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-20T18:58:17.000Z</v>
+        <v>2026-07-21T07:52:42.999Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-21T07:52:42.999Z</v>
+        <v>2026-07-21T11:43:36.999Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>WO0000000309779</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-21T11:43:36.999Z</v>
+        <v>2026-07-21T10:36:26.000Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-21T10:36:26.000Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>INC000000153121</v>
+        <v>INC000000153031</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-21T09:40:02.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>INC000000153031</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-21T09:40:02.000Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>WO0000000309780</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>WO0000000309837</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>WO0000000309781</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-21T08:57:28.999Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>WO0000000309783</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>WO0000000309838</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-21T07:41:05.999Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>INC000000153034</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-21T07:41:05.999Z</v>
+        <v>2026-07-21T07:47:06.000Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>INC000000153035</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-21T07:47:06.000Z</v>
+        <v>2026-07-21T07:58:21.000Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>INC000000153036</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-21T07:58:21.000Z</v>
+        <v>2026-07-21T08:01:28.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>INC000000153037</v>
+        <v>INC000000153123</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-21T08:01:28.000Z</v>
+        <v>2026-07-21T07:54:40.000Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>INC000000153123</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-21T07:54:40.000Z</v>
+        <v>2026-07-20T08:42:15.000Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153125</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-20T08:42:15.000Z</v>
+        <v>2026-07-21T07:46:07.000Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>INC000000153125</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-21T07:46:07.000Z</v>
+        <v>2026-07-21T09:45:18.000Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309791</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-21T09:45:18.000Z</v>
+        <v>2026-07-21T12:02:04.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>WO0000000309791</v>
+        <v>WO0000000309792</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-21T12:02:04.000Z</v>
+        <v>2026-07-20T14:10:35.999Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>WO0000000309792</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-20T14:10:35.999Z</v>
+        <v>2026-07-21T09:36:30.999Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000309841</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-21T09:36:30.999Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>WO0000000309842</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T08:43:23.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>INC000000153128</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-21T08:43:23.000Z</v>
+        <v>2026-07-20T18:35:59.000Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>WO0000000309793</v>
+        <v>WO0000000309794</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-20T18:35:59.000Z</v>
+        <v>2026-07-20T18:20:05.999Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>WO0000000309794</v>
+        <v>WO0000000309843</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-20T18:20:05.999Z</v>
+        <v>2026-07-20T18:23:24.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>WO0000000309843</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-20T18:23:24.000Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>WO0000000309848</v>
+        <v>WO0000000309797</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-20T19:09:36.000Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>WO0000000309797</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-20T19:09:36.000Z</v>
+        <v>2026-07-21T10:57:08.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>WO0000000309851</v>
+        <v>WO0000000309798</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-21T10:57:08.000Z</v>
+        <v>2026-07-21T07:04:25.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>WO0000000309798</v>
+        <v>WO0000000309852</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-21T07:04:25.000Z</v>
+        <v>2026-07-20T22:58:26.999Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>WO0000000309852</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-20T22:58:26.999Z</v>
+        <v>2026-07-21T11:38:15.000Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-21T11:38:15.000Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>WO0000000309902</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T06:40:04.000Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153050</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-21T06:40:04.000Z</v>
+        <v>2026-07-21T07:46:48.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>INC000000153050</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-21T07:46:48.000Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>INC000000153048</v>
+        <v>INC000000153137</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T07:03:14.999Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>INC000000153137</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-21T07:03:14.999Z</v>
+        <v>2026-07-21T11:41:14.000Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>WO0000000309914</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-21T07:20:13.999Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>INC000000153138</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-21T11:41:14.000Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>INC000000153052</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T09:37:42.999Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>WO0000000309862</v>
+        <v>INC000000153053</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T08:05:04.000Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>WO0000000309861</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-21T09:37:42.999Z</v>
+        <v>2026-07-21T12:00:33.000Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>INC000000153053</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-21T08:05:04.000Z</v>
+        <v>2026-07-21T08:34:57.999Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>WO0000000309927</v>
+        <v>WO0000000309867</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-21T07:54:45.999Z</v>
+        <v>2026-07-21T08:13:16.000Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>INC000000153056</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-21T12:00:33.000Z</v>
+        <v>2026-07-21T07:57:56.999Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>WO0000000309931</v>
+        <v>INC000000153060</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-21T08:34:57.999Z</v>
+        <v>2026-07-21T12:04:42.000Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>WO0000000309867</v>
+        <v>INC000000153061</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-21T08:13:16.000Z</v>
+        <v>2026-07-21T10:54:42.999Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-21T07:57:56.999Z</v>
+        <v>2026-07-21T10:38:36.000Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>INC000000153060</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-21T12:04:42.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>INC000000153061</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-21T10:54:42.999Z</v>
+        <v>2026-07-21T10:15:53.000Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>INC000000153062</v>
+        <v>WO0000000309877</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-21T10:38:36.000Z</v>
+        <v>2026-07-21T08:15:48.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>INC000000153143</v>
+        <v>WO0000000309878</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T08:35:47.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>INC000000153145</v>
+        <v>WO0000000309941</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-21T10:15:53.000Z</v>
+        <v>2026-07-21T09:14:35.999Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>WO0000000309877</v>
+        <v>WO0000000309879</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-21T08:15:48.000Z</v>
+        <v>2026-07-21T08:17:04.000Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000309878</v>
+        <v>WO0000000309944</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-21T08:35:47.000Z</v>
+        <v>2026-07-21T11:26:10.999Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>WO0000000309941</v>
+        <v>INC000000153149</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-21T09:14:35.999Z</v>
+        <v>2026-07-21T08:58:21.000Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>WO0000000309879</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-21T08:17:04.000Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>WO0000000309944</v>
+        <v>INC000000153151</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-21T11:26:10.999Z</v>
+        <v>2026-07-21T09:13:22.999Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>INC000000153149</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-21T08:58:21.000Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>WO0000000309880</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>INC000000153151</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-21T09:13:22.999Z</v>
+        <v>2026-07-21T11:32:54.000Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>WO0000000309945</v>
+        <v>INC000000153064</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T08:40:21.000Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>WO0000000309946</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T09:45:12.999Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>INC000000153065</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-21T11:32:54.000Z</v>
+        <v>2026-07-21T09:47:21.999Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>INC000000153064</v>
+        <v>WO0000000309888</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-21T08:40:21.000Z</v>
+        <v>2026-07-21T08:44:29.999Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>INC000000153153</v>
+        <v>WO0000000309950</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-21T09:45:12.999Z</v>
+        <v>2026-07-21T08:39:49.000Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>WO0000000309949</v>
+        <v>WO0000000309952</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-21T09:47:21.999Z</v>
+        <v>2026-07-21T08:33:13.000Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>WO0000000309888</v>
+        <v>WO0000000309953</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-21T08:44:29.999Z</v>
+        <v>2026-07-21T08:41:50.000Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>WO0000000309950</v>
+        <v>WO0000000309889</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-21T08:39:49.000Z</v>
+        <v>2026-07-21T08:33:25.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>WO0000000309952</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-21T08:33:13.000Z</v>
+        <v>2026-07-21T08:48:14.999Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>WO0000000309953</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-21T08:41:50.000Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000309889</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-21T08:33:25.000Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-21T08:48:14.999Z</v>
+        <v>2026-07-21T08:49:28.000Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>WO0000000309892</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-21T09:04:46.000Z</v>
+        <v>2026-07-21T10:35:54.000Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>WO0000000309954</v>
+        <v>INC000000153073</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T10:27:24.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>INC000000153072</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-21T08:49:28.000Z</v>
+        <v>2026-07-21T12:07:43.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>INC000000153159</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-21T10:35:54.000Z</v>
+        <v>2026-07-21T10:28:57.999Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>INC000000153073</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-21T10:27:24.000Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>INC000000153075</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-21T09:12:07.000Z</v>
+        <v>2026-07-21T12:09:03.000Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000310002</v>
+        <v>WO0000000310005</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-21T09:22:48.000Z</v>
+        <v>2026-07-21T09:32:59.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>WO0000000309957</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-21T10:28:57.999Z</v>
+        <v>2026-07-21T11:27:26.000Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>WO0000000309958</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-21T08:54:45.000Z</v>
+        <v>2026-07-21T09:20:33.000Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>WO0000000310004</v>
+        <v>INC000000153076</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-21T09:21:34.000Z</v>
+        <v>2026-07-21T11:26:27.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>WO0000000310005</v>
+        <v>WO0000000310008</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T09:32:59.000Z</v>
+        <v>2026-07-21T11:05:13.999Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>WO0000000309959</v>
+        <v>WO0000000309962</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-21T11:27:26.000Z</v>
+        <v>2026-07-21T09:15:42.999Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>WO0000000310006</v>
+        <v>WO0000000310009</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-21T09:20:33.000Z</v>
+        <v>2026-07-21T10:38:41.000Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000153076</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T11:26:27.000Z</v>
+        <v>2026-07-21T09:03:20.999Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>WO0000000310008</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-21T11:05:13.999Z</v>
+        <v>2026-07-21T09:28:19.000Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>WO0000000309962</v>
+        <v>WO0000000309967</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-21T09:15:42.999Z</v>
+        <v>2026-07-21T09:02:23.000Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000310009</v>
+        <v>WO0000000310013</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-21T10:38:41.000Z</v>
+        <v>2026-07-21T09:07:07.000Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>INC000000153074</v>
+        <v>WO0000000309973</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-21T09:03:20.999Z</v>
+        <v>2026-07-21T11:05:17.000Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>WO0000000309961</v>
+        <v>WO0000000310015</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-21T09:28:19.000Z</v>
+        <v>2026-07-21T09:27:41.000Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>WO0000000309967</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-21T09:02:23.000Z</v>
+        <v>2026-07-21T11:44:25.999Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>WO0000000310013</v>
+        <v>WO0000000310016</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-21T09:07:07.000Z</v>
+        <v>2026-07-21T11:47:23.999Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>WO0000000309973</v>
+        <v>INC000000153168</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-21T11:05:17.000Z</v>
+        <v>2026-07-21T09:54:40.000Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>WO0000000310015</v>
+        <v>WO0000000310017</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-21T09:27:41.000Z</v>
+        <v>2026-07-21T09:29:50.999Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>INC000000153163</v>
+        <v>WO0000000310018</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-21T11:44:25.999Z</v>
+        <v>2026-07-21T09:18:47.000Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>WO0000000310016</v>
+        <v>WO0000000310019</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-21T11:47:23.999Z</v>
+        <v>2026-07-21T10:19:05.000Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>INC000000153168</v>
+        <v>WO0000000309981</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-21T09:54:40.000Z</v>
+        <v>2026-07-21T11:22:20.000Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>WO0000000310017</v>
+        <v>INC000000153165</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-21T09:29:50.999Z</v>
+        <v>2026-07-21T09:36:23.000Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>WO0000000310018</v>
+        <v>WO0000000310021</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-21T09:18:47.000Z</v>
+        <v>2026-07-21T09:24:02.000Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>WO0000000310019</v>
+        <v>INC000000153172</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-21T10:19:05.000Z</v>
+        <v>2026-07-21T09:52:46.999Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>WO0000000309981</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-21T11:22:20.000Z</v>
+        <v>2026-07-21T10:36:09.999Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>INC000000153165</v>
+        <v>INC000000153174</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-21T09:36:23.000Z</v>
+        <v>2026-07-21T09:57:25.000Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>WO0000000310021</v>
+        <v>INC000000153175</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-21T09:24:02.000Z</v>
+        <v>2026-07-21T09:28:26.000Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>INC000000153172</v>
+        <v>WO0000000309986</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-21T09:52:46.999Z</v>
+        <v>2026-07-21T09:28:28.999Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>INC000000153167</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-21T10:36:09.999Z</v>
+        <v>2026-07-21T09:27:18.999Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>INC000000153174</v>
+        <v>WO0000000309975</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-21T09:57:25.000Z</v>
+        <v>2026-07-21T09:49:40.999Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>INC000000153175</v>
+        <v>WO0000000309984</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-21T09:28:26.000Z</v>
+        <v>2026-07-21T09:31:44.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>WO0000000309986</v>
+        <v>INC000000153177</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-21T09:28:28.999Z</v>
+        <v>2026-07-21T09:31:53.000Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>WO0000000309985</v>
+        <v>INC000000153080</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-21T09:27:18.999Z</v>
+        <v>2026-07-21T11:54:46.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>WO0000000309975</v>
+        <v>INC000000153171</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-21T09:49:40.999Z</v>
+        <v>2026-07-21T10:25:59.000Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>WO0000000309984</v>
+        <v>INC000000153176</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-21T09:31:44.000Z</v>
+        <v>2026-07-21T09:43:34.000Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>WO0000000309987</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-21T09:30:18.000Z</v>
+        <v>2026-07-21T09:37:20.999Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>INC000000153177</v>
+        <v>WO0000000310025</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-21T09:31:53.000Z</v>
+        <v>2026-07-21T09:36:55.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>INC000000153080</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-21T11:54:46.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>INC000000153171</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-21T10:25:59.000Z</v>
+        <v>2026-07-21T09:40:19.000Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>INC000000153176</v>
+        <v>INC000000153181</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-21T09:43:34.000Z</v>
+        <v>2026-07-21T09:48:10.999Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000309993</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-21T09:37:20.999Z</v>
+        <v>2026-07-21T09:41:07.000Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>WO0000000310025</v>
+        <v>INC000000153178</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-21T09:36:55.000Z</v>
+        <v>2026-07-21T10:29:02.000Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>WO0000000310028</v>
+        <v>INC000000153082</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-21T09:40:19.000Z</v>
+        <v>2026-07-21T10:22:17.000Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>INC000000153181</v>
+        <v>WO0000000309991</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-21T09:48:10.999Z</v>
+        <v>2026-07-21T11:20:05.000Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>WO0000000309993</v>
+        <v>INC000000153179</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-21T09:41:07.000Z</v>
+        <v>2026-07-21T09:46:47.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>INC000000153178</v>
+        <v>WO0000000309995</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-21T10:29:02.000Z</v>
+        <v>2026-07-21T10:01:19.000Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000305266</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>INC000000153082</v>
+        <v>WO0000000309997</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-21T10:22:17.000Z</v>
+        <v>2026-07-21T11:45:35.000Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>WO0000000309991</v>
+        <v>WO0000000309998</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-21T11:20:05.000Z</v>
+        <v>2026-07-21T09:47:07.999Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>INC000000153179</v>
+        <v>WO0000000309996</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-21T09:46:47.000Z</v>
+        <v>2026-07-21T09:49:05.999Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>WO0000000309995</v>
+        <v>INC000000153182</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-21T10:01:19.000Z</v>
+        <v>2026-07-21T10:35:39.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>WO0000000305266</v>
+        <v>WO0000000310000</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
+        <v>2026-07-21T09:49:32.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>WO0000000309997</v>
+        <v>WO0000000309999</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-21T11:45:35.000Z</v>
+        <v>2026-07-21T09:50:29.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>WO0000000309998</v>
+        <v>WO0000000310102</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-21T09:47:07.999Z</v>
+        <v>2026-07-21T09:50:55.000Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>WO0000000309996</v>
+        <v>WO0000000310033</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-21T09:49:05.999Z</v>
+        <v>2026-07-21T09:51:00.000Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>INC000000153182</v>
+        <v>INC000000153185</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-21T10:35:39.000Z</v>
+        <v>2026-07-21T10:21:27.999Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>WO0000000310000</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-21T09:49:32.000Z</v>
+        <v>2026-07-21T09:55:33.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>WO0000000309999</v>
+        <v>WO0000000305268</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-21T09:50:29.000Z</v>
+        <v>2026-07-21T09:55:25.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>WO0000000310102</v>
+        <v>INC000000153083</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-21T09:50:55.000Z</v>
+        <v>2026-07-21T10:29:05.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>WO0000000310033</v>
+        <v>WO0000000310105</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-21T09:51:00.000Z</v>
+        <v>2026-07-21T10:09:51.000Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>INC000000153185</v>
+        <v>INC000000153084</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-21T10:21:27.999Z</v>
+        <v>2026-07-21T10:22:19.000Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>INC000000153183</v>
+        <v>WO0000000305269</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-21T09:55:33.000Z</v>
+        <v>2026-07-21T09:57:11.000Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>WO0000000305268</v>
+        <v>WO0000000310034</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-21T09:55:25.000Z</v>
+        <v>2026-07-21T10:02:08.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>INC000000153083</v>
+        <v>WO0000000310106</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-21T10:29:05.000Z</v>
+        <v>2026-07-21T10:02:21.999Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000310105</v>
+        <v>WO0000000310107</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-21T10:09:51.000Z</v>
+        <v>2026-07-21T10:27:27.999Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>INC000000153084</v>
+        <v>WO0000000310036</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-21T10:22:19.000Z</v>
+        <v>2026-07-21T09:59:20.000Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>WO0000000305269</v>
+        <v>INC000000153186</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-21T09:57:11.000Z</v>
+        <v>2026-07-21T11:41:02.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>WO0000000310034</v>
+        <v>WO0000000310109</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-21T10:02:08.000Z</v>
+        <v>2026-07-21T10:07:20.999Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>WO0000000310106</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-21T10:02:21.999Z</v>
+        <v>2026-07-21T10:05:59.000Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>WO0000000310107</v>
+        <v>WO0000000310039</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-21T10:27:27.999Z</v>
+        <v>2026-07-21T11:49:30.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>WO0000000310036</v>
+        <v>INC000000153086</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-21T09:59:20.000Z</v>
+        <v>2026-07-21T10:23:37.999Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>INC000000153186</v>
+        <v>WO0000000310040</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-21T11:41:02.000Z</v>
+        <v>2026-07-21T10:09:05.000Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>WO0000000310109</v>
+        <v>INC000000153187</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-21T10:07:20.999Z</v>
+        <v>2026-07-21T10:25:14.000Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>INC000000153184</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-21T10:05:59.000Z</v>
+        <v>2026-07-21T10:31:45.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>WO0000000310039</v>
+        <v>INC000000153089</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-21T11:49:30.000Z</v>
+        <v>2026-07-21T10:28:35.000Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>INC000000153086</v>
+        <v>WO0000000310045</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-21T10:23:37.999Z</v>
+        <v>2026-07-21T11:47:28.999Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>WO0000000310040</v>
+        <v>INC000000153090</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-21T10:09:05.000Z</v>
+        <v>2026-07-21T10:32:06.999Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>INC000000153187</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-21T10:25:14.000Z</v>
+        <v>2026-07-21T11:44:30.999Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>WO0000000310111</v>
+        <v>INC000000153091</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-21T10:31:45.000Z</v>
+        <v>2026-07-21T10:30:46.000Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>INC000000153089</v>
+        <v>INC000000153094</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-21T10:28:35.000Z</v>
+        <v>2026-07-21T10:34:10.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>WO0000000310045</v>
+        <v>WO0000000310114</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-21T11:47:28.999Z</v>
+        <v>2026-07-21T10:12:20.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>INC000000153090</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-21T10:32:06.999Z</v>
+        <v>2026-07-21T10:13:41.000Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310113</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-21T11:44:30.999Z</v>
+        <v>2026-07-21T10:32:45.000Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>INC000000153091</v>
+        <v>WO0000000310046</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-21T10:30:46.000Z</v>
+        <v>2026-07-21T10:13:36.000Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>INC000000153094</v>
+        <v>INC000000153088</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-21T10:34:10.000Z</v>
+        <v>2026-07-21T10:17:32.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>WO0000000310114</v>
+        <v>WO0000000310047</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-21T10:12:20.000Z</v>
+        <v>2026-07-21T10:14:06.000Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153188</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-21T10:13:41.000Z</v>
+        <v>2026-07-21T10:16:45.000Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>WO0000000310113</v>
+        <v>WO0000000310118</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-21T10:32:45.000Z</v>
+        <v>2026-07-21T10:29:50.999Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>WO0000000310046</v>
+        <v>INC000000153189</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-21T10:13:36.000Z</v>
+        <v>2026-07-21T11:21:36.999Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>INC000000153088</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-21T10:17:32.000Z</v>
+        <v>2026-07-21T11:39:39.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>WO0000000310047</v>
+        <v>WO0000000310049</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-21T10:14:06.000Z</v>
+        <v>2026-07-21T10:20:08.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>INC000000153188</v>
+        <v>INC000000153190</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-21T10:16:45.000Z</v>
+        <v>2026-07-21T10:38:37.999Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>WO0000000310118</v>
+        <v>WO0000000310050</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-21T10:29:50.999Z</v>
+        <v>2026-07-21T10:21:12.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>INC000000153189</v>
+        <v>INC000000153191</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-21T11:21:36.999Z</v>
+        <v>2026-07-21T10:54:13.999Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153192</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-21T11:39:39.000Z</v>
+        <v>2026-07-21T10:26:23.999Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>WO0000000310049</v>
+        <v>WO0000000310051</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-21T10:20:08.000Z</v>
+        <v>2026-07-21T10:23:58.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>INC000000153190</v>
+        <v>INC000000153193</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-21T10:38:37.999Z</v>
+        <v>2026-07-21T10:25:57.999Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>WO0000000310050</v>
+        <v>WO0000000310120</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-21T10:21:12.000Z</v>
+        <v>2026-07-21T10:35:25.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>INC000000153191</v>
+        <v>WO0000000310053</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-21T10:54:13.999Z</v>
+        <v>2026-07-21T10:27:39.999Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>INC000000153192</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-21T10:26:23.999Z</v>
+        <v>2026-07-21T10:53:52.000Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>WO0000000310051</v>
+        <v>INC000000153100</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-21T10:23:58.000Z</v>
+        <v>2026-07-21T10:36:40.000Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>INC000000153193</v>
+        <v>INC000000153194</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-21T10:25:57.999Z</v>
+        <v>2026-07-21T10:31:29.999Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>WO0000000310120</v>
+        <v>INC000000153099</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-21T10:35:25.000Z</v>
+        <v>2026-07-21T10:34:51.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>WO0000000310053</v>
+        <v>INC000000153095</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-21T10:27:39.999Z</v>
+        <v>2026-07-21T10:34:35.999Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>INC000000153195</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-21T10:53:52.000Z</v>
+        <v>2026-07-21T10:52:52.999Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>INC000000153100</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-21T10:36:40.000Z</v>
+        <v>2026-07-21T11:15:36.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>INC000000153194</v>
+        <v>INC000000153201</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-21T10:31:29.999Z</v>
+        <v>2026-07-21T10:39:28.000Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>INC000000153099</v>
+        <v>WO0000000310123</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-21T10:34:51.000Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>INC000000153095</v>
+        <v>WO0000000310055</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-21T10:34:35.999Z</v>
+        <v>2026-07-21T11:51:43.999Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>WO0000000310124</v>
+        <v>INC000000153202</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-21T10:52:52.999Z</v>
+        <v>2026-07-21T10:40:42.000Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>INC000000153196</v>
+        <v>INC000000153197</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-21T11:15:36.000Z</v>
+        <v>2026-07-21T10:44:35.999Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>INC000000153201</v>
+        <v>INC000000153203</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-21T10:39:28.000Z</v>
+        <v>2026-07-21T11:06:42.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>WO0000000310123</v>
+        <v>WO0000000310127</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-21T10:36:47.999Z</v>
+        <v>2026-07-21T11:02:10.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>WO0000000310055</v>
+        <v>INC000000153204</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-21T11:51:43.999Z</v>
+        <v>2026-07-21T11:17:56.000Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>INC000000153202</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-21T10:40:42.000Z</v>
+        <v>2026-07-21T10:46:52.000Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>INC000000153197</v>
+        <v>WO0000000310061</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-21T10:44:35.999Z</v>
+        <v>2026-07-21T10:47:06.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>INC000000153203</v>
+        <v>INC000000153205</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-21T11:06:42.000Z</v>
+        <v>2026-07-21T10:54:13.999Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>WO0000000310127</v>
+        <v>WO0000000310130</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-21T11:02:10.000Z</v>
+        <v>2026-07-21T11:43:10.000Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>INC000000153204</v>
+        <v>INC000000153210</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-21T11:17:56.000Z</v>
+        <v>2026-07-21T10:50:21.999Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>WO0000000310060</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-21T10:46:52.000Z</v>
+        <v>2026-07-21T11:06:54.000Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>WO0000000310061</v>
+        <v>INC000000153209</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-21T10:47:06.000Z</v>
+        <v>2026-07-21T11:43:04.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>INC000000153205</v>
+        <v>INC000000153211</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-21T10:54:13.999Z</v>
+        <v>2026-07-21T10:52:02.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>WO0000000310130</v>
+        <v>WO0000000310135</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-21T11:43:10.000Z</v>
+        <v>2026-07-21T10:51:40.000Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>INC000000153210</v>
+        <v>INC000000153200</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-21T10:50:21.999Z</v>
+        <v>2026-07-21T11:03:32.000Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>INC000000153206</v>
+        <v>WO0000000310136</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-21T11:06:54.000Z</v>
+        <v>2026-07-21T10:53:26.000Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>INC000000153209</v>
+        <v>WO0000000310133</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-21T11:43:04.000Z</v>
+        <v>2026-07-21T10:56:06.999Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>INC000000153211</v>
+        <v>INC000000153301</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-21T10:52:02.000Z</v>
+        <v>2026-07-21T10:56:25.000Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>WO0000000310135</v>
+        <v>INC000000153214</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-21T10:51:40.000Z</v>
+        <v>2026-07-21T11:00:05.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>INC000000153200</v>
+        <v>INC000000153302</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-21T11:03:32.000Z</v>
+        <v>2026-07-21T11:41:02.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>WO0000000310136</v>
+        <v>INC000000153216</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-21T10:53:26.000Z</v>
+        <v>2026-07-21T11:56:48.000Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>WO0000000310133</v>
+        <v>WO0000000310065</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-21T10:56:06.999Z</v>
+        <v>2026-07-21T10:59:33.000Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>INC000000153301</v>
+        <v>INC000000153303</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-21T10:56:25.000Z</v>
+        <v>2026-07-21T11:58:21.000Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>INC000000153214</v>
+        <v>INC000000153215</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-21T11:00:05.000Z</v>
+        <v>2026-07-21T11:22:23.000Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>INC000000153302</v>
+        <v>WO0000000310066</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-21T11:41:02.000Z</v>
+        <v>2026-07-21T11:39:17.000Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>INC000000153216</v>
+        <v>WO0000000310069</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-21T11:56:48.000Z</v>
+        <v>2026-07-21T11:40:34.000Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>WO0000000310065</v>
+        <v>WO0000000310144</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-21T10:59:33.000Z</v>
+        <v>2026-07-21T11:06:24.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>INC000000153303</v>
+        <v>INC000000153217</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-21T11:58:21.000Z</v>
+        <v>2026-07-21T11:09:03.999Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>INC000000153215</v>
+        <v>WO0000000310145</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-21T11:22:23.000Z</v>
+        <v>2026-07-21T11:44:29.999Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>WO0000000310066</v>
+        <v>INC000000153306</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-21T11:39:17.000Z</v>
+        <v>2026-07-21T12:03:12.000Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>WO0000000310069</v>
+        <v>WO0000000310143</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-21T11:40:34.000Z</v>
+        <v>2026-07-21T11:08:15.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>WO0000000310144</v>
+        <v>INC000000153305</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-21T11:06:24.000Z</v>
+        <v>2026-07-21T11:15:25.999Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>INC000000153217</v>
+        <v>INC000000153307</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-21T11:09:03.999Z</v>
+        <v>2026-07-21T11:58:18.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>WO0000000310145</v>
+        <v>INC000000153308</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-21T11:44:29.999Z</v>
+        <v>2026-07-21T11:12:32.000Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>INC000000153306</v>
+        <v>WO0000000310147</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-21T12:03:12.000Z</v>
+        <v>2026-07-21T11:11:37.999Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>WO0000000310143</v>
+        <v>WO0000000310070</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-21T11:08:15.000Z</v>
+        <v>2026-07-21T11:11:55.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>INC000000153305</v>
+        <v>WO0000000310148</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-21T11:15:25.999Z</v>
+        <v>2026-07-21T12:03:39.000Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>INC000000153307</v>
+        <v>WO0000000310071</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-21T11:58:18.000Z</v>
+        <v>2026-07-21T11:47:34.000Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>INC000000153308</v>
+        <v>WO0000000310150</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-21T11:12:32.000Z</v>
+        <v>2026-07-21T11:39:39.000Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>WO0000000310147</v>
+        <v>INC000000153309</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-21T11:11:37.999Z</v>
+        <v>2026-07-21T11:17:57.999Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>WO0000000310070</v>
+        <v>INC000000153218</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-21T11:11:55.000Z</v>
+        <v>2026-07-21T11:47:28.999Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>WO0000000310148</v>
+        <v>INC000000153313</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-21T12:03:39.000Z</v>
+        <v>2026-07-21T11:25:19.000Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>WO0000000310071</v>
+        <v>WO0000000310078</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-21T11:47:34.000Z</v>
+        <v>2026-07-21T11:19:43.999Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>WO0000000310150</v>
+        <v>WO0000000310079</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-21T11:39:39.000Z</v>
+        <v>2026-07-21T11:48:08.999Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>INC000000153309</v>
+        <v>WO0000000310080</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-21T11:17:57.999Z</v>
+        <v>2026-07-21T11:20:20.000Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>INC000000153218</v>
+        <v>WO0000000310082</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-21T11:47:28.999Z</v>
+        <v>2026-07-21T11:21:29.000Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>INC000000153313</v>
+        <v>WO0000000310157</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-21T11:25:19.000Z</v>
+        <v>2026-07-21T11:45:08.999Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>WO0000000310078</v>
+        <v>WO0000000310083</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-21T11:19:43.999Z</v>
+        <v>2026-07-21T11:46:24.999Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>WO0000000310079</v>
+        <v>INC000000153315</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-21T11:48:08.999Z</v>
+        <v>2026-07-21T11:38:51.000Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>WO0000000310080</v>
+        <v>WO0000000310160</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-21T11:20:20.000Z</v>
+        <v>2026-07-21T11:27:58.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>WO0000000310082</v>
+        <v>WO0000000310161</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-21T11:21:29.000Z</v>
+        <v>2026-07-21T11:25:35.000Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>WO0000000310157</v>
+        <v>WO0000000310158</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-21T11:45:08.999Z</v>
+        <v>2026-07-21T11:26:22.000Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>WO0000000310083</v>
+        <v>WO0000000310076</v>
       </c>
       <c r="B1181" s="1" t="d">
-        <v>2026-07-21T11:46:24.999Z</v>
+        <v>2026-07-21T11:39:13.000Z</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="str">
-        <v>INC000000153315</v>
+        <v>WO0000000310087</v>
       </c>
       <c r="B1182" s="1" t="d">
-        <v>2026-07-21T11:38:51.000Z</v>
+        <v>2026-07-21T11:46:35.000Z</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="str">
-        <v>WO0000000310160</v>
+        <v>INC000000153220</v>
       </c>
       <c r="B1183" s="1" t="d">
-        <v>2026-07-21T11:27:58.000Z</v>
+        <v>2026-07-21T11:47:03.000Z</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="str">
-        <v>WO0000000310161</v>
+        <v>INC000000153219</v>
       </c>
       <c r="B1184" s="1" t="d">
-        <v>2026-07-21T11:25:35.000Z</v>
+        <v>2026-07-21T11:33:12.000Z</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>WO0000000310158</v>
+        <v>INC000000153317</v>
       </c>
       <c r="B1185" s="1" t="d">
-        <v>2026-07-21T11:26:22.000Z</v>
+        <v>2026-07-21T11:51:10.000Z</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>WO0000000310076</v>
+        <v>INC000000153222</v>
       </c>
       <c r="B1186" s="1" t="d">
-        <v>2026-07-21T11:39:13.000Z</v>
+        <v>2026-07-21T11:45:37.999Z</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="str">
-        <v>WO0000000310087</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B1187" s="1" t="d">
-        <v>2026-07-21T11:46:35.000Z</v>
+        <v>2026-07-21T11:44:50.999Z</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="str">
-        <v>INC000000153220</v>
+        <v>INC000000153316</v>
       </c>
       <c r="B1188" s="1" t="d">
-        <v>2026-07-21T11:47:03.000Z</v>
+        <v>2026-07-21T11:44:00.000Z</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="str">
-        <v>INC000000153219</v>
+        <v>INC000000153224</v>
       </c>
       <c r="B1189" s="1" t="d">
-        <v>2026-07-21T11:33:12.000Z</v>
+        <v>2026-07-21T11:38:28.999Z</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="str">
-        <v>INC000000153317</v>
+        <v>WO0000000310091</v>
       </c>
       <c r="B1190" s="1" t="d">
-        <v>2026-07-21T11:51:10.000Z</v>
+        <v>2026-07-21T11:48:18.000Z</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="str">
-        <v>INC000000153222</v>
+        <v>WO0000000310092</v>
       </c>
       <c r="B1191" s="1" t="d">
-        <v>2026-07-21T11:45:37.999Z</v>
+        <v>2026-07-21T11:41:17.000Z</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="str">
-        <v>WO0000000310164</v>
+        <v>WO0000000310168</v>
       </c>
       <c r="B1192" s="1" t="d">
-        <v>2026-07-21T11:44:50.999Z</v>
+        <v>2026-07-21T11:47:52.000Z</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="str">
-        <v>INC000000153316</v>
+        <v>WO0000000310170</v>
       </c>
       <c r="B1193" s="1" t="d">
-        <v>2026-07-21T11:44:00.000Z</v>
+        <v>2026-07-21T11:40:48.000Z</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="str">
-        <v>INC000000153224</v>
+        <v>INC000000153225</v>
       </c>
       <c r="B1194" s="1" t="d">
-        <v>2026-07-21T11:38:28.999Z</v>
+        <v>2026-07-21T11:59:26.000Z</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="str">
-        <v>WO0000000310091</v>
+        <v>INC000000153221</v>
       </c>
       <c r="B1195" s="1" t="d">
-        <v>2026-07-21T11:48:18.000Z</v>
+        <v>2026-07-21T11:45:32.000Z</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="str">
-        <v>WO0000000310092</v>
+        <v>WO0000000310172</v>
       </c>
       <c r="B1196" s="1" t="d">
-        <v>2026-07-21T11:41:17.000Z</v>
+        <v>2026-07-21T11:41:57.000Z</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="str">
-        <v>WO0000000310168</v>
+        <v>INC000000153223</v>
       </c>
       <c r="B1197" s="1" t="d">
-        <v>2026-07-21T11:47:52.000Z</v>
+        <v>2026-07-21T11:53:49.000Z</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="str">
-        <v>WO0000000310170</v>
+        <v>INC000000153318</v>
       </c>
       <c r="B1198" s="1" t="d">
-        <v>2026-07-21T11:40:48.000Z</v>
+        <v>2026-07-21T11:50:13.000Z</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="str">
-        <v>INC000000153225</v>
+        <v>WO0000000310173</v>
       </c>
       <c r="B1199" s="1" t="d">
-        <v>2026-07-21T11:59:26.000Z</v>
+        <v>2026-07-21T11:57:54.999Z</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="str">
-        <v>INC000000153221</v>
+        <v>WO0000000310174</v>
       </c>
       <c r="B1200" s="1" t="d">
-        <v>2026-07-21T11:45:32.000Z</v>
+        <v>2026-07-21T11:45:39.000Z</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="str">
-        <v>WO0000000310172</v>
+        <v>WO0000000310175</v>
       </c>
       <c r="B1201" s="1" t="d">
-        <v>2026-07-21T11:41:57.000Z</v>
+        <v>2026-07-21T11:46:24.000Z</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="str">
-        <v>INC000000153223</v>
+        <v>WO0000000310146</v>
       </c>
       <c r="B1202" s="1" t="d">
-        <v>2026-07-21T11:53:49.000Z</v>
+        <v>2026-07-21T11:50:49.000Z</v>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="str">
-        <v>INC000000153318</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B1203" s="1" t="d">
-        <v>2026-07-21T11:50:13.000Z</v>
+        <v>2026-07-21T11:51:10.000Z</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="str">
-        <v>WO0000000310173</v>
+        <v>WO0000000310095</v>
       </c>
       <c r="B1204" s="1" t="d">
-        <v>2026-07-21T11:57:54.999Z</v>
+        <v>2026-07-21T11:48:59.000Z</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="str">
-        <v>WO0000000310174</v>
+        <v>WO0000000310171</v>
       </c>
       <c r="B1205" s="1" t="d">
-        <v>2026-07-21T11:45:39.000Z</v>
+        <v>2026-07-21T11:57:09.000Z</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="str">
-        <v>WO0000000310175</v>
+        <v>INC000000153320</v>
       </c>
       <c r="B1206" s="1" t="d">
-        <v>2026-07-21T11:46:24.000Z</v>
+        <v>2026-07-21T11:54:43.999Z</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="str">
-        <v>WO0000000310146</v>
+        <v>WO0000000310096</v>
       </c>
       <c r="B1207" s="1" t="d">
-        <v>2026-07-21T11:50:49.000Z</v>
+        <v>2026-07-21T12:05:21.000Z</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="str">
-        <v>INC000000153226</v>
+        <v>INC000000153227</v>
       </c>
       <c r="B1208" s="1" t="d">
-        <v>2026-07-21T11:51:10.000Z</v>
+        <v>2026-07-21T11:54:36.000Z</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="str">
-        <v>WO0000000310095</v>
+        <v>INC000000153229</v>
       </c>
       <c r="B1209" s="1" t="d">
-        <v>2026-07-21T11:48:59.000Z</v>
+        <v>2026-07-21T12:07:41.000Z</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="str">
-        <v>WO0000000310171</v>
+        <v>WO0000000310178</v>
       </c>
       <c r="B1210" s="1" t="d">
-        <v>2026-07-21T11:57:09.000Z</v>
+        <v>2026-07-21T11:52:33.000Z</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="str">
-        <v>INC000000153320</v>
+        <v>INC000000153321</v>
       </c>
       <c r="B1211" s="1" t="d">
-        <v>2026-07-21T11:54:43.999Z</v>
+        <v>2026-07-21T11:55:29.999Z</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="str">
-        <v>WO0000000310096</v>
+        <v>WO0000000310098</v>
       </c>
       <c r="B1212" s="1" t="d">
-        <v>2026-07-21T11:51:08.000Z</v>
+        <v>2026-07-21T11:52:54.000Z</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="str">
-        <v>INC000000153227</v>
+        <v>INC000000153231</v>
       </c>
       <c r="B1213" s="1" t="d">
-        <v>2026-07-21T11:54:36.000Z</v>
+        <v>2026-07-21T11:53:42.000Z</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="str">
-        <v>INC000000153229</v>
+        <v>INC000000153230</v>
       </c>
       <c r="B1214" s="1" t="d">
-        <v>2026-07-21T11:51:48.000Z</v>
+        <v>2026-07-21T11:55:49.000Z</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="str">
-        <v>WO0000000310178</v>
+        <v>INC000000153322</v>
       </c>
       <c r="B1215" s="1" t="d">
-        <v>2026-07-21T11:52:33.000Z</v>
+        <v>2026-07-21T11:56:58.999Z</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="str">
-        <v>INC000000153321</v>
+        <v>INC000000153232</v>
       </c>
       <c r="B1216" s="1" t="d">
-        <v>2026-07-21T11:55:29.999Z</v>
+        <v>2026-07-21T12:02:12.999Z</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="str">
-        <v>WO0000000310098</v>
+        <v>INC000000153323</v>
       </c>
       <c r="B1217" s="1" t="d">
-        <v>2026-07-21T11:52:54.000Z</v>
+        <v>2026-07-21T11:57:35.000Z</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="str">
-        <v>INC000000153231</v>
+        <v>WO0000000310179</v>
       </c>
       <c r="B1218" s="1" t="d">
-        <v>2026-07-21T11:53:42.000Z</v>
+        <v>2026-07-21T12:04:24.000Z</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="str">
-        <v>INC000000153230</v>
+        <v>INC000000153324</v>
       </c>
       <c r="B1219" s="1" t="d">
-        <v>2026-07-21T11:55:49.000Z</v>
+        <v>2026-07-21T12:03:28.000Z</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="str">
-        <v>INC000000153322</v>
+        <v>WO0000000310202</v>
       </c>
       <c r="B1220" s="1" t="d">
-        <v>2026-07-21T11:56:58.999Z</v>
+        <v>2026-07-21T12:04:50.000Z</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="str">
-        <v>INC000000153232</v>
+        <v>WO0000000310180</v>
       </c>
       <c r="B1221" s="1" t="d">
-        <v>2026-07-21T12:02:12.999Z</v>
+        <v>2026-07-21T12:00:37.000Z</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="str">
-        <v>INC000000153323</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B1222" s="1" t="d">
-        <v>2026-07-21T11:57:35.000Z</v>
+        <v>2026-07-21T12:04:01.999Z</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="str">
-        <v>WO0000000310179</v>
+        <v>INC000000153327</v>
       </c>
       <c r="B1223" s="1" t="d">
-        <v>2026-07-21T12:04:24.000Z</v>
+        <v>2026-07-21T12:08:54.000Z</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="str">
-        <v>INC000000153324</v>
+        <v>WO0000000310181</v>
       </c>
       <c r="B1224" s="1" t="d">
-        <v>2026-07-21T12:03:28.000Z</v>
+        <v>2026-07-21T12:03:52.999Z</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="str">
-        <v>WO0000000310202</v>
+        <v>INC000000153328</v>
       </c>
       <c r="B1225" s="1" t="d">
-        <v>2026-07-21T11:59:10.000Z</v>
+        <v>2026-07-21T12:07:57.000Z</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="str">
-        <v>WO0000000310201</v>
+        <v>INC000000153233</v>
       </c>
       <c r="B1226" s="1" t="d">
-        <v>2026-07-21T12:03:23.000Z</v>
+        <v>2026-07-21T12:07:20.999Z</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="str">
-        <v>WO0000000310180</v>
+        <v>INC000000153319</v>
       </c>
       <c r="B1227" s="1" t="d">
-        <v>2026-07-21T12:00:37.000Z</v>
+        <v>2026-07-21T12:06:50.999Z</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310204</v>
       </c>
       <c r="B1228" s="1" t="d">
-        <v>2026-07-21T12:04:01.999Z</v>
+        <v>2026-07-21T12:07:52.999Z</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="str">
-        <v>INC000000153327</v>
+        <v>WO0000000310205</v>
       </c>
       <c r="B1229" s="1" t="d">
-        <v>2026-07-21T12:02:55.000Z</v>
+        <v>2026-07-21T12:08:42.000Z</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="str">
-        <v>WO0000000310181</v>
+        <v>WO0000000310203</v>
       </c>
       <c r="B1230" s="1" t="d">
-        <v>2026-07-21T12:03:52.999Z</v>
+        <v>2026-07-21T12:09:05.000Z</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="str">
-        <v>INC000000153328</v>
-      </c>
-      <c r="B1231" s="1" t="d">
-        <v>2026-07-21T12:04:09.000Z</v>
-      </c>
-    </row>
-    <row r="1232">
-      <c r="A1232" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1232"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1231"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1193"/>
+  <dimension ref="A1:B1181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3179,34 +3179,34 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>WO0000000306439</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2026-07-14T16:14:53.000Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>INC000000151466</v>
+        <v>WO0000000306439</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2026-07-14T15:33:23.000Z</v>
+        <v>2026-07-14T16:14:53.000Z</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>INC000000151499</v>
+        <v>INC000000151466</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-14T15:33:23.000Z</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>WO0000000306799</v>
+        <v>INC000000151499</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2026-07-17T08:21:12.999Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="352">
@@ -3486,7 +3486,7 @@
         <v>WO0000000308206</v>
       </c>
       <c r="B386" s="1" t="d">
-        <v>2026-07-17T15:50:26.999Z</v>
+        <v>2026-07-22T09:05:30.000Z</v>
       </c>
     </row>
     <row r="387">
@@ -3494,7 +3494,7 @@
         <v>WO0000000308218</v>
       </c>
       <c r="B387" s="1" t="d">
-        <v>2026-07-17T15:52:30.000Z</v>
+        <v>2026-07-22T09:07:32.000Z</v>
       </c>
     </row>
     <row r="388">
@@ -3539,447 +3539,447 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>WO0000000308340</v>
+        <v>INC000000152378</v>
       </c>
       <c r="B393" s="1" t="d">
-        <v>2026-07-16T09:24:24.999Z</v>
+        <v>2026-07-17T09:05:30.000Z</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>WO0000000308416</v>
+        <v>WO0000000308340</v>
       </c>
       <c r="B394" s="1" t="d">
-        <v>2026-07-16T09:47:42.999Z</v>
+        <v>2026-07-16T09:24:24.999Z</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>WO0000000308442</v>
+        <v>WO0000000308416</v>
       </c>
       <c r="B395" s="1" t="d">
-        <v>2026-07-21T15:41:52.999Z</v>
+        <v>2026-07-16T09:47:42.999Z</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308442</v>
       </c>
       <c r="B396" s="1" t="d">
-        <v>2026-07-16T10:44:20.999Z</v>
+        <v>2026-07-21T15:41:52.999Z</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>WO0000000308360</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B397" s="1" t="d">
-        <v>2026-07-16T12:54:40.000Z</v>
+        <v>2026-07-16T10:44:20.999Z</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>WO0000000308366</v>
+        <v>WO0000000308360</v>
       </c>
       <c r="B398" s="1" t="d">
-        <v>2026-07-16T09:45:50.999Z</v>
+        <v>2026-07-16T12:54:40.000Z</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>WO0000000308461</v>
+        <v>WO0000000308366</v>
       </c>
       <c r="B399" s="1" t="d">
-        <v>2026-07-21T09:25:59.000Z</v>
+        <v>2026-07-16T09:45:50.999Z</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>WO0000000308379</v>
+        <v>WO0000000308461</v>
       </c>
       <c r="B400" s="1" t="d">
-        <v>2026-07-21T12:30:22.999Z</v>
+        <v>2026-07-21T09:25:59.000Z</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>WO0000000308398</v>
+        <v>WO0000000308379</v>
       </c>
       <c r="B401" s="1" t="d">
-        <v>2026-07-16T08:57:27.000Z</v>
+        <v>2026-07-21T12:30:22.999Z</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>WO0000000308399</v>
+        <v>WO0000000308398</v>
       </c>
       <c r="B402" s="1" t="d">
-        <v>2026-07-21T12:30:24.000Z</v>
+        <v>2026-07-16T08:57:27.000Z</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>WO0000000308487</v>
+        <v>WO0000000308399</v>
       </c>
       <c r="B403" s="1" t="d">
-        <v>2026-07-15T22:21:47.000Z</v>
+        <v>2026-07-21T12:30:24.000Z</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>WO0000000308493</v>
+        <v>WO0000000308487</v>
       </c>
       <c r="B404" s="1" t="d">
-        <v>2026-07-22T08:01:07.000Z</v>
+        <v>2026-07-15T22:21:47.000Z</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>INC000000152513</v>
+        <v>WO0000000308493</v>
       </c>
       <c r="B405" s="1" t="d">
-        <v>2026-07-16T09:23:02.000Z</v>
+        <v>2026-07-22T08:01:07.000Z</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>WO0000000308552</v>
+        <v>INC000000152513</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2026-07-16T09:20:55.000Z</v>
+        <v>2026-07-16T09:23:02.000Z</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>WO0000000308648</v>
+        <v>WO0000000308552</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2026-07-21T11:10:08.000Z</v>
+        <v>2026-07-16T09:20:55.000Z</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2026-07-21T11:24:28.999Z</v>
+        <v>2026-07-21T11:10:08.000Z</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2026-07-21T11:55:19.000Z</v>
+        <v>2026-07-21T11:24:28.999Z</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>WO0000000308662</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2026-07-21T16:24:57.000Z</v>
+        <v>2026-07-22T09:40:25.000Z</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>WO0000000308673</v>
+        <v>WO0000000308662</v>
       </c>
       <c r="B411" s="1" t="d">
-        <v>2026-07-16T10:02:00.999Z</v>
+        <v>2026-07-21T16:24:57.000Z</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>WO0000000308675</v>
+        <v>WO0000000308673</v>
       </c>
       <c r="B412" s="1" t="d">
-        <v>2026-07-17T07:31:47.000Z</v>
+        <v>2026-07-16T10:02:00.999Z</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>WO0000000308685</v>
+        <v>WO0000000308675</v>
       </c>
       <c r="B413" s="1" t="d">
-        <v>2026-07-16T10:12:45.000Z</v>
+        <v>2026-07-17T07:31:47.000Z</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>WO0000000308596</v>
+        <v>WO0000000308685</v>
       </c>
       <c r="B414" s="1" t="d">
-        <v>2026-07-16T10:19:52.000Z</v>
+        <v>2026-07-16T10:12:45.000Z</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>WO0000000308701</v>
+        <v>WO0000000308596</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2026-07-16T10:22:52.000Z</v>
+        <v>2026-07-16T10:19:52.000Z</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308701</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-21T12:28:21.000Z</v>
+        <v>2026-07-16T10:22:52.000Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308695</v>
+        <v>WO0000000308696</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-21T15:02:42.000Z</v>
+        <v>2026-07-21T12:28:21.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-21T15:10:53.000Z</v>
+        <v>2026-07-21T15:02:42.000Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>WO0000000308715</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-21T10:45:16.999Z</v>
+        <v>2026-07-21T15:10:53.000Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-21T15:17:00.999Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308809</v>
+        <v>WO0000000308717</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-16T11:14:01.000Z</v>
+        <v>2026-07-21T10:45:16.999Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-21T16:02:36.000Z</v>
+        <v>2026-07-21T15:17:00.999Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308754</v>
+        <v>WO0000000308809</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-21T16:27:01.999Z</v>
+        <v>2026-07-16T11:14:01.000Z</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-21T16:02:36.000Z</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>WO0000000308873</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2026-07-22T08:44:17.000Z</v>
+        <v>2026-07-21T16:27:01.999Z</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>WO0000000308794</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2026-07-21T10:58:56.000Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>WO0000000308917</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2026-07-17T07:59:19.999Z</v>
+        <v>2026-07-22T08:44:17.000Z</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>WO0000000308899</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B429" s="1" t="d">
-        <v>2026-07-22T08:34:00.000Z</v>
+        <v>2026-07-22T09:05:30.000Z</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>WO0000000308926</v>
+        <v>WO0000000308917</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2026-07-21T11:31:06.000Z</v>
+        <v>2026-07-17T07:59:19.999Z</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>WO0000000309002</v>
+        <v>WO0000000308899</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-22T08:34:00.000Z</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>WO0000000309011</v>
+        <v>WO0000000308926</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-21T11:40:57.000Z</v>
+        <v>2026-07-21T11:31:06.000Z</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>WO0000000308938</v>
+        <v>WO0000000309002</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-16T15:07:58.000Z</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>WO0000000308947</v>
+        <v>WO0000000309011</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-22T08:44:17.000Z</v>
+        <v>2026-07-21T11:40:57.000Z</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>WO0000000309025</v>
+        <v>WO0000000308938</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-16T15:31:18.000Z</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000308947</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-21T11:22:24.000Z</v>
+        <v>2026-07-22T08:44:17.000Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>WO0000000309036</v>
+        <v>WO0000000309025</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-16T15:47:35.000Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000309031</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-21T11:34:46.000Z</v>
+        <v>2026-07-22T09:07:32.000Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>WO0000000309041</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-16T16:05:14.000Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>WO0000000308966</v>
+        <v>WO0000000309039</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-22T09:20:00.000Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-21T11:57:24.000Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000309044</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-21T12:03:35.000Z</v>
+        <v>2026-07-22T09:42:27.000Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>WO0000000308975</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-21T12:13:55.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>WO0000000309050</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-22T09:48:32.000Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>WO0000000308987</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-21T12:13:55.000Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>WO0000000309073</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-22T08:01:07.999Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B448" s="1" t="d">
         <v>2026-07-21T12:30:25.000Z</v>
@@ -3987,2183 +3987,2183 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>WO0000000309077</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-22T08:01:07.999Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>WO0000000309079</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-21T12:30:25.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WO0000000308997</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WO0000000308999</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>INC000000152733</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-21T12:30:25.000Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-21T16:29:08.999Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>WO0000000309154</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-21T13:25:40.000Z</v>
+        <v>2026-07-17T06:53:11.000Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>INC000000110345</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-21T17:59:20.999Z</v>
+        <v>2026-07-21T16:29:08.999Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>WO0000000239963</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-21T14:26:22.999Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>WO0000000278645</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-21T14:27:16.000Z</v>
+        <v>2026-07-21T13:25:40.000Z</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>INC000000140158</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-22T09:13:49.000Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>INC000000140767</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>INC000000141766</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-21T08:55:08.000Z</v>
+        <v>2026-07-21T13:50:33.000Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>INC000000142452</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-22T07:39:21.999Z</v>
+        <v>2026-07-21T13:58:39.999Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>INC000000146339</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-21T15:05:15.000Z</v>
+        <v>2026-07-21T16:31:56.000Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>WO0000000295598</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-21T14:09:08.000Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>INC000000147926</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-21T15:43:45.999Z</v>
+        <v>2026-07-21T14:09:08.000Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>WO0000000298353</v>
+        <v>INC000000110345</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-21T19:17:08.000Z</v>
+        <v>2026-07-21T17:59:20.999Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>WO0000000298838</v>
+        <v>WO0000000239963</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-21T15:22:31.000Z</v>
+        <v>2026-07-21T14:26:22.999Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>WO0000000299920</v>
+        <v>WO0000000278645</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-21T15:24:13.999Z</v>
+        <v>2026-07-21T14:27:16.000Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>WO0000000300081</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>INC000000148888</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>WO0000000302331</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-22T08:57:51.999Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>INC000000149757</v>
+        <v>INC000000142452</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-21T16:21:08.000Z</v>
+        <v>2026-07-22T07:39:21.999Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>WO0000000303117</v>
+        <v>INC000000146339</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-21T10:43:30.000Z</v>
+        <v>2026-07-21T15:05:15.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-21T15:30:07.000Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>WO0000000303244</v>
+        <v>INC000000147926</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-21T15:29:08.000Z</v>
+        <v>2026-07-21T15:43:45.999Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>INC000000150141</v>
+        <v>WO0000000298353</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-21T17:04:17.000Z</v>
+        <v>2026-07-21T19:17:08.000Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-21T15:23:28.000Z</v>
+        <v>2026-07-21T15:22:31.000Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-21T12:33:01.000Z</v>
+        <v>2026-07-21T15:24:13.999Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-21T12:27:03.000Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WO0000000304990</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-22T08:16:13.000Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>INC000000150838</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-21T17:01:11.000Z</v>
+        <v>2026-07-22T08:57:51.999Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>WO0000000305131</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-22T08:56:56.000Z</v>
+        <v>2026-07-21T16:21:08.000Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>WO0000000305138</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-21T10:43:30.000Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>INC000000150748</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-21T16:48:15.999Z</v>
+        <v>2026-07-21T15:30:07.000Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>WO0000000305336</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-21T15:29:08.000Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000150141</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-21T18:19:52.000Z</v>
+        <v>2026-07-21T17:04:17.000Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>WO0000000305863</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-21T17:19:07.000Z</v>
+        <v>2026-07-21T15:23:28.000Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>WO0000000305877</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-22T08:01:39.999Z</v>
+        <v>2026-07-21T12:33:01.000Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>WO0000000305769</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-21T12:28:00.000Z</v>
+        <v>2026-07-21T12:27:03.000Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>WO0000000305770</v>
+        <v>WO0000000304990</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-21T12:28:53.999Z</v>
+        <v>2026-07-22T08:16:13.000Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>INC000000151203</v>
+        <v>INC000000150838</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-21T17:01:11.000Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>INC000000151143</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-21T15:24:31.000Z</v>
+        <v>2026-07-22T09:50:35.000Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>INC000000151157</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-21T10:59:03.000Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>INC000000151271</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-21T16:56:06.999Z</v>
+        <v>2026-07-21T16:48:15.999Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>WO0000000306256</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-21T17:15:05.000Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>INC000000151313</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-21T18:19:52.000Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>WO0000000306718</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-21T12:29:34.000Z</v>
+        <v>2026-07-21T17:19:07.000Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>WO0000000306721</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-21T23:51:23.000Z</v>
+        <v>2026-07-22T08:01:39.999Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>WO0000000306726</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-21T12:30:16.000Z</v>
+        <v>2026-07-21T12:28:00.000Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>WO0000000306862</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-21T16:32:53.999Z</v>
+        <v>2026-07-21T12:28:53.999Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>WO0000000306927</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>WO0000000306876</v>
+        <v>INC000000151143</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-21T15:41:43.000Z</v>
+        <v>2026-07-21T15:24:31.000Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>WO0000000306890</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-17T14:42:13.999Z</v>
+        <v>2026-07-21T10:59:03.000Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>WO0000000306899</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-21T16:45:23.000Z</v>
+        <v>2026-07-21T16:56:06.999Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>WO0000000306988</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-21T09:13:38.000Z</v>
+        <v>2026-07-21T17:15:05.000Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-21T16:17:14.000Z</v>
+        <v>2026-07-21T12:29:34.000Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-21T16:34:09.000Z</v>
+        <v>2026-07-21T23:51:23.000Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>INC000000151941</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-22T07:50:34.000Z</v>
+        <v>2026-07-21T12:30:16.000Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>WO0000000307437</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-21T23:52:20.999Z</v>
+        <v>2026-07-22T09:16:58.000Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000306862</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-21T16:32:53.999Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>WO0000000307483</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-21T13:01:38.000Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-21T15:41:43.000Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>WO0000000307671</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-21T19:54:45.000Z</v>
+        <v>2026-07-22T09:28:33.000Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>WO0000000307701</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-21T19:54:53.000Z</v>
+        <v>2026-07-21T16:45:23.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-21T16:24:16.999Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>WO0000000307725</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-21T15:39:21.000Z</v>
+        <v>2026-07-21T16:17:14.000Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>WO0000000307733</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-21T23:59:33.000Z</v>
+        <v>2026-07-21T16:34:09.000Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>INC000000152145</v>
+        <v>INC000000151941</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-22T08:19:43.999Z</v>
+        <v>2026-07-22T07:50:34.000Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>WO0000000307812</v>
+        <v>WO0000000307437</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-22T07:02:06.000Z</v>
+        <v>2026-07-21T23:52:20.999Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>WO0000000307820</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-21T09:49:48.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>WO0000000307940</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-21T13:01:38.000Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>INC000000152212</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000308040</v>
+        <v>WO0000000307671</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-21T19:54:45.000Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000308042</v>
+        <v>WO0000000307701</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-21T15:40:08.000Z</v>
+        <v>2026-07-21T19:54:53.000Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-21T16:24:16.999Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>WO0000000308052</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-21T16:25:50.000Z</v>
+        <v>2026-07-21T15:39:21.000Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307733</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-21T23:59:33.000Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>WO0000000308105</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-21T15:30:21.999Z</v>
+        <v>2026-07-22T08:19:43.999Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>WO0000000308075</v>
+        <v>WO0000000307812</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-21T12:31:18.000Z</v>
+        <v>2026-07-22T07:02:06.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>WO0000000308106</v>
+        <v>WO0000000307820</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-21T15:40:12.000Z</v>
+        <v>2026-07-21T09:49:48.000Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-21T15:43:15.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>WO0000000308086</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-21T09:28:00.000Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-21T14:50:24.000Z</v>
+        <v>2026-07-21T15:40:08.000Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>WO0000000308234</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-19T12:53:47.000Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>INC000000152251</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-21T16:16:11.000Z</v>
+        <v>2026-07-21T16:25:50.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>INC000000152361</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-21T18:11:35.999Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000308196</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-21T08:49:13.000Z</v>
+        <v>2026-07-21T15:30:21.999Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-17T12:34:20.000Z</v>
+        <v>2026-07-21T12:31:18.000Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>INC000000152369</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-17T10:42:03.000Z</v>
+        <v>2026-07-21T15:40:12.000Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>INC000000152378</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-17T09:05:30.000Z</v>
+        <v>2026-07-21T15:43:15.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-21T09:09:06.999Z</v>
+        <v>2026-07-21T09:28:00.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>WO0000000308432</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-21T13:10:12.999Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>INC000000152389</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-17T10:53:19.000Z</v>
+        <v>2026-07-21T14:50:24.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000308463</v>
+        <v>WO0000000308234</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-21T14:37:05.999Z</v>
+        <v>2026-07-19T12:53:47.000Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>WO0000000308475</v>
+        <v>INC000000152251</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-22T08:01:06.000Z</v>
+        <v>2026-07-21T16:16:11.000Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>WO0000000308478</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-22T08:01:07.000Z</v>
+        <v>2026-07-21T18:11:35.999Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>WO0000000308503</v>
+        <v>WO0000000308196</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-22T08:50:36.000Z</v>
+        <v>2026-07-21T08:49:13.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>INC000000152419</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-21T08:54:50.000Z</v>
+        <v>2026-07-17T12:34:20.000Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>INC000000152517</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-17T10:21:00.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-21T11:34:44.999Z</v>
+        <v>2026-07-21T09:09:06.999Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>INC000000152458</v>
+        <v>WO0000000308432</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-21T10:45:45.000Z</v>
+        <v>2026-07-21T13:10:12.999Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>INC000000152461</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-20T09:23:43.999Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308679</v>
+        <v>WO0000000308463</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-22T07:46:19.000Z</v>
+        <v>2026-07-21T14:37:05.999Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308475</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-22T09:37:35.999Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308478</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-21T16:40:02.000Z</v>
+        <v>2026-07-22T09:36:55.000Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>INC000000152565</v>
+        <v>WO0000000308503</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-21T07:47:38.999Z</v>
+        <v>2026-07-22T08:50:36.000Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>WO0000000308727</v>
+        <v>INC000000152517</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-21T15:25:15.999Z</v>
+        <v>2026-07-17T10:21:00.000Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-21T09:27:37.000Z</v>
+        <v>2026-07-21T11:34:44.999Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>INC000000152566</v>
+        <v>INC000000152458</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-21T17:16:36.999Z</v>
+        <v>2026-07-21T10:45:45.000Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>WO0000000308834</v>
+        <v>INC000000152461</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-21T14:03:00.000Z</v>
+        <v>2026-07-20T09:23:43.999Z</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>INC000000152486</v>
+        <v>WO0000000308679</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-07-21T07:42:45.999Z</v>
+        <v>2026-07-22T07:46:19.000Z</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-07-21T18:43:19.000Z</v>
+        <v>2026-07-21T16:40:02.000Z</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>INC000000152586</v>
+        <v>INC000000152565</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-07-17T10:46:28.000Z</v>
+        <v>2026-07-21T07:47:38.999Z</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>INC000000152591</v>
+        <v>WO0000000308727</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-07-17T11:00:29.999Z</v>
+        <v>2026-07-21T15:25:15.999Z</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>INC000000152594</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-07-20T13:46:11.000Z</v>
+        <v>2026-07-21T09:27:37.000Z</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>WO0000000308895</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-07-21T11:27:56.999Z</v>
+        <v>2026-07-21T17:16:36.999Z</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>WO0000000309009</v>
+        <v>WO0000000308755</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-07-22T08:19:25.000Z</v>
+        <v>2026-07-22T09:15:04.999Z</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>WO0000000309018</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-07-22T08:46:20.999Z</v>
+        <v>2026-07-21T14:03:00.000Z</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>WO0000000309021</v>
+        <v>INC000000152486</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-07-21T11:44:57.000Z</v>
+        <v>2026-07-21T07:42:45.999Z</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>WO0000000309028</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-07-22T08:50:35.000Z</v>
+        <v>2026-07-21T18:43:19.000Z</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>INC000000152628</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-07-17T10:44:38.000Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>WO0000000308967</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-07-21T10:04:47.000Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>INC000000152630</v>
+        <v>INC000000152594</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-07-21T07:35:42.000Z</v>
+        <v>2026-07-20T13:46:11.000Z</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>WO0000000308970</v>
+        <v>WO0000000308895</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-07-21T16:29:18.000Z</v>
+        <v>2026-07-21T11:27:56.999Z</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309018</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-07-21T14:13:19.000Z</v>
+        <v>2026-07-22T09:22:31.999Z</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>INC000000152643</v>
+        <v>WO0000000309021</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-07-22T08:14:00.000Z</v>
+        <v>2026-07-21T11:44:57.000Z</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>INC000000152737</v>
+        <v>WO0000000309028</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-21T14:29:46.000Z</v>
+        <v>2026-07-22T08:50:35.000Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>WO0000000309124</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-22T08:06:26.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>WO0000000309136</v>
+        <v>WO0000000308967</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-21T12:55:08.999Z</v>
+        <v>2026-07-21T10:04:47.000Z</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000152630</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-07-21T13:13:25.000Z</v>
+        <v>2026-07-21T07:35:42.000Z</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>INC000000152664</v>
+        <v>WO0000000308970</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-21T16:29:18.000Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>WO0000000309155</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-21T16:08:01.000Z</v>
+        <v>2026-07-21T14:13:19.000Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-22T08:31:28.000Z</v>
+        <v>2026-07-22T08:14:00.000Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>WO0000000309231</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-21T10:52:02.000Z</v>
+        <v>2026-07-21T14:29:46.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-07-17T09:57:18.999Z</v>
+        <v>2026-07-22T08:06:26.000Z</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>INC000000152673</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-21T08:52:59.000Z</v>
+        <v>2026-07-21T12:55:08.999Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-21T13:13:25.000Z</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309155</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-07-18T09:51:08.000Z</v>
+        <v>2026-07-22T09:03:05.999Z</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B592" s="1" t="d">
-        <v>2026-07-17T11:14:23.000Z</v>
+        <v>2026-07-22T08:31:28.000Z</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>WO0000000309164</v>
+        <v>WO0000000309231</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-07-21T13:50:33.000Z</v>
+        <v>2026-07-21T10:52:02.000Z</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-07-21T13:58:39.999Z</v>
+        <v>2026-07-18T09:51:08.000Z</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>INC000000152678</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B595" s="1" t="d">
-        <v>2026-07-21T15:37:16.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>WO0000000309168</v>
+        <v>INC000000152678</v>
       </c>
       <c r="B596" s="1" t="d">
-        <v>2026-07-21T16:31:56.000Z</v>
+        <v>2026-07-22T09:09:03.000Z</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309250</v>
       </c>
       <c r="B597" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-21T10:04:01.000Z</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>WO0000000309172</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B598" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-21T08:45:24.000Z</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>WO0000000309249</v>
+        <v>WO0000000309179</v>
       </c>
       <c r="B599" s="1" t="d">
-        <v>2026-07-17T09:38:10.000Z</v>
+        <v>2026-07-21T21:24:45.999Z</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>WO0000000309250</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-07-21T10:04:01.000Z</v>
+        <v>2026-07-21T14:29:44.000Z</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>INC000000152760</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-21T08:45:24.000Z</v>
+        <v>2026-07-21T11:59:19.000Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>WO0000000309179</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-21T21:24:45.999Z</v>
+        <v>2026-07-21T14:33:58.000Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-21T14:29:44.000Z</v>
+        <v>2026-07-21T11:58:05.000Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-21T11:59:19.000Z</v>
+        <v>2026-07-21T12:14:00.999Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-07-21T14:33:58.000Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>WO0000000309256</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-21T11:58:05.000Z</v>
+        <v>2026-07-21T12:14:33.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>WO0000000309189</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-21T12:14:00.999Z</v>
+        <v>2026-07-21T09:55:04.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>WO0000000309258</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-21T14:50:25.000Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>WO0000000309259</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-21T12:14:33.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>INC000000152768</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-07-21T09:55:04.000Z</v>
+        <v>2026-07-21T12:18:50.000Z</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>WO0000000309262</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-07-21T14:50:25.000Z</v>
+        <v>2026-07-21T14:27:36.000Z</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>INC000000152690</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-21T10:37:55.000Z</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>WO0000000309195</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-07-21T12:18:50.000Z</v>
+        <v>2026-07-21T15:17:00.999Z</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>INC000000152772</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-07-21T14:27:36.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>INC000000152774</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-07-21T10:37:55.000Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>WO0000000309199</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-07-21T15:17:00.999Z</v>
+        <v>2026-07-21T15:08:50.000Z</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>WO0000000309200</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-21T14:49:58.000Z</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-21T09:07:41.000Z</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>WO0000000309271</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-07-21T15:08:50.000Z</v>
+        <v>2026-07-21T15:19:01.999Z</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>WO0000000309407</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-07-17T10:43:38.999Z</v>
+        <v>2026-07-21T15:19:03.000Z</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>INC000000152777</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-07-21T14:49:58.000Z</v>
+        <v>2026-07-22T08:56:04.000Z</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-07-21T09:07:41.000Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-07-21T15:19:01.999Z</v>
+        <v>2026-07-21T15:27:18.999Z</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>WO0000000309411</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-07-21T15:19:03.000Z</v>
+        <v>2026-07-21T14:26:49.000Z</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-07-22T08:56:04.000Z</v>
+        <v>2026-07-21T15:44:00.000Z</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>WO0000000309282</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-22T09:27:31.000Z</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-07-21T15:27:18.999Z</v>
+        <v>2026-07-21T15:48:12.000Z</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>INC000000152802</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-07-21T14:26:49.000Z</v>
+        <v>2026-07-21T15:52:20.999Z</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-07-21T15:44:00.000Z</v>
+        <v>2026-07-21T15:52:20.000Z</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-07-21T15:46:02.000Z</v>
+        <v>2026-07-22T09:10:18.000Z</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-07-21T15:48:12.000Z</v>
+        <v>2026-07-21T15:56:24.000Z</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-07-21T15:52:20.999Z</v>
+        <v>2026-07-21T16:00:27.000Z</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-07-21T15:52:20.000Z</v>
+        <v>2026-07-21T16:02:36.000Z</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-07-21T15:54:21.999Z</v>
+        <v>2026-07-21T12:22:28.000Z</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>WO0000000309433</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-07-21T15:56:24.000Z</v>
+        <v>2026-07-22T08:52:02.000Z</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>WO0000000309299</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-07-22T08:35:51.999Z</v>
+        <v>2026-07-21T17:13:09.000Z</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>WO0000000309435</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-07-21T16:00:27.000Z</v>
+        <v>2026-07-21T17:18:56.000Z</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>WO0000000309438</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-07-21T16:02:36.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>WO0000000309503</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-07-21T12:22:28.000Z</v>
+        <v>2026-07-21T16:20:21.000Z</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>INC000000152789</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-07-22T08:52:02.000Z</v>
+        <v>2026-07-21T16:14:50.000Z</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-07-21T17:13:09.000Z</v>
+        <v>2026-07-21T16:24:57.999Z</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B642" s="1" t="d">
-        <v>2026-07-21T17:18:56.000Z</v>
+        <v>2026-07-21T16:24:57.000Z</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B643" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-22T08:58:10.000Z</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>WO0000000309441</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B644" s="1" t="d">
-        <v>2026-07-21T16:20:21.000Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>WO0000000309447</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B645" s="1" t="d">
-        <v>2026-07-21T16:14:50.000Z</v>
+        <v>2026-07-21T16:29:03.000Z</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B646" s="1" t="d">
-        <v>2026-07-21T16:24:57.999Z</v>
+        <v>2026-07-21T15:41:22.000Z</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B647" s="1" t="d">
-        <v>2026-07-21T16:24:57.000Z</v>
+        <v>2026-07-21T16:33:06.999Z</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B648" s="1" t="d">
-        <v>2026-07-22T08:58:10.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>WO0000000309513</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B649" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B650" s="1" t="d">
-        <v>2026-07-21T16:29:03.000Z</v>
+        <v>2026-07-21T16:55:28.999Z</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B651" s="1" t="d">
-        <v>2026-07-21T15:41:22.000Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>WO0000000309457</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B652" s="1" t="d">
-        <v>2026-07-21T16:33:06.999Z</v>
+        <v>2026-07-22T08:28:02.000Z</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>WO0000000309514</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B653" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-21T09:11:31.000Z</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>WO0000000309462</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B654" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-22T09:09:51.000Z</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>WO0000000309465</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B655" s="1" t="d">
-        <v>2026-07-21T16:55:28.999Z</v>
+        <v>2026-07-22T08:25:38.999Z</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>WO0000000309520</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B656" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-21T15:23:06.000Z</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>WO0000000309466</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B657" s="1" t="d">
-        <v>2026-07-22T09:00:03.000Z</v>
+        <v>2026-07-21T16:41:07.000Z</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>INC000000152903</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B658" s="1" t="d">
-        <v>2026-07-22T08:28:02.000Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>WO0000000309470</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B659" s="1" t="d">
-        <v>2026-07-21T09:11:31.000Z</v>
+        <v>2026-07-21T15:42:45.000Z</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B660" s="1" t="d">
-        <v>2026-07-21T10:47:55.000Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B661" s="1" t="d">
-        <v>2026-07-22T08:25:38.999Z</v>
+        <v>2026-07-22T09:42:27.000Z</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>WO0000000309534</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B662" s="1" t="d">
-        <v>2026-07-22T08:31:56.000Z</v>
+        <v>2026-07-22T08:30:58.000Z</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>WO0000000309489</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-21T15:23:06.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>INC000000152914</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-21T16:41:07.000Z</v>
+        <v>2026-07-21T12:29:32.000Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000309487</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-21T16:31:50.000Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>WO0000000309497</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-21T15:42:45.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>WO0000000309499</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-22T09:38:23.000Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>WO0000000309546</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-17T14:11:39.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>INC000000152824</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-22T08:30:58.000Z</v>
+        <v>2026-07-21T19:55:20.000Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>INC000000152921</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>WO0000000309603</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-21T12:29:32.000Z</v>
+        <v>2026-07-21T12:15:31.999Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000309549</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-21T16:31:50.000Z</v>
+        <v>2026-07-22T09:15:12.000Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>WO0000000309551</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-22T08:43:13.999Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000309609</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-21T10:51:05.000Z</v>
+        <v>2026-07-21T12:33:40.999Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000309553</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-22T09:22:01.000Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>WO0000000309555</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-21T19:55:20.000Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>WO0000000309616</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-21T12:15:31.999Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>INC000000152931</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-21T13:43:52.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-17T15:20:43.999Z</v>
+        <v>2026-07-21T10:39:19.000Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>WO0000000309563</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-17T15:24:26.000Z</v>
+        <v>2026-07-21T15:44:41.000Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>INC000000152933</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-22T08:43:13.999Z</v>
+        <v>2026-07-22T08:03:11.000Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-21T12:33:40.999Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-17T15:31:50.999Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-21T16:16:50.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>WO0000000309574</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>WO0000000309576</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-21T15:23:46.000Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-21T16:18:57.999Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>WO0000000309626</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-21T10:39:19.000Z</v>
+        <v>2026-07-21T15:25:40.000Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>WO0000000309627</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-21T15:44:41.000Z</v>
+        <v>2026-07-22T09:26:17.000Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>WO0000000309629</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-22T08:03:11.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000309632</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-21T16:49:09.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>WO0000000309636</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-21T16:16:50.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>INC000000152838</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-21T15:23:46.000Z</v>
+        <v>2026-07-21T10:23:48.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000309586</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-21T16:18:57.999Z</v>
+        <v>2026-07-21T11:20:55.000Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>WO0000000309589</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-21T15:25:40.000Z</v>
+        <v>2026-07-22T09:47:37.000Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>WO0000000309592</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-21T10:09:45.000Z</v>
+        <v>2026-07-21T17:15:25.999Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-21T11:21:15.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>WO0000000309647</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-21T09:05:18.000Z</v>
+        <v>2026-07-22T09:42:27.999Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-21T16:49:09.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>WO0000000309595</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>WO0000000309596</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-22T09:01:41.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>WO0000000309597</v>
+        <v>INC000000152953</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-21T10:23:48.000Z</v>
+        <v>2026-07-22T09:47:14.000Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>WO0000000309309</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-21T11:20:55.000Z</v>
+        <v>2026-07-22T09:19:20.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>INC000000152948</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-22T08:37:24.000Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>INC000000152845</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-21T17:15:25.999Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>WO0000000309310</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-21T11:21:15.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>INC000000152848</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-17T18:11:18.000Z</v>
+        <v>2026-07-22T08:01:09.000Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>WO0000000309657</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000309599</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-22T08:01:09.000Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>WO0000000309704</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-21T15:27:43.999Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>INC000000152953</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-21T12:58:47.000Z</v>
+        <v>2026-07-21T16:21:36.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>INC000000152955</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-21T12:44:12.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>WO0000000309664</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>WO0000000309666</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>WO0000000309714</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-21T13:07:15.000Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>WO0000000309669</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-22T08:01:09.000Z</v>
+        <v>2026-07-22T09:01:01.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>INC000000152856</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-21T10:10:23.000Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000309671</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B721" s="1" t="d">
         <v>2026-07-22T08:01:09.000Z</v>
@@ -6171,3780 +6171,3684 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>INC000000152873</v>
+        <v>INC000000152985</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-22T07:43:18.000Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>INC000000152971</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-21T16:21:36.000Z</v>
+        <v>2026-07-21T13:14:23.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>WO0000000309682</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000309686</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-21T11:12:41.000Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>INC000000152879</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-18T08:11:58.000Z</v>
+        <v>2026-07-21T11:11:58.999Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>WO0000000309689</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-22T08:34:20.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>INC000000152883</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-21T13:07:15.000Z</v>
+        <v>2026-07-21T10:52:04.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>WO0000000309692</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-22T09:01:01.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>INC000000152981</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-21T10:10:23.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>WO0000000309697</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-22T08:01:09.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>INC000000152985</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-22T07:43:18.000Z</v>
+        <v>2026-07-21T14:33:57.000Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>INC000000152989</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-21T13:14:23.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>WO0000000309803</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-21T17:15:57.000Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>WO0000000309804</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-21T11:12:41.000Z</v>
+        <v>2026-07-22T08:58:13.000Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>WO0000000309807</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-21T11:11:58.999Z</v>
+        <v>2026-07-21T20:35:02.000Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>INC000000152896</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-22T08:34:20.000Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>INC000000152898</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-21T10:52:04.000Z</v>
+        <v>2026-07-21T09:58:01.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>WO0000000309810</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>WO0000000309752</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-21T13:04:28.000Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>WO0000000309816</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-21T15:24:57.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-21T14:33:57.000Z</v>
+        <v>2026-07-22T08:54:15.000Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>WO0000000309759</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>INC000000153013</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-22T08:56:14.000Z</v>
+        <v>2026-07-21T17:09:00.000Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>WO0000000309825</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-21T17:15:57.000Z</v>
+        <v>2026-07-21T15:26:52.999Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>INC000000153105</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-22T08:58:13.000Z</v>
+        <v>2026-07-21T15:06:50.999Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>WO0000000309826</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-21T20:35:02.000Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>WO0000000309768</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>INC000000153107</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-21T09:58:01.000Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>WO0000000309829</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>WO0000000309830</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-21T11:24:34.000Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>INC000000153019</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-21T13:04:28.000Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-21T15:24:57.000Z</v>
+        <v>2026-07-22T07:46:52.000Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>INC000000153022</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-22T08:54:15.000Z</v>
+        <v>2026-07-22T07:53:16.999Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>INC000000153111</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-22T07:47:57.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-21T17:09:00.000Z</v>
+        <v>2026-07-22T07:49:20.000Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>WO0000000309834</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-21T15:26:52.999Z</v>
+        <v>2026-07-21T13:30:52.000Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-21T15:06:50.999Z</v>
+        <v>2026-07-21T09:45:18.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>INC000000153121</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-21T09:36:30.999Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>INC000000153031</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-22T08:59:20.999Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>WO0000000309780</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-22T09:01:02.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>WO0000000309837</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309781</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-21T08:57:28.999Z</v>
+        <v>2026-07-21T10:57:08.000Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>WO0000000309783</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>WO0000000309838</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>INC000000153034</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-22T07:46:52.000Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>INC000000153035</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-22T07:53:16.999Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>INC000000153036</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-22T07:47:57.000Z</v>
+        <v>2026-07-21T15:13:04.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>INC000000153037</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-22T07:49:20.000Z</v>
+        <v>2026-07-21T10:38:36.000Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-21T13:30:52.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-21T09:45:18.000Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>WO0000000309841</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-21T09:36:30.999Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309842</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>WO0000000309793</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-22T09:01:02.000Z</v>
+        <v>2026-07-22T09:44:39.000Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>WO0000000309848</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T15:22:52.000Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>WO0000000309851</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-21T10:57:08.000Z</v>
+        <v>2026-07-21T09:47:21.999Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>WO0000000309902</v>
+        <v>WO0000000309953</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T15:33:38.000Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>INC000000153048</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T12:13:26.000Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>INC000000153138</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-22T07:50:38.000Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>INC000000153052</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000309862</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T15:25:48.000Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309861</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-21T15:13:04.000Z</v>
+        <v>2026-07-21T15:56:24.000Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>INC000000153053</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-21T20:38:14.000Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>INC000000153062</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-21T10:38:36.000Z</v>
+        <v>2026-07-21T15:28:12.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>INC000000153143</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T11:27:26.000Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000309878</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-21T08:35:47.000Z</v>
+        <v>2026-07-21T15:29:06.999Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>WO0000000309880</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T09:28:19.000Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>WO0000000309945</v>
+        <v>WO0000000310015</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T09:27:41.000Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>WO0000000309946</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T11:44:25.999Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>INC000000153065</v>
+        <v>WO0000000310016</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-21T11:32:54.000Z</v>
+        <v>2026-07-21T11:47:23.999Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>INC000000153153</v>
+        <v>WO0000000310019</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-21T15:22:52.000Z</v>
+        <v>2026-07-21T10:19:05.000Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>WO0000000309949</v>
+        <v>WO0000000309981</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-21T09:47:21.999Z</v>
+        <v>2026-07-21T11:22:20.000Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>WO0000000309950</v>
+        <v>WO0000000310021</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-21T15:33:38.000Z</v>
+        <v>2026-07-21T09:24:02.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>WO0000000309952</v>
+        <v>INC000000153174</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-21T08:33:13.000Z</v>
+        <v>2026-07-21T14:40:04.000Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>WO0000000309953</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-21T15:33:38.000Z</v>
+        <v>2026-07-21T15:06:30.000Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>INC000000153069</v>
+        <v>WO0000000309975</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-21T12:13:26.000Z</v>
+        <v>2026-07-22T09:30:14.000Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>WO0000000309892</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-21T09:04:46.000Z</v>
+        <v>2026-07-21T09:37:20.999Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>WO0000000309954</v>
+        <v>WO0000000310025</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:36:55.000Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000310002</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-21T15:25:48.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>WO0000000309957</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-21T15:56:24.000Z</v>
+        <v>2026-07-21T09:40:19.000Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>WO0000000309958</v>
+        <v>INC000000153181</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-21T08:54:45.000Z</v>
+        <v>2026-07-21T09:48:10.999Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000310004</v>
+        <v>WO0000000309993</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-21T15:28:12.000Z</v>
+        <v>2026-07-22T09:42:27.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000309959</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-21T11:27:26.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>WO0000000310006</v>
+        <v>INC000000153082</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-21T15:29:06.999Z</v>
+        <v>2026-07-21T10:22:17.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>WO0000000310008</v>
+        <v>INC000000153179</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-21T11:05:13.999Z</v>
+        <v>2026-07-22T08:51:46.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309961</v>
+        <v>WO0000000309997</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-21T09:28:19.000Z</v>
+        <v>2026-07-21T11:45:35.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>WO0000000310015</v>
+        <v>WO0000000309998</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-21T09:27:41.000Z</v>
+        <v>2026-07-21T09:47:07.999Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153182</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-21T11:44:25.999Z</v>
+        <v>2026-07-21T10:35:39.000Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>WO0000000310016</v>
+        <v>WO0000000310000</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-21T11:47:23.999Z</v>
+        <v>2026-07-22T09:55:11.999Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>INC000000153168</v>
+        <v>WO0000000309999</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-21T09:54:40.000Z</v>
+        <v>2026-07-21T09:50:29.000Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>WO0000000310019</v>
+        <v>WO0000000310102</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-21T10:19:05.000Z</v>
+        <v>2026-07-21T09:50:55.000Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000309981</v>
+        <v>WO0000000310033</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-21T11:22:20.000Z</v>
+        <v>2026-07-21T09:51:00.000Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>WO0000000310021</v>
+        <v>WO0000000305268</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-21T09:24:02.000Z</v>
+        <v>2026-07-21T09:55:25.000Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>INC000000153172</v>
+        <v>WO0000000305269</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-21T09:52:46.999Z</v>
+        <v>2026-07-21T16:30:36.000Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>INC000000153174</v>
+        <v>WO0000000310106</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-21T14:40:04.000Z</v>
+        <v>2026-07-21T10:02:21.999Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>WO0000000309986</v>
+        <v>WO0000000310036</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-21T09:28:28.999Z</v>
+        <v>2026-07-21T09:59:20.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>WO0000000309985</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-21T15:06:30.000Z</v>
+        <v>2026-07-21T10:31:45.000Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>WO0000000309975</v>
+        <v>WO0000000310045</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-21T09:49:40.999Z</v>
+        <v>2026-07-22T08:58:36.000Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>INC000000153171</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-21T10:25:59.000Z</v>
+        <v>2026-07-21T11:44:30.999Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000310114</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-21T09:37:20.999Z</v>
+        <v>2026-07-21T10:12:20.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>WO0000000310025</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-21T09:36:55.000Z</v>
+        <v>2026-07-21T15:54:47.999Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310046</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T10:13:36.000Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310047</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-21T09:40:19.000Z</v>
+        <v>2026-07-21T10:14:06.000Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>INC000000153181</v>
+        <v>WO0000000310118</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-21T09:48:10.999Z</v>
+        <v>2026-07-21T10:29:50.999Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>WO0000000309993</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-21T16:18:38.000Z</v>
+        <v>2026-07-21T16:09:03.000Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310049</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-21T10:20:08.000Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>INC000000153082</v>
+        <v>WO0000000310051</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-21T10:22:17.000Z</v>
+        <v>2026-07-21T10:23:58.000Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>INC000000153179</v>
+        <v>WO0000000310120</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-22T08:51:46.000Z</v>
+        <v>2026-07-21T10:35:25.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000309997</v>
+        <v>WO0000000310053</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-21T11:45:35.000Z</v>
+        <v>2026-07-21T10:27:39.999Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>WO0000000309998</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-21T09:47:07.999Z</v>
+        <v>2026-07-21T13:42:39.999Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>INC000000153182</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-21T10:35:39.000Z</v>
+        <v>2026-07-21T20:55:08.999Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>WO0000000310000</v>
+        <v>INC000000153201</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-21T16:36:31.000Z</v>
+        <v>2026-07-22T09:50:24.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000309999</v>
+        <v>WO0000000310123</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-21T09:50:29.000Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000310102</v>
+        <v>WO0000000310055</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-21T09:50:55.000Z</v>
+        <v>2026-07-21T11:51:43.999Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>WO0000000310033</v>
+        <v>WO0000000310127</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-21T09:51:00.000Z</v>
+        <v>2026-07-22T08:42:13.999Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>WO0000000305268</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-21T09:55:25.000Z</v>
+        <v>2026-07-21T10:46:52.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>INC000000153083</v>
+        <v>WO0000000310061</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-22T08:59:27.000Z</v>
+        <v>2026-07-21T23:22:22.000Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>WO0000000305269</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-21T16:30:36.000Z</v>
+        <v>2026-07-21T18:21:06.000Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000310106</v>
+        <v>WO0000000310135</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-21T10:02:21.999Z</v>
+        <v>2026-07-21T10:51:40.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000310036</v>
+        <v>WO0000000310136</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-21T09:59:20.000Z</v>
+        <v>2026-07-21T15:04:13.000Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310065</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-21T10:31:45.000Z</v>
+        <v>2026-07-21T16:12:37.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>INC000000153089</v>
+        <v>WO0000000310066</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-21T10:28:35.000Z</v>
+        <v>2026-07-21T15:16:35.000Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>WO0000000310045</v>
+        <v>WO0000000310069</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-22T08:58:36.000Z</v>
+        <v>2026-07-21T11:40:34.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310144</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-21T11:44:30.999Z</v>
+        <v>2026-07-21T11:06:24.000Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000310114</v>
+        <v>WO0000000310145</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-21T10:12:20.000Z</v>
+        <v>2026-07-21T11:44:29.999Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153306</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-21T15:54:47.999Z</v>
+        <v>2026-07-21T12:03:12.000Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000310046</v>
+        <v>WO0000000310143</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-21T10:13:36.000Z</v>
+        <v>2026-07-21T11:08:15.000Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>WO0000000310047</v>
+        <v>WO0000000310147</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-21T10:14:06.000Z</v>
+        <v>2026-07-21T11:11:37.999Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000310118</v>
+        <v>WO0000000310070</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-21T10:29:50.999Z</v>
+        <v>2026-07-21T14:40:42.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>INC000000153092</v>
+        <v>WO0000000310078</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-21T16:09:03.000Z</v>
+        <v>2026-07-21T17:48:37.000Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000310049</v>
+        <v>WO0000000310079</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-21T10:20:08.000Z</v>
+        <v>2026-07-22T09:11:31.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>WO0000000310051</v>
+        <v>WO0000000310082</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-21T10:23:58.000Z</v>
+        <v>2026-07-21T11:21:29.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000310120</v>
+        <v>WO0000000310157</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-21T10:35:25.000Z</v>
+        <v>2026-07-21T11:45:08.999Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>WO0000000310053</v>
+        <v>WO0000000310160</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-21T10:27:39.999Z</v>
+        <v>2026-07-21T11:27:58.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>INC000000153195</v>
+        <v>WO0000000310161</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-21T13:42:39.999Z</v>
+        <v>2026-07-21T11:25:35.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>INC000000153100</v>
+        <v>WO0000000310076</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-21T16:44:45.000Z</v>
+        <v>2026-07-21T12:27:55.000Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>INC000000153099</v>
+        <v>WO0000000310087</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-22T08:04:56.000Z</v>
+        <v>2026-07-21T12:41:20.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>INC000000153196</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-21T20:55:08.999Z</v>
+        <v>2026-07-21T16:18:46.999Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>INC000000153201</v>
+        <v>INC000000153224</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-21T10:39:28.000Z</v>
+        <v>2026-07-21T13:20:41.000Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>WO0000000310123</v>
+        <v>WO0000000310092</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-21T10:36:47.999Z</v>
+        <v>2026-07-21T11:41:17.000Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>WO0000000310055</v>
+        <v>WO0000000310173</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-21T11:51:43.999Z</v>
+        <v>2026-07-21T12:23:28.000Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>WO0000000310127</v>
+        <v>WO0000000310146</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-22T08:42:13.999Z</v>
+        <v>2026-07-21T11:50:49.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>WO0000000310060</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-21T10:46:52.000Z</v>
+        <v>2026-07-21T12:56:25.000Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000310061</v>
+        <v>WO0000000310095</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-21T23:22:22.000Z</v>
+        <v>2026-07-22T09:50:34.000Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>INC000000153206</v>
+        <v>WO0000000310171</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-21T18:21:06.000Z</v>
+        <v>2026-07-21T15:53:05.000Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>WO0000000310135</v>
+        <v>WO0000000310178</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-21T10:51:40.000Z</v>
+        <v>2026-07-21T15:20:09.000Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>INC000000153200</v>
+        <v>WO0000000310098</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-21T11:03:32.000Z</v>
+        <v>2026-07-21T14:10:01.000Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>WO0000000310136</v>
+        <v>INC000000153322</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-21T15:04:13.000Z</v>
+        <v>2026-07-21T15:32:25.000Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>WO0000000310065</v>
+        <v>INC000000153232</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-21T16:12:37.000Z</v>
+        <v>2026-07-21T12:02:12.999Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>WO0000000310066</v>
+        <v>INC000000153323</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-21T15:16:35.000Z</v>
+        <v>2026-07-21T12:13:51.000Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>WO0000000310069</v>
+        <v>WO0000000310179</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-21T11:40:34.000Z</v>
+        <v>2026-07-21T17:16:41.999Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000310144</v>
+        <v>WO0000000310202</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-21T11:06:24.000Z</v>
+        <v>2026-07-21T12:04:50.000Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000310145</v>
+        <v>WO0000000310180</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-21T11:44:29.999Z</v>
+        <v>2026-07-21T12:00:37.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>INC000000153306</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-21T12:03:12.000Z</v>
+        <v>2026-07-22T08:20:31.999Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000310143</v>
+        <v>WO0000000310181</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-21T11:08:15.000Z</v>
+        <v>2026-07-21T12:18:59.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>WO0000000310147</v>
+        <v>INC000000153319</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-21T11:11:37.999Z</v>
+        <v>2026-07-21T12:06:50.999Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>WO0000000310070</v>
+        <v>WO0000000310204</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-21T14:40:42.000Z</v>
+        <v>2026-07-21T12:52:00.999Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>INC000000153218</v>
+        <v>WO0000000310182</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-21T16:46:25.000Z</v>
+        <v>2026-07-21T14:10:32.000Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>WO0000000310078</v>
+        <v>WO0000000310208</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-21T17:48:37.000Z</v>
+        <v>2026-07-21T16:00:45.000Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>WO0000000310079</v>
+        <v>INC000000153332</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-21T11:48:08.999Z</v>
+        <v>2026-07-21T13:57:51.999Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>WO0000000310082</v>
+        <v>INC000000153235</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-21T11:21:29.000Z</v>
+        <v>2026-07-22T09:43:50.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>WO0000000310157</v>
+        <v>WO0000000310207</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-21T11:45:08.999Z</v>
+        <v>2026-07-21T12:19:01.999Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>WO0000000310160</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-21T11:27:58.000Z</v>
+        <v>2026-07-21T16:27:35.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>WO0000000310161</v>
+        <v>WO0000000310192</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-21T11:25:35.000Z</v>
+        <v>2026-07-21T13:13:38.999Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>WO0000000310076</v>
+        <v>INC000000153237</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-21T12:27:55.000Z</v>
+        <v>2026-07-22T09:03:20.999Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000310087</v>
+        <v>WO0000000310193</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-21T12:41:20.000Z</v>
+        <v>2026-07-21T12:33:26.000Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>INC000000153222</v>
+        <v>INC000000153340</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-21T21:20:08.000Z</v>
+        <v>2026-07-21T14:30:28.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000310164</v>
+        <v>WO0000000310213</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-21T16:18:46.999Z</v>
+        <v>2026-07-21T14:03:25.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>INC000000153224</v>
+        <v>WO0000000310214</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-21T13:20:41.000Z</v>
+        <v>2026-07-21T13:12:50.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>WO0000000310092</v>
+        <v>INC000000153342</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-21T11:41:17.000Z</v>
+        <v>2026-07-21T13:57:08.000Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>INC000000153223</v>
+        <v>WO0000000310195</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-21T12:24:34.000Z</v>
+        <v>2026-07-21T13:11:13.000Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>WO0000000310173</v>
+        <v>WO0000000310217</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-21T12:23:28.000Z</v>
+        <v>2026-07-22T08:11:20.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>WO0000000310146</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-21T11:50:49.000Z</v>
+        <v>2026-07-21T13:39:49.000Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>INC000000153226</v>
+        <v>WO0000000310215</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-21T12:56:25.000Z</v>
+        <v>2026-07-21T12:51:50.999Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>WO0000000310095</v>
+        <v>WO0000000310218</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-22T08:11:30.000Z</v>
+        <v>2026-07-21T12:42:44.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>WO0000000310171</v>
+        <v>WO0000000310198</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-21T15:53:05.000Z</v>
+        <v>2026-07-21T12:43:18.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>WO0000000310096</v>
+        <v>WO0000000310199</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-21T12:05:21.000Z</v>
+        <v>2026-07-21T12:44:20.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>WO0000000310178</v>
+        <v>WO0000000310200</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-21T15:20:09.000Z</v>
+        <v>2026-07-21T12:53:42.000Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>WO0000000310098</v>
+        <v>INC000000153343</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-21T14:10:01.000Z</v>
+        <v>2026-07-21T17:09:54.999Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>INC000000153322</v>
+        <v>INC000000153241</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-21T15:32:25.000Z</v>
+        <v>2026-07-21T15:30:45.000Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>INC000000153232</v>
+        <v>WO0000000310303</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-21T12:02:12.999Z</v>
+        <v>2026-07-22T08:29:29.999Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>INC000000153323</v>
+        <v>WO0000000310224</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-21T12:13:51.000Z</v>
+        <v>2026-07-21T13:06:20.000Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>WO0000000310179</v>
+        <v>WO0000000310305</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-21T17:16:41.999Z</v>
+        <v>2026-07-21T13:01:00.000Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>WO0000000310202</v>
+        <v>INC000000153346</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-21T12:04:50.000Z</v>
+        <v>2026-07-21T17:02:06.000Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>WO0000000310180</v>
+        <v>INC000000153347</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-21T12:00:37.000Z</v>
+        <v>2026-07-21T15:22:02.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310314</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-22T08:20:31.999Z</v>
+        <v>2026-07-21T13:20:57.999Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>WO0000000310181</v>
+        <v>INC000000153248</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-21T12:18:59.000Z</v>
+        <v>2026-07-21T15:43:27.000Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>INC000000153319</v>
+        <v>WO0000000305270</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-21T12:06:50.999Z</v>
+        <v>2026-07-21T13:24:28.999Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>WO0000000310204</v>
+        <v>WO0000000310316</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-21T12:52:00.999Z</v>
+        <v>2026-07-21T16:40:32.000Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>WO0000000310182</v>
+        <v>WO0000000310317</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-21T14:10:32.000Z</v>
+        <v>2026-07-21T13:34:35.999Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>WO0000000310208</v>
+        <v>WO0000000310320</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-21T16:00:45.000Z</v>
+        <v>2026-07-21T13:43:30.000Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>INC000000153332</v>
+        <v>WO0000000310231</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-21T13:57:51.999Z</v>
+        <v>2026-07-21T13:45:42.999Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>INC000000153235</v>
+        <v>INC000000153352</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-21T15:15:50.000Z</v>
+        <v>2026-07-21T14:29:53.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000310207</v>
+        <v>WO0000000305271</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-21T12:19:01.999Z</v>
+        <v>2026-07-22T08:56:41.000Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>INC000000153335</v>
+        <v>WO0000000305272</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-21T16:27:35.000Z</v>
+        <v>2026-07-21T14:30:16.999Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>WO0000000310187</v>
+        <v>INC000000153353</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-21T12:25:12.999Z</v>
+        <v>2026-07-22T07:45:45.000Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>WO0000000310190</v>
+        <v>WO0000000310325</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-21T12:26:49.000Z</v>
+        <v>2026-07-22T08:34:20.999Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>WO0000000310192</v>
+        <v>WO0000000310236</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-21T13:13:38.999Z</v>
+        <v>2026-07-21T14:04:48.999Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>INC000000153237</v>
+        <v>WO0000000310327</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-22T08:19:54.000Z</v>
+        <v>2026-07-21T14:08:12.999Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>WO0000000310193</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-21T12:33:26.000Z</v>
+        <v>2026-07-21T15:07:23.000Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>INC000000153340</v>
+        <v>WO0000000309312</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-21T14:30:28.000Z</v>
+        <v>2026-07-21T14:09:08.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>WO0000000310213</v>
+        <v>WO0000000309313</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-21T14:03:25.000Z</v>
+        <v>2026-07-21T14:09:18.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>WO0000000310214</v>
+        <v>WO0000000305274</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-21T13:12:50.000Z</v>
+        <v>2026-07-21T14:09:28.999Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>INC000000153342</v>
+        <v>INC000000153354</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-21T13:57:08.000Z</v>
+        <v>2026-07-21T14:48:30.000Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>WO0000000310195</v>
+        <v>WO0000000305276</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-21T13:11:13.000Z</v>
+        <v>2026-07-21T15:52:57.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>WO0000000310217</v>
+        <v>WO0000000310237</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-22T08:11:20.000Z</v>
+        <v>2026-07-21T14:11:40.000Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>INC000000153344</v>
+        <v>WO0000000310238</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-21T13:39:49.000Z</v>
+        <v>2026-07-21T14:13:45.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>WO0000000310215</v>
+        <v>WO0000000310326</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-21T12:51:50.999Z</v>
+        <v>2026-07-21T14:17:53.999Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>WO0000000310218</v>
+        <v>WO0000000310239</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-21T12:42:44.000Z</v>
+        <v>2026-07-22T09:50:34.000Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>WO0000000310198</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-21T12:43:18.000Z</v>
+        <v>2026-07-21T17:01:11.000Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>WO0000000310199</v>
+        <v>WO0000000310242</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-21T12:44:20.000Z</v>
+        <v>2026-07-22T06:16:26.000Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>WO0000000310200</v>
+        <v>WO0000000310244</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-21T12:53:42.000Z</v>
+        <v>2026-07-22T09:50:04.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>INC000000153343</v>
+        <v>WO0000000310247</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-21T17:09:54.999Z</v>
+        <v>2026-07-21T16:18:26.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>INC000000153241</v>
+        <v>INC000000153256</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-21T15:30:45.000Z</v>
+        <v>2026-07-21T15:08:16.999Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>WO0000000310303</v>
+        <v>WO0000000310250</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-22T08:29:29.999Z</v>
+        <v>2026-07-21T14:39:36.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>WO0000000310224</v>
+        <v>WO0000000310342</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-21T13:06:20.000Z</v>
+        <v>2026-07-21T14:43:32.000Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>WO0000000310305</v>
+        <v>WO0000000310345</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-21T13:01:00.000Z</v>
+        <v>2026-07-21T16:14:23.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>INC000000153346</v>
+        <v>INC000000153363</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-21T17:02:06.000Z</v>
+        <v>2026-07-21T15:14:31.000Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>INC000000153347</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-21T15:22:02.000Z</v>
+        <v>2026-07-21T14:56:31.999Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>WO0000000310314</v>
+        <v>INC000000153367</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-21T13:20:57.999Z</v>
+        <v>2026-07-21T18:10:11.999Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>INC000000153248</v>
+        <v>WO0000000310348</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-21T15:43:27.000Z</v>
+        <v>2026-07-21T14:55:19.000Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>WO0000000305270</v>
+        <v>INC000000153368</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-21T13:24:28.999Z</v>
+        <v>2026-07-21T15:22:41.000Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>WO0000000310316</v>
+        <v>WO0000000305277</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-21T16:40:32.000Z</v>
+        <v>2026-07-21T14:59:08.000Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>WO0000000310317</v>
+        <v>WO0000000310246</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-21T13:34:35.999Z</v>
+        <v>2026-07-21T16:06:31.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>WO0000000310320</v>
+        <v>WO0000000310350</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-21T13:43:30.000Z</v>
+        <v>2026-07-21T15:00:50.000Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>WO0000000310231</v>
+        <v>INC000000153365</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-21T13:45:42.999Z</v>
+        <v>2026-07-21T15:21:23.999Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>INC000000153352</v>
+        <v>INC000000153369</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-21T14:29:53.000Z</v>
+        <v>2026-07-21T16:08:53.000Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>WO0000000305271</v>
+        <v>INC000000153370</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-22T08:56:41.000Z</v>
+        <v>2026-07-21T15:53:24.000Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>WO0000000305272</v>
+        <v>WO0000000310357</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-21T14:30:16.999Z</v>
+        <v>2026-07-21T15:05:01.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>INC000000153353</v>
+        <v>WO0000000310356</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-22T07:45:45.000Z</v>
+        <v>2026-07-21T16:13:26.999Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>WO0000000310325</v>
+        <v>INC000000153372</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-22T08:34:20.999Z</v>
+        <v>2026-07-21T17:10:32.999Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>WO0000000310236</v>
+        <v>WO0000000310363</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-21T14:04:48.999Z</v>
+        <v>2026-07-21T15:15:23.000Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>WO0000000310327</v>
+        <v>WO0000000310258</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-21T14:08:12.999Z</v>
+        <v>2026-07-21T15:15:49.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310260</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-21T15:07:23.000Z</v>
+        <v>2026-07-21T15:16:15.000Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>WO0000000309312</v>
+        <v>WO0000000310366</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-22T09:52:40.000Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>WO0000000309313</v>
+        <v>WO0000000310365</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-21T14:09:18.000Z</v>
+        <v>2026-07-21T15:23:38.000Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>WO0000000305274</v>
+        <v>WO0000000310367</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-21T14:09:28.999Z</v>
+        <v>2026-07-22T08:54:30.999Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>INC000000153354</v>
+        <v>WO0000000310265</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-21T14:48:30.000Z</v>
+        <v>2026-07-21T15:45:54.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>WO0000000305276</v>
+        <v>WO0000000310266</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-21T15:52:57.000Z</v>
+        <v>2026-07-21T16:25:17.000Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>WO0000000310237</v>
+        <v>WO0000000310368</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-21T14:11:40.000Z</v>
+        <v>2026-07-22T08:53:03.000Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000310238</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-21T14:13:45.000Z</v>
+        <v>2026-07-22T09:08:56.000Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>WO0000000310326</v>
+        <v>WO0000000310267</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-21T14:17:53.999Z</v>
+        <v>2026-07-21T15:44:10.000Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>WO0000000310239</v>
+        <v>WO0000000310374</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-21T14:18:52.999Z</v>
+        <v>2026-07-22T06:31:19.000Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310268</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-21T17:01:11.000Z</v>
+        <v>2026-07-21T18:53:18.000Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>WO0000000310242</v>
+        <v>INC000000153375</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-22T06:16:26.000Z</v>
+        <v>2026-07-21T16:40:23.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>WO0000000310244</v>
+        <v>WO0000000310271</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-21T14:31:11.000Z</v>
+        <v>2026-07-21T16:17:27.999Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>WO0000000310247</v>
+        <v>WO0000000310272</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-21T16:18:26.000Z</v>
+        <v>2026-07-21T15:41:09.000Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>INC000000153256</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-21T15:08:16.999Z</v>
+        <v>2026-07-21T19:03:59.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>WO0000000310249</v>
+        <v>INC000000153377</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-21T14:38:22.000Z</v>
+        <v>2026-07-22T09:36:10.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>WO0000000310250</v>
+        <v>WO0000000310276</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-21T14:39:36.000Z</v>
+        <v>2026-07-21T16:27:22.999Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>WO0000000310342</v>
+        <v>INC000000153376</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-21T14:43:32.000Z</v>
+        <v>2026-07-22T08:11:07.000Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>WO0000000310345</v>
+        <v>WO0000000310279</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-21T16:14:23.000Z</v>
+        <v>2026-07-21T15:44:54.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>INC000000153363</v>
+        <v>WO0000000310280</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-21T15:14:31.000Z</v>
+        <v>2026-07-21T15:49:22.999Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>INC000000153364</v>
+        <v>WO0000000310282</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-21T16:00:12.999Z</v>
+        <v>2026-07-21T15:51:25.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310283</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-21T14:56:31.999Z</v>
+        <v>2026-07-22T08:27:07.999Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>INC000000153367</v>
+        <v>INC000000153259</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-21T18:10:11.999Z</v>
+        <v>2026-07-21T15:55:21.000Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>WO0000000310348</v>
+        <v>WO0000000305278</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-21T14:55:19.000Z</v>
+        <v>2026-07-21T15:56:10.999Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>INC000000153368</v>
+        <v>WO0000000310384</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-21T15:22:41.000Z</v>
+        <v>2026-07-21T15:56:37.999Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>WO0000000305277</v>
+        <v>INC000000153261</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-21T14:59:08.000Z</v>
+        <v>2026-07-21T15:57:54.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>WO0000000310246</v>
+        <v>WO0000000310386</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-21T16:06:31.000Z</v>
+        <v>2026-07-21T16:53:00.000Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>WO0000000310350</v>
+        <v>WO0000000310387</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-21T15:00:50.000Z</v>
+        <v>2026-07-21T16:05:38.000Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>INC000000153365</v>
+        <v>WO0000000310289</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-21T15:21:23.999Z</v>
+        <v>2026-07-21T16:03:05.999Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>INC000000153369</v>
+        <v>WO0000000310390</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-21T16:08:53.000Z</v>
+        <v>2026-07-21T16:04:24.000Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>INC000000153370</v>
+        <v>INC000000153262</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-21T15:53:24.000Z</v>
+        <v>2026-07-22T08:19:51.000Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>WO0000000310357</v>
+        <v>WO0000000310392</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-21T15:05:01.000Z</v>
+        <v>2026-07-21T16:09:09.000Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>WO0000000310356</v>
+        <v>WO0000000310293</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-21T16:13:26.999Z</v>
+        <v>2026-07-21T16:21:50.000Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>WO0000000310359</v>
+        <v>WO0000000310292</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-21T15:10:08.000Z</v>
+        <v>2026-07-21T16:24:33.000Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>INC000000153372</v>
+        <v>INC000000153380</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-21T17:10:32.999Z</v>
+        <v>2026-07-22T09:32:42.999Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>WO0000000310363</v>
+        <v>WO0000000310396</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-21T15:15:23.000Z</v>
+        <v>2026-07-21T16:25:21.000Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>WO0000000310258</v>
+        <v>INC000000153381</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-21T15:15:49.000Z</v>
+        <v>2026-07-21T16:28:35.000Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>WO0000000310260</v>
+        <v>WO0000000310297</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-21T15:16:15.000Z</v>
+        <v>2026-07-21T16:43:51.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>WO0000000310366</v>
+        <v>WO0000000305279</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-22T08:56:18.000Z</v>
+        <v>2026-07-21T16:35:21.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>WO0000000310365</v>
+        <v>INC000000153382</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-21T15:23:38.000Z</v>
+        <v>2026-07-22T07:45:47.000Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>WO0000000310367</v>
+        <v>INC000000153383</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-22T08:54:30.999Z</v>
+        <v>2026-07-21T18:07:46.999Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000310265</v>
+        <v>WO0000000310403</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-21T15:45:54.000Z</v>
+        <v>2026-07-21T16:51:45.000Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>WO0000000310266</v>
+        <v>WO0000000310404</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-21T16:25:17.000Z</v>
+        <v>2026-07-22T08:36:02.999Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>WO0000000310368</v>
+        <v>WO0000000310408</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-22T08:53:03.000Z</v>
+        <v>2026-07-21T17:58:11.000Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>WO0000000309315</v>
+        <v>INC000000153384</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-21T15:48:12.999Z</v>
+        <v>2026-07-21T21:45:20.000Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>WO0000000310267</v>
+        <v>WO0000000310501</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-21T15:44:10.000Z</v>
+        <v>2026-07-21T16:48:31.000Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>WO0000000310374</v>
+        <v>WO0000000310411</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-22T06:31:19.000Z</v>
+        <v>2026-07-21T17:01:37.999Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>WO0000000310268</v>
+        <v>WO0000000310502</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-21T18:53:18.000Z</v>
+        <v>2026-07-21T16:58:28.999Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>INC000000153375</v>
+        <v>WO0000000310417</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-21T16:40:23.000Z</v>
+        <v>2026-07-22T08:40:57.000Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>WO0000000310271</v>
+        <v>WO0000000310418</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-21T16:17:27.999Z</v>
+        <v>2026-07-22T08:42:18.000Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>WO0000000310272</v>
+        <v>WO0000000310420</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-21T15:41:09.000Z</v>
+        <v>2026-07-21T16:57:24.999Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310419</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-21T19:03:59.000Z</v>
+        <v>2026-07-21T17:15:29.000Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>INC000000153377</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-21T20:57:26.000Z</v>
+        <v>2026-07-22T07:31:05.999Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>WO0000000310276</v>
+        <v>WO0000000310422</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-21T16:27:22.999Z</v>
+        <v>2026-07-22T08:43:44.000Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>INC000000153376</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-22T08:11:07.000Z</v>
+        <v>2026-07-21T17:58:51.999Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>WO0000000310279</v>
+        <v>INC000000153266</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-21T15:44:54.000Z</v>
+        <v>2026-07-22T09:42:57.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>WO0000000310280</v>
+        <v>WO0000000310423</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-21T15:49:22.999Z</v>
+        <v>2026-07-22T08:40:44.999Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>WO0000000310382</v>
+        <v>WO0000000310424</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-21T19:58:30.000Z</v>
+        <v>2026-07-21T17:11:58.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000310282</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-21T15:51:25.000Z</v>
+        <v>2026-07-21T18:17:03.000Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>WO0000000310283</v>
+        <v>WO0000000310426</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-22T08:27:07.999Z</v>
+        <v>2026-07-21T17:14:16.000Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>INC000000153259</v>
+        <v>WO0000000310427</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-21T15:55:21.000Z</v>
+        <v>2026-07-21T17:15:07.000Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>WO0000000305278</v>
+        <v>INC000000153390</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-21T15:56:10.999Z</v>
+        <v>2026-07-22T08:03:11.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>WO0000000310384</v>
+        <v>WO0000000310430</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-21T15:56:37.999Z</v>
+        <v>2026-07-21T17:28:57.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>INC000000153261</v>
+        <v>WO0000000310509</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-21T15:57:54.000Z</v>
+        <v>2026-07-21T18:19:46.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>WO0000000310386</v>
+        <v>INC000000153391</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-21T16:53:00.000Z</v>
+        <v>2026-07-21T18:01:02.000Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>WO0000000310387</v>
+        <v>INC000000153393</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-21T16:05:38.000Z</v>
+        <v>2026-07-22T09:40:21.999Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000310289</v>
+        <v>WO0000000310512</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-21T16:03:05.999Z</v>
+        <v>2026-07-22T08:38:38.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>WO0000000310390</v>
+        <v>WO0000000310438</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-21T16:04:24.000Z</v>
+        <v>2026-07-21T17:56:18.000Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>INC000000153262</v>
+        <v>WO0000000310439</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-22T08:19:51.000Z</v>
+        <v>2026-07-21T18:12:13.000Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>WO0000000310392</v>
+        <v>INC000000153394</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-21T16:09:09.000Z</v>
+        <v>2026-07-21T18:47:18.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>WO0000000310293</v>
+        <v>WO0000000310440</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T16:21:50.000Z</v>
+        <v>2026-07-21T18:11:24.000Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>WO0000000310395</v>
+        <v>WO0000000310441</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-21T18:52:37.000Z</v>
+        <v>2026-07-22T09:29:47.000Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>WO0000000310292</v>
+        <v>WO0000000310513</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-21T16:24:33.000Z</v>
+        <v>2026-07-21T18:07:29.000Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000153380</v>
+        <v>INC000000153270</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T21:01:00.000Z</v>
+        <v>2026-07-21T18:48:09.000Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>WO0000000310396</v>
+        <v>INC000000153396</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-21T16:25:21.000Z</v>
+        <v>2026-07-22T07:47:35.000Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>INC000000153381</v>
+        <v>INC000000153397</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-21T16:28:35.000Z</v>
+        <v>2026-07-22T08:01:43.000Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000310297</v>
+        <v>WO0000000310515</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-21T16:43:51.000Z</v>
+        <v>2026-07-21T18:25:31.000Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>WO0000000305279</v>
+        <v>WO0000000310516</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-21T16:35:21.000Z</v>
+        <v>2026-07-21T18:28:36.000Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>INC000000153382</v>
+        <v>WO0000000310445</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-22T07:45:47.000Z</v>
+        <v>2026-07-22T07:51:48.000Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>INC000000153383</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-21T18:07:46.999Z</v>
+        <v>2026-07-21T19:01:53.000Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>WO0000000310403</v>
+        <v>INC000000153272</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-21T16:51:45.000Z</v>
+        <v>2026-07-22T08:25:27.999Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>WO0000000310404</v>
+        <v>WO0000000310519</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-22T08:36:02.999Z</v>
+        <v>2026-07-21T19:23:16.000Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>WO0000000310408</v>
+        <v>WO0000000310447</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-21T17:58:11.000Z</v>
+        <v>2026-07-22T09:28:13.000Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>WO0000000310409</v>
+        <v>INC000000153401</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-21T18:52:08.999Z</v>
+        <v>2026-07-21T21:50:55.000Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>INC000000153384</v>
+        <v>WO0000000310520</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-21T21:45:20.000Z</v>
+        <v>2026-07-21T22:18:08.999Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>WO0000000310501</v>
+        <v>WO0000000310521</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-21T16:48:31.000Z</v>
+        <v>2026-07-22T07:48:20.000Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>WO0000000310411</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-21T17:01:37.999Z</v>
+        <v>2026-07-21T22:46:20.000Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>WO0000000310502</v>
+        <v>WO0000000310522</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-21T16:58:28.999Z</v>
+        <v>2026-07-22T08:07:44.000Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>WO0000000310417</v>
+        <v>WO0000000310453</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-22T08:40:57.000Z</v>
+        <v>2026-07-22T01:46:45.000Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>WO0000000310418</v>
+        <v>WO0000000310524</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-22T08:42:18.000Z</v>
+        <v>2026-07-22T07:56:01.000Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>WO0000000310420</v>
+        <v>INC000000153276</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-21T16:57:24.999Z</v>
+        <v>2026-07-22T05:50:36.999Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>WO0000000310419</v>
+        <v>INC000000153405</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-21T17:15:29.000Z</v>
+        <v>2026-07-22T05:48:35.999Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>INC000000153385</v>
+        <v>INC000000153404</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-22T07:31:05.999Z</v>
+        <v>2026-07-22T05:26:24.000Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>WO0000000310503</v>
+        <v>WO0000000310530</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-21T18:51:41.000Z</v>
+        <v>2026-07-22T06:43:06.999Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>WO0000000310422</v>
+        <v>INC000000153277</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-22T08:43:44.000Z</v>
+        <v>2026-07-22T08:42:13.000Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>INC000000153267</v>
+        <v>WO0000000310533</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-21T17:58:51.999Z</v>
+        <v>2026-07-22T09:06:28.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>INC000000153266</v>
+        <v>INC000000153278</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-21T17:11:42.000Z</v>
+        <v>2026-07-22T06:16:38.000Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>WO0000000310423</v>
+        <v>INC000000153279</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-22T08:40:44.999Z</v>
+        <v>2026-07-22T06:43:11.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>WO0000000310424</v>
+        <v>WO0000000310535</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-21T17:11:58.000Z</v>
+        <v>2026-07-22T07:47:51.999Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>WO0000000310425</v>
+        <v>INC000000153406</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-21T18:17:03.000Z</v>
+        <v>2026-07-22T07:10:48.000Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>WO0000000310426</v>
+        <v>INC000000153280</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-21T17:14:16.000Z</v>
+        <v>2026-07-22T06:52:56.000Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>WO0000000310427</v>
+        <v>WO0000000310459</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-21T17:15:07.000Z</v>
+        <v>2026-07-22T08:10:31.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>INC000000153390</v>
+        <v>INC000000153281</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-22T08:03:11.000Z</v>
+        <v>2026-07-22T06:54:42.999Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>WO0000000310430</v>
+        <v>INC000000153407</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-21T17:28:57.000Z</v>
+        <v>2026-07-22T07:11:31.000Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>WO0000000310509</v>
+        <v>WO0000000310539</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-21T18:19:46.000Z</v>
+        <v>2026-07-22T07:01:57.000Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>INC000000153391</v>
+        <v>INC000000153410</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-21T18:01:02.000Z</v>
+        <v>2026-07-22T07:03:37.000Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>INC000000153393</v>
+        <v>WO0000000310541</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-22T08:39:50.000Z</v>
+        <v>2026-07-22T07:05:16.000Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>WO0000000310512</v>
+        <v>WO0000000310540</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-22T08:38:38.000Z</v>
+        <v>2026-07-22T08:01:51.999Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>WO0000000310438</v>
+        <v>INC000000153414</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-21T17:56:18.000Z</v>
+        <v>2026-07-22T08:32:43.000Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>WO0000000310439</v>
+        <v>WO0000000310461</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-21T18:12:13.000Z</v>
+        <v>2026-07-22T07:11:04.000Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>INC000000153394</v>
+        <v>INC000000153283</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-21T18:47:18.000Z</v>
+        <v>2026-07-22T07:29:20.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>WO0000000310440</v>
+        <v>WO0000000310464</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-21T18:11:24.000Z</v>
+        <v>2026-07-22T07:17:47.000Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>WO0000000310441</v>
+        <v>INC000000153284</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-21T18:30:29.999Z</v>
+        <v>2026-07-22T07:34:14.000Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>WO0000000310513</v>
+        <v>WO0000000310543</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-21T18:07:29.000Z</v>
+        <v>2026-07-22T08:13:50.000Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>INC000000153270</v>
+        <v>WO0000000310466</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-21T18:48:09.000Z</v>
+        <v>2026-07-22T07:41:27.000Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>INC000000153396</v>
+        <v>INC000000153285</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-22T07:47:35.000Z</v>
+        <v>2026-07-22T07:46:35.000Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>INC000000153397</v>
+        <v>INC000000153286</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-22T08:01:43.000Z</v>
+        <v>2026-07-22T07:46:51.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>WO0000000310515</v>
+        <v>INC000000153287</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-21T18:25:31.000Z</v>
+        <v>2026-07-22T07:47:06.999Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>WO0000000310516</v>
+        <v>INC000000153288</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-21T18:28:36.000Z</v>
+        <v>2026-07-22T07:47:27.999Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>WO0000000310445</v>
+        <v>INC000000153415</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-22T07:51:48.000Z</v>
+        <v>2026-07-22T07:34:59.000Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153289</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-21T19:01:53.000Z</v>
+        <v>2026-07-22T09:37:02.000Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>INC000000153272</v>
+        <v>INC000000153290</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-22T08:25:27.999Z</v>
+        <v>2026-07-22T09:01:27.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>WO0000000310519</v>
+        <v>INC000000153291</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-21T19:23:16.000Z</v>
+        <v>2026-07-22T09:00:48.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>WO0000000310447</v>
+        <v>INC000000153292</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-22T08:44:57.000Z</v>
+        <v>2026-07-22T08:59:53.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>INC000000153400</v>
+        <v>WO0000000310549</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-21T20:24:00.000Z</v>
+        <v>2026-07-22T08:57:31.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>INC000000153401</v>
+        <v>INC000000153416</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-21T21:50:55.000Z</v>
+        <v>2026-07-22T08:33:02.999Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>WO0000000310520</v>
+        <v>WO0000000310551</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-21T22:18:08.999Z</v>
+        <v>2026-07-22T07:42:09.999Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>WO0000000310521</v>
+        <v>WO0000000310552</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-22T07:48:20.000Z</v>
+        <v>2026-07-22T07:47:12.999Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>WO0000000310452</v>
+        <v>INC000000153293</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-21T22:46:20.000Z</v>
+        <v>2026-07-22T07:50:49.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>WO0000000310522</v>
+        <v>WO0000000305280</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-22T08:07:44.000Z</v>
+        <v>2026-07-22T09:23:02.000Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>WO0000000310453</v>
+        <v>INC000000153295</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-22T01:46:45.000Z</v>
+        <v>2026-07-22T08:53:05.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>WO0000000310524</v>
+        <v>WO0000000310553</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-22T07:56:01.000Z</v>
+        <v>2026-07-22T09:50:10.000Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>INC000000153276</v>
+        <v>WO0000000310556</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-22T05:50:36.999Z</v>
+        <v>2026-07-22T08:01:05.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>INC000000153405</v>
+        <v>INC000000153421</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-22T05:48:35.999Z</v>
+        <v>2026-07-22T08:49:13.000Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>INC000000153404</v>
+        <v>WO0000000310557</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-22T05:26:24.000Z</v>
+        <v>2026-07-22T08:01:09.000Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>WO0000000310530</v>
+        <v>INC000000153296</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-22T06:43:06.999Z</v>
+        <v>2026-07-22T08:55:37.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>INC000000153277</v>
+        <v>WO0000000310560</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-22T08:42:13.000Z</v>
+        <v>2026-07-22T09:50:38.000Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>WO0000000310533</v>
+        <v>WO0000000310474</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-22T08:24:44.000Z</v>
+        <v>2026-07-22T08:05:13.000Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>INC000000153278</v>
+        <v>WO0000000310476</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-22T06:16:38.000Z</v>
+        <v>2026-07-22T08:14:42.999Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>INC000000153279</v>
+        <v>WO0000000310562</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-22T06:43:11.000Z</v>
+        <v>2026-07-22T08:29:34.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>WO0000000310535</v>
+        <v>WO0000000310478</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-22T07:47:51.999Z</v>
+        <v>2026-07-22T08:14:23.000Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>INC000000153406</v>
+        <v>WO0000000310563</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-22T07:10:48.000Z</v>
+        <v>2026-07-22T08:31:57.000Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>INC000000153280</v>
+        <v>WO0000000310480</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-22T06:52:56.000Z</v>
+        <v>2026-07-22T08:30:01.000Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>WO0000000310459</v>
+        <v>INC000000153422</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-22T08:10:31.000Z</v>
+        <v>2026-07-22T08:19:43.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>INC000000153281</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-22T06:54:42.999Z</v>
+        <v>2026-07-22T08:55:35.999Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>INC000000153407</v>
+        <v>WO0000000310482</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-22T07:11:31.000Z</v>
+        <v>2026-07-22T08:16:50.000Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>WO0000000310539</v>
+        <v>WO0000000310564</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-22T07:01:57.000Z</v>
+        <v>2026-07-22T08:20:03.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>INC000000153410</v>
+        <v>WO0000000310570</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-22T07:03:37.000Z</v>
+        <v>2026-07-22T08:22:25.000Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>WO0000000310541</v>
+        <v>INC000000153425</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-22T07:05:16.000Z</v>
+        <v>2026-07-22T08:54:19.000Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>WO0000000310540</v>
+        <v>WO0000000310483</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-22T08:01:51.999Z</v>
+        <v>2026-07-22T09:27:48.000Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>INC000000153414</v>
+        <v>WO0000000310569</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-22T08:32:43.000Z</v>
+        <v>2026-07-22T09:51:30.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>WO0000000310461</v>
+        <v>WO0000000310485</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-22T07:11:04.000Z</v>
+        <v>2026-07-22T09:41:20.999Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>INC000000153283</v>
+        <v>WO0000000310573</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-22T07:29:20.000Z</v>
+        <v>2026-07-22T08:31:26.000Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>WO0000000310464</v>
+        <v>INC000000153300</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-22T07:17:47.000Z</v>
+        <v>2026-07-22T08:48:44.000Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>INC000000153284</v>
+        <v>WO0000000310489</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-22T07:34:14.000Z</v>
+        <v>2026-07-22T08:32:18.000Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>WO0000000310543</v>
+        <v>INC000000153429</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-22T08:13:50.000Z</v>
+        <v>2026-07-22T08:50:04.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>WO0000000310466</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-22T07:41:27.000Z</v>
+        <v>2026-07-22T08:40:26.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>INC000000153285</v>
+        <v>INC000000153428</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-22T07:46:35.000Z</v>
+        <v>2026-07-22T08:56:43.000Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>INC000000153286</v>
+        <v>WO0000000310491</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-22T07:46:51.000Z</v>
+        <v>2026-07-22T09:12:34.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>INC000000153287</v>
+        <v>WO0000000310492</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-22T07:47:06.999Z</v>
+        <v>2026-07-22T09:45:54.999Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>INC000000153288</v>
+        <v>WO0000000310493</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-22T07:47:27.999Z</v>
+        <v>2026-07-22T08:40:50.000Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>INC000000153415</v>
+        <v>WO0000000310579</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-22T07:34:59.000Z</v>
+        <v>2026-07-22T08:41:33.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>INC000000153289</v>
+        <v>INC000000153427</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-22T07:48:56.000Z</v>
+        <v>2026-07-22T08:45:20.000Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>INC000000153290</v>
+        <v>WO0000000310581</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-22T07:48:56.000Z</v>
+        <v>2026-07-22T09:34:31.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>INC000000153291</v>
+        <v>WO0000000310494</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-22T09:00:48.000Z</v>
+        <v>2026-07-22T09:28:19.000Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>INC000000153292</v>
+        <v>INC000000153501</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-22T08:59:53.000Z</v>
+        <v>2026-07-22T09:37:10.999Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>INC000000153417</v>
+        <v>INC000000153502</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-22T07:36:23.999Z</v>
+        <v>2026-07-22T09:49:39.000Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>WO0000000310549</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-22T08:57:31.000Z</v>
+        <v>2026-07-22T09:20:21.999Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>WO0000000310550</v>
+        <v>WO0000000310575</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-22T07:56:30.000Z</v>
+        <v>2026-07-22T09:38:20.999Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>INC000000153416</v>
+        <v>WO0000000310498</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-22T08:33:02.999Z</v>
+        <v>2026-07-22T08:49:48.000Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>INC000000153294</v>
+        <v>INC000000153503</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-22T07:55:02.000Z</v>
+        <v>2026-07-22T08:53:18.000Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>WO0000000310551</v>
+        <v>WO0000000310500</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-22T07:42:09.999Z</v>
+        <v>2026-07-22T08:50:36.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>WO0000000310552</v>
+        <v>WO0000000310604</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-22T07:47:12.999Z</v>
+        <v>2026-07-22T09:48:30.000Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>INC000000153293</v>
+        <v>WO0000000310495</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-22T07:50:49.000Z</v>
+        <v>2026-07-22T09:37:27.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>WO0000000305280</v>
+        <v>INC000000153504</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-22T07:49:28.999Z</v>
+        <v>2026-07-22T09:04:34.000Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>INC000000153295</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-22T08:53:05.000Z</v>
+        <v>2026-07-22T08:58:13.000Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>WO0000000310553</v>
+        <v>WO0000000310605</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-22T07:52:58.000Z</v>
+        <v>2026-07-22T08:54:06.999Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>WO0000000310556</v>
+        <v>WO0000000310499</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-22T08:01:05.000Z</v>
+        <v>2026-07-22T08:55:32.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>INC000000153421</v>
+        <v>INC000000153507</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-22T08:49:13.000Z</v>
+        <v>2026-07-22T09:11:18.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>WO0000000310557</v>
+        <v>INC000000153508</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-22T08:01:09.000Z</v>
+        <v>2026-07-22T09:17:19.000Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>INC000000153296</v>
+        <v>WO0000000310607</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-22T08:55:37.000Z</v>
+        <v>2026-07-22T09:48:52.000Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>WO0000000310560</v>
+        <v>WO0000000310586</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-22T08:04:18.000Z</v>
+        <v>2026-07-22T09:46:58.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>WO0000000310474</v>
+        <v>INC000000153509</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-22T08:05:13.000Z</v>
+        <v>2026-07-22T09:15:53.000Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>WO0000000310476</v>
+        <v>WO0000000310588</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-22T08:14:42.999Z</v>
+        <v>2026-07-22T09:00:54.000Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>WO0000000310562</v>
+        <v>INC000000153506</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-22T08:29:34.000Z</v>
+        <v>2026-07-22T09:13:44.000Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>WO0000000310478</v>
+        <v>WO0000000305281</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-22T08:14:23.000Z</v>
+        <v>2026-07-22T09:49:18.000Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>WO0000000310563</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-22T08:31:57.000Z</v>
+        <v>2026-07-22T09:20:50.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>WO0000000310480</v>
+        <v>WO0000000310594</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-22T08:30:01.000Z</v>
+        <v>2026-07-22T09:06:53.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>INC000000153422</v>
+        <v>WO0000000310609</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-22T08:19:43.000Z</v>
+        <v>2026-07-22T09:07:17.000Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>INC000000153299</v>
+        <v>WO0000000310611</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-22T08:55:35.999Z</v>
+        <v>2026-07-22T09:09:14.000Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>WO0000000310482</v>
+        <v>INC000000153511</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-22T08:16:50.000Z</v>
+        <v>2026-07-22T09:21:37.000Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>WO0000000310564</v>
+        <v>WO0000000310701</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-22T08:20:03.000Z</v>
+        <v>2026-07-22T09:51:55.000Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>WO0000000310570</v>
+        <v>WO0000000310613</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-22T08:22:25.000Z</v>
+        <v>2026-07-22T09:17:27.000Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>INC000000153425</v>
+        <v>WO0000000310592</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-22T08:54:19.000Z</v>
+        <v>2026-07-22T09:18:25.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>WO0000000310483</v>
+        <v>WO0000000310615</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-22T08:46:36.999Z</v>
+        <v>2026-07-22T09:40:11.000Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>WO0000000310484</v>
+        <v>WO0000000310616</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-22T08:42:18.999Z</v>
+        <v>2026-07-22T09:47:20.000Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>WO0000000310569</v>
+        <v>WO0000000310617</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-22T08:30:11.000Z</v>
+        <v>2026-07-22T09:18:02.999Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>INC000000153426</v>
+        <v>WO0000000310703</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-22T08:39:32.000Z</v>
+        <v>2026-07-22T09:36:22.000Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>WO0000000310485</v>
+        <v>WO0000000310705</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-22T08:29:00.000Z</v>
+        <v>2026-07-22T09:24:59.000Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>WO0000000310486</v>
+        <v>WO0000000310706</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-22T08:29:12.999Z</v>
+        <v>2026-07-22T09:21:12.999Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>WO0000000310573</v>
+        <v>WO0000000310618</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-22T08:31:26.000Z</v>
+        <v>2026-07-22T09:49:34.000Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>INC000000153300</v>
+        <v>INC000000153512</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-22T08:48:44.000Z</v>
+        <v>2026-07-22T09:22:37.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>WO0000000310489</v>
+        <v>WO0000000310585</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-22T08:32:18.000Z</v>
+        <v>2026-07-22T09:23:52.000Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>WO0000000310572</v>
+        <v>WO0000000310600</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-22T08:52:37.999Z</v>
+        <v>2026-07-22T09:23:46.999Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>INC000000153429</v>
+        <v>WO0000000310709</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-22T08:50:04.000Z</v>
+        <v>2026-07-22T09:26:30.000Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000310710</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-22T08:40:26.000Z</v>
+        <v>2026-07-22T09:27:16.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>WO0000000310576</v>
+        <v>WO0000000310621</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-22T08:56:44.999Z</v>
+        <v>2026-07-22T09:27:43.000Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>INC000000153428</v>
+        <v>INC000000153513</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-22T08:56:43.000Z</v>
+        <v>2026-07-22T09:51:49.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>WO0000000310491</v>
+        <v>WO0000000310708</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-22T08:40:42.999Z</v>
+        <v>2026-07-22T09:46:30.999Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>WO0000000310492</v>
+        <v>WO0000000310714</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-22T08:40:48.000Z</v>
+        <v>2026-07-22T09:32:57.999Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>WO0000000310493</v>
+        <v>WO0000000310712</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-22T08:40:50.000Z</v>
+        <v>2026-07-22T09:53:42.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>WO0000000310579</v>
+        <v>WO0000000310704</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-22T08:41:33.000Z</v>
+        <v>2026-07-22T09:34:48.000Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>INC000000153427</v>
+        <v>WO0000000310715</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-22T08:45:20.000Z</v>
+        <v>2026-07-22T09:35:21.999Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>WO0000000310581</v>
+        <v>INC000000153516</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-22T08:43:33.000Z</v>
+        <v>2026-07-22T09:44:04.000Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>WO0000000310494</v>
+        <v>INC000000153514</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-22T08:44:29.999Z</v>
+        <v>2026-07-22T09:48:36.999Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>INC000000153501</v>
+        <v>WO0000000310717</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-22T08:44:06.000Z</v>
+        <v>2026-07-22T09:39:33.000Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>INC000000153502</v>
+        <v>WO0000000310626</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-22T09:00:58.000Z</v>
+        <v>2026-07-22T09:39:42.999Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>INC000000153431</v>
+        <v>WO0000000310627</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-22T08:57:41.000Z</v>
+        <v>2026-07-22T09:51:09.999Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>WO0000000310582</v>
+        <v>WO0000000310624</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-22T08:46:50.000Z</v>
+        <v>2026-07-22T09:40:45.999Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>WO0000000310575</v>
+        <v>INC000000153517</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-22T08:48:43.000Z</v>
+        <v>2026-07-22T09:50:56.000Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>WO0000000310498</v>
+        <v>WO0000000310721</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-22T08:49:48.000Z</v>
+        <v>2026-07-22T09:44:55.999Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>WO0000000310583</v>
+        <v>WO0000000310722</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-22T08:49:58.000Z</v>
+        <v>2026-07-22T09:50:45.000Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>INC000000153503</v>
+        <v>WO0000000310723</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-22T08:53:18.000Z</v>
+        <v>2026-07-22T09:47:36.000Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>WO0000000310500</v>
+        <v>INC000000153435</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-22T08:50:36.000Z</v>
+        <v>2026-07-22T09:50:03.000Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>WO0000000310604</v>
+        <v>INC000000153518</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-22T08:52:59.000Z</v>
+        <v>2026-07-22T09:51:41.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>WO0000000310495</v>
+        <v>INC000000153520</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-22T08:54:30.999Z</v>
+        <v>2026-07-22T09:54:05.000Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>INC000000153504</v>
+        <v>WO0000000310631</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-22T08:54:00.000Z</v>
+        <v>2026-07-22T09:55:42.000Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
-        <v>INC000000153505</v>
-      </c>
-      <c r="B1181" s="1" t="d">
-        <v>2026-07-22T08:58:13.000Z</v>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" t="str">
-        <v>WO0000000310605</v>
-      </c>
-      <c r="B1182" s="1" t="d">
-        <v>2026-07-22T08:54:06.999Z</v>
-      </c>
-    </row>
-    <row r="1183">
-      <c r="A1183" t="str">
-        <v>WO0000000310499</v>
-      </c>
-      <c r="B1183" s="1" t="d">
-        <v>2026-07-22T08:55:32.000Z</v>
-      </c>
-    </row>
-    <row r="1184">
-      <c r="A1184" t="str">
-        <v>WO0000000310606</v>
-      </c>
-      <c r="B1184" s="1" t="d">
-        <v>2026-07-22T08:56:10.000Z</v>
-      </c>
-    </row>
-    <row r="1185">
-      <c r="A1185" t="str">
-        <v>WO0000000310601</v>
-      </c>
-      <c r="B1185" s="1" t="d">
-        <v>2026-07-22T08:56:42.000Z</v>
-      </c>
-    </row>
-    <row r="1186">
-      <c r="A1186" t="str">
-        <v>INC000000153507</v>
-      </c>
-      <c r="B1186" s="1" t="d">
-        <v>2026-07-22T08:58:56.999Z</v>
-      </c>
-    </row>
-    <row r="1187">
-      <c r="A1187" t="str">
-        <v>INC000000153508</v>
-      </c>
-      <c r="B1187" s="1" t="d">
-        <v>2026-07-22T08:59:05.000Z</v>
-      </c>
-    </row>
-    <row r="1188">
-      <c r="A1188" t="str">
-        <v>WO0000000310602</v>
-      </c>
-      <c r="B1188" s="1" t="d">
-        <v>2026-07-22T09:00:03.000Z</v>
-      </c>
-    </row>
-    <row r="1189">
-      <c r="A1189" t="str">
-        <v>WO0000000310607</v>
-      </c>
-      <c r="B1189" s="1" t="d">
-        <v>2026-07-22T09:00:22.000Z</v>
-      </c>
-    </row>
-    <row r="1190">
-      <c r="A1190" t="str">
-        <v>WO0000000310586</v>
-      </c>
-      <c r="B1190" s="1" t="d">
-        <v>2026-07-22T09:00:41.000Z</v>
-      </c>
-    </row>
-    <row r="1191">
-      <c r="A1191" t="str">
-        <v>INC000000153509</v>
-      </c>
-      <c r="B1191" s="1" t="d">
-        <v>2026-07-22T09:00:48.000Z</v>
-      </c>
-    </row>
-    <row r="1192">
-      <c r="A1192" t="str">
-        <v>WO0000000310588</v>
-      </c>
-      <c r="B1192" s="1" t="d">
-        <v>2026-07-22T09:00:54.000Z</v>
-      </c>
-    </row>
-    <row r="1193">
-      <c r="A1193" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1184"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3635,1490 +3635,1490 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>WO0000000308493</v>
+        <v>INC000000152513</v>
       </c>
       <c r="B405" s="1" t="d">
-        <v>2026-07-22T08:01:07.000Z</v>
+        <v>2026-07-16T09:23:02.000Z</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>INC000000152513</v>
+        <v>WO0000000308552</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2026-07-16T09:23:02.000Z</v>
+        <v>2026-07-16T09:20:55.000Z</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>WO0000000308552</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2026-07-16T09:20:55.000Z</v>
+        <v>2026-07-21T11:10:08.000Z</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>WO0000000308648</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2026-07-21T11:10:08.000Z</v>
+        <v>2026-07-21T11:24:28.999Z</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2026-07-21T11:24:28.999Z</v>
+        <v>2026-07-22T09:40:25.000Z</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000308662</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2026-07-22T09:40:25.000Z</v>
+        <v>2026-07-21T16:24:57.000Z</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>WO0000000308662</v>
+        <v>WO0000000308673</v>
       </c>
       <c r="B411" s="1" t="d">
-        <v>2026-07-21T16:24:57.000Z</v>
+        <v>2026-07-16T10:02:00.999Z</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>WO0000000308673</v>
+        <v>WO0000000308675</v>
       </c>
       <c r="B412" s="1" t="d">
-        <v>2026-07-16T10:02:00.999Z</v>
+        <v>2026-07-17T07:31:47.000Z</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>WO0000000308675</v>
+        <v>WO0000000308685</v>
       </c>
       <c r="B413" s="1" t="d">
-        <v>2026-07-17T07:31:47.000Z</v>
+        <v>2026-07-16T10:12:45.000Z</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>WO0000000308685</v>
+        <v>WO0000000308596</v>
       </c>
       <c r="B414" s="1" t="d">
-        <v>2026-07-16T10:12:45.000Z</v>
+        <v>2026-07-16T10:19:52.000Z</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>WO0000000308596</v>
+        <v>WO0000000308701</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2026-07-16T10:19:52.000Z</v>
+        <v>2026-07-16T10:22:52.000Z</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308701</v>
+        <v>WO0000000308696</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-16T10:22:52.000Z</v>
+        <v>2026-07-21T12:28:21.000Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-21T12:28:21.000Z</v>
+        <v>2026-07-21T15:02:42.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>WO0000000308695</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-21T15:02:42.000Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-21T15:10:53.000Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-21T15:10:53.000Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308715</v>
+        <v>WO0000000308717</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-21T10:45:16.999Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-21T10:45:16.999Z</v>
+        <v>2026-07-21T15:17:00.999Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308809</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-21T15:17:00.999Z</v>
+        <v>2026-07-16T11:14:01.000Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308809</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-16T11:14:01.000Z</v>
+        <v>2026-07-21T16:02:36.000Z</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2026-07-21T16:02:36.000Z</v>
+        <v>2026-07-21T16:27:01.999Z</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>WO0000000308754</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2026-07-21T16:27:01.999Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-22T08:44:17.000Z</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>WO0000000308873</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2026-07-22T08:44:17.000Z</v>
+        <v>2026-07-22T09:05:30.000Z</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>WO0000000308794</v>
+        <v>WO0000000308917</v>
       </c>
       <c r="B429" s="1" t="d">
-        <v>2026-07-22T09:05:30.000Z</v>
+        <v>2026-07-22T09:58:41.000Z</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>WO0000000308917</v>
+        <v>WO0000000308899</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2026-07-17T07:59:19.999Z</v>
+        <v>2026-07-22T08:34:00.000Z</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>WO0000000308899</v>
+        <v>WO0000000308926</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-22T08:34:00.000Z</v>
+        <v>2026-07-21T11:31:06.000Z</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>WO0000000308926</v>
+        <v>WO0000000309002</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-21T11:31:06.000Z</v>
+        <v>2026-07-16T15:07:58.000Z</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>WO0000000309002</v>
+        <v>WO0000000309011</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-21T11:40:57.000Z</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>WO0000000309011</v>
+        <v>WO0000000308938</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-21T11:40:57.000Z</v>
+        <v>2026-07-16T15:31:18.000Z</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>WO0000000308938</v>
+        <v>WO0000000308947</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-22T08:44:17.000Z</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>WO0000000308947</v>
+        <v>WO0000000309025</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-22T08:44:17.000Z</v>
+        <v>2026-07-16T15:47:35.000Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>WO0000000309025</v>
+        <v>WO0000000309031</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-22T09:07:32.000Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-22T09:07:32.000Z</v>
+        <v>2026-07-16T16:05:14.000Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>WO0000000309036</v>
+        <v>WO0000000309039</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-22T09:20:00.000Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-22T09:20:00.000Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000309041</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>WO0000000308966</v>
+        <v>WO0000000309044</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-22T09:42:27.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-22T09:42:27.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-22T09:48:32.000Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-22T09:48:32.000Z</v>
+        <v>2026-07-22T09:58:42.000Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>WO0000000308975</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-21T12:13:55.000Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>WO0000000309050</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-21T12:30:25.000Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>WO0000000308987</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-22T08:01:07.999Z</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>WO0000000309073</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-22T08:01:07.999Z</v>
+        <v>2026-07-21T12:30:25.000Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>WO0000000309077</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WO0000000309079</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>WO0000000308997</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-21T12:30:25.000Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>WO0000000308999</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>WO0000000309101</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-22T10:00:42.999Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>INC000000152733</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-17T06:53:11.000Z</v>
+        <v>2026-07-21T16:29:08.999Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-21T16:29:08.999Z</v>
+        <v>2026-07-21T13:25:40.000Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>INC000000152664</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-22T09:13:49.000Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-21T13:25:40.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309164</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-22T09:13:49.000Z</v>
+        <v>2026-07-21T13:50:33.000Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>WO0000000309235</v>
+        <v>WO0000000309241</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-21T13:58:39.999Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>WO0000000309164</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-21T13:50:33.000Z</v>
+        <v>2026-07-21T16:31:56.000Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-21T13:58:39.999Z</v>
+        <v>2026-07-21T14:09:08.000Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>WO0000000309168</v>
+        <v>WO0000000309172</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-21T16:31:56.000Z</v>
+        <v>2026-07-21T14:09:08.000Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309254</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-21T14:29:44.000Z</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>WO0000000309172</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-21T14:33:58.000Z</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>INC000000110345</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2026-07-21T17:59:20.999Z</v>
+        <v>2026-07-21T11:58:05.000Z</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>WO0000000239963</v>
+        <v>WO0000000309258</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2026-07-21T14:26:22.999Z</v>
+        <v>2026-07-17T11:09:59.000Z</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>WO0000000278645</v>
+        <v>INC000000110345</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2026-07-21T14:27:16.000Z</v>
+        <v>2026-07-21T17:59:20.999Z</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>INC000000140158</v>
+        <v>WO0000000239963</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2026-07-20T13:11:54.000Z</v>
+        <v>2026-07-21T14:26:22.999Z</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>INC000000140767</v>
+        <v>WO0000000278645</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2026-07-19T12:56:19.000Z</v>
+        <v>2026-07-21T14:27:16.000Z</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>INC000000141766</v>
+        <v>INC000000140158</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2026-07-21T08:55:08.000Z</v>
+        <v>2026-07-20T13:11:54.000Z</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>INC000000142452</v>
+        <v>INC000000140767</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2026-07-22T07:39:21.999Z</v>
+        <v>2026-07-19T12:56:19.000Z</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>INC000000146339</v>
+        <v>INC000000141766</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2026-07-21T15:05:15.000Z</v>
+        <v>2026-07-21T08:55:08.000Z</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>WO0000000295598</v>
+        <v>INC000000142452</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2026-07-17T10:51:51.999Z</v>
+        <v>2026-07-22T07:39:21.999Z</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>INC000000147926</v>
+        <v>INC000000146339</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2026-07-21T15:43:45.999Z</v>
+        <v>2026-07-21T15:05:15.000Z</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>WO0000000298353</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2026-07-21T19:17:08.000Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>WO0000000298838</v>
+        <v>INC000000147926</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2026-07-21T15:22:31.000Z</v>
+        <v>2026-07-21T15:43:45.999Z</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>WO0000000299920</v>
+        <v>WO0000000298838</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2026-07-21T15:24:13.999Z</v>
+        <v>2026-07-21T15:22:31.000Z</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>WO0000000300081</v>
+        <v>WO0000000299920</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-07-17T13:08:07.000Z</v>
+        <v>2026-07-21T15:24:13.999Z</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>INC000000148888</v>
+        <v>WO0000000300081</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2026-07-21T08:08:07.999Z</v>
+        <v>2026-07-17T13:08:07.000Z</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WO0000000302331</v>
+        <v>INC000000148888</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2026-07-22T08:57:51.999Z</v>
+        <v>2026-07-21T08:08:07.999Z</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>INC000000149757</v>
+        <v>WO0000000302331</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-07-21T16:21:08.000Z</v>
+        <v>2026-07-22T08:57:51.999Z</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>WO0000000303117</v>
+        <v>INC000000149757</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-07-21T10:43:30.000Z</v>
+        <v>2026-07-21T16:21:08.000Z</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>WO0000000303240</v>
+        <v>WO0000000303117</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-07-21T15:30:07.000Z</v>
+        <v>2026-07-21T10:43:30.000Z</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>WO0000000303244</v>
+        <v>WO0000000303240</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-07-21T15:29:08.000Z</v>
+        <v>2026-07-21T15:30:07.000Z</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>INC000000150141</v>
+        <v>WO0000000303244</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-07-21T17:04:17.000Z</v>
+        <v>2026-07-21T15:29:08.000Z</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000150141</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-07-21T15:23:28.000Z</v>
+        <v>2026-07-21T17:04:17.000Z</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>WO0000000304331</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-07-21T12:33:01.000Z</v>
+        <v>2026-07-21T15:23:28.000Z</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>WO0000000304946</v>
+        <v>WO0000000304331</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-07-21T12:27:03.000Z</v>
+        <v>2026-07-21T12:33:01.000Z</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>WO0000000304990</v>
+        <v>WO0000000304946</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-07-22T08:16:13.000Z</v>
+        <v>2026-07-21T12:27:03.000Z</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>INC000000150838</v>
+        <v>WO0000000304990</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-07-21T17:01:11.000Z</v>
+        <v>2026-07-22T08:16:13.000Z</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>WO0000000305131</v>
+        <v>INC000000150838</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-07-22T09:50:35.000Z</v>
+        <v>2026-07-21T17:01:11.000Z</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>WO0000000305138</v>
+        <v>WO0000000305131</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-07-17T12:33:23.000Z</v>
+        <v>2026-07-22T09:50:35.000Z</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>INC000000150748</v>
+        <v>WO0000000305138</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-07-21T16:48:15.999Z</v>
+        <v>2026-07-17T12:33:23.000Z</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>WO0000000305336</v>
+        <v>INC000000150748</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-07-17T13:06:08.999Z</v>
+        <v>2026-07-21T16:48:15.999Z</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305336</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-07-21T18:19:52.000Z</v>
+        <v>2026-07-17T13:06:08.999Z</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>WO0000000305863</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-07-21T17:19:07.000Z</v>
+        <v>2026-07-21T18:19:52.000Z</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>WO0000000305877</v>
+        <v>WO0000000305863</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-07-22T08:01:39.999Z</v>
+        <v>2026-07-21T17:19:07.000Z</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>WO0000000305769</v>
+        <v>WO0000000305877</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-07-21T12:28:00.000Z</v>
+        <v>2026-07-22T08:01:39.999Z</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>WO0000000305770</v>
+        <v>WO0000000305769</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-07-21T12:28:53.999Z</v>
+        <v>2026-07-21T12:28:00.000Z</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>INC000000151203</v>
+        <v>WO0000000305770</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-07-20T09:23:20.000Z</v>
+        <v>2026-07-21T12:28:53.999Z</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>INC000000151143</v>
+        <v>INC000000151203</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-07-21T15:24:31.000Z</v>
+        <v>2026-07-20T09:23:20.000Z</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>INC000000151157</v>
+        <v>INC000000151143</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-07-21T10:59:03.000Z</v>
+        <v>2026-07-21T15:24:31.000Z</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>INC000000151271</v>
+        <v>INC000000151157</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-07-21T16:56:06.999Z</v>
+        <v>2026-07-21T10:59:03.000Z</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>WO0000000306256</v>
+        <v>INC000000151271</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-07-21T17:15:05.000Z</v>
+        <v>2026-07-21T16:56:06.999Z</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>WO0000000306718</v>
+        <v>WO0000000306256</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-07-21T12:29:34.000Z</v>
+        <v>2026-07-21T17:15:05.000Z</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>WO0000000306721</v>
+        <v>WO0000000306718</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-07-21T23:51:23.000Z</v>
+        <v>2026-07-21T12:29:34.000Z</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>WO0000000306726</v>
+        <v>WO0000000306721</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-07-21T12:30:16.000Z</v>
+        <v>2026-07-21T23:51:23.000Z</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>WO0000000306799</v>
+        <v>WO0000000306726</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-07-22T09:16:58.000Z</v>
+        <v>2026-07-21T12:30:16.000Z</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>WO0000000306862</v>
+        <v>WO0000000306799</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-07-21T16:32:53.999Z</v>
+        <v>2026-07-22T09:16:58.000Z</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>WO0000000306927</v>
+        <v>WO0000000306862</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-07-20T23:31:46.999Z</v>
+        <v>2026-07-21T16:32:53.999Z</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>WO0000000306876</v>
+        <v>WO0000000306927</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-07-21T15:41:43.000Z</v>
+        <v>2026-07-20T23:31:46.999Z</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>WO0000000306890</v>
+        <v>WO0000000306876</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-07-22T09:28:33.000Z</v>
+        <v>2026-07-21T15:41:43.000Z</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>WO0000000306899</v>
+        <v>WO0000000306890</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-07-21T16:45:23.000Z</v>
+        <v>2026-07-22T09:28:33.000Z</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>WO0000000306988</v>
+        <v>WO0000000306899</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-07-21T09:13:38.000Z</v>
+        <v>2026-07-21T16:45:23.000Z</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000306988</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-07-21T16:17:14.000Z</v>
+        <v>2026-07-21T09:13:38.000Z</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>WO0000000307090</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-07-21T16:34:09.000Z</v>
+        <v>2026-07-21T16:17:14.000Z</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>INC000000151941</v>
+        <v>WO0000000307090</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-07-22T07:50:34.000Z</v>
+        <v>2026-07-21T16:34:09.000Z</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>WO0000000307437</v>
+        <v>INC000000151941</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-07-21T23:52:20.999Z</v>
+        <v>2026-07-22T07:50:34.000Z</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>INC000000152002</v>
+        <v>WO0000000307437</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-07-17T16:32:59.999Z</v>
+        <v>2026-07-21T23:52:20.999Z</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>WO0000000307483</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-07-21T13:01:38.000Z</v>
+        <v>2026-07-17T16:32:59.999Z</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>WO0000000307635</v>
+        <v>WO0000000307483</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-07-17T13:07:17.000Z</v>
+        <v>2026-07-22T10:05:34.000Z</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>WO0000000307671</v>
+        <v>WO0000000307635</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-07-21T19:54:45.000Z</v>
+        <v>2026-07-17T13:07:17.000Z</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>WO0000000307701</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-07-21T19:54:53.000Z</v>
+        <v>2026-07-21T16:24:16.999Z</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000307725</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-07-21T16:24:16.999Z</v>
+        <v>2026-07-21T15:39:21.000Z</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>WO0000000307725</v>
+        <v>WO0000000307733</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-07-21T15:39:21.000Z</v>
+        <v>2026-07-21T23:59:33.000Z</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>WO0000000307733</v>
+        <v>INC000000152145</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-07-21T23:59:33.000Z</v>
+        <v>2026-07-22T08:19:43.999Z</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>INC000000152145</v>
+        <v>WO0000000307812</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-07-22T08:19:43.999Z</v>
+        <v>2026-07-22T07:02:06.000Z</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>WO0000000307812</v>
+        <v>WO0000000307820</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-07-22T07:02:06.000Z</v>
+        <v>2026-07-21T09:49:48.000Z</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>WO0000000307820</v>
+        <v>WO0000000307940</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-07-21T09:49:48.000Z</v>
+        <v>2026-07-17T16:45:16.999Z</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>WO0000000307940</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-07-17T16:45:16.999Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>INC000000152212</v>
+        <v>WO0000000308040</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-07-17T11:31:35.000Z</v>
+        <v>2026-07-17T15:06:23.000Z</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>WO0000000308040</v>
+        <v>WO0000000308042</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-07-17T15:06:23.000Z</v>
+        <v>2026-07-21T15:40:08.000Z</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>WO0000000308042</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-07-21T15:40:08.000Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>INC000000152214</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-07-17T10:47:42.000Z</v>
+        <v>2026-07-21T16:25:50.000Z</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>WO0000000308052</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-07-21T16:25:50.000Z</v>
+        <v>2026-07-18T12:59:34.000Z</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308105</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-07-18T12:59:34.000Z</v>
+        <v>2026-07-21T15:30:21.999Z</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>WO0000000308105</v>
+        <v>WO0000000308075</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-07-21T15:30:21.999Z</v>
+        <v>2026-07-21T12:31:18.000Z</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>WO0000000308075</v>
+        <v>WO0000000308106</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-07-21T12:31:18.000Z</v>
+        <v>2026-07-21T15:40:12.000Z</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>WO0000000308106</v>
+        <v>WO0000000308083</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-07-21T15:40:12.000Z</v>
+        <v>2026-07-21T15:43:15.000Z</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>WO0000000308083</v>
+        <v>WO0000000308086</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-07-21T15:43:15.000Z</v>
+        <v>2026-07-21T09:28:00.000Z</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>WO0000000308086</v>
+        <v>INC000000152350</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-07-21T09:28:00.000Z</v>
+        <v>2026-07-19T07:58:51.000Z</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>INC000000152350</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-07-19T07:58:51.000Z</v>
+        <v>2026-07-21T14:50:24.000Z</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000308234</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-07-21T14:50:24.000Z</v>
+        <v>2026-07-19T12:53:47.000Z</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>WO0000000308234</v>
+        <v>INC000000152251</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-07-19T12:53:47.000Z</v>
+        <v>2026-07-21T16:16:11.000Z</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>INC000000152251</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-07-21T16:16:11.000Z</v>
+        <v>2026-07-21T18:11:35.999Z</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>INC000000152361</v>
+        <v>WO0000000308196</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-07-21T18:11:35.999Z</v>
+        <v>2026-07-21T08:49:13.000Z</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>WO0000000308196</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-07-21T08:49:13.000Z</v>
+        <v>2026-07-17T12:34:20.000Z</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>WO0000000308197</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-07-17T12:34:20.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>INC000000152369</v>
+        <v>WO0000000308428</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-07-17T10:42:03.000Z</v>
+        <v>2026-07-21T09:09:06.999Z</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>WO0000000308428</v>
+        <v>WO0000000308432</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-07-21T09:09:06.999Z</v>
+        <v>2026-07-21T13:10:12.999Z</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>WO0000000308432</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-07-21T13:10:12.999Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>INC000000152389</v>
+        <v>WO0000000308463</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-07-17T10:53:19.000Z</v>
+        <v>2026-07-21T14:37:05.999Z</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>WO0000000308463</v>
+        <v>WO0000000308475</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-07-21T14:37:05.999Z</v>
+        <v>2026-07-22T09:37:35.999Z</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>WO0000000308475</v>
+        <v>WO0000000308478</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-07-22T09:37:35.999Z</v>
+        <v>2026-07-22T09:36:55.000Z</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>WO0000000308478</v>
+        <v>WO0000000308503</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-07-22T09:36:55.000Z</v>
+        <v>2026-07-22T08:50:36.000Z</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>WO0000000308503</v>
+        <v>INC000000152517</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-07-22T08:50:36.000Z</v>
+        <v>2026-07-17T10:21:00.000Z</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>INC000000152517</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-07-17T10:21:00.000Z</v>
+        <v>2026-07-21T11:34:44.999Z</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000152458</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-07-21T11:34:44.999Z</v>
+        <v>2026-07-22T10:08:45.000Z</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>INC000000152458</v>
+        <v>INC000000152461</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-07-21T10:45:45.000Z</v>
+        <v>2026-07-20T09:23:43.999Z</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>INC000000152461</v>
+        <v>WO0000000308679</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-07-20T09:23:43.999Z</v>
+        <v>2026-07-22T10:06:59.000Z</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>WO0000000308679</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-07-22T07:46:19.000Z</v>
+        <v>2026-07-21T16:40:02.000Z</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>WO0000000308723</v>
+        <v>INC000000152565</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-07-21T16:40:02.000Z</v>
+        <v>2026-07-21T07:47:38.999Z</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>INC000000152565</v>
+        <v>WO0000000308727</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-07-21T07:47:38.999Z</v>
+        <v>2026-07-21T15:25:15.999Z</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>WO0000000308727</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-07-21T15:25:15.999Z</v>
+        <v>2026-07-21T09:27:37.000Z</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-07-21T09:27:37.000Z</v>
+        <v>2026-07-21T17:16:36.999Z</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>INC000000152566</v>
+        <v>WO0000000308755</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-07-21T17:16:36.999Z</v>
+        <v>2026-07-22T09:15:04.999Z</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>WO0000000308755</v>
+        <v>WO0000000308834</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-07-22T09:15:04.999Z</v>
+        <v>2026-07-21T14:03:00.000Z</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>WO0000000308834</v>
+        <v>INC000000152486</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-07-21T14:03:00.000Z</v>
+        <v>2026-07-21T07:42:45.999Z</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>INC000000152486</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-07-21T07:42:45.999Z</v>
+        <v>2026-07-21T18:43:19.000Z</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-07-21T18:43:19.000Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>INC000000152586</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-07-17T10:46:28.000Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>INC000000152591</v>
+        <v>INC000000152594</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-07-17T11:00:29.999Z</v>
+        <v>2026-07-20T13:46:11.000Z</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>INC000000152594</v>
+        <v>WO0000000308895</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-07-20T13:46:11.000Z</v>
+        <v>2026-07-21T11:27:56.999Z</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>WO0000000308895</v>
+        <v>WO0000000309018</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-07-21T11:27:56.999Z</v>
+        <v>2026-07-22T09:22:31.999Z</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>WO0000000309018</v>
+        <v>WO0000000309021</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-07-22T09:22:31.999Z</v>
+        <v>2026-07-21T11:44:57.000Z</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>WO0000000309021</v>
+        <v>WO0000000309028</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-07-21T11:44:57.000Z</v>
+        <v>2026-07-22T08:50:35.000Z</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>WO0000000309028</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-07-22T08:50:35.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>INC000000152628</v>
+        <v>WO0000000308967</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-07-17T10:44:38.000Z</v>
+        <v>2026-07-21T10:04:47.000Z</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>WO0000000308967</v>
+        <v>INC000000152630</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-07-21T10:04:47.000Z</v>
+        <v>2026-07-21T07:35:42.000Z</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>INC000000152630</v>
+        <v>WO0000000308970</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-07-21T07:35:42.000Z</v>
+        <v>2026-07-21T16:29:18.000Z</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>WO0000000308970</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-07-21T16:29:18.000Z</v>
+        <v>2026-07-21T14:13:19.000Z</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>WO0000000308986</v>
+        <v>INC000000152643</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-07-21T14:13:19.000Z</v>
+        <v>2026-07-22T08:14:00.000Z</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>INC000000152643</v>
+        <v>INC000000152737</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-07-22T08:14:00.000Z</v>
+        <v>2026-07-21T14:29:46.000Z</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>INC000000152737</v>
+        <v>WO0000000309124</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-07-21T14:29:46.000Z</v>
+        <v>2026-07-22T08:06:26.000Z</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>WO0000000309124</v>
+        <v>WO0000000309136</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-07-22T08:06:26.000Z</v>
+        <v>2026-07-21T12:55:08.999Z</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>WO0000000309136</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-07-21T12:55:08.999Z</v>
+        <v>2026-07-21T13:13:25.000Z</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000152664</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-07-21T13:13:25.000Z</v>
+        <v>2026-07-22T09:58:27.999Z</v>
       </c>
     </row>
     <row r="591">
@@ -5195,4660 +5195,4684 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309187</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-07-21T14:29:44.000Z</v>
+        <v>2026-07-21T11:59:19.000Z</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>WO0000000309187</v>
+        <v>WO0000000309189</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-07-21T11:59:19.000Z</v>
+        <v>2026-07-21T12:14:00.999Z</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>WO0000000309183</v>
+        <v>WO0000000309259</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-07-21T14:33:58.000Z</v>
+        <v>2026-07-21T12:14:33.000Z</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>WO0000000309256</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-07-21T11:58:05.000Z</v>
+        <v>2026-07-21T09:55:04.000Z</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>WO0000000309189</v>
+        <v>WO0000000309262</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-07-21T12:14:00.999Z</v>
+        <v>2026-07-21T14:50:25.000Z</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>WO0000000309258</v>
+        <v>INC000000152690</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-07-17T11:09:59.000Z</v>
+        <v>2026-07-17T15:06:00.000Z</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>WO0000000309259</v>
+        <v>WO0000000309195</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-07-21T12:14:33.000Z</v>
+        <v>2026-07-21T12:18:50.000Z</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152772</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-07-21T09:55:04.000Z</v>
+        <v>2026-07-21T14:27:36.000Z</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>WO0000000309262</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-07-21T14:50:25.000Z</v>
+        <v>2026-07-21T10:37:55.000Z</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>INC000000152690</v>
+        <v>WO0000000309199</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-07-17T15:06:00.000Z</v>
+        <v>2026-07-21T15:17:00.999Z</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>WO0000000309195</v>
+        <v>WO0000000309200</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-07-21T12:18:50.000Z</v>
+        <v>2026-07-17T10:36:06.999Z</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>INC000000152772</v>
+        <v>WO0000000309401</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-07-21T14:27:36.000Z</v>
+        <v>2026-07-17T11:10:53.000Z</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>INC000000152774</v>
+        <v>WO0000000309271</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-07-21T10:37:55.000Z</v>
+        <v>2026-07-21T15:08:50.000Z</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>WO0000000309199</v>
+        <v>INC000000152777</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-07-21T15:17:00.999Z</v>
+        <v>2026-07-21T14:49:58.000Z</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>WO0000000309200</v>
+        <v>WO0000000309410</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-07-17T10:36:06.999Z</v>
+        <v>2026-07-21T09:07:41.000Z</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>WO0000000309401</v>
+        <v>WO0000000309278</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-07-17T11:10:53.000Z</v>
+        <v>2026-07-21T15:19:01.999Z</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>WO0000000309271</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-07-21T15:08:50.000Z</v>
+        <v>2026-07-21T15:19:03.000Z</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>INC000000152777</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-07-21T14:49:58.000Z</v>
+        <v>2026-07-22T08:56:04.000Z</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>WO0000000309410</v>
+        <v>WO0000000309282</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-07-21T09:07:41.000Z</v>
+        <v>2026-07-17T11:17:29.000Z</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>WO0000000309278</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-07-21T15:19:01.999Z</v>
+        <v>2026-07-21T15:27:18.999Z</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>WO0000000309411</v>
+        <v>INC000000152802</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-07-21T15:19:03.000Z</v>
+        <v>2026-07-21T14:26:49.000Z</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309425</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-07-22T08:56:04.000Z</v>
+        <v>2026-07-21T15:44:00.000Z</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>WO0000000309282</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-07-17T11:17:29.000Z</v>
+        <v>2026-07-22T09:27:31.000Z</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309412</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-07-21T15:27:18.999Z</v>
+        <v>2026-07-21T15:48:12.000Z</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>INC000000152802</v>
+        <v>WO0000000309295</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-07-21T14:26:49.000Z</v>
+        <v>2026-07-21T15:52:20.999Z</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>WO0000000309425</v>
+        <v>WO0000000309430</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-07-21T15:44:00.000Z</v>
+        <v>2026-07-21T15:52:20.000Z</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309431</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-07-22T09:27:31.000Z</v>
+        <v>2026-07-22T09:10:18.000Z</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>WO0000000309412</v>
+        <v>WO0000000309433</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-07-21T15:48:12.000Z</v>
+        <v>2026-07-21T15:56:24.000Z</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>WO0000000309295</v>
+        <v>WO0000000309435</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-07-21T15:52:20.999Z</v>
+        <v>2026-07-22T10:13:06.000Z</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>WO0000000309430</v>
+        <v>WO0000000309438</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-07-21T15:52:20.000Z</v>
+        <v>2026-07-21T16:02:36.000Z</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>WO0000000309431</v>
+        <v>WO0000000309503</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-07-22T09:10:18.000Z</v>
+        <v>2026-07-21T12:22:28.000Z</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>WO0000000309433</v>
+        <v>INC000000152789</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-07-21T15:56:24.000Z</v>
+        <v>2026-07-22T10:01:06.000Z</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>WO0000000309435</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-07-21T16:00:27.000Z</v>
+        <v>2026-07-21T17:13:09.000Z</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>WO0000000309438</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-07-21T16:02:36.000Z</v>
+        <v>2026-07-21T17:18:56.000Z</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>WO0000000309503</v>
+        <v>WO0000000309501</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-07-21T12:22:28.000Z</v>
+        <v>2026-07-17T11:59:29.000Z</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>INC000000152789</v>
+        <v>WO0000000309441</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-07-22T08:52:02.000Z</v>
+        <v>2026-07-21T16:20:21.000Z</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>INC000000152790</v>
+        <v>WO0000000309447</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-07-21T17:13:09.000Z</v>
+        <v>2026-07-21T16:14:50.000Z</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309509</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-07-21T17:18:56.000Z</v>
+        <v>2026-07-21T16:24:57.999Z</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>WO0000000309501</v>
+        <v>WO0000000309453</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-07-17T11:59:29.000Z</v>
+        <v>2026-07-21T16:24:57.000Z</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>WO0000000309441</v>
+        <v>WO0000000309512</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-07-21T16:20:21.000Z</v>
+        <v>2026-07-22T08:58:10.000Z</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>WO0000000309447</v>
+        <v>WO0000000309513</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-07-21T16:14:50.000Z</v>
+        <v>2026-07-17T11:58:10.000Z</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>WO0000000309509</v>
+        <v>WO0000000309454</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-07-21T16:24:57.999Z</v>
+        <v>2026-07-21T16:29:03.000Z</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>WO0000000309453</v>
+        <v>WO0000000309515</v>
       </c>
       <c r="B642" s="1" t="d">
-        <v>2026-07-21T16:24:57.000Z</v>
+        <v>2026-07-21T15:41:22.000Z</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>WO0000000309512</v>
+        <v>WO0000000309457</v>
       </c>
       <c r="B643" s="1" t="d">
-        <v>2026-07-22T08:58:10.000Z</v>
+        <v>2026-07-21T16:33:06.999Z</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>WO0000000309513</v>
+        <v>WO0000000309514</v>
       </c>
       <c r="B644" s="1" t="d">
-        <v>2026-07-17T11:58:10.000Z</v>
+        <v>2026-07-17T12:10:33.000Z</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>WO0000000309454</v>
+        <v>WO0000000309462</v>
       </c>
       <c r="B645" s="1" t="d">
-        <v>2026-07-21T16:29:03.000Z</v>
+        <v>2026-07-17T15:22:05.999Z</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>WO0000000309515</v>
+        <v>WO0000000309465</v>
       </c>
       <c r="B646" s="1" t="d">
-        <v>2026-07-21T15:41:22.000Z</v>
+        <v>2026-07-21T16:55:28.999Z</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>WO0000000309457</v>
+        <v>WO0000000309520</v>
       </c>
       <c r="B647" s="1" t="d">
-        <v>2026-07-21T16:33:06.999Z</v>
+        <v>2026-07-17T14:05:08.000Z</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>WO0000000309514</v>
+        <v>INC000000152903</v>
       </c>
       <c r="B648" s="1" t="d">
-        <v>2026-07-17T12:10:33.000Z</v>
+        <v>2026-07-22T08:28:02.000Z</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>WO0000000309462</v>
+        <v>WO0000000309470</v>
       </c>
       <c r="B649" s="1" t="d">
-        <v>2026-07-17T15:22:05.999Z</v>
+        <v>2026-07-21T09:11:31.000Z</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>WO0000000309465</v>
+        <v>INC000000152908</v>
       </c>
       <c r="B650" s="1" t="d">
-        <v>2026-07-21T16:55:28.999Z</v>
+        <v>2026-07-22T09:09:51.000Z</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>WO0000000309520</v>
+        <v>WO0000000309479</v>
       </c>
       <c r="B651" s="1" t="d">
-        <v>2026-07-17T14:05:08.000Z</v>
+        <v>2026-07-22T08:25:38.999Z</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>INC000000152903</v>
+        <v>WO0000000309489</v>
       </c>
       <c r="B652" s="1" t="d">
-        <v>2026-07-22T08:28:02.000Z</v>
+        <v>2026-07-21T15:23:06.000Z</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>WO0000000309470</v>
+        <v>INC000000152914</v>
       </c>
       <c r="B653" s="1" t="d">
-        <v>2026-07-21T09:11:31.000Z</v>
+        <v>2026-07-21T16:41:07.000Z</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>INC000000152908</v>
+        <v>WO0000000309487</v>
       </c>
       <c r="B654" s="1" t="d">
-        <v>2026-07-22T09:09:51.000Z</v>
+        <v>2026-07-17T13:37:56.000Z</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>WO0000000309479</v>
+        <v>WO0000000309497</v>
       </c>
       <c r="B655" s="1" t="d">
-        <v>2026-07-22T08:25:38.999Z</v>
+        <v>2026-07-21T15:42:45.000Z</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>WO0000000309489</v>
+        <v>WO0000000309499</v>
       </c>
       <c r="B656" s="1" t="d">
-        <v>2026-07-21T15:23:06.000Z</v>
+        <v>2026-07-17T15:54:58.999Z</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>INC000000152914</v>
+        <v>WO0000000309546</v>
       </c>
       <c r="B657" s="1" t="d">
-        <v>2026-07-21T16:41:07.000Z</v>
+        <v>2026-07-22T09:42:27.000Z</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>WO0000000309487</v>
+        <v>INC000000152824</v>
       </c>
       <c r="B658" s="1" t="d">
-        <v>2026-07-17T13:37:56.000Z</v>
+        <v>2026-07-22T08:30:58.000Z</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>WO0000000309497</v>
+        <v>INC000000152921</v>
       </c>
       <c r="B659" s="1" t="d">
-        <v>2026-07-21T15:42:45.000Z</v>
+        <v>2026-07-17T17:39:36.000Z</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>WO0000000309499</v>
+        <v>WO0000000309603</v>
       </c>
       <c r="B660" s="1" t="d">
-        <v>2026-07-17T15:54:58.999Z</v>
+        <v>2026-07-21T12:29:32.000Z</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>WO0000000309546</v>
+        <v>WO0000000309549</v>
       </c>
       <c r="B661" s="1" t="d">
-        <v>2026-07-22T09:42:27.000Z</v>
+        <v>2026-07-21T16:31:50.000Z</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>INC000000152824</v>
+        <v>WO0000000309551</v>
       </c>
       <c r="B662" s="1" t="d">
-        <v>2026-07-22T08:30:58.000Z</v>
+        <v>2026-07-17T14:48:06.999Z</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>INC000000152921</v>
+        <v>WO0000000309609</v>
       </c>
       <c r="B663" s="1" t="d">
-        <v>2026-07-17T17:39:36.000Z</v>
+        <v>2026-07-22T09:38:23.000Z</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>WO0000000309603</v>
+        <v>WO0000000309553</v>
       </c>
       <c r="B664" s="1" t="d">
-        <v>2026-07-21T12:29:32.000Z</v>
+        <v>2026-07-17T14:55:11.000Z</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>WO0000000309549</v>
+        <v>WO0000000309555</v>
       </c>
       <c r="B665" s="1" t="d">
-        <v>2026-07-21T16:31:50.000Z</v>
+        <v>2026-07-21T19:55:20.000Z</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>WO0000000309551</v>
+        <v>WO0000000309558</v>
       </c>
       <c r="B666" s="1" t="d">
-        <v>2026-07-17T14:48:06.999Z</v>
+        <v>2026-07-17T15:14:07.000Z</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>WO0000000309609</v>
+        <v>WO0000000309616</v>
       </c>
       <c r="B667" s="1" t="d">
-        <v>2026-07-22T09:38:23.000Z</v>
+        <v>2026-07-21T12:15:31.999Z</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>WO0000000309553</v>
+        <v>WO0000000309618</v>
       </c>
       <c r="B668" s="1" t="d">
-        <v>2026-07-17T14:55:11.000Z</v>
+        <v>2026-07-22T09:15:12.000Z</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>WO0000000309555</v>
+        <v>INC000000152933</v>
       </c>
       <c r="B669" s="1" t="d">
-        <v>2026-07-21T19:55:20.000Z</v>
+        <v>2026-07-22T08:43:13.999Z</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>WO0000000309558</v>
+        <v>WO0000000309569</v>
       </c>
       <c r="B670" s="1" t="d">
-        <v>2026-07-17T15:14:07.000Z</v>
+        <v>2026-07-21T12:33:40.999Z</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>WO0000000309616</v>
+        <v>WO0000000309570</v>
       </c>
       <c r="B671" s="1" t="d">
-        <v>2026-07-21T12:15:31.999Z</v>
+        <v>2026-07-22T09:22:01.000Z</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>WO0000000309618</v>
+        <v>WO0000000309624</v>
       </c>
       <c r="B672" s="1" t="d">
-        <v>2026-07-22T09:15:12.000Z</v>
+        <v>2026-07-21T07:06:23.999Z</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>INC000000152933</v>
+        <v>WO0000000309574</v>
       </c>
       <c r="B673" s="1" t="d">
-        <v>2026-07-22T08:43:13.999Z</v>
+        <v>2026-07-17T15:38:37.000Z</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>WO0000000309569</v>
+        <v>WO0000000309576</v>
       </c>
       <c r="B674" s="1" t="d">
-        <v>2026-07-21T12:33:40.999Z</v>
+        <v>2026-07-17T15:44:12.000Z</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>WO0000000309570</v>
+        <v>WO0000000309625</v>
       </c>
       <c r="B675" s="1" t="d">
-        <v>2026-07-22T09:22:01.000Z</v>
+        <v>2026-07-21T07:17:15.999Z</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>WO0000000309624</v>
+        <v>WO0000000309626</v>
       </c>
       <c r="B676" s="1" t="d">
-        <v>2026-07-21T07:06:23.999Z</v>
+        <v>2026-07-21T10:39:19.000Z</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>WO0000000309574</v>
+        <v>WO0000000309627</v>
       </c>
       <c r="B677" s="1" t="d">
-        <v>2026-07-17T15:38:37.000Z</v>
+        <v>2026-07-21T15:44:41.000Z</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>WO0000000309576</v>
+        <v>WO0000000309629</v>
       </c>
       <c r="B678" s="1" t="d">
-        <v>2026-07-17T15:44:12.000Z</v>
+        <v>2026-07-22T08:03:11.000Z</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>WO0000000309625</v>
+        <v>WO0000000309632</v>
       </c>
       <c r="B679" s="1" t="d">
-        <v>2026-07-21T07:17:15.999Z</v>
+        <v>2026-07-20T21:58:45.000Z</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>WO0000000309626</v>
+        <v>WO0000000309633</v>
       </c>
       <c r="B680" s="1" t="d">
-        <v>2026-07-21T10:39:19.000Z</v>
+        <v>2026-07-17T18:31:57.000Z</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>WO0000000309627</v>
+        <v>WO0000000309636</v>
       </c>
       <c r="B681" s="1" t="d">
-        <v>2026-07-21T15:44:41.000Z</v>
+        <v>2026-07-21T16:16:50.000Z</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>WO0000000309629</v>
+        <v>INC000000152838</v>
       </c>
       <c r="B682" s="1" t="d">
-        <v>2026-07-22T08:03:11.000Z</v>
+        <v>2026-07-21T07:14:10.000Z</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>WO0000000309632</v>
+        <v>INC000000152943</v>
       </c>
       <c r="B683" s="1" t="d">
-        <v>2026-07-20T21:58:45.000Z</v>
+        <v>2026-07-21T15:23:46.000Z</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>WO0000000309633</v>
+        <v>WO0000000309586</v>
       </c>
       <c r="B684" s="1" t="d">
-        <v>2026-07-17T18:31:57.000Z</v>
+        <v>2026-07-21T16:18:57.999Z</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>WO0000000309636</v>
+        <v>WO0000000309589</v>
       </c>
       <c r="B685" s="1" t="d">
-        <v>2026-07-21T16:16:50.000Z</v>
+        <v>2026-07-21T15:25:40.000Z</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>INC000000152838</v>
+        <v>WO0000000309592</v>
       </c>
       <c r="B686" s="1" t="d">
-        <v>2026-07-21T07:14:10.000Z</v>
+        <v>2026-07-22T09:26:17.000Z</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>INC000000152943</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B687" s="1" t="d">
-        <v>2026-07-21T15:23:46.000Z</v>
+        <v>2026-07-18T14:28:30.999Z</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>WO0000000309586</v>
+        <v>WO0000000309647</v>
       </c>
       <c r="B688" s="1" t="d">
-        <v>2026-07-21T16:18:57.999Z</v>
+        <v>2026-07-21T09:05:18.000Z</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>WO0000000309589</v>
+        <v>WO0000000309651</v>
       </c>
       <c r="B689" s="1" t="d">
-        <v>2026-07-21T15:25:40.000Z</v>
+        <v>2026-07-21T16:49:09.000Z</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>WO0000000309592</v>
+        <v>WO0000000309595</v>
       </c>
       <c r="B690" s="1" t="d">
-        <v>2026-07-22T09:26:17.000Z</v>
+        <v>2026-07-21T08:34:47.000Z</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309596</v>
       </c>
       <c r="B691" s="1" t="d">
-        <v>2026-07-18T14:28:30.999Z</v>
+        <v>2026-07-18T13:56:50.000Z</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>WO0000000309647</v>
+        <v>WO0000000309597</v>
       </c>
       <c r="B692" s="1" t="d">
-        <v>2026-07-21T09:05:18.000Z</v>
+        <v>2026-07-21T10:23:48.000Z</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>WO0000000309651</v>
+        <v>WO0000000309309</v>
       </c>
       <c r="B693" s="1" t="d">
-        <v>2026-07-21T16:49:09.000Z</v>
+        <v>2026-07-21T11:20:55.000Z</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>WO0000000309595</v>
+        <v>INC000000152948</v>
       </c>
       <c r="B694" s="1" t="d">
-        <v>2026-07-21T08:34:47.000Z</v>
+        <v>2026-07-22T09:47:37.000Z</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>WO0000000309596</v>
+        <v>INC000000152845</v>
       </c>
       <c r="B695" s="1" t="d">
-        <v>2026-07-18T13:56:50.000Z</v>
+        <v>2026-07-21T17:15:25.999Z</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>WO0000000309597</v>
+        <v>WO0000000309310</v>
       </c>
       <c r="B696" s="1" t="d">
-        <v>2026-07-21T10:23:48.000Z</v>
+        <v>2026-07-21T11:21:15.000Z</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>WO0000000309309</v>
+        <v>INC000000152848</v>
       </c>
       <c r="B697" s="1" t="d">
-        <v>2026-07-21T11:20:55.000Z</v>
+        <v>2026-07-22T09:42:27.999Z</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>INC000000152948</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B698" s="1" t="d">
-        <v>2026-07-22T09:47:37.000Z</v>
+        <v>2026-07-20T22:53:08.999Z</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>INC000000152845</v>
+        <v>WO0000000309599</v>
       </c>
       <c r="B699" s="1" t="d">
-        <v>2026-07-21T17:15:25.999Z</v>
+        <v>2026-07-17T17:35:48.000Z</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>WO0000000309310</v>
+        <v>WO0000000309704</v>
       </c>
       <c r="B700" s="1" t="d">
-        <v>2026-07-21T11:21:15.000Z</v>
+        <v>2026-07-22T09:01:41.000Z</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>INC000000152848</v>
+        <v>INC000000152955</v>
       </c>
       <c r="B701" s="1" t="d">
-        <v>2026-07-22T09:42:27.999Z</v>
+        <v>2026-07-22T09:19:20.000Z</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309664</v>
       </c>
       <c r="B702" s="1" t="d">
-        <v>2026-07-20T22:53:08.999Z</v>
+        <v>2026-07-17T18:55:57.000Z</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>WO0000000309599</v>
+        <v>WO0000000309666</v>
       </c>
       <c r="B703" s="1" t="d">
-        <v>2026-07-17T17:35:48.000Z</v>
+        <v>2026-07-17T19:16:56.000Z</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>WO0000000309704</v>
+        <v>WO0000000309714</v>
       </c>
       <c r="B704" s="1" t="d">
-        <v>2026-07-22T09:01:41.000Z</v>
+        <v>2026-07-20T22:53:50.000Z</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>INC000000152953</v>
+        <v>WO0000000309669</v>
       </c>
       <c r="B705" s="1" t="d">
-        <v>2026-07-22T09:47:14.000Z</v>
+        <v>2026-07-22T08:01:09.000Z</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>INC000000152955</v>
+        <v>INC000000152856</v>
       </c>
       <c r="B706" s="1" t="d">
-        <v>2026-07-22T09:19:20.000Z</v>
+        <v>2026-07-18T06:08:03.000Z</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>WO0000000309664</v>
+        <v>WO0000000309671</v>
       </c>
       <c r="B707" s="1" t="d">
-        <v>2026-07-17T18:55:57.000Z</v>
+        <v>2026-07-22T08:01:09.000Z</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>WO0000000309666</v>
+        <v>INC000000152873</v>
       </c>
       <c r="B708" s="1" t="d">
-        <v>2026-07-17T19:16:56.000Z</v>
+        <v>2026-07-21T08:30:37.999Z</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>WO0000000309714</v>
+        <v>INC000000152971</v>
       </c>
       <c r="B709" s="1" t="d">
-        <v>2026-07-20T22:53:50.000Z</v>
+        <v>2026-07-21T16:21:36.000Z</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>WO0000000309669</v>
+        <v>WO0000000309682</v>
       </c>
       <c r="B710" s="1" t="d">
-        <v>2026-07-22T08:01:09.000Z</v>
+        <v>2026-07-18T07:56:16.000Z</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>INC000000152856</v>
+        <v>WO0000000309686</v>
       </c>
       <c r="B711" s="1" t="d">
-        <v>2026-07-18T06:08:03.000Z</v>
+        <v>2026-07-18T08:09:34.000Z</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>WO0000000309671</v>
+        <v>WO0000000309689</v>
       </c>
       <c r="B712" s="1" t="d">
-        <v>2026-07-22T08:01:09.000Z</v>
+        <v>2026-07-20T22:58:39.999Z</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>INC000000152873</v>
+        <v>INC000000152883</v>
       </c>
       <c r="B713" s="1" t="d">
-        <v>2026-07-21T08:30:37.999Z</v>
+        <v>2026-07-21T13:07:15.000Z</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>INC000000152971</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B714" s="1" t="d">
-        <v>2026-07-21T16:21:36.000Z</v>
+        <v>2026-07-22T09:01:01.000Z</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>WO0000000309682</v>
+        <v>INC000000152981</v>
       </c>
       <c r="B715" s="1" t="d">
-        <v>2026-07-18T07:56:16.000Z</v>
+        <v>2026-07-21T10:10:23.000Z</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>WO0000000309686</v>
+        <v>WO0000000309697</v>
       </c>
       <c r="B716" s="1" t="d">
-        <v>2026-07-18T08:09:34.000Z</v>
+        <v>2026-07-22T08:01:09.000Z</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>WO0000000309689</v>
+        <v>INC000000152989</v>
       </c>
       <c r="B717" s="1" t="d">
-        <v>2026-07-20T22:58:39.999Z</v>
+        <v>2026-07-21T13:14:23.000Z</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>INC000000152883</v>
+        <v>WO0000000309803</v>
       </c>
       <c r="B718" s="1" t="d">
-        <v>2026-07-21T13:07:15.000Z</v>
+        <v>2026-07-18T10:20:12.000Z</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>WO0000000309692</v>
+        <v>WO0000000309804</v>
       </c>
       <c r="B719" s="1" t="d">
-        <v>2026-07-22T09:01:01.000Z</v>
+        <v>2026-07-21T11:12:41.000Z</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>INC000000152981</v>
+        <v>WO0000000309807</v>
       </c>
       <c r="B720" s="1" t="d">
-        <v>2026-07-21T10:10:23.000Z</v>
+        <v>2026-07-21T11:11:58.999Z</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>WO0000000309697</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B721" s="1" t="d">
-        <v>2026-07-22T08:01:09.000Z</v>
+        <v>2026-07-22T08:34:20.000Z</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>INC000000152985</v>
+        <v>INC000000152898</v>
       </c>
       <c r="B722" s="1" t="d">
-        <v>2026-07-22T07:43:18.000Z</v>
+        <v>2026-07-21T10:52:04.000Z</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>INC000000152989</v>
+        <v>WO0000000309810</v>
       </c>
       <c r="B723" s="1" t="d">
-        <v>2026-07-21T13:14:23.000Z</v>
+        <v>2026-07-18T11:06:11.000Z</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>WO0000000309803</v>
+        <v>WO0000000309752</v>
       </c>
       <c r="B724" s="1" t="d">
-        <v>2026-07-18T10:20:12.000Z</v>
+        <v>2026-07-18T11:09:41.999Z</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>WO0000000309804</v>
+        <v>WO0000000309816</v>
       </c>
       <c r="B725" s="1" t="d">
-        <v>2026-07-21T11:12:41.000Z</v>
+        <v>2026-07-20T23:12:13.999Z</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>WO0000000309807</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B726" s="1" t="d">
-        <v>2026-07-21T11:11:58.999Z</v>
+        <v>2026-07-21T14:33:57.000Z</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>INC000000152896</v>
+        <v>WO0000000309759</v>
       </c>
       <c r="B727" s="1" t="d">
-        <v>2026-07-22T08:34:20.000Z</v>
+        <v>2026-07-18T12:43:30.000Z</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>INC000000152898</v>
+        <v>WO0000000309825</v>
       </c>
       <c r="B728" s="1" t="d">
-        <v>2026-07-21T10:52:04.000Z</v>
+        <v>2026-07-21T17:15:57.000Z</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>WO0000000309810</v>
+        <v>INC000000153105</v>
       </c>
       <c r="B729" s="1" t="d">
-        <v>2026-07-18T11:06:11.000Z</v>
+        <v>2026-07-22T08:58:13.000Z</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>WO0000000309752</v>
+        <v>WO0000000309826</v>
       </c>
       <c r="B730" s="1" t="d">
-        <v>2026-07-18T11:09:41.999Z</v>
+        <v>2026-07-21T20:35:02.000Z</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>WO0000000309816</v>
+        <v>WO0000000309768</v>
       </c>
       <c r="B731" s="1" t="d">
-        <v>2026-07-20T23:12:13.999Z</v>
+        <v>2026-07-18T16:42:39.000Z</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153107</v>
       </c>
       <c r="B732" s="1" t="d">
-        <v>2026-07-21T14:33:57.000Z</v>
+        <v>2026-07-21T09:58:01.000Z</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>WO0000000309759</v>
+        <v>WO0000000309829</v>
       </c>
       <c r="B733" s="1" t="d">
-        <v>2026-07-18T12:43:30.000Z</v>
+        <v>2026-07-21T07:31:20.000Z</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>WO0000000309825</v>
+        <v>INC000000153019</v>
       </c>
       <c r="B734" s="1" t="d">
-        <v>2026-07-21T17:15:57.000Z</v>
+        <v>2026-07-21T13:04:28.000Z</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>INC000000153105</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B735" s="1" t="d">
-        <v>2026-07-22T08:58:13.000Z</v>
+        <v>2026-07-21T15:24:57.000Z</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>WO0000000309826</v>
+        <v>INC000000153022</v>
       </c>
       <c r="B736" s="1" t="d">
-        <v>2026-07-21T20:35:02.000Z</v>
+        <v>2026-07-22T08:54:15.000Z</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>WO0000000309768</v>
+        <v>INC000000153111</v>
       </c>
       <c r="B737" s="1" t="d">
-        <v>2026-07-18T16:42:39.000Z</v>
+        <v>2026-07-19T10:28:24.000Z</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>INC000000153107</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B738" s="1" t="d">
-        <v>2026-07-21T09:58:01.000Z</v>
+        <v>2026-07-21T17:09:00.000Z</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>WO0000000309829</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B739" s="1" t="d">
-        <v>2026-07-21T07:31:20.000Z</v>
+        <v>2026-07-21T15:26:52.999Z</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>INC000000153019</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B740" s="1" t="d">
-        <v>2026-07-21T13:04:28.000Z</v>
+        <v>2026-07-21T15:06:50.999Z</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153121</v>
       </c>
       <c r="B741" s="1" t="d">
-        <v>2026-07-21T15:24:57.000Z</v>
+        <v>2026-07-19T15:02:53.000Z</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>INC000000153022</v>
+        <v>WO0000000309780</v>
       </c>
       <c r="B742" s="1" t="d">
-        <v>2026-07-22T08:54:15.000Z</v>
+        <v>2026-07-21T07:27:19.000Z</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>INC000000153111</v>
+        <v>WO0000000309837</v>
       </c>
       <c r="B743" s="1" t="d">
-        <v>2026-07-19T10:28:24.000Z</v>
+        <v>2026-07-21T07:31:02.000Z</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>INC000000153027</v>
+        <v>WO0000000309781</v>
       </c>
       <c r="B744" s="1" t="d">
-        <v>2026-07-21T17:09:00.000Z</v>
+        <v>2026-07-21T08:57:28.999Z</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309783</v>
       </c>
       <c r="B745" s="1" t="d">
-        <v>2026-07-21T15:26:52.999Z</v>
+        <v>2026-07-21T07:17:41.000Z</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309838</v>
       </c>
       <c r="B746" s="1" t="d">
-        <v>2026-07-21T15:06:50.999Z</v>
+        <v>2026-07-20T00:21:08.999Z</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>INC000000153121</v>
+        <v>INC000000153034</v>
       </c>
       <c r="B747" s="1" t="d">
-        <v>2026-07-19T15:02:53.000Z</v>
+        <v>2026-07-22T07:46:52.000Z</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>WO0000000309780</v>
+        <v>INC000000153035</v>
       </c>
       <c r="B748" s="1" t="d">
-        <v>2026-07-21T07:27:19.000Z</v>
+        <v>2026-07-22T07:53:16.999Z</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>WO0000000309837</v>
+        <v>INC000000153036</v>
       </c>
       <c r="B749" s="1" t="d">
-        <v>2026-07-21T07:31:02.000Z</v>
+        <v>2026-07-22T07:47:57.000Z</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>WO0000000309781</v>
+        <v>INC000000153037</v>
       </c>
       <c r="B750" s="1" t="d">
-        <v>2026-07-21T08:57:28.999Z</v>
+        <v>2026-07-22T07:49:20.000Z</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>WO0000000309783</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B751" s="1" t="d">
-        <v>2026-07-21T07:17:41.000Z</v>
+        <v>2026-07-21T13:30:52.000Z</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>WO0000000309838</v>
+        <v>WO0000000309789</v>
       </c>
       <c r="B752" s="1" t="d">
-        <v>2026-07-20T00:21:08.999Z</v>
+        <v>2026-07-21T09:45:18.000Z</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>INC000000153034</v>
+        <v>WO0000000309841</v>
       </c>
       <c r="B753" s="1" t="d">
-        <v>2026-07-22T07:46:52.000Z</v>
+        <v>2026-07-21T09:36:30.999Z</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>INC000000153035</v>
+        <v>WO0000000309842</v>
       </c>
       <c r="B754" s="1" t="d">
-        <v>2026-07-22T07:53:16.999Z</v>
+        <v>2026-07-20T15:31:42.000Z</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>INC000000153036</v>
+        <v>WO0000000309793</v>
       </c>
       <c r="B755" s="1" t="d">
-        <v>2026-07-22T07:47:57.000Z</v>
+        <v>2026-07-22T09:01:02.000Z</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>INC000000153037</v>
+        <v>WO0000000309848</v>
       </c>
       <c r="B756" s="1" t="d">
-        <v>2026-07-22T07:49:20.000Z</v>
+        <v>2026-07-20T19:12:35.999Z</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>INC000000153038</v>
+        <v>WO0000000309851</v>
       </c>
       <c r="B757" s="1" t="d">
-        <v>2026-07-21T13:30:52.000Z</v>
+        <v>2026-07-21T10:57:08.000Z</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>WO0000000309789</v>
+        <v>WO0000000309902</v>
       </c>
       <c r="B758" s="1" t="d">
-        <v>2026-07-21T09:45:18.000Z</v>
+        <v>2026-07-21T07:14:42.000Z</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>WO0000000309841</v>
+        <v>INC000000153048</v>
       </c>
       <c r="B759" s="1" t="d">
-        <v>2026-07-21T09:36:30.999Z</v>
+        <v>2026-07-21T08:15:57.000Z</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>WO0000000309842</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B760" s="1" t="d">
-        <v>2026-07-20T15:31:42.000Z</v>
+        <v>2026-07-21T08:36:23.999Z</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>WO0000000309793</v>
+        <v>WO0000000309862</v>
       </c>
       <c r="B761" s="1" t="d">
-        <v>2026-07-22T09:01:02.000Z</v>
+        <v>2026-07-21T07:21:46.000Z</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>WO0000000309848</v>
+        <v>WO0000000309861</v>
       </c>
       <c r="B762" s="1" t="d">
-        <v>2026-07-20T19:12:35.999Z</v>
+        <v>2026-07-21T15:13:04.000Z</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>WO0000000309851</v>
+        <v>INC000000153062</v>
       </c>
       <c r="B763" s="1" t="d">
-        <v>2026-07-21T10:57:08.000Z</v>
+        <v>2026-07-21T10:38:36.000Z</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>WO0000000309902</v>
+        <v>INC000000153143</v>
       </c>
       <c r="B764" s="1" t="d">
-        <v>2026-07-21T07:14:42.000Z</v>
+        <v>2026-07-21T08:04:39.999Z</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>INC000000153048</v>
+        <v>WO0000000309880</v>
       </c>
       <c r="B765" s="1" t="d">
-        <v>2026-07-21T08:15:57.000Z</v>
+        <v>2026-07-21T08:43:11.000Z</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>INC000000153052</v>
+        <v>WO0000000309945</v>
       </c>
       <c r="B766" s="1" t="d">
-        <v>2026-07-21T08:36:23.999Z</v>
+        <v>2026-07-21T08:19:14.999Z</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>WO0000000309862</v>
+        <v>WO0000000309946</v>
       </c>
       <c r="B767" s="1" t="d">
-        <v>2026-07-21T07:21:46.000Z</v>
+        <v>2026-07-21T08:19:40.999Z</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>WO0000000309861</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B768" s="1" t="d">
-        <v>2026-07-21T15:13:04.000Z</v>
+        <v>2026-07-22T09:44:39.000Z</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>INC000000153062</v>
+        <v>INC000000153153</v>
       </c>
       <c r="B769" s="1" t="d">
-        <v>2026-07-21T10:38:36.000Z</v>
+        <v>2026-07-21T15:22:52.000Z</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>INC000000153143</v>
+        <v>WO0000000309949</v>
       </c>
       <c r="B770" s="1" t="d">
-        <v>2026-07-21T08:04:39.999Z</v>
+        <v>2026-07-21T09:47:21.999Z</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>WO0000000309880</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B771" s="1" t="d">
-        <v>2026-07-21T08:43:11.000Z</v>
+        <v>2026-07-21T12:13:26.000Z</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>WO0000000309945</v>
+        <v>WO0000000309892</v>
       </c>
       <c r="B772" s="1" t="d">
-        <v>2026-07-21T08:19:14.999Z</v>
+        <v>2026-07-21T09:04:46.000Z</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>WO0000000309946</v>
+        <v>WO0000000309954</v>
       </c>
       <c r="B773" s="1" t="d">
-        <v>2026-07-21T08:19:40.999Z</v>
+        <v>2026-07-21T08:40:01.000Z</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>INC000000153065</v>
+        <v>WO0000000310002</v>
       </c>
       <c r="B774" s="1" t="d">
-        <v>2026-07-22T09:44:39.000Z</v>
+        <v>2026-07-21T15:25:48.000Z</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>INC000000153153</v>
+        <v>WO0000000309957</v>
       </c>
       <c r="B775" s="1" t="d">
-        <v>2026-07-21T15:22:52.000Z</v>
+        <v>2026-07-21T15:56:24.000Z</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>WO0000000309949</v>
+        <v>WO0000000309958</v>
       </c>
       <c r="B776" s="1" t="d">
-        <v>2026-07-21T09:47:21.999Z</v>
+        <v>2026-07-21T08:54:45.000Z</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>WO0000000309953</v>
+        <v>WO0000000310004</v>
       </c>
       <c r="B777" s="1" t="d">
-        <v>2026-07-21T15:33:38.000Z</v>
+        <v>2026-07-21T15:28:12.000Z</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>INC000000153069</v>
+        <v>WO0000000309959</v>
       </c>
       <c r="B778" s="1" t="d">
-        <v>2026-07-21T12:13:26.000Z</v>
+        <v>2026-07-22T09:56:40.999Z</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>WO0000000309892</v>
+        <v>WO0000000310006</v>
       </c>
       <c r="B779" s="1" t="d">
-        <v>2026-07-21T09:04:46.000Z</v>
+        <v>2026-07-21T15:29:06.999Z</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>WO0000000309954</v>
+        <v>WO0000000309961</v>
       </c>
       <c r="B780" s="1" t="d">
-        <v>2026-07-21T08:40:01.000Z</v>
+        <v>2026-07-21T09:28:19.000Z</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>WO0000000310002</v>
+        <v>WO0000000310015</v>
       </c>
       <c r="B781" s="1" t="d">
-        <v>2026-07-21T15:25:48.000Z</v>
+        <v>2026-07-21T09:27:41.000Z</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>WO0000000309957</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B782" s="1" t="d">
-        <v>2026-07-21T15:56:24.000Z</v>
+        <v>2026-07-21T11:44:25.999Z</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>WO0000000309958</v>
+        <v>WO0000000310016</v>
       </c>
       <c r="B783" s="1" t="d">
-        <v>2026-07-21T08:54:45.000Z</v>
+        <v>2026-07-21T11:47:23.999Z</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>WO0000000310004</v>
+        <v>WO0000000310019</v>
       </c>
       <c r="B784" s="1" t="d">
-        <v>2026-07-21T15:28:12.000Z</v>
+        <v>2026-07-21T10:19:05.000Z</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>WO0000000309959</v>
+        <v>WO0000000309981</v>
       </c>
       <c r="B785" s="1" t="d">
-        <v>2026-07-21T11:27:26.000Z</v>
+        <v>2026-07-21T11:22:20.000Z</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>WO0000000310006</v>
+        <v>WO0000000310021</v>
       </c>
       <c r="B786" s="1" t="d">
-        <v>2026-07-21T15:29:06.999Z</v>
+        <v>2026-07-21T09:24:02.000Z</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>WO0000000309961</v>
+        <v>INC000000153174</v>
       </c>
       <c r="B787" s="1" t="d">
-        <v>2026-07-21T09:28:19.000Z</v>
+        <v>2026-07-21T14:40:04.000Z</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>WO0000000310015</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B788" s="1" t="d">
-        <v>2026-07-21T09:27:41.000Z</v>
+        <v>2026-07-21T15:06:30.000Z</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>INC000000153163</v>
+        <v>WO0000000309975</v>
       </c>
       <c r="B789" s="1" t="d">
-        <v>2026-07-21T11:44:25.999Z</v>
+        <v>2026-07-22T09:30:14.000Z</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>WO0000000310016</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B790" s="1" t="d">
-        <v>2026-07-21T11:47:23.999Z</v>
+        <v>2026-07-21T09:37:20.999Z</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>WO0000000310019</v>
+        <v>WO0000000310025</v>
       </c>
       <c r="B791" s="1" t="d">
-        <v>2026-07-21T10:19:05.000Z</v>
+        <v>2026-07-21T09:36:55.000Z</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>WO0000000309981</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B792" s="1" t="d">
-        <v>2026-07-21T11:22:20.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>WO0000000310021</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B793" s="1" t="d">
-        <v>2026-07-21T09:24:02.000Z</v>
+        <v>2026-07-21T09:40:19.000Z</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>INC000000153174</v>
+        <v>INC000000153181</v>
       </c>
       <c r="B794" s="1" t="d">
-        <v>2026-07-21T14:40:04.000Z</v>
+        <v>2026-07-21T09:48:10.999Z</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>WO0000000309985</v>
+        <v>WO0000000309993</v>
       </c>
       <c r="B795" s="1" t="d">
-        <v>2026-07-21T15:06:30.000Z</v>
+        <v>2026-07-22T09:42:27.000Z</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>WO0000000309975</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B796" s="1" t="d">
-        <v>2026-07-22T09:30:14.000Z</v>
+        <v>2026-07-21T09:41:54.000Z</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>WO0000000309990</v>
+        <v>INC000000153082</v>
       </c>
       <c r="B797" s="1" t="d">
-        <v>2026-07-21T09:37:20.999Z</v>
+        <v>2026-07-22T09:55:53.000Z</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>WO0000000310025</v>
+        <v>INC000000153179</v>
       </c>
       <c r="B798" s="1" t="d">
-        <v>2026-07-21T09:36:55.000Z</v>
+        <v>2026-07-22T08:51:46.000Z</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000309997</v>
       </c>
       <c r="B799" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T11:45:35.000Z</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000309998</v>
       </c>
       <c r="B800" s="1" t="d">
-        <v>2026-07-21T09:40:19.000Z</v>
+        <v>2026-07-21T09:47:07.999Z</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>INC000000153181</v>
+        <v>INC000000153182</v>
       </c>
       <c r="B801" s="1" t="d">
-        <v>2026-07-21T09:48:10.999Z</v>
+        <v>2026-07-21T10:35:39.000Z</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>WO0000000309993</v>
+        <v>WO0000000310000</v>
       </c>
       <c r="B802" s="1" t="d">
-        <v>2026-07-22T09:42:27.000Z</v>
+        <v>2026-07-22T10:02:54.000Z</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000309999</v>
       </c>
       <c r="B803" s="1" t="d">
-        <v>2026-07-21T09:41:54.000Z</v>
+        <v>2026-07-21T09:50:29.000Z</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>INC000000153082</v>
+        <v>WO0000000310102</v>
       </c>
       <c r="B804" s="1" t="d">
-        <v>2026-07-21T10:22:17.000Z</v>
+        <v>2026-07-21T09:50:55.000Z</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>INC000000153179</v>
+        <v>WO0000000310033</v>
       </c>
       <c r="B805" s="1" t="d">
-        <v>2026-07-22T08:51:46.000Z</v>
+        <v>2026-07-21T09:51:00.000Z</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>WO0000000309997</v>
+        <v>WO0000000305268</v>
       </c>
       <c r="B806" s="1" t="d">
-        <v>2026-07-21T11:45:35.000Z</v>
+        <v>2026-07-21T09:55:25.000Z</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>WO0000000309998</v>
+        <v>WO0000000305269</v>
       </c>
       <c r="B807" s="1" t="d">
-        <v>2026-07-21T09:47:07.999Z</v>
+        <v>2026-07-21T16:30:36.000Z</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>INC000000153182</v>
+        <v>WO0000000310106</v>
       </c>
       <c r="B808" s="1" t="d">
-        <v>2026-07-21T10:35:39.000Z</v>
+        <v>2026-07-21T10:02:21.999Z</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>WO0000000310000</v>
+        <v>WO0000000310036</v>
       </c>
       <c r="B809" s="1" t="d">
-        <v>2026-07-22T09:55:11.999Z</v>
+        <v>2026-07-21T09:59:20.000Z</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>WO0000000309999</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B810" s="1" t="d">
-        <v>2026-07-21T09:50:29.000Z</v>
+        <v>2026-07-21T10:31:45.000Z</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>WO0000000310102</v>
+        <v>WO0000000310045</v>
       </c>
       <c r="B811" s="1" t="d">
-        <v>2026-07-21T09:50:55.000Z</v>
+        <v>2026-07-22T08:58:36.000Z</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>WO0000000310033</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B812" s="1" t="d">
-        <v>2026-07-21T09:51:00.000Z</v>
+        <v>2026-07-21T11:44:30.999Z</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>WO0000000305268</v>
+        <v>WO0000000310114</v>
       </c>
       <c r="B813" s="1" t="d">
-        <v>2026-07-21T09:55:25.000Z</v>
+        <v>2026-07-21T10:12:20.000Z</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>WO0000000305269</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B814" s="1" t="d">
-        <v>2026-07-21T16:30:36.000Z</v>
+        <v>2026-07-21T15:54:47.999Z</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>WO0000000310106</v>
+        <v>WO0000000310046</v>
       </c>
       <c r="B815" s="1" t="d">
-        <v>2026-07-21T10:02:21.999Z</v>
+        <v>2026-07-21T10:13:36.000Z</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>WO0000000310036</v>
+        <v>WO0000000310047</v>
       </c>
       <c r="B816" s="1" t="d">
-        <v>2026-07-21T09:59:20.000Z</v>
+        <v>2026-07-21T10:14:06.000Z</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310118</v>
       </c>
       <c r="B817" s="1" t="d">
-        <v>2026-07-21T10:31:45.000Z</v>
+        <v>2026-07-21T10:29:50.999Z</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>WO0000000310045</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B818" s="1" t="d">
-        <v>2026-07-22T08:58:36.000Z</v>
+        <v>2026-07-21T16:09:03.000Z</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310049</v>
       </c>
       <c r="B819" s="1" t="d">
-        <v>2026-07-21T11:44:30.999Z</v>
+        <v>2026-07-21T10:20:08.000Z</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>WO0000000310114</v>
+        <v>WO0000000310051</v>
       </c>
       <c r="B820" s="1" t="d">
-        <v>2026-07-21T10:12:20.000Z</v>
+        <v>2026-07-21T10:23:58.000Z</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>INC000000153093</v>
+        <v>WO0000000310120</v>
       </c>
       <c r="B821" s="1" t="d">
-        <v>2026-07-21T15:54:47.999Z</v>
+        <v>2026-07-21T10:35:25.000Z</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>WO0000000310046</v>
+        <v>WO0000000310053</v>
       </c>
       <c r="B822" s="1" t="d">
-        <v>2026-07-21T10:13:36.000Z</v>
+        <v>2026-07-21T10:27:39.999Z</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>WO0000000310047</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B823" s="1" t="d">
-        <v>2026-07-21T10:14:06.000Z</v>
+        <v>2026-07-21T13:42:39.999Z</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>WO0000000310118</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B824" s="1" t="d">
-        <v>2026-07-21T10:29:50.999Z</v>
+        <v>2026-07-21T20:55:08.999Z</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>INC000000153092</v>
+        <v>WO0000000310123</v>
       </c>
       <c r="B825" s="1" t="d">
-        <v>2026-07-21T16:09:03.000Z</v>
+        <v>2026-07-21T10:36:47.999Z</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>WO0000000310049</v>
+        <v>WO0000000310055</v>
       </c>
       <c r="B826" s="1" t="d">
-        <v>2026-07-21T10:20:08.000Z</v>
+        <v>2026-07-21T11:51:43.999Z</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>WO0000000310051</v>
+        <v>WO0000000310127</v>
       </c>
       <c r="B827" s="1" t="d">
-        <v>2026-07-21T10:23:58.000Z</v>
+        <v>2026-07-22T08:42:13.999Z</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>WO0000000310120</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B828" s="1" t="d">
-        <v>2026-07-21T10:35:25.000Z</v>
+        <v>2026-07-21T10:46:52.000Z</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>WO0000000310053</v>
+        <v>WO0000000310061</v>
       </c>
       <c r="B829" s="1" t="d">
-        <v>2026-07-21T10:27:39.999Z</v>
+        <v>2026-07-21T23:22:22.000Z</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>INC000000153195</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B830" s="1" t="d">
-        <v>2026-07-21T13:42:39.999Z</v>
+        <v>2026-07-21T18:21:06.000Z</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>INC000000153196</v>
+        <v>WO0000000310135</v>
       </c>
       <c r="B831" s="1" t="d">
-        <v>2026-07-21T20:55:08.999Z</v>
+        <v>2026-07-21T10:51:40.000Z</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>INC000000153201</v>
+        <v>WO0000000310136</v>
       </c>
       <c r="B832" s="1" t="d">
-        <v>2026-07-22T09:50:24.000Z</v>
+        <v>2026-07-21T15:04:13.000Z</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>WO0000000310123</v>
+        <v>WO0000000310065</v>
       </c>
       <c r="B833" s="1" t="d">
-        <v>2026-07-21T10:36:47.999Z</v>
+        <v>2026-07-21T16:12:37.000Z</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>WO0000000310055</v>
+        <v>WO0000000310066</v>
       </c>
       <c r="B834" s="1" t="d">
-        <v>2026-07-21T11:51:43.999Z</v>
+        <v>2026-07-21T15:16:35.000Z</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>WO0000000310127</v>
+        <v>WO0000000310069</v>
       </c>
       <c r="B835" s="1" t="d">
-        <v>2026-07-22T08:42:13.999Z</v>
+        <v>2026-07-21T11:40:34.000Z</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310144</v>
       </c>
       <c r="B836" s="1" t="d">
-        <v>2026-07-21T10:46:52.000Z</v>
+        <v>2026-07-21T11:06:24.000Z</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>WO0000000310061</v>
+        <v>WO0000000310145</v>
       </c>
       <c r="B837" s="1" t="d">
-        <v>2026-07-21T23:22:22.000Z</v>
+        <v>2026-07-21T11:44:29.999Z</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>INC000000153206</v>
+        <v>INC000000153306</v>
       </c>
       <c r="B838" s="1" t="d">
-        <v>2026-07-21T18:21:06.000Z</v>
+        <v>2026-07-21T12:03:12.000Z</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>WO0000000310135</v>
+        <v>WO0000000310143</v>
       </c>
       <c r="B839" s="1" t="d">
-        <v>2026-07-21T10:51:40.000Z</v>
+        <v>2026-07-21T11:08:15.000Z</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>WO0000000310136</v>
+        <v>WO0000000310147</v>
       </c>
       <c r="B840" s="1" t="d">
-        <v>2026-07-21T15:04:13.000Z</v>
+        <v>2026-07-21T11:11:37.999Z</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>WO0000000310065</v>
+        <v>WO0000000310070</v>
       </c>
       <c r="B841" s="1" t="d">
-        <v>2026-07-21T16:12:37.000Z</v>
+        <v>2026-07-21T14:40:42.000Z</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>WO0000000310066</v>
+        <v>WO0000000310078</v>
       </c>
       <c r="B842" s="1" t="d">
-        <v>2026-07-21T15:16:35.000Z</v>
+        <v>2026-07-21T17:48:37.000Z</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>WO0000000310069</v>
+        <v>WO0000000310079</v>
       </c>
       <c r="B843" s="1" t="d">
-        <v>2026-07-21T11:40:34.000Z</v>
+        <v>2026-07-22T09:11:31.000Z</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>WO0000000310144</v>
+        <v>WO0000000310082</v>
       </c>
       <c r="B844" s="1" t="d">
-        <v>2026-07-21T11:06:24.000Z</v>
+        <v>2026-07-21T11:21:29.000Z</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>WO0000000310145</v>
+        <v>WO0000000310157</v>
       </c>
       <c r="B845" s="1" t="d">
-        <v>2026-07-21T11:44:29.999Z</v>
+        <v>2026-07-21T11:45:08.999Z</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>INC000000153306</v>
+        <v>WO0000000310160</v>
       </c>
       <c r="B846" s="1" t="d">
-        <v>2026-07-21T12:03:12.000Z</v>
+        <v>2026-07-21T11:27:58.000Z</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>WO0000000310143</v>
+        <v>WO0000000310161</v>
       </c>
       <c r="B847" s="1" t="d">
-        <v>2026-07-21T11:08:15.000Z</v>
+        <v>2026-07-21T11:25:35.000Z</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>WO0000000310147</v>
+        <v>WO0000000310076</v>
       </c>
       <c r="B848" s="1" t="d">
-        <v>2026-07-21T11:11:37.999Z</v>
+        <v>2026-07-21T12:27:55.000Z</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>WO0000000310070</v>
+        <v>WO0000000310087</v>
       </c>
       <c r="B849" s="1" t="d">
-        <v>2026-07-21T14:40:42.000Z</v>
+        <v>2026-07-21T12:41:20.000Z</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>WO0000000310078</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B850" s="1" t="d">
-        <v>2026-07-21T17:48:37.000Z</v>
+        <v>2026-07-21T16:18:46.999Z</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>WO0000000310079</v>
+        <v>INC000000153224</v>
       </c>
       <c r="B851" s="1" t="d">
-        <v>2026-07-22T09:11:31.000Z</v>
+        <v>2026-07-21T13:20:41.000Z</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>WO0000000310082</v>
+        <v>WO0000000310092</v>
       </c>
       <c r="B852" s="1" t="d">
-        <v>2026-07-21T11:21:29.000Z</v>
+        <v>2026-07-21T11:41:17.000Z</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>WO0000000310157</v>
+        <v>WO0000000310173</v>
       </c>
       <c r="B853" s="1" t="d">
-        <v>2026-07-21T11:45:08.999Z</v>
+        <v>2026-07-21T12:23:28.000Z</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>WO0000000310160</v>
+        <v>WO0000000310146</v>
       </c>
       <c r="B854" s="1" t="d">
-        <v>2026-07-21T11:27:58.000Z</v>
+        <v>2026-07-21T11:50:49.000Z</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>WO0000000310161</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B855" s="1" t="d">
-        <v>2026-07-21T11:25:35.000Z</v>
+        <v>2026-07-21T12:56:25.000Z</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>WO0000000310076</v>
+        <v>WO0000000310095</v>
       </c>
       <c r="B856" s="1" t="d">
-        <v>2026-07-21T12:27:55.000Z</v>
+        <v>2026-07-22T09:50:34.000Z</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>WO0000000310087</v>
+        <v>WO0000000310171</v>
       </c>
       <c r="B857" s="1" t="d">
-        <v>2026-07-21T12:41:20.000Z</v>
+        <v>2026-07-21T15:53:05.000Z</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>WO0000000310164</v>
+        <v>WO0000000310178</v>
       </c>
       <c r="B858" s="1" t="d">
-        <v>2026-07-21T16:18:46.999Z</v>
+        <v>2026-07-21T15:20:09.000Z</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>INC000000153224</v>
+        <v>WO0000000310098</v>
       </c>
       <c r="B859" s="1" t="d">
-        <v>2026-07-21T13:20:41.000Z</v>
+        <v>2026-07-21T14:10:01.000Z</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>WO0000000310092</v>
+        <v>INC000000153322</v>
       </c>
       <c r="B860" s="1" t="d">
-        <v>2026-07-21T11:41:17.000Z</v>
+        <v>2026-07-21T15:32:25.000Z</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>WO0000000310173</v>
+        <v>INC000000153232</v>
       </c>
       <c r="B861" s="1" t="d">
-        <v>2026-07-21T12:23:28.000Z</v>
+        <v>2026-07-21T12:02:12.999Z</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>WO0000000310146</v>
+        <v>INC000000153323</v>
       </c>
       <c r="B862" s="1" t="d">
-        <v>2026-07-21T11:50:49.000Z</v>
+        <v>2026-07-21T12:13:51.000Z</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>INC000000153226</v>
+        <v>WO0000000310179</v>
       </c>
       <c r="B863" s="1" t="d">
-        <v>2026-07-21T12:56:25.000Z</v>
+        <v>2026-07-21T17:16:41.999Z</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>WO0000000310095</v>
+        <v>WO0000000310202</v>
       </c>
       <c r="B864" s="1" t="d">
-        <v>2026-07-22T09:50:34.000Z</v>
+        <v>2026-07-21T12:04:50.000Z</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>WO0000000310171</v>
+        <v>WO0000000310180</v>
       </c>
       <c r="B865" s="1" t="d">
-        <v>2026-07-21T15:53:05.000Z</v>
+        <v>2026-07-21T12:00:37.000Z</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>WO0000000310178</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B866" s="1" t="d">
-        <v>2026-07-21T15:20:09.000Z</v>
+        <v>2026-07-22T08:20:31.999Z</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>WO0000000310098</v>
+        <v>WO0000000310181</v>
       </c>
       <c r="B867" s="1" t="d">
-        <v>2026-07-21T14:10:01.000Z</v>
+        <v>2026-07-21T12:18:59.000Z</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>INC000000153322</v>
+        <v>INC000000153319</v>
       </c>
       <c r="B868" s="1" t="d">
-        <v>2026-07-21T15:32:25.000Z</v>
+        <v>2026-07-21T12:06:50.999Z</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>INC000000153232</v>
+        <v>WO0000000310204</v>
       </c>
       <c r="B869" s="1" t="d">
-        <v>2026-07-21T12:02:12.999Z</v>
+        <v>2026-07-21T12:52:00.999Z</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>INC000000153323</v>
+        <v>WO0000000310182</v>
       </c>
       <c r="B870" s="1" t="d">
-        <v>2026-07-21T12:13:51.000Z</v>
+        <v>2026-07-21T14:10:32.000Z</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>WO0000000310179</v>
+        <v>WO0000000310208</v>
       </c>
       <c r="B871" s="1" t="d">
-        <v>2026-07-21T17:16:41.999Z</v>
+        <v>2026-07-21T16:00:45.000Z</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>WO0000000310202</v>
+        <v>INC000000153332</v>
       </c>
       <c r="B872" s="1" t="d">
-        <v>2026-07-21T12:04:50.000Z</v>
+        <v>2026-07-21T13:57:51.999Z</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>WO0000000310180</v>
+        <v>INC000000153235</v>
       </c>
       <c r="B873" s="1" t="d">
-        <v>2026-07-21T12:00:37.000Z</v>
+        <v>2026-07-22T09:43:50.000Z</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310207</v>
       </c>
       <c r="B874" s="1" t="d">
-        <v>2026-07-22T08:20:31.999Z</v>
+        <v>2026-07-21T12:19:01.999Z</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>WO0000000310181</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B875" s="1" t="d">
-        <v>2026-07-21T12:18:59.000Z</v>
+        <v>2026-07-21T16:27:35.000Z</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>INC000000153319</v>
+        <v>WO0000000310192</v>
       </c>
       <c r="B876" s="1" t="d">
-        <v>2026-07-21T12:06:50.999Z</v>
+        <v>2026-07-21T13:13:38.999Z</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>WO0000000310204</v>
+        <v>INC000000153237</v>
       </c>
       <c r="B877" s="1" t="d">
-        <v>2026-07-21T12:52:00.999Z</v>
+        <v>2026-07-22T09:03:20.999Z</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>WO0000000310182</v>
+        <v>WO0000000310193</v>
       </c>
       <c r="B878" s="1" t="d">
-        <v>2026-07-21T14:10:32.000Z</v>
+        <v>2026-07-21T12:33:26.000Z</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>WO0000000310208</v>
+        <v>INC000000153340</v>
       </c>
       <c r="B879" s="1" t="d">
-        <v>2026-07-21T16:00:45.000Z</v>
+        <v>2026-07-21T14:30:28.000Z</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>INC000000153332</v>
+        <v>WO0000000310213</v>
       </c>
       <c r="B880" s="1" t="d">
-        <v>2026-07-21T13:57:51.999Z</v>
+        <v>2026-07-21T14:03:25.000Z</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>INC000000153235</v>
+        <v>WO0000000310214</v>
       </c>
       <c r="B881" s="1" t="d">
-        <v>2026-07-22T09:43:50.000Z</v>
+        <v>2026-07-21T13:12:50.000Z</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>WO0000000310207</v>
+        <v>INC000000153342</v>
       </c>
       <c r="B882" s="1" t="d">
-        <v>2026-07-21T12:19:01.999Z</v>
+        <v>2026-07-21T13:57:08.000Z</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>INC000000153335</v>
+        <v>WO0000000310195</v>
       </c>
       <c r="B883" s="1" t="d">
-        <v>2026-07-21T16:27:35.000Z</v>
+        <v>2026-07-21T13:11:13.000Z</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>WO0000000310192</v>
+        <v>WO0000000310217</v>
       </c>
       <c r="B884" s="1" t="d">
-        <v>2026-07-21T13:13:38.999Z</v>
+        <v>2026-07-22T08:11:20.000Z</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>INC000000153237</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B885" s="1" t="d">
-        <v>2026-07-22T09:03:20.999Z</v>
+        <v>2026-07-21T13:39:49.000Z</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>WO0000000310193</v>
+        <v>WO0000000310215</v>
       </c>
       <c r="B886" s="1" t="d">
-        <v>2026-07-21T12:33:26.000Z</v>
+        <v>2026-07-21T12:51:50.999Z</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>INC000000153340</v>
+        <v>WO0000000310218</v>
       </c>
       <c r="B887" s="1" t="d">
-        <v>2026-07-21T14:30:28.000Z</v>
+        <v>2026-07-21T12:42:44.000Z</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>WO0000000310213</v>
+        <v>WO0000000310198</v>
       </c>
       <c r="B888" s="1" t="d">
-        <v>2026-07-21T14:03:25.000Z</v>
+        <v>2026-07-21T12:43:18.000Z</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>WO0000000310214</v>
+        <v>WO0000000310199</v>
       </c>
       <c r="B889" s="1" t="d">
-        <v>2026-07-21T13:12:50.000Z</v>
+        <v>2026-07-21T12:44:20.000Z</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>INC000000153342</v>
+        <v>WO0000000310200</v>
       </c>
       <c r="B890" s="1" t="d">
-        <v>2026-07-21T13:57:08.000Z</v>
+        <v>2026-07-21T12:53:42.000Z</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>WO0000000310195</v>
+        <v>INC000000153343</v>
       </c>
       <c r="B891" s="1" t="d">
-        <v>2026-07-21T13:11:13.000Z</v>
+        <v>2026-07-21T17:09:54.999Z</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>WO0000000310217</v>
+        <v>INC000000153241</v>
       </c>
       <c r="B892" s="1" t="d">
-        <v>2026-07-22T08:11:20.000Z</v>
+        <v>2026-07-21T15:30:45.000Z</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>INC000000153344</v>
+        <v>WO0000000310303</v>
       </c>
       <c r="B893" s="1" t="d">
-        <v>2026-07-21T13:39:49.000Z</v>
+        <v>2026-07-22T08:29:29.999Z</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>WO0000000310215</v>
+        <v>WO0000000310224</v>
       </c>
       <c r="B894" s="1" t="d">
-        <v>2026-07-21T12:51:50.999Z</v>
+        <v>2026-07-21T13:06:20.000Z</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>WO0000000310218</v>
+        <v>WO0000000310305</v>
       </c>
       <c r="B895" s="1" t="d">
-        <v>2026-07-21T12:42:44.000Z</v>
+        <v>2026-07-21T13:01:00.000Z</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>WO0000000310198</v>
+        <v>INC000000153346</v>
       </c>
       <c r="B896" s="1" t="d">
-        <v>2026-07-21T12:43:18.000Z</v>
+        <v>2026-07-21T17:02:06.000Z</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>WO0000000310199</v>
+        <v>INC000000153347</v>
       </c>
       <c r="B897" s="1" t="d">
-        <v>2026-07-21T12:44:20.000Z</v>
+        <v>2026-07-21T15:22:02.000Z</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>WO0000000310200</v>
+        <v>WO0000000310314</v>
       </c>
       <c r="B898" s="1" t="d">
-        <v>2026-07-21T12:53:42.000Z</v>
+        <v>2026-07-21T13:20:57.999Z</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>INC000000153343</v>
+        <v>INC000000153248</v>
       </c>
       <c r="B899" s="1" t="d">
-        <v>2026-07-21T17:09:54.999Z</v>
+        <v>2026-07-21T15:43:27.000Z</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>INC000000153241</v>
+        <v>WO0000000305270</v>
       </c>
       <c r="B900" s="1" t="d">
-        <v>2026-07-21T15:30:45.000Z</v>
+        <v>2026-07-21T13:24:28.999Z</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>WO0000000310303</v>
+        <v>WO0000000310316</v>
       </c>
       <c r="B901" s="1" t="d">
-        <v>2026-07-22T08:29:29.999Z</v>
+        <v>2026-07-22T10:03:55.000Z</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>WO0000000310224</v>
+        <v>WO0000000310317</v>
       </c>
       <c r="B902" s="1" t="d">
-        <v>2026-07-21T13:06:20.000Z</v>
+        <v>2026-07-21T13:34:35.999Z</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>WO0000000310305</v>
+        <v>WO0000000310320</v>
       </c>
       <c r="B903" s="1" t="d">
-        <v>2026-07-21T13:01:00.000Z</v>
+        <v>2026-07-21T13:43:30.000Z</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>INC000000153346</v>
+        <v>WO0000000310231</v>
       </c>
       <c r="B904" s="1" t="d">
-        <v>2026-07-21T17:02:06.000Z</v>
+        <v>2026-07-21T13:45:42.999Z</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>INC000000153347</v>
+        <v>INC000000153352</v>
       </c>
       <c r="B905" s="1" t="d">
-        <v>2026-07-21T15:22:02.000Z</v>
+        <v>2026-07-21T14:29:53.000Z</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>WO0000000310314</v>
+        <v>WO0000000305271</v>
       </c>
       <c r="B906" s="1" t="d">
-        <v>2026-07-21T13:20:57.999Z</v>
+        <v>2026-07-22T08:56:41.000Z</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>INC000000153248</v>
+        <v>WO0000000305272</v>
       </c>
       <c r="B907" s="1" t="d">
-        <v>2026-07-21T15:43:27.000Z</v>
+        <v>2026-07-21T14:30:16.999Z</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>WO0000000305270</v>
+        <v>INC000000153353</v>
       </c>
       <c r="B908" s="1" t="d">
-        <v>2026-07-21T13:24:28.999Z</v>
+        <v>2026-07-22T07:45:45.000Z</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>WO0000000310316</v>
+        <v>WO0000000310325</v>
       </c>
       <c r="B909" s="1" t="d">
-        <v>2026-07-21T16:40:32.000Z</v>
+        <v>2026-07-22T08:34:20.999Z</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>WO0000000310317</v>
+        <v>WO0000000310236</v>
       </c>
       <c r="B910" s="1" t="d">
-        <v>2026-07-21T13:34:35.999Z</v>
+        <v>2026-07-21T14:04:48.999Z</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>WO0000000310320</v>
+        <v>WO0000000310327</v>
       </c>
       <c r="B911" s="1" t="d">
-        <v>2026-07-21T13:43:30.000Z</v>
+        <v>2026-07-21T14:08:12.999Z</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>WO0000000310231</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B912" s="1" t="d">
-        <v>2026-07-21T13:45:42.999Z</v>
+        <v>2026-07-21T15:07:23.000Z</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>INC000000153352</v>
+        <v>WO0000000309312</v>
       </c>
       <c r="B913" s="1" t="d">
-        <v>2026-07-21T14:29:53.000Z</v>
+        <v>2026-07-21T14:09:08.000Z</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>WO0000000305271</v>
+        <v>WO0000000309313</v>
       </c>
       <c r="B914" s="1" t="d">
-        <v>2026-07-22T08:56:41.000Z</v>
+        <v>2026-07-21T14:09:18.000Z</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>WO0000000305272</v>
+        <v>WO0000000305274</v>
       </c>
       <c r="B915" s="1" t="d">
-        <v>2026-07-21T14:30:16.999Z</v>
+        <v>2026-07-21T14:09:28.999Z</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>INC000000153353</v>
+        <v>INC000000153354</v>
       </c>
       <c r="B916" s="1" t="d">
-        <v>2026-07-22T07:45:45.000Z</v>
+        <v>2026-07-21T14:48:30.000Z</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>WO0000000310325</v>
+        <v>WO0000000305276</v>
       </c>
       <c r="B917" s="1" t="d">
-        <v>2026-07-22T08:34:20.999Z</v>
+        <v>2026-07-21T15:52:57.000Z</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>WO0000000310236</v>
+        <v>WO0000000310237</v>
       </c>
       <c r="B918" s="1" t="d">
-        <v>2026-07-21T14:04:48.999Z</v>
+        <v>2026-07-21T14:11:40.000Z</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>WO0000000310327</v>
+        <v>WO0000000310238</v>
       </c>
       <c r="B919" s="1" t="d">
-        <v>2026-07-21T14:08:12.999Z</v>
+        <v>2026-07-21T14:13:45.000Z</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310326</v>
       </c>
       <c r="B920" s="1" t="d">
-        <v>2026-07-21T15:07:23.000Z</v>
+        <v>2026-07-21T14:17:53.999Z</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>WO0000000309312</v>
+        <v>WO0000000310239</v>
       </c>
       <c r="B921" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-22T09:50:34.000Z</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>WO0000000309313</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B922" s="1" t="d">
-        <v>2026-07-21T14:09:18.000Z</v>
+        <v>2026-07-21T17:01:11.000Z</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>WO0000000305274</v>
+        <v>WO0000000310242</v>
       </c>
       <c r="B923" s="1" t="d">
-        <v>2026-07-21T14:09:28.999Z</v>
+        <v>2026-07-22T06:16:26.000Z</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>INC000000153354</v>
+        <v>WO0000000310244</v>
       </c>
       <c r="B924" s="1" t="d">
-        <v>2026-07-21T14:48:30.000Z</v>
+        <v>2026-07-22T09:50:04.000Z</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>WO0000000305276</v>
+        <v>WO0000000310247</v>
       </c>
       <c r="B925" s="1" t="d">
-        <v>2026-07-21T15:52:57.000Z</v>
+        <v>2026-07-21T16:18:26.000Z</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>WO0000000310237</v>
+        <v>INC000000153256</v>
       </c>
       <c r="B926" s="1" t="d">
-        <v>2026-07-21T14:11:40.000Z</v>
+        <v>2026-07-21T15:08:16.999Z</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>WO0000000310238</v>
+        <v>WO0000000310345</v>
       </c>
       <c r="B927" s="1" t="d">
-        <v>2026-07-21T14:13:45.000Z</v>
+        <v>2026-07-21T16:14:23.000Z</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>WO0000000310326</v>
+        <v>INC000000153363</v>
       </c>
       <c r="B928" s="1" t="d">
-        <v>2026-07-21T14:17:53.999Z</v>
+        <v>2026-07-21T15:14:31.000Z</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>WO0000000310239</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B929" s="1" t="d">
-        <v>2026-07-22T09:50:34.000Z</v>
+        <v>2026-07-21T14:56:31.999Z</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>WO0000000310240</v>
+        <v>INC000000153367</v>
       </c>
       <c r="B930" s="1" t="d">
-        <v>2026-07-21T17:01:11.000Z</v>
+        <v>2026-07-21T18:10:11.999Z</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>WO0000000310242</v>
+        <v>WO0000000310348</v>
       </c>
       <c r="B931" s="1" t="d">
-        <v>2026-07-22T06:16:26.000Z</v>
+        <v>2026-07-21T14:55:19.000Z</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>WO0000000310244</v>
+        <v>INC000000153368</v>
       </c>
       <c r="B932" s="1" t="d">
-        <v>2026-07-22T09:50:04.000Z</v>
+        <v>2026-07-21T15:22:41.000Z</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>WO0000000310247</v>
+        <v>WO0000000305277</v>
       </c>
       <c r="B933" s="1" t="d">
-        <v>2026-07-21T16:18:26.000Z</v>
+        <v>2026-07-21T14:59:08.000Z</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>INC000000153256</v>
+        <v>WO0000000310246</v>
       </c>
       <c r="B934" s="1" t="d">
-        <v>2026-07-21T15:08:16.999Z</v>
+        <v>2026-07-21T16:06:31.000Z</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>WO0000000310250</v>
+        <v>WO0000000310350</v>
       </c>
       <c r="B935" s="1" t="d">
-        <v>2026-07-21T14:39:36.000Z</v>
+        <v>2026-07-21T15:00:50.000Z</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>WO0000000310342</v>
+        <v>INC000000153365</v>
       </c>
       <c r="B936" s="1" t="d">
-        <v>2026-07-21T14:43:32.000Z</v>
+        <v>2026-07-21T15:21:23.999Z</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>WO0000000310345</v>
+        <v>INC000000153369</v>
       </c>
       <c r="B937" s="1" t="d">
-        <v>2026-07-21T16:14:23.000Z</v>
+        <v>2026-07-21T16:08:53.000Z</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>INC000000153363</v>
+        <v>INC000000153370</v>
       </c>
       <c r="B938" s="1" t="d">
-        <v>2026-07-21T15:14:31.000Z</v>
+        <v>2026-07-21T15:53:24.000Z</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310357</v>
       </c>
       <c r="B939" s="1" t="d">
-        <v>2026-07-21T14:56:31.999Z</v>
+        <v>2026-07-21T15:05:01.000Z</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>INC000000153367</v>
+        <v>WO0000000310356</v>
       </c>
       <c r="B940" s="1" t="d">
-        <v>2026-07-21T18:10:11.999Z</v>
+        <v>2026-07-21T16:13:26.999Z</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>WO0000000310348</v>
+        <v>INC000000153372</v>
       </c>
       <c r="B941" s="1" t="d">
-        <v>2026-07-21T14:55:19.000Z</v>
+        <v>2026-07-21T17:10:32.999Z</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>INC000000153368</v>
+        <v>WO0000000310363</v>
       </c>
       <c r="B942" s="1" t="d">
-        <v>2026-07-21T15:22:41.000Z</v>
+        <v>2026-07-21T15:15:23.000Z</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>WO0000000305277</v>
+        <v>WO0000000310258</v>
       </c>
       <c r="B943" s="1" t="d">
-        <v>2026-07-21T14:59:08.000Z</v>
+        <v>2026-07-21T15:15:49.000Z</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>WO0000000310246</v>
+        <v>WO0000000310260</v>
       </c>
       <c r="B944" s="1" t="d">
-        <v>2026-07-21T16:06:31.000Z</v>
+        <v>2026-07-21T15:16:15.000Z</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>WO0000000310350</v>
+        <v>WO0000000310366</v>
       </c>
       <c r="B945" s="1" t="d">
-        <v>2026-07-21T15:00:50.000Z</v>
+        <v>2026-07-22T10:02:50.000Z</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>INC000000153365</v>
+        <v>WO0000000310365</v>
       </c>
       <c r="B946" s="1" t="d">
-        <v>2026-07-21T15:21:23.999Z</v>
+        <v>2026-07-21T15:23:38.000Z</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>INC000000153369</v>
+        <v>WO0000000310367</v>
       </c>
       <c r="B947" s="1" t="d">
-        <v>2026-07-21T16:08:53.000Z</v>
+        <v>2026-07-22T08:54:30.999Z</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>INC000000153370</v>
+        <v>WO0000000310265</v>
       </c>
       <c r="B948" s="1" t="d">
-        <v>2026-07-21T15:53:24.000Z</v>
+        <v>2026-07-21T15:45:54.000Z</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>WO0000000310357</v>
+        <v>WO0000000310266</v>
       </c>
       <c r="B949" s="1" t="d">
-        <v>2026-07-21T15:05:01.000Z</v>
+        <v>2026-07-21T16:25:17.000Z</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>WO0000000310356</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B950" s="1" t="d">
-        <v>2026-07-21T16:13:26.999Z</v>
+        <v>2026-07-22T09:08:56.000Z</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>INC000000153372</v>
+        <v>WO0000000310267</v>
       </c>
       <c r="B951" s="1" t="d">
-        <v>2026-07-21T17:10:32.999Z</v>
+        <v>2026-07-21T15:44:10.000Z</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>WO0000000310363</v>
+        <v>WO0000000310374</v>
       </c>
       <c r="B952" s="1" t="d">
-        <v>2026-07-21T15:15:23.000Z</v>
+        <v>2026-07-22T06:31:19.000Z</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>WO0000000310258</v>
+        <v>WO0000000310268</v>
       </c>
       <c r="B953" s="1" t="d">
-        <v>2026-07-21T15:15:49.000Z</v>
+        <v>2026-07-21T18:53:18.000Z</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>WO0000000310260</v>
+        <v>INC000000153375</v>
       </c>
       <c r="B954" s="1" t="d">
-        <v>2026-07-21T15:16:15.000Z</v>
+        <v>2026-07-21T16:40:23.000Z</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>WO0000000310366</v>
+        <v>WO0000000310271</v>
       </c>
       <c r="B955" s="1" t="d">
-        <v>2026-07-22T09:52:40.000Z</v>
+        <v>2026-07-21T16:17:27.999Z</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>WO0000000310365</v>
+        <v>WO0000000310272</v>
       </c>
       <c r="B956" s="1" t="d">
-        <v>2026-07-21T15:23:38.000Z</v>
+        <v>2026-07-21T15:41:09.000Z</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>WO0000000310367</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B957" s="1" t="d">
-        <v>2026-07-22T08:54:30.999Z</v>
+        <v>2026-07-21T19:03:59.000Z</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>WO0000000310265</v>
+        <v>INC000000153377</v>
       </c>
       <c r="B958" s="1" t="d">
-        <v>2026-07-21T15:45:54.000Z</v>
+        <v>2026-07-22T09:36:10.000Z</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>WO0000000310266</v>
+        <v>WO0000000310276</v>
       </c>
       <c r="B959" s="1" t="d">
-        <v>2026-07-21T16:25:17.000Z</v>
+        <v>2026-07-21T16:27:22.999Z</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>WO0000000310368</v>
+        <v>INC000000153376</v>
       </c>
       <c r="B960" s="1" t="d">
-        <v>2026-07-22T08:53:03.000Z</v>
+        <v>2026-07-22T08:11:07.000Z</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000310279</v>
       </c>
       <c r="B961" s="1" t="d">
-        <v>2026-07-22T09:08:56.000Z</v>
+        <v>2026-07-21T15:44:54.000Z</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>WO0000000310267</v>
+        <v>WO0000000310280</v>
       </c>
       <c r="B962" s="1" t="d">
-        <v>2026-07-21T15:44:10.000Z</v>
+        <v>2026-07-21T15:49:22.999Z</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>WO0000000310374</v>
+        <v>WO0000000310282</v>
       </c>
       <c r="B963" s="1" t="d">
-        <v>2026-07-22T06:31:19.000Z</v>
+        <v>2026-07-21T15:51:25.000Z</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>WO0000000310268</v>
+        <v>WO0000000310283</v>
       </c>
       <c r="B964" s="1" t="d">
-        <v>2026-07-21T18:53:18.000Z</v>
+        <v>2026-07-22T08:27:07.999Z</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>INC000000153375</v>
+        <v>INC000000153259</v>
       </c>
       <c r="B965" s="1" t="d">
-        <v>2026-07-21T16:40:23.000Z</v>
+        <v>2026-07-21T15:55:21.000Z</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>WO0000000310271</v>
+        <v>WO0000000305278</v>
       </c>
       <c r="B966" s="1" t="d">
-        <v>2026-07-21T16:17:27.999Z</v>
+        <v>2026-07-21T15:56:10.999Z</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>WO0000000310272</v>
+        <v>WO0000000310384</v>
       </c>
       <c r="B967" s="1" t="d">
-        <v>2026-07-21T15:41:09.000Z</v>
+        <v>2026-07-21T15:56:37.999Z</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>WO0000000310376</v>
+        <v>INC000000153261</v>
       </c>
       <c r="B968" s="1" t="d">
-        <v>2026-07-21T19:03:59.000Z</v>
+        <v>2026-07-21T15:57:54.000Z</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>INC000000153377</v>
+        <v>WO0000000310386</v>
       </c>
       <c r="B969" s="1" t="d">
-        <v>2026-07-22T09:36:10.000Z</v>
+        <v>2026-07-21T16:53:00.000Z</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>WO0000000310276</v>
+        <v>WO0000000310387</v>
       </c>
       <c r="B970" s="1" t="d">
-        <v>2026-07-21T16:27:22.999Z</v>
+        <v>2026-07-21T16:05:38.000Z</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>INC000000153376</v>
+        <v>WO0000000310289</v>
       </c>
       <c r="B971" s="1" t="d">
-        <v>2026-07-22T08:11:07.000Z</v>
+        <v>2026-07-21T16:03:05.999Z</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>WO0000000310279</v>
+        <v>WO0000000310390</v>
       </c>
       <c r="B972" s="1" t="d">
-        <v>2026-07-21T15:44:54.000Z</v>
+        <v>2026-07-21T16:04:24.000Z</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>WO0000000310280</v>
+        <v>INC000000153262</v>
       </c>
       <c r="B973" s="1" t="d">
-        <v>2026-07-21T15:49:22.999Z</v>
+        <v>2026-07-22T08:19:51.000Z</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>WO0000000310282</v>
+        <v>WO0000000310392</v>
       </c>
       <c r="B974" s="1" t="d">
-        <v>2026-07-21T15:51:25.000Z</v>
+        <v>2026-07-21T16:09:09.000Z</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>WO0000000310283</v>
+        <v>WO0000000310293</v>
       </c>
       <c r="B975" s="1" t="d">
-        <v>2026-07-22T08:27:07.999Z</v>
+        <v>2026-07-21T16:21:50.000Z</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>INC000000153259</v>
+        <v>WO0000000310292</v>
       </c>
       <c r="B976" s="1" t="d">
-        <v>2026-07-21T15:55:21.000Z</v>
+        <v>2026-07-21T16:24:33.000Z</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>WO0000000305278</v>
+        <v>INC000000153380</v>
       </c>
       <c r="B977" s="1" t="d">
-        <v>2026-07-21T15:56:10.999Z</v>
+        <v>2026-07-22T09:32:42.999Z</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>WO0000000310384</v>
+        <v>WO0000000310396</v>
       </c>
       <c r="B978" s="1" t="d">
-        <v>2026-07-21T15:56:37.999Z</v>
+        <v>2026-07-21T16:25:21.000Z</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>INC000000153261</v>
+        <v>INC000000153381</v>
       </c>
       <c r="B979" s="1" t="d">
-        <v>2026-07-21T15:57:54.000Z</v>
+        <v>2026-07-21T16:28:35.000Z</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>WO0000000310386</v>
+        <v>WO0000000310297</v>
       </c>
       <c r="B980" s="1" t="d">
-        <v>2026-07-21T16:53:00.000Z</v>
+        <v>2026-07-21T16:43:51.000Z</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>WO0000000310387</v>
+        <v>WO0000000305279</v>
       </c>
       <c r="B981" s="1" t="d">
-        <v>2026-07-21T16:05:38.000Z</v>
+        <v>2026-07-21T16:35:21.000Z</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>WO0000000310289</v>
+        <v>INC000000153382</v>
       </c>
       <c r="B982" s="1" t="d">
-        <v>2026-07-21T16:03:05.999Z</v>
+        <v>2026-07-22T07:45:47.000Z</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>WO0000000310390</v>
+        <v>INC000000153383</v>
       </c>
       <c r="B983" s="1" t="d">
-        <v>2026-07-21T16:04:24.000Z</v>
+        <v>2026-07-21T18:07:46.999Z</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>INC000000153262</v>
+        <v>WO0000000310403</v>
       </c>
       <c r="B984" s="1" t="d">
-        <v>2026-07-22T08:19:51.000Z</v>
+        <v>2026-07-21T16:51:45.000Z</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>WO0000000310392</v>
+        <v>WO0000000310404</v>
       </c>
       <c r="B985" s="1" t="d">
-        <v>2026-07-21T16:09:09.000Z</v>
+        <v>2026-07-22T09:56:47.000Z</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>WO0000000310293</v>
+        <v>WO0000000310408</v>
       </c>
       <c r="B986" s="1" t="d">
-        <v>2026-07-21T16:21:50.000Z</v>
+        <v>2026-07-21T17:58:11.000Z</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>WO0000000310292</v>
+        <v>INC000000153384</v>
       </c>
       <c r="B987" s="1" t="d">
-        <v>2026-07-21T16:24:33.000Z</v>
+        <v>2026-07-21T21:45:20.000Z</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>INC000000153380</v>
+        <v>WO0000000310501</v>
       </c>
       <c r="B988" s="1" t="d">
-        <v>2026-07-22T09:32:42.999Z</v>
+        <v>2026-07-21T16:48:31.000Z</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>WO0000000310396</v>
+        <v>WO0000000310411</v>
       </c>
       <c r="B989" s="1" t="d">
-        <v>2026-07-21T16:25:21.000Z</v>
+        <v>2026-07-21T17:01:37.999Z</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>INC000000153381</v>
+        <v>WO0000000310502</v>
       </c>
       <c r="B990" s="1" t="d">
-        <v>2026-07-21T16:28:35.000Z</v>
+        <v>2026-07-21T16:58:28.999Z</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>WO0000000310297</v>
+        <v>WO0000000310417</v>
       </c>
       <c r="B991" s="1" t="d">
-        <v>2026-07-21T16:43:51.000Z</v>
+        <v>2026-07-22T08:40:57.000Z</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>WO0000000305279</v>
+        <v>WO0000000310418</v>
       </c>
       <c r="B992" s="1" t="d">
-        <v>2026-07-21T16:35:21.000Z</v>
+        <v>2026-07-22T08:42:18.000Z</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>INC000000153382</v>
+        <v>WO0000000310420</v>
       </c>
       <c r="B993" s="1" t="d">
-        <v>2026-07-22T07:45:47.000Z</v>
+        <v>2026-07-21T16:57:24.999Z</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>INC000000153383</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B994" s="1" t="d">
-        <v>2026-07-21T18:07:46.999Z</v>
+        <v>2026-07-22T07:31:05.999Z</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>WO0000000310403</v>
+        <v>WO0000000310422</v>
       </c>
       <c r="B995" s="1" t="d">
-        <v>2026-07-21T16:51:45.000Z</v>
+        <v>2026-07-22T08:43:44.000Z</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>WO0000000310404</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B996" s="1" t="d">
-        <v>2026-07-22T08:36:02.999Z</v>
+        <v>2026-07-21T17:58:51.999Z</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>WO0000000310408</v>
+        <v>INC000000153266</v>
       </c>
       <c r="B997" s="1" t="d">
-        <v>2026-07-21T17:58:11.000Z</v>
+        <v>2026-07-22T09:42:57.000Z</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>INC000000153384</v>
+        <v>WO0000000310423</v>
       </c>
       <c r="B998" s="1" t="d">
-        <v>2026-07-21T21:45:20.000Z</v>
+        <v>2026-07-22T08:40:44.999Z</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>WO0000000310501</v>
+        <v>WO0000000310424</v>
       </c>
       <c r="B999" s="1" t="d">
-        <v>2026-07-21T16:48:31.000Z</v>
+        <v>2026-07-21T17:11:58.000Z</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>WO0000000310411</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B1000" s="1" t="d">
-        <v>2026-07-21T17:01:37.999Z</v>
+        <v>2026-07-21T18:17:03.000Z</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>WO0000000310502</v>
+        <v>WO0000000310426</v>
       </c>
       <c r="B1001" s="1" t="d">
-        <v>2026-07-21T16:58:28.999Z</v>
+        <v>2026-07-21T17:14:16.000Z</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>WO0000000310417</v>
+        <v>WO0000000310427</v>
       </c>
       <c r="B1002" s="1" t="d">
-        <v>2026-07-22T08:40:57.000Z</v>
+        <v>2026-07-21T17:15:07.000Z</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>WO0000000310418</v>
+        <v>INC000000153390</v>
       </c>
       <c r="B1003" s="1" t="d">
-        <v>2026-07-22T08:42:18.000Z</v>
+        <v>2026-07-22T08:03:11.000Z</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>WO0000000310420</v>
+        <v>WO0000000310430</v>
       </c>
       <c r="B1004" s="1" t="d">
-        <v>2026-07-21T16:57:24.999Z</v>
+        <v>2026-07-21T17:28:57.000Z</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>WO0000000310419</v>
+        <v>WO0000000310509</v>
       </c>
       <c r="B1005" s="1" t="d">
-        <v>2026-07-21T17:15:29.000Z</v>
+        <v>2026-07-21T18:19:46.000Z</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>INC000000153385</v>
+        <v>INC000000153391</v>
       </c>
       <c r="B1006" s="1" t="d">
-        <v>2026-07-22T07:31:05.999Z</v>
+        <v>2026-07-21T18:01:02.000Z</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>WO0000000310422</v>
+        <v>INC000000153393</v>
       </c>
       <c r="B1007" s="1" t="d">
-        <v>2026-07-22T08:43:44.000Z</v>
+        <v>2026-07-22T10:08:24.999Z</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>INC000000153267</v>
+        <v>WO0000000310512</v>
       </c>
       <c r="B1008" s="1" t="d">
-        <v>2026-07-21T17:58:51.999Z</v>
+        <v>2026-07-22T08:38:38.000Z</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>INC000000153266</v>
+        <v>WO0000000310438</v>
       </c>
       <c r="B1009" s="1" t="d">
-        <v>2026-07-22T09:42:57.000Z</v>
+        <v>2026-07-21T17:56:18.000Z</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>WO0000000310423</v>
+        <v>WO0000000310439</v>
       </c>
       <c r="B1010" s="1" t="d">
-        <v>2026-07-22T08:40:44.999Z</v>
+        <v>2026-07-21T18:12:13.000Z</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>WO0000000310424</v>
+        <v>INC000000153394</v>
       </c>
       <c r="B1011" s="1" t="d">
-        <v>2026-07-21T17:11:58.000Z</v>
+        <v>2026-07-21T18:47:18.000Z</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310440</v>
       </c>
       <c r="B1012" s="1" t="d">
-        <v>2026-07-21T18:17:03.000Z</v>
+        <v>2026-07-21T18:11:24.000Z</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>WO0000000310426</v>
+        <v>WO0000000310441</v>
       </c>
       <c r="B1013" s="1" t="d">
-        <v>2026-07-21T17:14:16.000Z</v>
+        <v>2026-07-22T09:29:47.000Z</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>WO0000000310427</v>
+        <v>WO0000000310513</v>
       </c>
       <c r="B1014" s="1" t="d">
-        <v>2026-07-21T17:15:07.000Z</v>
+        <v>2026-07-21T18:07:29.000Z</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>INC000000153390</v>
+        <v>INC000000153270</v>
       </c>
       <c r="B1015" s="1" t="d">
-        <v>2026-07-22T08:03:11.000Z</v>
+        <v>2026-07-21T18:48:09.000Z</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>WO0000000310430</v>
+        <v>INC000000153396</v>
       </c>
       <c r="B1016" s="1" t="d">
-        <v>2026-07-21T17:28:57.000Z</v>
+        <v>2026-07-22T07:47:35.000Z</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>WO0000000310509</v>
+        <v>INC000000153397</v>
       </c>
       <c r="B1017" s="1" t="d">
-        <v>2026-07-21T18:19:46.000Z</v>
+        <v>2026-07-22T08:01:43.000Z</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>INC000000153391</v>
+        <v>WO0000000310515</v>
       </c>
       <c r="B1018" s="1" t="d">
-        <v>2026-07-21T18:01:02.000Z</v>
+        <v>2026-07-21T18:25:31.000Z</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>INC000000153393</v>
+        <v>WO0000000310516</v>
       </c>
       <c r="B1019" s="1" t="d">
-        <v>2026-07-22T09:40:21.999Z</v>
+        <v>2026-07-21T18:28:36.000Z</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>WO0000000310512</v>
+        <v>WO0000000310445</v>
       </c>
       <c r="B1020" s="1" t="d">
-        <v>2026-07-22T08:38:38.000Z</v>
+        <v>2026-07-22T07:51:48.000Z</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>WO0000000310438</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B1021" s="1" t="d">
-        <v>2026-07-21T17:56:18.000Z</v>
+        <v>2026-07-21T19:01:53.000Z</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>WO0000000310439</v>
+        <v>INC000000153272</v>
       </c>
       <c r="B1022" s="1" t="d">
-        <v>2026-07-21T18:12:13.000Z</v>
+        <v>2026-07-22T08:25:27.999Z</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>INC000000153394</v>
+        <v>WO0000000310519</v>
       </c>
       <c r="B1023" s="1" t="d">
-        <v>2026-07-21T18:47:18.000Z</v>
+        <v>2026-07-21T19:23:16.000Z</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>WO0000000310440</v>
+        <v>WO0000000310447</v>
       </c>
       <c r="B1024" s="1" t="d">
-        <v>2026-07-21T18:11:24.000Z</v>
+        <v>2026-07-22T09:28:13.000Z</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>WO0000000310441</v>
+        <v>INC000000153401</v>
       </c>
       <c r="B1025" s="1" t="d">
-        <v>2026-07-22T09:29:47.000Z</v>
+        <v>2026-07-22T10:03:35.999Z</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>WO0000000310513</v>
+        <v>WO0000000310520</v>
       </c>
       <c r="B1026" s="1" t="d">
-        <v>2026-07-21T18:07:29.000Z</v>
+        <v>2026-07-21T22:18:08.999Z</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>INC000000153270</v>
+        <v>WO0000000310521</v>
       </c>
       <c r="B1027" s="1" t="d">
-        <v>2026-07-21T18:48:09.000Z</v>
+        <v>2026-07-22T07:48:20.000Z</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>INC000000153396</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B1028" s="1" t="d">
-        <v>2026-07-22T07:47:35.000Z</v>
+        <v>2026-07-21T22:46:20.000Z</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>INC000000153397</v>
+        <v>WO0000000310522</v>
       </c>
       <c r="B1029" s="1" t="d">
-        <v>2026-07-22T08:01:43.000Z</v>
+        <v>2026-07-22T08:07:44.000Z</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>WO0000000310515</v>
+        <v>WO0000000310453</v>
       </c>
       <c r="B1030" s="1" t="d">
-        <v>2026-07-21T18:25:31.000Z</v>
+        <v>2026-07-22T01:46:45.000Z</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>WO0000000310516</v>
+        <v>WO0000000310524</v>
       </c>
       <c r="B1031" s="1" t="d">
-        <v>2026-07-21T18:28:36.000Z</v>
+        <v>2026-07-22T07:56:01.000Z</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>WO0000000310445</v>
+        <v>INC000000153276</v>
       </c>
       <c r="B1032" s="1" t="d">
-        <v>2026-07-22T07:51:48.000Z</v>
+        <v>2026-07-22T05:50:36.999Z</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153405</v>
       </c>
       <c r="B1033" s="1" t="d">
-        <v>2026-07-21T19:01:53.000Z</v>
+        <v>2026-07-22T05:48:35.999Z</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>INC000000153272</v>
+        <v>INC000000153404</v>
       </c>
       <c r="B1034" s="1" t="d">
-        <v>2026-07-22T08:25:27.999Z</v>
+        <v>2026-07-22T05:26:24.000Z</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>WO0000000310519</v>
+        <v>WO0000000310530</v>
       </c>
       <c r="B1035" s="1" t="d">
-        <v>2026-07-21T19:23:16.000Z</v>
+        <v>2026-07-22T06:43:06.999Z</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>WO0000000310447</v>
+        <v>INC000000153277</v>
       </c>
       <c r="B1036" s="1" t="d">
-        <v>2026-07-22T09:28:13.000Z</v>
+        <v>2026-07-22T08:42:13.000Z</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>INC000000153401</v>
+        <v>WO0000000310533</v>
       </c>
       <c r="B1037" s="1" t="d">
-        <v>2026-07-21T21:50:55.000Z</v>
+        <v>2026-07-22T10:08:52.000Z</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>WO0000000310520</v>
+        <v>INC000000153278</v>
       </c>
       <c r="B1038" s="1" t="d">
-        <v>2026-07-21T22:18:08.999Z</v>
+        <v>2026-07-22T06:16:38.000Z</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>WO0000000310521</v>
+        <v>INC000000153279</v>
       </c>
       <c r="B1039" s="1" t="d">
-        <v>2026-07-22T07:48:20.000Z</v>
+        <v>2026-07-22T06:43:11.000Z</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310535</v>
       </c>
       <c r="B1040" s="1" t="d">
-        <v>2026-07-21T22:46:20.000Z</v>
+        <v>2026-07-22T07:47:51.999Z</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>WO0000000310522</v>
+        <v>INC000000153280</v>
       </c>
       <c r="B1041" s="1" t="d">
-        <v>2026-07-22T08:07:44.000Z</v>
+        <v>2026-07-22T06:52:56.000Z</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>WO0000000310453</v>
+        <v>WO0000000310459</v>
       </c>
       <c r="B1042" s="1" t="d">
-        <v>2026-07-22T01:46:45.000Z</v>
+        <v>2026-07-22T08:10:31.000Z</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>WO0000000310524</v>
+        <v>INC000000153281</v>
       </c>
       <c r="B1043" s="1" t="d">
-        <v>2026-07-22T07:56:01.000Z</v>
+        <v>2026-07-22T06:54:42.999Z</v>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>INC000000153276</v>
+        <v>INC000000153407</v>
       </c>
       <c r="B1044" s="1" t="d">
-        <v>2026-07-22T05:50:36.999Z</v>
+        <v>2026-07-22T07:11:31.000Z</v>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>INC000000153405</v>
+        <v>WO0000000310539</v>
       </c>
       <c r="B1045" s="1" t="d">
-        <v>2026-07-22T05:48:35.999Z</v>
+        <v>2026-07-22T07:01:57.000Z</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>INC000000153404</v>
+        <v>INC000000153410</v>
       </c>
       <c r="B1046" s="1" t="d">
-        <v>2026-07-22T05:26:24.000Z</v>
+        <v>2026-07-22T10:11:09.000Z</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>WO0000000310530</v>
+        <v>WO0000000310541</v>
       </c>
       <c r="B1047" s="1" t="d">
-        <v>2026-07-22T06:43:06.999Z</v>
+        <v>2026-07-22T07:05:16.000Z</v>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>INC000000153277</v>
+        <v>WO0000000310540</v>
       </c>
       <c r="B1048" s="1" t="d">
-        <v>2026-07-22T08:42:13.000Z</v>
+        <v>2026-07-22T08:01:51.999Z</v>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>WO0000000310533</v>
+        <v>INC000000153414</v>
       </c>
       <c r="B1049" s="1" t="d">
-        <v>2026-07-22T09:06:28.000Z</v>
+        <v>2026-07-22T08:32:43.000Z</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>INC000000153278</v>
+        <v>WO0000000310461</v>
       </c>
       <c r="B1050" s="1" t="d">
-        <v>2026-07-22T06:16:38.000Z</v>
+        <v>2026-07-22T07:11:04.000Z</v>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>INC000000153279</v>
+        <v>INC000000153283</v>
       </c>
       <c r="B1051" s="1" t="d">
-        <v>2026-07-22T06:43:11.000Z</v>
+        <v>2026-07-22T07:29:20.000Z</v>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>WO0000000310535</v>
+        <v>WO0000000310464</v>
       </c>
       <c r="B1052" s="1" t="d">
-        <v>2026-07-22T07:47:51.999Z</v>
+        <v>2026-07-22T07:17:47.000Z</v>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>INC000000153406</v>
+        <v>INC000000153284</v>
       </c>
       <c r="B1053" s="1" t="d">
-        <v>2026-07-22T07:10:48.000Z</v>
+        <v>2026-07-22T07:34:14.000Z</v>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>INC000000153280</v>
+        <v>WO0000000310543</v>
       </c>
       <c r="B1054" s="1" t="d">
-        <v>2026-07-22T06:52:56.000Z</v>
+        <v>2026-07-22T10:12:40.000Z</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>WO0000000310459</v>
+        <v>WO0000000310466</v>
       </c>
       <c r="B1055" s="1" t="d">
-        <v>2026-07-22T08:10:31.000Z</v>
+        <v>2026-07-22T07:41:27.000Z</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>INC000000153281</v>
+        <v>INC000000153285</v>
       </c>
       <c r="B1056" s="1" t="d">
-        <v>2026-07-22T06:54:42.999Z</v>
+        <v>2026-07-22T07:46:35.000Z</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>INC000000153407</v>
+        <v>INC000000153286</v>
       </c>
       <c r="B1057" s="1" t="d">
-        <v>2026-07-22T07:11:31.000Z</v>
+        <v>2026-07-22T07:46:51.000Z</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>WO0000000310539</v>
+        <v>INC000000153287</v>
       </c>
       <c r="B1058" s="1" t="d">
-        <v>2026-07-22T07:01:57.000Z</v>
+        <v>2026-07-22T07:47:06.999Z</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>INC000000153410</v>
+        <v>INC000000153288</v>
       </c>
       <c r="B1059" s="1" t="d">
-        <v>2026-07-22T07:03:37.000Z</v>
+        <v>2026-07-22T07:47:27.999Z</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>WO0000000310541</v>
+        <v>INC000000153415</v>
       </c>
       <c r="B1060" s="1" t="d">
-        <v>2026-07-22T07:05:16.000Z</v>
+        <v>2026-07-22T07:34:59.000Z</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>WO0000000310540</v>
+        <v>INC000000153289</v>
       </c>
       <c r="B1061" s="1" t="d">
-        <v>2026-07-22T08:01:51.999Z</v>
+        <v>2026-07-22T10:05:57.999Z</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>INC000000153414</v>
+        <v>INC000000153290</v>
       </c>
       <c r="B1062" s="1" t="d">
-        <v>2026-07-22T08:32:43.000Z</v>
+        <v>2026-07-22T10:08:16.999Z</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>WO0000000310461</v>
+        <v>INC000000153291</v>
       </c>
       <c r="B1063" s="1" t="d">
-        <v>2026-07-22T07:11:04.000Z</v>
+        <v>2026-07-22T10:10:44.999Z</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>INC000000153283</v>
+        <v>INC000000153292</v>
       </c>
       <c r="B1064" s="1" t="d">
-        <v>2026-07-22T07:29:20.000Z</v>
+        <v>2026-07-22T10:11:57.000Z</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>WO0000000310464</v>
+        <v>WO0000000310549</v>
       </c>
       <c r="B1065" s="1" t="d">
-        <v>2026-07-22T07:17:47.000Z</v>
+        <v>2026-07-22T08:57:31.000Z</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>INC000000153284</v>
+        <v>INC000000153416</v>
       </c>
       <c r="B1066" s="1" t="d">
-        <v>2026-07-22T07:34:14.000Z</v>
+        <v>2026-07-22T08:33:02.999Z</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>WO0000000310543</v>
+        <v>WO0000000310551</v>
       </c>
       <c r="B1067" s="1" t="d">
-        <v>2026-07-22T08:13:50.000Z</v>
+        <v>2026-07-22T07:42:09.999Z</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>WO0000000310466</v>
+        <v>WO0000000310552</v>
       </c>
       <c r="B1068" s="1" t="d">
-        <v>2026-07-22T07:41:27.000Z</v>
+        <v>2026-07-22T07:47:12.999Z</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>INC000000153285</v>
+        <v>INC000000153293</v>
       </c>
       <c r="B1069" s="1" t="d">
-        <v>2026-07-22T07:46:35.000Z</v>
+        <v>2026-07-22T07:50:49.000Z</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>INC000000153286</v>
+        <v>WO0000000305280</v>
       </c>
       <c r="B1070" s="1" t="d">
-        <v>2026-07-22T07:46:51.000Z</v>
+        <v>2026-07-22T09:23:02.000Z</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>INC000000153287</v>
+        <v>INC000000153295</v>
       </c>
       <c r="B1071" s="1" t="d">
-        <v>2026-07-22T07:47:06.999Z</v>
+        <v>2026-07-22T08:53:05.000Z</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>INC000000153288</v>
+        <v>WO0000000310553</v>
       </c>
       <c r="B1072" s="1" t="d">
-        <v>2026-07-22T07:47:27.999Z</v>
+        <v>2026-07-22T09:50:10.000Z</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>INC000000153415</v>
+        <v>WO0000000310556</v>
       </c>
       <c r="B1073" s="1" t="d">
-        <v>2026-07-22T07:34:59.000Z</v>
+        <v>2026-07-22T08:01:05.000Z</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>INC000000153289</v>
+        <v>INC000000153421</v>
       </c>
       <c r="B1074" s="1" t="d">
-        <v>2026-07-22T09:37:02.000Z</v>
+        <v>2026-07-22T08:49:13.000Z</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>INC000000153290</v>
+        <v>WO0000000310557</v>
       </c>
       <c r="B1075" s="1" t="d">
-        <v>2026-07-22T09:01:27.000Z</v>
+        <v>2026-07-22T08:01:09.000Z</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>INC000000153291</v>
+        <v>INC000000153296</v>
       </c>
       <c r="B1076" s="1" t="d">
-        <v>2026-07-22T09:00:48.000Z</v>
+        <v>2026-07-22T08:55:37.000Z</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>INC000000153292</v>
+        <v>WO0000000310560</v>
       </c>
       <c r="B1077" s="1" t="d">
-        <v>2026-07-22T08:59:53.000Z</v>
+        <v>2026-07-22T09:50:38.000Z</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>WO0000000310549</v>
+        <v>WO0000000310474</v>
       </c>
       <c r="B1078" s="1" t="d">
-        <v>2026-07-22T08:57:31.000Z</v>
+        <v>2026-07-22T08:05:13.000Z</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>INC000000153416</v>
+        <v>WO0000000310476</v>
       </c>
       <c r="B1079" s="1" t="d">
-        <v>2026-07-22T08:33:02.999Z</v>
+        <v>2026-07-22T08:14:42.999Z</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>WO0000000310551</v>
+        <v>WO0000000310562</v>
       </c>
       <c r="B1080" s="1" t="d">
-        <v>2026-07-22T07:42:09.999Z</v>
+        <v>2026-07-22T08:29:34.000Z</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>WO0000000310552</v>
+        <v>WO0000000310478</v>
       </c>
       <c r="B1081" s="1" t="d">
-        <v>2026-07-22T07:47:12.999Z</v>
+        <v>2026-07-22T08:14:23.000Z</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>INC000000153293</v>
+        <v>WO0000000310563</v>
       </c>
       <c r="B1082" s="1" t="d">
-        <v>2026-07-22T07:50:49.000Z</v>
+        <v>2026-07-22T08:31:57.000Z</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>WO0000000305280</v>
+        <v>WO0000000310480</v>
       </c>
       <c r="B1083" s="1" t="d">
-        <v>2026-07-22T09:23:02.000Z</v>
+        <v>2026-07-22T08:30:01.000Z</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>INC000000153295</v>
+        <v>INC000000153422</v>
       </c>
       <c r="B1084" s="1" t="d">
-        <v>2026-07-22T08:53:05.000Z</v>
+        <v>2026-07-22T08:19:43.000Z</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>WO0000000310553</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B1085" s="1" t="d">
-        <v>2026-07-22T09:50:10.000Z</v>
+        <v>2026-07-22T08:55:35.999Z</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>WO0000000310556</v>
+        <v>WO0000000310482</v>
       </c>
       <c r="B1086" s="1" t="d">
-        <v>2026-07-22T08:01:05.000Z</v>
+        <v>2026-07-22T08:16:50.000Z</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>INC000000153421</v>
+        <v>WO0000000310564</v>
       </c>
       <c r="B1087" s="1" t="d">
-        <v>2026-07-22T08:49:13.000Z</v>
+        <v>2026-07-22T08:20:03.000Z</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>WO0000000310557</v>
+        <v>WO0000000310570</v>
       </c>
       <c r="B1088" s="1" t="d">
-        <v>2026-07-22T08:01:09.000Z</v>
+        <v>2026-07-22T08:22:25.000Z</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="str">
-        <v>INC000000153296</v>
+        <v>INC000000153425</v>
       </c>
       <c r="B1089" s="1" t="d">
-        <v>2026-07-22T08:55:37.000Z</v>
+        <v>2026-07-22T08:54:19.000Z</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="str">
-        <v>WO0000000310560</v>
+        <v>WO0000000310483</v>
       </c>
       <c r="B1090" s="1" t="d">
-        <v>2026-07-22T09:50:38.000Z</v>
+        <v>2026-07-22T09:27:48.000Z</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="str">
-        <v>WO0000000310474</v>
+        <v>WO0000000310569</v>
       </c>
       <c r="B1091" s="1" t="d">
-        <v>2026-07-22T08:05:13.000Z</v>
+        <v>2026-07-22T09:51:30.000Z</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="str">
-        <v>WO0000000310476</v>
+        <v>WO0000000310573</v>
       </c>
       <c r="B1092" s="1" t="d">
-        <v>2026-07-22T08:14:42.999Z</v>
+        <v>2026-07-22T08:31:26.000Z</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="str">
-        <v>WO0000000310562</v>
+        <v>INC000000153300</v>
       </c>
       <c r="B1093" s="1" t="d">
-        <v>2026-07-22T08:29:34.000Z</v>
+        <v>2026-07-22T08:48:44.000Z</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="str">
-        <v>WO0000000310478</v>
+        <v>WO0000000310489</v>
       </c>
       <c r="B1094" s="1" t="d">
-        <v>2026-07-22T08:14:23.000Z</v>
+        <v>2026-07-22T08:32:18.000Z</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="str">
-        <v>WO0000000310563</v>
+        <v>INC000000153429</v>
       </c>
       <c r="B1095" s="1" t="d">
-        <v>2026-07-22T08:31:57.000Z</v>
+        <v>2026-07-22T08:50:04.000Z</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="str">
-        <v>WO0000000310480</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B1096" s="1" t="d">
-        <v>2026-07-22T08:30:01.000Z</v>
+        <v>2026-07-22T08:40:26.000Z</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="str">
-        <v>INC000000153422</v>
+        <v>INC000000153428</v>
       </c>
       <c r="B1097" s="1" t="d">
-        <v>2026-07-22T08:19:43.000Z</v>
+        <v>2026-07-22T08:56:43.000Z</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="str">
-        <v>INC000000153299</v>
+        <v>WO0000000310491</v>
       </c>
       <c r="B1098" s="1" t="d">
-        <v>2026-07-22T08:55:35.999Z</v>
+        <v>2026-07-22T09:12:34.000Z</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>WO0000000310482</v>
+        <v>WO0000000310492</v>
       </c>
       <c r="B1099" s="1" t="d">
-        <v>2026-07-22T08:16:50.000Z</v>
+        <v>2026-07-22T09:45:54.999Z</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="str">
-        <v>WO0000000310564</v>
+        <v>WO0000000310493</v>
       </c>
       <c r="B1100" s="1" t="d">
-        <v>2026-07-22T08:20:03.000Z</v>
+        <v>2026-07-22T08:40:50.000Z</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="str">
-        <v>WO0000000310570</v>
+        <v>WO0000000310579</v>
       </c>
       <c r="B1101" s="1" t="d">
-        <v>2026-07-22T08:22:25.000Z</v>
+        <v>2026-07-22T08:41:33.000Z</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="str">
-        <v>INC000000153425</v>
+        <v>INC000000153427</v>
       </c>
       <c r="B1102" s="1" t="d">
-        <v>2026-07-22T08:54:19.000Z</v>
+        <v>2026-07-22T08:45:20.000Z</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="str">
-        <v>WO0000000310483</v>
+        <v>WO0000000310581</v>
       </c>
       <c r="B1103" s="1" t="d">
-        <v>2026-07-22T09:27:48.000Z</v>
+        <v>2026-07-22T09:34:31.000Z</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="str">
-        <v>WO0000000310569</v>
+        <v>WO0000000310494</v>
       </c>
       <c r="B1104" s="1" t="d">
-        <v>2026-07-22T09:51:30.000Z</v>
+        <v>2026-07-22T09:28:19.000Z</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="str">
-        <v>WO0000000310485</v>
+        <v>INC000000153501</v>
       </c>
       <c r="B1105" s="1" t="d">
-        <v>2026-07-22T09:41:20.999Z</v>
+        <v>2026-07-22T10:11:03.000Z</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="str">
-        <v>WO0000000310573</v>
+        <v>INC000000153502</v>
       </c>
       <c r="B1106" s="1" t="d">
-        <v>2026-07-22T08:31:26.000Z</v>
+        <v>2026-07-22T09:49:39.000Z</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="str">
-        <v>INC000000153300</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B1107" s="1" t="d">
-        <v>2026-07-22T08:48:44.000Z</v>
+        <v>2026-07-22T09:20:21.999Z</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="str">
-        <v>WO0000000310489</v>
+        <v>WO0000000310575</v>
       </c>
       <c r="B1108" s="1" t="d">
-        <v>2026-07-22T08:32:18.000Z</v>
+        <v>2026-07-22T09:38:20.999Z</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="str">
-        <v>INC000000153429</v>
+        <v>WO0000000310498</v>
       </c>
       <c r="B1109" s="1" t="d">
-        <v>2026-07-22T08:50:04.000Z</v>
+        <v>2026-07-22T08:49:48.000Z</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="str">
-        <v>WO0000000310577</v>
+        <v>INC000000153503</v>
       </c>
       <c r="B1110" s="1" t="d">
-        <v>2026-07-22T08:40:26.000Z</v>
+        <v>2026-07-22T08:53:18.000Z</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="str">
-        <v>INC000000153428</v>
+        <v>WO0000000310500</v>
       </c>
       <c r="B1111" s="1" t="d">
-        <v>2026-07-22T08:56:43.000Z</v>
+        <v>2026-07-22T08:50:36.000Z</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="str">
-        <v>WO0000000310491</v>
+        <v>WO0000000310604</v>
       </c>
       <c r="B1112" s="1" t="d">
-        <v>2026-07-22T09:12:34.000Z</v>
+        <v>2026-07-22T09:48:30.000Z</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="str">
-        <v>WO0000000310492</v>
+        <v>WO0000000310495</v>
       </c>
       <c r="B1113" s="1" t="d">
-        <v>2026-07-22T09:45:54.999Z</v>
+        <v>2026-07-22T09:37:27.000Z</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="str">
-        <v>WO0000000310493</v>
+        <v>INC000000153504</v>
       </c>
       <c r="B1114" s="1" t="d">
-        <v>2026-07-22T08:40:50.000Z</v>
+        <v>2026-07-22T09:04:34.000Z</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="str">
-        <v>WO0000000310579</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B1115" s="1" t="d">
-        <v>2026-07-22T08:41:33.000Z</v>
+        <v>2026-07-22T08:58:13.000Z</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="str">
-        <v>INC000000153427</v>
+        <v>WO0000000310605</v>
       </c>
       <c r="B1116" s="1" t="d">
-        <v>2026-07-22T08:45:20.000Z</v>
+        <v>2026-07-22T08:54:06.999Z</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="str">
-        <v>WO0000000310581</v>
+        <v>WO0000000310499</v>
       </c>
       <c r="B1117" s="1" t="d">
-        <v>2026-07-22T09:34:31.000Z</v>
+        <v>2026-07-22T08:55:32.000Z</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="str">
-        <v>WO0000000310494</v>
+        <v>INC000000153507</v>
       </c>
       <c r="B1118" s="1" t="d">
-        <v>2026-07-22T09:28:19.000Z</v>
+        <v>2026-07-22T09:11:18.000Z</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>INC000000153501</v>
+        <v>INC000000153508</v>
       </c>
       <c r="B1119" s="1" t="d">
-        <v>2026-07-22T09:37:10.999Z</v>
+        <v>2026-07-22T09:57:15.000Z</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>INC000000153502</v>
+        <v>WO0000000310607</v>
       </c>
       <c r="B1120" s="1" t="d">
-        <v>2026-07-22T09:49:39.000Z</v>
+        <v>2026-07-22T09:48:52.000Z</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="str">
-        <v>INC000000153431</v>
+        <v>WO0000000310586</v>
       </c>
       <c r="B1121" s="1" t="d">
-        <v>2026-07-22T09:20:21.999Z</v>
+        <v>2026-07-22T10:11:26.000Z</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="str">
-        <v>WO0000000310575</v>
+        <v>INC000000153509</v>
       </c>
       <c r="B1122" s="1" t="d">
-        <v>2026-07-22T09:38:20.999Z</v>
+        <v>2026-07-22T10:04:49.000Z</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="str">
-        <v>WO0000000310498</v>
+        <v>WO0000000310588</v>
       </c>
       <c r="B1123" s="1" t="d">
-        <v>2026-07-22T08:49:48.000Z</v>
+        <v>2026-07-22T09:00:54.000Z</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="str">
-        <v>INC000000153503</v>
+        <v>INC000000153506</v>
       </c>
       <c r="B1124" s="1" t="d">
-        <v>2026-07-22T08:53:18.000Z</v>
+        <v>2026-07-22T09:13:44.000Z</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>WO0000000310500</v>
+        <v>WO0000000305281</v>
       </c>
       <c r="B1125" s="1" t="d">
-        <v>2026-07-22T08:50:36.000Z</v>
+        <v>2026-07-22T09:49:18.000Z</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>WO0000000310604</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B1126" s="1" t="d">
-        <v>2026-07-22T09:48:30.000Z</v>
+        <v>2026-07-22T09:20:50.000Z</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="str">
-        <v>WO0000000310495</v>
+        <v>WO0000000310594</v>
       </c>
       <c r="B1127" s="1" t="d">
-        <v>2026-07-22T09:37:27.000Z</v>
+        <v>2026-07-22T09:06:53.000Z</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="str">
-        <v>INC000000153504</v>
+        <v>WO0000000310609</v>
       </c>
       <c r="B1128" s="1" t="d">
-        <v>2026-07-22T09:04:34.000Z</v>
+        <v>2026-07-22T09:07:17.000Z</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="str">
-        <v>INC000000153505</v>
+        <v>WO0000000310611</v>
       </c>
       <c r="B1129" s="1" t="d">
-        <v>2026-07-22T08:58:13.000Z</v>
+        <v>2026-07-22T09:09:14.000Z</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="str">
-        <v>WO0000000310605</v>
+        <v>INC000000153511</v>
       </c>
       <c r="B1130" s="1" t="d">
-        <v>2026-07-22T08:54:06.999Z</v>
+        <v>2026-07-22T09:57:37.000Z</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="str">
-        <v>WO0000000310499</v>
+        <v>WO0000000310701</v>
       </c>
       <c r="B1131" s="1" t="d">
-        <v>2026-07-22T08:55:32.000Z</v>
+        <v>2026-07-22T09:51:55.000Z</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="str">
-        <v>INC000000153507</v>
+        <v>WO0000000310613</v>
       </c>
       <c r="B1132" s="1" t="d">
-        <v>2026-07-22T09:11:18.000Z</v>
+        <v>2026-07-22T09:17:27.000Z</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>INC000000153508</v>
+        <v>WO0000000310592</v>
       </c>
       <c r="B1133" s="1" t="d">
-        <v>2026-07-22T09:17:19.000Z</v>
+        <v>2026-07-22T09:18:25.000Z</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>WO0000000310607</v>
+        <v>WO0000000310615</v>
       </c>
       <c r="B1134" s="1" t="d">
-        <v>2026-07-22T09:48:52.000Z</v>
+        <v>2026-07-22T09:40:11.000Z</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="str">
-        <v>WO0000000310586</v>
+        <v>WO0000000310616</v>
       </c>
       <c r="B1135" s="1" t="d">
-        <v>2026-07-22T09:46:58.000Z</v>
+        <v>2026-07-22T09:47:20.000Z</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="str">
-        <v>INC000000153509</v>
+        <v>WO0000000310617</v>
       </c>
       <c r="B1136" s="1" t="d">
-        <v>2026-07-22T09:15:53.000Z</v>
+        <v>2026-07-22T09:18:02.999Z</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="str">
-        <v>WO0000000310588</v>
+        <v>WO0000000310703</v>
       </c>
       <c r="B1137" s="1" t="d">
-        <v>2026-07-22T09:00:54.000Z</v>
+        <v>2026-07-22T09:36:22.000Z</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="str">
-        <v>INC000000153506</v>
+        <v>WO0000000310705</v>
       </c>
       <c r="B1138" s="1" t="d">
-        <v>2026-07-22T09:13:44.000Z</v>
+        <v>2026-07-22T09:24:59.000Z</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="str">
-        <v>WO0000000305281</v>
+        <v>WO0000000310706</v>
       </c>
       <c r="B1139" s="1" t="d">
-        <v>2026-07-22T09:49:18.000Z</v>
+        <v>2026-07-22T09:21:12.999Z</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="str">
-        <v>INC000000153433</v>
+        <v>WO0000000310618</v>
       </c>
       <c r="B1140" s="1" t="d">
-        <v>2026-07-22T09:20:50.000Z</v>
+        <v>2026-07-22T09:49:34.000Z</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="str">
-        <v>WO0000000310594</v>
+        <v>INC000000153512</v>
       </c>
       <c r="B1141" s="1" t="d">
-        <v>2026-07-22T09:06:53.000Z</v>
+        <v>2026-07-22T09:22:37.000Z</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="str">
-        <v>WO0000000310609</v>
+        <v>WO0000000310585</v>
       </c>
       <c r="B1142" s="1" t="d">
-        <v>2026-07-22T09:07:17.000Z</v>
+        <v>2026-07-22T09:23:52.000Z</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="str">
-        <v>WO0000000310611</v>
+        <v>WO0000000310600</v>
       </c>
       <c r="B1143" s="1" t="d">
-        <v>2026-07-22T09:09:14.000Z</v>
+        <v>2026-07-22T09:23:46.999Z</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="str">
-        <v>INC000000153511</v>
+        <v>WO0000000310709</v>
       </c>
       <c r="B1144" s="1" t="d">
-        <v>2026-07-22T09:21:37.000Z</v>
+        <v>2026-07-22T09:26:30.000Z</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="str">
-        <v>WO0000000310701</v>
+        <v>WO0000000310710</v>
       </c>
       <c r="B1145" s="1" t="d">
-        <v>2026-07-22T09:51:55.000Z</v>
+        <v>2026-07-22T09:27:16.000Z</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="str">
-        <v>WO0000000310613</v>
+        <v>WO0000000310621</v>
       </c>
       <c r="B1146" s="1" t="d">
-        <v>2026-07-22T09:17:27.000Z</v>
+        <v>2026-07-22T09:27:43.000Z</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="str">
-        <v>WO0000000310592</v>
+        <v>INC000000153513</v>
       </c>
       <c r="B1147" s="1" t="d">
-        <v>2026-07-22T09:18:25.000Z</v>
+        <v>2026-07-22T10:06:55.000Z</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="str">
-        <v>WO0000000310615</v>
+        <v>WO0000000310708</v>
       </c>
       <c r="B1148" s="1" t="d">
-        <v>2026-07-22T09:40:11.000Z</v>
+        <v>2026-07-22T09:46:30.999Z</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="str">
-        <v>WO0000000310616</v>
+        <v>WO0000000310714</v>
       </c>
       <c r="B1149" s="1" t="d">
-        <v>2026-07-22T09:47:20.000Z</v>
+        <v>2026-07-22T09:32:57.999Z</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="str">
-        <v>WO0000000310617</v>
+        <v>WO0000000310712</v>
       </c>
       <c r="B1150" s="1" t="d">
-        <v>2026-07-22T09:18:02.999Z</v>
+        <v>2026-07-22T09:53:42.000Z</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="str">
-        <v>WO0000000310703</v>
+        <v>WO0000000310704</v>
       </c>
       <c r="B1151" s="1" t="d">
-        <v>2026-07-22T09:36:22.000Z</v>
+        <v>2026-07-22T09:34:48.000Z</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="str">
-        <v>WO0000000310705</v>
+        <v>WO0000000310715</v>
       </c>
       <c r="B1152" s="1" t="d">
-        <v>2026-07-22T09:24:59.000Z</v>
+        <v>2026-07-22T09:35:21.999Z</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>WO0000000310706</v>
+        <v>INC000000153516</v>
       </c>
       <c r="B1153" s="1" t="d">
-        <v>2026-07-22T09:21:12.999Z</v>
+        <v>2026-07-22T10:03:44.000Z</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>WO0000000310618</v>
+        <v>INC000000153514</v>
       </c>
       <c r="B1154" s="1" t="d">
-        <v>2026-07-22T09:49:34.000Z</v>
+        <v>2026-07-22T09:48:36.999Z</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="str">
-        <v>INC000000153512</v>
+        <v>WO0000000310717</v>
       </c>
       <c r="B1155" s="1" t="d">
-        <v>2026-07-22T09:22:37.000Z</v>
+        <v>2026-07-22T09:39:33.000Z</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="str">
-        <v>WO0000000310585</v>
+        <v>WO0000000310626</v>
       </c>
       <c r="B1156" s="1" t="d">
-        <v>2026-07-22T09:23:52.000Z</v>
+        <v>2026-07-22T09:39:42.999Z</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>WO0000000310600</v>
+        <v>WO0000000310627</v>
       </c>
       <c r="B1157" s="1" t="d">
-        <v>2026-07-22T09:23:46.999Z</v>
+        <v>2026-07-22T10:08:53.000Z</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="str">
-        <v>WO0000000310709</v>
+        <v>WO0000000310624</v>
       </c>
       <c r="B1158" s="1" t="d">
-        <v>2026-07-22T09:26:30.000Z</v>
+        <v>2026-07-22T09:40:45.999Z</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>WO0000000310710</v>
+        <v>INC000000153517</v>
       </c>
       <c r="B1159" s="1" t="d">
-        <v>2026-07-22T09:27:16.000Z</v>
+        <v>2026-07-22T10:11:33.000Z</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>WO0000000310621</v>
+        <v>WO0000000310721</v>
       </c>
       <c r="B1160" s="1" t="d">
-        <v>2026-07-22T09:27:43.000Z</v>
+        <v>2026-07-22T09:44:55.999Z</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>INC000000153513</v>
+        <v>WO0000000310722</v>
       </c>
       <c r="B1161" s="1" t="d">
-        <v>2026-07-22T09:51:49.000Z</v>
+        <v>2026-07-22T09:50:45.000Z</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="str">
-        <v>WO0000000310708</v>
+        <v>WO0000000310723</v>
       </c>
       <c r="B1162" s="1" t="d">
-        <v>2026-07-22T09:46:30.999Z</v>
+        <v>2026-07-22T09:47:36.000Z</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="str">
-        <v>WO0000000310714</v>
+        <v>INC000000153435</v>
       </c>
       <c r="B1163" s="1" t="d">
-        <v>2026-07-22T09:32:57.999Z</v>
+        <v>2026-07-22T10:06:58.000Z</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="str">
-        <v>WO0000000310712</v>
+        <v>INC000000153518</v>
       </c>
       <c r="B1164" s="1" t="d">
-        <v>2026-07-22T09:53:42.000Z</v>
+        <v>2026-07-22T10:06:58.000Z</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="str">
-        <v>WO0000000310704</v>
+        <v>INC000000153520</v>
       </c>
       <c r="B1165" s="1" t="d">
-        <v>2026-07-22T09:34:48.000Z</v>
+        <v>2026-07-22T10:13:06.000Z</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="str">
-        <v>WO0000000310715</v>
+        <v>WO0000000310719</v>
       </c>
       <c r="B1166" s="1" t="d">
-        <v>2026-07-22T09:35:21.999Z</v>
+        <v>2026-07-22T10:13:06.000Z</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="str">
-        <v>INC000000153516</v>
+        <v>WO0000000310726</v>
       </c>
       <c r="B1167" s="1" t="d">
-        <v>2026-07-22T09:44:04.000Z</v>
+        <v>2026-07-22T09:59:31.000Z</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="str">
-        <v>INC000000153514</v>
+        <v>WO0000000310725</v>
       </c>
       <c r="B1168" s="1" t="d">
-        <v>2026-07-22T09:48:36.999Z</v>
+        <v>2026-07-22T09:58:47.999Z</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="str">
-        <v>WO0000000310717</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B1169" s="1" t="d">
-        <v>2026-07-22T09:39:33.000Z</v>
+        <v>2026-07-22T09:59:51.999Z</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="str">
-        <v>WO0000000310626</v>
+        <v>WO0000000310632</v>
       </c>
       <c r="B1170" s="1" t="d">
-        <v>2026-07-22T09:39:42.999Z</v>
+        <v>2026-07-22T10:11:04.000Z</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="str">
-        <v>WO0000000310627</v>
+        <v>WO0000000309317</v>
       </c>
       <c r="B1171" s="1" t="d">
-        <v>2026-07-22T09:51:09.999Z</v>
+        <v>2026-07-22T10:00:33.000Z</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="str">
-        <v>WO0000000310624</v>
+        <v>INC000000153519</v>
       </c>
       <c r="B1172" s="1" t="d">
-        <v>2026-07-22T09:40:45.999Z</v>
+        <v>2026-07-22T10:04:17.000Z</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="str">
-        <v>INC000000153517</v>
+        <v>WO0000000310633</v>
       </c>
       <c r="B1173" s="1" t="d">
-        <v>2026-07-22T09:50:56.000Z</v>
+        <v>2026-07-22T10:11:05.000Z</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="str">
-        <v>WO0000000310721</v>
+        <v>WO0000000310635</v>
       </c>
       <c r="B1174" s="1" t="d">
-        <v>2026-07-22T09:44:55.999Z</v>
+        <v>2026-07-22T10:03:56.000Z</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="str">
-        <v>WO0000000310722</v>
+        <v>INC000000153437</v>
       </c>
       <c r="B1175" s="1" t="d">
-        <v>2026-07-22T09:50:45.000Z</v>
+        <v>2026-07-22T10:06:26.999Z</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="str">
-        <v>WO0000000310723</v>
+        <v>WO0000000310732</v>
       </c>
       <c r="B1176" s="1" t="d">
-        <v>2026-07-22T09:47:36.000Z</v>
+        <v>2026-07-22T10:08:16.000Z</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="str">
-        <v>INC000000153435</v>
+        <v>INC000000153521</v>
       </c>
       <c r="B1177" s="1" t="d">
-        <v>2026-07-22T09:50:03.000Z</v>
+        <v>2026-07-22T10:12:39.000Z</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="str">
-        <v>INC000000153518</v>
+        <v>WO0000000310639</v>
       </c>
       <c r="B1178" s="1" t="d">
-        <v>2026-07-22T09:51:41.000Z</v>
+        <v>2026-07-22T10:10:22.000Z</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="str">
-        <v>INC000000153520</v>
+        <v>INC000000153438</v>
       </c>
       <c r="B1179" s="1" t="d">
-        <v>2026-07-22T09:54:05.000Z</v>
+        <v>2026-07-22T10:12:09.999Z</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="str">
-        <v>WO0000000310631</v>
+        <v>INC000000153523</v>
       </c>
       <c r="B1180" s="1" t="d">
-        <v>2026-07-22T09:55:42.000Z</v>
+        <v>2026-07-22T10:13:13.000Z</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="str">
+        <v>INC000000153522</v>
+      </c>
+      <c r="B1181" s="1" t="d">
+        <v>2026-07-22T10:13:23.000Z</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="str">
+        <v>WO0000000310733</v>
+      </c>
+      <c r="B1182" s="1" t="d">
+        <v>2026-07-22T10:13:21.000Z</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="str">
+        <v>WO0000000310734</v>
+      </c>
+      <c r="B1183" s="1" t="d">
+        <v>2026-07-22T10:13:49.000Z</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="str">
         <v>Count all</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1184"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notas.xlsx
+++ b/notas.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1184"/>
+  <dimension ref="A1:B1165"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1803,1786 +1803,1786 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>WO0000000295822</v>
+        <v>INC000000146909</v>
       </c>
       <c r="B176" s="1" t="d">
-        <v>2026-06-17T08:27:58.000Z</v>
+        <v>2026-06-17T12:37:10.999Z</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>INC000000146909</v>
+        <v>WO0000000296202</v>
       </c>
       <c r="B177" s="1" t="d">
-        <v>2026-06-17T12:37:10.999Z</v>
+        <v>2026-06-18T14:56:58.999Z</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>WO0000000296202</v>
+        <v>INC000000146890</v>
       </c>
       <c r="B178" s="1" t="d">
-        <v>2026-06-18T14:56:58.999Z</v>
+        <v>2026-06-25T09:42:16.000Z</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>INC000000146890</v>
+        <v>WO0000000296452</v>
       </c>
       <c r="B179" s="1" t="d">
-        <v>2026-06-25T09:42:16.000Z</v>
+        <v>2026-06-25T08:00:46.000Z</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>WO0000000296452</v>
+        <v>WO0000000296750</v>
       </c>
       <c r="B180" s="1" t="d">
-        <v>2026-06-25T08:00:46.000Z</v>
+        <v>2026-06-22T12:16:58.999Z</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>WO0000000296750</v>
+        <v>INC000000147416</v>
       </c>
       <c r="B181" s="1" t="d">
-        <v>2026-06-22T12:16:58.999Z</v>
+        <v>2026-06-17T07:56:14.999Z</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>INC000000147416</v>
+        <v>INC000000147777</v>
       </c>
       <c r="B182" s="1" t="d">
-        <v>2026-06-17T07:56:14.999Z</v>
+        <v>2026-06-18T12:54:15.999Z</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>INC000000147777</v>
+        <v>INC000000147847</v>
       </c>
       <c r="B183" s="1" t="d">
-        <v>2026-06-18T12:54:15.999Z</v>
+        <v>2026-06-19T19:05:07.000Z</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>INC000000147847</v>
+        <v>INC000000147976</v>
       </c>
       <c r="B184" s="1" t="d">
-        <v>2026-06-19T19:05:07.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>INC000000147976</v>
+        <v>INC000000147982</v>
       </c>
       <c r="B185" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-06-19T11:55:18.000Z</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>INC000000147982</v>
+        <v>INC000000090925</v>
       </c>
       <c r="B186" s="1" t="d">
-        <v>2026-06-19T11:55:18.000Z</v>
+        <v>2026-07-10T08:13:02.000Z</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>INC000000090925</v>
+        <v>INC000000114588</v>
       </c>
       <c r="B187" s="1" t="d">
-        <v>2026-07-10T08:13:02.000Z</v>
+        <v>2026-07-09T16:48:55.000Z</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>INC000000114588</v>
+        <v>INC000000124474</v>
       </c>
       <c r="B188" s="1" t="d">
-        <v>2026-07-09T16:48:55.000Z</v>
+        <v>2026-06-26T20:32:27.999Z</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>INC000000124474</v>
+        <v>INC000000125491</v>
       </c>
       <c r="B189" s="1" t="d">
-        <v>2026-06-26T20:32:27.999Z</v>
+        <v>2026-06-26T20:32:43.000Z</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>INC000000125491</v>
+        <v>INC000000128139</v>
       </c>
       <c r="B190" s="1" t="d">
-        <v>2026-06-26T20:32:43.000Z</v>
+        <v>2026-06-26T20:32:56.000Z</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>INC000000128139</v>
+        <v>INC000000129391</v>
       </c>
       <c r="B191" s="1" t="d">
-        <v>2026-06-26T20:32:56.000Z</v>
+        <v>2026-06-30T10:50:24.999Z</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>INC000000129391</v>
+        <v>INC000000133126</v>
       </c>
       <c r="B192" s="1" t="d">
-        <v>2026-06-30T10:50:24.999Z</v>
+        <v>2026-06-26T20:33:23.999Z</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>INC000000133126</v>
+        <v>INC000000133420</v>
       </c>
       <c r="B193" s="1" t="d">
-        <v>2026-06-26T20:33:23.999Z</v>
+        <v>2026-06-26T20:33:57.000Z</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>INC000000133420</v>
+        <v>INC000000133435</v>
       </c>
       <c r="B194" s="1" t="d">
-        <v>2026-06-26T20:33:57.000Z</v>
+        <v>2026-06-26T20:34:07.999Z</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>INC000000133435</v>
+        <v>INC000000133349</v>
       </c>
       <c r="B195" s="1" t="d">
-        <v>2026-06-26T20:34:07.999Z</v>
+        <v>2026-06-26T20:33:42.000Z</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>INC000000133349</v>
+        <v>INC000000134481</v>
       </c>
       <c r="B196" s="1" t="d">
-        <v>2026-06-26T20:33:42.000Z</v>
+        <v>2026-06-30T09:24:11.000Z</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>INC000000134481</v>
+        <v>INC000000135695</v>
       </c>
       <c r="B197" s="1" t="d">
-        <v>2026-06-30T09:24:11.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>INC000000135695</v>
+        <v>INC000000136146</v>
       </c>
       <c r="B198" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-06-26T20:34:24.000Z</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>INC000000136146</v>
+        <v>INC000000137517</v>
       </c>
       <c r="B199" s="1" t="d">
-        <v>2026-06-26T20:34:24.000Z</v>
+        <v>2026-06-26T20:34:37.000Z</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>INC000000137517</v>
+        <v>INC000000138955</v>
       </c>
       <c r="B200" s="1" t="d">
-        <v>2026-06-26T20:34:37.000Z</v>
+        <v>2026-07-09T11:15:12.999Z</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>INC000000138955</v>
+        <v>INC000000139547</v>
       </c>
       <c r="B201" s="1" t="d">
-        <v>2026-07-09T11:15:12.999Z</v>
+        <v>2026-06-26T20:34:51.000Z</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>INC000000139547</v>
+        <v>INC000000139551</v>
       </c>
       <c r="B202" s="1" t="d">
-        <v>2026-06-26T20:34:51.000Z</v>
+        <v>2026-06-30T10:46:24.000Z</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>INC000000139551</v>
+        <v>INC000000139847</v>
       </c>
       <c r="B203" s="1" t="d">
-        <v>2026-06-30T10:46:24.000Z</v>
+        <v>2026-06-26T20:35:05.999Z</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>INC000000139847</v>
+        <v>INC000000141001</v>
       </c>
       <c r="B204" s="1" t="d">
-        <v>2026-06-26T20:35:05.999Z</v>
+        <v>2026-07-08T12:25:55.000Z</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>INC000000141001</v>
+        <v>INC000000141640</v>
       </c>
       <c r="B205" s="1" t="d">
-        <v>2026-07-08T12:25:55.000Z</v>
+        <v>2026-07-14T08:34:57.000Z</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>INC000000141640</v>
+        <v>INC000000142106</v>
       </c>
       <c r="B206" s="1" t="d">
-        <v>2026-07-14T08:34:57.000Z</v>
+        <v>2026-06-26T20:27:55.000Z</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>INC000000142106</v>
+        <v>WO0000000287464</v>
       </c>
       <c r="B207" s="1" t="d">
-        <v>2026-06-26T20:27:55.000Z</v>
+        <v>2026-07-08T10:11:20.999Z</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>WO0000000287464</v>
+        <v>INC000000142518</v>
       </c>
       <c r="B208" s="1" t="d">
-        <v>2026-07-08T10:11:20.999Z</v>
+        <v>2026-06-26T20:28:21.000Z</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>INC000000142518</v>
+        <v>WO0000000288840</v>
       </c>
       <c r="B209" s="1" t="d">
-        <v>2026-06-26T20:28:21.000Z</v>
+        <v>2026-07-03T12:08:05.000Z</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>WO0000000288840</v>
+        <v>WO0000000288737</v>
       </c>
       <c r="B210" s="1" t="d">
-        <v>2026-07-03T12:08:05.000Z</v>
+        <v>2026-07-03T11:40:50.999Z</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>WO0000000288737</v>
+        <v>INC000000143439</v>
       </c>
       <c r="B211" s="1" t="d">
-        <v>2026-07-03T11:40:50.999Z</v>
+        <v>2026-06-26T20:28:54.000Z</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>INC000000143439</v>
+        <v>INC000000144822</v>
       </c>
       <c r="B212" s="1" t="d">
-        <v>2026-06-26T20:28:54.000Z</v>
+        <v>2026-07-16T08:31:54.000Z</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>INC000000144822</v>
+        <v>INC000000145025</v>
       </c>
       <c r="B213" s="1" t="d">
-        <v>2026-07-16T08:31:54.000Z</v>
+        <v>2026-07-02T12:27:43.000Z</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>INC000000145025</v>
+        <v>INC000000145194</v>
       </c>
       <c r="B214" s="1" t="d">
-        <v>2026-07-02T12:27:43.000Z</v>
+        <v>2026-07-16T09:36:17.000Z</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>INC000000145194</v>
+        <v>INC000000146528</v>
       </c>
       <c r="B215" s="1" t="d">
-        <v>2026-07-16T09:36:17.000Z</v>
+        <v>2026-07-02T12:27:43.000Z</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>INC000000146528</v>
+        <v>WO0000000295650</v>
       </c>
       <c r="B216" s="1" t="d">
-        <v>2026-07-02T12:27:43.000Z</v>
+        <v>2026-07-07T08:33:04.999Z</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>WO0000000295650</v>
+        <v>WO0000000296601</v>
       </c>
       <c r="B217" s="1" t="d">
-        <v>2026-07-07T08:33:04.999Z</v>
+        <v>2026-06-30T09:52:50.999Z</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>WO0000000296601</v>
+        <v>INC000000147297</v>
       </c>
       <c r="B218" s="1" t="d">
-        <v>2026-06-30T09:52:50.999Z</v>
+        <v>2026-07-08T12:27:13.999Z</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>INC000000147297</v>
+        <v>WO0000000297046</v>
       </c>
       <c r="B219" s="1" t="d">
-        <v>2026-07-08T12:27:13.999Z</v>
+        <v>2026-07-16T15:23:18.000Z</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>WO0000000297046</v>
+        <v>WO0000000291773</v>
       </c>
       <c r="B220" s="1" t="d">
-        <v>2026-07-16T15:23:18.000Z</v>
+        <v>2026-07-06T12:05:36.000Z</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>WO0000000291773</v>
+        <v>INC000000147569</v>
       </c>
       <c r="B221" s="1" t="d">
-        <v>2026-07-06T12:05:36.000Z</v>
+        <v>2026-06-26T20:31:22.000Z</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>INC000000147569</v>
+        <v>WO0000000298379</v>
       </c>
       <c r="B222" s="1" t="d">
-        <v>2026-06-26T20:31:22.000Z</v>
+        <v>2026-06-24T13:42:23.000Z</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>WO0000000298379</v>
+        <v>WO0000000299246</v>
       </c>
       <c r="B223" s="1" t="d">
-        <v>2026-06-24T13:42:23.000Z</v>
+        <v>2026-06-25T11:19:04.000Z</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>WO0000000299246</v>
+        <v>WO0000000299346</v>
       </c>
       <c r="B224" s="1" t="d">
-        <v>2026-06-25T11:19:04.000Z</v>
+        <v>2026-07-02T15:43:45.000Z</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>WO0000000299346</v>
+        <v>INC000000148375</v>
       </c>
       <c r="B225" s="1" t="d">
-        <v>2026-07-02T15:43:45.000Z</v>
+        <v>2026-07-06T10:46:28.999Z</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>INC000000148375</v>
+        <v>INC000000148478</v>
       </c>
       <c r="B226" s="1" t="d">
-        <v>2026-07-06T10:46:28.999Z</v>
+        <v>2026-07-06T10:47:50.000Z</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>INC000000148478</v>
+        <v>INC000000148483</v>
       </c>
       <c r="B227" s="1" t="d">
-        <v>2026-07-06T10:47:50.000Z</v>
+        <v>2026-07-06T10:46:26.000Z</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>INC000000148483</v>
+        <v>INC000000148391</v>
       </c>
       <c r="B228" s="1" t="d">
-        <v>2026-07-06T10:46:26.000Z</v>
+        <v>2026-07-06T10:46:33.000Z</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>INC000000148391</v>
+        <v>INC000000148617</v>
       </c>
       <c r="B229" s="1" t="d">
-        <v>2026-07-06T10:46:33.000Z</v>
+        <v>2026-06-23T13:06:23.000Z</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>INC000000148617</v>
+        <v>INC000000148567</v>
       </c>
       <c r="B230" s="1" t="d">
-        <v>2026-06-23T13:06:23.000Z</v>
+        <v>2026-06-23T20:51:36.000Z</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>INC000000148567</v>
+        <v>WO0000000299917</v>
       </c>
       <c r="B231" s="1" t="d">
-        <v>2026-06-23T20:51:36.000Z</v>
+        <v>2026-07-14T12:23:04.000Z</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>WO0000000299917</v>
+        <v>INC000000148835</v>
       </c>
       <c r="B232" s="1" t="d">
-        <v>2026-07-14T12:23:04.000Z</v>
+        <v>2026-07-06T10:46:35.000Z</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>INC000000148835</v>
+        <v>WO0000000300350</v>
       </c>
       <c r="B233" s="1" t="d">
-        <v>2026-07-06T10:46:35.000Z</v>
+        <v>2026-07-21T12:59:11.000Z</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>WO0000000300350</v>
+        <v>WO0000000300621</v>
       </c>
       <c r="B234" s="1" t="d">
-        <v>2026-07-21T12:59:11.000Z</v>
+        <v>2026-07-07T08:00:34.000Z</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>WO0000000300621</v>
+        <v>INC000000148932</v>
       </c>
       <c r="B235" s="1" t="d">
-        <v>2026-07-07T08:00:34.000Z</v>
+        <v>2026-06-26T20:05:39.000Z</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>INC000000148932</v>
+        <v>INC000000149029</v>
       </c>
       <c r="B236" s="1" t="d">
-        <v>2026-06-26T20:05:39.000Z</v>
+        <v>2026-07-10T14:37:50.000Z</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>INC000000149029</v>
+        <v>WO0000000300825</v>
       </c>
       <c r="B237" s="1" t="d">
-        <v>2026-07-10T14:37:50.000Z</v>
+        <v>2026-07-06T16:31:51.000Z</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>WO0000000300825</v>
+        <v>INC000000149054</v>
       </c>
       <c r="B238" s="1" t="d">
-        <v>2026-07-06T16:31:51.000Z</v>
+        <v>2026-06-25T12:46:56.999Z</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>INC000000149054</v>
+        <v>WO0000000301205</v>
       </c>
       <c r="B239" s="1" t="d">
-        <v>2026-06-25T12:46:56.999Z</v>
+        <v>2026-07-21T08:00:58.999Z</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>WO0000000301205</v>
+        <v>WO0000000298649</v>
       </c>
       <c r="B240" s="1" t="d">
-        <v>2026-07-21T08:00:58.999Z</v>
+        <v>2026-07-08T10:16:58.999Z</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>WO0000000298649</v>
+        <v>INC000000149262</v>
       </c>
       <c r="B241" s="1" t="d">
-        <v>2026-07-08T10:16:58.999Z</v>
+        <v>2026-07-06T10:46:38.000Z</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>INC000000149262</v>
+        <v>INC000000149363</v>
       </c>
       <c r="B242" s="1" t="d">
-        <v>2026-07-06T10:46:38.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>INC000000149363</v>
+        <v>INC000000149449</v>
       </c>
       <c r="B243" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-06-30T13:18:04.000Z</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>INC000000149449</v>
+        <v>INC000000149711</v>
       </c>
       <c r="B244" s="1" t="d">
-        <v>2026-06-30T13:18:04.000Z</v>
+        <v>2026-07-02T16:46:09.999Z</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>INC000000149711</v>
+        <v>INC000000149814</v>
       </c>
       <c r="B245" s="1" t="d">
-        <v>2026-07-02T16:46:09.999Z</v>
+        <v>2026-07-01T12:39:49.000Z</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>INC000000149814</v>
+        <v>WO0000000302574</v>
       </c>
       <c r="B246" s="1" t="d">
-        <v>2026-07-01T12:39:49.000Z</v>
+        <v>2026-07-10T13:08:33.999Z</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>WO0000000302574</v>
+        <v>INC000000149891</v>
       </c>
       <c r="B247" s="1" t="d">
-        <v>2026-07-10T13:08:33.999Z</v>
+        <v>2026-07-02T10:27:00.000Z</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>INC000000149891</v>
+        <v>INC000000149936</v>
       </c>
       <c r="B248" s="1" t="d">
-        <v>2026-07-02T10:27:00.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>INC000000149936</v>
+        <v>WO0000000303077</v>
       </c>
       <c r="B249" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-17T13:54:02.000Z</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>WO0000000303077</v>
+        <v>INC000000150054</v>
       </c>
       <c r="B250" s="1" t="d">
-        <v>2026-07-17T13:54:02.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>INC000000150054</v>
+        <v>WO0000000303223</v>
       </c>
       <c r="B251" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-10T09:44:01.000Z</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>WO0000000303223</v>
+        <v>INC000000149979</v>
       </c>
       <c r="B252" s="1" t="d">
-        <v>2026-07-10T09:44:01.000Z</v>
+        <v>2026-07-06T09:02:53.000Z</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>INC000000149979</v>
+        <v>INC000000149982</v>
       </c>
       <c r="B253" s="1" t="d">
-        <v>2026-07-06T09:02:53.000Z</v>
+        <v>2026-07-06T10:46:41.999Z</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>INC000000149982</v>
+        <v>INC000000149983</v>
       </c>
       <c r="B254" s="1" t="d">
-        <v>2026-07-06T10:46:41.999Z</v>
+        <v>2026-07-06T09:06:44.000Z</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>INC000000149983</v>
+        <v>WO0000000303232</v>
       </c>
       <c r="B255" s="1" t="d">
-        <v>2026-07-06T09:06:44.000Z</v>
+        <v>2026-07-17T17:20:56.999Z</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>WO0000000303232</v>
+        <v>INC000000150063</v>
       </c>
       <c r="B256" s="1" t="d">
-        <v>2026-07-17T17:20:56.999Z</v>
+        <v>2026-07-06T09:10:00.999Z</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>INC000000150063</v>
+        <v>INC000000149989</v>
       </c>
       <c r="B257" s="1" t="d">
-        <v>2026-07-06T09:10:00.999Z</v>
+        <v>2026-07-06T09:10:52.000Z</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>INC000000149989</v>
+        <v>WO0000000303319</v>
       </c>
       <c r="B258" s="1" t="d">
-        <v>2026-07-06T09:10:52.000Z</v>
+        <v>2026-07-07T09:11:18.000Z</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>WO0000000303319</v>
+        <v>INC000000150108</v>
       </c>
       <c r="B259" s="1" t="d">
-        <v>2026-07-07T09:11:18.000Z</v>
+        <v>2026-07-06T10:48:13.000Z</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>INC000000150108</v>
+        <v>INC000000150240</v>
       </c>
       <c r="B260" s="1" t="d">
-        <v>2026-07-06T10:48:13.000Z</v>
+        <v>2026-07-17T17:20:51.999Z</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>INC000000150240</v>
+        <v>INC000000150131</v>
       </c>
       <c r="B261" s="1" t="d">
-        <v>2026-07-17T17:20:51.999Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>INC000000150131</v>
+        <v>WO0000000303640</v>
       </c>
       <c r="B262" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T11:51:27.000Z</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>WO0000000303640</v>
+        <v>WO0000000303579</v>
       </c>
       <c r="B263" s="1" t="d">
-        <v>2026-07-15T11:51:27.000Z</v>
+        <v>2026-07-17T12:57:13.000Z</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>WO0000000303579</v>
+        <v>INC000000150158</v>
       </c>
       <c r="B264" s="1" t="d">
-        <v>2026-07-17T12:57:13.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>INC000000150158</v>
+        <v>WO0000000303803</v>
       </c>
       <c r="B265" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-17T14:43:11.000Z</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>WO0000000303803</v>
+        <v>INC000000150288</v>
       </c>
       <c r="B266" s="1" t="d">
-        <v>2026-07-17T14:43:11.000Z</v>
+        <v>2026-07-10T12:39:00.000Z</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>INC000000150288</v>
+        <v>INC000000150172</v>
       </c>
       <c r="B267" s="1" t="d">
-        <v>2026-07-10T12:39:00.000Z</v>
+        <v>2026-07-06T12:25:58.000Z</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>INC000000150172</v>
+        <v>WO0000000303781</v>
       </c>
       <c r="B268" s="1" t="d">
-        <v>2026-07-06T12:25:58.000Z</v>
+        <v>2026-07-10T09:46:00.000Z</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>WO0000000303781</v>
+        <v>WO0000000303791</v>
       </c>
       <c r="B269" s="1" t="d">
-        <v>2026-07-10T09:46:00.000Z</v>
+        <v>2026-07-22T10:17:11.000Z</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>WO0000000303791</v>
+        <v>INC000000150407</v>
       </c>
       <c r="B270" s="1" t="d">
-        <v>2026-07-15T12:32:15.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>INC000000150407</v>
+        <v>WO0000000304363</v>
       </c>
       <c r="B271" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-15T13:27:05.000Z</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>WO0000000304363</v>
+        <v>INC000000150521</v>
       </c>
       <c r="B272" s="1" t="d">
-        <v>2026-07-15T13:27:05.000Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>INC000000150521</v>
+        <v>INC000000150630</v>
       </c>
       <c r="B273" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-10T08:48:46.999Z</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>INC000000150630</v>
+        <v>INC000000150536</v>
       </c>
       <c r="B274" s="1" t="d">
-        <v>2026-07-10T08:48:46.999Z</v>
+        <v>2026-07-09T11:26:10.999Z</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>INC000000150536</v>
+        <v>WO0000000304551</v>
       </c>
       <c r="B275" s="1" t="d">
-        <v>2026-07-09T11:26:10.999Z</v>
+        <v>2026-07-15T16:39:18.000Z</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>WO0000000304551</v>
+        <v>WO0000000304865</v>
       </c>
       <c r="B276" s="1" t="d">
-        <v>2026-07-15T16:39:18.000Z</v>
+        <v>2026-07-16T14:19:57.000Z</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>WO0000000304865</v>
+        <v>WO0000000304881</v>
       </c>
       <c r="B277" s="1" t="d">
-        <v>2026-07-16T14:19:57.000Z</v>
+        <v>2026-07-16T14:54:34.000Z</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>WO0000000304881</v>
+        <v>WO0000000304977</v>
       </c>
       <c r="B278" s="1" t="d">
-        <v>2026-07-16T14:54:34.000Z</v>
+        <v>2026-07-22T08:01:10.000Z</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>WO0000000304977</v>
+        <v>INC000000150832</v>
       </c>
       <c r="B279" s="1" t="d">
-        <v>2026-07-22T08:01:10.000Z</v>
+        <v>2026-07-10T09:16:28.000Z</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>INC000000150832</v>
+        <v>INC000000150843</v>
       </c>
       <c r="B280" s="1" t="d">
-        <v>2026-07-10T09:16:28.000Z</v>
+        <v>2026-07-07T14:07:42.999Z</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>INC000000150843</v>
+        <v>INC000000150743</v>
       </c>
       <c r="B281" s="1" t="d">
-        <v>2026-07-07T14:07:42.999Z</v>
+        <v>2026-07-08T12:53:21.000Z</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>INC000000150743</v>
+        <v>INC000000150849</v>
       </c>
       <c r="B282" s="1" t="d">
-        <v>2026-07-08T12:53:21.000Z</v>
+        <v>2026-07-07T14:25:27.999Z</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>INC000000150849</v>
+        <v>INC000000150851</v>
       </c>
       <c r="B283" s="1" t="d">
-        <v>2026-07-07T14:25:27.999Z</v>
+        <v>2026-07-14T08:25:23.999Z</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>INC000000150851</v>
+        <v>WO0000000305077</v>
       </c>
       <c r="B284" s="1" t="d">
-        <v>2026-07-14T08:25:23.999Z</v>
+        <v>2026-07-16T15:27:35.999Z</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>WO0000000305077</v>
+        <v>WO0000000305701</v>
       </c>
       <c r="B285" s="1" t="d">
-        <v>2026-07-16T15:27:35.999Z</v>
+        <v>2026-07-17T12:26:34.000Z</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>WO0000000305701</v>
+        <v>WO0000000305706</v>
       </c>
       <c r="B286" s="1" t="d">
-        <v>2026-07-17T12:26:34.000Z</v>
+        <v>2026-07-17T12:32:44.000Z</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>WO0000000305706</v>
+        <v>WO0000000305880</v>
       </c>
       <c r="B287" s="1" t="d">
-        <v>2026-07-17T12:32:44.000Z</v>
+        <v>2026-07-21T06:23:37.000Z</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>WO0000000305880</v>
+        <v>WO0000000305897</v>
       </c>
       <c r="B288" s="1" t="d">
-        <v>2026-07-21T06:23:37.000Z</v>
+        <v>2026-07-17T16:35:20.000Z</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>WO0000000305897</v>
+        <v>WO0000000306041</v>
       </c>
       <c r="B289" s="1" t="d">
-        <v>2026-07-17T16:35:20.000Z</v>
+        <v>2026-07-15T08:16:13.999Z</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>WO0000000306041</v>
+        <v>WO0000000305998</v>
       </c>
       <c r="B290" s="1" t="d">
-        <v>2026-07-15T08:16:13.999Z</v>
+        <v>2026-07-10T12:10:19.000Z</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>WO0000000305998</v>
+        <v>INC000000151304</v>
       </c>
       <c r="B291" s="1" t="d">
-        <v>2026-07-10T12:10:19.000Z</v>
+        <v>2026-07-09T15:23:24.000Z</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>INC000000151304</v>
+        <v>INC000000151200</v>
       </c>
       <c r="B292" s="1" t="d">
-        <v>2026-07-09T15:23:24.000Z</v>
+        <v>2026-07-10T10:51:56.000Z</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>INC000000151200</v>
+        <v>WO0000000306433</v>
       </c>
       <c r="B293" s="1" t="d">
-        <v>2026-07-10T10:51:56.000Z</v>
+        <v>2026-07-16T16:04:33.999Z</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>WO0000000306433</v>
+        <v>WO0000000306374</v>
       </c>
       <c r="B294" s="1" t="d">
-        <v>2026-07-16T16:04:33.999Z</v>
+        <v>2026-07-10T13:36:36.000Z</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>WO0000000306374</v>
+        <v>WO0000000304733</v>
       </c>
       <c r="B295" s="1" t="d">
-        <v>2026-07-10T13:36:36.000Z</v>
+        <v>2026-07-15T10:28:05.999Z</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>WO0000000304733</v>
+        <v>INC000000135134</v>
       </c>
       <c r="B296" s="1" t="d">
-        <v>2026-07-15T10:28:05.999Z</v>
+        <v>2026-07-14T10:35:47.000Z</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>INC000000135134</v>
+        <v>INC000000136403</v>
       </c>
       <c r="B297" s="1" t="d">
-        <v>2026-07-14T10:35:47.000Z</v>
+        <v>2026-07-14T06:43:05.000Z</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>INC000000136403</v>
+        <v>INC000000138835</v>
       </c>
       <c r="B298" s="1" t="d">
-        <v>2026-07-14T06:43:05.000Z</v>
+        <v>2026-07-14T10:35:56.000Z</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>INC000000138835</v>
+        <v>INC000000139335</v>
       </c>
       <c r="B299" s="1" t="d">
-        <v>2026-07-14T10:35:56.000Z</v>
+        <v>2026-07-14T06:43:37.000Z</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>INC000000139335</v>
+        <v>INC000000139655</v>
       </c>
       <c r="B300" s="1" t="d">
-        <v>2026-07-14T06:43:37.000Z</v>
+        <v>2026-07-17T07:37:37.999Z</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>INC000000139655</v>
+        <v>INC000000139903</v>
       </c>
       <c r="B301" s="1" t="d">
-        <v>2026-07-17T07:37:37.999Z</v>
+        <v>2026-07-17T07:37:04.000Z</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>INC000000139903</v>
+        <v>WO0000000282199</v>
       </c>
       <c r="B302" s="1" t="d">
-        <v>2026-07-17T07:37:04.000Z</v>
+        <v>2026-07-14T15:02:42.000Z</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>WO0000000282199</v>
+        <v>INC000000140820</v>
       </c>
       <c r="B303" s="1" t="d">
-        <v>2026-07-14T15:02:42.000Z</v>
+        <v>2026-07-17T07:35:42.000Z</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>INC000000140820</v>
+        <v>INC000000140821</v>
       </c>
       <c r="B304" s="1" t="d">
-        <v>2026-07-17T07:35:42.000Z</v>
+        <v>2026-07-17T07:34:57.000Z</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>INC000000140821</v>
+        <v>INC000000141515</v>
       </c>
       <c r="B305" s="1" t="d">
-        <v>2026-07-17T07:34:57.000Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>INC000000141515</v>
+        <v>INC000000142421</v>
       </c>
       <c r="B306" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-17T07:33:48.000Z</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>INC000000142421</v>
+        <v>INC000000142515</v>
       </c>
       <c r="B307" s="1" t="d">
-        <v>2026-07-17T07:33:48.000Z</v>
+        <v>2026-07-17T07:33:05.000Z</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>INC000000142515</v>
+        <v>WO0000000288110</v>
       </c>
       <c r="B308" s="1" t="d">
-        <v>2026-07-17T07:33:05.000Z</v>
+        <v>2026-07-17T07:47:10.000Z</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>WO0000000288110</v>
+        <v>INC000000143401</v>
       </c>
       <c r="B309" s="1" t="d">
-        <v>2026-07-17T07:47:10.000Z</v>
+        <v>2026-07-17T07:32:06.000Z</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>INC000000143401</v>
+        <v>WO0000000292826</v>
       </c>
       <c r="B310" s="1" t="d">
-        <v>2026-07-17T07:32:06.000Z</v>
+        <v>2026-07-17T07:30:34.000Z</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>WO0000000292826</v>
+        <v>WO0000000295598</v>
       </c>
       <c r="B311" s="1" t="d">
-        <v>2026-07-17T07:30:34.000Z</v>
+        <v>2026-07-17T10:51:51.999Z</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>WO0000000293293</v>
+        <v>INC000000146720</v>
       </c>
       <c r="B312" s="1" t="d">
-        <v>2026-07-15T08:29:08.000Z</v>
+        <v>2026-07-16T08:34:09.000Z</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>INC000000146720</v>
+        <v>WO0000000295688</v>
       </c>
       <c r="B313" s="1" t="d">
-        <v>2026-07-16T08:34:09.000Z</v>
+        <v>2026-07-16T09:17:24.999Z</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>WO0000000295688</v>
+        <v>WO0000000295716</v>
       </c>
       <c r="B314" s="1" t="d">
-        <v>2026-07-16T09:17:24.999Z</v>
+        <v>2026-07-16T11:47:42.999Z</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>WO0000000295716</v>
+        <v>WO0000000295975</v>
       </c>
       <c r="B315" s="1" t="d">
-        <v>2026-07-16T11:47:42.999Z</v>
+        <v>2026-07-17T07:46:27.000Z</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>WO0000000295975</v>
+        <v>INC000000146886</v>
       </c>
       <c r="B316" s="1" t="d">
-        <v>2026-07-17T07:46:27.000Z</v>
+        <v>2026-07-16T13:10:02.999Z</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>INC000000146886</v>
+        <v>WO0000000296722</v>
       </c>
       <c r="B317" s="1" t="d">
-        <v>2026-07-16T13:10:02.999Z</v>
+        <v>2026-07-17T07:44:32.000Z</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>WO0000000296722</v>
+        <v>WO0000000296723</v>
       </c>
       <c r="B318" s="1" t="d">
-        <v>2026-07-17T07:44:32.000Z</v>
+        <v>2026-07-17T07:43:42.999Z</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>WO0000000296723</v>
+        <v>INC000000147260</v>
       </c>
       <c r="B319" s="1" t="d">
-        <v>2026-07-17T07:43:42.999Z</v>
+        <v>2026-07-14T08:08:06.000Z</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>INC000000147260</v>
+        <v>WO0000000297151</v>
       </c>
       <c r="B320" s="1" t="d">
-        <v>2026-07-14T08:08:06.000Z</v>
+        <v>2026-07-17T07:42:36.000Z</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>WO0000000297151</v>
+        <v>WO0000000297156</v>
       </c>
       <c r="B321" s="1" t="d">
-        <v>2026-07-17T07:42:36.000Z</v>
+        <v>2026-07-17T07:41:50.000Z</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>WO0000000297156</v>
+        <v>WO0000000297160</v>
       </c>
       <c r="B322" s="1" t="d">
-        <v>2026-07-17T07:41:50.000Z</v>
+        <v>2026-07-17T07:40:23.999Z</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>WO0000000297160</v>
+        <v>INC000000147613</v>
       </c>
       <c r="B323" s="1" t="d">
-        <v>2026-07-17T07:40:23.999Z</v>
+        <v>2026-07-22T10:54:42.999Z</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>INC000000147613</v>
+        <v>WO0000000301822</v>
       </c>
       <c r="B324" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-21T09:48:14.000Z</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>WO0000000301822</v>
+        <v>INC000000149760</v>
       </c>
       <c r="B325" s="1" t="d">
-        <v>2026-07-21T09:48:14.000Z</v>
+        <v>2026-07-17T07:52:31.999Z</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>INC000000149760</v>
+        <v>INC000000149860</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2026-07-17T07:52:31.999Z</v>
+        <v>2026-07-16T15:59:24.000Z</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>INC000000149860</v>
+        <v>INC000000150036</v>
       </c>
       <c r="B327" s="1" t="d">
-        <v>2026-07-16T15:59:24.000Z</v>
+        <v>2026-07-16T07:28:43.999Z</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>INC000000150036</v>
+        <v>WO0000000303120</v>
       </c>
       <c r="B328" s="1" t="d">
-        <v>2026-07-16T07:28:43.999Z</v>
+        <v>2026-07-17T07:38:45.000Z</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>WO0000000303120</v>
+        <v>INC000000149964</v>
       </c>
       <c r="B329" s="1" t="d">
-        <v>2026-07-17T07:38:45.000Z</v>
+        <v>2026-07-15T15:21:53.000Z</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>INC000000149964</v>
+        <v>WO0000000303471</v>
       </c>
       <c r="B330" s="1" t="d">
-        <v>2026-07-15T15:21:53.000Z</v>
+        <v>2026-07-16T14:24:05.000Z</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>WO0000000303471</v>
+        <v>INC000000150197</v>
       </c>
       <c r="B331" s="1" t="d">
-        <v>2026-07-16T14:24:05.000Z</v>
+        <v>2026-07-21T14:40:04.000Z</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>INC000000150197</v>
+        <v>WO0000000304437</v>
       </c>
       <c r="B332" s="1" t="d">
-        <v>2026-07-21T14:40:04.000Z</v>
+        <v>2026-07-16T12:22:04.999Z</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>WO0000000304256</v>
+        <v>WO0000000304614</v>
       </c>
       <c r="B333" s="1" t="d">
-        <v>2026-07-16T12:20:08.000Z</v>
+        <v>2026-07-16T12:25:00.000Z</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>WO0000000304437</v>
+        <v>INC000000150732</v>
       </c>
       <c r="B334" s="1" t="d">
-        <v>2026-07-16T12:22:04.999Z</v>
+        <v>2026-07-16T08:27:41.000Z</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>WO0000000304614</v>
+        <v>WO0000000305312</v>
       </c>
       <c r="B335" s="1" t="d">
-        <v>2026-07-16T12:25:00.000Z</v>
+        <v>2026-07-15T11:26:08.000Z</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>INC000000150732</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B336" s="1" t="d">
-        <v>2026-07-16T08:27:41.000Z</v>
+        <v>2026-07-22T00:04:59.000Z</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>WO0000000305312</v>
+        <v>INC000000150882</v>
       </c>
       <c r="B337" s="1" t="d">
-        <v>2026-07-15T11:26:08.000Z</v>
+        <v>2026-07-15T10:45:04.000Z</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000151036</v>
       </c>
       <c r="B338" s="1" t="d">
-        <v>2026-07-22T00:04:59.000Z</v>
+        <v>2026-07-16T16:01:20.999Z</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>INC000000150882</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B339" s="1" t="d">
-        <v>2026-07-15T10:45:04.000Z</v>
+        <v>2026-07-16T10:45:43.999Z</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>INC000000151036</v>
+        <v>INC000000150958</v>
       </c>
       <c r="B340" s="1" t="d">
-        <v>2026-07-16T16:01:20.999Z</v>
+        <v>2026-07-17T07:47:57.999Z</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>WO0000000305566</v>
+        <v>INC000000151204</v>
       </c>
       <c r="B341" s="1" t="d">
-        <v>2026-07-16T10:45:43.999Z</v>
+        <v>2026-07-14T12:46:36.000Z</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>INC000000150958</v>
+        <v>WO0000000305944</v>
       </c>
       <c r="B342" s="1" t="d">
-        <v>2026-07-17T07:47:57.999Z</v>
+        <v>2026-07-14T12:04:16.999Z</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>INC000000151204</v>
+        <v>INC000000151151</v>
       </c>
       <c r="B343" s="1" t="d">
-        <v>2026-07-14T12:46:36.000Z</v>
+        <v>2026-07-16T08:22:24.000Z</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>WO0000000305944</v>
+        <v>WO0000000306290</v>
       </c>
       <c r="B344" s="1" t="d">
-        <v>2026-07-14T12:04:16.999Z</v>
+        <v>2026-07-14T16:17:28.999Z</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>INC000000151151</v>
+        <v>INC000000151311</v>
       </c>
       <c r="B345" s="1" t="d">
-        <v>2026-07-16T08:22:24.000Z</v>
+        <v>2026-07-16T09:35:09.000Z</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>WO0000000306290</v>
+        <v>INC000000151313</v>
       </c>
       <c r="B346" s="1" t="d">
-        <v>2026-07-14T16:17:28.999Z</v>
+        <v>2026-07-17T09:19:01.000Z</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>INC000000151311</v>
+        <v>WO0000000306439</v>
       </c>
       <c r="B347" s="1" t="d">
-        <v>2026-07-16T09:35:09.000Z</v>
+        <v>2026-07-14T16:14:53.000Z</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>INC000000151313</v>
+        <v>INC000000151466</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2026-07-17T09:19:01.000Z</v>
+        <v>2026-07-14T15:33:23.000Z</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>WO0000000306439</v>
+        <v>INC000000151499</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2026-07-14T16:14:53.000Z</v>
+        <v>2026-07-17T12:51:08.999Z</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>INC000000151466</v>
+        <v>INC000000151525</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2026-07-14T15:33:23.000Z</v>
+        <v>2026-07-15T11:08:12.999Z</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>INC000000151499</v>
+        <v>WO0000000307033</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2026-07-17T12:51:08.999Z</v>
+        <v>2026-07-22T10:17:11.000Z</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>INC000000151525</v>
+        <v>WO0000000307106</v>
       </c>
       <c r="B352" s="1" t="d">
-        <v>2026-07-15T11:08:12.999Z</v>
+        <v>2026-07-11T16:22:34.000Z</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>WO0000000307033</v>
+        <v>WO0000000307093</v>
       </c>
       <c r="B353" s="1" t="d">
-        <v>2026-07-17T12:30:37.000Z</v>
+        <v>2026-07-14T07:58:26.000Z</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>WO0000000307106</v>
+        <v>WO0000000307237</v>
       </c>
       <c r="B354" s="1" t="d">
-        <v>2026-07-11T16:22:34.000Z</v>
+        <v>2026-07-14T08:00:43.999Z</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>WO0000000307093</v>
+        <v>WO0000000307368</v>
       </c>
       <c r="B355" s="1" t="d">
-        <v>2026-07-14T07:58:26.000Z</v>
+        <v>2026-07-21T09:55:05.000Z</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>WO0000000307237</v>
+        <v>WO0000000307397</v>
       </c>
       <c r="B356" s="1" t="d">
-        <v>2026-07-14T08:00:43.999Z</v>
+        <v>2026-07-15T09:56:22.000Z</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>WO0000000307368</v>
+        <v>WO0000000307513</v>
       </c>
       <c r="B357" s="1" t="d">
-        <v>2026-07-21T09:55:05.000Z</v>
+        <v>2026-07-22T11:04:14.000Z</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>WO0000000307397</v>
+        <v>INC000000151987</v>
       </c>
       <c r="B358" s="1" t="d">
-        <v>2026-07-15T09:56:22.000Z</v>
+        <v>2026-07-16T11:05:28.000Z</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>WO0000000307513</v>
+        <v>WO0000000307471</v>
       </c>
       <c r="B359" s="1" t="d">
-        <v>2026-07-21T10:03:23.000Z</v>
+        <v>2026-07-14T11:13:57.999Z</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>INC000000151987</v>
+        <v>WO0000000307482</v>
       </c>
       <c r="B360" s="1" t="d">
-        <v>2026-07-16T11:05:28.000Z</v>
+        <v>2026-07-14T13:21:57.000Z</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>WO0000000307471</v>
+        <v>INC000000151994</v>
       </c>
       <c r="B361" s="1" t="d">
-        <v>2026-07-14T11:13:57.999Z</v>
+        <v>2026-07-16T07:51:15.000Z</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>WO0000000307482</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B362" s="1" t="d">
-        <v>2026-07-14T13:21:57.000Z</v>
+        <v>2026-07-17T07:22:20.000Z</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>INC000000151994</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B363" s="1" t="d">
-        <v>2026-07-16T07:51:15.000Z</v>
+        <v>2026-07-22T00:05:18.999Z</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000152040</v>
       </c>
       <c r="B364" s="1" t="d">
-        <v>2026-07-17T07:22:20.000Z</v>
+        <v>2026-07-14T15:45:22.000Z</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000307592</v>
       </c>
       <c r="B365" s="1" t="d">
-        <v>2026-07-22T00:05:18.999Z</v>
+        <v>2026-07-17T13:37:57.000Z</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>INC000000152040</v>
+        <v>INC000000152117</v>
       </c>
       <c r="B366" s="1" t="d">
-        <v>2026-07-14T15:45:22.000Z</v>
+        <v>2026-07-15T14:11:25.000Z</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>WO0000000307592</v>
+        <v>INC000000152124</v>
       </c>
       <c r="B367" s="1" t="d">
-        <v>2026-07-17T13:37:57.000Z</v>
+        <v>2026-07-15T14:11:57.000Z</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>INC000000152117</v>
+        <v>INC000000152132</v>
       </c>
       <c r="B368" s="1" t="d">
-        <v>2026-07-15T14:11:25.000Z</v>
+        <v>2026-07-15T14:13:17.000Z</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>INC000000152124</v>
+        <v>INC000000152134</v>
       </c>
       <c r="B369" s="1" t="d">
-        <v>2026-07-15T14:11:57.000Z</v>
+        <v>2026-07-15T14:13:50.000Z</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>INC000000152132</v>
+        <v>INC000000152138</v>
       </c>
       <c r="B370" s="1" t="d">
-        <v>2026-07-15T14:13:17.000Z</v>
+        <v>2026-07-15T14:16:43.999Z</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>INC000000152134</v>
+        <v>INC000000152139</v>
       </c>
       <c r="B371" s="1" t="d">
-        <v>2026-07-15T14:13:50.000Z</v>
+        <v>2026-07-15T14:17:19.000Z</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>INC000000152138</v>
+        <v>INC000000152155</v>
       </c>
       <c r="B372" s="1" t="d">
-        <v>2026-07-15T14:16:43.999Z</v>
+        <v>2026-07-15T16:57:39.000Z</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>INC000000152139</v>
+        <v>INC000000152156</v>
       </c>
       <c r="B373" s="1" t="d">
-        <v>2026-07-15T14:17:19.000Z</v>
+        <v>2026-07-15T14:18:27.000Z</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>INC000000152155</v>
+        <v>INC000000152158</v>
       </c>
       <c r="B374" s="1" t="d">
-        <v>2026-07-15T16:57:39.000Z</v>
+        <v>2026-07-15T14:19:58.000Z</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>INC000000152156</v>
+        <v>INC000000152073</v>
       </c>
       <c r="B375" s="1" t="d">
-        <v>2026-07-15T14:18:27.000Z</v>
+        <v>2026-07-16T09:23:53.000Z</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>INC000000152158</v>
+        <v>WO0000000307769</v>
       </c>
       <c r="B376" s="1" t="d">
-        <v>2026-07-15T14:19:58.000Z</v>
+        <v>2026-07-14T17:17:47.000Z</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>INC000000152073</v>
+        <v>INC000000152212</v>
       </c>
       <c r="B377" s="1" t="d">
-        <v>2026-07-16T09:23:53.000Z</v>
+        <v>2026-07-17T11:31:35.000Z</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>WO0000000307834</v>
+        <v>INC000000152320</v>
       </c>
       <c r="B378" s="1" t="d">
-        <v>2026-07-21T08:01:01.000Z</v>
+        <v>2026-07-15T10:29:52.000Z</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>WO0000000307769</v>
+        <v>INC000000152214</v>
       </c>
       <c r="B379" s="1" t="d">
-        <v>2026-07-14T17:17:47.000Z</v>
+        <v>2026-07-17T10:47:42.000Z</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>WO0000000307852</v>
+        <v>WO0000000308052</v>
       </c>
       <c r="B380" s="1" t="d">
-        <v>2026-07-21T14:46:18.000Z</v>
+        <v>2026-07-21T16:25:50.000Z</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>INC000000152320</v>
+        <v>WO0000000307981</v>
       </c>
       <c r="B381" s="1" t="d">
-        <v>2026-07-15T10:29:52.000Z</v>
+        <v>2026-07-21T09:32:12.999Z</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>WO0000000307976</v>
+        <v>WO0000000307984</v>
       </c>
       <c r="B382" s="1" t="d">
-        <v>2026-07-21T16:12:43.000Z</v>
+        <v>2026-07-21T16:22:55.000Z</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>WO0000000307981</v>
+        <v>INC000000152339</v>
       </c>
       <c r="B383" s="1" t="d">
-        <v>2026-07-21T09:32:12.999Z</v>
+        <v>2026-07-16T08:34:04.000Z</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>WO0000000307984</v>
+        <v>WO0000000308206</v>
       </c>
       <c r="B384" s="1" t="d">
-        <v>2026-07-21T16:22:55.000Z</v>
+        <v>2026-07-22T09:05:30.000Z</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>INC000000152339</v>
+        <v>WO0000000308218</v>
       </c>
       <c r="B385" s="1" t="d">
-        <v>2026-07-16T08:34:04.000Z</v>
+        <v>2026-07-22T09:07:32.000Z</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>WO0000000308206</v>
+        <v>WO0000000308157</v>
       </c>
       <c r="B386" s="1" t="d">
-        <v>2026-07-22T09:05:30.000Z</v>
+        <v>2026-07-21T11:40:53.000Z</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>WO0000000308218</v>
+        <v>WO0000000308163</v>
       </c>
       <c r="B387" s="1" t="d">
-        <v>2026-07-22T09:07:32.000Z</v>
+        <v>2026-07-16T09:05:24.000Z</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>WO0000000308157</v>
+        <v>INC000000152358</v>
       </c>
       <c r="B388" s="1" t="d">
-        <v>2026-07-21T11:40:53.000Z</v>
+        <v>2026-07-16T09:12:05.999Z</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>WO0000000308163</v>
+        <v>INC000000152369</v>
       </c>
       <c r="B389" s="1" t="d">
-        <v>2026-07-16T09:05:24.000Z</v>
+        <v>2026-07-17T10:42:03.000Z</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>INC000000152358</v>
+        <v>WO0000000308269</v>
       </c>
       <c r="B390" s="1" t="d">
-        <v>2026-07-16T09:12:05.999Z</v>
+        <v>2026-07-22T11:34:48.000Z</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>WO0000000308269</v>
+        <v>WO0000000308284</v>
       </c>
       <c r="B391" s="1" t="d">
-        <v>2026-07-21T09:19:51.000Z</v>
+        <v>2026-07-21T21:27:56.999Z</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>WO0000000308284</v>
+        <v>INC000000152378</v>
       </c>
       <c r="B392" s="1" t="d">
-        <v>2026-07-21T21:27:56.999Z</v>
+        <v>2026-07-17T09:05:30.000Z</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>INC000000152378</v>
+        <v>WO0000000308340</v>
       </c>
       <c r="B393" s="1" t="d">
-        <v>2026-07-17T09:05:30.000Z</v>
+        <v>2026-07-16T09:24:24.999Z</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>WO0000000308340</v>
+        <v>WO0000000308416</v>
       </c>
       <c r="B394" s="1" t="d">
-        <v>2026-07-16T09:24:24.999Z</v>
+        <v>2026-07-16T09:47:42.999Z</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>WO0000000308416</v>
+        <v>WO0000000308442</v>
       </c>
       <c r="B395" s="1" t="d">
-        <v>2026-07-16T09:47:42.999Z</v>
+        <v>2026-07-21T15:41:52.999Z</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>WO0000000308442</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B396" s="1" t="d">
-        <v>2026-07-21T15:41:52.999Z</v>
+        <v>2026-07-16T10:44:20.999Z</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308360</v>
       </c>
       <c r="B397" s="1" t="d">
-        <v>2026-07-16T10:44:20.999Z</v>
+        <v>2026-07-16T12:54:40.000Z</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>WO0000000308360</v>
+        <v>INC000000152389</v>
       </c>
       <c r="B398" s="1" t="d">
-        <v>2026-07-16T12:54:40.000Z</v>
+        <v>2026-07-17T10:53:19.000Z</v>
       </c>
     </row>
     <row r="399">
@@ -3598,7 +3598,7 @@
         <v>WO0000000308461</v>
       </c>
       <c r="B400" s="1" t="d">
-        <v>2026-07-21T09:25:59.000Z</v>
+        <v>2026-07-22T10:25:21.000Z</v>
       </c>
     </row>
     <row r="401">
@@ -3643,42 +3643,42 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>WO0000000308552</v>
+        <v>INC000000152517</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2026-07-16T09:20:55.000Z</v>
+        <v>2026-07-17T10:21:00.000Z</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>WO0000000308648</v>
+        <v>WO0000000308552</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2026-07-21T11:10:08.000Z</v>
+        <v>2026-07-16T09:20:55.000Z</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>WO0000000304755</v>
+        <v>WO0000000308648</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2026-07-21T11:24:28.999Z</v>
+        <v>2026-07-21T11:10:08.000Z</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>WO0000000308577</v>
+        <v>WO0000000304755</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2026-07-22T09:40:25.000Z</v>
+        <v>2026-07-21T11:24:28.999Z</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>WO0000000308662</v>
+        <v>WO0000000308577</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2026-07-21T16:24:57.000Z</v>
+        <v>2026-07-22T09:40:25.000Z</v>
       </c>
     </row>
     <row r="411">
@@ -3723,106 +3723,106 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>WO0000000308696</v>
+        <v>WO0000000308695</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2026-07-21T12:28:21.000Z</v>
+        <v>2026-07-21T15:02:42.000Z</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>WO0000000308695</v>
+        <v>INC000000152556</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2026-07-21T15:02:42.000Z</v>
+        <v>2026-07-17T09:26:01.000Z</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>INC000000152556</v>
+        <v>WO0000000308801</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2026-07-17T09:26:01.000Z</v>
+        <v>2026-07-21T15:10:53.000Z</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>WO0000000308801</v>
+        <v>WO0000000308715</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2026-07-21T15:10:53.000Z</v>
+        <v>2026-07-16T10:42:31.999Z</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>WO0000000308715</v>
+        <v>WO0000000308718</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2026-07-16T10:42:31.999Z</v>
+        <v>2026-07-21T15:17:00.999Z</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>WO0000000308717</v>
+        <v>WO0000000308809</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2026-07-21T10:45:16.999Z</v>
+        <v>2026-07-16T11:14:01.000Z</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>WO0000000308718</v>
+        <v>WO0000000308751</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2026-07-21T15:17:00.999Z</v>
+        <v>2026-07-21T16:02:36.000Z</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>WO0000000308809</v>
+        <v>WO0000000308754</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2026-07-16T11:14:01.000Z</v>
+        <v>2026-07-21T16:27:01.999Z</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>WO0000000308751</v>
+        <v>WO0000000308757</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2026-07-21T16:02:36.000Z</v>
+        <v>2026-07-16T11:43:44.000Z</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>WO0000000308754</v>
+        <v>INC000000152586</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2026-07-21T16:27:01.999Z</v>
+        <v>2026-07-17T10:46:28.000Z</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>WO0000000308757</v>
+        <v>WO0000000308873</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2026-07-16T11:43:44.000Z</v>
+        <v>2026-07-22T08:44:17.000Z</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>WO0000000308873</v>
+        <v>WO0000000308794</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2026-07-22T08:44:17.000Z</v>
+        <v>2026-07-22T11:07:53.000Z</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>WO0000000308794</v>
+        <v>INC000000152591</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2026-07-22T09:05:30.000Z</v>
+        <v>2026-07-17T11:00:29.999Z</v>
       </c>
     </row>
     <row r="429">
@@ -3846,7 +3846,7 @@
         <v>WO0000000308926</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2026-07-21T11:31:06.000Z</v>
+        <v>2026-07-22T11:10:02.000Z</v>
       </c>
     </row>
     <row r="432">
@@ -3854,7 +3854,7 @@
         <v>WO0000000309002</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2026-07-16T15:07:58.000Z</v>
+        <v>2026-07-22T10:35:37.000Z</v>
       </c>
     </row>
     <row r="433">
@@ -3862,7 +3862,7 @@
         <v>WO0000000309011</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2026-07-21T11:40:57.000Z</v>
+        <v>2026-07-22T10:37:37.999Z</v>
       </c>
     </row>
     <row r="434">
@@ -3870,7 +3870,7 @@
         <v>WO0000000308938</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2026-07-16T15:31:18.000Z</v>
+        <v>2026-07-22T11:00:07.999Z</v>
       </c>
     </row>
     <row r="435">
@@ -3886,199 +3886,199 @@
         <v>WO0000000309025</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2026-07-16T15:47:35.000Z</v>
+        <v>2026-07-22T11:18:29.000Z</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>WO0000000309031</v>
+        <v>WO0000000309036</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2026-07-22T09:07:32.000Z</v>
+        <v>2026-07-22T11:30:45.000Z</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>WO0000000309036</v>
+        <v>INC000000152628</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2026-07-16T16:05:14.000Z</v>
+        <v>2026-07-17T10:44:38.000Z</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>WO0000000309039</v>
+        <v>WO0000000309041</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2026-07-22T09:20:00.000Z</v>
+        <v>2026-07-16T16:17:09.000Z</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>WO0000000309041</v>
+        <v>WO0000000308966</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2026-07-16T16:17:09.000Z</v>
+        <v>2026-07-16T16:20:56.000Z</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>WO0000000308966</v>
+        <v>WO0000000309045</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2026-07-16T16:20:56.000Z</v>
+        <v>2026-07-16T16:26:50.000Z</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>WO0000000309044</v>
+        <v>WO0000000309046</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2026-07-22T09:42:27.000Z</v>
+        <v>2026-07-22T09:48:32.000Z</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>WO0000000309045</v>
+        <v>WO0000000308975</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2026-07-16T16:26:50.000Z</v>
+        <v>2026-07-22T09:58:42.000Z</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>WO0000000309046</v>
+        <v>WO0000000309050</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2026-07-22T09:48:32.000Z</v>
+        <v>2026-07-16T16:47:00.999Z</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>WO0000000308975</v>
+        <v>WO0000000308987</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2026-07-22T09:58:42.000Z</v>
+        <v>2026-07-22T10:17:11.000Z</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>WO0000000309050</v>
+        <v>WO0000000309073</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2026-07-16T16:47:00.999Z</v>
+        <v>2026-07-22T08:01:07.999Z</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>WO0000000308987</v>
+        <v>WO0000000309074</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-22T10:17:11.000Z</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>WO0000000309073</v>
+        <v>WO0000000309077</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2026-07-22T08:01:07.999Z</v>
+        <v>2026-07-17T07:39:53.000Z</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>WO0000000309074</v>
+        <v>WO0000000309079</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-17T07:46:49.000Z</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>WO0000000309077</v>
+        <v>WO0000000308996</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2026-07-17T07:39:53.000Z</v>
+        <v>2026-07-17T08:00:37.000Z</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>WO0000000309079</v>
+        <v>WO0000000308997</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2026-07-17T07:46:49.000Z</v>
+        <v>2026-07-17T08:06:08.999Z</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WO0000000308996</v>
+        <v>WO0000000308999</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2026-07-17T08:00:37.000Z</v>
+        <v>2026-07-22T10:40:21.000Z</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WO0000000308997</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2026-07-17T08:06:08.999Z</v>
+        <v>2026-07-17T11:45:12.000Z</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>WO0000000308999</v>
+        <v>INC000000152733</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2026-07-21T12:30:25.000Z</v>
+        <v>2026-07-22T10:00:42.999Z</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309207</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2026-07-17T11:45:12.000Z</v>
+        <v>2026-07-22T10:23:19.000Z</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>INC000000152733</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2026-07-22T10:00:42.999Z</v>
+        <v>2026-07-22T10:58:06.000Z</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>WO0000000309207</v>
+        <v>WO0000000309154</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2026-07-21T16:29:08.999Z</v>
+        <v>2026-07-22T11:10:21.000Z</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>WO0000000309154</v>
+        <v>WO0000000309232</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2026-07-21T13:25:40.000Z</v>
+        <v>2026-07-22T09:13:49.000Z</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>WO0000000309232</v>
+        <v>WO0000000309235</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2026-07-22T09:13:49.000Z</v>
+        <v>2026-07-17T11:10:25.000Z</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>WO0000000309235</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2026-07-17T11:10:25.000Z</v>
+        <v>2026-07-17T11:14:23.000Z</v>
       </c>
     </row>
     <row r="461">
@@ -4086,727 +4086,727 @@
         <v>WO0000000309164</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2026-07-21T13:50:33.000Z</v>
+        <v>2026-07-22T11:36:50.999Z</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>WO0000000309241</v>
+        <v>WO0000000309168</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2026-07-21T13:58:39.999Z</v>
+        <v>2026-07-21T16:31:56.000Z</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>WO0000000309168</v>
+        <v>WO0000000309170</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2026-07-21T16:31:56.000Z</v>
+        <v>2026-07-22T11:53:12.000Z</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>WO0000000309170</v>
+        <v>WO0000000309183</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-21T14:33:58.000Z</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>WO0000000309172</v>
+        <v>WO0000000309256</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2026-07-21T14:09:08.000Z</v>
+        <v>2026-07-21T11:58:05.000Z</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>WO0000000309254</v>
+        <v>WO0000000309258</v>
       </c>
       <